--- a/data/ENV.MI.xlsx
+++ b/data/ENV.MI.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18965244293213</t>
+    <t xml:space="preserve">2.18965220451355</t>
   </si>
   <si>
     <t xml:space="preserve">ENV.MI</t>
@@ -50,94 +50,94 @@
     <t xml:space="preserve">2.1447126865387</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16175866127014</t>
+    <t xml:space="preserve">2.1617591381073</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03778696060181</t>
+    <t xml:space="preserve">2.03778719902039</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08272695541382</t>
+    <t xml:space="preserve">2.08272647857666</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05328369140625</t>
+    <t xml:space="preserve">2.05328345298767</t>
   </si>
   <si>
     <t xml:space="preserve">2.03623747825623</t>
   </si>
   <si>
-    <t xml:space="preserve">1.968052983284</t>
+    <t xml:space="preserve">1.96805274486542</t>
   </si>
   <si>
     <t xml:space="preserve">1.96030461788177</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89831864833832</t>
+    <t xml:space="preserve">1.89831852912903</t>
   </si>
   <si>
-    <t xml:space="preserve">1.881272315979</t>
+    <t xml:space="preserve">1.88127243518829</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96340394020081</t>
+    <t xml:space="preserve">1.96340382099152</t>
   </si>
   <si>
     <t xml:space="preserve">1.98354911804199</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01299262046814</t>
+    <t xml:space="preserve">2.01299238204956</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93551015853882</t>
+    <t xml:space="preserve">1.93551051616669</t>
   </si>
   <si>
     <t xml:space="preserve">1.93705987930298</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91381537914276</t>
+    <t xml:space="preserve">1.91381514072418</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91071605682373</t>
+    <t xml:space="preserve">1.91071617603302</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86577618122101</t>
+    <t xml:space="preserve">1.86577594280243</t>
   </si>
   <si>
     <t xml:space="preserve">1.89212000370026</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85182917118073</t>
+    <t xml:space="preserve">1.85182929039001</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93396055698395</t>
+    <t xml:space="preserve">1.93396067619324</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86732590198517</t>
+    <t xml:space="preserve">1.86732566356659</t>
   </si>
   <si>
     <t xml:space="preserve">1.88902056217194</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98664820194244</t>
+    <t xml:space="preserve">1.98664855957031</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11526918411255</t>
+    <t xml:space="preserve">2.11526894569397</t>
   </si>
   <si>
     <t xml:space="preserve">2.18500375747681</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20824837684631</t>
+    <t xml:space="preserve">2.20824813842773</t>
   </si>
   <si>
     <t xml:space="preserve">2.16950702667236</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08427667617798</t>
+    <t xml:space="preserve">2.0842764377594</t>
   </si>
   <si>
     <t xml:space="preserve">2.01454210281372</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0052444934845</t>
+    <t xml:space="preserve">2.00524425506592</t>
   </si>
   <si>
     <t xml:space="preserve">2.14626240730286</t>
@@ -146,10 +146,10 @@
     <t xml:space="preserve">2.22219514846802</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32447171211243</t>
+    <t xml:space="preserve">2.32447195053101</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20049977302551</t>
+    <t xml:space="preserve">2.20049953460693</t>
   </si>
   <si>
     <t xml:space="preserve">2.27178382873535</t>
@@ -176,103 +176,103 @@
     <t xml:space="preserve">2.43139743804932</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4499933719635</t>
+    <t xml:space="preserve">2.44999313354492</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38490843772888</t>
+    <t xml:space="preserve">2.3849081993103</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3616635799408</t>
+    <t xml:space="preserve">2.36166381835938</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36321258544922</t>
+    <t xml:space="preserve">2.3632128238678</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31982326507568</t>
+    <t xml:space="preserve">2.31982278823853</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35236549377441</t>
+    <t xml:space="preserve">2.35236525535583</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26868462562561</t>
+    <t xml:space="preserve">2.26868438720703</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32292199134827</t>
+    <t xml:space="preserve">2.32292222976685</t>
   </si>
   <si>
     <t xml:space="preserve">2.33531928062439</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33996844291687</t>
+    <t xml:space="preserve">2.33996796607971</t>
   </si>
   <si>
     <t xml:space="preserve">2.3105251789093</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28573107719421</t>
+    <t xml:space="preserve">2.28573083877563</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25473737716675</t>
+    <t xml:space="preserve">2.25473833084106</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29037952423096</t>
+    <t xml:space="preserve">2.29038000106812</t>
   </si>
   <si>
     <t xml:space="preserve">2.27488327026367</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2314932346344</t>
+    <t xml:space="preserve">2.23149299621582</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07497835159302</t>
+    <t xml:space="preserve">2.07497882843018</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00834369659424</t>
+    <t xml:space="preserve">2.00834345817566</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03468751907349</t>
+    <t xml:space="preserve">2.03468775749207</t>
   </si>
   <si>
     <t xml:space="preserve">2.02229046821594</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97580099105835</t>
+    <t xml:space="preserve">1.97580087184906</t>
   </si>
   <si>
     <t xml:space="preserve">1.919806599617</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88216352462769</t>
+    <t xml:space="preserve">1.88216364383698</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00136709213257</t>
+    <t xml:space="preserve">2.00136733055115</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96058690547943</t>
+    <t xml:space="preserve">1.96058702468872</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90255355834961</t>
+    <t xml:space="preserve">1.90255379676819</t>
   </si>
   <si>
     <t xml:space="preserve">1.92137515544891</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91353297233582</t>
+    <t xml:space="preserve">1.91353261470795</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89784848690033</t>
+    <t xml:space="preserve">1.89784801006317</t>
   </si>
   <si>
     <t xml:space="preserve">1.89000582695007</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85079395771027</t>
+    <t xml:space="preserve">1.85079407691956</t>
   </si>
   <si>
     <t xml:space="preserve">1.8805947303772</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86647880077362</t>
+    <t xml:space="preserve">1.8664790391922</t>
   </si>
   <si>
     <t xml:space="preserve">1.54651093482971</t>
@@ -281,16 +281,16 @@
     <t xml:space="preserve">1.68610489368439</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70178949832916</t>
+    <t xml:space="preserve">1.70178961753845</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70022094249725</t>
+    <t xml:space="preserve">1.70022106170654</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66257750988007</t>
+    <t xml:space="preserve">1.66257762908936</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64532482624054</t>
+    <t xml:space="preserve">1.64532458782196</t>
   </si>
   <si>
     <t xml:space="preserve">1.62336599826813</t>
@@ -305,7 +305,7 @@
     <t xml:space="preserve">1.58415424823761</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64689290523529</t>
+    <t xml:space="preserve">1.64689302444458</t>
   </si>
   <si>
     <t xml:space="preserve">1.64061915874481</t>
@@ -314,19 +314,19 @@
     <t xml:space="preserve">1.63905072212219</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60768103599548</t>
+    <t xml:space="preserve">1.60768127441406</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57631182670593</t>
+    <t xml:space="preserve">1.57631194591522</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59199666976929</t>
+    <t xml:space="preserve">1.59199643135071</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75668585300446</t>
+    <t xml:space="preserve">1.75668573379517</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84295165538788</t>
+    <t xml:space="preserve">1.84295153617859</t>
   </si>
   <si>
     <t xml:space="preserve">1.84608888626099</t>
@@ -335,28 +335,28 @@
     <t xml:space="preserve">1.92921757698059</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88530051708221</t>
+    <t xml:space="preserve">1.88530015945435</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90098524093628</t>
+    <t xml:space="preserve">1.9009850025177</t>
   </si>
   <si>
     <t xml:space="preserve">1.91823828220367</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9496077299118</t>
+    <t xml:space="preserve">1.94960784912109</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93078577518463</t>
+    <t xml:space="preserve">1.9307861328125</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84922564029694</t>
+    <t xml:space="preserve">1.84922575950623</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82413005828857</t>
+    <t xml:space="preserve">1.82413017749786</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85549938678741</t>
+    <t xml:space="preserve">1.85549926757812</t>
   </si>
   <si>
     <t xml:space="preserve">1.89627969264984</t>
@@ -365,34 +365,34 @@
     <t xml:space="preserve">1.93706011772156</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87432134151459</t>
+    <t xml:space="preserve">1.87432086467743</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94333350658417</t>
+    <t xml:space="preserve">1.94333386421204</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94490218162537</t>
+    <t xml:space="preserve">1.94490230083466</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9668607711792</t>
+    <t xml:space="preserve">1.96686053276062</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98411417007446</t>
+    <t xml:space="preserve">1.98411393165588</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0625376701355</t>
+    <t xml:space="preserve">2.06253743171692</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0531268119812</t>
+    <t xml:space="preserve">2.05312657356262</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05155801773071</t>
+    <t xml:space="preserve">2.05155825614929</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0233256816864</t>
+    <t xml:space="preserve">2.02332544326782</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02959966659546</t>
+    <t xml:space="preserve">2.02959942817688</t>
   </si>
   <si>
     <t xml:space="preserve">2.03116798400879</t>
@@ -401,10 +401,10 @@
     <t xml:space="preserve">2.06096911430359</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09390687942505</t>
+    <t xml:space="preserve">2.09390711784363</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08606433868408</t>
+    <t xml:space="preserve">2.08606457710266</t>
   </si>
   <si>
     <t xml:space="preserve">2.1550772190094</t>
@@ -413,22 +413,22 @@
     <t xml:space="preserve">2.18801498413086</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19585752487183</t>
+    <t xml:space="preserve">2.19585728645325</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2021312713623</t>
+    <t xml:space="preserve">2.20213103294373</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23350071907043</t>
+    <t xml:space="preserve">2.23350048065186</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20997405052185</t>
+    <t xml:space="preserve">2.20997381210327</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18017292022705</t>
+    <t xml:space="preserve">2.18017268180847</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16605663299561</t>
+    <t xml:space="preserve">2.16605687141418</t>
   </si>
   <si>
     <t xml:space="preserve">2.1942892074585</t>
@@ -437,13 +437,13 @@
     <t xml:space="preserve">2.17389869689941</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2005627155304</t>
+    <t xml:space="preserve">2.20056295394897</t>
   </si>
   <si>
     <t xml:space="preserve">2.21938443183899</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21781587600708</t>
+    <t xml:space="preserve">2.21781611442566</t>
   </si>
   <si>
     <t xml:space="preserve">2.1911518573761</t>
@@ -452,55 +452,55 @@
     <t xml:space="preserve">2.12057089805603</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15350890159607</t>
+    <t xml:space="preserve">2.15350866317749</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11743426322937</t>
+    <t xml:space="preserve">2.11743402481079</t>
   </si>
   <si>
     <t xml:space="preserve">2.16291928291321</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10802268981934</t>
+    <t xml:space="preserve">2.10802316665649</t>
   </si>
   <si>
     <t xml:space="preserve">2.01548337936401</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04528427124023</t>
+    <t xml:space="preserve">2.04528450965881</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98568224906921</t>
+    <t xml:space="preserve">1.9856823682785</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07822227478027</t>
+    <t xml:space="preserve">2.07822203636169</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06724262237549</t>
+    <t xml:space="preserve">2.06724286079407</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12998175621033</t>
+    <t xml:space="preserve">2.12998151779175</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11586570739746</t>
+    <t xml:space="preserve">2.11586499214172</t>
   </si>
   <si>
     <t xml:space="preserve">2.05469512939453</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11429691314697</t>
+    <t xml:space="preserve">2.11429738998413</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05626344680786</t>
+    <t xml:space="preserve">2.05626368522644</t>
   </si>
   <si>
     <t xml:space="preserve">2.06410598754883</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10488629341125</t>
+    <t xml:space="preserve">2.10488605499268</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00920987129211</t>
+    <t xml:space="preserve">2.00920939445496</t>
   </si>
   <si>
     <t xml:space="preserve">2.01391506195068</t>
@@ -509,28 +509,28 @@
     <t xml:space="preserve">2.04842138290405</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16448783874512</t>
+    <t xml:space="preserve">2.16448831558228</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1848783493042</t>
+    <t xml:space="preserve">2.18487811088562</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26643872261047</t>
+    <t xml:space="preserve">2.26643848419189</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27271246910095</t>
+    <t xml:space="preserve">2.27271223068237</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25702786445618</t>
+    <t xml:space="preserve">2.2570276260376</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30721855163574</t>
+    <t xml:space="preserve">2.30721879005432</t>
   </si>
   <si>
     <t xml:space="preserve">2.23036360740662</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37152600288391</t>
+    <t xml:space="preserve">2.37152576446533</t>
   </si>
   <si>
     <t xml:space="preserve">2.35270428657532</t>
@@ -542,28 +542,28 @@
     <t xml:space="preserve">2.33545112609863</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3134925365448</t>
+    <t xml:space="preserve">2.31349277496338</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37623119354248</t>
+    <t xml:space="preserve">2.37623143196106</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32917714118958</t>
+    <t xml:space="preserve">2.32917761802673</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24918580055237</t>
+    <t xml:space="preserve">2.24918532371521</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28839707374573</t>
+    <t xml:space="preserve">2.28839731216431</t>
   </si>
   <si>
     <t xml:space="preserve">2.33701968193054</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34486222267151</t>
+    <t xml:space="preserve">2.34486198425293</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34956765174866</t>
+    <t xml:space="preserve">2.34956741333008</t>
   </si>
   <si>
     <t xml:space="preserve">2.32604026794434</t>
@@ -572,7 +572,7 @@
     <t xml:space="preserve">2.30251336097717</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31192421913147</t>
+    <t xml:space="preserve">2.31192398071289</t>
   </si>
   <si>
     <t xml:space="preserve">2.25075364112854</t>
@@ -584,43 +584,43 @@
     <t xml:space="preserve">2.43897008895874</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48445582389832</t>
+    <t xml:space="preserve">2.48445558547974</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46249771118164</t>
+    <t xml:space="preserve">2.46249723434448</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50798273086548</t>
+    <t xml:space="preserve">2.50798296928406</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48602414131165</t>
+    <t xml:space="preserve">2.48602437973022</t>
   </si>
   <si>
     <t xml:space="preserve">2.60993337631226</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66639804840088</t>
+    <t xml:space="preserve">2.66639828681946</t>
   </si>
   <si>
     <t xml:space="preserve">2.66326117515564</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66012406349182</t>
+    <t xml:space="preserve">2.66012454032898</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64287137985229</t>
+    <t xml:space="preserve">2.64287114143372</t>
   </si>
   <si>
     <t xml:space="preserve">2.65855622291565</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60209131240845</t>
+    <t xml:space="preserve">2.60209083557129</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55033183097839</t>
+    <t xml:space="preserve">2.55033135414124</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63816571235657</t>
+    <t xml:space="preserve">2.63816595077515</t>
   </si>
   <si>
     <t xml:space="preserve">2.58013248443604</t>
@@ -629,13 +629,13 @@
     <t xml:space="preserve">2.59581708908081</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58170104026794</t>
+    <t xml:space="preserve">2.58170080184937</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60365962982178</t>
+    <t xml:space="preserve">2.6036593914032</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61934399604797</t>
+    <t xml:space="preserve">2.61934423446655</t>
   </si>
   <si>
     <t xml:space="preserve">2.57542705535889</t>
@@ -644,97 +644,97 @@
     <t xml:space="preserve">2.57385849952698</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50955104827881</t>
+    <t xml:space="preserve">2.50955128669739</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58797478675842</t>
+    <t xml:space="preserve">2.58797454833984</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56444764137268</t>
+    <t xml:space="preserve">2.56444787979126</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61150169372559</t>
+    <t xml:space="preserve">2.61150193214417</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56915330886841</t>
+    <t xml:space="preserve">2.56915307044983</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63502883911133</t>
+    <t xml:space="preserve">2.63502907752991</t>
   </si>
   <si>
     <t xml:space="preserve">2.62561821937561</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62718605995178</t>
+    <t xml:space="preserve">2.62718629837036</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83422470092773</t>
+    <t xml:space="preserve">2.83422446250916</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79030776023865</t>
+    <t xml:space="preserve">2.79030728340149</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7761914730072</t>
+    <t xml:space="preserve">2.77619123458862</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78089642524719</t>
+    <t xml:space="preserve">2.78089618682861</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69149351119995</t>
+    <t xml:space="preserve">2.69149374961853</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78246521949768</t>
+    <t xml:space="preserve">2.78246545791626</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8122661113739</t>
+    <t xml:space="preserve">2.81226587295532</t>
   </si>
   <si>
     <t xml:space="preserve">2.82324528694153</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68678855895996</t>
+    <t xml:space="preserve">2.68678832054138</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70090436935425</t>
+    <t xml:space="preserve">2.70090460777283</t>
   </si>
   <si>
     <t xml:space="preserve">2.80657124519348</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86433935165405</t>
+    <t xml:space="preserve">2.86433959007263</t>
   </si>
   <si>
     <t xml:space="preserve">2.81940889358521</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80817627906799</t>
+    <t xml:space="preserve">2.80817604064941</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88038635253906</t>
+    <t xml:space="preserve">2.88038611412048</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83385062217712</t>
+    <t xml:space="preserve">2.8338508605957</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74398946762085</t>
+    <t xml:space="preserve">2.74398899078369</t>
   </si>
   <si>
     <t xml:space="preserve">2.72794246673584</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70547699928284</t>
+    <t xml:space="preserve">2.70547723770142</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7327561378479</t>
+    <t xml:space="preserve">2.73275637626648</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67177844047546</t>
+    <t xml:space="preserve">2.67177891731262</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62363886833191</t>
+    <t xml:space="preserve">2.62363862991333</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61722040176392</t>
+    <t xml:space="preserve">2.61722016334534</t>
   </si>
   <si>
     <t xml:space="preserve">2.60438299179077</t>
@@ -743,19 +743,19 @@
     <t xml:space="preserve">2.62524342536926</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64129018783569</t>
+    <t xml:space="preserve">2.64128994941711</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6958487033844</t>
+    <t xml:space="preserve">2.69584894180298</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75040793418884</t>
+    <t xml:space="preserve">2.75040817260742</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74719834327698</t>
+    <t xml:space="preserve">2.74719858169556</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71991896629333</t>
+    <t xml:space="preserve">2.71991920471191</t>
   </si>
   <si>
     <t xml:space="preserve">2.72633767127991</t>
@@ -773,7 +773,7 @@
     <t xml:space="preserve">2.82422256469727</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78731513023376</t>
+    <t xml:space="preserve">2.78731536865234</t>
   </si>
   <si>
     <t xml:space="preserve">2.79373383522034</t>
@@ -782,61 +782,61 @@
     <t xml:space="preserve">2.80496668815613</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78410577774048</t>
+    <t xml:space="preserve">2.78410601615906</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77608275413513</t>
+    <t xml:space="preserve">2.77608251571655</t>
   </si>
   <si>
     <t xml:space="preserve">2.79533863067627</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82261776924133</t>
+    <t xml:space="preserve">2.82261800765991</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76003575325012</t>
+    <t xml:space="preserve">2.7600359916687</t>
   </si>
   <si>
     <t xml:space="preserve">2.77929210662842</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79854798316956</t>
+    <t xml:space="preserve">2.79854774475098</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77447772026062</t>
+    <t xml:space="preserve">2.77447819709778</t>
   </si>
   <si>
     <t xml:space="preserve">2.8033618927002</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83545517921448</t>
+    <t xml:space="preserve">2.83545541763306</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84026956558228</t>
+    <t xml:space="preserve">2.8402693271637</t>
   </si>
   <si>
     <t xml:space="preserve">2.83224606513977</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8113853931427</t>
+    <t xml:space="preserve">2.81138515472412</t>
   </si>
   <si>
     <t xml:space="preserve">2.81619930267334</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76324510574341</t>
+    <t xml:space="preserve">2.76324534416199</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71189570426941</t>
+    <t xml:space="preserve">2.71189594268799</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72473311424255</t>
+    <t xml:space="preserve">2.72473287582397</t>
   </si>
   <si>
     <t xml:space="preserve">2.7969434261322</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79052472114563</t>
+    <t xml:space="preserve">2.79052448272705</t>
   </si>
   <si>
     <t xml:space="preserve">2.76805925369263</t>
@@ -851,7 +851,7 @@
     <t xml:space="preserve">2.81459450721741</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82903695106506</t>
+    <t xml:space="preserve">2.82903671264648</t>
   </si>
   <si>
     <t xml:space="preserve">2.84347867965698</t>
@@ -872,10 +872,10 @@
     <t xml:space="preserve">2.89161920547485</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92852640151978</t>
+    <t xml:space="preserve">2.9285261631012</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85952568054199</t>
+    <t xml:space="preserve">2.85952544212341</t>
   </si>
   <si>
     <t xml:space="preserve">2.90927028656006</t>
@@ -884,25 +884,25 @@
     <t xml:space="preserve">2.99913215637207</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96864342689514</t>
+    <t xml:space="preserve">2.96864318847656</t>
   </si>
   <si>
     <t xml:space="preserve">2.830641746521</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87878179550171</t>
+    <t xml:space="preserve">2.87878131866455</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8771767616272</t>
+    <t xml:space="preserve">2.87717700004578</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87557220458984</t>
+    <t xml:space="preserve">2.875572681427</t>
   </si>
   <si>
     <t xml:space="preserve">2.7520124912262</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7616400718689</t>
+    <t xml:space="preserve">2.76164054870605</t>
   </si>
   <si>
     <t xml:space="preserve">2.78892016410828</t>
@@ -911,19 +911,19 @@
     <t xml:space="preserve">2.67980217933655</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73596572875977</t>
+    <t xml:space="preserve">2.73596596717834</t>
   </si>
   <si>
     <t xml:space="preserve">2.8258273601532</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84829258918762</t>
+    <t xml:space="preserve">2.8482928276062</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82101368904114</t>
+    <t xml:space="preserve">2.82101321220398</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73436093330383</t>
+    <t xml:space="preserve">2.73436141014099</t>
   </si>
   <si>
     <t xml:space="preserve">2.81780433654785</t>
@@ -935,34 +935,34 @@
     <t xml:space="preserve">2.74077963829041</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79212927818298</t>
+    <t xml:space="preserve">2.79212951660156</t>
   </si>
   <si>
     <t xml:space="preserve">2.66375541687012</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60759210586548</t>
+    <t xml:space="preserve">2.60759234428406</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55142879486084</t>
+    <t xml:space="preserve">2.55142855644226</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56747531890869</t>
+    <t xml:space="preserve">2.56747508049011</t>
   </si>
   <si>
     <t xml:space="preserve">2.59956860542297</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55945181846619</t>
+    <t xml:space="preserve">2.55945205688477</t>
   </si>
   <si>
     <t xml:space="preserve">2.50328826904297</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45514845848083</t>
+    <t xml:space="preserve">2.45514798164368</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47921800613403</t>
+    <t xml:space="preserve">2.47921848297119</t>
   </si>
   <si>
     <t xml:space="preserve">2.47119474411011</t>
@@ -974,52 +974,52 @@
     <t xml:space="preserve">2.46317148208618</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48724174499512</t>
+    <t xml:space="preserve">2.48724150657654</t>
   </si>
   <si>
     <t xml:space="preserve">2.49526500701904</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5273585319519</t>
+    <t xml:space="preserve">2.52735829353333</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5835223197937</t>
+    <t xml:space="preserve">2.58352208137512</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65573191642761</t>
+    <t xml:space="preserve">2.65573215484619</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91247987747192</t>
+    <t xml:space="preserve">2.91247963905334</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82002520561218</t>
+    <t xml:space="preserve">2.8200249671936</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80358147621155</t>
+    <t xml:space="preserve">2.80358171463013</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86935448646545</t>
+    <t xml:space="preserve">2.86935472488403</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8446900844574</t>
+    <t xml:space="preserve">2.84468984603882</t>
   </si>
   <si>
     <t xml:space="preserve">2.85291147232056</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81180357933044</t>
+    <t xml:space="preserve">2.81180334091187</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72136497497559</t>
+    <t xml:space="preserve">2.72136521339417</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68025708198547</t>
+    <t xml:space="preserve">2.68025684356689</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69669985771179</t>
+    <t xml:space="preserve">2.69670033454895</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64737057685852</t>
+    <t xml:space="preserve">2.64737033843994</t>
   </si>
   <si>
     <t xml:space="preserve">2.65559196472168</t>
@@ -1049,58 +1049,58 @@
     <t xml:space="preserve">2.60626220703125</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52404546737671</t>
+    <t xml:space="preserve">2.52404570579529</t>
   </si>
   <si>
     <t xml:space="preserve">2.58159708976746</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61448383331299</t>
+    <t xml:space="preserve">2.61448407173157</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58981895446777</t>
+    <t xml:space="preserve">2.58981847763062</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62270522117615</t>
+    <t xml:space="preserve">2.62270545959473</t>
   </si>
   <si>
     <t xml:space="preserve">2.51582384109497</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57337546348572</t>
+    <t xml:space="preserve">2.57337522506714</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5651535987854</t>
+    <t xml:space="preserve">2.56515383720398</t>
   </si>
   <si>
     <t xml:space="preserve">2.53226709365845</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47471570968628</t>
+    <t xml:space="preserve">2.4747154712677</t>
   </si>
   <si>
     <t xml:space="preserve">2.48293733596802</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45005059242249</t>
+    <t xml:space="preserve">2.45005106925964</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44182920455933</t>
+    <t xml:space="preserve">2.44182944297791</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42538595199585</t>
+    <t xml:space="preserve">2.42538571357727</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43360781669617</t>
+    <t xml:space="preserve">2.43360757827759</t>
   </si>
   <si>
     <t xml:space="preserve">2.49115896224976</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50760221481323</t>
+    <t xml:space="preserve">2.50760245323181</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54048871994019</t>
+    <t xml:space="preserve">2.54048895835876</t>
   </si>
   <si>
     <t xml:space="preserve">2.67203521728516</t>
@@ -1109,7 +1109,7 @@
     <t xml:space="preserve">2.68847846984863</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70492172241211</t>
+    <t xml:space="preserve">2.70492196083069</t>
   </si>
   <si>
     <t xml:space="preserve">2.71314358711243</t>
@@ -1124,22 +1124,22 @@
     <t xml:space="preserve">2.77069497108459</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7295868396759</t>
+    <t xml:space="preserve">2.72958660125732</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74603009223938</t>
+    <t xml:space="preserve">2.7460298538208</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77891683578491</t>
+    <t xml:space="preserve">2.77891659736633</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79535984992981</t>
+    <t xml:space="preserve">2.79536008834839</t>
   </si>
   <si>
     <t xml:space="preserve">2.87757658958435</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91868448257446</t>
+    <t xml:space="preserve">2.91868472099304</t>
   </si>
   <si>
     <t xml:space="preserve">2.89401960372925</t>
@@ -1148,22 +1148,25 @@
     <t xml:space="preserve">2.86113309860229</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90224146842957</t>
+    <t xml:space="preserve">2.90224123001099</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88579821586609</t>
+    <t xml:space="preserve">2.88579797744751</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83646821975708</t>
+    <t xml:space="preserve">2.8364679813385</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94334959983826</t>
+    <t xml:space="preserve">2.94334936141968</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82824635505676</t>
+    <t xml:space="preserve">2.82824659347534</t>
   </si>
   <si>
     <t xml:space="preserve">2.92690634727478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80358147621155</t>
   </si>
   <si>
     <t xml:space="preserve">2.77809453010559</t>
@@ -1172,19 +1175,19 @@
     <t xml:space="preserve">2.82057285308838</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82906818389893</t>
+    <t xml:space="preserve">2.8290684223175</t>
   </si>
   <si>
     <t xml:space="preserve">2.88853859901428</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88004279136658</t>
+    <t xml:space="preserve">2.88004302978516</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92252111434937</t>
+    <t xml:space="preserve">2.92252135276794</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90553021430969</t>
+    <t xml:space="preserve">2.90552997589111</t>
   </si>
   <si>
     <t xml:space="preserve">2.87154722213745</t>
@@ -1193,7 +1196,7 @@
     <t xml:space="preserve">2.85455560684204</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91402578353882</t>
+    <t xml:space="preserve">2.91402554512024</t>
   </si>
   <si>
     <t xml:space="preserve">2.93101692199707</t>
@@ -1205,22 +1208,22 @@
     <t xml:space="preserve">2.89703416824341</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93951272964478</t>
+    <t xml:space="preserve">2.93951296806335</t>
   </si>
   <si>
     <t xml:space="preserve">2.98199129104614</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79508566856384</t>
+    <t xml:space="preserve">2.79508590698242</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78658986091614</t>
+    <t xml:space="preserve">2.78659009933472</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76110291481018</t>
+    <t xml:space="preserve">2.76110315322876</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76959896087646</t>
+    <t xml:space="preserve">2.76959872245789</t>
   </si>
   <si>
     <t xml:space="preserve">2.81207704544067</t>
@@ -1232,46 +1235,43 @@
     <t xml:space="preserve">2.86305141448975</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62517142295837</t>
+    <t xml:space="preserve">2.62517189979553</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6761462688446</t>
+    <t xml:space="preserve">2.67614579200745</t>
   </si>
   <si>
     <t xml:space="preserve">2.61667585372925</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55720615386963</t>
+    <t xml:space="preserve">2.55720591545105</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54871034622192</t>
+    <t xml:space="preserve">2.51472759246826</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51472783088684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49773645401001</t>
+    <t xml:space="preserve">2.49773597717285</t>
   </si>
   <si>
     <t xml:space="preserve">2.4807448387146</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53171896934509</t>
+    <t xml:space="preserve">2.53171920776367</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46375370025635</t>
+    <t xml:space="preserve">2.46375346183777</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58269333839417</t>
+    <t xml:space="preserve">2.58269309997559</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5402147769928</t>
+    <t xml:space="preserve">2.54021453857422</t>
   </si>
   <si>
     <t xml:space="preserve">2.56570196151733</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59118890762329</t>
+    <t xml:space="preserve">2.59118914604187</t>
   </si>
   <si>
     <t xml:space="preserve">2.47224926948547</t>
@@ -1280,10 +1280,10 @@
     <t xml:space="preserve">2.63366746902466</t>
   </si>
   <si>
-    <t xml:space="preserve">2.599684715271</t>
+    <t xml:space="preserve">2.59968447685242</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52322340011597</t>
+    <t xml:space="preserve">2.52322363853455</t>
   </si>
   <si>
     <t xml:space="preserve">2.57419753074646</t>
@@ -1298,13 +1298,13 @@
     <t xml:space="preserve">2.99048686027527</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96499967575073</t>
+    <t xml:space="preserve">2.96499991416931</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97349572181702</t>
+    <t xml:space="preserve">2.97349548339844</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95650434494019</t>
+    <t xml:space="preserve">2.95650410652161</t>
   </si>
   <si>
     <t xml:space="preserve">2.84606003761292</t>
@@ -1316,19 +1316,19 @@
     <t xml:space="preserve">2.6676504611969</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65915465354919</t>
+    <t xml:space="preserve">2.65915441513062</t>
   </si>
   <si>
     <t xml:space="preserve">2.31083083152771</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3533091545105</t>
+    <t xml:space="preserve">2.35330939292908</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34481334686279</t>
+    <t xml:space="preserve">2.34481358528137</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45525789260864</t>
+    <t xml:space="preserve">2.45525765419006</t>
   </si>
   <si>
     <t xml:space="preserve">2.4892406463623</t>
@@ -1340,10 +1340,10 @@
     <t xml:space="preserve">2.64216303825378</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71012878417969</t>
+    <t xml:space="preserve">2.71012902259827</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69313740730286</t>
+    <t xml:space="preserve">2.69313764572144</t>
   </si>
   <si>
     <t xml:space="preserve">2.71862435340881</t>
@@ -1355,25 +1355,25 @@
     <t xml:space="preserve">2.68464183807373</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60818028450012</t>
+    <t xml:space="preserve">2.6081805229187</t>
   </si>
   <si>
     <t xml:space="preserve">2.50623202323914</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44676208496094</t>
+    <t xml:space="preserve">2.44676232337952</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37879657745361</t>
+    <t xml:space="preserve">2.37879633903503</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42977046966553</t>
+    <t xml:space="preserve">2.42977070808411</t>
   </si>
   <si>
     <t xml:space="preserve">2.37030076980591</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31932663917542</t>
+    <t xml:space="preserve">2.31932640075684</t>
   </si>
   <si>
     <t xml:space="preserve">2.27684807777405</t>
@@ -1385,7 +1385,7 @@
     <t xml:space="preserve">2.30233502388</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33631801605225</t>
+    <t xml:space="preserve">2.33631777763367</t>
   </si>
   <si>
     <t xml:space="preserve">2.39578771591187</t>
@@ -1394,19 +1394,19 @@
     <t xml:space="preserve">2.72712016105652</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99898266792297</t>
+    <t xml:space="preserve">2.99898242950439</t>
   </si>
   <si>
     <t xml:space="preserve">3.03296542167664</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01597380638123</t>
+    <t xml:space="preserve">3.0159740447998</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04146122932434</t>
+    <t xml:space="preserve">3.04146099090576</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19438362121582</t>
+    <t xml:space="preserve">3.19438409805298</t>
   </si>
   <si>
     <t xml:space="preserve">3.1264181137085</t>
@@ -1418,31 +1418,31 @@
     <t xml:space="preserve">3.09243559837341</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16040110588074</t>
+    <t xml:space="preserve">3.16040086746216</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21137523651123</t>
+    <t xml:space="preserve">3.21137547492981</t>
   </si>
   <si>
     <t xml:space="preserve">3.3133237361908</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26234936714172</t>
+    <t xml:space="preserve">3.26234912872314</t>
   </si>
   <si>
     <t xml:space="preserve">3.33031511306763</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22836661338806</t>
+    <t xml:space="preserve">3.22836637496948</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17739248275757</t>
+    <t xml:space="preserve">3.17739224433899</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14340972900391</t>
+    <t xml:space="preserve">3.14340949058533</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10942673683167</t>
+    <t xml:space="preserve">3.10942697525024</t>
   </si>
   <si>
     <t xml:space="preserve">3.27934074401855</t>
@@ -1451,22 +1451,22 @@
     <t xml:space="preserve">3.48323750495911</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39828062057495</t>
+    <t xml:space="preserve">3.39828038215637</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46624612808228</t>
+    <t xml:space="preserve">3.46624636650085</t>
   </si>
   <si>
     <t xml:space="preserve">3.36429786682129</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34730672836304</t>
+    <t xml:space="preserve">3.34730648994446</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24535799026489</t>
+    <t xml:space="preserve">3.24535775184631</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02446961402893</t>
+    <t xml:space="preserve">3.02446985244751</t>
   </si>
   <si>
     <t xml:space="preserve">3.16417121887207</t>
@@ -1499,10 +1499,13 @@
     <t xml:space="preserve">3.09405112266541</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07652139663696</t>
+    <t xml:space="preserve">3.07652115821838</t>
   </si>
   <si>
     <t xml:space="preserve">3.06775617599487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04146122932434</t>
   </si>
   <si>
     <t xml:space="preserve">3.00640106201172</t>
@@ -1523,13 +1526,13 @@
     <t xml:space="preserve">2.96257615089417</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86616063117981</t>
+    <t xml:space="preserve">2.86616086959839</t>
   </si>
   <si>
     <t xml:space="preserve">2.91875076293945</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80480575561523</t>
+    <t xml:space="preserve">2.80480551719666</t>
   </si>
   <si>
     <t xml:space="preserve">2.82233572006226</t>
@@ -1541,7 +1544,7 @@
     <t xml:space="preserve">2.95381093025208</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83110046386719</t>
+    <t xml:space="preserve">2.83110070228577</t>
   </si>
   <si>
     <t xml:space="preserve">2.93628096580505</t>
@@ -1565,10 +1568,10 @@
     <t xml:space="preserve">2.83986568450928</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68209552764893</t>
+    <t xml:space="preserve">2.68209528923035</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69086027145386</t>
+    <t xml:space="preserve">2.69086050987244</t>
   </si>
   <si>
     <t xml:space="preserve">2.66456532478333</t>
@@ -1586,7 +1589,7 @@
     <t xml:space="preserve">2.76974582672119</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79604053497314</t>
+    <t xml:space="preserve">2.79604077339172</t>
   </si>
   <si>
     <t xml:space="preserve">2.84863090515137</t>
@@ -1683,9 +1686,6 @@
   </si>
   <si>
     <t xml:space="preserve">2.85962271690369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80480551719666</t>
   </si>
   <si>
     <t xml:space="preserve">2.89616751670837</t>
@@ -24608,7 +24608,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G859" t="s">
-        <v>327</v>
+        <v>384</v>
       </c>
       <c r="H859" t="s">
         <v>9</v>
@@ -24634,7 +24634,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G860" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="H860" t="s">
         <v>9</v>
@@ -24660,7 +24660,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G861" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="H861" t="s">
         <v>9</v>
@@ -24686,7 +24686,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G862" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="H862" t="s">
         <v>9</v>
@@ -24712,7 +24712,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G863" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="H863" t="s">
         <v>9</v>
@@ -24738,7 +24738,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G864" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="H864" t="s">
         <v>9</v>
@@ -24764,7 +24764,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G865" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="H865" t="s">
         <v>9</v>
@@ -24790,7 +24790,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G866" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H866" t="s">
         <v>9</v>
@@ -24816,7 +24816,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G867" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H867" t="s">
         <v>9</v>
@@ -24842,7 +24842,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G868" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H868" t="s">
         <v>9</v>
@@ -24868,7 +24868,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G869" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H869" t="s">
         <v>9</v>
@@ -24894,7 +24894,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G870" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H870" t="s">
         <v>9</v>
@@ -24920,7 +24920,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G871" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H871" t="s">
         <v>9</v>
@@ -24946,7 +24946,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G872" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="H872" t="s">
         <v>9</v>
@@ -24972,7 +24972,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G873" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="H873" t="s">
         <v>9</v>
@@ -24998,7 +24998,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G874" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="H874" t="s">
         <v>9</v>
@@ -25024,7 +25024,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G875" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H875" t="s">
         <v>9</v>
@@ -25050,7 +25050,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G876" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="H876" t="s">
         <v>9</v>
@@ -25076,7 +25076,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G877" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="H877" t="s">
         <v>9</v>
@@ -25102,7 +25102,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G878" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="H878" t="s">
         <v>9</v>
@@ -25128,7 +25128,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G879" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="H879" t="s">
         <v>9</v>
@@ -25154,7 +25154,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G880" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="H880" t="s">
         <v>9</v>
@@ -25180,7 +25180,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G881" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="H881" t="s">
         <v>9</v>
@@ -25206,7 +25206,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G882" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="H882" t="s">
         <v>9</v>
@@ -25232,7 +25232,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G883" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="H883" t="s">
         <v>9</v>
@@ -25258,7 +25258,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G884" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="H884" t="s">
         <v>9</v>
@@ -25284,7 +25284,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G885" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="H885" t="s">
         <v>9</v>
@@ -25310,7 +25310,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G886" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="H886" t="s">
         <v>9</v>
@@ -25336,7 +25336,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G887" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="H887" t="s">
         <v>9</v>
@@ -25362,7 +25362,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G888" t="s">
-        <v>327</v>
+        <v>384</v>
       </c>
       <c r="H888" t="s">
         <v>9</v>
@@ -25388,7 +25388,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G889" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="H889" t="s">
         <v>9</v>
@@ -25414,7 +25414,7 @@
         <v>3.25</v>
       </c>
       <c r="G890" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="H890" t="s">
         <v>9</v>
@@ -25440,7 +25440,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G891" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="H891" t="s">
         <v>9</v>
@@ -25466,7 +25466,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G892" t="s">
-        <v>327</v>
+        <v>384</v>
       </c>
       <c r="H892" t="s">
         <v>9</v>
@@ -25492,7 +25492,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G893" t="s">
-        <v>327</v>
+        <v>384</v>
       </c>
       <c r="H893" t="s">
         <v>9</v>
@@ -25518,7 +25518,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G894" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="H894" t="s">
         <v>9</v>
@@ -25544,7 +25544,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G895" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H895" t="s">
         <v>9</v>
@@ -25570,7 +25570,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G896" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="H896" t="s">
         <v>9</v>
@@ -25596,7 +25596,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G897" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="H897" t="s">
         <v>9</v>
@@ -25622,7 +25622,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G898" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="H898" t="s">
         <v>9</v>
@@ -25648,7 +25648,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G899" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="H899" t="s">
         <v>9</v>
@@ -25674,7 +25674,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G900" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="H900" t="s">
         <v>9</v>
@@ -25700,7 +25700,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G901" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="H901" t="s">
         <v>9</v>
@@ -25726,7 +25726,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G902" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="H902" t="s">
         <v>9</v>
@@ -25752,7 +25752,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G903" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="H903" t="s">
         <v>9</v>
@@ -25778,7 +25778,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G904" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="H904" t="s">
         <v>9</v>
@@ -25804,7 +25804,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G905" t="s">
-        <v>327</v>
+        <v>384</v>
       </c>
       <c r="H905" t="s">
         <v>9</v>
@@ -25830,7 +25830,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G906" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="H906" t="s">
         <v>9</v>
@@ -25856,7 +25856,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G907" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="H907" t="s">
         <v>9</v>
@@ -25882,7 +25882,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G908" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="H908" t="s">
         <v>9</v>
@@ -25908,7 +25908,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G909" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="H909" t="s">
         <v>9</v>
@@ -25934,7 +25934,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G910" t="s">
-        <v>327</v>
+        <v>384</v>
       </c>
       <c r="H910" t="s">
         <v>9</v>
@@ -25960,7 +25960,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G911" t="s">
-        <v>327</v>
+        <v>384</v>
       </c>
       <c r="H911" t="s">
         <v>9</v>
@@ -25986,7 +25986,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G912" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="H912" t="s">
         <v>9</v>
@@ -26012,7 +26012,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G913" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="H913" t="s">
         <v>9</v>
@@ -26038,7 +26038,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G914" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="H914" t="s">
         <v>9</v>
@@ -26064,7 +26064,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G915" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="H915" t="s">
         <v>9</v>
@@ -26090,7 +26090,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G916" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="H916" t="s">
         <v>9</v>
@@ -26116,7 +26116,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G917" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="H917" t="s">
         <v>9</v>
@@ -26142,7 +26142,7 @@
         <v>3</v>
       </c>
       <c r="G918" t="s">
-        <v>410</v>
+        <v>342</v>
       </c>
       <c r="H918" t="s">
         <v>9</v>
@@ -26272,7 +26272,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G923" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="H923" t="s">
         <v>9</v>
@@ -26298,7 +26298,7 @@
         <v>3</v>
       </c>
       <c r="G924" t="s">
-        <v>410</v>
+        <v>342</v>
       </c>
       <c r="H924" t="s">
         <v>9</v>
@@ -26350,7 +26350,7 @@
         <v>3</v>
       </c>
       <c r="G926" t="s">
-        <v>410</v>
+        <v>342</v>
       </c>
       <c r="H926" t="s">
         <v>9</v>
@@ -26376,7 +26376,7 @@
         <v>3</v>
       </c>
       <c r="G927" t="s">
-        <v>410</v>
+        <v>342</v>
       </c>
       <c r="H927" t="s">
         <v>9</v>
@@ -26610,7 +26610,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G936" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="H936" t="s">
         <v>9</v>
@@ -26636,7 +26636,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G937" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="H937" t="s">
         <v>9</v>
@@ -27338,7 +27338,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G964" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="H964" t="s">
         <v>9</v>
@@ -27364,7 +27364,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G965" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="H965" t="s">
         <v>9</v>
@@ -27390,7 +27390,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G966" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="H966" t="s">
         <v>9</v>
@@ -27416,7 +27416,7 @@
         <v>3</v>
       </c>
       <c r="G967" t="s">
-        <v>410</v>
+        <v>342</v>
       </c>
       <c r="H967" t="s">
         <v>9</v>
@@ -27572,7 +27572,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G973" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="H973" t="s">
         <v>9</v>
@@ -27598,7 +27598,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G974" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="H974" t="s">
         <v>9</v>
@@ -27624,7 +27624,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G975" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="H975" t="s">
         <v>9</v>
@@ -27650,7 +27650,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G976" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="H976" t="s">
         <v>9</v>
@@ -27806,7 +27806,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G982" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="H982" t="s">
         <v>9</v>
@@ -27832,7 +27832,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G983" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H983" t="s">
         <v>9</v>
@@ -27884,7 +27884,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G985" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="H985" t="s">
         <v>9</v>
@@ -27936,7 +27936,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G987" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H987" t="s">
         <v>9</v>
@@ -27988,7 +27988,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G989" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H989" t="s">
         <v>9</v>
@@ -28014,7 +28014,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G990" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="H990" t="s">
         <v>9</v>
@@ -28040,7 +28040,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G991" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="H991" t="s">
         <v>9</v>
@@ -28066,7 +28066,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G992" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="H992" t="s">
         <v>9</v>
@@ -28092,7 +28092,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G993" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H993" t="s">
         <v>9</v>
@@ -28118,7 +28118,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G994" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H994" t="s">
         <v>9</v>
@@ -28144,7 +28144,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G995" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H995" t="s">
         <v>9</v>
@@ -28170,7 +28170,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G996" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="H996" t="s">
         <v>9</v>
@@ -28196,7 +28196,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G997" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H997" t="s">
         <v>9</v>
@@ -28222,7 +28222,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G998" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="H998" t="s">
         <v>9</v>
@@ -28248,7 +28248,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G999" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="H999" t="s">
         <v>9</v>
@@ -28274,7 +28274,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1000" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="H1000" t="s">
         <v>9</v>
@@ -28300,7 +28300,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G1001" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H1001" t="s">
         <v>9</v>
@@ -28326,7 +28326,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G1002" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H1002" t="s">
         <v>9</v>
@@ -28352,7 +28352,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1003" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H1003" t="s">
         <v>9</v>
@@ -28378,7 +28378,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1004" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="H1004" t="s">
         <v>9</v>
@@ -28404,7 +28404,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G1005" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H1005" t="s">
         <v>9</v>
@@ -28430,7 +28430,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G1006" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H1006" t="s">
         <v>9</v>
@@ -28456,7 +28456,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1007" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="H1007" t="s">
         <v>9</v>
@@ -28482,7 +28482,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1008" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="H1008" t="s">
         <v>9</v>
@@ -28508,7 +28508,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1009" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="H1009" t="s">
         <v>9</v>
@@ -28534,7 +28534,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G1010" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H1010" t="s">
         <v>9</v>
@@ -28560,7 +28560,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1011" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H1011" t="s">
         <v>9</v>
@@ -28586,7 +28586,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G1012" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H1012" t="s">
         <v>9</v>
@@ -28612,7 +28612,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1013" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="H1013" t="s">
         <v>9</v>
@@ -28638,7 +28638,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G1014" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H1014" t="s">
         <v>9</v>
@@ -28664,7 +28664,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G1015" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="H1015" t="s">
         <v>9</v>
@@ -28690,7 +28690,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1016" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="H1016" t="s">
         <v>9</v>
@@ -28716,7 +28716,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G1017" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H1017" t="s">
         <v>9</v>
@@ -28742,7 +28742,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G1018" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H1018" t="s">
         <v>9</v>
@@ -28768,7 +28768,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1019" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="H1019" t="s">
         <v>9</v>
@@ -28794,7 +28794,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1020" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="H1020" t="s">
         <v>9</v>
@@ -28820,7 +28820,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G1021" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H1021" t="s">
         <v>9</v>
@@ -28846,7 +28846,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1022" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="H1022" t="s">
         <v>9</v>
@@ -28924,7 +28924,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G1025" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H1025" t="s">
         <v>9</v>
@@ -28950,7 +28950,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1026" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H1026" t="s">
         <v>9</v>
@@ -28976,7 +28976,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1027" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H1027" t="s">
         <v>9</v>
@@ -29002,7 +29002,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G1028" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H1028" t="s">
         <v>9</v>
@@ -29028,7 +29028,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G1029" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H1029" t="s">
         <v>9</v>
@@ -29106,7 +29106,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1032" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="H1032" t="s">
         <v>9</v>
@@ -29132,7 +29132,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1033" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H1033" t="s">
         <v>9</v>
@@ -29158,7 +29158,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G1034" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H1034" t="s">
         <v>9</v>
@@ -29184,7 +29184,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G1035" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H1035" t="s">
         <v>9</v>
@@ -29210,7 +29210,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G1036" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="H1036" t="s">
         <v>9</v>
@@ -29236,7 +29236,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1037" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H1037" t="s">
         <v>9</v>
@@ -29262,7 +29262,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G1038" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="H1038" t="s">
         <v>9</v>
@@ -29392,7 +29392,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G1043" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="H1043" t="s">
         <v>9</v>
@@ -29418,7 +29418,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G1044" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="H1044" t="s">
         <v>9</v>
@@ -29444,7 +29444,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G1045" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="H1045" t="s">
         <v>9</v>
@@ -29470,7 +29470,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1046" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="H1046" t="s">
         <v>9</v>
@@ -29496,7 +29496,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G1047" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="H1047" t="s">
         <v>9</v>
@@ -29522,7 +29522,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1048" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H1048" t="s">
         <v>9</v>
@@ -29600,7 +29600,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1051" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H1051" t="s">
         <v>9</v>
@@ -29626,7 +29626,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G1052" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H1052" t="s">
         <v>9</v>
@@ -29652,7 +29652,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G1053" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="H1053" t="s">
         <v>9</v>
@@ -29678,7 +29678,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G1054" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="H1054" t="s">
         <v>9</v>
@@ -29704,7 +29704,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G1055" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="H1055" t="s">
         <v>9</v>
@@ -29730,7 +29730,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G1056" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="H1056" t="s">
         <v>9</v>
@@ -29756,7 +29756,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1057" t="s">
-        <v>327</v>
+        <v>384</v>
       </c>
       <c r="H1057" t="s">
         <v>9</v>
@@ -29782,7 +29782,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G1058" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="H1058" t="s">
         <v>9</v>
@@ -29808,7 +29808,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G1059" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="H1059" t="s">
         <v>9</v>
@@ -30354,7 +30354,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1080" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="H1080" t="s">
         <v>9</v>
@@ -30640,7 +30640,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G1091" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="H1091" t="s">
         <v>9</v>
@@ -30718,7 +30718,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G1094" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="H1094" t="s">
         <v>9</v>
@@ -30796,7 +30796,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G1097" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="H1097" t="s">
         <v>9</v>
@@ -30822,7 +30822,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G1098" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="H1098" t="s">
         <v>9</v>
@@ -30848,7 +30848,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G1099" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="H1099" t="s">
         <v>9</v>
@@ -30874,7 +30874,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G1100" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="H1100" t="s">
         <v>9</v>
@@ -30900,7 +30900,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1101" t="s">
-        <v>327</v>
+        <v>384</v>
       </c>
       <c r="H1101" t="s">
         <v>9</v>
@@ -31212,7 +31212,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G1113" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="H1113" t="s">
         <v>9</v>
@@ -31576,7 +31576,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1127" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="H1127" t="s">
         <v>9</v>
@@ -31628,7 +31628,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G1129" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="H1129" t="s">
         <v>9</v>
@@ -31654,7 +31654,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1130" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="H1130" t="s">
         <v>9</v>
@@ -31836,7 +31836,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G1137" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="H1137" t="s">
         <v>9</v>
@@ -31862,7 +31862,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G1138" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="H1138" t="s">
         <v>9</v>
@@ -32356,7 +32356,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G1157" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="H1157" t="s">
         <v>9</v>
@@ -32382,7 +32382,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G1158" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="H1158" t="s">
         <v>9</v>
@@ -32408,7 +32408,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G1159" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="H1159" t="s">
         <v>9</v>
@@ -32902,7 +32902,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1178" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="H1178" t="s">
         <v>9</v>
@@ -32928,7 +32928,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1179" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="H1179" t="s">
         <v>9</v>
@@ -33006,7 +33006,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1182" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="H1182" t="s">
         <v>9</v>
@@ -33032,7 +33032,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1183" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="H1183" t="s">
         <v>9</v>
@@ -33058,7 +33058,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G1184" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="H1184" t="s">
         <v>9</v>
@@ -33084,7 +33084,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G1185" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="H1185" t="s">
         <v>9</v>
@@ -33188,7 +33188,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G1189" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="H1189" t="s">
         <v>9</v>
@@ -33292,7 +33292,7 @@
         <v>3</v>
       </c>
       <c r="G1193" t="s">
-        <v>410</v>
+        <v>342</v>
       </c>
       <c r="H1193" t="s">
         <v>9</v>
@@ -33318,7 +33318,7 @@
         <v>3</v>
       </c>
       <c r="G1194" t="s">
-        <v>410</v>
+        <v>342</v>
       </c>
       <c r="H1194" t="s">
         <v>9</v>
@@ -33344,7 +33344,7 @@
         <v>3</v>
       </c>
       <c r="G1195" t="s">
-        <v>410</v>
+        <v>342</v>
       </c>
       <c r="H1195" t="s">
         <v>9</v>
@@ -33370,7 +33370,7 @@
         <v>3</v>
       </c>
       <c r="G1196" t="s">
-        <v>410</v>
+        <v>342</v>
       </c>
       <c r="H1196" t="s">
         <v>9</v>
@@ -33396,7 +33396,7 @@
         <v>3</v>
       </c>
       <c r="G1197" t="s">
-        <v>410</v>
+        <v>342</v>
       </c>
       <c r="H1197" t="s">
         <v>9</v>
@@ -33422,7 +33422,7 @@
         <v>3</v>
       </c>
       <c r="G1198" t="s">
-        <v>410</v>
+        <v>342</v>
       </c>
       <c r="H1198" t="s">
         <v>9</v>
@@ -33448,7 +33448,7 @@
         <v>3</v>
       </c>
       <c r="G1199" t="s">
-        <v>410</v>
+        <v>342</v>
       </c>
       <c r="H1199" t="s">
         <v>9</v>
@@ -35008,7 +35008,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1259" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="H1259" t="s">
         <v>9</v>
@@ -35138,7 +35138,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G1264" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="H1264" t="s">
         <v>9</v>
@@ -35164,7 +35164,7 @@
         <v>3.25</v>
       </c>
       <c r="G1265" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="H1265" t="s">
         <v>9</v>
@@ -35216,7 +35216,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G1267" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="H1267" t="s">
         <v>9</v>
@@ -35242,7 +35242,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1268" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="H1268" t="s">
         <v>9</v>
@@ -35268,7 +35268,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1269" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="H1269" t="s">
         <v>9</v>
@@ -35294,7 +35294,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1270" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="H1270" t="s">
         <v>9</v>
@@ -35320,7 +35320,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G1271" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="H1271" t="s">
         <v>9</v>
@@ -35346,7 +35346,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G1272" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H1272" t="s">
         <v>9</v>
@@ -35372,7 +35372,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G1273" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="H1273" t="s">
         <v>9</v>
@@ -35398,7 +35398,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G1274" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="H1274" t="s">
         <v>9</v>
@@ -35424,7 +35424,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1275" t="s">
-        <v>327</v>
+        <v>384</v>
       </c>
       <c r="H1275" t="s">
         <v>9</v>
@@ -35450,7 +35450,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G1276" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="H1276" t="s">
         <v>9</v>
@@ -35476,7 +35476,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1277" t="s">
-        <v>327</v>
+        <v>384</v>
       </c>
       <c r="H1277" t="s">
         <v>9</v>
@@ -35502,7 +35502,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G1278" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="H1278" t="s">
         <v>9</v>
@@ -35528,7 +35528,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G1279" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="H1279" t="s">
         <v>9</v>
@@ -35606,7 +35606,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1282" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H1282" t="s">
         <v>9</v>
@@ -35632,7 +35632,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1283" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H1283" t="s">
         <v>9</v>
@@ -35658,7 +35658,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1284" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="H1284" t="s">
         <v>9</v>
@@ -35684,7 +35684,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G1285" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H1285" t="s">
         <v>9</v>
@@ -35710,7 +35710,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G1286" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="H1286" t="s">
         <v>9</v>
@@ -35736,7 +35736,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G1287" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="H1287" t="s">
         <v>9</v>
@@ -35762,7 +35762,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G1288" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="H1288" t="s">
         <v>9</v>
@@ -35814,7 +35814,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G1290" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="H1290" t="s">
         <v>9</v>
@@ -35866,7 +35866,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1292" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="H1292" t="s">
         <v>9</v>
@@ -35892,7 +35892,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G1293" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H1293" t="s">
         <v>9</v>
@@ -35918,7 +35918,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G1294" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="H1294" t="s">
         <v>9</v>
@@ -35944,7 +35944,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1295" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H1295" t="s">
         <v>9</v>
@@ -35970,7 +35970,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G1296" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="H1296" t="s">
         <v>9</v>
@@ -35996,7 +35996,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G1297" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="H1297" t="s">
         <v>9</v>
@@ -36074,7 +36074,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G1300" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="H1300" t="s">
         <v>9</v>
@@ -36126,7 +36126,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G1302" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="H1302" t="s">
         <v>9</v>
@@ -36204,7 +36204,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1305" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="H1305" t="s">
         <v>9</v>
@@ -36230,7 +36230,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1306" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="H1306" t="s">
         <v>9</v>
@@ -36256,7 +36256,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1307" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="H1307" t="s">
         <v>9</v>
@@ -36282,7 +36282,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1308" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="H1308" t="s">
         <v>9</v>
@@ -36360,7 +36360,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G1311" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="H1311" t="s">
         <v>9</v>
@@ -36386,7 +36386,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G1312" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="H1312" t="s">
         <v>9</v>
@@ -36412,7 +36412,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G1313" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H1313" t="s">
         <v>9</v>
@@ -36438,7 +36438,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G1314" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H1314" t="s">
         <v>9</v>
@@ -36516,7 +36516,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G1317" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="H1317" t="s">
         <v>9</v>
@@ -36724,7 +36724,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G1325" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="H1325" t="s">
         <v>9</v>
@@ -36750,7 +36750,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G1326" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="H1326" t="s">
         <v>9</v>
@@ -36776,7 +36776,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G1327" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="H1327" t="s">
         <v>9</v>
@@ -36802,7 +36802,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1328" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="H1328" t="s">
         <v>9</v>
@@ -36854,7 +36854,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1330" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H1330" t="s">
         <v>9</v>
@@ -36906,7 +36906,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1332" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="H1332" t="s">
         <v>9</v>
@@ -36932,7 +36932,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1333" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="H1333" t="s">
         <v>9</v>
@@ -36958,7 +36958,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1334" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H1334" t="s">
         <v>9</v>
@@ -37140,7 +37140,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1341" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H1341" t="s">
         <v>9</v>
@@ -37374,7 +37374,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1350" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="H1350" t="s">
         <v>9</v>
@@ -37400,7 +37400,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1351" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="H1351" t="s">
         <v>9</v>
@@ -37426,7 +37426,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1352" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="H1352" t="s">
         <v>9</v>
@@ -37452,7 +37452,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1353" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="H1353" t="s">
         <v>9</v>
@@ -37660,7 +37660,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1361" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="H1361" t="s">
         <v>9</v>
@@ -37686,7 +37686,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1362" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="H1362" t="s">
         <v>9</v>
@@ -37712,7 +37712,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1363" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="H1363" t="s">
         <v>9</v>
@@ -37738,7 +37738,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1364" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="H1364" t="s">
         <v>9</v>
@@ -37764,7 +37764,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1365" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H1365" t="s">
         <v>9</v>
@@ -37790,7 +37790,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1366" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H1366" t="s">
         <v>9</v>
@@ -37816,7 +37816,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1367" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H1367" t="s">
         <v>9</v>
@@ -37894,7 +37894,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1370" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="H1370" t="s">
         <v>9</v>
@@ -37920,7 +37920,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1371" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H1371" t="s">
         <v>9</v>
@@ -37946,7 +37946,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1372" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="H1372" t="s">
         <v>9</v>
@@ -37972,7 +37972,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1373" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H1373" t="s">
         <v>9</v>
@@ -38050,7 +38050,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1376" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H1376" t="s">
         <v>9</v>
@@ -38102,7 +38102,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1378" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="H1378" t="s">
         <v>9</v>
@@ -38154,7 +38154,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1380" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H1380" t="s">
         <v>9</v>
@@ -38206,7 +38206,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1382" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H1382" t="s">
         <v>9</v>
@@ -38232,7 +38232,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1383" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H1383" t="s">
         <v>9</v>
@@ -38284,7 +38284,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1385" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H1385" t="s">
         <v>9</v>
@@ -38336,7 +38336,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1387" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="H1387" t="s">
         <v>9</v>
@@ -38414,7 +38414,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1390" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H1390" t="s">
         <v>9</v>
@@ -38440,7 +38440,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1391" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H1391" t="s">
         <v>9</v>
@@ -38466,7 +38466,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1392" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H1392" t="s">
         <v>9</v>
@@ -38492,7 +38492,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1393" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H1393" t="s">
         <v>9</v>
@@ -38518,7 +38518,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1394" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H1394" t="s">
         <v>9</v>
@@ -38544,7 +38544,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1395" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="H1395" t="s">
         <v>9</v>
@@ -38570,7 +38570,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1396" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="H1396" t="s">
         <v>9</v>
@@ -38596,7 +38596,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1397" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="H1397" t="s">
         <v>9</v>
@@ -38622,7 +38622,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1398" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="H1398" t="s">
         <v>9</v>
@@ -38648,7 +38648,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1399" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="H1399" t="s">
         <v>9</v>
@@ -38674,7 +38674,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1400" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="H1400" t="s">
         <v>9</v>
@@ -38700,7 +38700,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1401" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="H1401" t="s">
         <v>9</v>
@@ -38726,7 +38726,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1402" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="H1402" t="s">
         <v>9</v>
@@ -38752,7 +38752,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1403" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="H1403" t="s">
         <v>9</v>
@@ -38778,7 +38778,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1404" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="H1404" t="s">
         <v>9</v>
@@ -38804,7 +38804,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1405" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="H1405" t="s">
         <v>9</v>
@@ -38830,7 +38830,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1406" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="H1406" t="s">
         <v>9</v>
@@ -38856,7 +38856,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G1407" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="H1407" t="s">
         <v>9</v>
@@ -38882,7 +38882,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1408" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="H1408" t="s">
         <v>9</v>
@@ -38908,7 +38908,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1409" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="H1409" t="s">
         <v>9</v>
@@ -38934,7 +38934,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1410" t="s">
-        <v>327</v>
+        <v>384</v>
       </c>
       <c r="H1410" t="s">
         <v>9</v>
@@ -38960,7 +38960,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1411" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="H1411" t="s">
         <v>9</v>
@@ -38986,7 +38986,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1412" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="H1412" t="s">
         <v>9</v>
@@ -39012,7 +39012,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1413" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="H1413" t="s">
         <v>9</v>
@@ -39038,7 +39038,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1414" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H1414" t="s">
         <v>9</v>
@@ -39090,7 +39090,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1416" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="H1416" t="s">
         <v>9</v>
@@ -39116,7 +39116,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G1417" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="H1417" t="s">
         <v>9</v>
@@ -39142,7 +39142,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1418" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H1418" t="s">
         <v>9</v>
@@ -39194,7 +39194,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1420" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="H1420" t="s">
         <v>9</v>
@@ -39272,7 +39272,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1423" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H1423" t="s">
         <v>9</v>
@@ -39298,7 +39298,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1424" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="H1424" t="s">
         <v>9</v>
@@ -39506,7 +39506,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1432" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="H1432" t="s">
         <v>9</v>
@@ -39532,7 +39532,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1433" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="H1433" t="s">
         <v>9</v>
@@ -39792,7 +39792,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1443" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H1443" t="s">
         <v>9</v>
@@ -39818,7 +39818,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1444" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H1444" t="s">
         <v>9</v>
@@ -39844,7 +39844,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1445" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H1445" t="s">
         <v>9</v>
@@ -39922,7 +39922,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1448" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="H1448" t="s">
         <v>9</v>
@@ -40026,7 +40026,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1452" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="H1452" t="s">
         <v>9</v>
@@ -40052,7 +40052,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1453" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="H1453" t="s">
         <v>9</v>
@@ -40078,7 +40078,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1454" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H1454" t="s">
         <v>9</v>
@@ -40104,7 +40104,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1455" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H1455" t="s">
         <v>9</v>
@@ -42938,7 +42938,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1564" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H1564" t="s">
         <v>9</v>
@@ -42964,7 +42964,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G1565" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="H1565" t="s">
         <v>9</v>
@@ -42990,7 +42990,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1566" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="H1566" t="s">
         <v>9</v>
@@ -43016,7 +43016,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1567" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="H1567" t="s">
         <v>9</v>
@@ -43042,7 +43042,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1568" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H1568" t="s">
         <v>9</v>
@@ -43068,7 +43068,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1569" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H1569" t="s">
         <v>9</v>
@@ -43094,7 +43094,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1570" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H1570" t="s">
         <v>9</v>
@@ -43120,7 +43120,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1571" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="H1571" t="s">
         <v>9</v>
@@ -43146,7 +43146,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1572" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="H1572" t="s">
         <v>9</v>
@@ -43172,7 +43172,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G1573" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="H1573" t="s">
         <v>9</v>
@@ -43224,7 +43224,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1575" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="H1575" t="s">
         <v>9</v>
@@ -43250,7 +43250,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1576" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="H1576" t="s">
         <v>9</v>
@@ -43276,7 +43276,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1577" t="s">
-        <v>327</v>
+        <v>384</v>
       </c>
       <c r="H1577" t="s">
         <v>9</v>
@@ -43302,7 +43302,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G1578" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="H1578" t="s">
         <v>9</v>
@@ -43354,7 +43354,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1580" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="H1580" t="s">
         <v>9</v>
@@ -44134,7 +44134,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G1610" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="H1610" t="s">
         <v>9</v>
@@ -44186,7 +44186,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G1612" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="H1612" t="s">
         <v>9</v>
@@ -44238,7 +44238,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G1614" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="H1614" t="s">
         <v>9</v>
@@ -44342,7 +44342,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G1618" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="H1618" t="s">
         <v>9</v>
@@ -44368,7 +44368,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G1619" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="H1619" t="s">
         <v>9</v>
@@ -44394,7 +44394,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1620" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="H1620" t="s">
         <v>9</v>
@@ -44420,7 +44420,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G1621" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="H1621" t="s">
         <v>9</v>
@@ -44966,7 +44966,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G1642" t="s">
-        <v>463</v>
+        <v>497</v>
       </c>
       <c r="H1642" t="s">
         <v>9</v>
@@ -44992,7 +44992,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G1643" t="s">
-        <v>463</v>
+        <v>497</v>
       </c>
       <c r="H1643" t="s">
         <v>9</v>
@@ -45018,7 +45018,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G1644" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="H1644" t="s">
         <v>9</v>
@@ -45070,7 +45070,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G1646" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H1646" t="s">
         <v>9</v>
@@ -45096,7 +45096,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1647" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H1647" t="s">
         <v>9</v>
@@ -45122,7 +45122,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G1648" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="H1648" t="s">
         <v>9</v>
@@ -45174,7 +45174,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1650" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="H1650" t="s">
         <v>9</v>
@@ -45200,7 +45200,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1651" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="H1651" t="s">
         <v>9</v>
@@ -45226,7 +45226,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1652" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="H1652" t="s">
         <v>9</v>
@@ -45252,7 +45252,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G1653" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="H1653" t="s">
         <v>9</v>
@@ -45278,7 +45278,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G1654" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="H1654" t="s">
         <v>9</v>
@@ -45304,7 +45304,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G1655" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="H1655" t="s">
         <v>9</v>
@@ -45330,7 +45330,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G1656" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="H1656" t="s">
         <v>9</v>
@@ -45356,7 +45356,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G1657" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="H1657" t="s">
         <v>9</v>
@@ -45408,7 +45408,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G1659" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="H1659" t="s">
         <v>9</v>
@@ -45434,7 +45434,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1660" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="H1660" t="s">
         <v>9</v>
@@ -45460,7 +45460,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G1661" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="H1661" t="s">
         <v>9</v>
@@ -45486,7 +45486,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1662" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H1662" t="s">
         <v>9</v>
@@ -45512,7 +45512,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1663" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H1663" t="s">
         <v>9</v>
@@ -45538,7 +45538,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1664" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H1664" t="s">
         <v>9</v>
@@ -45564,7 +45564,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1665" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H1665" t="s">
         <v>9</v>
@@ -45590,7 +45590,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1666" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H1666" t="s">
         <v>9</v>
@@ -45616,7 +45616,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1667" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="H1667" t="s">
         <v>9</v>
@@ -45642,7 +45642,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G1668" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="H1668" t="s">
         <v>9</v>
@@ -45668,7 +45668,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1669" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="H1669" t="s">
         <v>9</v>
@@ -45694,7 +45694,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1670" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="H1670" t="s">
         <v>9</v>
@@ -45720,7 +45720,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G1671" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="H1671" t="s">
         <v>9</v>
@@ -45746,7 +45746,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1672" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="H1672" t="s">
         <v>9</v>
@@ -45772,7 +45772,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G1673" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="H1673" t="s">
         <v>9</v>
@@ -45798,7 +45798,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G1674" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="H1674" t="s">
         <v>9</v>
@@ -45824,7 +45824,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G1675" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="H1675" t="s">
         <v>9</v>
@@ -45850,7 +45850,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G1676" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="H1676" t="s">
         <v>9</v>
@@ -45876,7 +45876,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1677" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="H1677" t="s">
         <v>9</v>
@@ -45902,7 +45902,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G1678" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="H1678" t="s">
         <v>9</v>
@@ -45928,7 +45928,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G1679" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="H1679" t="s">
         <v>9</v>
@@ -45954,7 +45954,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1680" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="H1680" t="s">
         <v>9</v>
@@ -45980,7 +45980,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G1681" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="H1681" t="s">
         <v>9</v>
@@ -46032,7 +46032,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1683" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="H1683" t="s">
         <v>9</v>
@@ -46058,7 +46058,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G1684" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="H1684" t="s">
         <v>9</v>
@@ -46110,7 +46110,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G1686" t="s">
-        <v>463</v>
+        <v>497</v>
       </c>
       <c r="H1686" t="s">
         <v>9</v>
@@ -46136,7 +46136,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G1687" t="s">
-        <v>463</v>
+        <v>497</v>
       </c>
       <c r="H1687" t="s">
         <v>9</v>
@@ -46162,7 +46162,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G1688" t="s">
-        <v>463</v>
+        <v>497</v>
       </c>
       <c r="H1688" t="s">
         <v>9</v>
@@ -46188,7 +46188,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1689" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="H1689" t="s">
         <v>9</v>
@@ -46214,7 +46214,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G1690" t="s">
-        <v>463</v>
+        <v>497</v>
       </c>
       <c r="H1690" t="s">
         <v>9</v>
@@ -46240,7 +46240,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G1691" t="s">
-        <v>463</v>
+        <v>497</v>
       </c>
       <c r="H1691" t="s">
         <v>9</v>
@@ -46266,7 +46266,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G1692" t="s">
-        <v>463</v>
+        <v>497</v>
       </c>
       <c r="H1692" t="s">
         <v>9</v>
@@ -46292,7 +46292,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1693" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H1693" t="s">
         <v>9</v>
@@ -46318,7 +46318,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G1694" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="H1694" t="s">
         <v>9</v>
@@ -46344,7 +46344,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G1695" t="s">
-        <v>463</v>
+        <v>497</v>
       </c>
       <c r="H1695" t="s">
         <v>9</v>
@@ -46422,7 +46422,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G1698" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="H1698" t="s">
         <v>9</v>
@@ -46448,7 +46448,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G1699" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="H1699" t="s">
         <v>9</v>
@@ -46474,7 +46474,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1700" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="H1700" t="s">
         <v>9</v>
@@ -46526,7 +46526,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G1702" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="H1702" t="s">
         <v>9</v>
@@ -46552,7 +46552,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1703" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="H1703" t="s">
         <v>9</v>
@@ -46578,7 +46578,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G1704" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="H1704" t="s">
         <v>9</v>
@@ -46604,7 +46604,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G1705" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="H1705" t="s">
         <v>9</v>
@@ -46630,7 +46630,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1706" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="H1706" t="s">
         <v>9</v>
@@ -46656,7 +46656,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1707" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="H1707" t="s">
         <v>9</v>
@@ -46760,7 +46760,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G1711" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="H1711" t="s">
         <v>9</v>
@@ -46786,7 +46786,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1712" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="H1712" t="s">
         <v>9</v>
@@ -46812,7 +46812,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G1713" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="H1713" t="s">
         <v>9</v>
@@ -46838,7 +46838,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G1714" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="H1714" t="s">
         <v>9</v>
@@ -46864,7 +46864,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G1715" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="H1715" t="s">
         <v>9</v>
@@ -46890,7 +46890,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1716" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="H1716" t="s">
         <v>9</v>
@@ -46916,7 +46916,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G1717" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="H1717" t="s">
         <v>9</v>
@@ -46942,7 +46942,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G1718" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="H1718" t="s">
         <v>9</v>
@@ -46968,7 +46968,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1719" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="H1719" t="s">
         <v>9</v>
@@ -46994,7 +46994,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G1720" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="H1720" t="s">
         <v>9</v>
@@ -47020,7 +47020,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G1721" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="H1721" t="s">
         <v>9</v>
@@ -47046,7 +47046,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G1722" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="H1722" t="s">
         <v>9</v>
@@ -47072,7 +47072,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G1723" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="H1723" t="s">
         <v>9</v>
@@ -47098,7 +47098,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G1724" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="H1724" t="s">
         <v>9</v>
@@ -47124,7 +47124,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G1725" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="H1725" t="s">
         <v>9</v>
@@ -47150,7 +47150,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G1726" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="H1726" t="s">
         <v>9</v>
@@ -47176,7 +47176,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G1727" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="H1727" t="s">
         <v>9</v>
@@ -47202,7 +47202,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G1728" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="H1728" t="s">
         <v>9</v>
@@ -47228,7 +47228,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G1729" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="H1729" t="s">
         <v>9</v>
@@ -47254,7 +47254,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G1730" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="H1730" t="s">
         <v>9</v>
@@ -47280,7 +47280,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G1731" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="H1731" t="s">
         <v>9</v>
@@ -47306,7 +47306,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G1732" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="H1732" t="s">
         <v>9</v>
@@ -47332,7 +47332,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G1733" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="H1733" t="s">
         <v>9</v>
@@ -47358,7 +47358,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1734" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="H1734" t="s">
         <v>9</v>
@@ -47384,7 +47384,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1735" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="H1735" t="s">
         <v>9</v>
@@ -47410,7 +47410,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G1736" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="H1736" t="s">
         <v>9</v>
@@ -47436,7 +47436,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1737" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="H1737" t="s">
         <v>9</v>
@@ -47462,7 +47462,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G1738" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="H1738" t="s">
         <v>9</v>
@@ -47488,7 +47488,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G1739" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="H1739" t="s">
         <v>9</v>
@@ -47514,7 +47514,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G1740" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="H1740" t="s">
         <v>9</v>
@@ -47540,7 +47540,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1741" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H1741" t="s">
         <v>9</v>
@@ -47566,7 +47566,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1742" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H1742" t="s">
         <v>9</v>
@@ -47592,7 +47592,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G1743" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="H1743" t="s">
         <v>9</v>
@@ -47618,7 +47618,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G1744" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="H1744" t="s">
         <v>9</v>
@@ -47644,7 +47644,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G1745" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="H1745" t="s">
         <v>9</v>
@@ -47670,7 +47670,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G1746" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="H1746" t="s">
         <v>9</v>
@@ -47696,7 +47696,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1747" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="H1747" t="s">
         <v>9</v>
@@ -47722,7 +47722,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G1748" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="H1748" t="s">
         <v>9</v>
@@ -47748,7 +47748,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G1749" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="H1749" t="s">
         <v>9</v>
@@ -47774,7 +47774,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1750" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H1750" t="s">
         <v>9</v>
@@ -47800,7 +47800,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G1751" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="H1751" t="s">
         <v>9</v>
@@ -47826,7 +47826,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1752" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="H1752" t="s">
         <v>9</v>
@@ -47852,7 +47852,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G1753" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="H1753" t="s">
         <v>9</v>
@@ -47878,7 +47878,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G1754" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="H1754" t="s">
         <v>9</v>
@@ -47904,7 +47904,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G1755" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="H1755" t="s">
         <v>9</v>
@@ -47930,7 +47930,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G1756" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="H1756" t="s">
         <v>9</v>
@@ -47956,7 +47956,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1757" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H1757" t="s">
         <v>9</v>
@@ -47982,7 +47982,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G1758" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="H1758" t="s">
         <v>9</v>
@@ -48008,7 +48008,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G1759" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="H1759" t="s">
         <v>9</v>
@@ -48034,7 +48034,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G1760" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="H1760" t="s">
         <v>9</v>
@@ -48060,7 +48060,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G1761" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="H1761" t="s">
         <v>9</v>
@@ -48086,7 +48086,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G1762" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="H1762" t="s">
         <v>9</v>
@@ -48112,7 +48112,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1763" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="H1763" t="s">
         <v>9</v>
@@ -48138,7 +48138,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G1764" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="H1764" t="s">
         <v>9</v>
@@ -48164,7 +48164,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G1765" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="H1765" t="s">
         <v>9</v>
@@ -48190,7 +48190,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G1766" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="H1766" t="s">
         <v>9</v>
@@ -48216,7 +48216,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G1767" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="H1767" t="s">
         <v>9</v>
@@ -48242,7 +48242,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G1768" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="H1768" t="s">
         <v>9</v>
@@ -48268,7 +48268,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G1769" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="H1769" t="s">
         <v>9</v>
@@ -48294,7 +48294,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G1770" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="H1770" t="s">
         <v>9</v>
@@ -48320,7 +48320,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G1771" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="H1771" t="s">
         <v>9</v>
@@ -48346,7 +48346,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1772" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="H1772" t="s">
         <v>9</v>
@@ -48372,7 +48372,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1773" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="H1773" t="s">
         <v>9</v>
@@ -48398,7 +48398,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1774" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="H1774" t="s">
         <v>9</v>
@@ -48424,7 +48424,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1775" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="H1775" t="s">
         <v>9</v>
@@ -48450,7 +48450,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1776" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="H1776" t="s">
         <v>9</v>
@@ -48476,7 +48476,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1777" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="H1777" t="s">
         <v>9</v>
@@ -48502,7 +48502,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1778" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="H1778" t="s">
         <v>9</v>
@@ -48528,7 +48528,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1779" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="H1779" t="s">
         <v>9</v>
@@ -48554,7 +48554,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1780" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="H1780" t="s">
         <v>9</v>
@@ -48580,7 +48580,7 @@
         <v>3.25</v>
       </c>
       <c r="G1781" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="H1781" t="s">
         <v>9</v>
@@ -48606,7 +48606,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G1782" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="H1782" t="s">
         <v>9</v>
@@ -48632,7 +48632,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G1783" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="H1783" t="s">
         <v>9</v>
@@ -48658,7 +48658,7 @@
         <v>3.25</v>
       </c>
       <c r="G1784" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="H1784" t="s">
         <v>9</v>
@@ -48684,7 +48684,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G1785" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="H1785" t="s">
         <v>9</v>
@@ -48710,7 +48710,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G1786" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="H1786" t="s">
         <v>9</v>
@@ -48736,7 +48736,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G1787" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="H1787" t="s">
         <v>9</v>
@@ -48762,7 +48762,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G1788" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="H1788" t="s">
         <v>9</v>
@@ -48788,7 +48788,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1789" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H1789" t="s">
         <v>9</v>
@@ -48814,7 +48814,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1790" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H1790" t="s">
         <v>9</v>
@@ -48840,7 +48840,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1791" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H1791" t="s">
         <v>9</v>
@@ -48866,7 +48866,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1792" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H1792" t="s">
         <v>9</v>
@@ -48892,7 +48892,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G1793" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="H1793" t="s">
         <v>9</v>
@@ -48918,7 +48918,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1794" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H1794" t="s">
         <v>9</v>
@@ -48944,7 +48944,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G1795" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="H1795" t="s">
         <v>9</v>
@@ -48970,7 +48970,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G1796" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="H1796" t="s">
         <v>9</v>
@@ -48996,7 +48996,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1797" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="H1797" t="s">
         <v>9</v>
@@ -49022,7 +49022,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G1798" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="H1798" t="s">
         <v>9</v>
@@ -49048,7 +49048,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G1799" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="H1799" t="s">
         <v>9</v>
@@ -49074,7 +49074,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G1800" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="H1800" t="s">
         <v>9</v>
@@ -49100,7 +49100,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1801" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H1801" t="s">
         <v>9</v>
@@ -49126,7 +49126,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G1802" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="H1802" t="s">
         <v>9</v>
@@ -49152,7 +49152,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G1803" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="H1803" t="s">
         <v>9</v>
@@ -49178,7 +49178,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G1804" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="H1804" t="s">
         <v>9</v>
@@ -49204,7 +49204,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G1805" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="H1805" t="s">
         <v>9</v>
@@ -49230,7 +49230,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G1806" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="H1806" t="s">
         <v>9</v>
@@ -49256,7 +49256,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G1807" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="H1807" t="s">
         <v>9</v>
@@ -49282,7 +49282,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G1808" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="H1808" t="s">
         <v>9</v>
@@ -49308,7 +49308,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1809" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="H1809" t="s">
         <v>9</v>
@@ -49334,7 +49334,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G1810" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="H1810" t="s">
         <v>9</v>
@@ -49360,7 +49360,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1811" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="H1811" t="s">
         <v>9</v>
@@ -49386,7 +49386,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G1812" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="H1812" t="s">
         <v>9</v>
@@ -49412,7 +49412,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G1813" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="H1813" t="s">
         <v>9</v>
@@ -49438,7 +49438,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G1814" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="H1814" t="s">
         <v>9</v>
@@ -49464,7 +49464,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1815" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H1815" t="s">
         <v>9</v>
@@ -49490,7 +49490,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G1816" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="H1816" t="s">
         <v>9</v>
@@ -49516,7 +49516,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G1817" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="H1817" t="s">
         <v>9</v>
@@ -49542,7 +49542,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G1818" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="H1818" t="s">
         <v>9</v>
@@ -49568,7 +49568,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1819" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H1819" t="s">
         <v>9</v>
@@ -49594,7 +49594,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1820" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H1820" t="s">
         <v>9</v>
@@ -49620,7 +49620,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1821" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H1821" t="s">
         <v>9</v>
@@ -49646,7 +49646,7 @@
         <v>3.25</v>
       </c>
       <c r="G1822" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="H1822" t="s">
         <v>9</v>
@@ -49672,7 +49672,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G1823" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="H1823" t="s">
         <v>9</v>
@@ -49698,7 +49698,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G1824" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="H1824" t="s">
         <v>9</v>
@@ -49724,7 +49724,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G1825" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="H1825" t="s">
         <v>9</v>
@@ -49750,7 +49750,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G1826" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H1826" t="s">
         <v>9</v>
@@ -49776,7 +49776,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G1827" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="H1827" t="s">
         <v>9</v>
@@ -49802,7 +49802,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G1828" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="H1828" t="s">
         <v>9</v>
@@ -49828,7 +49828,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G1829" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="H1829" t="s">
         <v>9</v>
@@ -49854,7 +49854,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1830" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="H1830" t="s">
         <v>9</v>
@@ -49880,7 +49880,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G1831" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="H1831" t="s">
         <v>9</v>
@@ -49906,7 +49906,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1832" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="H1832" t="s">
         <v>9</v>
@@ -49932,7 +49932,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G1833" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="H1833" t="s">
         <v>9</v>
@@ -49958,7 +49958,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G1834" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="H1834" t="s">
         <v>9</v>
@@ -49984,7 +49984,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G1835" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="H1835" t="s">
         <v>9</v>
@@ -50010,7 +50010,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G1836" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="H1836" t="s">
         <v>9</v>
@@ -50036,7 +50036,7 @@
         <v>3.25</v>
       </c>
       <c r="G1837" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="H1837" t="s">
         <v>9</v>
@@ -50062,7 +50062,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G1838" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="H1838" t="s">
         <v>9</v>
@@ -50088,7 +50088,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G1839" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="H1839" t="s">
         <v>9</v>
@@ -50114,7 +50114,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1840" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H1840" t="s">
         <v>9</v>
@@ -50140,7 +50140,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G1841" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="H1841" t="s">
         <v>9</v>
@@ -50166,7 +50166,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G1842" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="H1842" t="s">
         <v>9</v>
@@ -50192,7 +50192,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G1843" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="H1843" t="s">
         <v>9</v>
@@ -50218,7 +50218,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G1844" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="H1844" t="s">
         <v>9</v>
@@ -50244,7 +50244,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1845" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="H1845" t="s">
         <v>9</v>
@@ -50270,7 +50270,7 @@
         <v>3.25</v>
       </c>
       <c r="G1846" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="H1846" t="s">
         <v>9</v>
@@ -50296,7 +50296,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1847" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="H1847" t="s">
         <v>9</v>
@@ -50322,7 +50322,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G1848" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="H1848" t="s">
         <v>9</v>
@@ -50348,7 +50348,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G1849" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="H1849" t="s">
         <v>9</v>
@@ -50374,7 +50374,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1850" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="H1850" t="s">
         <v>9</v>
@@ -50400,7 +50400,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1851" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="H1851" t="s">
         <v>9</v>
@@ -50426,7 +50426,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1852" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="H1852" t="s">
         <v>9</v>
@@ -50452,7 +50452,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G1853" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="H1853" t="s">
         <v>9</v>
@@ -50478,7 +50478,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1854" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="H1854" t="s">
         <v>9</v>
@@ -50504,7 +50504,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1855" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="H1855" t="s">
         <v>9</v>
@@ -50530,7 +50530,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G1856" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="H1856" t="s">
         <v>9</v>
@@ -50556,7 +50556,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1857" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="H1857" t="s">
         <v>9</v>
@@ -50582,7 +50582,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1858" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="H1858" t="s">
         <v>9</v>
@@ -50608,7 +50608,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G1859" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="H1859" t="s">
         <v>9</v>
@@ -50634,7 +50634,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G1860" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="H1860" t="s">
         <v>9</v>
@@ -50660,7 +50660,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G1861" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="H1861" t="s">
         <v>9</v>
@@ -50686,7 +50686,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G1862" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="H1862" t="s">
         <v>9</v>
@@ -50712,7 +50712,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1863" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="H1863" t="s">
         <v>9</v>
@@ -50738,7 +50738,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G1864" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="H1864" t="s">
         <v>9</v>
@@ -50764,7 +50764,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G1865" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="H1865" t="s">
         <v>9</v>
@@ -50790,7 +50790,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G1866" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="H1866" t="s">
         <v>9</v>
@@ -50816,7 +50816,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G1867" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="H1867" t="s">
         <v>9</v>
@@ -50842,7 +50842,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G1868" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="H1868" t="s">
         <v>9</v>
@@ -50868,7 +50868,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G1869" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="H1869" t="s">
         <v>9</v>
@@ -50894,7 +50894,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G1870" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="H1870" t="s">
         <v>9</v>
@@ -50920,7 +50920,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G1871" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="H1871" t="s">
         <v>9</v>
@@ -50946,7 +50946,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1872" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="H1872" t="s">
         <v>9</v>
@@ -50972,7 +50972,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1873" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="H1873" t="s">
         <v>9</v>
@@ -50998,7 +50998,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1874" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="H1874" t="s">
         <v>9</v>
@@ -51024,7 +51024,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G1875" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="H1875" t="s">
         <v>9</v>
@@ -51050,7 +51050,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1876" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="H1876" t="s">
         <v>9</v>
@@ -51076,7 +51076,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1877" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="H1877" t="s">
         <v>9</v>
@@ -51102,7 +51102,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G1878" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="H1878" t="s">
         <v>9</v>
@@ -51128,7 +51128,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G1879" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="H1879" t="s">
         <v>9</v>
@@ -51154,7 +51154,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G1880" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="H1880" t="s">
         <v>9</v>
@@ -51180,7 +51180,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G1881" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="H1881" t="s">
         <v>9</v>
@@ -51206,7 +51206,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G1882" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="H1882" t="s">
         <v>9</v>
@@ -51232,7 +51232,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G1883" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="H1883" t="s">
         <v>9</v>
@@ -51258,7 +51258,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G1884" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="H1884" t="s">
         <v>9</v>
@@ -51284,7 +51284,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1885" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="H1885" t="s">
         <v>9</v>
@@ -51310,7 +51310,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1886" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="H1886" t="s">
         <v>9</v>
@@ -51336,7 +51336,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1887" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="H1887" t="s">
         <v>9</v>
@@ -51362,7 +51362,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1888" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="H1888" t="s">
         <v>9</v>
@@ -51388,7 +51388,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G1889" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="H1889" t="s">
         <v>9</v>
@@ -51414,7 +51414,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1890" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="H1890" t="s">
         <v>9</v>
@@ -51440,7 +51440,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1891" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="H1891" t="s">
         <v>9</v>
@@ -51466,7 +51466,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G1892" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="H1892" t="s">
         <v>9</v>
@@ -51492,7 +51492,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1893" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="H1893" t="s">
         <v>9</v>
@@ -51518,7 +51518,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G1894" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="H1894" t="s">
         <v>9</v>
@@ -51544,7 +51544,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1895" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="H1895" t="s">
         <v>9</v>
@@ -51570,7 +51570,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1896" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="H1896" t="s">
         <v>9</v>
@@ -51596,7 +51596,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1897" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="H1897" t="s">
         <v>9</v>
@@ -51622,7 +51622,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1898" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="H1898" t="s">
         <v>9</v>
@@ -51648,7 +51648,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1899" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="H1899" t="s">
         <v>9</v>
@@ -51674,7 +51674,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1900" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="H1900" t="s">
         <v>9</v>
@@ -51700,7 +51700,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1901" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="H1901" t="s">
         <v>9</v>
@@ -51726,7 +51726,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1902" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="H1902" t="s">
         <v>9</v>
@@ -51752,7 +51752,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G1903" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="H1903" t="s">
         <v>9</v>
@@ -51778,7 +51778,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G1904" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="H1904" t="s">
         <v>9</v>
@@ -51804,7 +51804,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1905" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="H1905" t="s">
         <v>9</v>
@@ -51830,7 +51830,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1906" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="H1906" t="s">
         <v>9</v>
@@ -51856,7 +51856,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1907" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="H1907" t="s">
         <v>9</v>
@@ -51882,7 +51882,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1908" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="H1908" t="s">
         <v>9</v>
@@ -51908,7 +51908,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1909" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="H1909" t="s">
         <v>9</v>
@@ -51934,7 +51934,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G1910" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="H1910" t="s">
         <v>9</v>
@@ -51960,7 +51960,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1911" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="H1911" t="s">
         <v>9</v>
@@ -51986,7 +51986,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1912" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="H1912" t="s">
         <v>9</v>
@@ -52012,7 +52012,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1913" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="H1913" t="s">
         <v>9</v>
@@ -52038,7 +52038,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1914" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="H1914" t="s">
         <v>9</v>
@@ -52064,7 +52064,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1915" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="H1915" t="s">
         <v>9</v>
@@ -52090,7 +52090,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1916" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="H1916" t="s">
         <v>9</v>
@@ -52116,7 +52116,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1917" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="H1917" t="s">
         <v>9</v>
@@ -52142,7 +52142,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G1918" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="H1918" t="s">
         <v>9</v>
@@ -52168,7 +52168,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G1919" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="H1919" t="s">
         <v>9</v>
@@ -52194,7 +52194,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G1920" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="H1920" t="s">
         <v>9</v>
@@ -52220,7 +52220,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1921" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="H1921" t="s">
         <v>9</v>
@@ -52246,7 +52246,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1922" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="H1922" t="s">
         <v>9</v>
@@ -52272,7 +52272,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G1923" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="H1923" t="s">
         <v>9</v>
@@ -52298,7 +52298,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G1924" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="H1924" t="s">
         <v>9</v>
@@ -52324,7 +52324,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1925" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="H1925" t="s">
         <v>9</v>
@@ -52350,7 +52350,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G1926" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="H1926" t="s">
         <v>9</v>
@@ -52376,7 +52376,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1927" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="H1927" t="s">
         <v>9</v>
@@ -52402,7 +52402,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G1928" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="H1928" t="s">
         <v>9</v>
@@ -52428,7 +52428,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G1929" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="H1929" t="s">
         <v>9</v>
@@ -52454,7 +52454,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G1930" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="H1930" t="s">
         <v>9</v>
@@ -52480,7 +52480,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G1931" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="H1931" t="s">
         <v>9</v>
@@ -52506,7 +52506,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G1932" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="H1932" t="s">
         <v>9</v>
@@ -52532,7 +52532,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G1933" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="H1933" t="s">
         <v>9</v>
@@ -52558,7 +52558,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G1934" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="H1934" t="s">
         <v>9</v>
@@ -52584,7 +52584,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1935" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="H1935" t="s">
         <v>9</v>
@@ -52610,7 +52610,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1936" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="H1936" t="s">
         <v>9</v>
@@ -52636,7 +52636,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1937" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="H1937" t="s">
         <v>9</v>
@@ -52662,7 +52662,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1938" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="H1938" t="s">
         <v>9</v>
@@ -52688,7 +52688,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1939" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="H1939" t="s">
         <v>9</v>
@@ -52714,7 +52714,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G1940" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="H1940" t="s">
         <v>9</v>
@@ -52740,7 +52740,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1941" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="H1941" t="s">
         <v>9</v>
@@ -52766,7 +52766,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1942" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="H1942" t="s">
         <v>9</v>
@@ -52792,7 +52792,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1943" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="H1943" t="s">
         <v>9</v>
@@ -52818,7 +52818,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1944" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="H1944" t="s">
         <v>9</v>
@@ -52844,7 +52844,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1945" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="H1945" t="s">
         <v>9</v>
@@ -52870,7 +52870,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G1946" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="H1946" t="s">
         <v>9</v>
@@ -52896,7 +52896,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1947" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="H1947" t="s">
         <v>9</v>
@@ -52922,7 +52922,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1948" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="H1948" t="s">
         <v>9</v>
@@ -52948,7 +52948,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1949" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="H1949" t="s">
         <v>9</v>
@@ -52974,7 +52974,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G1950" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="H1950" t="s">
         <v>9</v>
@@ -53000,7 +53000,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G1951" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="H1951" t="s">
         <v>9</v>
@@ -53026,7 +53026,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1952" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="H1952" t="s">
         <v>9</v>
@@ -53052,7 +53052,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1953" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="H1953" t="s">
         <v>9</v>
@@ -53078,7 +53078,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1954" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="H1954" t="s">
         <v>9</v>
@@ -53104,7 +53104,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G1955" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="H1955" t="s">
         <v>9</v>
@@ -53130,7 +53130,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G1956" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="H1956" t="s">
         <v>9</v>
@@ -53156,7 +53156,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G1957" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="H1957" t="s">
         <v>9</v>
@@ -53182,7 +53182,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1958" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="H1958" t="s">
         <v>9</v>
@@ -53208,7 +53208,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1959" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="H1959" t="s">
         <v>9</v>
@@ -53234,7 +53234,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1960" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="H1960" t="s">
         <v>9</v>
@@ -53260,7 +53260,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G1961" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="H1961" t="s">
         <v>9</v>
@@ -53286,7 +53286,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G1962" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="H1962" t="s">
         <v>9</v>
@@ -53312,7 +53312,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G1963" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="H1963" t="s">
         <v>9</v>
@@ -53338,7 +53338,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G1964" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="H1964" t="s">
         <v>9</v>
@@ -53364,7 +53364,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G1965" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="H1965" t="s">
         <v>9</v>
@@ -53390,7 +53390,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G1966" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="H1966" t="s">
         <v>9</v>
@@ -53416,7 +53416,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1967" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="H1967" t="s">
         <v>9</v>
@@ -53442,7 +53442,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G1968" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="H1968" t="s">
         <v>9</v>
@@ -53468,7 +53468,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G1969" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="H1969" t="s">
         <v>9</v>
@@ -53494,7 +53494,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G1970" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="H1970" t="s">
         <v>9</v>
@@ -53520,7 +53520,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G1971" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="H1971" t="s">
         <v>9</v>
@@ -53546,7 +53546,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G1972" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="H1972" t="s">
         <v>9</v>
@@ -53572,7 +53572,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G1973" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="H1973" t="s">
         <v>9</v>
@@ -53598,7 +53598,7 @@
         <v>3</v>
       </c>
       <c r="G1974" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="H1974" t="s">
         <v>9</v>
@@ -53624,7 +53624,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1975" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="H1975" t="s">
         <v>9</v>
@@ -53650,7 +53650,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G1976" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="H1976" t="s">
         <v>9</v>
@@ -53676,7 +53676,7 @@
         <v>3</v>
       </c>
       <c r="G1977" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="H1977" t="s">
         <v>9</v>
@@ -53702,7 +53702,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G1978" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="H1978" t="s">
         <v>9</v>
@@ -53728,7 +53728,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G1979" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="H1979" t="s">
         <v>9</v>
@@ -53754,7 +53754,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1980" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="H1980" t="s">
         <v>9</v>
@@ -53780,7 +53780,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G1981" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="H1981" t="s">
         <v>9</v>
@@ -53806,7 +53806,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G1982" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="H1982" t="s">
         <v>9</v>
@@ -53832,7 +53832,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1983" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="H1983" t="s">
         <v>9</v>
@@ -53858,7 +53858,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1984" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="H1984" t="s">
         <v>9</v>
@@ -53884,7 +53884,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G1985" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="H1985" t="s">
         <v>9</v>
@@ -53910,7 +53910,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1986" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="H1986" t="s">
         <v>9</v>
@@ -53936,7 +53936,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1987" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="H1987" t="s">
         <v>9</v>
@@ -53962,7 +53962,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G1988" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="H1988" t="s">
         <v>9</v>
@@ -53988,7 +53988,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G1989" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="H1989" t="s">
         <v>9</v>
@@ -54014,7 +54014,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G1990" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="H1990" t="s">
         <v>9</v>
@@ -54040,7 +54040,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G1991" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="H1991" t="s">
         <v>9</v>
@@ -54066,7 +54066,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1992" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="H1992" t="s">
         <v>9</v>
@@ -54092,7 +54092,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1993" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="H1993" t="s">
         <v>9</v>
@@ -54118,7 +54118,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1994" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="H1994" t="s">
         <v>9</v>
@@ -54144,7 +54144,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1995" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="H1995" t="s">
         <v>9</v>
@@ -54170,7 +54170,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G1996" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="H1996" t="s">
         <v>9</v>
@@ -54196,7 +54196,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G1997" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="H1997" t="s">
         <v>9</v>
@@ -54222,7 +54222,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1998" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="H1998" t="s">
         <v>9</v>
@@ -54248,7 +54248,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1999" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="H1999" t="s">
         <v>9</v>
@@ -54274,7 +54274,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G2000" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="H2000" t="s">
         <v>9</v>
@@ -54300,7 +54300,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G2001" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="H2001" t="s">
         <v>9</v>
@@ -54326,7 +54326,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G2002" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="H2002" t="s">
         <v>9</v>
@@ -54352,7 +54352,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G2003" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="H2003" t="s">
         <v>9</v>
@@ -54378,7 +54378,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G2004" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="H2004" t="s">
         <v>9</v>
@@ -54404,7 +54404,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G2005" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="H2005" t="s">
         <v>9</v>
@@ -54430,7 +54430,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G2006" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="H2006" t="s">
         <v>9</v>
@@ -54456,7 +54456,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G2007" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="H2007" t="s">
         <v>9</v>
@@ -54482,7 +54482,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G2008" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="H2008" t="s">
         <v>9</v>
@@ -54508,7 +54508,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G2009" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="H2009" t="s">
         <v>9</v>
@@ -54534,7 +54534,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G2010" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="H2010" t="s">
         <v>9</v>
@@ -54560,7 +54560,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G2011" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="H2011" t="s">
         <v>9</v>
@@ -54586,7 +54586,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G2012" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="H2012" t="s">
         <v>9</v>
@@ -54612,7 +54612,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G2013" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="H2013" t="s">
         <v>9</v>
@@ -54638,7 +54638,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2014" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="H2014" t="s">
         <v>9</v>
@@ -54664,7 +54664,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G2015" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="H2015" t="s">
         <v>9</v>
@@ -54690,7 +54690,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G2016" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="H2016" t="s">
         <v>9</v>
@@ -54716,7 +54716,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G2017" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="H2017" t="s">
         <v>9</v>
@@ -54742,7 +54742,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2018" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="H2018" t="s">
         <v>9</v>
@@ -54768,7 +54768,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2019" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="H2019" t="s">
         <v>9</v>
@@ -54794,7 +54794,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G2020" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="H2020" t="s">
         <v>9</v>
@@ -54820,7 +54820,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2021" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="H2021" t="s">
         <v>9</v>
@@ -54846,7 +54846,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G2022" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="H2022" t="s">
         <v>9</v>
@@ -54872,7 +54872,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2023" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="H2023" t="s">
         <v>9</v>
@@ -54898,7 +54898,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2024" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="H2024" t="s">
         <v>9</v>
@@ -54924,7 +54924,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G2025" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="H2025" t="s">
         <v>9</v>
@@ -54950,7 +54950,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G2026" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="H2026" t="s">
         <v>9</v>
@@ -54976,7 +54976,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2027" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="H2027" t="s">
         <v>9</v>
@@ -55002,7 +55002,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2028" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="H2028" t="s">
         <v>9</v>
@@ -55028,7 +55028,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G2029" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="H2029" t="s">
         <v>9</v>
@@ -55054,7 +55054,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2030" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="H2030" t="s">
         <v>9</v>
@@ -55080,7 +55080,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G2031" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="H2031" t="s">
         <v>9</v>
@@ -55106,7 +55106,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G2032" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="H2032" t="s">
         <v>9</v>
@@ -55132,7 +55132,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G2033" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="H2033" t="s">
         <v>9</v>
@@ -55158,7 +55158,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G2034" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="H2034" t="s">
         <v>9</v>
@@ -55184,7 +55184,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G2035" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="H2035" t="s">
         <v>9</v>
@@ -55210,7 +55210,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2036" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="H2036" t="s">
         <v>9</v>
@@ -55236,7 +55236,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G2037" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="H2037" t="s">
         <v>9</v>
@@ -55262,7 +55262,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G2038" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="H2038" t="s">
         <v>9</v>
@@ -55288,7 +55288,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2039" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="H2039" t="s">
         <v>9</v>
@@ -55314,7 +55314,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G2040" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="H2040" t="s">
         <v>9</v>
@@ -55340,7 +55340,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G2041" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="H2041" t="s">
         <v>9</v>
@@ -55366,7 +55366,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G2042" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="H2042" t="s">
         <v>9</v>
@@ -55392,7 +55392,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G2043" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="H2043" t="s">
         <v>9</v>
@@ -55418,7 +55418,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2044" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="H2044" t="s">
         <v>9</v>
@@ -55444,7 +55444,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2045" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="H2045" t="s">
         <v>9</v>
@@ -55470,7 +55470,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2046" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="H2046" t="s">
         <v>9</v>
@@ -55496,7 +55496,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G2047" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="H2047" t="s">
         <v>9</v>
@@ -55522,7 +55522,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2048" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="H2048" t="s">
         <v>9</v>
@@ -55548,7 +55548,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2049" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="H2049" t="s">
         <v>9</v>
@@ -55574,7 +55574,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2050" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="H2050" t="s">
         <v>9</v>
@@ -55600,7 +55600,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G2051" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="H2051" t="s">
         <v>9</v>
@@ -55626,7 +55626,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G2052" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="H2052" t="s">
         <v>9</v>
@@ -55652,7 +55652,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G2053" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="H2053" t="s">
         <v>9</v>
@@ -55678,7 +55678,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2054" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="H2054" t="s">
         <v>9</v>
@@ -55704,7 +55704,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G2055" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="H2055" t="s">
         <v>9</v>
@@ -55730,7 +55730,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2056" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="H2056" t="s">
         <v>9</v>
@@ -55756,7 +55756,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2057" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="H2057" t="s">
         <v>9</v>
@@ -55782,7 +55782,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G2058" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="H2058" t="s">
         <v>9</v>
@@ -55808,7 +55808,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G2059" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="H2059" t="s">
         <v>9</v>
@@ -55834,7 +55834,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2060" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="H2060" t="s">
         <v>9</v>
@@ -55860,7 +55860,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2061" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="H2061" t="s">
         <v>9</v>
@@ -55886,7 +55886,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2062" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="H2062" t="s">
         <v>9</v>
@@ -55912,7 +55912,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G2063" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="H2063" t="s">
         <v>9</v>
@@ -55938,7 +55938,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G2064" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="H2064" t="s">
         <v>9</v>
@@ -55964,7 +55964,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G2065" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="H2065" t="s">
         <v>9</v>
@@ -55990,7 +55990,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G2066" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="H2066" t="s">
         <v>9</v>
@@ -56016,7 +56016,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G2067" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="H2067" t="s">
         <v>9</v>
@@ -56042,7 +56042,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G2068" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="H2068" t="s">
         <v>9</v>
@@ -56068,7 +56068,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G2069" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="H2069" t="s">
         <v>9</v>
@@ -56094,7 +56094,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G2070" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="H2070" t="s">
         <v>9</v>
@@ -56120,7 +56120,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G2071" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="H2071" t="s">
         <v>9</v>
@@ -56146,7 +56146,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G2072" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="H2072" t="s">
         <v>9</v>
@@ -56172,7 +56172,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G2073" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="H2073" t="s">
         <v>9</v>
@@ -56198,7 +56198,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2074" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="H2074" t="s">
         <v>9</v>
@@ -56224,7 +56224,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G2075" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="H2075" t="s">
         <v>9</v>
@@ -56250,7 +56250,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G2076" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="H2076" t="s">
         <v>9</v>
@@ -56276,7 +56276,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G2077" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="H2077" t="s">
         <v>9</v>
@@ -56302,7 +56302,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G2078" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="H2078" t="s">
         <v>9</v>
@@ -56328,7 +56328,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G2079" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="H2079" t="s">
         <v>9</v>
@@ -56354,7 +56354,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G2080" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="H2080" t="s">
         <v>9</v>
@@ -56380,7 +56380,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G2081" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="H2081" t="s">
         <v>9</v>
@@ -56406,7 +56406,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G2082" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="H2082" t="s">
         <v>9</v>
@@ -56432,7 +56432,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G2083" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="H2083" t="s">
         <v>9</v>
@@ -56458,7 +56458,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G2084" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="H2084" t="s">
         <v>9</v>
@@ -56484,7 +56484,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G2085" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="H2085" t="s">
         <v>9</v>
@@ -56510,7 +56510,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G2086" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="H2086" t="s">
         <v>9</v>
@@ -56536,7 +56536,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G2087" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="H2087" t="s">
         <v>9</v>
@@ -56562,7 +56562,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G2088" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="H2088" t="s">
         <v>9</v>
@@ -56588,7 +56588,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2089" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="H2089" t="s">
         <v>9</v>
@@ -56614,7 +56614,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G2090" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="H2090" t="s">
         <v>9</v>
@@ -56640,7 +56640,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2091" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="H2091" t="s">
         <v>9</v>
@@ -56666,7 +56666,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2092" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="H2092" t="s">
         <v>9</v>
@@ -56692,7 +56692,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2093" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="H2093" t="s">
         <v>9</v>
@@ -56718,7 +56718,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G2094" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="H2094" t="s">
         <v>9</v>
@@ -56744,7 +56744,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G2095" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="H2095" t="s">
         <v>9</v>
@@ -56770,7 +56770,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G2096" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="H2096" t="s">
         <v>9</v>
@@ -56796,7 +56796,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G2097" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="H2097" t="s">
         <v>9</v>
@@ -56822,7 +56822,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G2098" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="H2098" t="s">
         <v>9</v>
@@ -56848,7 +56848,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G2099" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="H2099" t="s">
         <v>9</v>
@@ -56874,7 +56874,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G2100" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="H2100" t="s">
         <v>9</v>
@@ -56900,7 +56900,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G2101" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="H2101" t="s">
         <v>9</v>
@@ -56926,7 +56926,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G2102" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="H2102" t="s">
         <v>9</v>
@@ -56952,7 +56952,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G2103" t="s">
-        <v>557</v>
+        <v>506</v>
       </c>
       <c r="H2103" t="s">
         <v>9</v>
@@ -56978,7 +56978,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G2104" t="s">
-        <v>557</v>
+        <v>506</v>
       </c>
       <c r="H2104" t="s">
         <v>9</v>
@@ -57004,7 +57004,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G2105" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="H2105" t="s">
         <v>9</v>
@@ -57030,7 +57030,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G2106" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="H2106" t="s">
         <v>9</v>
@@ -57056,7 +57056,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G2107" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="H2107" t="s">
         <v>9</v>
@@ -57082,7 +57082,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G2108" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="H2108" t="s">
         <v>9</v>
@@ -57108,7 +57108,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G2109" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="H2109" t="s">
         <v>9</v>
@@ -57134,7 +57134,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G2110" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="H2110" t="s">
         <v>9</v>
@@ -57160,7 +57160,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G2111" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="H2111" t="s">
         <v>9</v>
@@ -57212,7 +57212,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G2113" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="H2113" t="s">
         <v>9</v>
@@ -57238,7 +57238,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G2114" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="H2114" t="s">
         <v>9</v>
@@ -57264,7 +57264,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G2115" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="H2115" t="s">
         <v>9</v>
@@ -57290,7 +57290,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G2116" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="H2116" t="s">
         <v>9</v>
@@ -57394,7 +57394,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G2120" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="H2120" t="s">
         <v>9</v>
@@ -57472,7 +57472,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2123" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="H2123" t="s">
         <v>9</v>
@@ -57654,7 +57654,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G2130" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="H2130" t="s">
         <v>9</v>
@@ -57680,7 +57680,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G2131" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="H2131" t="s">
         <v>9</v>
@@ -57706,7 +57706,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G2132" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="H2132" t="s">
         <v>9</v>
@@ -62568,7 +62568,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G2319" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="H2319" t="s">
         <v>9</v>
@@ -67074,7 +67074,7 @@
     </row>
     <row r="2493">
       <c r="A2493" s="1" t="n">
-        <v>45950.5414930556</v>
+        <v>45950.2916666667</v>
       </c>
       <c r="B2493" t="n">
         <v>5176</v>
@@ -67095,6 +67095,32 @@
         <v>638</v>
       </c>
       <c r="H2493" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2494">
+      <c r="A2494" s="1" t="n">
+        <v>45951.6493055556</v>
+      </c>
+      <c r="B2494" t="n">
+        <v>7607</v>
+      </c>
+      <c r="C2494" t="n">
+        <v>4.80000019073486</v>
+      </c>
+      <c r="D2494" t="n">
+        <v>4.69999980926514</v>
+      </c>
+      <c r="E2494" t="n">
+        <v>4.78000020980835</v>
+      </c>
+      <c r="F2494" t="n">
+        <v>4.69999980926514</v>
+      </c>
+      <c r="G2494" t="s">
+        <v>639</v>
+      </c>
+      <c r="H2494" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ENV.MI.xlsx
+++ b/data/ENV.MI.xlsx
@@ -38,25 +38,25 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18965220451355</t>
+    <t xml:space="preserve">2.18965244293213</t>
   </si>
   <si>
     <t xml:space="preserve">ENV.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20979785919189</t>
+    <t xml:space="preserve">2.20979809761047</t>
   </si>
   <si>
     <t xml:space="preserve">2.1447126865387</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1617591381073</t>
+    <t xml:space="preserve">2.16175889968872</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03778719902039</t>
+    <t xml:space="preserve">2.03778696060181</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08272647857666</t>
+    <t xml:space="preserve">2.08272671699524</t>
   </si>
   <si>
     <t xml:space="preserve">2.05328345298767</t>
@@ -68,64 +68,64 @@
     <t xml:space="preserve">1.96805274486542</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96030461788177</t>
+    <t xml:space="preserve">1.96030426025391</t>
   </si>
   <si>
     <t xml:space="preserve">1.89831852912903</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88127243518829</t>
+    <t xml:space="preserve">1.88127255439758</t>
   </si>
   <si>
     <t xml:space="preserve">1.96340382099152</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98354911804199</t>
+    <t xml:space="preserve">1.98354959487915</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01299238204956</t>
+    <t xml:space="preserve">2.01299285888672</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93551051616669</t>
+    <t xml:space="preserve">1.93551027774811</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93705987930298</t>
+    <t xml:space="preserve">1.93705976009369</t>
   </si>
   <si>
     <t xml:space="preserve">1.91381514072418</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91071617603302</t>
+    <t xml:space="preserve">1.91071581840515</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86577594280243</t>
+    <t xml:space="preserve">1.8657763004303</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89212000370026</t>
+    <t xml:space="preserve">1.89212012290955</t>
   </si>
   <si>
     <t xml:space="preserve">1.85182929039001</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93396067619324</t>
+    <t xml:space="preserve">1.93396031856537</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86732566356659</t>
+    <t xml:space="preserve">1.86732578277588</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88902056217194</t>
+    <t xml:space="preserve">1.8890209197998</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98664855957031</t>
+    <t xml:space="preserve">1.9866486787796</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11526894569397</t>
+    <t xml:space="preserve">2.11526942253113</t>
   </si>
   <si>
     <t xml:space="preserve">2.18500375747681</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20824813842773</t>
+    <t xml:space="preserve">2.20824837684631</t>
   </si>
   <si>
     <t xml:space="preserve">2.16950702667236</t>
@@ -134,28 +134,28 @@
     <t xml:space="preserve">2.0842764377594</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01454210281372</t>
+    <t xml:space="preserve">2.0145423412323</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00524425506592</t>
+    <t xml:space="preserve">2.0052444934845</t>
   </si>
   <si>
     <t xml:space="preserve">2.14626240730286</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22219514846802</t>
+    <t xml:space="preserve">2.22219491004944</t>
   </si>
   <si>
     <t xml:space="preserve">2.32447195053101</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20049953460693</t>
+    <t xml:space="preserve">2.20049977302551</t>
   </si>
   <si>
     <t xml:space="preserve">2.27178382873535</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24698972702026</t>
+    <t xml:space="preserve">2.24698948860168</t>
   </si>
   <si>
     <t xml:space="preserve">2.32137274742126</t>
@@ -164,25 +164,25 @@
     <t xml:space="preserve">2.28418111801147</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37870931625366</t>
+    <t xml:space="preserve">2.37870955467224</t>
   </si>
   <si>
     <t xml:space="preserve">2.35546469688416</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4406955242157</t>
+    <t xml:space="preserve">2.44069504737854</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43139743804932</t>
+    <t xml:space="preserve">2.43139719963074</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44999313354492</t>
+    <t xml:space="preserve">2.4499933719635</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3849081993103</t>
+    <t xml:space="preserve">2.38490796089172</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36166381835938</t>
+    <t xml:space="preserve">2.3616635799408</t>
   </si>
   <si>
     <t xml:space="preserve">2.3632128238678</t>
@@ -191,31 +191,31 @@
     <t xml:space="preserve">2.31982278823853</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35236525535583</t>
+    <t xml:space="preserve">2.35236573219299</t>
   </si>
   <si>
     <t xml:space="preserve">2.26868438720703</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32292222976685</t>
+    <t xml:space="preserve">2.32292175292969</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33531928062439</t>
+    <t xml:space="preserve">2.33531951904297</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33996796607971</t>
+    <t xml:space="preserve">2.33996844291687</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3105251789093</t>
+    <t xml:space="preserve">2.31052494049072</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28573083877563</t>
+    <t xml:space="preserve">2.28573060035706</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25473833084106</t>
+    <t xml:space="preserve">2.25473761558533</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29038000106812</t>
+    <t xml:space="preserve">2.29037976264954</t>
   </si>
   <si>
     <t xml:space="preserve">2.27488327026367</t>
@@ -224,82 +224,82 @@
     <t xml:space="preserve">2.23149299621582</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07497882843018</t>
+    <t xml:space="preserve">2.0749785900116</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00834345817566</t>
+    <t xml:space="preserve">2.00834369659424</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03468775749207</t>
+    <t xml:space="preserve">2.03468728065491</t>
   </si>
   <si>
     <t xml:space="preserve">2.02229046821594</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97580087184906</t>
+    <t xml:space="preserve">1.97580111026764</t>
   </si>
   <si>
-    <t xml:space="preserve">1.919806599617</t>
+    <t xml:space="preserve">1.91980683803558</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88216364383698</t>
+    <t xml:space="preserve">1.88216376304626</t>
   </si>
   <si>
     <t xml:space="preserve">2.00136733055115</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96058702468872</t>
+    <t xml:space="preserve">1.96058690547943</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90255379676819</t>
+    <t xml:space="preserve">1.9025536775589</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92137515544891</t>
+    <t xml:space="preserve">1.92137503623962</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91353261470795</t>
+    <t xml:space="preserve">1.91353273391724</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89784801006317</t>
+    <t xml:space="preserve">1.89784824848175</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89000582695007</t>
+    <t xml:space="preserve">1.89000606536865</t>
   </si>
   <si>
     <t xml:space="preserve">1.85079407691956</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8805947303772</t>
+    <t xml:space="preserve">1.88059508800507</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8664790391922</t>
+    <t xml:space="preserve">1.86647868156433</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54651093482971</t>
+    <t xml:space="preserve">1.546511054039</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68610489368439</t>
+    <t xml:space="preserve">1.68610465526581</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70178961753845</t>
+    <t xml:space="preserve">1.70178973674774</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70022106170654</t>
+    <t xml:space="preserve">1.70022094249725</t>
   </si>
   <si>
     <t xml:space="preserve">1.66257762908936</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64532458782196</t>
+    <t xml:space="preserve">1.64532470703125</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62336599826813</t>
+    <t xml:space="preserve">1.62336587905884</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61552357673645</t>
+    <t xml:space="preserve">1.61552369594574</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63120818138123</t>
+    <t xml:space="preserve">1.63120830059052</t>
   </si>
   <si>
     <t xml:space="preserve">1.58415424823761</t>
@@ -311,43 +311,43 @@
     <t xml:space="preserve">1.64061915874481</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63905072212219</t>
+    <t xml:space="preserve">1.6390506029129</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60768127441406</t>
+    <t xml:space="preserve">1.60768139362335</t>
   </si>
   <si>
     <t xml:space="preserve">1.57631194591522</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59199643135071</t>
+    <t xml:space="preserve">1.59199678897858</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75668573379517</t>
+    <t xml:space="preserve">1.75668597221375</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84295153617859</t>
+    <t xml:space="preserve">1.84295189380646</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84608888626099</t>
+    <t xml:space="preserve">1.84608864784241</t>
   </si>
   <si>
     <t xml:space="preserve">1.92921757698059</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88530015945435</t>
+    <t xml:space="preserve">1.88530051708221</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9009850025177</t>
+    <t xml:space="preserve">1.90098524093628</t>
   </si>
   <si>
     <t xml:space="preserve">1.91823828220367</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94960784912109</t>
+    <t xml:space="preserve">1.9496077299118</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9307861328125</t>
+    <t xml:space="preserve">1.93078601360321</t>
   </si>
   <si>
     <t xml:space="preserve">1.84922575950623</t>
@@ -356,28 +356,28 @@
     <t xml:space="preserve">1.82413017749786</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85549926757812</t>
+    <t xml:space="preserve">1.85549938678741</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89627969264984</t>
+    <t xml:space="preserve">1.89627957344055</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93706011772156</t>
+    <t xml:space="preserve">1.93705999851227</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87432086467743</t>
+    <t xml:space="preserve">1.87432110309601</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94333386421204</t>
+    <t xml:space="preserve">1.94333374500275</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94490230083466</t>
+    <t xml:space="preserve">1.94490218162537</t>
   </si>
   <si>
     <t xml:space="preserve">1.96686053276062</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98411393165588</t>
+    <t xml:space="preserve">1.9841136932373</t>
   </si>
   <si>
     <t xml:space="preserve">2.06253743171692</t>
@@ -386,58 +386,58 @@
     <t xml:space="preserve">2.05312657356262</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05155825614929</t>
+    <t xml:space="preserve">2.05155849456787</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02332544326782</t>
+    <t xml:space="preserve">2.0233256816864</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02959942817688</t>
+    <t xml:space="preserve">2.02959966659546</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03116798400879</t>
+    <t xml:space="preserve">2.03116774559021</t>
   </si>
   <si>
     <t xml:space="preserve">2.06096911430359</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09390711784363</t>
+    <t xml:space="preserve">2.09390687942505</t>
   </si>
   <si>
     <t xml:space="preserve">2.08606457710266</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1550772190094</t>
+    <t xml:space="preserve">2.15507698059082</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18801498413086</t>
+    <t xml:space="preserve">2.18801522254944</t>
   </si>
   <si>
     <t xml:space="preserve">2.19585728645325</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20213103294373</t>
+    <t xml:space="preserve">2.20213150978088</t>
   </si>
   <si>
     <t xml:space="preserve">2.23350048065186</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20997381210327</t>
+    <t xml:space="preserve">2.20997405052185</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18017268180847</t>
+    <t xml:space="preserve">2.18017244338989</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16605687141418</t>
+    <t xml:space="preserve">2.16605663299561</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1942892074585</t>
+    <t xml:space="preserve">2.19428896903992</t>
   </si>
   <si>
     <t xml:space="preserve">2.17389869689941</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20056295394897</t>
+    <t xml:space="preserve">2.2005627155304</t>
   </si>
   <si>
     <t xml:space="preserve">2.21938443183899</t>
@@ -446,13 +446,13 @@
     <t xml:space="preserve">2.21781611442566</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1911518573761</t>
+    <t xml:space="preserve">2.19115209579468</t>
   </si>
   <si>
     <t xml:space="preserve">2.12057089805603</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15350866317749</t>
+    <t xml:space="preserve">2.15350890159607</t>
   </si>
   <si>
     <t xml:space="preserve">2.11743402481079</t>
@@ -464,16 +464,16 @@
     <t xml:space="preserve">2.10802316665649</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01548337936401</t>
+    <t xml:space="preserve">2.01548314094543</t>
   </si>
   <si>
     <t xml:space="preserve">2.04528450965881</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9856823682785</t>
+    <t xml:space="preserve">1.98568284511566</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07822203636169</t>
+    <t xml:space="preserve">2.07822227478027</t>
   </si>
   <si>
     <t xml:space="preserve">2.06724286079407</t>
@@ -482,22 +482,22 @@
     <t xml:space="preserve">2.12998151779175</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11586499214172</t>
+    <t xml:space="preserve">2.1158652305603</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05469512939453</t>
+    <t xml:space="preserve">2.05469489097595</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11429738998413</t>
+    <t xml:space="preserve">2.11429691314697</t>
   </si>
   <si>
     <t xml:space="preserve">2.05626368522644</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06410598754883</t>
+    <t xml:space="preserve">2.06410574913025</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10488605499268</t>
+    <t xml:space="preserve">2.10488629341125</t>
   </si>
   <si>
     <t xml:space="preserve">2.00920939445496</t>
@@ -509,25 +509,25 @@
     <t xml:space="preserve">2.04842138290405</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16448831558228</t>
+    <t xml:space="preserve">2.16448783874512</t>
   </si>
   <si>
     <t xml:space="preserve">2.18487811088562</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26643848419189</t>
+    <t xml:space="preserve">2.26643872261047</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27271223068237</t>
+    <t xml:space="preserve">2.27271270751953</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2570276260376</t>
+    <t xml:space="preserve">2.25702786445618</t>
   </si>
   <si>
     <t xml:space="preserve">2.30721879005432</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23036360740662</t>
+    <t xml:space="preserve">2.2303638458252</t>
   </si>
   <si>
     <t xml:space="preserve">2.37152576446533</t>
@@ -542,25 +542,25 @@
     <t xml:space="preserve">2.33545112609863</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31349277496338</t>
+    <t xml:space="preserve">2.3134925365448</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37623143196106</t>
+    <t xml:space="preserve">2.37623119354248</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32917761802673</t>
+    <t xml:space="preserve">2.32917737960815</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24918532371521</t>
+    <t xml:space="preserve">2.24918508529663</t>
   </si>
   <si>
     <t xml:space="preserve">2.28839731216431</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33701968193054</t>
+    <t xml:space="preserve">2.33701992034912</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34486198425293</t>
+    <t xml:space="preserve">2.34486174583435</t>
   </si>
   <si>
     <t xml:space="preserve">2.34956741333008</t>
@@ -569,13 +569,13 @@
     <t xml:space="preserve">2.32604026794434</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30251336097717</t>
+    <t xml:space="preserve">2.30251359939575</t>
   </si>
   <si>
     <t xml:space="preserve">2.31192398071289</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25075364112854</t>
+    <t xml:space="preserve">2.2507541179657</t>
   </si>
   <si>
     <t xml:space="preserve">2.27428102493286</t>
@@ -584,7 +584,7 @@
     <t xml:space="preserve">2.43897008895874</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48445558547974</t>
+    <t xml:space="preserve">2.48445582389832</t>
   </si>
   <si>
     <t xml:space="preserve">2.46249723434448</t>
@@ -593,31 +593,31 @@
     <t xml:space="preserve">2.50798296928406</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48602437973022</t>
+    <t xml:space="preserve">2.4860246181488</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60993337631226</t>
+    <t xml:space="preserve">2.60993313789368</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66639828681946</t>
+    <t xml:space="preserve">2.66639852523804</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66326117515564</t>
+    <t xml:space="preserve">2.66326093673706</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66012454032898</t>
+    <t xml:space="preserve">2.66012406349182</t>
   </si>
   <si>
     <t xml:space="preserve">2.64287114143372</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65855622291565</t>
+    <t xml:space="preserve">2.65855598449707</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60209083557129</t>
+    <t xml:space="preserve">2.60209131240845</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55033135414124</t>
+    <t xml:space="preserve">2.55033159255981</t>
   </si>
   <si>
     <t xml:space="preserve">2.63816595077515</t>
@@ -629,10 +629,10 @@
     <t xml:space="preserve">2.59581708908081</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58170080184937</t>
+    <t xml:space="preserve">2.58170056343079</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6036593914032</t>
+    <t xml:space="preserve">2.60365915298462</t>
   </si>
   <si>
     <t xml:space="preserve">2.61934423446655</t>
@@ -641,34 +641,34 @@
     <t xml:space="preserve">2.57542705535889</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57385849952698</t>
+    <t xml:space="preserve">2.57385873794556</t>
   </si>
   <si>
     <t xml:space="preserve">2.50955128669739</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58797454833984</t>
+    <t xml:space="preserve">2.58797478675842</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56444787979126</t>
+    <t xml:space="preserve">2.56444764137268</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61150193214417</t>
+    <t xml:space="preserve">2.61150169372559</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56915307044983</t>
+    <t xml:space="preserve">2.56915330886841</t>
   </si>
   <si>
     <t xml:space="preserve">2.63502907752991</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62561821937561</t>
+    <t xml:space="preserve">2.62561798095703</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62718629837036</t>
+    <t xml:space="preserve">2.62718653678894</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83422446250916</t>
+    <t xml:space="preserve">2.83422470092773</t>
   </si>
   <si>
     <t xml:space="preserve">2.79030728340149</t>
@@ -677,10 +677,10 @@
     <t xml:space="preserve">2.77619123458862</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78089618682861</t>
+    <t xml:space="preserve">2.78089642524719</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69149374961853</t>
+    <t xml:space="preserve">2.69149351119995</t>
   </si>
   <si>
     <t xml:space="preserve">2.78246545791626</t>
@@ -689,10 +689,10 @@
     <t xml:space="preserve">2.81226587295532</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82324528694153</t>
+    <t xml:space="preserve">2.82324504852295</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68678832054138</t>
+    <t xml:space="preserve">2.68678855895996</t>
   </si>
   <si>
     <t xml:space="preserve">2.70090460777283</t>
@@ -704,28 +704,28 @@
     <t xml:space="preserve">2.86433959007263</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81940889358521</t>
+    <t xml:space="preserve">2.81940865516663</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80817604064941</t>
+    <t xml:space="preserve">2.80817627906799</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88038611412048</t>
+    <t xml:space="preserve">2.88038635253906</t>
   </si>
   <si>
     <t xml:space="preserve">2.8338508605957</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74398899078369</t>
+    <t xml:space="preserve">2.74398922920227</t>
   </si>
   <si>
     <t xml:space="preserve">2.72794246673584</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70547723770142</t>
+    <t xml:space="preserve">2.70547699928284</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73275637626648</t>
+    <t xml:space="preserve">2.7327561378479</t>
   </si>
   <si>
     <t xml:space="preserve">2.67177891731262</t>
@@ -737,7 +737,7 @@
     <t xml:space="preserve">2.61722016334534</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60438299179077</t>
+    <t xml:space="preserve">2.60438275337219</t>
   </si>
   <si>
     <t xml:space="preserve">2.62524342536926</t>
@@ -749,7 +749,7 @@
     <t xml:space="preserve">2.69584894180298</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75040817260742</t>
+    <t xml:space="preserve">2.75040793418884</t>
   </si>
   <si>
     <t xml:space="preserve">2.74719858169556</t>
@@ -758,73 +758,73 @@
     <t xml:space="preserve">2.71991920471191</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72633767127991</t>
+    <t xml:space="preserve">2.72633790969849</t>
   </si>
   <si>
     <t xml:space="preserve">2.74238443374634</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80015254020691</t>
+    <t xml:space="preserve">2.80015277862549</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78571057319641</t>
+    <t xml:space="preserve">2.78571033477783</t>
   </si>
   <si>
     <t xml:space="preserve">2.82422256469727</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78731536865234</t>
+    <t xml:space="preserve">2.78731513023376</t>
   </si>
   <si>
     <t xml:space="preserve">2.79373383522034</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80496668815613</t>
+    <t xml:space="preserve">2.80496692657471</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78410601615906</t>
+    <t xml:space="preserve">2.78410577774048</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77608251571655</t>
+    <t xml:space="preserve">2.77608275413513</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79533863067627</t>
+    <t xml:space="preserve">2.79533886909485</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82261800765991</t>
+    <t xml:space="preserve">2.82261776924133</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7600359916687</t>
+    <t xml:space="preserve">2.76003575325012</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77929210662842</t>
+    <t xml:space="preserve">2.77929186820984</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79854774475098</t>
+    <t xml:space="preserve">2.79854798316956</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77447819709778</t>
+    <t xml:space="preserve">2.77447772026062</t>
   </si>
   <si>
     <t xml:space="preserve">2.8033618927002</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83545541763306</t>
+    <t xml:space="preserve">2.83545517921448</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8402693271637</t>
+    <t xml:space="preserve">2.84026956558228</t>
   </si>
   <si>
     <t xml:space="preserve">2.83224606513977</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81138515472412</t>
+    <t xml:space="preserve">2.81138563156128</t>
   </si>
   <si>
     <t xml:space="preserve">2.81619930267334</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76324534416199</t>
+    <t xml:space="preserve">2.76324510574341</t>
   </si>
   <si>
     <t xml:space="preserve">2.71189594268799</t>
@@ -833,7 +833,7 @@
     <t xml:space="preserve">2.72473287582397</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7969434261322</t>
+    <t xml:space="preserve">2.79694318771362</t>
   </si>
   <si>
     <t xml:space="preserve">2.79052448272705</t>
@@ -845,13 +845,13 @@
     <t xml:space="preserve">2.73115181922913</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7038722038269</t>
+    <t xml:space="preserve">2.70387244224548</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81459450721741</t>
+    <t xml:space="preserve">2.81459498405457</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82903671264648</t>
+    <t xml:space="preserve">2.82903647422791</t>
   </si>
   <si>
     <t xml:space="preserve">2.84347867965698</t>
@@ -872,7 +872,7 @@
     <t xml:space="preserve">2.89161920547485</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9285261631012</t>
+    <t xml:space="preserve">2.92852640151978</t>
   </si>
   <si>
     <t xml:space="preserve">2.85952544212341</t>
@@ -881,7 +881,7 @@
     <t xml:space="preserve">2.90927028656006</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99913215637207</t>
+    <t xml:space="preserve">2.99913191795349</t>
   </si>
   <si>
     <t xml:space="preserve">2.96864318847656</t>
@@ -890,22 +890,22 @@
     <t xml:space="preserve">2.830641746521</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87878131866455</t>
+    <t xml:space="preserve">2.87878179550171</t>
   </si>
   <si>
     <t xml:space="preserve">2.87717700004578</t>
   </si>
   <si>
-    <t xml:space="preserve">2.875572681427</t>
+    <t xml:space="preserve">2.87557244300842</t>
   </si>
   <si>
     <t xml:space="preserve">2.7520124912262</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76164054870605</t>
+    <t xml:space="preserve">2.76164031028748</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78892016410828</t>
+    <t xml:space="preserve">2.7889199256897</t>
   </si>
   <si>
     <t xml:space="preserve">2.67980217933655</t>
@@ -917,28 +917,28 @@
     <t xml:space="preserve">2.8258273601532</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8482928276062</t>
+    <t xml:space="preserve">2.84829258918762</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82101321220398</t>
+    <t xml:space="preserve">2.82101345062256</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73436141014099</t>
+    <t xml:space="preserve">2.73436117172241</t>
   </si>
   <si>
     <t xml:space="preserve">2.81780433654785</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76485013961792</t>
+    <t xml:space="preserve">2.76484990119934</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74077963829041</t>
+    <t xml:space="preserve">2.74077987670898</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79212951660156</t>
+    <t xml:space="preserve">2.7921290397644</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66375541687012</t>
+    <t xml:space="preserve">2.66375517845154</t>
   </si>
   <si>
     <t xml:space="preserve">2.60759234428406</t>
@@ -950,22 +950,22 @@
     <t xml:space="preserve">2.56747508049011</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59956860542297</t>
+    <t xml:space="preserve">2.59956836700439</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55945205688477</t>
+    <t xml:space="preserve">2.55945181846619</t>
   </si>
   <si>
     <t xml:space="preserve">2.50328826904297</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45514798164368</t>
+    <t xml:space="preserve">2.45514845848083</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47921848297119</t>
+    <t xml:space="preserve">2.47921824455261</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47119474411011</t>
+    <t xml:space="preserve">2.47119498252869</t>
   </si>
   <si>
     <t xml:space="preserve">2.43107795715332</t>
@@ -974,10 +974,10 @@
     <t xml:space="preserve">2.46317148208618</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48724150657654</t>
+    <t xml:space="preserve">2.48724174499512</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49526500701904</t>
+    <t xml:space="preserve">2.49526476860046</t>
   </si>
   <si>
     <t xml:space="preserve">2.52735829353333</t>
@@ -989,16 +989,16 @@
     <t xml:space="preserve">2.65573215484619</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91247963905334</t>
+    <t xml:space="preserve">2.91247987747192</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8200249671936</t>
+    <t xml:space="preserve">2.82002472877502</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80358171463013</t>
+    <t xml:space="preserve">2.80358147621155</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86935472488403</t>
+    <t xml:space="preserve">2.86935496330261</t>
   </si>
   <si>
     <t xml:space="preserve">2.84468984603882</t>
@@ -1010,13 +1010,13 @@
     <t xml:space="preserve">2.81180334091187</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72136521339417</t>
+    <t xml:space="preserve">2.72136497497559</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68025684356689</t>
+    <t xml:space="preserve">2.68025708198547</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69670033454895</t>
+    <t xml:space="preserve">2.69670009613037</t>
   </si>
   <si>
     <t xml:space="preserve">2.64737033843994</t>
@@ -1034,7 +1034,7 @@
     <t xml:space="preserve">2.6391487121582</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55693221092224</t>
+    <t xml:space="preserve">2.55693173408508</t>
   </si>
   <si>
     <t xml:space="preserve">2.59804058074951</t>
@@ -1043,49 +1043,49 @@
     <t xml:space="preserve">2.5487105846405</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46649408340454</t>
+    <t xml:space="preserve">2.46649384498596</t>
   </si>
   <si>
     <t xml:space="preserve">2.60626220703125</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52404570579529</t>
+    <t xml:space="preserve">2.52404546737671</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58159708976746</t>
+    <t xml:space="preserve">2.58159732818604</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61448407173157</t>
+    <t xml:space="preserve">2.61448383331299</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58981847763062</t>
+    <t xml:space="preserve">2.58981871604919</t>
   </si>
   <si>
     <t xml:space="preserve">2.62270545959473</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51582384109497</t>
+    <t xml:space="preserve">2.51582407951355</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57337522506714</t>
+    <t xml:space="preserve">2.57337546348572</t>
   </si>
   <si>
     <t xml:space="preserve">2.56515383720398</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53226709365845</t>
+    <t xml:space="preserve">2.53226733207703</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4747154712677</t>
+    <t xml:space="preserve">2.47471594810486</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48293733596802</t>
+    <t xml:space="preserve">2.4829375743866</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45005106925964</t>
+    <t xml:space="preserve">2.45005083084106</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44182944297791</t>
+    <t xml:space="preserve">2.44182920455933</t>
   </si>
   <si>
     <t xml:space="preserve">2.42538571357727</t>
@@ -1100,10 +1100,10 @@
     <t xml:space="preserve">2.50760245323181</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54048895835876</t>
+    <t xml:space="preserve">2.54048871994019</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67203521728516</t>
+    <t xml:space="preserve">2.67203545570374</t>
   </si>
   <si>
     <t xml:space="preserve">2.68847846984863</t>
@@ -1112,13 +1112,13 @@
     <t xml:space="preserve">2.70492196083069</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71314358711243</t>
+    <t xml:space="preserve">2.71314334869385</t>
   </si>
   <si>
     <t xml:space="preserve">2.75425171852112</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78713846206665</t>
+    <t xml:space="preserve">2.78713822364807</t>
   </si>
   <si>
     <t xml:space="preserve">2.77069497108459</t>
@@ -1130,7 +1130,7 @@
     <t xml:space="preserve">2.7460298538208</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77891659736633</t>
+    <t xml:space="preserve">2.77891707420349</t>
   </si>
   <si>
     <t xml:space="preserve">2.79536008834839</t>
@@ -1139,7 +1139,7 @@
     <t xml:space="preserve">2.87757658958435</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91868472099304</t>
+    <t xml:space="preserve">2.91868448257446</t>
   </si>
   <si>
     <t xml:space="preserve">2.89401960372925</t>
@@ -1151,28 +1151,25 @@
     <t xml:space="preserve">2.90224123001099</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88579797744751</t>
+    <t xml:space="preserve">2.88579821586609</t>
   </si>
   <si>
     <t xml:space="preserve">2.8364679813385</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94334936141968</t>
+    <t xml:space="preserve">2.94334959983826</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82824659347534</t>
+    <t xml:space="preserve">2.82824635505676</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92690634727478</t>
+    <t xml:space="preserve">2.9269061088562</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80358147621155</t>
+    <t xml:space="preserve">2.77809429168701</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77809453010559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82057285308838</t>
+    <t xml:space="preserve">2.8205726146698</t>
   </si>
   <si>
     <t xml:space="preserve">2.8290684223175</t>
@@ -1181,19 +1178,19 @@
     <t xml:space="preserve">2.88853859901428</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88004302978516</t>
+    <t xml:space="preserve">2.88004279136658</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92252135276794</t>
+    <t xml:space="preserve">2.92252111434937</t>
   </si>
   <si>
     <t xml:space="preserve">2.90552997589111</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87154722213745</t>
+    <t xml:space="preserve">2.87154746055603</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85455560684204</t>
+    <t xml:space="preserve">2.85455584526062</t>
   </si>
   <si>
     <t xml:space="preserve">2.91402554512024</t>
@@ -1208,7 +1205,7 @@
     <t xml:space="preserve">2.89703416824341</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93951296806335</t>
+    <t xml:space="preserve">2.93951272964478</t>
   </si>
   <si>
     <t xml:space="preserve">2.98199129104614</t>
@@ -1223,34 +1220,37 @@
     <t xml:space="preserve">2.76110315322876</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76959872245789</t>
+    <t xml:space="preserve">2.76959896087646</t>
   </si>
   <si>
     <t xml:space="preserve">2.81207704544067</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83756422996521</t>
+    <t xml:space="preserve">2.83756399154663</t>
   </si>
   <si>
     <t xml:space="preserve">2.86305141448975</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62517189979553</t>
+    <t xml:space="preserve">2.62517166137695</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67614579200745</t>
+    <t xml:space="preserve">2.67614603042603</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61667585372925</t>
+    <t xml:space="preserve">2.61667609214783</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55720591545105</t>
+    <t xml:space="preserve">2.55720639228821</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51472759246826</t>
+    <t xml:space="preserve">2.54871034622192</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49773597717285</t>
+    <t xml:space="preserve">2.51472783088684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49773645401001</t>
   </si>
   <si>
     <t xml:space="preserve">2.4807448387146</t>
@@ -1259,7 +1259,7 @@
     <t xml:space="preserve">2.53171920776367</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46375346183777</t>
+    <t xml:space="preserve">2.46375370025635</t>
   </si>
   <si>
     <t xml:space="preserve">2.58269309997559</t>
@@ -1280,10 +1280,10 @@
     <t xml:space="preserve">2.63366746902466</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59968447685242</t>
+    <t xml:space="preserve">2.599684715271</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52322363853455</t>
+    <t xml:space="preserve">2.52322340011597</t>
   </si>
   <si>
     <t xml:space="preserve">2.57419753074646</t>
@@ -1301,7 +1301,7 @@
     <t xml:space="preserve">2.96499991416931</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97349548339844</t>
+    <t xml:space="preserve">2.97349572181702</t>
   </si>
   <si>
     <t xml:space="preserve">2.95650410652161</t>
@@ -1316,7 +1316,7 @@
     <t xml:space="preserve">2.6676504611969</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65915441513062</t>
+    <t xml:space="preserve">2.65915465354919</t>
   </si>
   <si>
     <t xml:space="preserve">2.31083083152771</t>
@@ -1328,7 +1328,7 @@
     <t xml:space="preserve">2.34481358528137</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45525765419006</t>
+    <t xml:space="preserve">2.45525789260864</t>
   </si>
   <si>
     <t xml:space="preserve">2.4892406463623</t>
@@ -1337,10 +1337,10 @@
     <t xml:space="preserve">2.65065884590149</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64216303825378</t>
+    <t xml:space="preserve">2.64216279983521</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71012902259827</t>
+    <t xml:space="preserve">2.71012878417969</t>
   </si>
   <si>
     <t xml:space="preserve">2.69313764572144</t>
@@ -1355,16 +1355,16 @@
     <t xml:space="preserve">2.68464183807373</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6081805229187</t>
+    <t xml:space="preserve">2.60818028450012</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50623202323914</t>
+    <t xml:space="preserve">2.50623178482056</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44676232337952</t>
+    <t xml:space="preserve">2.44676208496094</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37879633903503</t>
+    <t xml:space="preserve">2.37879657745361</t>
   </si>
   <si>
     <t xml:space="preserve">2.42977070808411</t>
@@ -1376,7 +1376,7 @@
     <t xml:space="preserve">2.31932640075684</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27684807777405</t>
+    <t xml:space="preserve">2.27684831619263</t>
   </si>
   <si>
     <t xml:space="preserve">2.26835250854492</t>
@@ -1388,7 +1388,7 @@
     <t xml:space="preserve">2.33631777763367</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39578771591187</t>
+    <t xml:space="preserve">2.39578795433044</t>
   </si>
   <si>
     <t xml:space="preserve">2.72712016105652</t>
@@ -1400,13 +1400,13 @@
     <t xml:space="preserve">3.03296542167664</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0159740447998</t>
+    <t xml:space="preserve">3.01597380638123</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04146099090576</t>
+    <t xml:space="preserve">3.04146122932434</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19438409805298</t>
+    <t xml:space="preserve">3.1943838596344</t>
   </si>
   <si>
     <t xml:space="preserve">3.1264181137085</t>
@@ -1415,13 +1415,13 @@
     <t xml:space="preserve">3.05845236778259</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09243559837341</t>
+    <t xml:space="preserve">3.09243535995483</t>
   </si>
   <si>
     <t xml:space="preserve">3.16040086746216</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21137547492981</t>
+    <t xml:space="preserve">3.21137523651123</t>
   </si>
   <si>
     <t xml:space="preserve">3.3133237361908</t>
@@ -1433,13 +1433,13 @@
     <t xml:space="preserve">3.33031511306763</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22836637496948</t>
+    <t xml:space="preserve">3.22836661338806</t>
   </si>
   <si>
     <t xml:space="preserve">3.17739224433899</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14340949058533</t>
+    <t xml:space="preserve">3.14340972900391</t>
   </si>
   <si>
     <t xml:space="preserve">3.10942697525024</t>
@@ -1454,7 +1454,7 @@
     <t xml:space="preserve">3.39828038215637</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46624636650085</t>
+    <t xml:space="preserve">3.46624612808228</t>
   </si>
   <si>
     <t xml:space="preserve">3.36429786682129</t>
@@ -1463,10 +1463,10 @@
     <t xml:space="preserve">3.34730648994446</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24535775184631</t>
+    <t xml:space="preserve">3.24535799026489</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02446985244751</t>
+    <t xml:space="preserve">3.02446961402893</t>
   </si>
   <si>
     <t xml:space="preserve">3.16417121887207</t>
@@ -1499,13 +1499,10 @@
     <t xml:space="preserve">3.09405112266541</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07652115821838</t>
+    <t xml:space="preserve">3.07652139663696</t>
   </si>
   <si>
     <t xml:space="preserve">3.06775617599487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04146122932434</t>
   </si>
   <si>
     <t xml:space="preserve">3.00640106201172</t>
@@ -1526,13 +1523,13 @@
     <t xml:space="preserve">2.96257615089417</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86616086959839</t>
+    <t xml:space="preserve">2.86616063117981</t>
   </si>
   <si>
     <t xml:space="preserve">2.91875076293945</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80480551719666</t>
+    <t xml:space="preserve">2.80480575561523</t>
   </si>
   <si>
     <t xml:space="preserve">2.82233572006226</t>
@@ -1544,7 +1541,7 @@
     <t xml:space="preserve">2.95381093025208</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83110070228577</t>
+    <t xml:space="preserve">2.83110046386719</t>
   </si>
   <si>
     <t xml:space="preserve">2.93628096580505</t>
@@ -1568,10 +1565,10 @@
     <t xml:space="preserve">2.83986568450928</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68209528923035</t>
+    <t xml:space="preserve">2.68209552764893</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69086050987244</t>
+    <t xml:space="preserve">2.69086027145386</t>
   </si>
   <si>
     <t xml:space="preserve">2.66456532478333</t>
@@ -1589,7 +1586,7 @@
     <t xml:space="preserve">2.76974582672119</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79604077339172</t>
+    <t xml:space="preserve">2.79604053497314</t>
   </si>
   <si>
     <t xml:space="preserve">2.84863090515137</t>
@@ -1686,6 +1683,9 @@
   </si>
   <si>
     <t xml:space="preserve">2.85962271690369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80480551719666</t>
   </si>
   <si>
     <t xml:space="preserve">2.89616751670837</t>
@@ -24608,7 +24608,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G859" t="s">
-        <v>384</v>
+        <v>327</v>
       </c>
       <c r="H859" t="s">
         <v>9</v>
@@ -24634,7 +24634,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G860" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="H860" t="s">
         <v>9</v>
@@ -24660,7 +24660,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G861" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="H861" t="s">
         <v>9</v>
@@ -24686,7 +24686,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G862" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="H862" t="s">
         <v>9</v>
@@ -24712,7 +24712,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G863" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H863" t="s">
         <v>9</v>
@@ -24738,7 +24738,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G864" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H864" t="s">
         <v>9</v>
@@ -24764,7 +24764,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G865" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H865" t="s">
         <v>9</v>
@@ -24790,7 +24790,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G866" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H866" t="s">
         <v>9</v>
@@ -24816,7 +24816,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G867" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H867" t="s">
         <v>9</v>
@@ -24842,7 +24842,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G868" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H868" t="s">
         <v>9</v>
@@ -24868,7 +24868,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G869" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H869" t="s">
         <v>9</v>
@@ -24894,7 +24894,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G870" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H870" t="s">
         <v>9</v>
@@ -24920,7 +24920,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G871" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H871" t="s">
         <v>9</v>
@@ -24946,7 +24946,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G872" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H872" t="s">
         <v>9</v>
@@ -24972,7 +24972,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G873" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="H873" t="s">
         <v>9</v>
@@ -24998,7 +24998,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G874" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H874" t="s">
         <v>9</v>
@@ -25024,7 +25024,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G875" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H875" t="s">
         <v>9</v>
@@ -25050,7 +25050,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G876" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H876" t="s">
         <v>9</v>
@@ -25076,7 +25076,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G877" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H877" t="s">
         <v>9</v>
@@ -25102,7 +25102,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G878" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H878" t="s">
         <v>9</v>
@@ -25128,7 +25128,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G879" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H879" t="s">
         <v>9</v>
@@ -25154,7 +25154,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G880" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H880" t="s">
         <v>9</v>
@@ -25180,7 +25180,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G881" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H881" t="s">
         <v>9</v>
@@ -25206,7 +25206,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G882" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H882" t="s">
         <v>9</v>
@@ -25232,7 +25232,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G883" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H883" t="s">
         <v>9</v>
@@ -25258,7 +25258,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G884" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H884" t="s">
         <v>9</v>
@@ -25284,7 +25284,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G885" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H885" t="s">
         <v>9</v>
@@ -25310,7 +25310,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G886" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="H886" t="s">
         <v>9</v>
@@ -25336,7 +25336,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G887" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="H887" t="s">
         <v>9</v>
@@ -25362,7 +25362,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G888" t="s">
-        <v>384</v>
+        <v>327</v>
       </c>
       <c r="H888" t="s">
         <v>9</v>
@@ -25388,7 +25388,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G889" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="H889" t="s">
         <v>9</v>
@@ -25414,7 +25414,7 @@
         <v>3.25</v>
       </c>
       <c r="G890" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="H890" t="s">
         <v>9</v>
@@ -25440,7 +25440,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G891" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="H891" t="s">
         <v>9</v>
@@ -25466,7 +25466,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G892" t="s">
-        <v>384</v>
+        <v>327</v>
       </c>
       <c r="H892" t="s">
         <v>9</v>
@@ -25492,7 +25492,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G893" t="s">
-        <v>384</v>
+        <v>327</v>
       </c>
       <c r="H893" t="s">
         <v>9</v>
@@ -25518,7 +25518,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G894" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="H894" t="s">
         <v>9</v>
@@ -25544,7 +25544,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G895" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H895" t="s">
         <v>9</v>
@@ -25570,7 +25570,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G896" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H896" t="s">
         <v>9</v>
@@ -25596,7 +25596,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G897" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H897" t="s">
         <v>9</v>
@@ -25622,7 +25622,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G898" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="H898" t="s">
         <v>9</v>
@@ -25648,7 +25648,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G899" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="H899" t="s">
         <v>9</v>
@@ -25674,7 +25674,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G900" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="H900" t="s">
         <v>9</v>
@@ -25700,7 +25700,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G901" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H901" t="s">
         <v>9</v>
@@ -25726,7 +25726,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G902" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H902" t="s">
         <v>9</v>
@@ -25752,7 +25752,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G903" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="H903" t="s">
         <v>9</v>
@@ -25778,7 +25778,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G904" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="H904" t="s">
         <v>9</v>
@@ -25804,7 +25804,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G905" t="s">
-        <v>384</v>
+        <v>327</v>
       </c>
       <c r="H905" t="s">
         <v>9</v>
@@ -25830,7 +25830,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G906" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="H906" t="s">
         <v>9</v>
@@ -25856,7 +25856,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G907" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="H907" t="s">
         <v>9</v>
@@ -25882,7 +25882,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G908" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="H908" t="s">
         <v>9</v>
@@ -25908,7 +25908,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G909" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="H909" t="s">
         <v>9</v>
@@ -25934,7 +25934,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G910" t="s">
-        <v>384</v>
+        <v>327</v>
       </c>
       <c r="H910" t="s">
         <v>9</v>
@@ -25960,7 +25960,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G911" t="s">
-        <v>384</v>
+        <v>327</v>
       </c>
       <c r="H911" t="s">
         <v>9</v>
@@ -25986,7 +25986,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G912" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H912" t="s">
         <v>9</v>
@@ -26012,7 +26012,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G913" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H913" t="s">
         <v>9</v>
@@ -26038,7 +26038,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G914" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="H914" t="s">
         <v>9</v>
@@ -26064,7 +26064,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G915" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="H915" t="s">
         <v>9</v>
@@ -26090,7 +26090,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G916" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="H916" t="s">
         <v>9</v>
@@ -26116,7 +26116,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G917" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H917" t="s">
         <v>9</v>
@@ -26142,7 +26142,7 @@
         <v>3</v>
       </c>
       <c r="G918" t="s">
-        <v>342</v>
+        <v>410</v>
       </c>
       <c r="H918" t="s">
         <v>9</v>
@@ -26272,7 +26272,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G923" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H923" t="s">
         <v>9</v>
@@ -26298,7 +26298,7 @@
         <v>3</v>
       </c>
       <c r="G924" t="s">
-        <v>342</v>
+        <v>410</v>
       </c>
       <c r="H924" t="s">
         <v>9</v>
@@ -26350,7 +26350,7 @@
         <v>3</v>
       </c>
       <c r="G926" t="s">
-        <v>342</v>
+        <v>410</v>
       </c>
       <c r="H926" t="s">
         <v>9</v>
@@ -26376,7 +26376,7 @@
         <v>3</v>
       </c>
       <c r="G927" t="s">
-        <v>342</v>
+        <v>410</v>
       </c>
       <c r="H927" t="s">
         <v>9</v>
@@ -26610,7 +26610,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G936" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="H936" t="s">
         <v>9</v>
@@ -26636,7 +26636,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G937" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="H937" t="s">
         <v>9</v>
@@ -27338,7 +27338,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G964" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H964" t="s">
         <v>9</v>
@@ -27364,7 +27364,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G965" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H965" t="s">
         <v>9</v>
@@ -27390,7 +27390,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G966" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H966" t="s">
         <v>9</v>
@@ -27416,7 +27416,7 @@
         <v>3</v>
       </c>
       <c r="G967" t="s">
-        <v>342</v>
+        <v>410</v>
       </c>
       <c r="H967" t="s">
         <v>9</v>
@@ -27572,7 +27572,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G973" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="H973" t="s">
         <v>9</v>
@@ -27598,7 +27598,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G974" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H974" t="s">
         <v>9</v>
@@ -27624,7 +27624,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G975" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H975" t="s">
         <v>9</v>
@@ -27650,7 +27650,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G976" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H976" t="s">
         <v>9</v>
@@ -27806,7 +27806,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G982" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H982" t="s">
         <v>9</v>
@@ -27832,7 +27832,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G983" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H983" t="s">
         <v>9</v>
@@ -27884,7 +27884,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G985" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H985" t="s">
         <v>9</v>
@@ -27936,7 +27936,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G987" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H987" t="s">
         <v>9</v>
@@ -27988,7 +27988,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G989" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H989" t="s">
         <v>9</v>
@@ -28014,7 +28014,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G990" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H990" t="s">
         <v>9</v>
@@ -28040,7 +28040,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G991" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H991" t="s">
         <v>9</v>
@@ -28066,7 +28066,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G992" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H992" t="s">
         <v>9</v>
@@ -28092,7 +28092,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G993" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H993" t="s">
         <v>9</v>
@@ -28118,7 +28118,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G994" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H994" t="s">
         <v>9</v>
@@ -28144,7 +28144,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G995" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H995" t="s">
         <v>9</v>
@@ -28170,7 +28170,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G996" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H996" t="s">
         <v>9</v>
@@ -28196,7 +28196,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G997" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H997" t="s">
         <v>9</v>
@@ -28222,7 +28222,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G998" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="H998" t="s">
         <v>9</v>
@@ -28248,7 +28248,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G999" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H999" t="s">
         <v>9</v>
@@ -28274,7 +28274,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1000" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H1000" t="s">
         <v>9</v>
@@ -28300,7 +28300,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G1001" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H1001" t="s">
         <v>9</v>
@@ -28326,7 +28326,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G1002" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H1002" t="s">
         <v>9</v>
@@ -28352,7 +28352,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1003" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H1003" t="s">
         <v>9</v>
@@ -28378,7 +28378,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1004" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H1004" t="s">
         <v>9</v>
@@ -28404,7 +28404,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G1005" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H1005" t="s">
         <v>9</v>
@@ -28430,7 +28430,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G1006" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H1006" t="s">
         <v>9</v>
@@ -28456,7 +28456,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1007" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H1007" t="s">
         <v>9</v>
@@ -28482,7 +28482,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1008" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H1008" t="s">
         <v>9</v>
@@ -28508,7 +28508,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1009" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H1009" t="s">
         <v>9</v>
@@ -28534,7 +28534,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G1010" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H1010" t="s">
         <v>9</v>
@@ -28560,7 +28560,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1011" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H1011" t="s">
         <v>9</v>
@@ -28586,7 +28586,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G1012" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H1012" t="s">
         <v>9</v>
@@ -28612,7 +28612,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1013" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H1013" t="s">
         <v>9</v>
@@ -28638,7 +28638,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G1014" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H1014" t="s">
         <v>9</v>
@@ -28664,7 +28664,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G1015" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H1015" t="s">
         <v>9</v>
@@ -28690,7 +28690,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1016" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H1016" t="s">
         <v>9</v>
@@ -28716,7 +28716,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G1017" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H1017" t="s">
         <v>9</v>
@@ -28742,7 +28742,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G1018" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H1018" t="s">
         <v>9</v>
@@ -28768,7 +28768,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1019" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H1019" t="s">
         <v>9</v>
@@ -28794,7 +28794,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1020" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H1020" t="s">
         <v>9</v>
@@ -28820,7 +28820,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G1021" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H1021" t="s">
         <v>9</v>
@@ -28846,7 +28846,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1022" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H1022" t="s">
         <v>9</v>
@@ -28924,7 +28924,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G1025" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H1025" t="s">
         <v>9</v>
@@ -28950,7 +28950,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1026" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H1026" t="s">
         <v>9</v>
@@ -28976,7 +28976,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1027" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H1027" t="s">
         <v>9</v>
@@ -29002,7 +29002,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G1028" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H1028" t="s">
         <v>9</v>
@@ -29028,7 +29028,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G1029" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H1029" t="s">
         <v>9</v>
@@ -29106,7 +29106,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1032" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H1032" t="s">
         <v>9</v>
@@ -29132,7 +29132,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1033" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H1033" t="s">
         <v>9</v>
@@ -29158,7 +29158,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G1034" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H1034" t="s">
         <v>9</v>
@@ -29184,7 +29184,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G1035" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H1035" t="s">
         <v>9</v>
@@ -29210,7 +29210,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G1036" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H1036" t="s">
         <v>9</v>
@@ -29236,7 +29236,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1037" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H1037" t="s">
         <v>9</v>
@@ -29262,7 +29262,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G1038" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H1038" t="s">
         <v>9</v>
@@ -29392,7 +29392,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G1043" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H1043" t="s">
         <v>9</v>
@@ -29418,7 +29418,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G1044" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H1044" t="s">
         <v>9</v>
@@ -29444,7 +29444,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G1045" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H1045" t="s">
         <v>9</v>
@@ -29470,7 +29470,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1046" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H1046" t="s">
         <v>9</v>
@@ -29496,7 +29496,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G1047" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H1047" t="s">
         <v>9</v>
@@ -29522,7 +29522,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1048" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H1048" t="s">
         <v>9</v>
@@ -29600,7 +29600,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1051" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H1051" t="s">
         <v>9</v>
@@ -29626,7 +29626,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G1052" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H1052" t="s">
         <v>9</v>
@@ -29652,7 +29652,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G1053" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="H1053" t="s">
         <v>9</v>
@@ -29678,7 +29678,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G1054" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="H1054" t="s">
         <v>9</v>
@@ -29704,7 +29704,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G1055" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="H1055" t="s">
         <v>9</v>
@@ -29730,7 +29730,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G1056" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="H1056" t="s">
         <v>9</v>
@@ -29756,7 +29756,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1057" t="s">
-        <v>384</v>
+        <v>327</v>
       </c>
       <c r="H1057" t="s">
         <v>9</v>
@@ -29782,7 +29782,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G1058" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="H1058" t="s">
         <v>9</v>
@@ -29808,7 +29808,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G1059" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="H1059" t="s">
         <v>9</v>
@@ -30354,7 +30354,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1080" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H1080" t="s">
         <v>9</v>
@@ -30640,7 +30640,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G1091" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="H1091" t="s">
         <v>9</v>
@@ -30718,7 +30718,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G1094" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="H1094" t="s">
         <v>9</v>
@@ -30796,7 +30796,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G1097" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="H1097" t="s">
         <v>9</v>
@@ -30822,7 +30822,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G1098" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="H1098" t="s">
         <v>9</v>
@@ -30848,7 +30848,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G1099" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H1099" t="s">
         <v>9</v>
@@ -30874,7 +30874,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G1100" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H1100" t="s">
         <v>9</v>
@@ -30900,7 +30900,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1101" t="s">
-        <v>384</v>
+        <v>327</v>
       </c>
       <c r="H1101" t="s">
         <v>9</v>
@@ -31212,7 +31212,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G1113" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="H1113" t="s">
         <v>9</v>
@@ -31576,7 +31576,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1127" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H1127" t="s">
         <v>9</v>
@@ -31628,7 +31628,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G1129" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="H1129" t="s">
         <v>9</v>
@@ -31654,7 +31654,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1130" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H1130" t="s">
         <v>9</v>
@@ -31836,7 +31836,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G1137" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="H1137" t="s">
         <v>9</v>
@@ -31862,7 +31862,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G1138" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="H1138" t="s">
         <v>9</v>
@@ -32356,7 +32356,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G1157" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H1157" t="s">
         <v>9</v>
@@ -32382,7 +32382,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G1158" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="H1158" t="s">
         <v>9</v>
@@ -32408,7 +32408,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G1159" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="H1159" t="s">
         <v>9</v>
@@ -32902,7 +32902,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1178" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H1178" t="s">
         <v>9</v>
@@ -32928,7 +32928,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1179" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H1179" t="s">
         <v>9</v>
@@ -33006,7 +33006,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1182" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H1182" t="s">
         <v>9</v>
@@ -33032,7 +33032,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1183" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H1183" t="s">
         <v>9</v>
@@ -33058,7 +33058,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G1184" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="H1184" t="s">
         <v>9</v>
@@ -33084,7 +33084,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G1185" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H1185" t="s">
         <v>9</v>
@@ -33188,7 +33188,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G1189" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="H1189" t="s">
         <v>9</v>
@@ -33292,7 +33292,7 @@
         <v>3</v>
       </c>
       <c r="G1193" t="s">
-        <v>342</v>
+        <v>410</v>
       </c>
       <c r="H1193" t="s">
         <v>9</v>
@@ -33318,7 +33318,7 @@
         <v>3</v>
       </c>
       <c r="G1194" t="s">
-        <v>342</v>
+        <v>410</v>
       </c>
       <c r="H1194" t="s">
         <v>9</v>
@@ -33344,7 +33344,7 @@
         <v>3</v>
       </c>
       <c r="G1195" t="s">
-        <v>342</v>
+        <v>410</v>
       </c>
       <c r="H1195" t="s">
         <v>9</v>
@@ -33370,7 +33370,7 @@
         <v>3</v>
       </c>
       <c r="G1196" t="s">
-        <v>342</v>
+        <v>410</v>
       </c>
       <c r="H1196" t="s">
         <v>9</v>
@@ -33396,7 +33396,7 @@
         <v>3</v>
       </c>
       <c r="G1197" t="s">
-        <v>342</v>
+        <v>410</v>
       </c>
       <c r="H1197" t="s">
         <v>9</v>
@@ -33422,7 +33422,7 @@
         <v>3</v>
       </c>
       <c r="G1198" t="s">
-        <v>342</v>
+        <v>410</v>
       </c>
       <c r="H1198" t="s">
         <v>9</v>
@@ -33448,7 +33448,7 @@
         <v>3</v>
       </c>
       <c r="G1199" t="s">
-        <v>342</v>
+        <v>410</v>
       </c>
       <c r="H1199" t="s">
         <v>9</v>
@@ -35008,7 +35008,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1259" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H1259" t="s">
         <v>9</v>
@@ -35138,7 +35138,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G1264" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="H1264" t="s">
         <v>9</v>
@@ -35164,7 +35164,7 @@
         <v>3.25</v>
       </c>
       <c r="G1265" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="H1265" t="s">
         <v>9</v>
@@ -35216,7 +35216,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G1267" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="H1267" t="s">
         <v>9</v>
@@ -35242,7 +35242,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1268" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H1268" t="s">
         <v>9</v>
@@ -35268,7 +35268,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1269" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H1269" t="s">
         <v>9</v>
@@ -35294,7 +35294,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1270" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H1270" t="s">
         <v>9</v>
@@ -35320,7 +35320,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G1271" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="H1271" t="s">
         <v>9</v>
@@ -35346,7 +35346,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G1272" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H1272" t="s">
         <v>9</v>
@@ -35372,7 +35372,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G1273" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H1273" t="s">
         <v>9</v>
@@ -35398,7 +35398,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G1274" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="H1274" t="s">
         <v>9</v>
@@ -35424,7 +35424,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1275" t="s">
-        <v>384</v>
+        <v>327</v>
       </c>
       <c r="H1275" t="s">
         <v>9</v>
@@ -35450,7 +35450,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G1276" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="H1276" t="s">
         <v>9</v>
@@ -35476,7 +35476,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1277" t="s">
-        <v>384</v>
+        <v>327</v>
       </c>
       <c r="H1277" t="s">
         <v>9</v>
@@ -35502,7 +35502,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G1278" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="H1278" t="s">
         <v>9</v>
@@ -35528,7 +35528,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G1279" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="H1279" t="s">
         <v>9</v>
@@ -35606,7 +35606,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1282" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H1282" t="s">
         <v>9</v>
@@ -35632,7 +35632,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1283" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H1283" t="s">
         <v>9</v>
@@ -35658,7 +35658,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1284" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H1284" t="s">
         <v>9</v>
@@ -35684,7 +35684,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G1285" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H1285" t="s">
         <v>9</v>
@@ -35710,7 +35710,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G1286" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="H1286" t="s">
         <v>9</v>
@@ -35736,7 +35736,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G1287" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="H1287" t="s">
         <v>9</v>
@@ -35762,7 +35762,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G1288" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="H1288" t="s">
         <v>9</v>
@@ -35814,7 +35814,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G1290" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H1290" t="s">
         <v>9</v>
@@ -35866,7 +35866,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1292" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H1292" t="s">
         <v>9</v>
@@ -35892,7 +35892,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G1293" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H1293" t="s">
         <v>9</v>
@@ -35918,7 +35918,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G1294" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H1294" t="s">
         <v>9</v>
@@ -35944,7 +35944,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1295" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H1295" t="s">
         <v>9</v>
@@ -35970,7 +35970,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G1296" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H1296" t="s">
         <v>9</v>
@@ -35996,7 +35996,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G1297" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H1297" t="s">
         <v>9</v>
@@ -36074,7 +36074,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G1300" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H1300" t="s">
         <v>9</v>
@@ -36126,7 +36126,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G1302" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H1302" t="s">
         <v>9</v>
@@ -36204,7 +36204,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1305" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H1305" t="s">
         <v>9</v>
@@ -36230,7 +36230,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1306" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H1306" t="s">
         <v>9</v>
@@ -36256,7 +36256,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1307" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H1307" t="s">
         <v>9</v>
@@ -36282,7 +36282,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1308" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H1308" t="s">
         <v>9</v>
@@ -36360,7 +36360,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G1311" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H1311" t="s">
         <v>9</v>
@@ -36386,7 +36386,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G1312" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H1312" t="s">
         <v>9</v>
@@ -36412,7 +36412,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G1313" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H1313" t="s">
         <v>9</v>
@@ -36438,7 +36438,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G1314" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H1314" t="s">
         <v>9</v>
@@ -36516,7 +36516,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G1317" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H1317" t="s">
         <v>9</v>
@@ -36724,7 +36724,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G1325" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H1325" t="s">
         <v>9</v>
@@ -36750,7 +36750,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G1326" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H1326" t="s">
         <v>9</v>
@@ -36776,7 +36776,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G1327" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H1327" t="s">
         <v>9</v>
@@ -36802,7 +36802,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1328" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H1328" t="s">
         <v>9</v>
@@ -36854,7 +36854,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1330" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H1330" t="s">
         <v>9</v>
@@ -36906,7 +36906,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1332" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H1332" t="s">
         <v>9</v>
@@ -36932,7 +36932,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1333" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H1333" t="s">
         <v>9</v>
@@ -36958,7 +36958,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1334" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H1334" t="s">
         <v>9</v>
@@ -37140,7 +37140,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1341" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H1341" t="s">
         <v>9</v>
@@ -37374,7 +37374,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1350" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H1350" t="s">
         <v>9</v>
@@ -37400,7 +37400,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1351" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H1351" t="s">
         <v>9</v>
@@ -37426,7 +37426,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1352" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H1352" t="s">
         <v>9</v>
@@ -37452,7 +37452,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1353" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H1353" t="s">
         <v>9</v>
@@ -37660,7 +37660,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1361" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H1361" t="s">
         <v>9</v>
@@ -37686,7 +37686,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1362" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H1362" t="s">
         <v>9</v>
@@ -37712,7 +37712,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1363" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H1363" t="s">
         <v>9</v>
@@ -37738,7 +37738,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1364" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H1364" t="s">
         <v>9</v>
@@ -37764,7 +37764,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1365" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H1365" t="s">
         <v>9</v>
@@ -37790,7 +37790,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1366" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H1366" t="s">
         <v>9</v>
@@ -37816,7 +37816,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1367" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H1367" t="s">
         <v>9</v>
@@ -37894,7 +37894,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1370" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H1370" t="s">
         <v>9</v>
@@ -37920,7 +37920,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1371" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H1371" t="s">
         <v>9</v>
@@ -37946,7 +37946,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1372" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H1372" t="s">
         <v>9</v>
@@ -37972,7 +37972,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1373" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H1373" t="s">
         <v>9</v>
@@ -38050,7 +38050,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1376" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H1376" t="s">
         <v>9</v>
@@ -38102,7 +38102,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1378" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H1378" t="s">
         <v>9</v>
@@ -38154,7 +38154,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1380" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H1380" t="s">
         <v>9</v>
@@ -38206,7 +38206,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1382" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H1382" t="s">
         <v>9</v>
@@ -38232,7 +38232,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1383" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H1383" t="s">
         <v>9</v>
@@ -38284,7 +38284,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1385" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H1385" t="s">
         <v>9</v>
@@ -38336,7 +38336,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1387" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H1387" t="s">
         <v>9</v>
@@ -38414,7 +38414,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1390" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H1390" t="s">
         <v>9</v>
@@ -38440,7 +38440,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1391" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H1391" t="s">
         <v>9</v>
@@ -38466,7 +38466,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1392" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H1392" t="s">
         <v>9</v>
@@ -38492,7 +38492,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1393" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H1393" t="s">
         <v>9</v>
@@ -38518,7 +38518,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1394" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H1394" t="s">
         <v>9</v>
@@ -38544,7 +38544,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1395" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H1395" t="s">
         <v>9</v>
@@ -38570,7 +38570,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1396" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H1396" t="s">
         <v>9</v>
@@ -38596,7 +38596,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1397" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H1397" t="s">
         <v>9</v>
@@ -38622,7 +38622,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1398" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H1398" t="s">
         <v>9</v>
@@ -38648,7 +38648,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1399" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H1399" t="s">
         <v>9</v>
@@ -38674,7 +38674,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1400" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H1400" t="s">
         <v>9</v>
@@ -38700,7 +38700,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1401" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H1401" t="s">
         <v>9</v>
@@ -38726,7 +38726,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1402" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H1402" t="s">
         <v>9</v>
@@ -38752,7 +38752,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1403" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H1403" t="s">
         <v>9</v>
@@ -38778,7 +38778,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1404" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H1404" t="s">
         <v>9</v>
@@ -38804,7 +38804,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1405" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H1405" t="s">
         <v>9</v>
@@ -38830,7 +38830,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1406" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H1406" t="s">
         <v>9</v>
@@ -38856,7 +38856,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G1407" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="H1407" t="s">
         <v>9</v>
@@ -38882,7 +38882,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1408" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H1408" t="s">
         <v>9</v>
@@ -38908,7 +38908,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1409" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H1409" t="s">
         <v>9</v>
@@ -38934,7 +38934,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1410" t="s">
-        <v>384</v>
+        <v>327</v>
       </c>
       <c r="H1410" t="s">
         <v>9</v>
@@ -38960,7 +38960,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1411" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H1411" t="s">
         <v>9</v>
@@ -38986,7 +38986,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1412" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H1412" t="s">
         <v>9</v>
@@ -39012,7 +39012,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1413" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H1413" t="s">
         <v>9</v>
@@ -39038,7 +39038,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1414" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H1414" t="s">
         <v>9</v>
@@ -39090,7 +39090,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1416" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H1416" t="s">
         <v>9</v>
@@ -39116,7 +39116,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G1417" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="H1417" t="s">
         <v>9</v>
@@ -39142,7 +39142,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1418" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H1418" t="s">
         <v>9</v>
@@ -39194,7 +39194,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1420" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H1420" t="s">
         <v>9</v>
@@ -39272,7 +39272,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1423" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H1423" t="s">
         <v>9</v>
@@ -39298,7 +39298,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1424" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H1424" t="s">
         <v>9</v>
@@ -39506,7 +39506,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1432" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H1432" t="s">
         <v>9</v>
@@ -39532,7 +39532,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1433" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H1433" t="s">
         <v>9</v>
@@ -39792,7 +39792,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1443" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H1443" t="s">
         <v>9</v>
@@ -39818,7 +39818,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1444" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H1444" t="s">
         <v>9</v>
@@ -39844,7 +39844,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1445" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H1445" t="s">
         <v>9</v>
@@ -39922,7 +39922,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1448" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H1448" t="s">
         <v>9</v>
@@ -40026,7 +40026,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1452" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H1452" t="s">
         <v>9</v>
@@ -40052,7 +40052,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1453" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H1453" t="s">
         <v>9</v>
@@ -40078,7 +40078,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1454" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H1454" t="s">
         <v>9</v>
@@ -40104,7 +40104,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1455" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H1455" t="s">
         <v>9</v>
@@ -42938,7 +42938,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1564" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H1564" t="s">
         <v>9</v>
@@ -42964,7 +42964,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G1565" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="H1565" t="s">
         <v>9</v>
@@ -42990,7 +42990,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1566" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H1566" t="s">
         <v>9</v>
@@ -43016,7 +43016,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1567" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H1567" t="s">
         <v>9</v>
@@ -43042,7 +43042,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1568" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H1568" t="s">
         <v>9</v>
@@ -43068,7 +43068,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1569" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H1569" t="s">
         <v>9</v>
@@ -43094,7 +43094,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1570" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H1570" t="s">
         <v>9</v>
@@ -43120,7 +43120,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1571" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H1571" t="s">
         <v>9</v>
@@ -43146,7 +43146,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1572" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H1572" t="s">
         <v>9</v>
@@ -43172,7 +43172,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G1573" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="H1573" t="s">
         <v>9</v>
@@ -43224,7 +43224,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1575" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H1575" t="s">
         <v>9</v>
@@ -43250,7 +43250,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1576" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H1576" t="s">
         <v>9</v>
@@ -43276,7 +43276,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1577" t="s">
-        <v>384</v>
+        <v>327</v>
       </c>
       <c r="H1577" t="s">
         <v>9</v>
@@ -43302,7 +43302,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G1578" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="H1578" t="s">
         <v>9</v>
@@ -43354,7 +43354,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1580" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H1580" t="s">
         <v>9</v>
@@ -44134,7 +44134,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G1610" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H1610" t="s">
         <v>9</v>
@@ -44186,7 +44186,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G1612" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H1612" t="s">
         <v>9</v>
@@ -44238,7 +44238,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G1614" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="H1614" t="s">
         <v>9</v>
@@ -44342,7 +44342,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G1618" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H1618" t="s">
         <v>9</v>
@@ -44368,7 +44368,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G1619" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H1619" t="s">
         <v>9</v>
@@ -44394,7 +44394,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1620" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H1620" t="s">
         <v>9</v>
@@ -44420,7 +44420,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G1621" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H1621" t="s">
         <v>9</v>
@@ -44966,7 +44966,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G1642" t="s">
-        <v>497</v>
+        <v>463</v>
       </c>
       <c r="H1642" t="s">
         <v>9</v>
@@ -44992,7 +44992,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G1643" t="s">
-        <v>497</v>
+        <v>463</v>
       </c>
       <c r="H1643" t="s">
         <v>9</v>
@@ -45018,7 +45018,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G1644" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="H1644" t="s">
         <v>9</v>
@@ -45070,7 +45070,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G1646" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="H1646" t="s">
         <v>9</v>
@@ -45096,7 +45096,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1647" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="H1647" t="s">
         <v>9</v>
@@ -45122,7 +45122,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G1648" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="H1648" t="s">
         <v>9</v>
@@ -45174,7 +45174,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1650" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="H1650" t="s">
         <v>9</v>
@@ -45200,7 +45200,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1651" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="H1651" t="s">
         <v>9</v>
@@ -45226,7 +45226,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1652" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="H1652" t="s">
         <v>9</v>
@@ -45252,7 +45252,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G1653" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H1653" t="s">
         <v>9</v>
@@ -45278,7 +45278,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G1654" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="H1654" t="s">
         <v>9</v>
@@ -45304,7 +45304,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G1655" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="H1655" t="s">
         <v>9</v>
@@ -45330,7 +45330,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G1656" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="H1656" t="s">
         <v>9</v>
@@ -45356,7 +45356,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G1657" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="H1657" t="s">
         <v>9</v>
@@ -45408,7 +45408,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G1659" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="H1659" t="s">
         <v>9</v>
@@ -45434,7 +45434,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1660" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="H1660" t="s">
         <v>9</v>
@@ -45460,7 +45460,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G1661" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="H1661" t="s">
         <v>9</v>
@@ -45486,7 +45486,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1662" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H1662" t="s">
         <v>9</v>
@@ -45512,7 +45512,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1663" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H1663" t="s">
         <v>9</v>
@@ -45538,7 +45538,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1664" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H1664" t="s">
         <v>9</v>
@@ -45564,7 +45564,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1665" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H1665" t="s">
         <v>9</v>
@@ -45590,7 +45590,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1666" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H1666" t="s">
         <v>9</v>
@@ -45616,7 +45616,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1667" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="H1667" t="s">
         <v>9</v>
@@ -45642,7 +45642,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G1668" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="H1668" t="s">
         <v>9</v>
@@ -45668,7 +45668,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1669" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="H1669" t="s">
         <v>9</v>
@@ -45694,7 +45694,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1670" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="H1670" t="s">
         <v>9</v>
@@ -45720,7 +45720,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G1671" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="H1671" t="s">
         <v>9</v>
@@ -45746,7 +45746,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1672" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="H1672" t="s">
         <v>9</v>
@@ -45772,7 +45772,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G1673" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="H1673" t="s">
         <v>9</v>
@@ -45798,7 +45798,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G1674" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="H1674" t="s">
         <v>9</v>
@@ -45824,7 +45824,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G1675" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="H1675" t="s">
         <v>9</v>
@@ -45850,7 +45850,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G1676" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="H1676" t="s">
         <v>9</v>
@@ -45876,7 +45876,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1677" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="H1677" t="s">
         <v>9</v>
@@ -45902,7 +45902,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G1678" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H1678" t="s">
         <v>9</v>
@@ -45928,7 +45928,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G1679" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="H1679" t="s">
         <v>9</v>
@@ -45954,7 +45954,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1680" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="H1680" t="s">
         <v>9</v>
@@ -45980,7 +45980,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G1681" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="H1681" t="s">
         <v>9</v>
@@ -46032,7 +46032,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1683" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="H1683" t="s">
         <v>9</v>
@@ -46058,7 +46058,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G1684" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="H1684" t="s">
         <v>9</v>
@@ -46110,7 +46110,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G1686" t="s">
-        <v>497</v>
+        <v>463</v>
       </c>
       <c r="H1686" t="s">
         <v>9</v>
@@ -46136,7 +46136,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G1687" t="s">
-        <v>497</v>
+        <v>463</v>
       </c>
       <c r="H1687" t="s">
         <v>9</v>
@@ -46162,7 +46162,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G1688" t="s">
-        <v>497</v>
+        <v>463</v>
       </c>
       <c r="H1688" t="s">
         <v>9</v>
@@ -46188,7 +46188,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1689" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="H1689" t="s">
         <v>9</v>
@@ -46214,7 +46214,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G1690" t="s">
-        <v>497</v>
+        <v>463</v>
       </c>
       <c r="H1690" t="s">
         <v>9</v>
@@ -46240,7 +46240,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G1691" t="s">
-        <v>497</v>
+        <v>463</v>
       </c>
       <c r="H1691" t="s">
         <v>9</v>
@@ -46266,7 +46266,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G1692" t="s">
-        <v>497</v>
+        <v>463</v>
       </c>
       <c r="H1692" t="s">
         <v>9</v>
@@ -46292,7 +46292,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1693" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H1693" t="s">
         <v>9</v>
@@ -46318,7 +46318,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G1694" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="H1694" t="s">
         <v>9</v>
@@ -46344,7 +46344,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G1695" t="s">
-        <v>497</v>
+        <v>463</v>
       </c>
       <c r="H1695" t="s">
         <v>9</v>
@@ -46422,7 +46422,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G1698" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="H1698" t="s">
         <v>9</v>
@@ -46448,7 +46448,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G1699" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="H1699" t="s">
         <v>9</v>
@@ -46474,7 +46474,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1700" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="H1700" t="s">
         <v>9</v>
@@ -46526,7 +46526,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G1702" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="H1702" t="s">
         <v>9</v>
@@ -46552,7 +46552,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1703" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="H1703" t="s">
         <v>9</v>
@@ -46578,7 +46578,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G1704" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="H1704" t="s">
         <v>9</v>
@@ -46604,7 +46604,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G1705" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="H1705" t="s">
         <v>9</v>
@@ -46630,7 +46630,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1706" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="H1706" t="s">
         <v>9</v>
@@ -46656,7 +46656,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1707" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="H1707" t="s">
         <v>9</v>
@@ -46760,7 +46760,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G1711" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="H1711" t="s">
         <v>9</v>
@@ -46786,7 +46786,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1712" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="H1712" t="s">
         <v>9</v>
@@ -46812,7 +46812,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G1713" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="H1713" t="s">
         <v>9</v>
@@ -46838,7 +46838,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G1714" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="H1714" t="s">
         <v>9</v>
@@ -46864,7 +46864,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G1715" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="H1715" t="s">
         <v>9</v>
@@ -46890,7 +46890,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1716" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="H1716" t="s">
         <v>9</v>
@@ -46916,7 +46916,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G1717" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="H1717" t="s">
         <v>9</v>
@@ -46942,7 +46942,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G1718" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="H1718" t="s">
         <v>9</v>
@@ -46968,7 +46968,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1719" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="H1719" t="s">
         <v>9</v>
@@ -46994,7 +46994,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G1720" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="H1720" t="s">
         <v>9</v>
@@ -47020,7 +47020,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G1721" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="H1721" t="s">
         <v>9</v>
@@ -47046,7 +47046,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G1722" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="H1722" t="s">
         <v>9</v>
@@ -47072,7 +47072,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G1723" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="H1723" t="s">
         <v>9</v>
@@ -47098,7 +47098,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G1724" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="H1724" t="s">
         <v>9</v>
@@ -47124,7 +47124,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G1725" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="H1725" t="s">
         <v>9</v>
@@ -47150,7 +47150,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G1726" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="H1726" t="s">
         <v>9</v>
@@ -47176,7 +47176,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G1727" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="H1727" t="s">
         <v>9</v>
@@ -47202,7 +47202,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G1728" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H1728" t="s">
         <v>9</v>
@@ -47228,7 +47228,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G1729" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="H1729" t="s">
         <v>9</v>
@@ -47254,7 +47254,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G1730" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="H1730" t="s">
         <v>9</v>
@@ -47280,7 +47280,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G1731" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="H1731" t="s">
         <v>9</v>
@@ -47306,7 +47306,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G1732" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="H1732" t="s">
         <v>9</v>
@@ -47332,7 +47332,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G1733" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H1733" t="s">
         <v>9</v>
@@ -47358,7 +47358,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1734" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="H1734" t="s">
         <v>9</v>
@@ -47384,7 +47384,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1735" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="H1735" t="s">
         <v>9</v>
@@ -47410,7 +47410,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G1736" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="H1736" t="s">
         <v>9</v>
@@ -47436,7 +47436,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1737" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="H1737" t="s">
         <v>9</v>
@@ -47462,7 +47462,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G1738" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="H1738" t="s">
         <v>9</v>
@@ -47488,7 +47488,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G1739" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="H1739" t="s">
         <v>9</v>
@@ -47514,7 +47514,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G1740" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="H1740" t="s">
         <v>9</v>
@@ -47540,7 +47540,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1741" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="H1741" t="s">
         <v>9</v>
@@ -47566,7 +47566,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1742" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="H1742" t="s">
         <v>9</v>
@@ -47592,7 +47592,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G1743" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="H1743" t="s">
         <v>9</v>
@@ -47618,7 +47618,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G1744" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H1744" t="s">
         <v>9</v>
@@ -47644,7 +47644,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G1745" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="H1745" t="s">
         <v>9</v>
@@ -47670,7 +47670,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G1746" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="H1746" t="s">
         <v>9</v>
@@ -47696,7 +47696,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1747" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="H1747" t="s">
         <v>9</v>
@@ -47722,7 +47722,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G1748" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="H1748" t="s">
         <v>9</v>
@@ -47748,7 +47748,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G1749" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="H1749" t="s">
         <v>9</v>
@@ -47774,7 +47774,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1750" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H1750" t="s">
         <v>9</v>
@@ -47800,7 +47800,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G1751" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H1751" t="s">
         <v>9</v>
@@ -47826,7 +47826,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1752" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="H1752" t="s">
         <v>9</v>
@@ -47852,7 +47852,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G1753" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="H1753" t="s">
         <v>9</v>
@@ -47878,7 +47878,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G1754" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="H1754" t="s">
         <v>9</v>
@@ -47904,7 +47904,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G1755" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="H1755" t="s">
         <v>9</v>
@@ -47930,7 +47930,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G1756" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="H1756" t="s">
         <v>9</v>
@@ -47956,7 +47956,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1757" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="H1757" t="s">
         <v>9</v>
@@ -47982,7 +47982,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G1758" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="H1758" t="s">
         <v>9</v>
@@ -48008,7 +48008,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G1759" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="H1759" t="s">
         <v>9</v>
@@ -48034,7 +48034,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G1760" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="H1760" t="s">
         <v>9</v>
@@ -48060,7 +48060,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G1761" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="H1761" t="s">
         <v>9</v>
@@ -48086,7 +48086,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G1762" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H1762" t="s">
         <v>9</v>
@@ -48112,7 +48112,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1763" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="H1763" t="s">
         <v>9</v>
@@ -48138,7 +48138,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G1764" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H1764" t="s">
         <v>9</v>
@@ -48164,7 +48164,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G1765" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="H1765" t="s">
         <v>9</v>
@@ -48190,7 +48190,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G1766" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="H1766" t="s">
         <v>9</v>
@@ -48216,7 +48216,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G1767" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="H1767" t="s">
         <v>9</v>
@@ -48242,7 +48242,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G1768" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="H1768" t="s">
         <v>9</v>
@@ -48268,7 +48268,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G1769" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="H1769" t="s">
         <v>9</v>
@@ -48294,7 +48294,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G1770" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="H1770" t="s">
         <v>9</v>
@@ -48320,7 +48320,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G1771" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="H1771" t="s">
         <v>9</v>
@@ -48346,7 +48346,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1772" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="H1772" t="s">
         <v>9</v>
@@ -48372,7 +48372,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1773" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="H1773" t="s">
         <v>9</v>
@@ -48398,7 +48398,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1774" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="H1774" t="s">
         <v>9</v>
@@ -48424,7 +48424,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1775" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="H1775" t="s">
         <v>9</v>
@@ -48450,7 +48450,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1776" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="H1776" t="s">
         <v>9</v>
@@ -48476,7 +48476,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1777" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="H1777" t="s">
         <v>9</v>
@@ -48502,7 +48502,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1778" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="H1778" t="s">
         <v>9</v>
@@ -48528,7 +48528,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1779" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="H1779" t="s">
         <v>9</v>
@@ -48554,7 +48554,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1780" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="H1780" t="s">
         <v>9</v>
@@ -48580,7 +48580,7 @@
         <v>3.25</v>
       </c>
       <c r="G1781" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="H1781" t="s">
         <v>9</v>
@@ -48606,7 +48606,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G1782" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="H1782" t="s">
         <v>9</v>
@@ -48632,7 +48632,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G1783" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="H1783" t="s">
         <v>9</v>
@@ -48658,7 +48658,7 @@
         <v>3.25</v>
       </c>
       <c r="G1784" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="H1784" t="s">
         <v>9</v>
@@ -48684,7 +48684,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G1785" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="H1785" t="s">
         <v>9</v>
@@ -48710,7 +48710,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G1786" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H1786" t="s">
         <v>9</v>
@@ -48736,7 +48736,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G1787" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="H1787" t="s">
         <v>9</v>
@@ -48762,7 +48762,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G1788" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="H1788" t="s">
         <v>9</v>
@@ -48788,7 +48788,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1789" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="H1789" t="s">
         <v>9</v>
@@ -48814,7 +48814,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1790" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="H1790" t="s">
         <v>9</v>
@@ -48840,7 +48840,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1791" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="H1791" t="s">
         <v>9</v>
@@ -48866,7 +48866,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1792" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="H1792" t="s">
         <v>9</v>
@@ -48892,7 +48892,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G1793" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H1793" t="s">
         <v>9</v>
@@ -48918,7 +48918,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1794" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="H1794" t="s">
         <v>9</v>
@@ -48944,7 +48944,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G1795" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="H1795" t="s">
         <v>9</v>
@@ -48970,7 +48970,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G1796" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="H1796" t="s">
         <v>9</v>
@@ -48996,7 +48996,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1797" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="H1797" t="s">
         <v>9</v>
@@ -49022,7 +49022,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G1798" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="H1798" t="s">
         <v>9</v>
@@ -49048,7 +49048,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G1799" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H1799" t="s">
         <v>9</v>
@@ -49074,7 +49074,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G1800" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="H1800" t="s">
         <v>9</v>
@@ -49100,7 +49100,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1801" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="H1801" t="s">
         <v>9</v>
@@ -49126,7 +49126,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G1802" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H1802" t="s">
         <v>9</v>
@@ -49152,7 +49152,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G1803" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H1803" t="s">
         <v>9</v>
@@ -49178,7 +49178,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G1804" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="H1804" t="s">
         <v>9</v>
@@ -49204,7 +49204,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G1805" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="H1805" t="s">
         <v>9</v>
@@ -49230,7 +49230,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G1806" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="H1806" t="s">
         <v>9</v>
@@ -49256,7 +49256,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G1807" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="H1807" t="s">
         <v>9</v>
@@ -49282,7 +49282,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G1808" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="H1808" t="s">
         <v>9</v>
@@ -49308,7 +49308,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1809" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="H1809" t="s">
         <v>9</v>
@@ -49334,7 +49334,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G1810" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="H1810" t="s">
         <v>9</v>
@@ -49360,7 +49360,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1811" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="H1811" t="s">
         <v>9</v>
@@ -49386,7 +49386,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G1812" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="H1812" t="s">
         <v>9</v>
@@ -49412,7 +49412,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G1813" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H1813" t="s">
         <v>9</v>
@@ -49438,7 +49438,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G1814" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="H1814" t="s">
         <v>9</v>
@@ -49464,7 +49464,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1815" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="H1815" t="s">
         <v>9</v>
@@ -49490,7 +49490,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G1816" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="H1816" t="s">
         <v>9</v>
@@ -49516,7 +49516,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G1817" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H1817" t="s">
         <v>9</v>
@@ -49542,7 +49542,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G1818" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H1818" t="s">
         <v>9</v>
@@ -49568,7 +49568,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1819" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="H1819" t="s">
         <v>9</v>
@@ -49594,7 +49594,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1820" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="H1820" t="s">
         <v>9</v>
@@ -49620,7 +49620,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1821" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="H1821" t="s">
         <v>9</v>
@@ -49646,7 +49646,7 @@
         <v>3.25</v>
       </c>
       <c r="G1822" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="H1822" t="s">
         <v>9</v>
@@ -49672,7 +49672,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G1823" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="H1823" t="s">
         <v>9</v>
@@ -49698,7 +49698,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G1824" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="H1824" t="s">
         <v>9</v>
@@ -49724,7 +49724,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G1825" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="H1825" t="s">
         <v>9</v>
@@ -49750,7 +49750,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G1826" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H1826" t="s">
         <v>9</v>
@@ -49776,7 +49776,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G1827" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="H1827" t="s">
         <v>9</v>
@@ -49802,7 +49802,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G1828" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="H1828" t="s">
         <v>9</v>
@@ -49828,7 +49828,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G1829" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="H1829" t="s">
         <v>9</v>
@@ -49854,7 +49854,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1830" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="H1830" t="s">
         <v>9</v>
@@ -49880,7 +49880,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G1831" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="H1831" t="s">
         <v>9</v>
@@ -49906,7 +49906,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1832" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="H1832" t="s">
         <v>9</v>
@@ -49932,7 +49932,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G1833" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="H1833" t="s">
         <v>9</v>
@@ -49958,7 +49958,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G1834" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="H1834" t="s">
         <v>9</v>
@@ -49984,7 +49984,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G1835" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="H1835" t="s">
         <v>9</v>
@@ -50010,7 +50010,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G1836" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="H1836" t="s">
         <v>9</v>
@@ -50036,7 +50036,7 @@
         <v>3.25</v>
       </c>
       <c r="G1837" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="H1837" t="s">
         <v>9</v>
@@ -50062,7 +50062,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G1838" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="H1838" t="s">
         <v>9</v>
@@ -50088,7 +50088,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G1839" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="H1839" t="s">
         <v>9</v>
@@ -50114,7 +50114,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1840" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="H1840" t="s">
         <v>9</v>
@@ -50140,7 +50140,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G1841" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="H1841" t="s">
         <v>9</v>
@@ -50166,7 +50166,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G1842" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="H1842" t="s">
         <v>9</v>
@@ -50192,7 +50192,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G1843" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="H1843" t="s">
         <v>9</v>
@@ -50218,7 +50218,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G1844" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="H1844" t="s">
         <v>9</v>
@@ -50244,7 +50244,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1845" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="H1845" t="s">
         <v>9</v>
@@ -50270,7 +50270,7 @@
         <v>3.25</v>
       </c>
       <c r="G1846" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="H1846" t="s">
         <v>9</v>
@@ -50296,7 +50296,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1847" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="H1847" t="s">
         <v>9</v>
@@ -50322,7 +50322,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G1848" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="H1848" t="s">
         <v>9</v>
@@ -50348,7 +50348,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G1849" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="H1849" t="s">
         <v>9</v>
@@ -50374,7 +50374,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1850" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="H1850" t="s">
         <v>9</v>
@@ -50400,7 +50400,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1851" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="H1851" t="s">
         <v>9</v>
@@ -50426,7 +50426,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1852" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="H1852" t="s">
         <v>9</v>
@@ -50452,7 +50452,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G1853" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="H1853" t="s">
         <v>9</v>
@@ -50478,7 +50478,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1854" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="H1854" t="s">
         <v>9</v>
@@ -50504,7 +50504,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1855" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="H1855" t="s">
         <v>9</v>
@@ -50530,7 +50530,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G1856" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="H1856" t="s">
         <v>9</v>
@@ -50556,7 +50556,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1857" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="H1857" t="s">
         <v>9</v>
@@ -50582,7 +50582,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1858" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="H1858" t="s">
         <v>9</v>
@@ -50608,7 +50608,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G1859" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="H1859" t="s">
         <v>9</v>
@@ -50634,7 +50634,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G1860" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="H1860" t="s">
         <v>9</v>
@@ -50660,7 +50660,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G1861" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="H1861" t="s">
         <v>9</v>
@@ -50686,7 +50686,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G1862" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="H1862" t="s">
         <v>9</v>
@@ -50712,7 +50712,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1863" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="H1863" t="s">
         <v>9</v>
@@ -50738,7 +50738,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G1864" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="H1864" t="s">
         <v>9</v>
@@ -50764,7 +50764,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G1865" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="H1865" t="s">
         <v>9</v>
@@ -50790,7 +50790,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G1866" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="H1866" t="s">
         <v>9</v>
@@ -50816,7 +50816,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G1867" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="H1867" t="s">
         <v>9</v>
@@ -50842,7 +50842,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G1868" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="H1868" t="s">
         <v>9</v>
@@ -50868,7 +50868,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G1869" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="H1869" t="s">
         <v>9</v>
@@ -50894,7 +50894,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G1870" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="H1870" t="s">
         <v>9</v>
@@ -50920,7 +50920,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G1871" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="H1871" t="s">
         <v>9</v>
@@ -50946,7 +50946,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1872" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="H1872" t="s">
         <v>9</v>
@@ -50972,7 +50972,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1873" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="H1873" t="s">
         <v>9</v>
@@ -50998,7 +50998,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1874" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="H1874" t="s">
         <v>9</v>
@@ -51024,7 +51024,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G1875" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="H1875" t="s">
         <v>9</v>
@@ -51050,7 +51050,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1876" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="H1876" t="s">
         <v>9</v>
@@ -51076,7 +51076,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1877" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="H1877" t="s">
         <v>9</v>
@@ -51102,7 +51102,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G1878" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="H1878" t="s">
         <v>9</v>
@@ -51128,7 +51128,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G1879" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="H1879" t="s">
         <v>9</v>
@@ -51154,7 +51154,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G1880" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H1880" t="s">
         <v>9</v>
@@ -51180,7 +51180,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G1881" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H1881" t="s">
         <v>9</v>
@@ -51206,7 +51206,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G1882" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="H1882" t="s">
         <v>9</v>
@@ -51232,7 +51232,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G1883" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H1883" t="s">
         <v>9</v>
@@ -51258,7 +51258,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G1884" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="H1884" t="s">
         <v>9</v>
@@ -51284,7 +51284,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1885" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H1885" t="s">
         <v>9</v>
@@ -51310,7 +51310,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1886" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H1886" t="s">
         <v>9</v>
@@ -51336,7 +51336,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1887" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="H1887" t="s">
         <v>9</v>
@@ -51362,7 +51362,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1888" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="H1888" t="s">
         <v>9</v>
@@ -51388,7 +51388,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G1889" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H1889" t="s">
         <v>9</v>
@@ -51414,7 +51414,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1890" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="H1890" t="s">
         <v>9</v>
@@ -51440,7 +51440,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1891" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="H1891" t="s">
         <v>9</v>
@@ -51466,7 +51466,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G1892" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H1892" t="s">
         <v>9</v>
@@ -51492,7 +51492,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1893" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="H1893" t="s">
         <v>9</v>
@@ -51518,7 +51518,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G1894" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="H1894" t="s">
         <v>9</v>
@@ -51544,7 +51544,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1895" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="H1895" t="s">
         <v>9</v>
@@ -51570,7 +51570,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1896" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="H1896" t="s">
         <v>9</v>
@@ -51596,7 +51596,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1897" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="H1897" t="s">
         <v>9</v>
@@ -51622,7 +51622,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1898" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="H1898" t="s">
         <v>9</v>
@@ -51648,7 +51648,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1899" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="H1899" t="s">
         <v>9</v>
@@ -51674,7 +51674,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1900" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="H1900" t="s">
         <v>9</v>
@@ -51700,7 +51700,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1901" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="H1901" t="s">
         <v>9</v>
@@ -51726,7 +51726,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1902" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="H1902" t="s">
         <v>9</v>
@@ -51752,7 +51752,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G1903" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="H1903" t="s">
         <v>9</v>
@@ -51778,7 +51778,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G1904" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H1904" t="s">
         <v>9</v>
@@ -51804,7 +51804,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1905" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="H1905" t="s">
         <v>9</v>
@@ -51830,7 +51830,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1906" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H1906" t="s">
         <v>9</v>
@@ -51856,7 +51856,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1907" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="H1907" t="s">
         <v>9</v>
@@ -51882,7 +51882,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1908" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="H1908" t="s">
         <v>9</v>
@@ -51908,7 +51908,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1909" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="H1909" t="s">
         <v>9</v>
@@ -51934,7 +51934,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G1910" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H1910" t="s">
         <v>9</v>
@@ -51960,7 +51960,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1911" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="H1911" t="s">
         <v>9</v>
@@ -51986,7 +51986,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1912" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="H1912" t="s">
         <v>9</v>
@@ -52012,7 +52012,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1913" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="H1913" t="s">
         <v>9</v>
@@ -52038,7 +52038,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1914" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="H1914" t="s">
         <v>9</v>
@@ -52064,7 +52064,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1915" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="H1915" t="s">
         <v>9</v>
@@ -52090,7 +52090,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1916" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="H1916" t="s">
         <v>9</v>
@@ -52116,7 +52116,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1917" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="H1917" t="s">
         <v>9</v>
@@ -52142,7 +52142,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G1918" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H1918" t="s">
         <v>9</v>
@@ -52168,7 +52168,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G1919" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="H1919" t="s">
         <v>9</v>
@@ -52194,7 +52194,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G1920" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H1920" t="s">
         <v>9</v>
@@ -52220,7 +52220,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1921" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="H1921" t="s">
         <v>9</v>
@@ -52246,7 +52246,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1922" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="H1922" t="s">
         <v>9</v>
@@ -52272,7 +52272,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G1923" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H1923" t="s">
         <v>9</v>
@@ -52298,7 +52298,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G1924" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H1924" t="s">
         <v>9</v>
@@ -52324,7 +52324,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1925" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="H1925" t="s">
         <v>9</v>
@@ -52350,7 +52350,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G1926" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H1926" t="s">
         <v>9</v>
@@ -52376,7 +52376,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1927" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="H1927" t="s">
         <v>9</v>
@@ -52402,7 +52402,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G1928" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="H1928" t="s">
         <v>9</v>
@@ -52428,7 +52428,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G1929" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H1929" t="s">
         <v>9</v>
@@ -52454,7 +52454,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G1930" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H1930" t="s">
         <v>9</v>
@@ -52480,7 +52480,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G1931" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H1931" t="s">
         <v>9</v>
@@ -52506,7 +52506,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G1932" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H1932" t="s">
         <v>9</v>
@@ -52532,7 +52532,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G1933" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="H1933" t="s">
         <v>9</v>
@@ -52558,7 +52558,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G1934" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="H1934" t="s">
         <v>9</v>
@@ -52584,7 +52584,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1935" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="H1935" t="s">
         <v>9</v>
@@ -52610,7 +52610,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1936" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="H1936" t="s">
         <v>9</v>
@@ -52636,7 +52636,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1937" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="H1937" t="s">
         <v>9</v>
@@ -52662,7 +52662,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1938" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="H1938" t="s">
         <v>9</v>
@@ -52688,7 +52688,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1939" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="H1939" t="s">
         <v>9</v>
@@ -52714,7 +52714,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G1940" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H1940" t="s">
         <v>9</v>
@@ -52740,7 +52740,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1941" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="H1941" t="s">
         <v>9</v>
@@ -52766,7 +52766,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1942" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="H1942" t="s">
         <v>9</v>
@@ -52792,7 +52792,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1943" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="H1943" t="s">
         <v>9</v>
@@ -52818,7 +52818,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1944" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="H1944" t="s">
         <v>9</v>
@@ -52844,7 +52844,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1945" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H1945" t="s">
         <v>9</v>
@@ -52870,7 +52870,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G1946" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="H1946" t="s">
         <v>9</v>
@@ -52896,7 +52896,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1947" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="H1947" t="s">
         <v>9</v>
@@ -52922,7 +52922,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1948" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="H1948" t="s">
         <v>9</v>
@@ -52948,7 +52948,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1949" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="H1949" t="s">
         <v>9</v>
@@ -52974,7 +52974,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G1950" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H1950" t="s">
         <v>9</v>
@@ -53000,7 +53000,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G1951" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H1951" t="s">
         <v>9</v>
@@ -53026,7 +53026,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1952" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="H1952" t="s">
         <v>9</v>
@@ -53052,7 +53052,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1953" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H1953" t="s">
         <v>9</v>
@@ -53078,7 +53078,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1954" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="H1954" t="s">
         <v>9</v>
@@ -53104,7 +53104,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G1955" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H1955" t="s">
         <v>9</v>
@@ -53130,7 +53130,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G1956" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H1956" t="s">
         <v>9</v>
@@ -53156,7 +53156,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G1957" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="H1957" t="s">
         <v>9</v>
@@ -53182,7 +53182,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1958" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H1958" t="s">
         <v>9</v>
@@ -53208,7 +53208,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1959" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H1959" t="s">
         <v>9</v>
@@ -53234,7 +53234,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1960" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H1960" t="s">
         <v>9</v>
@@ -53260,7 +53260,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G1961" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="H1961" t="s">
         <v>9</v>
@@ -53286,7 +53286,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G1962" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H1962" t="s">
         <v>9</v>
@@ -53312,7 +53312,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G1963" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H1963" t="s">
         <v>9</v>
@@ -53338,7 +53338,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G1964" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="H1964" t="s">
         <v>9</v>
@@ -53364,7 +53364,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G1965" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="H1965" t="s">
         <v>9</v>
@@ -53390,7 +53390,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G1966" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="H1966" t="s">
         <v>9</v>
@@ -53416,7 +53416,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1967" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="H1967" t="s">
         <v>9</v>
@@ -53442,7 +53442,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G1968" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="H1968" t="s">
         <v>9</v>
@@ -53468,7 +53468,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G1969" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="H1969" t="s">
         <v>9</v>
@@ -53494,7 +53494,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G1970" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="H1970" t="s">
         <v>9</v>
@@ -53520,7 +53520,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G1971" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="H1971" t="s">
         <v>9</v>
@@ -53546,7 +53546,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G1972" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="H1972" t="s">
         <v>9</v>
@@ -53572,7 +53572,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G1973" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="H1973" t="s">
         <v>9</v>
@@ -53598,7 +53598,7 @@
         <v>3</v>
       </c>
       <c r="G1974" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="H1974" t="s">
         <v>9</v>
@@ -53624,7 +53624,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1975" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="H1975" t="s">
         <v>9</v>
@@ -53650,7 +53650,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G1976" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="H1976" t="s">
         <v>9</v>
@@ -53676,7 +53676,7 @@
         <v>3</v>
       </c>
       <c r="G1977" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="H1977" t="s">
         <v>9</v>
@@ -53702,7 +53702,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G1978" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="H1978" t="s">
         <v>9</v>
@@ -53728,7 +53728,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G1979" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="H1979" t="s">
         <v>9</v>
@@ -53754,7 +53754,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1980" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="H1980" t="s">
         <v>9</v>
@@ -53780,7 +53780,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G1981" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="H1981" t="s">
         <v>9</v>
@@ -53806,7 +53806,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G1982" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="H1982" t="s">
         <v>9</v>
@@ -53832,7 +53832,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1983" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="H1983" t="s">
         <v>9</v>
@@ -53858,7 +53858,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1984" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="H1984" t="s">
         <v>9</v>
@@ -53884,7 +53884,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G1985" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="H1985" t="s">
         <v>9</v>
@@ -53910,7 +53910,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1986" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="H1986" t="s">
         <v>9</v>
@@ -53936,7 +53936,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1987" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="H1987" t="s">
         <v>9</v>
@@ -53962,7 +53962,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G1988" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="H1988" t="s">
         <v>9</v>
@@ -53988,7 +53988,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G1989" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="H1989" t="s">
         <v>9</v>
@@ -54014,7 +54014,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G1990" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="H1990" t="s">
         <v>9</v>
@@ -54040,7 +54040,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G1991" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="H1991" t="s">
         <v>9</v>
@@ -54066,7 +54066,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1992" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="H1992" t="s">
         <v>9</v>
@@ -54092,7 +54092,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1993" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="H1993" t="s">
         <v>9</v>
@@ -54118,7 +54118,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1994" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="H1994" t="s">
         <v>9</v>
@@ -54144,7 +54144,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1995" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="H1995" t="s">
         <v>9</v>
@@ -54170,7 +54170,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G1996" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="H1996" t="s">
         <v>9</v>
@@ -54196,7 +54196,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G1997" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="H1997" t="s">
         <v>9</v>
@@ -54222,7 +54222,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1998" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="H1998" t="s">
         <v>9</v>
@@ -54248,7 +54248,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1999" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="H1999" t="s">
         <v>9</v>
@@ -54274,7 +54274,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G2000" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="H2000" t="s">
         <v>9</v>
@@ -54300,7 +54300,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G2001" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="H2001" t="s">
         <v>9</v>
@@ -54326,7 +54326,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G2002" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="H2002" t="s">
         <v>9</v>
@@ -54352,7 +54352,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G2003" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="H2003" t="s">
         <v>9</v>
@@ -54378,7 +54378,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G2004" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="H2004" t="s">
         <v>9</v>
@@ -54404,7 +54404,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G2005" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="H2005" t="s">
         <v>9</v>
@@ -54430,7 +54430,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G2006" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="H2006" t="s">
         <v>9</v>
@@ -54456,7 +54456,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G2007" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="H2007" t="s">
         <v>9</v>
@@ -54482,7 +54482,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G2008" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="H2008" t="s">
         <v>9</v>
@@ -54508,7 +54508,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G2009" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="H2009" t="s">
         <v>9</v>
@@ -54534,7 +54534,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G2010" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="H2010" t="s">
         <v>9</v>
@@ -54560,7 +54560,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G2011" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H2011" t="s">
         <v>9</v>
@@ -54586,7 +54586,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G2012" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="H2012" t="s">
         <v>9</v>
@@ -54612,7 +54612,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G2013" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="H2013" t="s">
         <v>9</v>
@@ -54638,7 +54638,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2014" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H2014" t="s">
         <v>9</v>
@@ -54664,7 +54664,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G2015" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H2015" t="s">
         <v>9</v>
@@ -54690,7 +54690,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G2016" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="H2016" t="s">
         <v>9</v>
@@ -54716,7 +54716,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G2017" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="H2017" t="s">
         <v>9</v>
@@ -54742,7 +54742,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2018" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H2018" t="s">
         <v>9</v>
@@ -54768,7 +54768,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2019" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H2019" t="s">
         <v>9</v>
@@ -54794,7 +54794,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G2020" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="H2020" t="s">
         <v>9</v>
@@ -54820,7 +54820,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2021" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H2021" t="s">
         <v>9</v>
@@ -54846,7 +54846,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G2022" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="H2022" t="s">
         <v>9</v>
@@ -54872,7 +54872,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2023" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H2023" t="s">
         <v>9</v>
@@ -54898,7 +54898,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2024" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H2024" t="s">
         <v>9</v>
@@ -54924,7 +54924,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G2025" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="H2025" t="s">
         <v>9</v>
@@ -54950,7 +54950,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G2026" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H2026" t="s">
         <v>9</v>
@@ -54976,7 +54976,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2027" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H2027" t="s">
         <v>9</v>
@@ -55002,7 +55002,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2028" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H2028" t="s">
         <v>9</v>
@@ -55028,7 +55028,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G2029" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H2029" t="s">
         <v>9</v>
@@ -55054,7 +55054,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2030" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H2030" t="s">
         <v>9</v>
@@ -55080,7 +55080,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G2031" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H2031" t="s">
         <v>9</v>
@@ -55106,7 +55106,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G2032" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="H2032" t="s">
         <v>9</v>
@@ -55132,7 +55132,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G2033" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H2033" t="s">
         <v>9</v>
@@ -55158,7 +55158,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G2034" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="H2034" t="s">
         <v>9</v>
@@ -55184,7 +55184,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G2035" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="H2035" t="s">
         <v>9</v>
@@ -55210,7 +55210,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2036" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H2036" t="s">
         <v>9</v>
@@ -55236,7 +55236,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G2037" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H2037" t="s">
         <v>9</v>
@@ -55262,7 +55262,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G2038" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H2038" t="s">
         <v>9</v>
@@ -55288,7 +55288,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2039" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H2039" t="s">
         <v>9</v>
@@ -55314,7 +55314,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G2040" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="H2040" t="s">
         <v>9</v>
@@ -55340,7 +55340,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G2041" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="H2041" t="s">
         <v>9</v>
@@ -55366,7 +55366,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G2042" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="H2042" t="s">
         <v>9</v>
@@ -55392,7 +55392,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G2043" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="H2043" t="s">
         <v>9</v>
@@ -55418,7 +55418,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2044" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H2044" t="s">
         <v>9</v>
@@ -55444,7 +55444,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2045" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H2045" t="s">
         <v>9</v>
@@ -55470,7 +55470,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2046" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H2046" t="s">
         <v>9</v>
@@ -55496,7 +55496,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G2047" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H2047" t="s">
         <v>9</v>
@@ -55522,7 +55522,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2048" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H2048" t="s">
         <v>9</v>
@@ -55548,7 +55548,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2049" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H2049" t="s">
         <v>9</v>
@@ -55574,7 +55574,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2050" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H2050" t="s">
         <v>9</v>
@@ -55600,7 +55600,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G2051" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="H2051" t="s">
         <v>9</v>
@@ -55626,7 +55626,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G2052" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H2052" t="s">
         <v>9</v>
@@ -55652,7 +55652,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G2053" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H2053" t="s">
         <v>9</v>
@@ -55678,7 +55678,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2054" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H2054" t="s">
         <v>9</v>
@@ -55704,7 +55704,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G2055" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="H2055" t="s">
         <v>9</v>
@@ -55730,7 +55730,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2056" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H2056" t="s">
         <v>9</v>
@@ -55756,7 +55756,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2057" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H2057" t="s">
         <v>9</v>
@@ -55782,7 +55782,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G2058" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="H2058" t="s">
         <v>9</v>
@@ -55808,7 +55808,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G2059" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="H2059" t="s">
         <v>9</v>
@@ -55834,7 +55834,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2060" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H2060" t="s">
         <v>9</v>
@@ -55860,7 +55860,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2061" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H2061" t="s">
         <v>9</v>
@@ -55886,7 +55886,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2062" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H2062" t="s">
         <v>9</v>
@@ -55912,7 +55912,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G2063" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H2063" t="s">
         <v>9</v>
@@ -55938,7 +55938,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G2064" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H2064" t="s">
         <v>9</v>
@@ -55964,7 +55964,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G2065" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H2065" t="s">
         <v>9</v>
@@ -55990,7 +55990,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G2066" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H2066" t="s">
         <v>9</v>
@@ -56016,7 +56016,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G2067" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="H2067" t="s">
         <v>9</v>
@@ -56042,7 +56042,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G2068" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="H2068" t="s">
         <v>9</v>
@@ -56068,7 +56068,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G2069" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="H2069" t="s">
         <v>9</v>
@@ -56094,7 +56094,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G2070" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H2070" t="s">
         <v>9</v>
@@ -56120,7 +56120,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G2071" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="H2071" t="s">
         <v>9</v>
@@ -56146,7 +56146,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G2072" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H2072" t="s">
         <v>9</v>
@@ -56172,7 +56172,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G2073" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="H2073" t="s">
         <v>9</v>
@@ -56198,7 +56198,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2074" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H2074" t="s">
         <v>9</v>
@@ -56224,7 +56224,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G2075" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H2075" t="s">
         <v>9</v>
@@ -56250,7 +56250,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G2076" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H2076" t="s">
         <v>9</v>
@@ -56276,7 +56276,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G2077" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H2077" t="s">
         <v>9</v>
@@ -56302,7 +56302,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G2078" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="H2078" t="s">
         <v>9</v>
@@ -56328,7 +56328,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G2079" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="H2079" t="s">
         <v>9</v>
@@ -56354,7 +56354,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G2080" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="H2080" t="s">
         <v>9</v>
@@ -56380,7 +56380,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G2081" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="H2081" t="s">
         <v>9</v>
@@ -56406,7 +56406,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G2082" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="H2082" t="s">
         <v>9</v>
@@ -56432,7 +56432,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G2083" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="H2083" t="s">
         <v>9</v>
@@ -56458,7 +56458,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G2084" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="H2084" t="s">
         <v>9</v>
@@ -56484,7 +56484,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G2085" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="H2085" t="s">
         <v>9</v>
@@ -56510,7 +56510,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G2086" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="H2086" t="s">
         <v>9</v>
@@ -56536,7 +56536,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G2087" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="H2087" t="s">
         <v>9</v>
@@ -56562,7 +56562,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G2088" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="H2088" t="s">
         <v>9</v>
@@ -56588,7 +56588,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2089" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H2089" t="s">
         <v>9</v>
@@ -56614,7 +56614,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G2090" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="H2090" t="s">
         <v>9</v>
@@ -56640,7 +56640,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2091" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H2091" t="s">
         <v>9</v>
@@ -56666,7 +56666,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2092" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H2092" t="s">
         <v>9</v>
@@ -56692,7 +56692,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2093" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H2093" t="s">
         <v>9</v>
@@ -56718,7 +56718,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G2094" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H2094" t="s">
         <v>9</v>
@@ -56744,7 +56744,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G2095" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="H2095" t="s">
         <v>9</v>
@@ -56770,7 +56770,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G2096" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="H2096" t="s">
         <v>9</v>
@@ -56796,7 +56796,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G2097" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H2097" t="s">
         <v>9</v>
@@ -56822,7 +56822,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G2098" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="H2098" t="s">
         <v>9</v>
@@ -56848,7 +56848,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G2099" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="H2099" t="s">
         <v>9</v>
@@ -56874,7 +56874,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G2100" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H2100" t="s">
         <v>9</v>
@@ -56900,7 +56900,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G2101" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="H2101" t="s">
         <v>9</v>
@@ -56926,7 +56926,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G2102" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="H2102" t="s">
         <v>9</v>
@@ -56952,7 +56952,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G2103" t="s">
-        <v>506</v>
+        <v>557</v>
       </c>
       <c r="H2103" t="s">
         <v>9</v>
@@ -56978,7 +56978,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G2104" t="s">
-        <v>506</v>
+        <v>557</v>
       </c>
       <c r="H2104" t="s">
         <v>9</v>
@@ -57004,7 +57004,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G2105" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H2105" t="s">
         <v>9</v>
@@ -57030,7 +57030,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G2106" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H2106" t="s">
         <v>9</v>
@@ -57056,7 +57056,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G2107" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="H2107" t="s">
         <v>9</v>
@@ -57082,7 +57082,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G2108" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H2108" t="s">
         <v>9</v>
@@ -57108,7 +57108,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G2109" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H2109" t="s">
         <v>9</v>
@@ -57134,7 +57134,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G2110" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H2110" t="s">
         <v>9</v>
@@ -57160,7 +57160,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G2111" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H2111" t="s">
         <v>9</v>
@@ -57212,7 +57212,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G2113" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H2113" t="s">
         <v>9</v>
@@ -57238,7 +57238,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G2114" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H2114" t="s">
         <v>9</v>
@@ -57264,7 +57264,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G2115" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H2115" t="s">
         <v>9</v>
@@ -57290,7 +57290,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G2116" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="H2116" t="s">
         <v>9</v>
@@ -57394,7 +57394,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G2120" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="H2120" t="s">
         <v>9</v>
@@ -57472,7 +57472,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2123" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H2123" t="s">
         <v>9</v>
@@ -57654,7 +57654,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G2130" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="H2130" t="s">
         <v>9</v>
@@ -57680,7 +57680,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G2131" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="H2131" t="s">
         <v>9</v>
@@ -57706,7 +57706,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G2132" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="H2132" t="s">
         <v>9</v>
@@ -62568,7 +62568,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G2319" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="H2319" t="s">
         <v>9</v>
@@ -67100,7 +67100,7 @@
     </row>
     <row r="2494">
       <c r="A2494" s="1" t="n">
-        <v>45951.6493055556</v>
+        <v>45951.2916666667</v>
       </c>
       <c r="B2494" t="n">
         <v>7607</v>
@@ -67121,6 +67121,32 @@
         <v>639</v>
       </c>
       <c r="H2494" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2495">
+      <c r="A2495" s="1" t="n">
+        <v>45952.6494328704</v>
+      </c>
+      <c r="B2495" t="n">
+        <v>6467</v>
+      </c>
+      <c r="C2495" t="n">
+        <v>4.78000020980835</v>
+      </c>
+      <c r="D2495" t="n">
+        <v>4.65999984741211</v>
+      </c>
+      <c r="E2495" t="n">
+        <v>4.73999977111816</v>
+      </c>
+      <c r="F2495" t="n">
+        <v>4.69999980926514</v>
+      </c>
+      <c r="G2495" t="s">
+        <v>639</v>
+      </c>
+      <c r="H2495" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ENV.MI.xlsx
+++ b/data/ENV.MI.xlsx
@@ -44,7 +44,7 @@
     <t xml:space="preserve">ENV.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20979809761047</t>
+    <t xml:space="preserve">2.20979785919189</t>
   </si>
   <si>
     <t xml:space="preserve">2.1447126865387</t>
@@ -56,85 +56,85 @@
     <t xml:space="preserve">2.03778696060181</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08272671699524</t>
+    <t xml:space="preserve">2.08272647857666</t>
   </si>
   <si>
     <t xml:space="preserve">2.05328345298767</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03623747825623</t>
+    <t xml:space="preserve">2.03623723983765</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96805274486542</t>
+    <t xml:space="preserve">1.96805262565613</t>
   </si>
   <si>
     <t xml:space="preserve">1.96030426025391</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89831852912903</t>
+    <t xml:space="preserve">1.89831864833832</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88127255439758</t>
+    <t xml:space="preserve">1.88127267360687</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96340382099152</t>
+    <t xml:space="preserve">1.96340370178223</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98354959487915</t>
+    <t xml:space="preserve">1.98354935646057</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01299285888672</t>
+    <t xml:space="preserve">2.01299262046814</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93551027774811</t>
+    <t xml:space="preserve">1.93550992012024</t>
   </si>
   <si>
     <t xml:space="preserve">1.93705976009369</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91381514072418</t>
+    <t xml:space="preserve">1.91381549835205</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91071581840515</t>
+    <t xml:space="preserve">1.91071605682373</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8657763004303</t>
+    <t xml:space="preserve">1.86577618122101</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89212012290955</t>
+    <t xml:space="preserve">1.89211988449097</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85182929039001</t>
+    <t xml:space="preserve">1.85182917118073</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93396031856537</t>
+    <t xml:space="preserve">1.93396067619324</t>
   </si>
   <si>
     <t xml:space="preserve">1.86732578277588</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8890209197998</t>
+    <t xml:space="preserve">1.88902056217194</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9866486787796</t>
+    <t xml:space="preserve">1.98664855957031</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11526942253113</t>
+    <t xml:space="preserve">2.11526966094971</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18500375747681</t>
+    <t xml:space="preserve">2.18500351905823</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20824837684631</t>
+    <t xml:space="preserve">2.20824813842773</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16950702667236</t>
+    <t xml:space="preserve">2.16950726509094</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0842764377594</t>
+    <t xml:space="preserve">2.08427619934082</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0145423412323</t>
+    <t xml:space="preserve">2.01454186439514</t>
   </si>
   <si>
     <t xml:space="preserve">2.0052444934845</t>
@@ -143,25 +143,25 @@
     <t xml:space="preserve">2.14626240730286</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22219491004944</t>
+    <t xml:space="preserve">2.22219514846802</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32447195053101</t>
+    <t xml:space="preserve">2.32447171211243</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20049977302551</t>
+    <t xml:space="preserve">2.20050001144409</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27178382873535</t>
+    <t xml:space="preserve">2.27178359031677</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24698948860168</t>
+    <t xml:space="preserve">2.24698925018311</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32137274742126</t>
+    <t xml:space="preserve">2.32137250900269</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28418111801147</t>
+    <t xml:space="preserve">2.2841808795929</t>
   </si>
   <si>
     <t xml:space="preserve">2.37870955467224</t>
@@ -170,22 +170,22 @@
     <t xml:space="preserve">2.35546469688416</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44069504737854</t>
+    <t xml:space="preserve">2.4406955242157</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43139719963074</t>
+    <t xml:space="preserve">2.43139743804932</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4499933719635</t>
+    <t xml:space="preserve">2.44999313354492</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38490796089172</t>
+    <t xml:space="preserve">2.3849081993103</t>
   </si>
   <si>
     <t xml:space="preserve">2.3616635799408</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3632128238678</t>
+    <t xml:space="preserve">2.36321306228638</t>
   </si>
   <si>
     <t xml:space="preserve">2.31982278823853</t>
@@ -197,22 +197,22 @@
     <t xml:space="preserve">2.26868438720703</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32292175292969</t>
+    <t xml:space="preserve">2.32292222976685</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33531951904297</t>
+    <t xml:space="preserve">2.33531928062439</t>
   </si>
   <si>
     <t xml:space="preserve">2.33996844291687</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31052494049072</t>
+    <t xml:space="preserve">2.3105251789093</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28573060035706</t>
+    <t xml:space="preserve">2.28573083877563</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25473761558533</t>
+    <t xml:space="preserve">2.25473737716675</t>
   </si>
   <si>
     <t xml:space="preserve">2.29037976264954</t>
@@ -224,7 +224,7 @@
     <t xml:space="preserve">2.23149299621582</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0749785900116</t>
+    <t xml:space="preserve">2.07497835159302</t>
   </si>
   <si>
     <t xml:space="preserve">2.00834369659424</t>
@@ -233,31 +233,31 @@
     <t xml:space="preserve">2.03468728065491</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02229046821594</t>
+    <t xml:space="preserve">2.02229022979736</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97580111026764</t>
+    <t xml:space="preserve">1.97580099105835</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91980683803558</t>
+    <t xml:space="preserve">1.91980648040771</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88216376304626</t>
+    <t xml:space="preserve">1.88216352462769</t>
   </si>
   <si>
     <t xml:space="preserve">2.00136733055115</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96058690547943</t>
+    <t xml:space="preserve">1.96058678627014</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9025536775589</t>
+    <t xml:space="preserve">1.90255355834961</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92137503623962</t>
+    <t xml:space="preserve">1.9213752746582</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91353273391724</t>
+    <t xml:space="preserve">1.91353321075439</t>
   </si>
   <si>
     <t xml:space="preserve">1.89784824848175</t>
@@ -266,37 +266,37 @@
     <t xml:space="preserve">1.89000606536865</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85079407691956</t>
+    <t xml:space="preserve">1.85079395771027</t>
   </si>
   <si>
     <t xml:space="preserve">1.88059508800507</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86647868156433</t>
+    <t xml:space="preserve">1.8664790391922</t>
   </si>
   <si>
-    <t xml:space="preserve">1.546511054039</t>
+    <t xml:space="preserve">1.54651093482971</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68610465526581</t>
+    <t xml:space="preserve">1.6861047744751</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70178973674774</t>
+    <t xml:space="preserve">1.70178949832916</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70022094249725</t>
+    <t xml:space="preserve">1.70022106170654</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66257762908936</t>
+    <t xml:space="preserve">1.66257774829865</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64532470703125</t>
+    <t xml:space="preserve">1.64532458782196</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62336587905884</t>
+    <t xml:space="preserve">1.62336623668671</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61552369594574</t>
+    <t xml:space="preserve">1.61552357673645</t>
   </si>
   <si>
     <t xml:space="preserve">1.63120830059052</t>
@@ -305,7 +305,7 @@
     <t xml:space="preserve">1.58415424823761</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64689302444458</t>
+    <t xml:space="preserve">1.64689290523529</t>
   </si>
   <si>
     <t xml:space="preserve">1.64061915874481</t>
@@ -314,13 +314,13 @@
     <t xml:space="preserve">1.6390506029129</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60768139362335</t>
+    <t xml:space="preserve">1.60768151283264</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57631194591522</t>
+    <t xml:space="preserve">1.57631182670593</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59199678897858</t>
+    <t xml:space="preserve">1.59199655056</t>
   </si>
   <si>
     <t xml:space="preserve">1.75668597221375</t>
@@ -329,25 +329,25 @@
     <t xml:space="preserve">1.84295189380646</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84608864784241</t>
+    <t xml:space="preserve">1.8460887670517</t>
   </si>
   <si>
     <t xml:space="preserve">1.92921757698059</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88530051708221</t>
+    <t xml:space="preserve">1.88530039787292</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90098524093628</t>
+    <t xml:space="preserve">1.9009850025177</t>
   </si>
   <si>
     <t xml:space="preserve">1.91823828220367</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9496077299118</t>
+    <t xml:space="preserve">1.94960761070251</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93078601360321</t>
+    <t xml:space="preserve">1.9307861328125</t>
   </si>
   <si>
     <t xml:space="preserve">1.84922575950623</t>
@@ -356,46 +356,46 @@
     <t xml:space="preserve">1.82413017749786</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85549938678741</t>
+    <t xml:space="preserve">1.85549962520599</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89627957344055</t>
+    <t xml:space="preserve">1.89627969264984</t>
   </si>
   <si>
     <t xml:space="preserve">1.93705999851227</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87432110309601</t>
+    <t xml:space="preserve">1.8743212223053</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94333374500275</t>
+    <t xml:space="preserve">1.94333386421204</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94490218162537</t>
+    <t xml:space="preserve">1.94490253925323</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96686053276062</t>
+    <t xml:space="preserve">1.96686065196991</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9841136932373</t>
+    <t xml:space="preserve">1.98411393165588</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06253743171692</t>
+    <t xml:space="preserve">2.0625376701355</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05312657356262</t>
+    <t xml:space="preserve">2.0531268119812</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05155849456787</t>
+    <t xml:space="preserve">2.05155825614929</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0233256816864</t>
+    <t xml:space="preserve">2.02332544326782</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02959966659546</t>
+    <t xml:space="preserve">2.02959990501404</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03116774559021</t>
+    <t xml:space="preserve">2.03116798400879</t>
   </si>
   <si>
     <t xml:space="preserve">2.06096911430359</t>
@@ -407,10 +407,10 @@
     <t xml:space="preserve">2.08606457710266</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15507698059082</t>
+    <t xml:space="preserve">2.1550772190094</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18801522254944</t>
+    <t xml:space="preserve">2.18801498413086</t>
   </si>
   <si>
     <t xml:space="preserve">2.19585728645325</t>
@@ -419,37 +419,37 @@
     <t xml:space="preserve">2.20213150978088</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23350048065186</t>
+    <t xml:space="preserve">2.23350071907043</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20997405052185</t>
+    <t xml:space="preserve">2.20997333526611</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18017244338989</t>
+    <t xml:space="preserve">2.18017268180847</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16605663299561</t>
+    <t xml:space="preserve">2.16605639457703</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19428896903992</t>
+    <t xml:space="preserve">2.19428873062134</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17389869689941</t>
+    <t xml:space="preserve">2.17389893531799</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2005627155304</t>
+    <t xml:space="preserve">2.20056247711182</t>
   </si>
   <si>
     <t xml:space="preserve">2.21938443183899</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21781611442566</t>
+    <t xml:space="preserve">2.21781587600708</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19115209579468</t>
+    <t xml:space="preserve">2.1911518573761</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12057089805603</t>
+    <t xml:space="preserve">2.12057113647461</t>
   </si>
   <si>
     <t xml:space="preserve">2.15350890159607</t>
@@ -458,91 +458,91 @@
     <t xml:space="preserve">2.11743402481079</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16291928291321</t>
+    <t xml:space="preserve">2.16291975975037</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10802316665649</t>
+    <t xml:space="preserve">2.10802340507507</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01548314094543</t>
+    <t xml:space="preserve">2.01548337936401</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04528450965881</t>
+    <t xml:space="preserve">2.04528427124023</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98568284511566</t>
+    <t xml:space="preserve">1.98568260669708</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07822227478027</t>
+    <t xml:space="preserve">2.07822251319885</t>
   </si>
   <si>
     <t xml:space="preserve">2.06724286079407</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12998151779175</t>
+    <t xml:space="preserve">2.12998175621033</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1158652305603</t>
+    <t xml:space="preserve">2.11586546897888</t>
   </si>
   <si>
     <t xml:space="preserve">2.05469489097595</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11429691314697</t>
+    <t xml:space="preserve">2.11429715156555</t>
   </si>
   <si>
     <t xml:space="preserve">2.05626368522644</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06410574913025</t>
+    <t xml:space="preserve">2.06410551071167</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10488629341125</t>
+    <t xml:space="preserve">2.1048858165741</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00920939445496</t>
+    <t xml:space="preserve">2.00920963287354</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01391506195068</t>
+    <t xml:space="preserve">2.0139148235321</t>
   </si>
   <si>
     <t xml:space="preserve">2.04842138290405</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16448783874512</t>
+    <t xml:space="preserve">2.1644880771637</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18487811088562</t>
+    <t xml:space="preserve">2.18487787246704</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26643872261047</t>
+    <t xml:space="preserve">2.26643848419189</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27271270751953</t>
+    <t xml:space="preserve">2.27271246910095</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25702786445618</t>
+    <t xml:space="preserve">2.25702738761902</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30721879005432</t>
+    <t xml:space="preserve">2.30721855163574</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2303638458252</t>
+    <t xml:space="preserve">2.23036360740662</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37152576446533</t>
+    <t xml:space="preserve">2.37152600288391</t>
   </si>
   <si>
     <t xml:space="preserve">2.35270428657532</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39191603660583</t>
+    <t xml:space="preserve">2.39191627502441</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33545112609863</t>
+    <t xml:space="preserve">2.33545088768005</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3134925365448</t>
+    <t xml:space="preserve">2.31349277496338</t>
   </si>
   <si>
     <t xml:space="preserve">2.37623119354248</t>
@@ -551,64 +551,64 @@
     <t xml:space="preserve">2.32917737960815</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24918508529663</t>
+    <t xml:space="preserve">2.24918532371521</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28839731216431</t>
+    <t xml:space="preserve">2.28839707374573</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33701992034912</t>
+    <t xml:space="preserve">2.33701968193054</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34486174583435</t>
+    <t xml:space="preserve">2.34486198425293</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34956741333008</t>
+    <t xml:space="preserve">2.34956765174866</t>
   </si>
   <si>
     <t xml:space="preserve">2.32604026794434</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30251359939575</t>
+    <t xml:space="preserve">2.30251336097717</t>
   </si>
   <si>
     <t xml:space="preserve">2.31192398071289</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2507541179657</t>
+    <t xml:space="preserve">2.25075340270996</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27428102493286</t>
+    <t xml:space="preserve">2.27428078651428</t>
   </si>
   <si>
     <t xml:space="preserve">2.43897008895874</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48445582389832</t>
+    <t xml:space="preserve">2.48445558547974</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46249723434448</t>
+    <t xml:space="preserve">2.46249771118164</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50798296928406</t>
+    <t xml:space="preserve">2.50798273086548</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4860246181488</t>
+    <t xml:space="preserve">2.48602437973022</t>
   </si>
   <si>
     <t xml:space="preserve">2.60993313789368</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66639852523804</t>
+    <t xml:space="preserve">2.66639828681946</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66326093673706</t>
+    <t xml:space="preserve">2.66326141357422</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66012406349182</t>
+    <t xml:space="preserve">2.6601243019104</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64287114143372</t>
+    <t xml:space="preserve">2.64287137985229</t>
   </si>
   <si>
     <t xml:space="preserve">2.65855598449707</t>
@@ -620,31 +620,31 @@
     <t xml:space="preserve">2.55033159255981</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63816595077515</t>
+    <t xml:space="preserve">2.63816571235657</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58013248443604</t>
+    <t xml:space="preserve">2.58013224601746</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59581708908081</t>
+    <t xml:space="preserve">2.59581685066223</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58170056343079</t>
+    <t xml:space="preserve">2.58170080184937</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60365915298462</t>
+    <t xml:space="preserve">2.6036593914032</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61934423446655</t>
+    <t xml:space="preserve">2.61934399604797</t>
   </si>
   <si>
     <t xml:space="preserve">2.57542705535889</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57385873794556</t>
+    <t xml:space="preserve">2.57385849952698</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50955128669739</t>
+    <t xml:space="preserve">2.50955104827881</t>
   </si>
   <si>
     <t xml:space="preserve">2.58797478675842</t>
@@ -656,61 +656,61 @@
     <t xml:space="preserve">2.61150169372559</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56915330886841</t>
+    <t xml:space="preserve">2.56915307044983</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63502907752991</t>
+    <t xml:space="preserve">2.63502860069275</t>
   </si>
   <si>
     <t xml:space="preserve">2.62561798095703</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62718653678894</t>
+    <t xml:space="preserve">2.62718629837036</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83422470092773</t>
+    <t xml:space="preserve">2.83422446250916</t>
   </si>
   <si>
     <t xml:space="preserve">2.79030728340149</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77619123458862</t>
+    <t xml:space="preserve">2.77619099617004</t>
   </si>
   <si>
     <t xml:space="preserve">2.78089642524719</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69149351119995</t>
+    <t xml:space="preserve">2.69149374961853</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78246545791626</t>
+    <t xml:space="preserve">2.78246521949768</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81226587295532</t>
+    <t xml:space="preserve">2.8122661113739</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82324504852295</t>
+    <t xml:space="preserve">2.82324528694153</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68678855895996</t>
+    <t xml:space="preserve">2.68678832054138</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70090460777283</t>
+    <t xml:space="preserve">2.70090436935425</t>
   </si>
   <si>
     <t xml:space="preserve">2.80657124519348</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86433959007263</t>
+    <t xml:space="preserve">2.86433935165405</t>
   </si>
   <si>
     <t xml:space="preserve">2.81940865516663</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80817627906799</t>
+    <t xml:space="preserve">2.80817604064941</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88038635253906</t>
+    <t xml:space="preserve">2.88038611412048</t>
   </si>
   <si>
     <t xml:space="preserve">2.8338508605957</t>
@@ -722,19 +722,19 @@
     <t xml:space="preserve">2.72794246673584</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70547699928284</t>
+    <t xml:space="preserve">2.70547676086426</t>
   </si>
   <si>
     <t xml:space="preserve">2.7327561378479</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67177891731262</t>
+    <t xml:space="preserve">2.67177867889404</t>
   </si>
   <si>
     <t xml:space="preserve">2.62363862991333</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61722016334534</t>
+    <t xml:space="preserve">2.61722040176392</t>
   </si>
   <si>
     <t xml:space="preserve">2.60438275337219</t>
@@ -746,61 +746,61 @@
     <t xml:space="preserve">2.64128994941711</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69584894180298</t>
+    <t xml:space="preserve">2.6958487033844</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75040793418884</t>
+    <t xml:space="preserve">2.75040769577026</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74719858169556</t>
+    <t xml:space="preserve">2.74719834327698</t>
   </si>
   <si>
     <t xml:space="preserve">2.71991920471191</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72633790969849</t>
+    <t xml:space="preserve">2.72633767127991</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74238443374634</t>
+    <t xml:space="preserve">2.74238467216492</t>
   </si>
   <si>
     <t xml:space="preserve">2.80015277862549</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78571033477783</t>
+    <t xml:space="preserve">2.78571057319641</t>
   </si>
   <si>
     <t xml:space="preserve">2.82422256469727</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78731513023376</t>
+    <t xml:space="preserve">2.78731536865234</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79373383522034</t>
+    <t xml:space="preserve">2.79373407363892</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80496692657471</t>
+    <t xml:space="preserve">2.80496668815613</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78410577774048</t>
+    <t xml:space="preserve">2.78410601615906</t>
   </si>
   <si>
     <t xml:space="preserve">2.77608275413513</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79533886909485</t>
+    <t xml:space="preserve">2.79533863067627</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82261776924133</t>
+    <t xml:space="preserve">2.82261800765991</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76003575325012</t>
+    <t xml:space="preserve">2.7600359916687</t>
   </si>
   <si>
     <t xml:space="preserve">2.77929186820984</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79854798316956</t>
+    <t xml:space="preserve">2.79854774475098</t>
   </si>
   <si>
     <t xml:space="preserve">2.77447772026062</t>
@@ -809,31 +809,31 @@
     <t xml:space="preserve">2.8033618927002</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83545517921448</t>
+    <t xml:space="preserve">2.83545541763306</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84026956558228</t>
+    <t xml:space="preserve">2.8402693271637</t>
   </si>
   <si>
     <t xml:space="preserve">2.83224606513977</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81138563156128</t>
+    <t xml:space="preserve">2.8113853931427</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81619930267334</t>
+    <t xml:space="preserve">2.81619906425476</t>
   </si>
   <si>
     <t xml:space="preserve">2.76324510574341</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71189594268799</t>
+    <t xml:space="preserve">2.71189570426941</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72473287582397</t>
+    <t xml:space="preserve">2.72473311424255</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79694318771362</t>
+    <t xml:space="preserve">2.79694366455078</t>
   </si>
   <si>
     <t xml:space="preserve">2.79052448272705</t>
@@ -842,55 +842,55 @@
     <t xml:space="preserve">2.76805925369263</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73115181922913</t>
+    <t xml:space="preserve">2.73115158081055</t>
   </si>
   <si>
     <t xml:space="preserve">2.70387244224548</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81459498405457</t>
+    <t xml:space="preserve">2.81459450721741</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82903647422791</t>
+    <t xml:space="preserve">2.82903695106506</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84347867965698</t>
+    <t xml:space="preserve">2.84347891807556</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77768731117249</t>
+    <t xml:space="preserve">2.77768707275391</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77126836776733</t>
+    <t xml:space="preserve">2.77126860618591</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88840937614441</t>
+    <t xml:space="preserve">2.88840961456299</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87236309051514</t>
+    <t xml:space="preserve">2.87236285209656</t>
   </si>
   <si>
     <t xml:space="preserve">2.89161920547485</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92852640151978</t>
+    <t xml:space="preserve">2.92852663993835</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85952544212341</t>
+    <t xml:space="preserve">2.85952568054199</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90927028656006</t>
+    <t xml:space="preserve">2.90927052497864</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99913191795349</t>
+    <t xml:space="preserve">2.99913239479065</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96864318847656</t>
+    <t xml:space="preserve">2.96864342689514</t>
   </si>
   <si>
-    <t xml:space="preserve">2.830641746521</t>
+    <t xml:space="preserve">2.83064150810242</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87878179550171</t>
+    <t xml:space="preserve">2.87878155708313</t>
   </si>
   <si>
     <t xml:space="preserve">2.87717700004578</t>
@@ -911,10 +911,10 @@
     <t xml:space="preserve">2.67980217933655</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73596596717834</t>
+    <t xml:space="preserve">2.73596572875977</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8258273601532</t>
+    <t xml:space="preserve">2.82582759857178</t>
   </si>
   <si>
     <t xml:space="preserve">2.84829258918762</t>
@@ -932,34 +932,34 @@
     <t xml:space="preserve">2.76484990119934</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74077987670898</t>
+    <t xml:space="preserve">2.74077963829041</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7921290397644</t>
+    <t xml:space="preserve">2.79212951660156</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66375517845154</t>
+    <t xml:space="preserve">2.66375541687012</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60759234428406</t>
+    <t xml:space="preserve">2.60759210586548</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55142855644226</t>
+    <t xml:space="preserve">2.55142879486084</t>
   </si>
   <si>
     <t xml:space="preserve">2.56747508049011</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59956836700439</t>
+    <t xml:space="preserve">2.59956860542297</t>
   </si>
   <si>
     <t xml:space="preserve">2.55945181846619</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50328826904297</t>
+    <t xml:space="preserve">2.50328850746155</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45514845848083</t>
+    <t xml:space="preserve">2.45514822006226</t>
   </si>
   <si>
     <t xml:space="preserve">2.47921824455261</t>
@@ -977,31 +977,31 @@
     <t xml:space="preserve">2.48724174499512</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49526476860046</t>
+    <t xml:space="preserve">2.49526500701904</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52735829353333</t>
+    <t xml:space="preserve">2.52735877037048</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58352208137512</t>
+    <t xml:space="preserve">2.58352184295654</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65573215484619</t>
+    <t xml:space="preserve">2.65573191642761</t>
   </si>
   <si>
     <t xml:space="preserve">2.91247987747192</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82002472877502</t>
+    <t xml:space="preserve">2.8200249671936</t>
   </si>
   <si>
     <t xml:space="preserve">2.80358147621155</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86935496330261</t>
+    <t xml:space="preserve">2.86935472488403</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84468984603882</t>
+    <t xml:space="preserve">2.8446900844574</t>
   </si>
   <si>
     <t xml:space="preserve">2.85291147232056</t>
@@ -1019,10 +1019,10 @@
     <t xml:space="preserve">2.69670009613037</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64737033843994</t>
+    <t xml:space="preserve">2.64737057685852</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65559196472168</t>
+    <t xml:space="preserve">2.6555917263031</t>
   </si>
   <si>
     <t xml:space="preserve">2.66381359100342</t>
@@ -1034,7 +1034,7 @@
     <t xml:space="preserve">2.6391487121582</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55693173408508</t>
+    <t xml:space="preserve">2.55693197250366</t>
   </si>
   <si>
     <t xml:space="preserve">2.59804058074951</t>
@@ -1043,16 +1043,16 @@
     <t xml:space="preserve">2.5487105846405</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46649384498596</t>
+    <t xml:space="preserve">2.46649408340454</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60626220703125</t>
+    <t xml:space="preserve">2.60626244544983</t>
   </si>
   <si>
     <t xml:space="preserve">2.52404546737671</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58159732818604</t>
+    <t xml:space="preserve">2.58159708976746</t>
   </si>
   <si>
     <t xml:space="preserve">2.61448383331299</t>
@@ -1061,16 +1061,16 @@
     <t xml:space="preserve">2.58981871604919</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62270545959473</t>
+    <t xml:space="preserve">2.62270522117615</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51582407951355</t>
+    <t xml:space="preserve">2.51582384109497</t>
   </si>
   <si>
     <t xml:space="preserve">2.57337546348572</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56515383720398</t>
+    <t xml:space="preserve">2.5651535987854</t>
   </si>
   <si>
     <t xml:space="preserve">2.53226733207703</t>
@@ -1079,7 +1079,7 @@
     <t xml:space="preserve">2.47471594810486</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4829375743866</t>
+    <t xml:space="preserve">2.48293733596802</t>
   </si>
   <si>
     <t xml:space="preserve">2.45005083084106</t>
@@ -1091,7 +1091,7 @@
     <t xml:space="preserve">2.42538571357727</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43360757827759</t>
+    <t xml:space="preserve">2.43360781669617</t>
   </si>
   <si>
     <t xml:space="preserve">2.49115896224976</t>
@@ -1100,25 +1100,25 @@
     <t xml:space="preserve">2.50760245323181</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54048871994019</t>
+    <t xml:space="preserve">2.54048895835876</t>
   </si>
   <si>
     <t xml:space="preserve">2.67203545570374</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68847846984863</t>
+    <t xml:space="preserve">2.68847823143005</t>
   </si>
   <si>
     <t xml:space="preserve">2.70492196083069</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71314334869385</t>
+    <t xml:space="preserve">2.71314358711243</t>
   </si>
   <si>
     <t xml:space="preserve">2.75425171852112</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78713822364807</t>
+    <t xml:space="preserve">2.78713846206665</t>
   </si>
   <si>
     <t xml:space="preserve">2.77069497108459</t>
@@ -1133,7 +1133,7 @@
     <t xml:space="preserve">2.77891707420349</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79536008834839</t>
+    <t xml:space="preserve">2.79535984992981</t>
   </si>
   <si>
     <t xml:space="preserve">2.87757658958435</t>
@@ -1145,7 +1145,7 @@
     <t xml:space="preserve">2.89401960372925</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86113309860229</t>
+    <t xml:space="preserve">2.86113286018372</t>
   </si>
   <si>
     <t xml:space="preserve">2.90224123001099</t>
@@ -1154,7 +1154,7 @@
     <t xml:space="preserve">2.88579821586609</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8364679813385</t>
+    <t xml:space="preserve">2.83646821975708</t>
   </si>
   <si>
     <t xml:space="preserve">2.94334959983826</t>
@@ -1163,7 +1163,7 @@
     <t xml:space="preserve">2.82824635505676</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9269061088562</t>
+    <t xml:space="preserve">2.92690634727478</t>
   </si>
   <si>
     <t xml:space="preserve">2.77809429168701</t>
@@ -67126,7 +67126,7 @@
     </row>
     <row r="2495">
       <c r="A2495" s="1" t="n">
-        <v>45952.6494328704</v>
+        <v>45952.2916666667</v>
       </c>
       <c r="B2495" t="n">
         <v>6467</v>
@@ -67138,7 +67138,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="E2495" t="n">
-        <v>4.73999977111816</v>
+        <v>4.78000020980835</v>
       </c>
       <c r="F2495" t="n">
         <v>4.69999980926514</v>
@@ -67147,6 +67147,32 @@
         <v>639</v>
       </c>
       <c r="H2495" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2496">
+      <c r="A2496" s="1" t="n">
+        <v>45953.422650463</v>
+      </c>
+      <c r="B2496" t="n">
+        <v>2450</v>
+      </c>
+      <c r="C2496" t="n">
+        <v>4.69999980926514</v>
+      </c>
+      <c r="D2496" t="n">
+        <v>4.67999982833862</v>
+      </c>
+      <c r="E2496" t="n">
+        <v>4.67999982833862</v>
+      </c>
+      <c r="F2496" t="n">
+        <v>4.69999980926514</v>
+      </c>
+      <c r="G2496" t="s">
+        <v>639</v>
+      </c>
+      <c r="H2496" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ENV.MI.xlsx
+++ b/data/ENV.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="644" uniqueCount="644">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="643" uniqueCount="643">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -50,7 +50,7 @@
     <t xml:space="preserve">2.1447126865387</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16175889968872</t>
+    <t xml:space="preserve">2.16175866127014</t>
   </si>
   <si>
     <t xml:space="preserve">2.03778696060181</t>
@@ -59,25 +59,25 @@
     <t xml:space="preserve">2.08272647857666</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05328345298767</t>
+    <t xml:space="preserve">2.05328369140625</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03623723983765</t>
+    <t xml:space="preserve">2.03623747825623</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96805262565613</t>
+    <t xml:space="preserve">1.96805286407471</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96030426025391</t>
+    <t xml:space="preserve">1.96030473709106</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89831864833832</t>
+    <t xml:space="preserve">1.89831900596619</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88127267360687</t>
+    <t xml:space="preserve">1.88127243518829</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96340370178223</t>
+    <t xml:space="preserve">1.96340358257294</t>
   </si>
   <si>
     <t xml:space="preserve">1.98354935646057</t>
@@ -86,55 +86,55 @@
     <t xml:space="preserve">2.01299262046814</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93550992012024</t>
+    <t xml:space="preserve">1.93551027774811</t>
   </si>
   <si>
     <t xml:space="preserve">1.93705976009369</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91381549835205</t>
+    <t xml:space="preserve">1.91381525993347</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91071605682373</t>
+    <t xml:space="preserve">1.91071593761444</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86577618122101</t>
+    <t xml:space="preserve">1.86577582359314</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89211988449097</t>
+    <t xml:space="preserve">1.89211976528168</t>
   </si>
   <si>
     <t xml:space="preserve">1.85182917118073</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93396067619324</t>
+    <t xml:space="preserve">1.93396043777466</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86732578277588</t>
+    <t xml:space="preserve">1.86732590198517</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88902056217194</t>
+    <t xml:space="preserve">1.8890209197998</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98664855957031</t>
+    <t xml:space="preserve">1.98664832115173</t>
   </si>
   <si>
     <t xml:space="preserve">2.11526966094971</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18500351905823</t>
+    <t xml:space="preserve">2.18500328063965</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20824813842773</t>
+    <t xml:space="preserve">2.20824861526489</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16950726509094</t>
+    <t xml:space="preserve">2.16950702667236</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08427619934082</t>
+    <t xml:space="preserve">2.08427667617798</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01454186439514</t>
+    <t xml:space="preserve">2.0145423412323</t>
   </si>
   <si>
     <t xml:space="preserve">2.0052444934845</t>
@@ -152,7 +152,7 @@
     <t xml:space="preserve">2.20050001144409</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27178359031677</t>
+    <t xml:space="preserve">2.27178382873535</t>
   </si>
   <si>
     <t xml:space="preserve">2.24698925018311</t>
@@ -161,16 +161,16 @@
     <t xml:space="preserve">2.32137250900269</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2841808795929</t>
+    <t xml:space="preserve">2.28418111801147</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37870955467224</t>
+    <t xml:space="preserve">2.37870931625366</t>
   </si>
   <si>
     <t xml:space="preserve">2.35546469688416</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4406955242157</t>
+    <t xml:space="preserve">2.44069528579712</t>
   </si>
   <si>
     <t xml:space="preserve">2.43139743804932</t>
@@ -179,7 +179,7 @@
     <t xml:space="preserve">2.44999313354492</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3849081993103</t>
+    <t xml:space="preserve">2.38490772247314</t>
   </si>
   <si>
     <t xml:space="preserve">2.3616635799408</t>
@@ -188,31 +188,31 @@
     <t xml:space="preserve">2.36321306228638</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31982278823853</t>
+    <t xml:space="preserve">2.3198230266571</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35236573219299</t>
+    <t xml:space="preserve">2.35236525535583</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26868438720703</t>
+    <t xml:space="preserve">2.26868414878845</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32292222976685</t>
+    <t xml:space="preserve">2.32292199134827</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33531928062439</t>
+    <t xml:space="preserve">2.33531951904297</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33996844291687</t>
+    <t xml:space="preserve">2.33996820449829</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3105251789093</t>
+    <t xml:space="preserve">2.31052494049072</t>
   </si>
   <si>
     <t xml:space="preserve">2.28573083877563</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25473737716675</t>
+    <t xml:space="preserve">2.25473785400391</t>
   </si>
   <si>
     <t xml:space="preserve">2.29037976264954</t>
@@ -227,40 +227,40 @@
     <t xml:space="preserve">2.07497835159302</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00834369659424</t>
+    <t xml:space="preserve">2.00834345817566</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03468728065491</t>
+    <t xml:space="preserve">2.03468751907349</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02229022979736</t>
+    <t xml:space="preserve">2.02229046821594</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97580099105835</t>
+    <t xml:space="preserve">1.97580087184906</t>
   </si>
   <si>
     <t xml:space="preserve">1.91980648040771</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88216352462769</t>
+    <t xml:space="preserve">1.8821634054184</t>
   </si>
   <si>
     <t xml:space="preserve">2.00136733055115</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96058678627014</t>
+    <t xml:space="preserve">1.96058690547943</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90255355834961</t>
+    <t xml:space="preserve">1.90255379676819</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9213752746582</t>
+    <t xml:space="preserve">1.92137551307678</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91353321075439</t>
+    <t xml:space="preserve">1.91353297233582</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89784824848175</t>
+    <t xml:space="preserve">1.89784812927246</t>
   </si>
   <si>
     <t xml:space="preserve">1.89000606536865</t>
@@ -269,10 +269,10 @@
     <t xml:space="preserve">1.85079395771027</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88059508800507</t>
+    <t xml:space="preserve">1.88059520721436</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8664790391922</t>
+    <t xml:space="preserve">1.86647868156433</t>
   </si>
   <si>
     <t xml:space="preserve">1.54651093482971</t>
@@ -281,43 +281,43 @@
     <t xml:space="preserve">1.6861047744751</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70178949832916</t>
+    <t xml:space="preserve">1.70178973674774</t>
   </si>
   <si>
     <t xml:space="preserve">1.70022106170654</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66257774829865</t>
+    <t xml:space="preserve">1.66257762908936</t>
   </si>
   <si>
     <t xml:space="preserve">1.64532458782196</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62336623668671</t>
+    <t xml:space="preserve">1.62336587905884</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61552357673645</t>
+    <t xml:space="preserve">1.61552369594574</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63120830059052</t>
+    <t xml:space="preserve">1.63120818138123</t>
   </si>
   <si>
     <t xml:space="preserve">1.58415424823761</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64689290523529</t>
+    <t xml:space="preserve">1.64689302444458</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64061915874481</t>
+    <t xml:space="preserve">1.6406192779541</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6390506029129</t>
+    <t xml:space="preserve">1.63905072212219</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60768151283264</t>
+    <t xml:space="preserve">1.60768115520477</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57631182670593</t>
+    <t xml:space="preserve">1.57631194591522</t>
   </si>
   <si>
     <t xml:space="preserve">1.59199655056</t>
@@ -326,73 +326,73 @@
     <t xml:space="preserve">1.75668597221375</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84295189380646</t>
+    <t xml:space="preserve">1.84295165538788</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8460887670517</t>
+    <t xml:space="preserve">1.84608888626099</t>
   </si>
   <si>
     <t xml:space="preserve">1.92921757698059</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88530039787292</t>
+    <t xml:space="preserve">1.88530027866364</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9009850025177</t>
+    <t xml:space="preserve">1.90098524093628</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91823828220367</t>
+    <t xml:space="preserve">1.91823816299438</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94960761070251</t>
+    <t xml:space="preserve">1.94960749149323</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9307861328125</t>
+    <t xml:space="preserve">1.93078577518463</t>
   </si>
   <si>
     <t xml:space="preserve">1.84922575950623</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82413017749786</t>
+    <t xml:space="preserve">1.82413029670715</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85549962520599</t>
+    <t xml:space="preserve">1.85549914836884</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89627969264984</t>
+    <t xml:space="preserve">1.89627981185913</t>
   </si>
   <si>
     <t xml:space="preserve">1.93705999851227</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8743212223053</t>
+    <t xml:space="preserve">1.87432110309601</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94333386421204</t>
+    <t xml:space="preserve">1.94333374500275</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94490253925323</t>
+    <t xml:space="preserve">1.94490242004395</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96686065196991</t>
+    <t xml:space="preserve">1.9668607711792</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98411393165588</t>
+    <t xml:space="preserve">1.98411417007446</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0625376701355</t>
+    <t xml:space="preserve">2.06253743171692</t>
   </si>
   <si>
     <t xml:space="preserve">2.0531268119812</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05155825614929</t>
+    <t xml:space="preserve">2.05155801773071</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02332544326782</t>
+    <t xml:space="preserve">2.02332592010498</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02959990501404</t>
+    <t xml:space="preserve">2.02959966659546</t>
   </si>
   <si>
     <t xml:space="preserve">2.03116798400879</t>
@@ -407,7 +407,7 @@
     <t xml:space="preserve">2.08606457710266</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1550772190094</t>
+    <t xml:space="preserve">2.15507745742798</t>
   </si>
   <si>
     <t xml:space="preserve">2.18801498413086</t>
@@ -416,19 +416,19 @@
     <t xml:space="preserve">2.19585728645325</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20213150978088</t>
+    <t xml:space="preserve">2.20213103294373</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23350071907043</t>
+    <t xml:space="preserve">2.23350048065186</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20997333526611</t>
+    <t xml:space="preserve">2.20997381210327</t>
   </si>
   <si>
     <t xml:space="preserve">2.18017268180847</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16605639457703</t>
+    <t xml:space="preserve">2.16605687141418</t>
   </si>
   <si>
     <t xml:space="preserve">2.19428873062134</t>
@@ -437,13 +437,13 @@
     <t xml:space="preserve">2.17389893531799</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20056247711182</t>
+    <t xml:space="preserve">2.2005627155304</t>
   </si>
   <si>
     <t xml:space="preserve">2.21938443183899</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21781587600708</t>
+    <t xml:space="preserve">2.21781611442566</t>
   </si>
   <si>
     <t xml:space="preserve">2.1911518573761</t>
@@ -458,16 +458,16 @@
     <t xml:space="preserve">2.11743402481079</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16291975975037</t>
+    <t xml:space="preserve">2.16291952133179</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10802340507507</t>
+    <t xml:space="preserve">2.10802268981934</t>
   </si>
   <si>
     <t xml:space="preserve">2.01548337936401</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04528427124023</t>
+    <t xml:space="preserve">2.04528403282166</t>
   </si>
   <si>
     <t xml:space="preserve">1.98568260669708</t>
@@ -479,7 +479,7 @@
     <t xml:space="preserve">2.06724286079407</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12998175621033</t>
+    <t xml:space="preserve">2.12998151779175</t>
   </si>
   <si>
     <t xml:space="preserve">2.11586546897888</t>
@@ -488,16 +488,16 @@
     <t xml:space="preserve">2.05469489097595</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11429715156555</t>
+    <t xml:space="preserve">2.11429691314697</t>
   </si>
   <si>
     <t xml:space="preserve">2.05626368522644</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06410551071167</t>
+    <t xml:space="preserve">2.06410574913025</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1048858165741</t>
+    <t xml:space="preserve">2.10488629341125</t>
   </si>
   <si>
     <t xml:space="preserve">2.00920963287354</t>
@@ -509,25 +509,25 @@
     <t xml:space="preserve">2.04842138290405</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1644880771637</t>
+    <t xml:space="preserve">2.16448783874512</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18487787246704</t>
+    <t xml:space="preserve">2.18487811088562</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26643848419189</t>
+    <t xml:space="preserve">2.26643872261047</t>
   </si>
   <si>
     <t xml:space="preserve">2.27271246910095</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25702738761902</t>
+    <t xml:space="preserve">2.2570276260376</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30721855163574</t>
+    <t xml:space="preserve">2.30721879005432</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23036360740662</t>
+    <t xml:space="preserve">2.23036408424377</t>
   </si>
   <si>
     <t xml:space="preserve">2.37152600288391</t>
@@ -536,10 +536,10 @@
     <t xml:space="preserve">2.35270428657532</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39191627502441</t>
+    <t xml:space="preserve">2.39191603660583</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33545088768005</t>
+    <t xml:space="preserve">2.33545112609863</t>
   </si>
   <si>
     <t xml:space="preserve">2.31349277496338</t>
@@ -548,7 +548,7 @@
     <t xml:space="preserve">2.37623119354248</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32917737960815</t>
+    <t xml:space="preserve">2.32917761802673</t>
   </si>
   <si>
     <t xml:space="preserve">2.24918532371521</t>
@@ -560,40 +560,40 @@
     <t xml:space="preserve">2.33701968193054</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34486198425293</t>
+    <t xml:space="preserve">2.34486222267151</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34956765174866</t>
+    <t xml:space="preserve">2.34956741333008</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32604026794434</t>
+    <t xml:space="preserve">2.32604050636292</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30251336097717</t>
+    <t xml:space="preserve">2.30251359939575</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31192398071289</t>
+    <t xml:space="preserve">2.31192421913147</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25075340270996</t>
+    <t xml:space="preserve">2.25075387954712</t>
   </si>
   <si>
     <t xml:space="preserve">2.27428078651428</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43897008895874</t>
+    <t xml:space="preserve">2.43897032737732</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48445558547974</t>
+    <t xml:space="preserve">2.48445582389832</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46249771118164</t>
+    <t xml:space="preserve">2.4624969959259</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50798273086548</t>
+    <t xml:space="preserve">2.50798296928406</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48602437973022</t>
+    <t xml:space="preserve">2.48602414131165</t>
   </si>
   <si>
     <t xml:space="preserve">2.60993313789368</t>
@@ -602,16 +602,16 @@
     <t xml:space="preserve">2.66639828681946</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66326141357422</t>
+    <t xml:space="preserve">2.66326117515564</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6601243019104</t>
+    <t xml:space="preserve">2.66012406349182</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64287137985229</t>
+    <t xml:space="preserve">2.64287090301514</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65855598449707</t>
+    <t xml:space="preserve">2.65855574607849</t>
   </si>
   <si>
     <t xml:space="preserve">2.60209131240845</t>
@@ -620,34 +620,34 @@
     <t xml:space="preserve">2.55033159255981</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63816571235657</t>
+    <t xml:space="preserve">2.63816618919373</t>
   </si>
   <si>
     <t xml:space="preserve">2.58013224601746</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59581685066223</t>
+    <t xml:space="preserve">2.59581708908081</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58170080184937</t>
+    <t xml:space="preserve">2.58170104026794</t>
   </si>
   <si>
     <t xml:space="preserve">2.6036593914032</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61934399604797</t>
+    <t xml:space="preserve">2.61934423446655</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57542705535889</t>
+    <t xml:space="preserve">2.57542681694031</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57385849952698</t>
+    <t xml:space="preserve">2.57385873794556</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50955104827881</t>
+    <t xml:space="preserve">2.50955152511597</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58797478675842</t>
+    <t xml:space="preserve">2.58797454833984</t>
   </si>
   <si>
     <t xml:space="preserve">2.56444764137268</t>
@@ -656,13 +656,13 @@
     <t xml:space="preserve">2.61150169372559</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56915307044983</t>
+    <t xml:space="preserve">2.56915330886841</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63502860069275</t>
+    <t xml:space="preserve">2.63502883911133</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62561798095703</t>
+    <t xml:space="preserve">2.62561821937561</t>
   </si>
   <si>
     <t xml:space="preserve">2.62718629837036</t>
@@ -671,49 +671,49 @@
     <t xml:space="preserve">2.83422446250916</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79030728340149</t>
+    <t xml:space="preserve">2.79030752182007</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77619099617004</t>
+    <t xml:space="preserve">2.77619123458862</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78089642524719</t>
+    <t xml:space="preserve">2.78089666366577</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69149374961853</t>
+    <t xml:space="preserve">2.69149351119995</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78246521949768</t>
+    <t xml:space="preserve">2.78246545791626</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8122661113739</t>
+    <t xml:space="preserve">2.81226587295532</t>
   </si>
   <si>
     <t xml:space="preserve">2.82324528694153</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68678832054138</t>
+    <t xml:space="preserve">2.68678855895996</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70090436935425</t>
+    <t xml:space="preserve">2.70090484619141</t>
   </si>
   <si>
     <t xml:space="preserve">2.80657124519348</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86433935165405</t>
+    <t xml:space="preserve">2.86433959007263</t>
   </si>
   <si>
     <t xml:space="preserve">2.81940865516663</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80817604064941</t>
+    <t xml:space="preserve">2.80817627906799</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88038611412048</t>
+    <t xml:space="preserve">2.88038635253906</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8338508605957</t>
+    <t xml:space="preserve">2.83385062217712</t>
   </si>
   <si>
     <t xml:space="preserve">2.74398922920227</t>
@@ -722,49 +722,49 @@
     <t xml:space="preserve">2.72794246673584</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70547676086426</t>
+    <t xml:space="preserve">2.70547699928284</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7327561378479</t>
+    <t xml:space="preserve">2.73275637626648</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67177867889404</t>
+    <t xml:space="preserve">2.67177891731262</t>
   </si>
   <si>
     <t xml:space="preserve">2.62363862991333</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61722040176392</t>
+    <t xml:space="preserve">2.61722016334534</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60438275337219</t>
+    <t xml:space="preserve">2.60438251495361</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62524342536926</t>
+    <t xml:space="preserve">2.62524366378784</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64128994941711</t>
+    <t xml:space="preserve">2.64129018783569</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6958487033844</t>
+    <t xml:space="preserve">2.69584894180298</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75040769577026</t>
+    <t xml:space="preserve">2.75040793418884</t>
   </si>
   <si>
     <t xml:space="preserve">2.74719834327698</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71991920471191</t>
+    <t xml:space="preserve">2.71991896629333</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72633767127991</t>
+    <t xml:space="preserve">2.72633790969849</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74238467216492</t>
+    <t xml:space="preserve">2.74238443374634</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80015277862549</t>
+    <t xml:space="preserve">2.80015254020691</t>
   </si>
   <si>
     <t xml:space="preserve">2.78571057319641</t>
@@ -773,7 +773,7 @@
     <t xml:space="preserve">2.82422256469727</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78731536865234</t>
+    <t xml:space="preserve">2.78731513023376</t>
   </si>
   <si>
     <t xml:space="preserve">2.79373407363892</t>
@@ -788,31 +788,31 @@
     <t xml:space="preserve">2.77608275413513</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79533863067627</t>
+    <t xml:space="preserve">2.79533886909485</t>
   </si>
   <si>
     <t xml:space="preserve">2.82261800765991</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7600359916687</t>
+    <t xml:space="preserve">2.76003575325012</t>
   </si>
   <si>
     <t xml:space="preserve">2.77929186820984</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79854774475098</t>
+    <t xml:space="preserve">2.79854798316956</t>
   </si>
   <si>
     <t xml:space="preserve">2.77447772026062</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8033618927002</t>
+    <t xml:space="preserve">2.80336213111877</t>
   </si>
   <si>
     <t xml:space="preserve">2.83545541763306</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8402693271637</t>
+    <t xml:space="preserve">2.84026956558228</t>
   </si>
   <si>
     <t xml:space="preserve">2.83224606513977</t>
@@ -821,19 +821,19 @@
     <t xml:space="preserve">2.8113853931427</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81619906425476</t>
+    <t xml:space="preserve">2.81619930267334</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76324510574341</t>
+    <t xml:space="preserve">2.76324558258057</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71189570426941</t>
+    <t xml:space="preserve">2.71189594268799</t>
   </si>
   <si>
     <t xml:space="preserve">2.72473311424255</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79694366455078</t>
+    <t xml:space="preserve">2.7969434261322</t>
   </si>
   <si>
     <t xml:space="preserve">2.79052448272705</t>
@@ -842,19 +842,19 @@
     <t xml:space="preserve">2.76805925369263</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73115158081055</t>
+    <t xml:space="preserve">2.73115181922913</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70387244224548</t>
+    <t xml:space="preserve">2.7038722038269</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81459450721741</t>
+    <t xml:space="preserve">2.81459498405457</t>
   </si>
   <si>
     <t xml:space="preserve">2.82903695106506</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84347891807556</t>
+    <t xml:space="preserve">2.8434784412384</t>
   </si>
   <si>
     <t xml:space="preserve">2.77768707275391</t>
@@ -863,10 +863,10 @@
     <t xml:space="preserve">2.77126860618591</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88840961456299</t>
+    <t xml:space="preserve">2.88840937614441</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87236285209656</t>
+    <t xml:space="preserve">2.87236309051514</t>
   </si>
   <si>
     <t xml:space="preserve">2.89161920547485</t>
@@ -878,64 +878,64 @@
     <t xml:space="preserve">2.85952568054199</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90927052497864</t>
+    <t xml:space="preserve">2.90927028656006</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99913239479065</t>
+    <t xml:space="preserve">2.99913167953491</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96864342689514</t>
+    <t xml:space="preserve">2.96864318847656</t>
   </si>
   <si>
     <t xml:space="preserve">2.83064150810242</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87878155708313</t>
+    <t xml:space="preserve">2.87878179550171</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87717700004578</t>
+    <t xml:space="preserve">2.8771767616272</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87557244300842</t>
+    <t xml:space="preserve">2.87557220458984</t>
   </si>
   <si>
     <t xml:space="preserve">2.7520124912262</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76164031028748</t>
+    <t xml:space="preserve">2.76164054870605</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7889199256897</t>
+    <t xml:space="preserve">2.78892016410828</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67980217933655</t>
+    <t xml:space="preserve">2.67980241775513</t>
   </si>
   <si>
     <t xml:space="preserve">2.73596572875977</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82582759857178</t>
+    <t xml:space="preserve">2.8258273601532</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84829258918762</t>
+    <t xml:space="preserve">2.8482928276062</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82101345062256</t>
+    <t xml:space="preserve">2.82101321220398</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73436117172241</t>
+    <t xml:space="preserve">2.73436093330383</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81780433654785</t>
+    <t xml:space="preserve">2.81780409812927</t>
   </si>
   <si>
     <t xml:space="preserve">2.76484990119934</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74077963829041</t>
+    <t xml:space="preserve">2.74077987670898</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79212951660156</t>
+    <t xml:space="preserve">2.79212927818298</t>
   </si>
   <si>
     <t xml:space="preserve">2.66375541687012</t>
@@ -944,19 +944,19 @@
     <t xml:space="preserve">2.60759210586548</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55142879486084</t>
+    <t xml:space="preserve">2.55142855644226</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56747508049011</t>
+    <t xml:space="preserve">2.56747531890869</t>
   </si>
   <si>
     <t xml:space="preserve">2.59956860542297</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55945181846619</t>
+    <t xml:space="preserve">2.55945205688477</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50328850746155</t>
+    <t xml:space="preserve">2.50328826904297</t>
   </si>
   <si>
     <t xml:space="preserve">2.45514822006226</t>
@@ -965,7 +965,7 @@
     <t xml:space="preserve">2.47921824455261</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47119498252869</t>
+    <t xml:space="preserve">2.47119474411011</t>
   </si>
   <si>
     <t xml:space="preserve">2.43107795715332</t>
@@ -974,19 +974,19 @@
     <t xml:space="preserve">2.46317148208618</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48724174499512</t>
+    <t xml:space="preserve">2.48724150657654</t>
   </si>
   <si>
     <t xml:space="preserve">2.49526500701904</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52735877037048</t>
+    <t xml:space="preserve">2.5273585319519</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58352184295654</t>
+    <t xml:space="preserve">2.5835223197937</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65573191642761</t>
+    <t xml:space="preserve">2.65573215484619</t>
   </si>
   <si>
     <t xml:space="preserve">2.91247987747192</t>
@@ -1007,34 +1007,34 @@
     <t xml:space="preserve">2.85291147232056</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81180334091187</t>
+    <t xml:space="preserve">2.81180357933044</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72136497497559</t>
+    <t xml:space="preserve">2.72136521339417</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68025708198547</t>
+    <t xml:space="preserve">2.68025684356689</t>
   </si>
   <si>
     <t xml:space="preserve">2.69670009613037</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64737057685852</t>
+    <t xml:space="preserve">2.64737033843994</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6555917263031</t>
+    <t xml:space="preserve">2.65559196472168</t>
   </si>
   <si>
     <t xml:space="preserve">2.66381359100342</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63092684745789</t>
+    <t xml:space="preserve">2.63092708587646</t>
   </si>
   <si>
     <t xml:space="preserve">2.6391487121582</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55693197250366</t>
+    <t xml:space="preserve">2.55693221092224</t>
   </si>
   <si>
     <t xml:space="preserve">2.59804058074951</t>
@@ -1043,43 +1043,43 @@
     <t xml:space="preserve">2.5487105846405</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46649408340454</t>
+    <t xml:space="preserve">2.46649384498596</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60626244544983</t>
+    <t xml:space="preserve">2.60626220703125</t>
   </si>
   <si>
     <t xml:space="preserve">2.52404546737671</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58159708976746</t>
+    <t xml:space="preserve">2.58159732818604</t>
   </si>
   <si>
     <t xml:space="preserve">2.61448383331299</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58981871604919</t>
+    <t xml:space="preserve">2.58981895446777</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62270522117615</t>
+    <t xml:space="preserve">2.62270545959473</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51582384109497</t>
+    <t xml:space="preserve">2.51582407951355</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57337546348572</t>
+    <t xml:space="preserve">2.57337522506714</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5651535987854</t>
+    <t xml:space="preserve">2.56515383720398</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53226733207703</t>
+    <t xml:space="preserve">2.53226709365845</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47471594810486</t>
+    <t xml:space="preserve">2.47471570968628</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48293733596802</t>
+    <t xml:space="preserve">2.4829375743866</t>
   </si>
   <si>
     <t xml:space="preserve">2.45005083084106</t>
@@ -1088,37 +1088,37 @@
     <t xml:space="preserve">2.44182920455933</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42538571357727</t>
+    <t xml:space="preserve">2.42538595199585</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43360781669617</t>
+    <t xml:space="preserve">2.43360757827759</t>
   </si>
   <si>
     <t xml:space="preserve">2.49115896224976</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50760245323181</t>
+    <t xml:space="preserve">2.50760221481323</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54048895835876</t>
+    <t xml:space="preserve">2.54048871994019</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67203545570374</t>
+    <t xml:space="preserve">2.67203497886658</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68847823143005</t>
+    <t xml:space="preserve">2.68847870826721</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70492196083069</t>
+    <t xml:space="preserve">2.70492172241211</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71314358711243</t>
+    <t xml:space="preserve">2.71314334869385</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75425171852112</t>
+    <t xml:space="preserve">2.75425148010254</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78713846206665</t>
+    <t xml:space="preserve">2.78713822364807</t>
   </si>
   <si>
     <t xml:space="preserve">2.77069497108459</t>
@@ -1127,49 +1127,49 @@
     <t xml:space="preserve">2.72958660125732</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7460298538208</t>
+    <t xml:space="preserve">2.74603009223938</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77891707420349</t>
+    <t xml:space="preserve">2.77891659736633</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79535984992981</t>
+    <t xml:space="preserve">2.79536008834839</t>
   </si>
   <si>
     <t xml:space="preserve">2.87757658958435</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91868448257446</t>
+    <t xml:space="preserve">2.91868472099304</t>
   </si>
   <si>
     <t xml:space="preserve">2.89401960372925</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86113286018372</t>
+    <t xml:space="preserve">2.86113309860229</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90224123001099</t>
+    <t xml:space="preserve">2.90224146842957</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88579821586609</t>
+    <t xml:space="preserve">2.88579797744751</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83646821975708</t>
+    <t xml:space="preserve">2.8364679813385</t>
   </si>
   <si>
     <t xml:space="preserve">2.94334959983826</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82824635505676</t>
+    <t xml:space="preserve">2.82824659347534</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92690634727478</t>
+    <t xml:space="preserve">2.9269061088562</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77809429168701</t>
+    <t xml:space="preserve">2.77809453010559</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8205726146698</t>
+    <t xml:space="preserve">2.82057285308838</t>
   </si>
   <si>
     <t xml:space="preserve">2.8290684223175</t>
@@ -1181,19 +1181,19 @@
     <t xml:space="preserve">2.88004279136658</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92252111434937</t>
+    <t xml:space="preserve">2.92252135276794</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90552997589111</t>
+    <t xml:space="preserve">2.90553021430969</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87154746055603</t>
+    <t xml:space="preserve">2.87154698371887</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85455584526062</t>
+    <t xml:space="preserve">2.85455560684204</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91402554512024</t>
+    <t xml:space="preserve">2.91402578353882</t>
   </si>
   <si>
     <t xml:space="preserve">2.93101692199707</t>
@@ -1205,28 +1205,28 @@
     <t xml:space="preserve">2.89703416824341</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93951272964478</t>
+    <t xml:space="preserve">2.93951296806335</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98199129104614</t>
+    <t xml:space="preserve">2.98199105262756</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79508590698242</t>
+    <t xml:space="preserve">2.79508566856384</t>
   </si>
   <si>
     <t xml:space="preserve">2.78659009933472</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76110315322876</t>
+    <t xml:space="preserve">2.7611026763916</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76959896087646</t>
+    <t xml:space="preserve">2.76959872245789</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81207704544067</t>
+    <t xml:space="preserve">2.81207728385925</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83756399154663</t>
+    <t xml:space="preserve">2.83756422996521</t>
   </si>
   <si>
     <t xml:space="preserve">2.86305141448975</t>
@@ -1235,13 +1235,13 @@
     <t xml:space="preserve">2.62517166137695</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67614603042603</t>
+    <t xml:space="preserve">2.6761462688446</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61667609214783</t>
+    <t xml:space="preserve">2.61667585372925</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55720639228821</t>
+    <t xml:space="preserve">2.55720615386963</t>
   </si>
   <si>
     <t xml:space="preserve">2.54871034622192</t>
@@ -1259,22 +1259,22 @@
     <t xml:space="preserve">2.53171920776367</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46375370025635</t>
+    <t xml:space="preserve">2.46375346183777</t>
   </si>
   <si>
     <t xml:space="preserve">2.58269309997559</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54021453857422</t>
+    <t xml:space="preserve">2.5402147769928</t>
   </si>
   <si>
     <t xml:space="preserve">2.56570196151733</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59118914604187</t>
+    <t xml:space="preserve">2.59118890762329</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47224926948547</t>
+    <t xml:space="preserve">2.47224903106689</t>
   </si>
   <si>
     <t xml:space="preserve">2.63366746902466</t>
@@ -1298,7 +1298,7 @@
     <t xml:space="preserve">2.99048686027527</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96499991416931</t>
+    <t xml:space="preserve">2.96499967575073</t>
   </si>
   <si>
     <t xml:space="preserve">2.97349572181702</t>
@@ -1307,7 +1307,7 @@
     <t xml:space="preserve">2.95650410652161</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84606003761292</t>
+    <t xml:space="preserve">2.84605979919434</t>
   </si>
   <si>
     <t xml:space="preserve">2.75260734558105</t>
@@ -1316,19 +1316,19 @@
     <t xml:space="preserve">2.6676504611969</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65915465354919</t>
+    <t xml:space="preserve">2.65915441513062</t>
   </si>
   <si>
     <t xml:space="preserve">2.31083083152771</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35330939292908</t>
+    <t xml:space="preserve">2.3533091545105</t>
   </si>
   <si>
     <t xml:space="preserve">2.34481358528137</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45525789260864</t>
+    <t xml:space="preserve">2.45525813102722</t>
   </si>
   <si>
     <t xml:space="preserve">2.4892406463623</t>
@@ -1337,16 +1337,16 @@
     <t xml:space="preserve">2.65065884590149</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64216279983521</t>
+    <t xml:space="preserve">2.64216327667236</t>
   </si>
   <si>
     <t xml:space="preserve">2.71012878417969</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69313764572144</t>
+    <t xml:space="preserve">2.69313740730286</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71862435340881</t>
+    <t xml:space="preserve">2.71862459182739</t>
   </si>
   <si>
     <t xml:space="preserve">2.74411153793335</t>
@@ -1358,7 +1358,7 @@
     <t xml:space="preserve">2.60818028450012</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50623178482056</t>
+    <t xml:space="preserve">2.50623202323914</t>
   </si>
   <si>
     <t xml:space="preserve">2.44676208496094</t>
@@ -1367,16 +1367,16 @@
     <t xml:space="preserve">2.37879657745361</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42977070808411</t>
+    <t xml:space="preserve">2.42977046966553</t>
   </si>
   <si>
     <t xml:space="preserve">2.37030076980591</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31932640075684</t>
+    <t xml:space="preserve">2.31932663917542</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27684831619263</t>
+    <t xml:space="preserve">2.27684807777405</t>
   </si>
   <si>
     <t xml:space="preserve">2.26835250854492</t>
@@ -1385,22 +1385,22 @@
     <t xml:space="preserve">2.30233502388</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33631777763367</t>
+    <t xml:space="preserve">2.33631801605225</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39578795433044</t>
+    <t xml:space="preserve">2.39578771591187</t>
   </si>
   <si>
     <t xml:space="preserve">2.72712016105652</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99898242950439</t>
+    <t xml:space="preserve">2.99898266792297</t>
   </si>
   <si>
     <t xml:space="preserve">3.03296542167664</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01597380638123</t>
+    <t xml:space="preserve">3.0159740447998</t>
   </si>
   <si>
     <t xml:space="preserve">3.04146122932434</t>
@@ -1409,7 +1409,7 @@
     <t xml:space="preserve">3.1943838596344</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1264181137085</t>
+    <t xml:space="preserve">3.12641835212708</t>
   </si>
   <si>
     <t xml:space="preserve">3.05845236778259</t>
@@ -1418,7 +1418,7 @@
     <t xml:space="preserve">3.09243535995483</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16040086746216</t>
+    <t xml:space="preserve">3.16040110588074</t>
   </si>
   <si>
     <t xml:space="preserve">3.21137523651123</t>
@@ -1427,7 +1427,7 @@
     <t xml:space="preserve">3.3133237361908</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26234912872314</t>
+    <t xml:space="preserve">3.26234936714172</t>
   </si>
   <si>
     <t xml:space="preserve">3.33031511306763</t>
@@ -1436,31 +1436,31 @@
     <t xml:space="preserve">3.22836661338806</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17739224433899</t>
+    <t xml:space="preserve">3.17739248275757</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14340972900391</t>
+    <t xml:space="preserve">3.14340949058533</t>
   </si>
   <si>
     <t xml:space="preserve">3.10942697525024</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27934074401855</t>
+    <t xml:space="preserve">3.27934050559998</t>
   </si>
   <si>
     <t xml:space="preserve">3.48323750495911</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39828038215637</t>
+    <t xml:space="preserve">3.39828062057495</t>
   </si>
   <si>
     <t xml:space="preserve">3.46624612808228</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36429786682129</t>
+    <t xml:space="preserve">3.36429762840271</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34730648994446</t>
+    <t xml:space="preserve">3.34730672836304</t>
   </si>
   <si>
     <t xml:space="preserve">3.24535799026489</t>
@@ -1499,7 +1499,7 @@
     <t xml:space="preserve">3.09405112266541</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07652139663696</t>
+    <t xml:space="preserve">3.07652115821838</t>
   </si>
   <si>
     <t xml:space="preserve">3.06775617599487</t>
@@ -1523,13 +1523,13 @@
     <t xml:space="preserve">2.96257615089417</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86616063117981</t>
+    <t xml:space="preserve">2.86616086959839</t>
   </si>
   <si>
     <t xml:space="preserve">2.91875076293945</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80480575561523</t>
+    <t xml:space="preserve">2.80480551719666</t>
   </si>
   <si>
     <t xml:space="preserve">2.82233572006226</t>
@@ -1541,7 +1541,7 @@
     <t xml:space="preserve">2.95381093025208</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83110046386719</t>
+    <t xml:space="preserve">2.83110070228577</t>
   </si>
   <si>
     <t xml:space="preserve">2.93628096580505</t>
@@ -1565,10 +1565,10 @@
     <t xml:space="preserve">2.83986568450928</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68209552764893</t>
+    <t xml:space="preserve">2.68209528923035</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69086027145386</t>
+    <t xml:space="preserve">2.69086050987244</t>
   </si>
   <si>
     <t xml:space="preserve">2.66456532478333</t>
@@ -1586,7 +1586,7 @@
     <t xml:space="preserve">2.76974582672119</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79604053497314</t>
+    <t xml:space="preserve">2.79604077339172</t>
   </si>
   <si>
     <t xml:space="preserve">2.84863090515137</t>
@@ -1683,9 +1683,6 @@
   </si>
   <si>
     <t xml:space="preserve">2.85962271690369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80480551719666</t>
   </si>
   <si>
     <t xml:space="preserve">2.89616751670837</t>
@@ -56952,7 +56949,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G2103" t="s">
-        <v>557</v>
+        <v>505</v>
       </c>
       <c r="H2103" t="s">
         <v>9</v>
@@ -56978,7 +56975,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G2104" t="s">
-        <v>557</v>
+        <v>505</v>
       </c>
       <c r="H2104" t="s">
         <v>9</v>
@@ -57186,7 +57183,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G2112" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="H2112" t="s">
         <v>9</v>
@@ -57316,7 +57313,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G2117" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="H2117" t="s">
         <v>9</v>
@@ -57342,7 +57339,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G2118" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="H2118" t="s">
         <v>9</v>
@@ -57368,7 +57365,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G2119" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="H2119" t="s">
         <v>9</v>
@@ -57420,7 +57417,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G2121" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="H2121" t="s">
         <v>9</v>
@@ -57446,7 +57443,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G2122" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="H2122" t="s">
         <v>9</v>
@@ -57498,7 +57495,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G2124" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="H2124" t="s">
         <v>9</v>
@@ -57524,7 +57521,7 @@
         <v>3.25</v>
       </c>
       <c r="G2125" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="H2125" t="s">
         <v>9</v>
@@ -57550,7 +57547,7 @@
         <v>3.25</v>
       </c>
       <c r="G2126" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="H2126" t="s">
         <v>9</v>
@@ -57576,7 +57573,7 @@
         <v>3.25</v>
       </c>
       <c r="G2127" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="H2127" t="s">
         <v>9</v>
@@ -57602,7 +57599,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G2128" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="H2128" t="s">
         <v>9</v>
@@ -57628,7 +57625,7 @@
         <v>3.25</v>
       </c>
       <c r="G2129" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="H2129" t="s">
         <v>9</v>
@@ -57732,7 +57729,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G2133" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="H2133" t="s">
         <v>9</v>
@@ -57758,7 +57755,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G2134" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="H2134" t="s">
         <v>9</v>
@@ -57784,7 +57781,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G2135" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="H2135" t="s">
         <v>9</v>
@@ -57810,7 +57807,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G2136" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="H2136" t="s">
         <v>9</v>
@@ -57836,7 +57833,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G2137" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H2137" t="s">
         <v>9</v>
@@ -57862,7 +57859,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G2138" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="H2138" t="s">
         <v>9</v>
@@ -57888,7 +57885,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G2139" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="H2139" t="s">
         <v>9</v>
@@ -57914,7 +57911,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2140" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="H2140" t="s">
         <v>9</v>
@@ -57940,7 +57937,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G2141" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H2141" t="s">
         <v>9</v>
@@ -57966,7 +57963,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G2142" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="H2142" t="s">
         <v>9</v>
@@ -57992,7 +57989,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G2143" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="H2143" t="s">
         <v>9</v>
@@ -58018,7 +58015,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G2144" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="H2144" t="s">
         <v>9</v>
@@ -58044,7 +58041,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G2145" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="H2145" t="s">
         <v>9</v>
@@ -58070,7 +58067,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G2146" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="H2146" t="s">
         <v>9</v>
@@ -58096,7 +58093,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G2147" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="H2147" t="s">
         <v>9</v>
@@ -58122,7 +58119,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G2148" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="H2148" t="s">
         <v>9</v>
@@ -58148,7 +58145,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G2149" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="H2149" t="s">
         <v>9</v>
@@ -58174,7 +58171,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G2150" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="H2150" t="s">
         <v>9</v>
@@ -58200,7 +58197,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G2151" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="H2151" t="s">
         <v>9</v>
@@ -58226,7 +58223,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G2152" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="H2152" t="s">
         <v>9</v>
@@ -58252,7 +58249,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G2153" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="H2153" t="s">
         <v>9</v>
@@ -58278,7 +58275,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G2154" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="H2154" t="s">
         <v>9</v>
@@ -58304,7 +58301,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G2155" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="H2155" t="s">
         <v>9</v>
@@ -58330,7 +58327,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G2156" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="H2156" t="s">
         <v>9</v>
@@ -58356,7 +58353,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G2157" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="H2157" t="s">
         <v>9</v>
@@ -58382,7 +58379,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G2158" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="H2158" t="s">
         <v>9</v>
@@ -58408,7 +58405,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G2159" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="H2159" t="s">
         <v>9</v>
@@ -58434,7 +58431,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G2160" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="H2160" t="s">
         <v>9</v>
@@ -58460,7 +58457,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G2161" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="H2161" t="s">
         <v>9</v>
@@ -58486,7 +58483,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G2162" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="H2162" t="s">
         <v>9</v>
@@ -58512,7 +58509,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G2163" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H2163" t="s">
         <v>9</v>
@@ -58538,7 +58535,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G2164" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="H2164" t="s">
         <v>9</v>
@@ -58564,7 +58561,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G2165" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H2165" t="s">
         <v>9</v>
@@ -58590,7 +58587,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G2166" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="H2166" t="s">
         <v>9</v>
@@ -58616,7 +58613,7 @@
         <v>3.25</v>
       </c>
       <c r="G2167" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="H2167" t="s">
         <v>9</v>
@@ -58642,7 +58639,7 @@
         <v>3.25</v>
       </c>
       <c r="G2168" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="H2168" t="s">
         <v>9</v>
@@ -58668,7 +58665,7 @@
         <v>3.25</v>
       </c>
       <c r="G2169" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="H2169" t="s">
         <v>9</v>
@@ -58694,7 +58691,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G2170" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="H2170" t="s">
         <v>9</v>
@@ -58720,7 +58717,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G2171" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H2171" t="s">
         <v>9</v>
@@ -58746,7 +58743,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G2172" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="H2172" t="s">
         <v>9</v>
@@ -58772,7 +58769,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G2173" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="H2173" t="s">
         <v>9</v>
@@ -58798,7 +58795,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G2174" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="H2174" t="s">
         <v>9</v>
@@ -58824,7 +58821,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2175" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="H2175" t="s">
         <v>9</v>
@@ -58850,7 +58847,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2176" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="H2176" t="s">
         <v>9</v>
@@ -58876,7 +58873,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2177" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="H2177" t="s">
         <v>9</v>
@@ -58902,7 +58899,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G2178" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="H2178" t="s">
         <v>9</v>
@@ -58928,7 +58925,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G2179" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H2179" t="s">
         <v>9</v>
@@ -58954,7 +58951,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G2180" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="H2180" t="s">
         <v>9</v>
@@ -58980,7 +58977,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G2181" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="H2181" t="s">
         <v>9</v>
@@ -59006,7 +59003,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2182" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="H2182" t="s">
         <v>9</v>
@@ -59032,7 +59029,7 @@
         <v>3.25</v>
       </c>
       <c r="G2183" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="H2183" t="s">
         <v>9</v>
@@ -59058,7 +59055,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G2184" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="H2184" t="s">
         <v>9</v>
@@ -59084,7 +59081,7 @@
         <v>3.25</v>
       </c>
       <c r="G2185" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="H2185" t="s">
         <v>9</v>
@@ -59110,7 +59107,7 @@
         <v>3.25</v>
       </c>
       <c r="G2186" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="H2186" t="s">
         <v>9</v>
@@ -59136,7 +59133,7 @@
         <v>3.25</v>
       </c>
       <c r="G2187" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="H2187" t="s">
         <v>9</v>
@@ -59162,7 +59159,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G2188" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="H2188" t="s">
         <v>9</v>
@@ -59188,7 +59185,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G2189" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="H2189" t="s">
         <v>9</v>
@@ -59214,7 +59211,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G2190" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="H2190" t="s">
         <v>9</v>
@@ -59240,7 +59237,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G2191" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="H2191" t="s">
         <v>9</v>
@@ -59266,7 +59263,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G2192" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="H2192" t="s">
         <v>9</v>
@@ -59292,7 +59289,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G2193" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="H2193" t="s">
         <v>9</v>
@@ -59318,7 +59315,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G2194" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="H2194" t="s">
         <v>9</v>
@@ -59344,7 +59341,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G2195" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="H2195" t="s">
         <v>9</v>
@@ -59370,7 +59367,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G2196" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="H2196" t="s">
         <v>9</v>
@@ -59396,7 +59393,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2197" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="H2197" t="s">
         <v>9</v>
@@ -59422,7 +59419,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G2198" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="H2198" t="s">
         <v>9</v>
@@ -59448,7 +59445,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G2199" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="H2199" t="s">
         <v>9</v>
@@ -59474,7 +59471,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G2200" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="H2200" t="s">
         <v>9</v>
@@ -59500,7 +59497,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G2201" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H2201" t="s">
         <v>9</v>
@@ -59526,7 +59523,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G2202" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="H2202" t="s">
         <v>9</v>
@@ -59552,7 +59549,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G2203" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="H2203" t="s">
         <v>9</v>
@@ -59578,7 +59575,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G2204" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H2204" t="s">
         <v>9</v>
@@ -59604,7 +59601,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G2205" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="H2205" t="s">
         <v>9</v>
@@ -59630,7 +59627,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2206" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="H2206" t="s">
         <v>9</v>
@@ -59656,7 +59653,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G2207" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="H2207" t="s">
         <v>9</v>
@@ -59682,7 +59679,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G2208" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H2208" t="s">
         <v>9</v>
@@ -59708,7 +59705,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G2209" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H2209" t="s">
         <v>9</v>
@@ -59734,7 +59731,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G2210" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H2210" t="s">
         <v>9</v>
@@ -59760,7 +59757,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G2211" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H2211" t="s">
         <v>9</v>
@@ -59786,7 +59783,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G2212" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="H2212" t="s">
         <v>9</v>
@@ -59812,7 +59809,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G2213" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="H2213" t="s">
         <v>9</v>
@@ -59838,7 +59835,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G2214" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="H2214" t="s">
         <v>9</v>
@@ -59864,7 +59861,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G2215" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="H2215" t="s">
         <v>9</v>
@@ -59890,7 +59887,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G2216" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="H2216" t="s">
         <v>9</v>
@@ -59916,7 +59913,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G2217" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H2217" t="s">
         <v>9</v>
@@ -59942,7 +59939,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G2218" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H2218" t="s">
         <v>9</v>
@@ -59968,7 +59965,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G2219" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="H2219" t="s">
         <v>9</v>
@@ -59994,7 +59991,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G2220" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="H2220" t="s">
         <v>9</v>
@@ -60020,7 +60017,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G2221" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H2221" t="s">
         <v>9</v>
@@ -60046,7 +60043,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G2222" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="H2222" t="s">
         <v>9</v>
@@ -60072,7 +60069,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G2223" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="H2223" t="s">
         <v>9</v>
@@ -60098,7 +60095,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G2224" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H2224" t="s">
         <v>9</v>
@@ -60124,7 +60121,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G2225" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="H2225" t="s">
         <v>9</v>
@@ -60150,7 +60147,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G2226" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="H2226" t="s">
         <v>9</v>
@@ -60176,7 +60173,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2227" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="H2227" t="s">
         <v>9</v>
@@ -60202,7 +60199,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G2228" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="H2228" t="s">
         <v>9</v>
@@ -60228,7 +60225,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G2229" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="H2229" t="s">
         <v>9</v>
@@ -60254,7 +60251,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G2230" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="H2230" t="s">
         <v>9</v>
@@ -60280,7 +60277,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G2231" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="H2231" t="s">
         <v>9</v>
@@ -60306,7 +60303,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G2232" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="H2232" t="s">
         <v>9</v>
@@ -60332,7 +60329,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G2233" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H2233" t="s">
         <v>9</v>
@@ -60358,7 +60355,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G2234" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="H2234" t="s">
         <v>9</v>
@@ -60384,7 +60381,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G2235" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="H2235" t="s">
         <v>9</v>
@@ -60410,7 +60407,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G2236" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="H2236" t="s">
         <v>9</v>
@@ -60436,7 +60433,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G2237" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="H2237" t="s">
         <v>9</v>
@@ -60462,7 +60459,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G2238" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="H2238" t="s">
         <v>9</v>
@@ -60488,7 +60485,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G2239" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="H2239" t="s">
         <v>9</v>
@@ -60514,7 +60511,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G2240" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="H2240" t="s">
         <v>9</v>
@@ -60540,7 +60537,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G2241" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="H2241" t="s">
         <v>9</v>
@@ -60566,7 +60563,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G2242" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="H2242" t="s">
         <v>9</v>
@@ -60592,7 +60589,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G2243" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="H2243" t="s">
         <v>9</v>
@@ -60618,7 +60615,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G2244" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="H2244" t="s">
         <v>9</v>
@@ -60644,7 +60641,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G2245" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="H2245" t="s">
         <v>9</v>
@@ -60670,7 +60667,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G2246" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="H2246" t="s">
         <v>9</v>
@@ -60696,7 +60693,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G2247" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="H2247" t="s">
         <v>9</v>
@@ -60722,7 +60719,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G2248" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="H2248" t="s">
         <v>9</v>
@@ -60748,7 +60745,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G2249" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="H2249" t="s">
         <v>9</v>
@@ -60774,7 +60771,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G2250" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="H2250" t="s">
         <v>9</v>
@@ -60800,7 +60797,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G2251" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="H2251" t="s">
         <v>9</v>
@@ -60826,7 +60823,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G2252" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="H2252" t="s">
         <v>9</v>
@@ -60852,7 +60849,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G2253" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="H2253" t="s">
         <v>9</v>
@@ -60878,7 +60875,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G2254" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="H2254" t="s">
         <v>9</v>
@@ -60904,7 +60901,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G2255" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="H2255" t="s">
         <v>9</v>
@@ -60930,7 +60927,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G2256" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="H2256" t="s">
         <v>9</v>
@@ -60956,7 +60953,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G2257" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="H2257" t="s">
         <v>9</v>
@@ -60982,7 +60979,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G2258" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="H2258" t="s">
         <v>9</v>
@@ -61008,7 +61005,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G2259" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="H2259" t="s">
         <v>9</v>
@@ -61034,7 +61031,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G2260" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="H2260" t="s">
         <v>9</v>
@@ -61060,7 +61057,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G2261" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="H2261" t="s">
         <v>9</v>
@@ -61086,7 +61083,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G2262" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="H2262" t="s">
         <v>9</v>
@@ -61112,7 +61109,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G2263" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="H2263" t="s">
         <v>9</v>
@@ -61138,7 +61135,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G2264" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="H2264" t="s">
         <v>9</v>
@@ -61164,7 +61161,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G2265" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="H2265" t="s">
         <v>9</v>
@@ -61190,7 +61187,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G2266" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="H2266" t="s">
         <v>9</v>
@@ -61216,7 +61213,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G2267" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="H2267" t="s">
         <v>9</v>
@@ -61242,7 +61239,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G2268" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="H2268" t="s">
         <v>9</v>
@@ -61268,7 +61265,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G2269" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="H2269" t="s">
         <v>9</v>
@@ -61294,7 +61291,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G2270" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="H2270" t="s">
         <v>9</v>
@@ -61320,7 +61317,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G2271" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="H2271" t="s">
         <v>9</v>
@@ -61346,7 +61343,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G2272" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="H2272" t="s">
         <v>9</v>
@@ -61372,7 +61369,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G2273" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="H2273" t="s">
         <v>9</v>
@@ -61398,7 +61395,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G2274" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="H2274" t="s">
         <v>9</v>
@@ -61424,7 +61421,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G2275" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="H2275" t="s">
         <v>9</v>
@@ -61450,7 +61447,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G2276" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="H2276" t="s">
         <v>9</v>
@@ -61476,7 +61473,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G2277" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="H2277" t="s">
         <v>9</v>
@@ -61502,7 +61499,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G2278" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="H2278" t="s">
         <v>9</v>
@@ -61528,7 +61525,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G2279" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H2279" t="s">
         <v>9</v>
@@ -61554,7 +61551,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G2280" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="H2280" t="s">
         <v>9</v>
@@ -61580,7 +61577,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G2281" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H2281" t="s">
         <v>9</v>
@@ -61606,7 +61603,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G2282" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="H2282" t="s">
         <v>9</v>
@@ -61632,7 +61629,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G2283" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="H2283" t="s">
         <v>9</v>
@@ -61658,7 +61655,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G2284" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H2284" t="s">
         <v>9</v>
@@ -61684,7 +61681,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G2285" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="H2285" t="s">
         <v>9</v>
@@ -61710,7 +61707,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G2286" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H2286" t="s">
         <v>9</v>
@@ -61736,7 +61733,7 @@
         <v>3.25</v>
       </c>
       <c r="G2287" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="H2287" t="s">
         <v>9</v>
@@ -61762,7 +61759,7 @@
         <v>3.25</v>
       </c>
       <c r="G2288" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="H2288" t="s">
         <v>9</v>
@@ -61788,7 +61785,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G2289" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="H2289" t="s">
         <v>9</v>
@@ -61814,7 +61811,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G2290" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="H2290" t="s">
         <v>9</v>
@@ -61840,7 +61837,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G2291" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H2291" t="s">
         <v>9</v>
@@ -61866,7 +61863,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G2292" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="H2292" t="s">
         <v>9</v>
@@ -61892,7 +61889,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G2293" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="H2293" t="s">
         <v>9</v>
@@ -61918,7 +61915,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G2294" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H2294" t="s">
         <v>9</v>
@@ -61944,7 +61941,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G2295" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H2295" t="s">
         <v>9</v>
@@ -61970,7 +61967,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G2296" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H2296" t="s">
         <v>9</v>
@@ -61996,7 +61993,7 @@
         <v>3.25</v>
       </c>
       <c r="G2297" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="H2297" t="s">
         <v>9</v>
@@ -62022,7 +62019,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G2298" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="H2298" t="s">
         <v>9</v>
@@ -62048,7 +62045,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G2299" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H2299" t="s">
         <v>9</v>
@@ -62074,7 +62071,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2300" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="H2300" t="s">
         <v>9</v>
@@ -62100,7 +62097,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G2301" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="H2301" t="s">
         <v>9</v>
@@ -62126,7 +62123,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G2302" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="H2302" t="s">
         <v>9</v>
@@ -62152,7 +62149,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G2303" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="H2303" t="s">
         <v>9</v>
@@ -62178,7 +62175,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G2304" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="H2304" t="s">
         <v>9</v>
@@ -62204,7 +62201,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G2305" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="H2305" t="s">
         <v>9</v>
@@ -62230,7 +62227,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G2306" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="H2306" t="s">
         <v>9</v>
@@ -62256,7 +62253,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G2307" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="H2307" t="s">
         <v>9</v>
@@ -62282,7 +62279,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G2308" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="H2308" t="s">
         <v>9</v>
@@ -62308,7 +62305,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G2309" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="H2309" t="s">
         <v>9</v>
@@ -62334,7 +62331,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G2310" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="H2310" t="s">
         <v>9</v>
@@ -62360,7 +62357,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2311" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="H2311" t="s">
         <v>9</v>
@@ -62386,7 +62383,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2312" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="H2312" t="s">
         <v>9</v>
@@ -62412,7 +62409,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G2313" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="H2313" t="s">
         <v>9</v>
@@ -62438,7 +62435,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G2314" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="H2314" t="s">
         <v>9</v>
@@ -62464,7 +62461,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G2315" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="H2315" t="s">
         <v>9</v>
@@ -62490,7 +62487,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G2316" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="H2316" t="s">
         <v>9</v>
@@ -62516,7 +62513,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G2317" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="H2317" t="s">
         <v>9</v>
@@ -62542,7 +62539,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G2318" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="H2318" t="s">
         <v>9</v>
@@ -62594,7 +62591,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G2320" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="H2320" t="s">
         <v>9</v>
@@ -62620,7 +62617,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G2321" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H2321" t="s">
         <v>9</v>
@@ -62646,7 +62643,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G2322" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H2322" t="s">
         <v>9</v>
@@ -62672,7 +62669,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2323" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="H2323" t="s">
         <v>9</v>
@@ -62698,7 +62695,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2324" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="H2324" t="s">
         <v>9</v>
@@ -62724,7 +62721,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2325" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="H2325" t="s">
         <v>9</v>
@@ -62750,7 +62747,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G2326" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="H2326" t="s">
         <v>9</v>
@@ -62776,7 +62773,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2327" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="H2327" t="s">
         <v>9</v>
@@ -62802,7 +62799,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G2328" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="H2328" t="s">
         <v>9</v>
@@ -62828,7 +62825,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G2329" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="H2329" t="s">
         <v>9</v>
@@ -62854,7 +62851,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G2330" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="H2330" t="s">
         <v>9</v>
@@ -62880,7 +62877,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G2331" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="H2331" t="s">
         <v>9</v>
@@ -62906,7 +62903,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G2332" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="H2332" t="s">
         <v>9</v>
@@ -62932,7 +62929,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G2333" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="H2333" t="s">
         <v>9</v>
@@ -62958,7 +62955,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G2334" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="H2334" t="s">
         <v>9</v>
@@ -62984,7 +62981,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G2335" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="H2335" t="s">
         <v>9</v>
@@ -63010,7 +63007,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G2336" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="H2336" t="s">
         <v>9</v>
@@ -63036,7 +63033,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G2337" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="H2337" t="s">
         <v>9</v>
@@ -63062,7 +63059,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G2338" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="H2338" t="s">
         <v>9</v>
@@ -63088,7 +63085,7 @@
         <v>3.25</v>
       </c>
       <c r="G2339" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="H2339" t="s">
         <v>9</v>
@@ -63114,7 +63111,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G2340" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="H2340" t="s">
         <v>9</v>
@@ -63140,7 +63137,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G2341" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="H2341" t="s">
         <v>9</v>
@@ -63166,7 +63163,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G2342" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="H2342" t="s">
         <v>9</v>
@@ -63192,7 +63189,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G2343" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="H2343" t="s">
         <v>9</v>
@@ -63218,7 +63215,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G2344" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="H2344" t="s">
         <v>9</v>
@@ -63244,7 +63241,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G2345" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="H2345" t="s">
         <v>9</v>
@@ -63270,7 +63267,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G2346" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="H2346" t="s">
         <v>9</v>
@@ -63296,7 +63293,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G2347" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="H2347" t="s">
         <v>9</v>
@@ -63322,7 +63319,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G2348" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="H2348" t="s">
         <v>9</v>
@@ -63348,7 +63345,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G2349" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H2349" t="s">
         <v>9</v>
@@ -63374,7 +63371,7 @@
         <v>3.25</v>
       </c>
       <c r="G2350" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="H2350" t="s">
         <v>9</v>
@@ -63400,7 +63397,7 @@
         <v>3.25</v>
       </c>
       <c r="G2351" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="H2351" t="s">
         <v>9</v>
@@ -63426,7 +63423,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G2352" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H2352" t="s">
         <v>9</v>
@@ -63452,7 +63449,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G2353" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="H2353" t="s">
         <v>9</v>
@@ -63478,7 +63475,7 @@
         <v>3.25</v>
       </c>
       <c r="G2354" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="H2354" t="s">
         <v>9</v>
@@ -63504,7 +63501,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G2355" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="H2355" t="s">
         <v>9</v>
@@ -63530,7 +63527,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G2356" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="H2356" t="s">
         <v>9</v>
@@ -63556,7 +63553,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G2357" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="H2357" t="s">
         <v>9</v>
@@ -63582,7 +63579,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G2358" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="H2358" t="s">
         <v>9</v>
@@ -63608,7 +63605,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G2359" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="H2359" t="s">
         <v>9</v>
@@ -63634,7 +63631,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G2360" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="H2360" t="s">
         <v>9</v>
@@ -63660,7 +63657,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G2361" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="H2361" t="s">
         <v>9</v>
@@ -63686,7 +63683,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G2362" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="H2362" t="s">
         <v>9</v>
@@ -63712,7 +63709,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2363" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="H2363" t="s">
         <v>9</v>
@@ -63738,7 +63735,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2364" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="H2364" t="s">
         <v>9</v>
@@ -63764,7 +63761,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G2365" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="H2365" t="s">
         <v>9</v>
@@ -63790,7 +63787,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2366" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="H2366" t="s">
         <v>9</v>
@@ -63816,7 +63813,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G2367" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="H2367" t="s">
         <v>9</v>
@@ -63842,7 +63839,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G2368" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="H2368" t="s">
         <v>9</v>
@@ -63868,7 +63865,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G2369" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="H2369" t="s">
         <v>9</v>
@@ -63894,7 +63891,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G2370" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="H2370" t="s">
         <v>9</v>
@@ -63920,7 +63917,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G2371" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="H2371" t="s">
         <v>9</v>
@@ -63946,7 +63943,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G2372" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="H2372" t="s">
         <v>9</v>
@@ -63972,7 +63969,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G2373" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="H2373" t="s">
         <v>9</v>
@@ -63998,7 +63995,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G2374" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="H2374" t="s">
         <v>9</v>
@@ -64024,7 +64021,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G2375" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="H2375" t="s">
         <v>9</v>
@@ -64050,7 +64047,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G2376" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="H2376" t="s">
         <v>9</v>
@@ -64076,7 +64073,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G2377" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="H2377" t="s">
         <v>9</v>
@@ -64102,7 +64099,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G2378" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="H2378" t="s">
         <v>9</v>
@@ -64128,7 +64125,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G2379" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="H2379" t="s">
         <v>9</v>
@@ -64154,7 +64151,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G2380" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="H2380" t="s">
         <v>9</v>
@@ -64180,7 +64177,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G2381" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="H2381" t="s">
         <v>9</v>
@@ -64206,7 +64203,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G2382" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="H2382" t="s">
         <v>9</v>
@@ -64232,7 +64229,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G2383" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="H2383" t="s">
         <v>9</v>
@@ -64258,7 +64255,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2384" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="H2384" t="s">
         <v>9</v>
@@ -64284,7 +64281,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G2385" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="H2385" t="s">
         <v>9</v>
@@ -64310,7 +64307,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G2386" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="H2386" t="s">
         <v>9</v>
@@ -64336,7 +64333,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G2387" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="H2387" t="s">
         <v>9</v>
@@ -64362,7 +64359,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G2388" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="H2388" t="s">
         <v>9</v>
@@ -64388,7 +64385,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G2389" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="H2389" t="s">
         <v>9</v>
@@ -64414,7 +64411,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2390" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="H2390" t="s">
         <v>9</v>
@@ -64440,7 +64437,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2391" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="H2391" t="s">
         <v>9</v>
@@ -64466,7 +64463,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G2392" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="H2392" t="s">
         <v>9</v>
@@ -64492,7 +64489,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G2393" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="H2393" t="s">
         <v>9</v>
@@ -64518,7 +64515,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G2394" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="H2394" t="s">
         <v>9</v>
@@ -64544,7 +64541,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2395" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="H2395" t="s">
         <v>9</v>
@@ -64570,7 +64567,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2396" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="H2396" t="s">
         <v>9</v>
@@ -64596,7 +64593,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G2397" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="H2397" t="s">
         <v>9</v>
@@ -64622,7 +64619,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2398" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="H2398" t="s">
         <v>9</v>
@@ -64648,7 +64645,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G2399" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="H2399" t="s">
         <v>9</v>
@@ -64674,7 +64671,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G2400" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="H2400" t="s">
         <v>9</v>
@@ -64700,7 +64697,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G2401" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="H2401" t="s">
         <v>9</v>
@@ -64726,7 +64723,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G2402" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="H2402" t="s">
         <v>9</v>
@@ -64752,7 +64749,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G2403" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="H2403" t="s">
         <v>9</v>
@@ -64778,7 +64775,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G2404" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="H2404" t="s">
         <v>9</v>
@@ -64804,7 +64801,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G2405" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="H2405" t="s">
         <v>9</v>
@@ -64830,7 +64827,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G2406" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="H2406" t="s">
         <v>9</v>
@@ -64856,7 +64853,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G2407" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="H2407" t="s">
         <v>9</v>
@@ -64882,7 +64879,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G2408" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="H2408" t="s">
         <v>9</v>
@@ -64908,7 +64905,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2409" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="H2409" t="s">
         <v>9</v>
@@ -64934,7 +64931,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G2410" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="H2410" t="s">
         <v>9</v>
@@ -64960,7 +64957,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G2411" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="H2411" t="s">
         <v>9</v>
@@ -64986,7 +64983,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G2412" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="H2412" t="s">
         <v>9</v>
@@ -65012,7 +65009,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G2413" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="H2413" t="s">
         <v>9</v>
@@ -65038,7 +65035,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G2414" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="H2414" t="s">
         <v>9</v>
@@ -65064,7 +65061,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G2415" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="H2415" t="s">
         <v>9</v>
@@ -65090,7 +65087,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G2416" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="H2416" t="s">
         <v>9</v>
@@ -65116,7 +65113,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G2417" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="H2417" t="s">
         <v>9</v>
@@ -65142,7 +65139,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G2418" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="H2418" t="s">
         <v>9</v>
@@ -65168,7 +65165,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G2419" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="H2419" t="s">
         <v>9</v>
@@ -65194,7 +65191,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G2420" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="H2420" t="s">
         <v>9</v>
@@ -65220,7 +65217,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G2421" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="H2421" t="s">
         <v>9</v>
@@ -65246,7 +65243,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G2422" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="H2422" t="s">
         <v>9</v>
@@ -65272,7 +65269,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G2423" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="H2423" t="s">
         <v>9</v>
@@ -65298,7 +65295,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G2424" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="H2424" t="s">
         <v>9</v>
@@ -65324,7 +65321,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G2425" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="H2425" t="s">
         <v>9</v>
@@ -65350,7 +65347,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G2426" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="H2426" t="s">
         <v>9</v>
@@ -65376,7 +65373,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G2427" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="H2427" t="s">
         <v>9</v>
@@ -65402,7 +65399,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G2428" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="H2428" t="s">
         <v>9</v>
@@ -65428,7 +65425,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G2429" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="H2429" t="s">
         <v>9</v>
@@ -65454,7 +65451,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G2430" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="H2430" t="s">
         <v>9</v>
@@ -65480,7 +65477,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G2431" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="H2431" t="s">
         <v>9</v>
@@ -65506,7 +65503,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G2432" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="H2432" t="s">
         <v>9</v>
@@ -65532,7 +65529,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G2433" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="H2433" t="s">
         <v>9</v>
@@ -65558,7 +65555,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G2434" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="H2434" t="s">
         <v>9</v>
@@ -65584,7 +65581,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G2435" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="H2435" t="s">
         <v>9</v>
@@ -65610,7 +65607,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G2436" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="H2436" t="s">
         <v>9</v>
@@ -65636,7 +65633,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G2437" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="H2437" t="s">
         <v>9</v>
@@ -65662,7 +65659,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G2438" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="H2438" t="s">
         <v>9</v>
@@ -65688,7 +65685,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G2439" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="H2439" t="s">
         <v>9</v>
@@ -65714,7 +65711,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G2440" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="H2440" t="s">
         <v>9</v>
@@ -65740,7 +65737,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G2441" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="H2441" t="s">
         <v>9</v>
@@ -65766,7 +65763,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G2442" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="H2442" t="s">
         <v>9</v>
@@ -65792,7 +65789,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G2443" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="H2443" t="s">
         <v>9</v>
@@ -65818,7 +65815,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G2444" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="H2444" t="s">
         <v>9</v>
@@ -65844,7 +65841,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G2445" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="H2445" t="s">
         <v>9</v>
@@ -65870,7 +65867,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G2446" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="H2446" t="s">
         <v>9</v>
@@ -65896,7 +65893,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G2447" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="H2447" t="s">
         <v>9</v>
@@ -65922,7 +65919,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G2448" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="H2448" t="s">
         <v>9</v>
@@ -65948,7 +65945,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G2449" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="H2449" t="s">
         <v>9</v>
@@ -65974,7 +65971,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G2450" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="H2450" t="s">
         <v>9</v>
@@ -66000,7 +65997,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G2451" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="H2451" t="s">
         <v>9</v>
@@ -66026,7 +66023,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G2452" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="H2452" t="s">
         <v>9</v>
@@ -66052,7 +66049,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G2453" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="H2453" t="s">
         <v>9</v>
@@ -66078,7 +66075,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G2454" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="H2454" t="s">
         <v>9</v>
@@ -66104,7 +66101,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G2455" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="H2455" t="s">
         <v>9</v>
@@ -66130,7 +66127,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G2456" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="H2456" t="s">
         <v>9</v>
@@ -66156,7 +66153,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G2457" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="H2457" t="s">
         <v>9</v>
@@ -66182,7 +66179,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G2458" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="H2458" t="s">
         <v>9</v>
@@ -66208,7 +66205,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G2459" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="H2459" t="s">
         <v>9</v>
@@ -66234,7 +66231,7 @@
         <v>4</v>
       </c>
       <c r="G2460" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="H2460" t="s">
         <v>9</v>
@@ -66260,7 +66257,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G2461" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="H2461" t="s">
         <v>9</v>
@@ -66286,7 +66283,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G2462" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="H2462" t="s">
         <v>9</v>
@@ -66312,7 +66309,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G2463" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="H2463" t="s">
         <v>9</v>
@@ -66338,7 +66335,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G2464" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="H2464" t="s">
         <v>9</v>
@@ -66364,7 +66361,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G2465" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="H2465" t="s">
         <v>9</v>
@@ -66390,7 +66387,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G2466" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="H2466" t="s">
         <v>9</v>
@@ -66416,7 +66413,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G2467" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="H2467" t="s">
         <v>9</v>
@@ -66442,7 +66439,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G2468" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="H2468" t="s">
         <v>9</v>
@@ -66468,7 +66465,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G2469" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="H2469" t="s">
         <v>9</v>
@@ -66494,7 +66491,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G2470" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="H2470" t="s">
         <v>9</v>
@@ -66520,7 +66517,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G2471" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="H2471" t="s">
         <v>9</v>
@@ -66546,7 +66543,7 @@
         <v>4</v>
       </c>
       <c r="G2472" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="H2472" t="s">
         <v>9</v>
@@ -66572,7 +66569,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G2473" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="H2473" t="s">
         <v>9</v>
@@ -66598,7 +66595,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G2474" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="H2474" t="s">
         <v>9</v>
@@ -66624,7 +66621,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G2475" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="H2475" t="s">
         <v>9</v>
@@ -66650,7 +66647,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G2476" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="H2476" t="s">
         <v>9</v>
@@ -66676,7 +66673,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G2477" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="H2477" t="s">
         <v>9</v>
@@ -66702,7 +66699,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G2478" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="H2478" t="s">
         <v>9</v>
@@ -66728,7 +66725,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G2479" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="H2479" t="s">
         <v>9</v>
@@ -66754,7 +66751,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G2480" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="H2480" t="s">
         <v>9</v>
@@ -66780,7 +66777,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G2481" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="H2481" t="s">
         <v>9</v>
@@ -66806,7 +66803,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G2482" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="H2482" t="s">
         <v>9</v>
@@ -66832,7 +66829,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G2483" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="H2483" t="s">
         <v>9</v>
@@ -66858,7 +66855,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G2484" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="H2484" t="s">
         <v>9</v>
@@ -66884,7 +66881,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G2485" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="H2485" t="s">
         <v>9</v>
@@ -66910,7 +66907,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G2486" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="H2486" t="s">
         <v>9</v>
@@ -66936,7 +66933,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G2487" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="H2487" t="s">
         <v>9</v>
@@ -66962,7 +66959,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G2488" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="H2488" t="s">
         <v>9</v>
@@ -66988,7 +66985,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G2489" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="H2489" t="s">
         <v>9</v>
@@ -67014,7 +67011,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G2490" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="H2490" t="s">
         <v>9</v>
@@ -67040,7 +67037,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G2491" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="H2491" t="s">
         <v>9</v>
@@ -67066,7 +67063,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G2492" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="H2492" t="s">
         <v>9</v>
@@ -67092,7 +67089,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G2493" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="H2493" t="s">
         <v>9</v>
@@ -67118,7 +67115,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G2494" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="H2494" t="s">
         <v>9</v>
@@ -67144,7 +67141,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G2495" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="H2495" t="s">
         <v>9</v>
@@ -67152,7 +67149,7 @@
     </row>
     <row r="2496">
       <c r="A2496" s="1" t="n">
-        <v>45953.422650463</v>
+        <v>45953.2916666667</v>
       </c>
       <c r="B2496" t="n">
         <v>2450</v>
@@ -67170,9 +67167,35 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G2496" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="H2496" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2497">
+      <c r="A2497" s="1" t="n">
+        <v>45954.6494791667</v>
+      </c>
+      <c r="B2497" t="n">
+        <v>12067</v>
+      </c>
+      <c r="C2497" t="n">
+        <v>4.69999980926514</v>
+      </c>
+      <c r="D2497" t="n">
+        <v>4.59999990463257</v>
+      </c>
+      <c r="E2497" t="n">
+        <v>4.69999980926514</v>
+      </c>
+      <c r="F2497" t="n">
+        <v>4.69999980926514</v>
+      </c>
+      <c r="G2497" t="s">
+        <v>638</v>
+      </c>
+      <c r="H2497" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ENV.MI.xlsx
+++ b/data/ENV.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="643" uniqueCount="643">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="644" uniqueCount="644">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,46 +38,46 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18965244293213</t>
+    <t xml:space="preserve">2.18965268135071</t>
   </si>
   <si>
     <t xml:space="preserve">ENV.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20979785919189</t>
+    <t xml:space="preserve">2.20979809761047</t>
   </si>
   <si>
     <t xml:space="preserve">2.1447126865387</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16175866127014</t>
+    <t xml:space="preserve">2.16175889968872</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03778696060181</t>
+    <t xml:space="preserve">2.03778719902039</t>
   </si>
   <si>
     <t xml:space="preserve">2.08272647857666</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05328369140625</t>
+    <t xml:space="preserve">2.05328392982483</t>
   </si>
   <si>
     <t xml:space="preserve">2.03623747825623</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96805286407471</t>
+    <t xml:space="preserve">1.96805262565613</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96030473709106</t>
+    <t xml:space="preserve">1.96030449867249</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89831900596619</t>
+    <t xml:space="preserve">1.89831876754761</t>
   </si>
   <si>
     <t xml:space="preserve">1.88127243518829</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96340358257294</t>
+    <t xml:space="preserve">1.96340370178223</t>
   </si>
   <si>
     <t xml:space="preserve">1.98354935646057</t>
@@ -86,16 +86,16 @@
     <t xml:space="preserve">2.01299262046814</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93551027774811</t>
+    <t xml:space="preserve">1.93550992012024</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93705976009369</t>
+    <t xml:space="preserve">1.9370596408844</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91381525993347</t>
+    <t xml:space="preserve">1.91381514072418</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91071593761444</t>
+    <t xml:space="preserve">1.91071605682373</t>
   </si>
   <si>
     <t xml:space="preserve">1.86577582359314</t>
@@ -104,37 +104,37 @@
     <t xml:space="preserve">1.89211976528168</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85182917118073</t>
+    <t xml:space="preserve">1.8518294095993</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93396043777466</t>
+    <t xml:space="preserve">1.93396055698395</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86732590198517</t>
+    <t xml:space="preserve">1.86732566356659</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8890209197998</t>
+    <t xml:space="preserve">1.88902080059052</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98664832115173</t>
+    <t xml:space="preserve">1.98664855957031</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11526966094971</t>
+    <t xml:space="preserve">2.11526918411255</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18500328063965</t>
+    <t xml:space="preserve">2.18500351905823</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20824861526489</t>
+    <t xml:space="preserve">2.20824837684631</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16950702667236</t>
+    <t xml:space="preserve">2.16950678825378</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08427667617798</t>
+    <t xml:space="preserve">2.0842764377594</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0145423412323</t>
+    <t xml:space="preserve">2.01454186439514</t>
   </si>
   <si>
     <t xml:space="preserve">2.0052444934845</t>
@@ -152,37 +152,37 @@
     <t xml:space="preserve">2.20050001144409</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27178382873535</t>
+    <t xml:space="preserve">2.27178406715393</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24698925018311</t>
+    <t xml:space="preserve">2.24698948860168</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32137250900269</t>
+    <t xml:space="preserve">2.32137227058411</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28418111801147</t>
+    <t xml:space="preserve">2.2841808795929</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37870931625366</t>
+    <t xml:space="preserve">2.37870955467224</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35546469688416</t>
+    <t xml:space="preserve">2.35546493530273</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44069528579712</t>
+    <t xml:space="preserve">2.4406955242157</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43139743804932</t>
+    <t xml:space="preserve">2.4313976764679</t>
   </si>
   <si>
     <t xml:space="preserve">2.44999313354492</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38490772247314</t>
+    <t xml:space="preserve">2.3849081993103</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3616635799408</t>
+    <t xml:space="preserve">2.36166334152222</t>
   </si>
   <si>
     <t xml:space="preserve">2.36321306228638</t>
@@ -191,10 +191,10 @@
     <t xml:space="preserve">2.3198230266571</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35236525535583</t>
+    <t xml:space="preserve">2.35236549377441</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26868414878845</t>
+    <t xml:space="preserve">2.26868462562561</t>
   </si>
   <si>
     <t xml:space="preserve">2.32292199134827</t>
@@ -203,7 +203,7 @@
     <t xml:space="preserve">2.33531951904297</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33996820449829</t>
+    <t xml:space="preserve">2.33996844291687</t>
   </si>
   <si>
     <t xml:space="preserve">2.31052494049072</t>
@@ -224,10 +224,10 @@
     <t xml:space="preserve">2.23149299621582</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07497835159302</t>
+    <t xml:space="preserve">2.07497882843018</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00834345817566</t>
+    <t xml:space="preserve">2.00834393501282</t>
   </si>
   <si>
     <t xml:space="preserve">2.03468751907349</t>
@@ -236,157 +236,157 @@
     <t xml:space="preserve">2.02229046821594</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97580087184906</t>
+    <t xml:space="preserve">1.97580122947693</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91980648040771</t>
+    <t xml:space="preserve">1.91980671882629</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8821634054184</t>
+    <t xml:space="preserve">1.88216328620911</t>
   </si>
   <si>
     <t xml:space="preserve">2.00136733055115</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96058690547943</t>
+    <t xml:space="preserve">1.96058678627014</t>
   </si>
   <si>
     <t xml:space="preserve">1.90255379676819</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92137551307678</t>
+    <t xml:space="preserve">1.92137539386749</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91353297233582</t>
+    <t xml:space="preserve">1.91353285312653</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89784812927246</t>
+    <t xml:space="preserve">1.89784836769104</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89000606536865</t>
+    <t xml:space="preserve">1.89000594615936</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85079395771027</t>
+    <t xml:space="preserve">1.85079407691956</t>
   </si>
   <si>
     <t xml:space="preserve">1.88059520721436</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86647868156433</t>
+    <t xml:space="preserve">1.86647891998291</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54651093482971</t>
+    <t xml:space="preserve">1.54651081562042</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6861047744751</t>
+    <t xml:space="preserve">1.68610489368439</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70178973674774</t>
+    <t xml:space="preserve">1.70178961753845</t>
   </si>
   <si>
     <t xml:space="preserve">1.70022106170654</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66257762908936</t>
+    <t xml:space="preserve">1.66257774829865</t>
   </si>
   <si>
     <t xml:space="preserve">1.64532458782196</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62336587905884</t>
+    <t xml:space="preserve">1.62336599826813</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61552369594574</t>
+    <t xml:space="preserve">1.61552357673645</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63120818138123</t>
+    <t xml:space="preserve">1.63120806217194</t>
   </si>
   <si>
     <t xml:space="preserve">1.58415424823761</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64689302444458</t>
+    <t xml:space="preserve">1.64689290523529</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6406192779541</t>
+    <t xml:space="preserve">1.64061915874481</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63905072212219</t>
+    <t xml:space="preserve">1.6390506029129</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60768115520477</t>
+    <t xml:space="preserve">1.60768127441406</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57631194591522</t>
+    <t xml:space="preserve">1.57631182670593</t>
   </si>
   <si>
     <t xml:space="preserve">1.59199655056</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75668597221375</t>
+    <t xml:space="preserve">1.75668573379517</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84295165538788</t>
+    <t xml:space="preserve">1.84295177459717</t>
   </si>
   <si>
     <t xml:space="preserve">1.84608888626099</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92921757698059</t>
+    <t xml:space="preserve">1.92921769618988</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88530027866364</t>
+    <t xml:space="preserve">1.88530051708221</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90098524093628</t>
+    <t xml:space="preserve">1.90098488330841</t>
   </si>
   <si>
     <t xml:space="preserve">1.91823816299438</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94960749149323</t>
+    <t xml:space="preserve">1.9496077299118</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93078577518463</t>
+    <t xml:space="preserve">1.93078601360321</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84922575950623</t>
+    <t xml:space="preserve">1.84922564029694</t>
   </si>
   <si>
     <t xml:space="preserve">1.82413029670715</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85549914836884</t>
+    <t xml:space="preserve">1.85549938678741</t>
   </si>
   <si>
     <t xml:space="preserve">1.89627981185913</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93705999851227</t>
+    <t xml:space="preserve">1.93705987930298</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87432110309601</t>
+    <t xml:space="preserve">1.8743212223053</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94333374500275</t>
+    <t xml:space="preserve">1.94333362579346</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94490242004395</t>
+    <t xml:space="preserve">1.94490218162537</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9668607711792</t>
+    <t xml:space="preserve">1.96686089038849</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98411417007446</t>
+    <t xml:space="preserve">1.98411393165588</t>
   </si>
   <si>
     <t xml:space="preserve">2.06253743171692</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0531268119812</t>
+    <t xml:space="preserve">2.05312657356262</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05155801773071</t>
+    <t xml:space="preserve">2.05155825614929</t>
   </si>
   <si>
     <t xml:space="preserve">2.02332592010498</t>
@@ -398,25 +398,25 @@
     <t xml:space="preserve">2.03116798400879</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06096911430359</t>
+    <t xml:space="preserve">2.06096935272217</t>
   </si>
   <si>
     <t xml:space="preserve">2.09390687942505</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08606457710266</t>
+    <t xml:space="preserve">2.0860641002655</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15507745742798</t>
+    <t xml:space="preserve">2.15507698059082</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18801498413086</t>
+    <t xml:space="preserve">2.18801522254944</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19585728645325</t>
+    <t xml:space="preserve">2.19585704803467</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20213103294373</t>
+    <t xml:space="preserve">2.20213150978088</t>
   </si>
   <si>
     <t xml:space="preserve">2.23350048065186</t>
@@ -428,10 +428,10 @@
     <t xml:space="preserve">2.18017268180847</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16605687141418</t>
+    <t xml:space="preserve">2.16605663299561</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19428873062134</t>
+    <t xml:space="preserve">2.19428896903992</t>
   </si>
   <si>
     <t xml:space="preserve">2.17389893531799</t>
@@ -443,13 +443,13 @@
     <t xml:space="preserve">2.21938443183899</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21781611442566</t>
+    <t xml:space="preserve">2.21781587600708</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1911518573761</t>
+    <t xml:space="preserve">2.19115209579468</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12057113647461</t>
+    <t xml:space="preserve">2.12057089805603</t>
   </si>
   <si>
     <t xml:space="preserve">2.15350890159607</t>
@@ -458,40 +458,40 @@
     <t xml:space="preserve">2.11743402481079</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16291952133179</t>
+    <t xml:space="preserve">2.16291928291321</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10802268981934</t>
+    <t xml:space="preserve">2.10802316665649</t>
   </si>
   <si>
     <t xml:space="preserve">2.01548337936401</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04528403282166</t>
+    <t xml:space="preserve">2.04528427124023</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98568260669708</t>
+    <t xml:space="preserve">1.98568284511566</t>
   </si>
   <si>
     <t xml:space="preserve">2.07822251319885</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06724286079407</t>
+    <t xml:space="preserve">2.06724262237549</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12998151779175</t>
+    <t xml:space="preserve">2.12998175621033</t>
   </si>
   <si>
     <t xml:space="preserve">2.11586546897888</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05469489097595</t>
+    <t xml:space="preserve">2.05469512939453</t>
   </si>
   <si>
     <t xml:space="preserve">2.11429691314697</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05626368522644</t>
+    <t xml:space="preserve">2.05626344680786</t>
   </si>
   <si>
     <t xml:space="preserve">2.06410574913025</t>
@@ -506,34 +506,34 @@
     <t xml:space="preserve">2.0139148235321</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04842138290405</t>
+    <t xml:space="preserve">2.04842114448547</t>
   </si>
   <si>
     <t xml:space="preserve">2.16448783874512</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18487811088562</t>
+    <t xml:space="preserve">2.18487787246704</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26643872261047</t>
+    <t xml:space="preserve">2.26643848419189</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27271246910095</t>
+    <t xml:space="preserve">2.27271270751953</t>
   </si>
   <si>
     <t xml:space="preserve">2.2570276260376</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30721879005432</t>
+    <t xml:space="preserve">2.30721831321716</t>
   </si>
   <si>
     <t xml:space="preserve">2.23036408424377</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37152600288391</t>
+    <t xml:space="preserve">2.37152576446533</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35270428657532</t>
+    <t xml:space="preserve">2.35270404815674</t>
   </si>
   <si>
     <t xml:space="preserve">2.39191603660583</t>
@@ -548,55 +548,55 @@
     <t xml:space="preserve">2.37623119354248</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32917761802673</t>
+    <t xml:space="preserve">2.32917737960815</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24918532371521</t>
+    <t xml:space="preserve">2.24918580055237</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28839707374573</t>
+    <t xml:space="preserve">2.28839683532715</t>
   </si>
   <si>
     <t xml:space="preserve">2.33701968193054</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34486222267151</t>
+    <t xml:space="preserve">2.34486174583435</t>
   </si>
   <si>
     <t xml:space="preserve">2.34956741333008</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32604050636292</t>
+    <t xml:space="preserve">2.32604026794434</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30251359939575</t>
+    <t xml:space="preserve">2.30251336097717</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31192421913147</t>
+    <t xml:space="preserve">2.31192398071289</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25075387954712</t>
+    <t xml:space="preserve">2.25075364112854</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27428078651428</t>
+    <t xml:space="preserve">2.27428102493286</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43897032737732</t>
+    <t xml:space="preserve">2.43896985054016</t>
   </si>
   <si>
     <t xml:space="preserve">2.48445582389832</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4624969959259</t>
+    <t xml:space="preserve">2.46249747276306</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50798296928406</t>
+    <t xml:space="preserve">2.50798273086548</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48602414131165</t>
+    <t xml:space="preserve">2.48602437973022</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60993313789368</t>
+    <t xml:space="preserve">2.60993361473083</t>
   </si>
   <si>
     <t xml:space="preserve">2.66639828681946</t>
@@ -605,34 +605,34 @@
     <t xml:space="preserve">2.66326117515564</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66012406349182</t>
+    <t xml:space="preserve">2.6601243019104</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64287090301514</t>
+    <t xml:space="preserve">2.64287114143372</t>
   </si>
   <si>
     <t xml:space="preserve">2.65855574607849</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60209131240845</t>
+    <t xml:space="preserve">2.60209107398987</t>
   </si>
   <si>
     <t xml:space="preserve">2.55033159255981</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63816618919373</t>
+    <t xml:space="preserve">2.63816595077515</t>
   </si>
   <si>
     <t xml:space="preserve">2.58013224601746</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59581708908081</t>
+    <t xml:space="preserve">2.59581756591797</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58170104026794</t>
+    <t xml:space="preserve">2.58170127868652</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6036593914032</t>
+    <t xml:space="preserve">2.60365962982178</t>
   </si>
   <si>
     <t xml:space="preserve">2.61934423446655</t>
@@ -641,46 +641,46 @@
     <t xml:space="preserve">2.57542681694031</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57385873794556</t>
+    <t xml:space="preserve">2.57385849952698</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50955152511597</t>
+    <t xml:space="preserve">2.50955104827881</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58797454833984</t>
+    <t xml:space="preserve">2.58797478675842</t>
   </si>
   <si>
     <t xml:space="preserve">2.56444764137268</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61150169372559</t>
+    <t xml:space="preserve">2.61150193214417</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56915330886841</t>
+    <t xml:space="preserve">2.56915307044983</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63502883911133</t>
+    <t xml:space="preserve">2.63502860069275</t>
   </si>
   <si>
     <t xml:space="preserve">2.62561821937561</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62718629837036</t>
+    <t xml:space="preserve">2.62718653678894</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83422446250916</t>
+    <t xml:space="preserve">2.83422470092773</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79030752182007</t>
+    <t xml:space="preserve">2.79030728340149</t>
   </si>
   <si>
     <t xml:space="preserve">2.77619123458862</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78089666366577</t>
+    <t xml:space="preserve">2.78089642524719</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69149351119995</t>
+    <t xml:space="preserve">2.69149374961853</t>
   </si>
   <si>
     <t xml:space="preserve">2.78246545791626</t>
@@ -692,28 +692,28 @@
     <t xml:space="preserve">2.82324528694153</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68678855895996</t>
+    <t xml:space="preserve">2.68678832054138</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70090484619141</t>
+    <t xml:space="preserve">2.70090460777283</t>
   </si>
   <si>
     <t xml:space="preserve">2.80657124519348</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86433959007263</t>
+    <t xml:space="preserve">2.86433935165405</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81940865516663</t>
+    <t xml:space="preserve">2.81940841674805</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80817627906799</t>
+    <t xml:space="preserve">2.80817604064941</t>
   </si>
   <si>
     <t xml:space="preserve">2.88038635253906</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83385062217712</t>
+    <t xml:space="preserve">2.8338508605957</t>
   </si>
   <si>
     <t xml:space="preserve">2.74398922920227</t>
@@ -737,16 +737,16 @@
     <t xml:space="preserve">2.61722016334534</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60438251495361</t>
+    <t xml:space="preserve">2.60438275337219</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62524366378784</t>
+    <t xml:space="preserve">2.62524342536926</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64129018783569</t>
+    <t xml:space="preserve">2.64129042625427</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69584894180298</t>
+    <t xml:space="preserve">2.6958487033844</t>
   </si>
   <si>
     <t xml:space="preserve">2.75040793418884</t>
@@ -761,43 +761,43 @@
     <t xml:space="preserve">2.72633790969849</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74238443374634</t>
+    <t xml:space="preserve">2.74238419532776</t>
   </si>
   <si>
     <t xml:space="preserve">2.80015254020691</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78571057319641</t>
+    <t xml:space="preserve">2.78571033477783</t>
   </si>
   <si>
     <t xml:space="preserve">2.82422256469727</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78731513023376</t>
+    <t xml:space="preserve">2.78731536865234</t>
   </si>
   <si>
     <t xml:space="preserve">2.79373407363892</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80496668815613</t>
+    <t xml:space="preserve">2.80496644973755</t>
   </si>
   <si>
     <t xml:space="preserve">2.78410601615906</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77608275413513</t>
+    <t xml:space="preserve">2.77608251571655</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79533886909485</t>
+    <t xml:space="preserve">2.79533863067627</t>
   </si>
   <si>
     <t xml:space="preserve">2.82261800765991</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76003575325012</t>
+    <t xml:space="preserve">2.7600359916687</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77929186820984</t>
+    <t xml:space="preserve">2.77929210662842</t>
   </si>
   <si>
     <t xml:space="preserve">2.79854798316956</t>
@@ -809,7 +809,7 @@
     <t xml:space="preserve">2.80336213111877</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83545541763306</t>
+    <t xml:space="preserve">2.83545565605164</t>
   </si>
   <si>
     <t xml:space="preserve">2.84026956558228</t>
@@ -821,19 +821,19 @@
     <t xml:space="preserve">2.8113853931427</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81619930267334</t>
+    <t xml:space="preserve">2.81619954109192</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76324558258057</t>
+    <t xml:space="preserve">2.76324534416199</t>
   </si>
   <si>
     <t xml:space="preserve">2.71189594268799</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72473311424255</t>
+    <t xml:space="preserve">2.72473287582397</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7969434261322</t>
+    <t xml:space="preserve">2.79694318771362</t>
   </si>
   <si>
     <t xml:space="preserve">2.79052448272705</t>
@@ -842,28 +842,28 @@
     <t xml:space="preserve">2.76805925369263</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73115181922913</t>
+    <t xml:space="preserve">2.73115205764771</t>
   </si>
   <si>
     <t xml:space="preserve">2.7038722038269</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81459498405457</t>
+    <t xml:space="preserve">2.81459450721741</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82903695106506</t>
+    <t xml:space="preserve">2.82903671264648</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8434784412384</t>
+    <t xml:space="preserve">2.84347867965698</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77768707275391</t>
+    <t xml:space="preserve">2.77768731117249</t>
   </si>
   <si>
     <t xml:space="preserve">2.77126860618591</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88840937614441</t>
+    <t xml:space="preserve">2.88840961456299</t>
   </si>
   <si>
     <t xml:space="preserve">2.87236309051514</t>
@@ -875,13 +875,13 @@
     <t xml:space="preserve">2.92852663993835</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85952568054199</t>
+    <t xml:space="preserve">2.85952544212341</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90927028656006</t>
+    <t xml:space="preserve">2.90927004814148</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99913167953491</t>
+    <t xml:space="preserve">2.99913191795349</t>
   </si>
   <si>
     <t xml:space="preserve">2.96864318847656</t>
@@ -899,10 +899,10 @@
     <t xml:space="preserve">2.87557220458984</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7520124912262</t>
+    <t xml:space="preserve">2.75201225280762</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76164054870605</t>
+    <t xml:space="preserve">2.76164031028748</t>
   </si>
   <si>
     <t xml:space="preserve">2.78892016410828</t>
@@ -920,16 +920,16 @@
     <t xml:space="preserve">2.8482928276062</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82101321220398</t>
+    <t xml:space="preserve">2.82101345062256</t>
   </si>
   <si>
     <t xml:space="preserve">2.73436093330383</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81780409812927</t>
+    <t xml:space="preserve">2.81780433654785</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76484990119934</t>
+    <t xml:space="preserve">2.76485013961792</t>
   </si>
   <si>
     <t xml:space="preserve">2.74077987670898</t>
@@ -938,7 +938,7 @@
     <t xml:space="preserve">2.79212927818298</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66375541687012</t>
+    <t xml:space="preserve">2.6637556552887</t>
   </si>
   <si>
     <t xml:space="preserve">2.60759210586548</t>
@@ -947,10 +947,10 @@
     <t xml:space="preserve">2.55142855644226</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56747531890869</t>
+    <t xml:space="preserve">2.56747508049011</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59956860542297</t>
+    <t xml:space="preserve">2.59956884384155</t>
   </si>
   <si>
     <t xml:space="preserve">2.55945205688477</t>
@@ -959,10 +959,10 @@
     <t xml:space="preserve">2.50328826904297</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45514822006226</t>
+    <t xml:space="preserve">2.45514798164368</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47921824455261</t>
+    <t xml:space="preserve">2.47921776771545</t>
   </si>
   <si>
     <t xml:space="preserve">2.47119474411011</t>
@@ -974,10 +974,10 @@
     <t xml:space="preserve">2.46317148208618</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48724150657654</t>
+    <t xml:space="preserve">2.48724174499512</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49526500701904</t>
+    <t xml:space="preserve">2.49526476860046</t>
   </si>
   <si>
     <t xml:space="preserve">2.5273585319519</t>
@@ -986,13 +986,13 @@
     <t xml:space="preserve">2.5835223197937</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65573215484619</t>
+    <t xml:space="preserve">2.65573263168335</t>
   </si>
   <si>
     <t xml:space="preserve">2.91247987747192</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8200249671936</t>
+    <t xml:space="preserve">2.82002472877502</t>
   </si>
   <si>
     <t xml:space="preserve">2.80358147621155</t>
@@ -1001,43 +1001,43 @@
     <t xml:space="preserve">2.86935472488403</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8446900844574</t>
+    <t xml:space="preserve">2.84468984603882</t>
   </si>
   <si>
     <t xml:space="preserve">2.85291147232056</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81180357933044</t>
+    <t xml:space="preserve">2.81180334091187</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72136521339417</t>
+    <t xml:space="preserve">2.72136545181274</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68025684356689</t>
+    <t xml:space="preserve">2.68025708198547</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69670009613037</t>
+    <t xml:space="preserve">2.69670033454895</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64737033843994</t>
+    <t xml:space="preserve">2.64737057685852</t>
   </si>
   <si>
     <t xml:space="preserve">2.65559196472168</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66381359100342</t>
+    <t xml:space="preserve">2.663813829422</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63092708587646</t>
+    <t xml:space="preserve">2.63092684745789</t>
   </si>
   <si>
     <t xml:space="preserve">2.6391487121582</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55693221092224</t>
+    <t xml:space="preserve">2.55693197250366</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59804058074951</t>
+    <t xml:space="preserve">2.59804034233093</t>
   </si>
   <si>
     <t xml:space="preserve">2.5487105846405</t>
@@ -1064,10 +1064,10 @@
     <t xml:space="preserve">2.62270545959473</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51582407951355</t>
+    <t xml:space="preserve">2.51582384109497</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57337522506714</t>
+    <t xml:space="preserve">2.57337546348572</t>
   </si>
   <si>
     <t xml:space="preserve">2.56515383720398</t>
@@ -1076,10 +1076,10 @@
     <t xml:space="preserve">2.53226709365845</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47471570968628</t>
+    <t xml:space="preserve">2.4747154712677</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4829375743866</t>
+    <t xml:space="preserve">2.48293733596802</t>
   </si>
   <si>
     <t xml:space="preserve">2.45005083084106</t>
@@ -1091,7 +1091,7 @@
     <t xml:space="preserve">2.42538595199585</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43360757827759</t>
+    <t xml:space="preserve">2.43360733985901</t>
   </si>
   <si>
     <t xml:space="preserve">2.49115896224976</t>
@@ -1100,43 +1100,43 @@
     <t xml:space="preserve">2.50760221481323</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54048871994019</t>
+    <t xml:space="preserve">2.54048848152161</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67203497886658</t>
+    <t xml:space="preserve">2.67203521728516</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68847870826721</t>
+    <t xml:space="preserve">2.68847846984863</t>
   </si>
   <si>
     <t xml:space="preserve">2.70492172241211</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71314334869385</t>
+    <t xml:space="preserve">2.71314358711243</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75425148010254</t>
+    <t xml:space="preserve">2.75425171852112</t>
   </si>
   <si>
     <t xml:space="preserve">2.78713822364807</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77069497108459</t>
+    <t xml:space="preserve">2.77069473266602</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72958660125732</t>
+    <t xml:space="preserve">2.7295868396759</t>
   </si>
   <si>
     <t xml:space="preserve">2.74603009223938</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77891659736633</t>
+    <t xml:space="preserve">2.77891683578491</t>
   </si>
   <si>
     <t xml:space="preserve">2.79536008834839</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87757658958435</t>
+    <t xml:space="preserve">2.87757635116577</t>
   </si>
   <si>
     <t xml:space="preserve">2.91868472099304</t>
@@ -1148,22 +1148,22 @@
     <t xml:space="preserve">2.86113309860229</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90224146842957</t>
+    <t xml:space="preserve">2.90224123001099</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88579797744751</t>
+    <t xml:space="preserve">2.88579821586609</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8364679813385</t>
+    <t xml:space="preserve">2.83646821975708</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94334959983826</t>
+    <t xml:space="preserve">2.94334983825684</t>
   </si>
   <si>
     <t xml:space="preserve">2.82824659347534</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9269061088562</t>
+    <t xml:space="preserve">2.92690634727478</t>
   </si>
   <si>
     <t xml:space="preserve">2.77809453010559</t>
@@ -1178,7 +1178,7 @@
     <t xml:space="preserve">2.88853859901428</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88004279136658</t>
+    <t xml:space="preserve">2.88004302978516</t>
   </si>
   <si>
     <t xml:space="preserve">2.92252135276794</t>
@@ -1187,28 +1187,28 @@
     <t xml:space="preserve">2.90553021430969</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87154698371887</t>
+    <t xml:space="preserve">2.87154722213745</t>
   </si>
   <si>
     <t xml:space="preserve">2.85455560684204</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91402578353882</t>
+    <t xml:space="preserve">2.91402554512024</t>
   </si>
   <si>
     <t xml:space="preserve">2.93101692199707</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94800853729248</t>
+    <t xml:space="preserve">2.9480082988739</t>
   </si>
   <si>
     <t xml:space="preserve">2.89703416824341</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93951296806335</t>
+    <t xml:space="preserve">2.93951272964478</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98199105262756</t>
+    <t xml:space="preserve">2.98199129104614</t>
   </si>
   <si>
     <t xml:space="preserve">2.79508566856384</t>
@@ -1217,13 +1217,13 @@
     <t xml:space="preserve">2.78659009933472</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7611026763916</t>
+    <t xml:space="preserve">2.76110291481018</t>
   </si>
   <si>
     <t xml:space="preserve">2.76959872245789</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81207728385925</t>
+    <t xml:space="preserve">2.81207704544067</t>
   </si>
   <si>
     <t xml:space="preserve">2.83756422996521</t>
@@ -1235,10 +1235,10 @@
     <t xml:space="preserve">2.62517166137695</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6761462688446</t>
+    <t xml:space="preserve">2.67614603042603</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61667585372925</t>
+    <t xml:space="preserve">2.61667609214783</t>
   </si>
   <si>
     <t xml:space="preserve">2.55720615386963</t>
@@ -1247,7 +1247,7 @@
     <t xml:space="preserve">2.54871034622192</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51472783088684</t>
+    <t xml:space="preserve">2.51472759246826</t>
   </si>
   <si>
     <t xml:space="preserve">2.49773645401001</t>
@@ -1271,7 +1271,7 @@
     <t xml:space="preserve">2.56570196151733</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59118890762329</t>
+    <t xml:space="preserve">2.59118866920471</t>
   </si>
   <si>
     <t xml:space="preserve">2.47224903106689</t>
@@ -1283,7 +1283,7 @@
     <t xml:space="preserve">2.599684715271</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52322340011597</t>
+    <t xml:space="preserve">2.52322363853455</t>
   </si>
   <si>
     <t xml:space="preserve">2.57419753074646</t>
@@ -1292,13 +1292,13 @@
     <t xml:space="preserve">3.075443983078</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0074782371521</t>
+    <t xml:space="preserve">3.00747847557068</t>
   </si>
   <si>
     <t xml:space="preserve">2.99048686027527</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96499967575073</t>
+    <t xml:space="preserve">2.96499991416931</t>
   </si>
   <si>
     <t xml:space="preserve">2.97349572181702</t>
@@ -1307,7 +1307,7 @@
     <t xml:space="preserve">2.95650410652161</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84605979919434</t>
+    <t xml:space="preserve">2.84606003761292</t>
   </si>
   <si>
     <t xml:space="preserve">2.75260734558105</t>
@@ -1316,7 +1316,7 @@
     <t xml:space="preserve">2.6676504611969</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65915441513062</t>
+    <t xml:space="preserve">2.65915465354919</t>
   </si>
   <si>
     <t xml:space="preserve">2.31083083152771</t>
@@ -1328,13 +1328,13 @@
     <t xml:space="preserve">2.34481358528137</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45525813102722</t>
+    <t xml:space="preserve">2.45525789260864</t>
   </si>
   <si>
     <t xml:space="preserve">2.4892406463623</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65065884590149</t>
+    <t xml:space="preserve">2.65065860748291</t>
   </si>
   <si>
     <t xml:space="preserve">2.64216327667236</t>
@@ -1343,13 +1343,13 @@
     <t xml:space="preserve">2.71012878417969</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69313740730286</t>
+    <t xml:space="preserve">2.69313716888428</t>
   </si>
   <si>
     <t xml:space="preserve">2.71862459182739</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74411153793335</t>
+    <t xml:space="preserve">2.74411177635193</t>
   </si>
   <si>
     <t xml:space="preserve">2.68464183807373</t>
@@ -1364,13 +1364,13 @@
     <t xml:space="preserve">2.44676208496094</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37879657745361</t>
+    <t xml:space="preserve">2.37879633903503</t>
   </si>
   <si>
     <t xml:space="preserve">2.42977046966553</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37030076980591</t>
+    <t xml:space="preserve">2.37030053138733</t>
   </si>
   <si>
     <t xml:space="preserve">2.31932663917542</t>
@@ -1379,25 +1379,25 @@
     <t xml:space="preserve">2.27684807777405</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26835250854492</t>
+    <t xml:space="preserve">2.26835227012634</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30233502388</t>
+    <t xml:space="preserve">2.30233526229858</t>
   </si>
   <si>
     <t xml:space="preserve">2.33631801605225</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39578771591187</t>
+    <t xml:space="preserve">2.39578795433044</t>
   </si>
   <si>
     <t xml:space="preserve">2.72712016105652</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99898266792297</t>
+    <t xml:space="preserve">2.99898242950439</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03296542167664</t>
+    <t xml:space="preserve">3.03296518325806</t>
   </si>
   <si>
     <t xml:space="preserve">3.0159740447998</t>
@@ -1418,7 +1418,7 @@
     <t xml:space="preserve">3.09243535995483</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16040110588074</t>
+    <t xml:space="preserve">3.16040086746216</t>
   </si>
   <si>
     <t xml:space="preserve">3.21137523651123</t>
@@ -1439,7 +1439,7 @@
     <t xml:space="preserve">3.17739248275757</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14340949058533</t>
+    <t xml:space="preserve">3.14340972900391</t>
   </si>
   <si>
     <t xml:space="preserve">3.10942697525024</t>
@@ -1448,7 +1448,7 @@
     <t xml:space="preserve">3.27934050559998</t>
   </si>
   <si>
-    <t xml:space="preserve">3.48323750495911</t>
+    <t xml:space="preserve">3.48323726654053</t>
   </si>
   <si>
     <t xml:space="preserve">3.39828062057495</t>
@@ -1457,7 +1457,7 @@
     <t xml:space="preserve">3.46624612808228</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36429762840271</t>
+    <t xml:space="preserve">3.36429786682129</t>
   </si>
   <si>
     <t xml:space="preserve">3.34730672836304</t>
@@ -1487,10 +1487,10 @@
     <t xml:space="preserve">3.02393102645874</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10281610488892</t>
+    <t xml:space="preserve">3.1028163433075</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13787627220154</t>
+    <t xml:space="preserve">3.13787603378296</t>
   </si>
   <si>
     <t xml:space="preserve">2.98010611534119</t>
@@ -1502,7 +1502,7 @@
     <t xml:space="preserve">3.07652115821838</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06775617599487</t>
+    <t xml:space="preserve">3.06775641441345</t>
   </si>
   <si>
     <t xml:space="preserve">3.00640106201172</t>
@@ -1511,7 +1511,7 @@
     <t xml:space="preserve">2.9888710975647</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89245581626892</t>
+    <t xml:space="preserve">2.89245557785034</t>
   </si>
   <si>
     <t xml:space="preserve">2.92751574516296</t>
@@ -1523,13 +1523,13 @@
     <t xml:space="preserve">2.96257615089417</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86616086959839</t>
+    <t xml:space="preserve">2.86616063117981</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91875076293945</t>
+    <t xml:space="preserve">2.91875100135803</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80480551719666</t>
+    <t xml:space="preserve">2.80480575561523</t>
   </si>
   <si>
     <t xml:space="preserve">2.82233572006226</t>
@@ -1547,22 +1547,22 @@
     <t xml:space="preserve">2.93628096580505</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03269624710083</t>
+    <t xml:space="preserve">3.03269600868225</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90122079849243</t>
+    <t xml:space="preserve">2.90122103691101</t>
   </si>
   <si>
     <t xml:space="preserve">2.88369083404541</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8749258518219</t>
+    <t xml:space="preserve">2.87492561340332</t>
   </si>
   <si>
     <t xml:space="preserve">2.81357073783875</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83986568450928</t>
+    <t xml:space="preserve">2.83986592292786</t>
   </si>
   <si>
     <t xml:space="preserve">2.68209528923035</t>
@@ -1589,10 +1589,10 @@
     <t xml:space="preserve">2.79604077339172</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84863090515137</t>
+    <t xml:space="preserve">2.84863066673279</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08528614044189</t>
+    <t xml:space="preserve">3.08528637886047</t>
   </si>
   <si>
     <t xml:space="preserve">2.76098036766052</t>
@@ -1683,6 +1683,9 @@
   </si>
   <si>
     <t xml:space="preserve">2.85962271690369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80480551719666</t>
   </si>
   <si>
     <t xml:space="preserve">2.89616751670837</t>
@@ -56949,7 +56952,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G2103" t="s">
-        <v>505</v>
+        <v>557</v>
       </c>
       <c r="H2103" t="s">
         <v>9</v>
@@ -56975,7 +56978,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G2104" t="s">
-        <v>505</v>
+        <v>557</v>
       </c>
       <c r="H2104" t="s">
         <v>9</v>
@@ -57183,7 +57186,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G2112" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="H2112" t="s">
         <v>9</v>
@@ -57313,7 +57316,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G2117" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="H2117" t="s">
         <v>9</v>
@@ -57339,7 +57342,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G2118" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="H2118" t="s">
         <v>9</v>
@@ -57365,7 +57368,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G2119" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="H2119" t="s">
         <v>9</v>
@@ -57417,7 +57420,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G2121" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="H2121" t="s">
         <v>9</v>
@@ -57443,7 +57446,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G2122" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="H2122" t="s">
         <v>9</v>
@@ -57495,7 +57498,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G2124" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="H2124" t="s">
         <v>9</v>
@@ -57521,7 +57524,7 @@
         <v>3.25</v>
       </c>
       <c r="G2125" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="H2125" t="s">
         <v>9</v>
@@ -57547,7 +57550,7 @@
         <v>3.25</v>
       </c>
       <c r="G2126" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="H2126" t="s">
         <v>9</v>
@@ -57573,7 +57576,7 @@
         <v>3.25</v>
       </c>
       <c r="G2127" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="H2127" t="s">
         <v>9</v>
@@ -57599,7 +57602,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G2128" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="H2128" t="s">
         <v>9</v>
@@ -57625,7 +57628,7 @@
         <v>3.25</v>
       </c>
       <c r="G2129" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="H2129" t="s">
         <v>9</v>
@@ -57729,7 +57732,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G2133" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="H2133" t="s">
         <v>9</v>
@@ -57755,7 +57758,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G2134" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="H2134" t="s">
         <v>9</v>
@@ -57781,7 +57784,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G2135" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="H2135" t="s">
         <v>9</v>
@@ -57807,7 +57810,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G2136" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="H2136" t="s">
         <v>9</v>
@@ -57833,7 +57836,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G2137" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="H2137" t="s">
         <v>9</v>
@@ -57859,7 +57862,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G2138" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="H2138" t="s">
         <v>9</v>
@@ -57885,7 +57888,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G2139" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="H2139" t="s">
         <v>9</v>
@@ -57911,7 +57914,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2140" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="H2140" t="s">
         <v>9</v>
@@ -57937,7 +57940,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G2141" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="H2141" t="s">
         <v>9</v>
@@ -57963,7 +57966,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G2142" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="H2142" t="s">
         <v>9</v>
@@ -57989,7 +57992,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G2143" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="H2143" t="s">
         <v>9</v>
@@ -58015,7 +58018,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G2144" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="H2144" t="s">
         <v>9</v>
@@ -58041,7 +58044,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G2145" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="H2145" t="s">
         <v>9</v>
@@ -58067,7 +58070,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G2146" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="H2146" t="s">
         <v>9</v>
@@ -58093,7 +58096,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G2147" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="H2147" t="s">
         <v>9</v>
@@ -58119,7 +58122,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G2148" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="H2148" t="s">
         <v>9</v>
@@ -58145,7 +58148,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G2149" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="H2149" t="s">
         <v>9</v>
@@ -58171,7 +58174,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G2150" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="H2150" t="s">
         <v>9</v>
@@ -58197,7 +58200,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G2151" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="H2151" t="s">
         <v>9</v>
@@ -58223,7 +58226,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G2152" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="H2152" t="s">
         <v>9</v>
@@ -58249,7 +58252,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G2153" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="H2153" t="s">
         <v>9</v>
@@ -58275,7 +58278,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G2154" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="H2154" t="s">
         <v>9</v>
@@ -58301,7 +58304,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G2155" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="H2155" t="s">
         <v>9</v>
@@ -58327,7 +58330,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G2156" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="H2156" t="s">
         <v>9</v>
@@ -58353,7 +58356,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G2157" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="H2157" t="s">
         <v>9</v>
@@ -58379,7 +58382,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G2158" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="H2158" t="s">
         <v>9</v>
@@ -58405,7 +58408,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G2159" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="H2159" t="s">
         <v>9</v>
@@ -58431,7 +58434,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G2160" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="H2160" t="s">
         <v>9</v>
@@ -58457,7 +58460,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G2161" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="H2161" t="s">
         <v>9</v>
@@ -58483,7 +58486,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G2162" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="H2162" t="s">
         <v>9</v>
@@ -58509,7 +58512,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G2163" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="H2163" t="s">
         <v>9</v>
@@ -58535,7 +58538,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G2164" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="H2164" t="s">
         <v>9</v>
@@ -58561,7 +58564,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G2165" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="H2165" t="s">
         <v>9</v>
@@ -58587,7 +58590,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G2166" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="H2166" t="s">
         <v>9</v>
@@ -58613,7 +58616,7 @@
         <v>3.25</v>
       </c>
       <c r="G2167" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="H2167" t="s">
         <v>9</v>
@@ -58639,7 +58642,7 @@
         <v>3.25</v>
       </c>
       <c r="G2168" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="H2168" t="s">
         <v>9</v>
@@ -58665,7 +58668,7 @@
         <v>3.25</v>
       </c>
       <c r="G2169" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="H2169" t="s">
         <v>9</v>
@@ -58691,7 +58694,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G2170" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="H2170" t="s">
         <v>9</v>
@@ -58717,7 +58720,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G2171" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="H2171" t="s">
         <v>9</v>
@@ -58743,7 +58746,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G2172" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="H2172" t="s">
         <v>9</v>
@@ -58769,7 +58772,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G2173" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="H2173" t="s">
         <v>9</v>
@@ -58795,7 +58798,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G2174" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="H2174" t="s">
         <v>9</v>
@@ -58821,7 +58824,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2175" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="H2175" t="s">
         <v>9</v>
@@ -58847,7 +58850,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2176" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="H2176" t="s">
         <v>9</v>
@@ -58873,7 +58876,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2177" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="H2177" t="s">
         <v>9</v>
@@ -58899,7 +58902,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G2178" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="H2178" t="s">
         <v>9</v>
@@ -58925,7 +58928,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G2179" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="H2179" t="s">
         <v>9</v>
@@ -58951,7 +58954,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G2180" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="H2180" t="s">
         <v>9</v>
@@ -58977,7 +58980,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G2181" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="H2181" t="s">
         <v>9</v>
@@ -59003,7 +59006,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2182" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="H2182" t="s">
         <v>9</v>
@@ -59029,7 +59032,7 @@
         <v>3.25</v>
       </c>
       <c r="G2183" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="H2183" t="s">
         <v>9</v>
@@ -59055,7 +59058,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G2184" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="H2184" t="s">
         <v>9</v>
@@ -59081,7 +59084,7 @@
         <v>3.25</v>
       </c>
       <c r="G2185" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="H2185" t="s">
         <v>9</v>
@@ -59107,7 +59110,7 @@
         <v>3.25</v>
       </c>
       <c r="G2186" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="H2186" t="s">
         <v>9</v>
@@ -59133,7 +59136,7 @@
         <v>3.25</v>
       </c>
       <c r="G2187" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="H2187" t="s">
         <v>9</v>
@@ -59159,7 +59162,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G2188" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="H2188" t="s">
         <v>9</v>
@@ -59185,7 +59188,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G2189" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="H2189" t="s">
         <v>9</v>
@@ -59211,7 +59214,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G2190" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="H2190" t="s">
         <v>9</v>
@@ -59237,7 +59240,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G2191" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="H2191" t="s">
         <v>9</v>
@@ -59263,7 +59266,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G2192" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="H2192" t="s">
         <v>9</v>
@@ -59289,7 +59292,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G2193" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="H2193" t="s">
         <v>9</v>
@@ -59315,7 +59318,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G2194" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="H2194" t="s">
         <v>9</v>
@@ -59341,7 +59344,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G2195" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="H2195" t="s">
         <v>9</v>
@@ -59367,7 +59370,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G2196" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="H2196" t="s">
         <v>9</v>
@@ -59393,7 +59396,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2197" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="H2197" t="s">
         <v>9</v>
@@ -59419,7 +59422,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G2198" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="H2198" t="s">
         <v>9</v>
@@ -59445,7 +59448,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G2199" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="H2199" t="s">
         <v>9</v>
@@ -59471,7 +59474,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G2200" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="H2200" t="s">
         <v>9</v>
@@ -59497,7 +59500,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G2201" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="H2201" t="s">
         <v>9</v>
@@ -59523,7 +59526,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G2202" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="H2202" t="s">
         <v>9</v>
@@ -59549,7 +59552,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G2203" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="H2203" t="s">
         <v>9</v>
@@ -59575,7 +59578,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G2204" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="H2204" t="s">
         <v>9</v>
@@ -59601,7 +59604,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G2205" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="H2205" t="s">
         <v>9</v>
@@ -59627,7 +59630,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2206" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="H2206" t="s">
         <v>9</v>
@@ -59653,7 +59656,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G2207" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="H2207" t="s">
         <v>9</v>
@@ -59679,7 +59682,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G2208" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="H2208" t="s">
         <v>9</v>
@@ -59705,7 +59708,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G2209" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="H2209" t="s">
         <v>9</v>
@@ -59731,7 +59734,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G2210" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="H2210" t="s">
         <v>9</v>
@@ -59757,7 +59760,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G2211" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="H2211" t="s">
         <v>9</v>
@@ -59783,7 +59786,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G2212" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="H2212" t="s">
         <v>9</v>
@@ -59809,7 +59812,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G2213" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="H2213" t="s">
         <v>9</v>
@@ -59835,7 +59838,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G2214" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="H2214" t="s">
         <v>9</v>
@@ -59861,7 +59864,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G2215" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="H2215" t="s">
         <v>9</v>
@@ -59887,7 +59890,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G2216" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="H2216" t="s">
         <v>9</v>
@@ -59913,7 +59916,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G2217" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="H2217" t="s">
         <v>9</v>
@@ -59939,7 +59942,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G2218" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="H2218" t="s">
         <v>9</v>
@@ -59965,7 +59968,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G2219" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="H2219" t="s">
         <v>9</v>
@@ -59991,7 +59994,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G2220" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="H2220" t="s">
         <v>9</v>
@@ -60017,7 +60020,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G2221" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="H2221" t="s">
         <v>9</v>
@@ -60043,7 +60046,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G2222" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="H2222" t="s">
         <v>9</v>
@@ -60069,7 +60072,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G2223" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="H2223" t="s">
         <v>9</v>
@@ -60095,7 +60098,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G2224" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="H2224" t="s">
         <v>9</v>
@@ -60121,7 +60124,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G2225" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="H2225" t="s">
         <v>9</v>
@@ -60147,7 +60150,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G2226" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="H2226" t="s">
         <v>9</v>
@@ -60173,7 +60176,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2227" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="H2227" t="s">
         <v>9</v>
@@ -60199,7 +60202,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G2228" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="H2228" t="s">
         <v>9</v>
@@ -60225,7 +60228,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G2229" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="H2229" t="s">
         <v>9</v>
@@ -60251,7 +60254,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G2230" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="H2230" t="s">
         <v>9</v>
@@ -60277,7 +60280,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G2231" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="H2231" t="s">
         <v>9</v>
@@ -60303,7 +60306,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G2232" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="H2232" t="s">
         <v>9</v>
@@ -60329,7 +60332,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G2233" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="H2233" t="s">
         <v>9</v>
@@ -60355,7 +60358,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G2234" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="H2234" t="s">
         <v>9</v>
@@ -60381,7 +60384,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G2235" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="H2235" t="s">
         <v>9</v>
@@ -60407,7 +60410,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G2236" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="H2236" t="s">
         <v>9</v>
@@ -60433,7 +60436,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G2237" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="H2237" t="s">
         <v>9</v>
@@ -60459,7 +60462,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G2238" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="H2238" t="s">
         <v>9</v>
@@ -60485,7 +60488,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G2239" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="H2239" t="s">
         <v>9</v>
@@ -60511,7 +60514,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G2240" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="H2240" t="s">
         <v>9</v>
@@ -60537,7 +60540,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G2241" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="H2241" t="s">
         <v>9</v>
@@ -60563,7 +60566,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G2242" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="H2242" t="s">
         <v>9</v>
@@ -60589,7 +60592,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G2243" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="H2243" t="s">
         <v>9</v>
@@ -60615,7 +60618,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G2244" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="H2244" t="s">
         <v>9</v>
@@ -60641,7 +60644,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G2245" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="H2245" t="s">
         <v>9</v>
@@ -60667,7 +60670,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G2246" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="H2246" t="s">
         <v>9</v>
@@ -60693,7 +60696,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G2247" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="H2247" t="s">
         <v>9</v>
@@ -60719,7 +60722,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G2248" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="H2248" t="s">
         <v>9</v>
@@ -60745,7 +60748,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G2249" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="H2249" t="s">
         <v>9</v>
@@ -60771,7 +60774,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G2250" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="H2250" t="s">
         <v>9</v>
@@ -60797,7 +60800,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G2251" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="H2251" t="s">
         <v>9</v>
@@ -60823,7 +60826,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G2252" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="H2252" t="s">
         <v>9</v>
@@ -60849,7 +60852,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G2253" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="H2253" t="s">
         <v>9</v>
@@ -60875,7 +60878,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G2254" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="H2254" t="s">
         <v>9</v>
@@ -60901,7 +60904,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G2255" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="H2255" t="s">
         <v>9</v>
@@ -60927,7 +60930,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G2256" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="H2256" t="s">
         <v>9</v>
@@ -60953,7 +60956,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G2257" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="H2257" t="s">
         <v>9</v>
@@ -60979,7 +60982,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G2258" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="H2258" t="s">
         <v>9</v>
@@ -61005,7 +61008,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G2259" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="H2259" t="s">
         <v>9</v>
@@ -61031,7 +61034,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G2260" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="H2260" t="s">
         <v>9</v>
@@ -61057,7 +61060,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G2261" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="H2261" t="s">
         <v>9</v>
@@ -61083,7 +61086,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G2262" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="H2262" t="s">
         <v>9</v>
@@ -61109,7 +61112,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G2263" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="H2263" t="s">
         <v>9</v>
@@ -61135,7 +61138,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G2264" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="H2264" t="s">
         <v>9</v>
@@ -61161,7 +61164,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G2265" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="H2265" t="s">
         <v>9</v>
@@ -61187,7 +61190,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G2266" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="H2266" t="s">
         <v>9</v>
@@ -61213,7 +61216,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G2267" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="H2267" t="s">
         <v>9</v>
@@ -61239,7 +61242,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G2268" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="H2268" t="s">
         <v>9</v>
@@ -61265,7 +61268,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G2269" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="H2269" t="s">
         <v>9</v>
@@ -61291,7 +61294,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G2270" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="H2270" t="s">
         <v>9</v>
@@ -61317,7 +61320,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G2271" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="H2271" t="s">
         <v>9</v>
@@ -61343,7 +61346,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G2272" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="H2272" t="s">
         <v>9</v>
@@ -61369,7 +61372,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G2273" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="H2273" t="s">
         <v>9</v>
@@ -61395,7 +61398,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G2274" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="H2274" t="s">
         <v>9</v>
@@ -61421,7 +61424,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G2275" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="H2275" t="s">
         <v>9</v>
@@ -61447,7 +61450,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G2276" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="H2276" t="s">
         <v>9</v>
@@ -61473,7 +61476,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G2277" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="H2277" t="s">
         <v>9</v>
@@ -61499,7 +61502,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G2278" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="H2278" t="s">
         <v>9</v>
@@ -61525,7 +61528,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G2279" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="H2279" t="s">
         <v>9</v>
@@ -61551,7 +61554,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G2280" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="H2280" t="s">
         <v>9</v>
@@ -61577,7 +61580,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G2281" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="H2281" t="s">
         <v>9</v>
@@ -61603,7 +61606,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G2282" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="H2282" t="s">
         <v>9</v>
@@ -61629,7 +61632,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G2283" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="H2283" t="s">
         <v>9</v>
@@ -61655,7 +61658,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G2284" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="H2284" t="s">
         <v>9</v>
@@ -61681,7 +61684,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G2285" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="H2285" t="s">
         <v>9</v>
@@ -61707,7 +61710,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G2286" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="H2286" t="s">
         <v>9</v>
@@ -61733,7 +61736,7 @@
         <v>3.25</v>
       </c>
       <c r="G2287" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="H2287" t="s">
         <v>9</v>
@@ -61759,7 +61762,7 @@
         <v>3.25</v>
       </c>
       <c r="G2288" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="H2288" t="s">
         <v>9</v>
@@ -61785,7 +61788,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G2289" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="H2289" t="s">
         <v>9</v>
@@ -61811,7 +61814,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G2290" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="H2290" t="s">
         <v>9</v>
@@ -61837,7 +61840,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G2291" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="H2291" t="s">
         <v>9</v>
@@ -61863,7 +61866,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G2292" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="H2292" t="s">
         <v>9</v>
@@ -61889,7 +61892,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G2293" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="H2293" t="s">
         <v>9</v>
@@ -61915,7 +61918,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G2294" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="H2294" t="s">
         <v>9</v>
@@ -61941,7 +61944,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G2295" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="H2295" t="s">
         <v>9</v>
@@ -61967,7 +61970,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G2296" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="H2296" t="s">
         <v>9</v>
@@ -61993,7 +61996,7 @@
         <v>3.25</v>
       </c>
       <c r="G2297" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="H2297" t="s">
         <v>9</v>
@@ -62019,7 +62022,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G2298" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="H2298" t="s">
         <v>9</v>
@@ -62045,7 +62048,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G2299" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="H2299" t="s">
         <v>9</v>
@@ -62071,7 +62074,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2300" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="H2300" t="s">
         <v>9</v>
@@ -62097,7 +62100,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G2301" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="H2301" t="s">
         <v>9</v>
@@ -62123,7 +62126,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G2302" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="H2302" t="s">
         <v>9</v>
@@ -62149,7 +62152,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G2303" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="H2303" t="s">
         <v>9</v>
@@ -62175,7 +62178,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G2304" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="H2304" t="s">
         <v>9</v>
@@ -62201,7 +62204,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G2305" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="H2305" t="s">
         <v>9</v>
@@ -62227,7 +62230,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G2306" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="H2306" t="s">
         <v>9</v>
@@ -62253,7 +62256,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G2307" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="H2307" t="s">
         <v>9</v>
@@ -62279,7 +62282,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G2308" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="H2308" t="s">
         <v>9</v>
@@ -62305,7 +62308,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G2309" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="H2309" t="s">
         <v>9</v>
@@ -62331,7 +62334,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G2310" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="H2310" t="s">
         <v>9</v>
@@ -62357,7 +62360,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2311" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="H2311" t="s">
         <v>9</v>
@@ -62383,7 +62386,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2312" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="H2312" t="s">
         <v>9</v>
@@ -62409,7 +62412,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G2313" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="H2313" t="s">
         <v>9</v>
@@ -62435,7 +62438,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G2314" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="H2314" t="s">
         <v>9</v>
@@ -62461,7 +62464,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G2315" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="H2315" t="s">
         <v>9</v>
@@ -62487,7 +62490,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G2316" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="H2316" t="s">
         <v>9</v>
@@ -62513,7 +62516,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G2317" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="H2317" t="s">
         <v>9</v>
@@ -62539,7 +62542,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G2318" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="H2318" t="s">
         <v>9</v>
@@ -62591,7 +62594,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G2320" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="H2320" t="s">
         <v>9</v>
@@ -62617,7 +62620,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G2321" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="H2321" t="s">
         <v>9</v>
@@ -62643,7 +62646,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G2322" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="H2322" t="s">
         <v>9</v>
@@ -62669,7 +62672,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2323" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="H2323" t="s">
         <v>9</v>
@@ -62695,7 +62698,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2324" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="H2324" t="s">
         <v>9</v>
@@ -62721,7 +62724,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2325" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="H2325" t="s">
         <v>9</v>
@@ -62747,7 +62750,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G2326" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="H2326" t="s">
         <v>9</v>
@@ -62773,7 +62776,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2327" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="H2327" t="s">
         <v>9</v>
@@ -62799,7 +62802,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G2328" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="H2328" t="s">
         <v>9</v>
@@ -62825,7 +62828,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G2329" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="H2329" t="s">
         <v>9</v>
@@ -62851,7 +62854,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G2330" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="H2330" t="s">
         <v>9</v>
@@ -62877,7 +62880,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G2331" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="H2331" t="s">
         <v>9</v>
@@ -62903,7 +62906,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G2332" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="H2332" t="s">
         <v>9</v>
@@ -62929,7 +62932,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G2333" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="H2333" t="s">
         <v>9</v>
@@ -62955,7 +62958,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G2334" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="H2334" t="s">
         <v>9</v>
@@ -62981,7 +62984,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G2335" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="H2335" t="s">
         <v>9</v>
@@ -63007,7 +63010,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G2336" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="H2336" t="s">
         <v>9</v>
@@ -63033,7 +63036,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G2337" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="H2337" t="s">
         <v>9</v>
@@ -63059,7 +63062,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G2338" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="H2338" t="s">
         <v>9</v>
@@ -63085,7 +63088,7 @@
         <v>3.25</v>
       </c>
       <c r="G2339" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="H2339" t="s">
         <v>9</v>
@@ -63111,7 +63114,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G2340" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="H2340" t="s">
         <v>9</v>
@@ -63137,7 +63140,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G2341" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="H2341" t="s">
         <v>9</v>
@@ -63163,7 +63166,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G2342" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="H2342" t="s">
         <v>9</v>
@@ -63189,7 +63192,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G2343" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="H2343" t="s">
         <v>9</v>
@@ -63215,7 +63218,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G2344" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="H2344" t="s">
         <v>9</v>
@@ -63241,7 +63244,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G2345" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="H2345" t="s">
         <v>9</v>
@@ -63267,7 +63270,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G2346" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="H2346" t="s">
         <v>9</v>
@@ -63293,7 +63296,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G2347" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="H2347" t="s">
         <v>9</v>
@@ -63319,7 +63322,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G2348" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="H2348" t="s">
         <v>9</v>
@@ -63345,7 +63348,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G2349" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="H2349" t="s">
         <v>9</v>
@@ -63371,7 +63374,7 @@
         <v>3.25</v>
       </c>
       <c r="G2350" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="H2350" t="s">
         <v>9</v>
@@ -63397,7 +63400,7 @@
         <v>3.25</v>
       </c>
       <c r="G2351" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="H2351" t="s">
         <v>9</v>
@@ -63423,7 +63426,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G2352" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="H2352" t="s">
         <v>9</v>
@@ -63449,7 +63452,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G2353" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="H2353" t="s">
         <v>9</v>
@@ -63475,7 +63478,7 @@
         <v>3.25</v>
       </c>
       <c r="G2354" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="H2354" t="s">
         <v>9</v>
@@ -63501,7 +63504,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G2355" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="H2355" t="s">
         <v>9</v>
@@ -63527,7 +63530,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G2356" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="H2356" t="s">
         <v>9</v>
@@ -63553,7 +63556,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G2357" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="H2357" t="s">
         <v>9</v>
@@ -63579,7 +63582,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G2358" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="H2358" t="s">
         <v>9</v>
@@ -63605,7 +63608,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G2359" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="H2359" t="s">
         <v>9</v>
@@ -63631,7 +63634,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G2360" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="H2360" t="s">
         <v>9</v>
@@ -63657,7 +63660,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G2361" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="H2361" t="s">
         <v>9</v>
@@ -63683,7 +63686,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G2362" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="H2362" t="s">
         <v>9</v>
@@ -63709,7 +63712,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2363" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="H2363" t="s">
         <v>9</v>
@@ -63735,7 +63738,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2364" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="H2364" t="s">
         <v>9</v>
@@ -63761,7 +63764,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G2365" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="H2365" t="s">
         <v>9</v>
@@ -63787,7 +63790,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2366" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="H2366" t="s">
         <v>9</v>
@@ -63813,7 +63816,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G2367" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="H2367" t="s">
         <v>9</v>
@@ -63839,7 +63842,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G2368" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="H2368" t="s">
         <v>9</v>
@@ -63865,7 +63868,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G2369" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="H2369" t="s">
         <v>9</v>
@@ -63891,7 +63894,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G2370" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="H2370" t="s">
         <v>9</v>
@@ -63917,7 +63920,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G2371" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="H2371" t="s">
         <v>9</v>
@@ -63943,7 +63946,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G2372" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="H2372" t="s">
         <v>9</v>
@@ -63969,7 +63972,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G2373" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="H2373" t="s">
         <v>9</v>
@@ -63995,7 +63998,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G2374" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="H2374" t="s">
         <v>9</v>
@@ -64021,7 +64024,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G2375" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="H2375" t="s">
         <v>9</v>
@@ -64047,7 +64050,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G2376" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="H2376" t="s">
         <v>9</v>
@@ -64073,7 +64076,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G2377" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="H2377" t="s">
         <v>9</v>
@@ -64099,7 +64102,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G2378" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="H2378" t="s">
         <v>9</v>
@@ -64125,7 +64128,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G2379" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="H2379" t="s">
         <v>9</v>
@@ -64151,7 +64154,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G2380" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="H2380" t="s">
         <v>9</v>
@@ -64177,7 +64180,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G2381" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="H2381" t="s">
         <v>9</v>
@@ -64203,7 +64206,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G2382" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="H2382" t="s">
         <v>9</v>
@@ -64229,7 +64232,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G2383" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="H2383" t="s">
         <v>9</v>
@@ -64255,7 +64258,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2384" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="H2384" t="s">
         <v>9</v>
@@ -64281,7 +64284,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G2385" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="H2385" t="s">
         <v>9</v>
@@ -64307,7 +64310,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G2386" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="H2386" t="s">
         <v>9</v>
@@ -64333,7 +64336,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G2387" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="H2387" t="s">
         <v>9</v>
@@ -64359,7 +64362,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G2388" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="H2388" t="s">
         <v>9</v>
@@ -64385,7 +64388,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G2389" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="H2389" t="s">
         <v>9</v>
@@ -64411,7 +64414,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2390" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="H2390" t="s">
         <v>9</v>
@@ -64437,7 +64440,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2391" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="H2391" t="s">
         <v>9</v>
@@ -64463,7 +64466,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G2392" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="H2392" t="s">
         <v>9</v>
@@ -64489,7 +64492,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G2393" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="H2393" t="s">
         <v>9</v>
@@ -64515,7 +64518,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G2394" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="H2394" t="s">
         <v>9</v>
@@ -64541,7 +64544,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2395" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="H2395" t="s">
         <v>9</v>
@@ -64567,7 +64570,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2396" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="H2396" t="s">
         <v>9</v>
@@ -64593,7 +64596,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G2397" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="H2397" t="s">
         <v>9</v>
@@ -64619,7 +64622,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2398" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="H2398" t="s">
         <v>9</v>
@@ -64645,7 +64648,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G2399" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="H2399" t="s">
         <v>9</v>
@@ -64671,7 +64674,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G2400" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="H2400" t="s">
         <v>9</v>
@@ -64697,7 +64700,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G2401" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="H2401" t="s">
         <v>9</v>
@@ -64723,7 +64726,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G2402" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="H2402" t="s">
         <v>9</v>
@@ -64749,7 +64752,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G2403" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="H2403" t="s">
         <v>9</v>
@@ -64775,7 +64778,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G2404" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="H2404" t="s">
         <v>9</v>
@@ -64801,7 +64804,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G2405" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="H2405" t="s">
         <v>9</v>
@@ -64827,7 +64830,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G2406" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="H2406" t="s">
         <v>9</v>
@@ -64853,7 +64856,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G2407" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="H2407" t="s">
         <v>9</v>
@@ -64879,7 +64882,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G2408" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="H2408" t="s">
         <v>9</v>
@@ -64905,7 +64908,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2409" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="H2409" t="s">
         <v>9</v>
@@ -64931,7 +64934,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G2410" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="H2410" t="s">
         <v>9</v>
@@ -64957,7 +64960,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G2411" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="H2411" t="s">
         <v>9</v>
@@ -64983,7 +64986,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G2412" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="H2412" t="s">
         <v>9</v>
@@ -65009,7 +65012,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G2413" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="H2413" t="s">
         <v>9</v>
@@ -65035,7 +65038,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G2414" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="H2414" t="s">
         <v>9</v>
@@ -65061,7 +65064,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G2415" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="H2415" t="s">
         <v>9</v>
@@ -65087,7 +65090,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G2416" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="H2416" t="s">
         <v>9</v>
@@ -65113,7 +65116,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G2417" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="H2417" t="s">
         <v>9</v>
@@ -65139,7 +65142,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G2418" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="H2418" t="s">
         <v>9</v>
@@ -65165,7 +65168,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G2419" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="H2419" t="s">
         <v>9</v>
@@ -65191,7 +65194,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G2420" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="H2420" t="s">
         <v>9</v>
@@ -65217,7 +65220,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G2421" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="H2421" t="s">
         <v>9</v>
@@ -65243,7 +65246,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G2422" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="H2422" t="s">
         <v>9</v>
@@ -65269,7 +65272,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G2423" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="H2423" t="s">
         <v>9</v>
@@ -65295,7 +65298,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G2424" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="H2424" t="s">
         <v>9</v>
@@ -65321,7 +65324,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G2425" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="H2425" t="s">
         <v>9</v>
@@ -65347,7 +65350,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G2426" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="H2426" t="s">
         <v>9</v>
@@ -65373,7 +65376,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G2427" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="H2427" t="s">
         <v>9</v>
@@ -65399,7 +65402,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G2428" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="H2428" t="s">
         <v>9</v>
@@ -65425,7 +65428,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G2429" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="H2429" t="s">
         <v>9</v>
@@ -65451,7 +65454,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G2430" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="H2430" t="s">
         <v>9</v>
@@ -65477,7 +65480,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G2431" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="H2431" t="s">
         <v>9</v>
@@ -65503,7 +65506,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G2432" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="H2432" t="s">
         <v>9</v>
@@ -65529,7 +65532,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G2433" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="H2433" t="s">
         <v>9</v>
@@ -65555,7 +65558,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G2434" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="H2434" t="s">
         <v>9</v>
@@ -65581,7 +65584,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G2435" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="H2435" t="s">
         <v>9</v>
@@ -65607,7 +65610,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G2436" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="H2436" t="s">
         <v>9</v>
@@ -65633,7 +65636,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G2437" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="H2437" t="s">
         <v>9</v>
@@ -65659,7 +65662,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G2438" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="H2438" t="s">
         <v>9</v>
@@ -65685,7 +65688,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G2439" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="H2439" t="s">
         <v>9</v>
@@ -65711,7 +65714,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G2440" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="H2440" t="s">
         <v>9</v>
@@ -65737,7 +65740,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G2441" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="H2441" t="s">
         <v>9</v>
@@ -65763,7 +65766,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G2442" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="H2442" t="s">
         <v>9</v>
@@ -65789,7 +65792,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G2443" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="H2443" t="s">
         <v>9</v>
@@ -65815,7 +65818,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G2444" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="H2444" t="s">
         <v>9</v>
@@ -65841,7 +65844,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G2445" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="H2445" t="s">
         <v>9</v>
@@ -65867,7 +65870,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G2446" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="H2446" t="s">
         <v>9</v>
@@ -65893,7 +65896,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G2447" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="H2447" t="s">
         <v>9</v>
@@ -65919,7 +65922,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G2448" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="H2448" t="s">
         <v>9</v>
@@ -65945,7 +65948,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G2449" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="H2449" t="s">
         <v>9</v>
@@ -65971,7 +65974,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G2450" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="H2450" t="s">
         <v>9</v>
@@ -65997,7 +66000,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G2451" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="H2451" t="s">
         <v>9</v>
@@ -66023,7 +66026,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G2452" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="H2452" t="s">
         <v>9</v>
@@ -66049,7 +66052,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G2453" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="H2453" t="s">
         <v>9</v>
@@ -66075,7 +66078,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G2454" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="H2454" t="s">
         <v>9</v>
@@ -66101,7 +66104,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G2455" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="H2455" t="s">
         <v>9</v>
@@ -66127,7 +66130,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G2456" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="H2456" t="s">
         <v>9</v>
@@ -66153,7 +66156,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G2457" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="H2457" t="s">
         <v>9</v>
@@ -66179,7 +66182,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G2458" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="H2458" t="s">
         <v>9</v>
@@ -66205,7 +66208,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G2459" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="H2459" t="s">
         <v>9</v>
@@ -66231,7 +66234,7 @@
         <v>4</v>
       </c>
       <c r="G2460" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="H2460" t="s">
         <v>9</v>
@@ -66257,7 +66260,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G2461" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="H2461" t="s">
         <v>9</v>
@@ -66283,7 +66286,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G2462" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="H2462" t="s">
         <v>9</v>
@@ -66309,7 +66312,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G2463" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="H2463" t="s">
         <v>9</v>
@@ -66335,7 +66338,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G2464" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="H2464" t="s">
         <v>9</v>
@@ -66361,7 +66364,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G2465" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="H2465" t="s">
         <v>9</v>
@@ -66387,7 +66390,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G2466" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="H2466" t="s">
         <v>9</v>
@@ -66413,7 +66416,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G2467" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="H2467" t="s">
         <v>9</v>
@@ -66439,7 +66442,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G2468" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="H2468" t="s">
         <v>9</v>
@@ -66465,7 +66468,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G2469" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="H2469" t="s">
         <v>9</v>
@@ -66491,7 +66494,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G2470" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="H2470" t="s">
         <v>9</v>
@@ -66517,7 +66520,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G2471" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="H2471" t="s">
         <v>9</v>
@@ -66543,7 +66546,7 @@
         <v>4</v>
       </c>
       <c r="G2472" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="H2472" t="s">
         <v>9</v>
@@ -66569,7 +66572,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G2473" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="H2473" t="s">
         <v>9</v>
@@ -66595,7 +66598,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G2474" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="H2474" t="s">
         <v>9</v>
@@ -66621,7 +66624,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G2475" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="H2475" t="s">
         <v>9</v>
@@ -66647,7 +66650,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G2476" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="H2476" t="s">
         <v>9</v>
@@ -66673,7 +66676,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G2477" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="H2477" t="s">
         <v>9</v>
@@ -66699,7 +66702,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G2478" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="H2478" t="s">
         <v>9</v>
@@ -66725,7 +66728,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G2479" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="H2479" t="s">
         <v>9</v>
@@ -66751,7 +66754,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G2480" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="H2480" t="s">
         <v>9</v>
@@ -66777,7 +66780,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G2481" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="H2481" t="s">
         <v>9</v>
@@ -66803,7 +66806,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G2482" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="H2482" t="s">
         <v>9</v>
@@ -66829,7 +66832,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G2483" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="H2483" t="s">
         <v>9</v>
@@ -66855,7 +66858,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G2484" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="H2484" t="s">
         <v>9</v>
@@ -66881,7 +66884,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G2485" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="H2485" t="s">
         <v>9</v>
@@ -66907,7 +66910,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G2486" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="H2486" t="s">
         <v>9</v>
@@ -66933,7 +66936,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G2487" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="H2487" t="s">
         <v>9</v>
@@ -66959,7 +66962,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G2488" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="H2488" t="s">
         <v>9</v>
@@ -66985,7 +66988,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G2489" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="H2489" t="s">
         <v>9</v>
@@ -67011,7 +67014,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G2490" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="H2490" t="s">
         <v>9</v>
@@ -67037,7 +67040,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G2491" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="H2491" t="s">
         <v>9</v>
@@ -67063,7 +67066,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G2492" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="H2492" t="s">
         <v>9</v>
@@ -67089,7 +67092,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G2493" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="H2493" t="s">
         <v>9</v>
@@ -67115,7 +67118,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G2494" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="H2494" t="s">
         <v>9</v>
@@ -67141,7 +67144,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G2495" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="H2495" t="s">
         <v>9</v>
@@ -67167,7 +67170,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G2496" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="H2496" t="s">
         <v>9</v>
@@ -67175,7 +67178,7 @@
     </row>
     <row r="2497">
       <c r="A2497" s="1" t="n">
-        <v>45954.6494791667</v>
+        <v>45954.2916666667</v>
       </c>
       <c r="B2497" t="n">
         <v>12067</v>
@@ -67193,9 +67196,35 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G2497" t="s">
+        <v>639</v>
+      </c>
+      <c r="H2497" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2498">
+      <c r="A2498" s="1" t="n">
+        <v>45957.6913078704</v>
+      </c>
+      <c r="B2498" t="n">
+        <v>1927</v>
+      </c>
+      <c r="C2498" t="n">
+        <v>4.76000022888184</v>
+      </c>
+      <c r="D2498" t="n">
+        <v>4.67999982833862</v>
+      </c>
+      <c r="E2498" t="n">
+        <v>4.71999979019165</v>
+      </c>
+      <c r="F2498" t="n">
+        <v>4.76000022888184</v>
+      </c>
+      <c r="G2498" t="s">
         <v>638</v>
       </c>
-      <c r="H2497" t="s">
+      <c r="H2498" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ENV.MI.xlsx
+++ b/data/ENV.MI.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18965244293213</t>
+    <t xml:space="preserve">2.18965268135071</t>
   </si>
   <si>
     <t xml:space="preserve">ENV.MI</t>
@@ -50,58 +50,58 @@
     <t xml:space="preserve">2.1447126865387</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16175842285156</t>
+    <t xml:space="preserve">2.16175866127014</t>
   </si>
   <si>
     <t xml:space="preserve">2.03778719902039</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08272647857666</t>
+    <t xml:space="preserve">2.08272695541382</t>
   </si>
   <si>
     <t xml:space="preserve">2.05328369140625</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03623747825623</t>
+    <t xml:space="preserve">2.03623723983765</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96805274486542</t>
+    <t xml:space="preserve">1.96805286407471</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9603043794632</t>
+    <t xml:space="preserve">1.96030461788177</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89831900596619</t>
+    <t xml:space="preserve">1.89831876754761</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88127279281616</t>
+    <t xml:space="preserve">1.88127243518829</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96340382099152</t>
+    <t xml:space="preserve">1.96340394020081</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98354935646057</t>
+    <t xml:space="preserve">1.98354911804199</t>
   </si>
   <si>
     <t xml:space="preserve">2.01299262046814</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93551015853882</t>
+    <t xml:space="preserve">1.93551003932953</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93705999851227</t>
+    <t xml:space="preserve">1.93705952167511</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91381537914276</t>
+    <t xml:space="preserve">1.91381514072418</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91071581840515</t>
+    <t xml:space="preserve">1.91071557998657</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86577594280243</t>
+    <t xml:space="preserve">1.86577606201172</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89212000370026</t>
+    <t xml:space="preserve">1.89211976528168</t>
   </si>
   <si>
     <t xml:space="preserve">1.85182929039001</t>
@@ -110,31 +110,31 @@
     <t xml:space="preserve">1.93396067619324</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86732602119446</t>
+    <t xml:space="preserve">1.86732578277588</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88902068138123</t>
+    <t xml:space="preserve">1.88902056217194</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98664879798889</t>
+    <t xml:space="preserve">1.98664844036102</t>
   </si>
   <si>
     <t xml:space="preserve">2.11526894569397</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18500328063965</t>
+    <t xml:space="preserve">2.18500351905823</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20824837684631</t>
+    <t xml:space="preserve">2.20824813842773</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16950702667236</t>
+    <t xml:space="preserve">2.16950678825378</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08427619934082</t>
+    <t xml:space="preserve">2.08427667617798</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01454210281372</t>
+    <t xml:space="preserve">2.0145423412323</t>
   </si>
   <si>
     <t xml:space="preserve">2.0052444934845</t>
@@ -143,7 +143,7 @@
     <t xml:space="preserve">2.14626240730286</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22219514846802</t>
+    <t xml:space="preserve">2.22219491004944</t>
   </si>
   <si>
     <t xml:space="preserve">2.32447195053101</t>
@@ -155,34 +155,34 @@
     <t xml:space="preserve">2.27178359031677</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24698948860168</t>
+    <t xml:space="preserve">2.24698925018311</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32137274742126</t>
+    <t xml:space="preserve">2.32137250900269</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2841808795929</t>
+    <t xml:space="preserve">2.28418111801147</t>
   </si>
   <si>
     <t xml:space="preserve">2.37870955467224</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35546469688416</t>
+    <t xml:space="preserve">2.35546493530273</t>
   </si>
   <si>
     <t xml:space="preserve">2.4406955242157</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43139743804932</t>
+    <t xml:space="preserve">2.43139719963074</t>
   </si>
   <si>
     <t xml:space="preserve">2.44999313354492</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38490796089172</t>
+    <t xml:space="preserve">2.3849081993103</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3616635799408</t>
+    <t xml:space="preserve">2.36166334152222</t>
   </si>
   <si>
     <t xml:space="preserve">2.36321330070496</t>
@@ -191,13 +191,13 @@
     <t xml:space="preserve">2.3198230266571</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35236525535583</t>
+    <t xml:space="preserve">2.35236549377441</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26868438720703</t>
+    <t xml:space="preserve">2.26868462562561</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32292199134827</t>
+    <t xml:space="preserve">2.32292222976685</t>
   </si>
   <si>
     <t xml:space="preserve">2.33531928062439</t>
@@ -212,37 +212,37 @@
     <t xml:space="preserve">2.28573083877563</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25473737716675</t>
+    <t xml:space="preserve">2.25473761558533</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29038000106812</t>
+    <t xml:space="preserve">2.29037976264954</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27488303184509</t>
+    <t xml:space="preserve">2.27488327026367</t>
   </si>
   <si>
     <t xml:space="preserve">2.2314932346344</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0749785900116</t>
+    <t xml:space="preserve">2.07497835159302</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00834345817566</t>
+    <t xml:space="preserve">2.00834369659424</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03468775749207</t>
+    <t xml:space="preserve">2.03468751907349</t>
   </si>
   <si>
     <t xml:space="preserve">2.02229046821594</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97580099105835</t>
+    <t xml:space="preserve">1.97580111026764</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91980695724487</t>
+    <t xml:space="preserve">1.919806599617</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88216352462769</t>
+    <t xml:space="preserve">1.88216376304626</t>
   </si>
   <si>
     <t xml:space="preserve">2.00136733055115</t>
@@ -251,37 +251,37 @@
     <t xml:space="preserve">1.96058702468872</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90255379676819</t>
+    <t xml:space="preserve">1.9025536775589</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9213752746582</t>
+    <t xml:space="preserve">1.92137515544891</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91353273391724</t>
+    <t xml:space="preserve">1.91353321075439</t>
   </si>
   <si>
     <t xml:space="preserve">1.89784848690033</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89000618457794</t>
+    <t xml:space="preserve">1.89000606536865</t>
   </si>
   <si>
     <t xml:space="preserve">1.85079395771027</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88059484958649</t>
+    <t xml:space="preserve">1.88059508800507</t>
   </si>
   <si>
     <t xml:space="preserve">1.8664790391922</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54651117324829</t>
+    <t xml:space="preserve">1.546511054039</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68610501289368</t>
+    <t xml:space="preserve">1.68610489368439</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70178949832916</t>
+    <t xml:space="preserve">1.70178961753845</t>
   </si>
   <si>
     <t xml:space="preserve">1.70022094249725</t>
@@ -293,13 +293,13 @@
     <t xml:space="preserve">1.64532446861267</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62336587905884</t>
+    <t xml:space="preserve">1.62336611747742</t>
   </si>
   <si>
     <t xml:space="preserve">1.61552357673645</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63120830059052</t>
+    <t xml:space="preserve">1.6312084197998</t>
   </si>
   <si>
     <t xml:space="preserve">1.5841543674469</t>
@@ -308,31 +308,31 @@
     <t xml:space="preserve">1.64689302444458</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64061915874481</t>
+    <t xml:space="preserve">1.6406192779541</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63905084133148</t>
+    <t xml:space="preserve">1.63905048370361</t>
   </si>
   <si>
     <t xml:space="preserve">1.60768139362335</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57631170749664</t>
+    <t xml:space="preserve">1.57631182670593</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59199655056</t>
+    <t xml:space="preserve">1.59199666976929</t>
   </si>
   <si>
     <t xml:space="preserve">1.75668609142303</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84295165538788</t>
+    <t xml:space="preserve">1.84295177459717</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84608888626099</t>
+    <t xml:space="preserve">1.84608864784241</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92921757698059</t>
+    <t xml:space="preserve">1.9292174577713</t>
   </si>
   <si>
     <t xml:space="preserve">1.88530027866364</t>
@@ -344,79 +344,79 @@
     <t xml:space="preserve">1.91823840141296</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94960784912109</t>
+    <t xml:space="preserve">1.9496077299118</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93078565597534</t>
+    <t xml:space="preserve">1.93078577518463</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84922575950623</t>
+    <t xml:space="preserve">1.84922552108765</t>
   </si>
   <si>
     <t xml:space="preserve">1.82413005828857</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8554995059967</t>
+    <t xml:space="preserve">1.85549938678741</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89627993106842</t>
+    <t xml:space="preserve">1.89627957344055</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8743212223053</t>
+    <t xml:space="preserve">1.87432110309601</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94333362579346</t>
+    <t xml:space="preserve">1.94333374500275</t>
   </si>
   <si>
     <t xml:space="preserve">1.94490230083466</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96686053276062</t>
+    <t xml:space="preserve">1.9668607711792</t>
   </si>
   <si>
     <t xml:space="preserve">1.98411393165588</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0625376701355</t>
+    <t xml:space="preserve">2.06253743171692</t>
   </si>
   <si>
     <t xml:space="preserve">2.0531268119812</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05155849456787</t>
+    <t xml:space="preserve">2.05155801773071</t>
   </si>
   <si>
     <t xml:space="preserve">2.0233256816864</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02959990501404</t>
+    <t xml:space="preserve">2.02959942817688</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03116822242737</t>
+    <t xml:space="preserve">2.03116798400879</t>
   </si>
   <si>
     <t xml:space="preserve">2.06096911430359</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09390664100647</t>
+    <t xml:space="preserve">2.09390711784363</t>
   </si>
   <si>
     <t xml:space="preserve">2.08606457710266</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15507698059082</t>
+    <t xml:space="preserve">2.1550772190094</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18801498413086</t>
+    <t xml:space="preserve">2.18801522254944</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19585704803467</t>
+    <t xml:space="preserve">2.19585728645325</t>
   </si>
   <si>
     <t xml:space="preserve">2.2021312713623</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23350048065186</t>
+    <t xml:space="preserve">2.23350071907043</t>
   </si>
   <si>
     <t xml:space="preserve">2.20997357368469</t>
@@ -428,16 +428,16 @@
     <t xml:space="preserve">2.16605663299561</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1942892074585</t>
+    <t xml:space="preserve">2.19428873062134</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17389917373657</t>
+    <t xml:space="preserve">2.17389869689941</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2005627155304</t>
+    <t xml:space="preserve">2.20056247711182</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21938443183899</t>
+    <t xml:space="preserve">2.21938419342041</t>
   </si>
   <si>
     <t xml:space="preserve">2.21781611442566</t>
@@ -449,40 +449,40 @@
     <t xml:space="preserve">2.12057113647461</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15350866317749</t>
+    <t xml:space="preserve">2.15350890159607</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11743378639221</t>
+    <t xml:space="preserve">2.11743402481079</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16291952133179</t>
+    <t xml:space="preserve">2.16291975975037</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10802292823792</t>
+    <t xml:space="preserve">2.10802316665649</t>
   </si>
   <si>
     <t xml:space="preserve">2.01548314094543</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04528427124023</t>
+    <t xml:space="preserve">2.04528403282166</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9856823682785</t>
+    <t xml:space="preserve">1.98568272590637</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07822227478027</t>
+    <t xml:space="preserve">2.07822251319885</t>
   </si>
   <si>
     <t xml:space="preserve">2.06724262237549</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12998151779175</t>
+    <t xml:space="preserve">2.12998175621033</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1158652305603</t>
+    <t xml:space="preserve">2.11586570739746</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05469512939453</t>
+    <t xml:space="preserve">2.05469489097595</t>
   </si>
   <si>
     <t xml:space="preserve">2.11429715156555</t>
@@ -494,25 +494,25 @@
     <t xml:space="preserve">2.06410574913025</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10488629341125</t>
+    <t xml:space="preserve">2.10488605499268</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00920963287354</t>
+    <t xml:space="preserve">2.00920939445496</t>
   </si>
   <si>
     <t xml:space="preserve">2.01391506195068</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04842114448547</t>
+    <t xml:space="preserve">2.04842138290405</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1644880771637</t>
+    <t xml:space="preserve">2.16448760032654</t>
   </si>
   <si>
     <t xml:space="preserve">2.18487811088562</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26643896102905</t>
+    <t xml:space="preserve">2.26643848419189</t>
   </si>
   <si>
     <t xml:space="preserve">2.27271246910095</t>
@@ -521,7 +521,7 @@
     <t xml:space="preserve">2.2570276260376</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3072190284729</t>
+    <t xml:space="preserve">2.30721879005432</t>
   </si>
   <si>
     <t xml:space="preserve">2.23036360740662</t>
@@ -536,28 +536,28 @@
     <t xml:space="preserve">2.39191603660583</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33545112609863</t>
+    <t xml:space="preserve">2.33545088768005</t>
   </si>
   <si>
     <t xml:space="preserve">2.31349277496338</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37623143196106</t>
+    <t xml:space="preserve">2.3762309551239</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32917714118958</t>
+    <t xml:space="preserve">2.32917737960815</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24918532371521</t>
+    <t xml:space="preserve">2.24918508529663</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28839707374573</t>
+    <t xml:space="preserve">2.28839731216431</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33701968193054</t>
+    <t xml:space="preserve">2.33701992034912</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34486198425293</t>
+    <t xml:space="preserve">2.34486174583435</t>
   </si>
   <si>
     <t xml:space="preserve">2.34956741333008</t>
@@ -569,73 +569,73 @@
     <t xml:space="preserve">2.30251336097717</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31192398071289</t>
+    <t xml:space="preserve">2.31192421913147</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25075340270996</t>
+    <t xml:space="preserve">2.25075364112854</t>
   </si>
   <si>
     <t xml:space="preserve">2.27428078651428</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43896985054016</t>
+    <t xml:space="preserve">2.43897008895874</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48445558547974</t>
+    <t xml:space="preserve">2.48445582389832</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46249723434448</t>
+    <t xml:space="preserve">2.46249747276306</t>
   </si>
   <si>
     <t xml:space="preserve">2.50798296928406</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48602437973022</t>
+    <t xml:space="preserve">2.4860246181488</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60993361473083</t>
+    <t xml:space="preserve">2.60993337631226</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66639828681946</t>
+    <t xml:space="preserve">2.66639852523804</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66326117515564</t>
+    <t xml:space="preserve">2.66326141357422</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6601243019104</t>
+    <t xml:space="preserve">2.66012454032898</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64287114143372</t>
+    <t xml:space="preserve">2.64287137985229</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65855598449707</t>
+    <t xml:space="preserve">2.65855622291565</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60209083557129</t>
+    <t xml:space="preserve">2.60209107398987</t>
   </si>
   <si>
     <t xml:space="preserve">2.55033159255981</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63816571235657</t>
+    <t xml:space="preserve">2.63816595077515</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58013200759888</t>
+    <t xml:space="preserve">2.58013224601746</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59581732749939</t>
+    <t xml:space="preserve">2.59581685066223</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58170104026794</t>
+    <t xml:space="preserve">2.58170080184937</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60365962982178</t>
+    <t xml:space="preserve">2.6036593914032</t>
   </si>
   <si>
     <t xml:space="preserve">2.61934399604797</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57542705535889</t>
+    <t xml:space="preserve">2.57542681694031</t>
   </si>
   <si>
     <t xml:space="preserve">2.57385873794556</t>
@@ -644,13 +644,13 @@
     <t xml:space="preserve">2.50955128669739</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58797454833984</t>
+    <t xml:space="preserve">2.58797478675842</t>
   </si>
   <si>
     <t xml:space="preserve">2.56444764137268</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61150193214417</t>
+    <t xml:space="preserve">2.61150169372559</t>
   </si>
   <si>
     <t xml:space="preserve">2.56915330886841</t>
@@ -662,76 +662,76 @@
     <t xml:space="preserve">2.62561798095703</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62718677520752</t>
+    <t xml:space="preserve">2.62718653678894</t>
   </si>
   <si>
     <t xml:space="preserve">2.83422470092773</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79030752182007</t>
+    <t xml:space="preserve">2.79030728340149</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77619123458862</t>
+    <t xml:space="preserve">2.77619099617004</t>
   </si>
   <si>
     <t xml:space="preserve">2.78089642524719</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69149374961853</t>
+    <t xml:space="preserve">2.69149351119995</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7824649810791</t>
+    <t xml:space="preserve">2.78246474266052</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81226563453674</t>
+    <t xml:space="preserve">2.8122661113739</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82324504852295</t>
+    <t xml:space="preserve">2.82324552536011</t>
   </si>
   <si>
     <t xml:space="preserve">2.68678855895996</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70090484619141</t>
+    <t xml:space="preserve">2.70090460777283</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80657124519348</t>
+    <t xml:space="preserve">2.80657148361206</t>
   </si>
   <si>
     <t xml:space="preserve">2.86433959007263</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81940889358521</t>
+    <t xml:space="preserve">2.81940865516663</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80817627906799</t>
+    <t xml:space="preserve">2.80817604064941</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88038611412048</t>
+    <t xml:space="preserve">2.8803858757019</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8338508605957</t>
+    <t xml:space="preserve">2.83385062217712</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74398899078369</t>
+    <t xml:space="preserve">2.74398946762085</t>
   </si>
   <si>
     <t xml:space="preserve">2.72794246673584</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70547699928284</t>
+    <t xml:space="preserve">2.70547676086426</t>
   </si>
   <si>
     <t xml:space="preserve">2.73275637626648</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6717791557312</t>
+    <t xml:space="preserve">2.67177867889404</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62363862991333</t>
+    <t xml:space="preserve">2.62363886833191</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61721992492676</t>
+    <t xml:space="preserve">2.6172206401825</t>
   </si>
   <si>
     <t xml:space="preserve">2.60438299179077</t>
@@ -740,46 +740,46 @@
     <t xml:space="preserve">2.62524342536926</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64129018783569</t>
+    <t xml:space="preserve">2.64129042625427</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69584894180298</t>
+    <t xml:space="preserve">2.6958487033844</t>
   </si>
   <si>
     <t xml:space="preserve">2.75040793418884</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74719882011414</t>
+    <t xml:space="preserve">2.74719858169556</t>
   </si>
   <si>
     <t xml:space="preserve">2.71991920471191</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72633790969849</t>
+    <t xml:space="preserve">2.72633767127991</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74238443374634</t>
+    <t xml:space="preserve">2.74238419532776</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80015277862549</t>
+    <t xml:space="preserve">2.80015254020691</t>
   </si>
   <si>
     <t xml:space="preserve">2.78571057319641</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82422280311584</t>
+    <t xml:space="preserve">2.82422256469727</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78731560707092</t>
+    <t xml:space="preserve">2.78731489181519</t>
   </si>
   <si>
     <t xml:space="preserve">2.79373407363892</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80496644973755</t>
+    <t xml:space="preserve">2.80496668815613</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78410601615906</t>
+    <t xml:space="preserve">2.78410577774048</t>
   </si>
   <si>
     <t xml:space="preserve">2.77608251571655</t>
@@ -788,13 +788,13 @@
     <t xml:space="preserve">2.79533863067627</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82261800765991</t>
+    <t xml:space="preserve">2.82261824607849</t>
   </si>
   <si>
     <t xml:space="preserve">2.7600359916687</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77929186820984</t>
+    <t xml:space="preserve">2.77929210662842</t>
   </si>
   <si>
     <t xml:space="preserve">2.79854774475098</t>
@@ -803,16 +803,16 @@
     <t xml:space="preserve">2.7744779586792</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80336165428162</t>
+    <t xml:space="preserve">2.80336213111877</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83545517921448</t>
+    <t xml:space="preserve">2.83545541763306</t>
   </si>
   <si>
     <t xml:space="preserve">2.84026956558228</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83224630355835</t>
+    <t xml:space="preserve">2.83224606513977</t>
   </si>
   <si>
     <t xml:space="preserve">2.8113853931427</t>
@@ -821,52 +821,52 @@
     <t xml:space="preserve">2.81619930267334</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76324534416199</t>
+    <t xml:space="preserve">2.76324510574341</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71189570426941</t>
+    <t xml:space="preserve">2.71189594268799</t>
   </si>
   <si>
     <t xml:space="preserve">2.72473311424255</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79694318771362</t>
+    <t xml:space="preserve">2.7969434261322</t>
   </si>
   <si>
     <t xml:space="preserve">2.79052448272705</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76805949211121</t>
+    <t xml:space="preserve">2.76805925369263</t>
   </si>
   <si>
     <t xml:space="preserve">2.73115181922913</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7038722038269</t>
+    <t xml:space="preserve">2.70387244224548</t>
   </si>
   <si>
     <t xml:space="preserve">2.81459474563599</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82903671264648</t>
+    <t xml:space="preserve">2.82903695106506</t>
   </si>
   <si>
     <t xml:space="preserve">2.84347867965698</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77768731117249</t>
+    <t xml:space="preserve">2.77768707275391</t>
   </si>
   <si>
     <t xml:space="preserve">2.77126860618591</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88840937614441</t>
+    <t xml:space="preserve">2.88840985298157</t>
   </si>
   <si>
     <t xml:space="preserve">2.87236285209656</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89161896705627</t>
+    <t xml:space="preserve">2.8916187286377</t>
   </si>
   <si>
     <t xml:space="preserve">2.92852640151978</t>
@@ -878,58 +878,58 @@
     <t xml:space="preserve">2.90927028656006</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99913215637207</t>
+    <t xml:space="preserve">2.99913167953491</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96864318847656</t>
+    <t xml:space="preserve">2.96864342689514</t>
   </si>
   <si>
-    <t xml:space="preserve">2.830641746521</t>
+    <t xml:space="preserve">2.83064150810242</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87878155708313</t>
+    <t xml:space="preserve">2.87878179550171</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8771767616272</t>
+    <t xml:space="preserve">2.87717723846436</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87557244300842</t>
+    <t xml:space="preserve">2.87557220458984</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7520124912262</t>
+    <t xml:space="preserve">2.75201225280762</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76164054870605</t>
+    <t xml:space="preserve">2.7616400718689</t>
   </si>
   <si>
     <t xml:space="preserve">2.78892016410828</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67980217933655</t>
+    <t xml:space="preserve">2.67980194091797</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73596572875977</t>
+    <t xml:space="preserve">2.73596596717834</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8258273601532</t>
+    <t xml:space="preserve">2.82582783699036</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8482928276062</t>
+    <t xml:space="preserve">2.84829306602478</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82101321220398</t>
+    <t xml:space="preserve">2.82101345062256</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73436093330383</t>
+    <t xml:space="preserve">2.73436117172241</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81780409812927</t>
+    <t xml:space="preserve">2.81780433654785</t>
   </si>
   <si>
     <t xml:space="preserve">2.76484990119934</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74077963829041</t>
+    <t xml:space="preserve">2.74077987670898</t>
   </si>
   <si>
     <t xml:space="preserve">2.79212951660156</t>
@@ -941,10 +941,10 @@
     <t xml:space="preserve">2.60759210586548</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55142855644226</t>
+    <t xml:space="preserve">2.55142879486084</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56747531890869</t>
+    <t xml:space="preserve">2.56747508049011</t>
   </si>
   <si>
     <t xml:space="preserve">2.59956884384155</t>
@@ -956,10 +956,10 @@
     <t xml:space="preserve">2.50328826904297</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45514822006226</t>
+    <t xml:space="preserve">2.45514798164368</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47921848297119</t>
+    <t xml:space="preserve">2.47921800613403</t>
   </si>
   <si>
     <t xml:space="preserve">2.47119474411011</t>
@@ -974,22 +974,22 @@
     <t xml:space="preserve">2.48724150657654</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49526476860046</t>
+    <t xml:space="preserve">2.49526524543762</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52735877037048</t>
+    <t xml:space="preserve">2.52735829353333</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58352208137512</t>
+    <t xml:space="preserve">2.58352184295654</t>
   </si>
   <si>
     <t xml:space="preserve">2.65573215484619</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91247987747192</t>
+    <t xml:space="preserve">2.9124801158905</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8200249671936</t>
+    <t xml:space="preserve">2.82002472877502</t>
   </si>
   <si>
     <t xml:space="preserve">2.80358171463013</t>
@@ -1004,37 +1004,37 @@
     <t xml:space="preserve">2.85291147232056</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81180334091187</t>
+    <t xml:space="preserve">2.81180310249329</t>
   </si>
   <si>
     <t xml:space="preserve">2.72136545181274</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68025660514832</t>
+    <t xml:space="preserve">2.68025684356689</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69670033454895</t>
+    <t xml:space="preserve">2.69670009613037</t>
   </si>
   <si>
     <t xml:space="preserve">2.64737033843994</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65559196472168</t>
+    <t xml:space="preserve">2.6555917263031</t>
   </si>
   <si>
     <t xml:space="preserve">2.663813829422</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63092708587646</t>
+    <t xml:space="preserve">2.63092732429504</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6391487121582</t>
+    <t xml:space="preserve">2.63914847373962</t>
   </si>
   <si>
     <t xml:space="preserve">2.55693221092224</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59804034233093</t>
+    <t xml:space="preserve">2.59804058074951</t>
   </si>
   <si>
     <t xml:space="preserve">2.5487105846405</t>
@@ -1061,7 +1061,7 @@
     <t xml:space="preserve">2.62270545959473</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51582384109497</t>
+    <t xml:space="preserve">2.51582407951355</t>
   </si>
   <si>
     <t xml:space="preserve">2.57337546348572</t>
@@ -1088,22 +1088,22 @@
     <t xml:space="preserve">2.42538571357727</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43360757827759</t>
+    <t xml:space="preserve">2.43360733985901</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49115896224976</t>
+    <t xml:space="preserve">2.49115872383118</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50760221481323</t>
+    <t xml:space="preserve">2.50760245323181</t>
   </si>
   <si>
     <t xml:space="preserve">2.54048871994019</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67203521728516</t>
+    <t xml:space="preserve">2.67203497886658</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68847823143005</t>
+    <t xml:space="preserve">2.68847846984863</t>
   </si>
   <si>
     <t xml:space="preserve">2.70492172241211</t>
@@ -1118,7 +1118,7 @@
     <t xml:space="preserve">2.78713846206665</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77069497108459</t>
+    <t xml:space="preserve">2.77069520950317</t>
   </si>
   <si>
     <t xml:space="preserve">2.7295868396759</t>
@@ -1133,13 +1133,13 @@
     <t xml:space="preserve">2.79536008834839</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87757682800293</t>
+    <t xml:space="preserve">2.87757658958435</t>
   </si>
   <si>
     <t xml:space="preserve">2.91868448257446</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89401960372925</t>
+    <t xml:space="preserve">2.89401984214783</t>
   </si>
   <si>
     <t xml:space="preserve">2.86113309860229</t>
@@ -1148,13 +1148,13 @@
     <t xml:space="preserve">2.90224146842957</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88579797744751</t>
+    <t xml:space="preserve">2.88579821586609</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8364679813385</t>
+    <t xml:space="preserve">2.83646821975708</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94334936141968</t>
+    <t xml:space="preserve">2.94334959983826</t>
   </si>
   <si>
     <t xml:space="preserve">2.82824659347534</t>
@@ -1166,13 +1166,13 @@
     <t xml:space="preserve">2.80358123779297</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77809429168701</t>
+    <t xml:space="preserve">2.77809453010559</t>
   </si>
   <si>
     <t xml:space="preserve">2.82057309150696</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82906866073608</t>
+    <t xml:space="preserve">2.82906889915466</t>
   </si>
   <si>
     <t xml:space="preserve">2.88853859901428</t>
@@ -1184,31 +1184,31 @@
     <t xml:space="preserve">2.92252135276794</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90552997589111</t>
+    <t xml:space="preserve">2.90552973747253</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87154698371887</t>
+    <t xml:space="preserve">2.87154722213745</t>
   </si>
   <si>
     <t xml:space="preserve">2.85455560684204</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91402554512024</t>
+    <t xml:space="preserve">2.91402578353882</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93101692199707</t>
+    <t xml:space="preserve">2.93101716041565</t>
   </si>
   <si>
     <t xml:space="preserve">2.94800853729248</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89703416824341</t>
+    <t xml:space="preserve">2.89703440666199</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93951296806335</t>
+    <t xml:space="preserve">2.93951272964478</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98199129104614</t>
+    <t xml:space="preserve">2.98199105262756</t>
   </si>
   <si>
     <t xml:space="preserve">2.79508566856384</t>
@@ -1241,7 +1241,7 @@
     <t xml:space="preserve">2.61667585372925</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55720615386963</t>
+    <t xml:space="preserve">2.55720639228821</t>
   </si>
   <si>
     <t xml:space="preserve">2.51472759246826</t>
@@ -1250,7 +1250,7 @@
     <t xml:space="preserve">2.49773621559143</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48074507713318</t>
+    <t xml:space="preserve">2.4807448387146</t>
   </si>
   <si>
     <t xml:space="preserve">2.53171896934509</t>
@@ -1271,10 +1271,10 @@
     <t xml:space="preserve">2.59118890762329</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47224903106689</t>
+    <t xml:space="preserve">2.47224926948547</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63366746902466</t>
+    <t xml:space="preserve">2.63366723060608</t>
   </si>
   <si>
     <t xml:space="preserve">2.599684715271</t>
@@ -1301,16 +1301,16 @@
     <t xml:space="preserve">2.97349572181702</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95650410652161</t>
+    <t xml:space="preserve">2.95650434494019</t>
   </si>
   <si>
     <t xml:space="preserve">2.84606003761292</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75260758399963</t>
+    <t xml:space="preserve">2.75260734558105</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6676504611969</t>
+    <t xml:space="preserve">2.66765022277832</t>
   </si>
   <si>
     <t xml:space="preserve">2.65915465354919</t>
@@ -1334,7 +1334,7 @@
     <t xml:space="preserve">2.65065860748291</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64216303825378</t>
+    <t xml:space="preserve">2.64216327667236</t>
   </si>
   <si>
     <t xml:space="preserve">2.71012902259827</t>
@@ -1346,10 +1346,10 @@
     <t xml:space="preserve">2.71862459182739</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74411153793335</t>
+    <t xml:space="preserve">2.74411177635193</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68464159965515</t>
+    <t xml:space="preserve">2.68464183807373</t>
   </si>
   <si>
     <t xml:space="preserve">2.6081805229187</t>
@@ -1358,7 +1358,7 @@
     <t xml:space="preserve">2.50623202323914</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44676232337952</t>
+    <t xml:space="preserve">2.44676208496094</t>
   </si>
   <si>
     <t xml:space="preserve">2.37879633903503</t>
@@ -1367,13 +1367,13 @@
     <t xml:space="preserve">2.42977046966553</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37030053138733</t>
+    <t xml:space="preserve">2.37030076980591</t>
   </si>
   <si>
     <t xml:space="preserve">2.31932640075684</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27684807777405</t>
+    <t xml:space="preserve">2.27684783935547</t>
   </si>
   <si>
     <t xml:space="preserve">2.26835227012634</t>
@@ -1385,7 +1385,7 @@
     <t xml:space="preserve">2.33631801605225</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39578771591187</t>
+    <t xml:space="preserve">2.39578747749329</t>
   </si>
   <si>
     <t xml:space="preserve">2.72712016105652</t>
@@ -1394,7 +1394,7 @@
     <t xml:space="preserve">2.99898266792297</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03296542167664</t>
+    <t xml:space="preserve">3.03296518325806</t>
   </si>
   <si>
     <t xml:space="preserve">3.01597380638123</t>
@@ -1418,7 +1418,7 @@
     <t xml:space="preserve">3.16040086746216</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21137547492981</t>
+    <t xml:space="preserve">3.21137523651123</t>
   </si>
   <si>
     <t xml:space="preserve">3.31332349777222</t>
@@ -1427,16 +1427,16 @@
     <t xml:space="preserve">3.26234936714172</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33031487464905</t>
+    <t xml:space="preserve">3.33031511306763</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22836661338806</t>
+    <t xml:space="preserve">3.22836685180664</t>
   </si>
   <si>
     <t xml:space="preserve">3.17739224433899</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14340949058533</t>
+    <t xml:space="preserve">3.14340972900391</t>
   </si>
   <si>
     <t xml:space="preserve">3.10942697525024</t>
@@ -1454,7 +1454,7 @@
     <t xml:space="preserve">3.46624636650085</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36429786682129</t>
+    <t xml:space="preserve">3.36429810523987</t>
   </si>
   <si>
     <t xml:space="preserve">3.34730648994446</t>
@@ -67537,7 +67537,7 @@
     </row>
     <row r="2510">
       <c r="A2510" s="1" t="n">
-        <v>45973.69125</v>
+        <v>45973.3333333333</v>
       </c>
       <c r="B2510" t="n">
         <v>79574</v>
@@ -67558,6 +67558,32 @@
         <v>624</v>
       </c>
       <c r="H2510" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2511">
+      <c r="A2511" s="1" t="n">
+        <v>45974.6914351852</v>
+      </c>
+      <c r="B2511" t="n">
+        <v>169855</v>
+      </c>
+      <c r="C2511" t="n">
+        <v>4.34000015258789</v>
+      </c>
+      <c r="D2511" t="n">
+        <v>3.77999997138977</v>
+      </c>
+      <c r="E2511" t="n">
+        <v>4.23999977111816</v>
+      </c>
+      <c r="F2511" t="n">
+        <v>3.75999999046326</v>
+      </c>
+      <c r="G2511" t="s">
+        <v>613</v>
+      </c>
+      <c r="H2511" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ENV.MI.xlsx
+++ b/data/ENV.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="650" uniqueCount="650">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="652" uniqueCount="652">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18965220451355</t>
+    <t xml:space="preserve">2.18965244293213</t>
   </si>
   <si>
     <t xml:space="preserve">ENV.MI</t>
@@ -47,7 +47,7 @@
     <t xml:space="preserve">2.20979809761047</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1447126865387</t>
+    <t xml:space="preserve">2.14471244812012</t>
   </si>
   <si>
     <t xml:space="preserve">2.16175866127014</t>
@@ -56,7 +56,7 @@
     <t xml:space="preserve">2.03778719902039</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08272647857666</t>
+    <t xml:space="preserve">2.08272695541382</t>
   </si>
   <si>
     <t xml:space="preserve">2.05328345298767</t>
@@ -68,25 +68,25 @@
     <t xml:space="preserve">1.96805262565613</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96030485630035</t>
+    <t xml:space="preserve">1.96030461788177</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89831876754761</t>
+    <t xml:space="preserve">1.89831864833832</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88127267360687</t>
+    <t xml:space="preserve">1.88127243518829</t>
   </si>
   <si>
     <t xml:space="preserve">1.96340394020081</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98354935646057</t>
+    <t xml:space="preserve">1.98354911804199</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01299262046814</t>
+    <t xml:space="preserve">2.01299285888672</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93551027774811</t>
+    <t xml:space="preserve">1.93551015853882</t>
   </si>
   <si>
     <t xml:space="preserve">1.93705987930298</t>
@@ -95,28 +95,28 @@
     <t xml:space="preserve">1.91381525993347</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91071605682373</t>
+    <t xml:space="preserve">1.91071593761444</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86577641963959</t>
+    <t xml:space="preserve">1.86577606201172</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89212000370026</t>
+    <t xml:space="preserve">1.89211988449097</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85182917118073</t>
+    <t xml:space="preserve">1.85182905197144</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93396043777466</t>
+    <t xml:space="preserve">1.93396055698395</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8673255443573</t>
+    <t xml:space="preserve">1.86732590198517</t>
   </si>
   <si>
     <t xml:space="preserve">1.88902056217194</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98664820194244</t>
+    <t xml:space="preserve">1.98664844036102</t>
   </si>
   <si>
     <t xml:space="preserve">2.11526918411255</t>
@@ -125,13 +125,13 @@
     <t xml:space="preserve">2.18500351905823</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20824813842773</t>
+    <t xml:space="preserve">2.20824790000916</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16950726509094</t>
+    <t xml:space="preserve">2.16950702667236</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0842764377594</t>
+    <t xml:space="preserve">2.08427667617798</t>
   </si>
   <si>
     <t xml:space="preserve">2.0145423412323</t>
@@ -140,10 +140,10 @@
     <t xml:space="preserve">2.0052444934845</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14626240730286</t>
+    <t xml:space="preserve">2.14626216888428</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2221953868866</t>
+    <t xml:space="preserve">2.22219514846802</t>
   </si>
   <si>
     <t xml:space="preserve">2.32447171211243</t>
@@ -155,49 +155,49 @@
     <t xml:space="preserve">2.27178359031677</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24698925018311</t>
+    <t xml:space="preserve">2.24698972702026</t>
   </si>
   <si>
     <t xml:space="preserve">2.32137250900269</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28418111801147</t>
+    <t xml:space="preserve">2.2841808795929</t>
   </si>
   <si>
     <t xml:space="preserve">2.37870979309082</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35546445846558</t>
+    <t xml:space="preserve">2.35546493530273</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44069576263428</t>
+    <t xml:space="preserve">2.4406955242157</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43139743804932</t>
+    <t xml:space="preserve">2.43139719963074</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44999361038208</t>
+    <t xml:space="preserve">2.44999313354492</t>
   </si>
   <si>
     <t xml:space="preserve">2.3849081993103</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36166334152222</t>
+    <t xml:space="preserve">2.3616635799408</t>
   </si>
   <si>
     <t xml:space="preserve">2.3632128238678</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31982278823853</t>
+    <t xml:space="preserve">2.31982326507568</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35236573219299</t>
+    <t xml:space="preserve">2.35236549377441</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26868486404419</t>
+    <t xml:space="preserve">2.26868438720703</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32292199134827</t>
+    <t xml:space="preserve">2.32292222976685</t>
   </si>
   <si>
     <t xml:space="preserve">2.33531928062439</t>
@@ -206,10 +206,10 @@
     <t xml:space="preserve">2.33996844291687</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3105251789093</t>
+    <t xml:space="preserve">2.31052494049072</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28573107719421</t>
+    <t xml:space="preserve">2.28573083877563</t>
   </si>
   <si>
     <t xml:space="preserve">2.25473785400391</t>
@@ -218,13 +218,13 @@
     <t xml:space="preserve">2.29037952423096</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27488327026367</t>
+    <t xml:space="preserve">2.27488303184509</t>
   </si>
   <si>
     <t xml:space="preserve">2.2314932346344</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07497882843018</t>
+    <t xml:space="preserve">2.0749785900116</t>
   </si>
   <si>
     <t xml:space="preserve">2.00834369659424</t>
@@ -239,7 +239,7 @@
     <t xml:space="preserve">1.97580099105835</t>
   </si>
   <si>
-    <t xml:space="preserve">1.919806599617</t>
+    <t xml:space="preserve">1.91980683803558</t>
   </si>
   <si>
     <t xml:space="preserve">1.88216352462769</t>
@@ -251,7 +251,7 @@
     <t xml:space="preserve">1.96058702468872</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90255343914032</t>
+    <t xml:space="preserve">1.90255355834961</t>
   </si>
   <si>
     <t xml:space="preserve">1.92137515544891</t>
@@ -260,28 +260,28 @@
     <t xml:space="preserve">1.91353297233582</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89784824848175</t>
+    <t xml:space="preserve">1.89784836769104</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89000570774078</t>
+    <t xml:space="preserve">1.89000606536865</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85079395771027</t>
+    <t xml:space="preserve">1.85079383850098</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88059496879578</t>
+    <t xml:space="preserve">1.88059484958649</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86647880077362</t>
+    <t xml:space="preserve">1.86647915840149</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54651093482971</t>
+    <t xml:space="preserve">1.54651117324829</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6861047744751</t>
+    <t xml:space="preserve">1.68610489368439</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70178961753845</t>
+    <t xml:space="preserve">1.70178949832916</t>
   </si>
   <si>
     <t xml:space="preserve">1.70022082328796</t>
@@ -290,7 +290,7 @@
     <t xml:space="preserve">1.66257762908936</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64532470703125</t>
+    <t xml:space="preserve">1.64532458782196</t>
   </si>
   <si>
     <t xml:space="preserve">1.62336587905884</t>
@@ -299,82 +299,82 @@
     <t xml:space="preserve">1.61552357673645</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6312084197998</t>
+    <t xml:space="preserve">1.63120830059052</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58415424823761</t>
+    <t xml:space="preserve">1.58415448665619</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64689302444458</t>
+    <t xml:space="preserve">1.64689290523529</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6406192779541</t>
+    <t xml:space="preserve">1.64061915874481</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6390506029129</t>
+    <t xml:space="preserve">1.63905072212219</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60768115520477</t>
+    <t xml:space="preserve">1.60768127441406</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57631182670593</t>
+    <t xml:space="preserve">1.57631194591522</t>
   </si>
   <si>
     <t xml:space="preserve">1.59199666976929</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75668585300446</t>
+    <t xml:space="preserve">1.75668597221375</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84295189380646</t>
+    <t xml:space="preserve">1.8429514169693</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84608852863312</t>
+    <t xml:space="preserve">1.84608864784241</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92921757698059</t>
+    <t xml:space="preserve">1.92921769618988</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88530051708221</t>
+    <t xml:space="preserve">1.88530027866364</t>
   </si>
   <si>
     <t xml:space="preserve">1.9009850025177</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91823840141296</t>
+    <t xml:space="preserve">1.91823828220367</t>
   </si>
   <si>
     <t xml:space="preserve">1.94960761070251</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93078589439392</t>
+    <t xml:space="preserve">1.93078601360321</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84922540187836</t>
+    <t xml:space="preserve">1.84922564029694</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82412993907928</t>
+    <t xml:space="preserve">1.82413017749786</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85549962520599</t>
+    <t xml:space="preserve">1.8554995059967</t>
   </si>
   <si>
     <t xml:space="preserve">1.89628005027771</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87432134151459</t>
+    <t xml:space="preserve">1.87432086467743</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94333362579346</t>
+    <t xml:space="preserve">1.94333374500275</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94490218162537</t>
+    <t xml:space="preserve">1.94490194320679</t>
   </si>
   <si>
     <t xml:space="preserve">1.96686065196991</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98411428928375</t>
+    <t xml:space="preserve">1.98411381244659</t>
   </si>
   <si>
     <t xml:space="preserve">2.0625376701355</t>
@@ -383,19 +383,19 @@
     <t xml:space="preserve">2.05312657356262</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05155801773071</t>
+    <t xml:space="preserve">2.05155777931213</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02332615852356</t>
+    <t xml:space="preserve">2.0233256816864</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0295991897583</t>
+    <t xml:space="preserve">2.02959966659546</t>
   </si>
   <si>
     <t xml:space="preserve">2.03116798400879</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06096935272217</t>
+    <t xml:space="preserve">2.06096911430359</t>
   </si>
   <si>
     <t xml:space="preserve">2.09390687942505</t>
@@ -404,13 +404,13 @@
     <t xml:space="preserve">2.08606457710266</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1550772190094</t>
+    <t xml:space="preserve">2.15507698059082</t>
   </si>
   <si>
     <t xml:space="preserve">2.18801522254944</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19585728645325</t>
+    <t xml:space="preserve">2.19585752487183</t>
   </si>
   <si>
     <t xml:space="preserve">2.2021312713623</t>
@@ -443,28 +443,28 @@
     <t xml:space="preserve">2.21781587600708</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19115209579468</t>
+    <t xml:space="preserve">2.1911518573761</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12057065963745</t>
+    <t xml:space="preserve">2.12057089805603</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15350866317749</t>
+    <t xml:space="preserve">2.15350842475891</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11743402481079</t>
+    <t xml:space="preserve">2.11743378639221</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16291975975037</t>
+    <t xml:space="preserve">2.16291952133179</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10802292823792</t>
+    <t xml:space="preserve">2.10802340507507</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01548314094543</t>
+    <t xml:space="preserve">2.01548337936401</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04528474807739</t>
+    <t xml:space="preserve">2.04528450965881</t>
   </si>
   <si>
     <t xml:space="preserve">1.98568260669708</t>
@@ -473,31 +473,31 @@
     <t xml:space="preserve">2.07822203636169</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06724286079407</t>
+    <t xml:space="preserve">2.06724262237549</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12998151779175</t>
+    <t xml:space="preserve">2.12998175621033</t>
   </si>
   <si>
     <t xml:space="preserve">2.1158652305603</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05469465255737</t>
+    <t xml:space="preserve">2.05469489097595</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11429715156555</t>
+    <t xml:space="preserve">2.11429691314697</t>
   </si>
   <si>
     <t xml:space="preserve">2.05626344680786</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06410622596741</t>
+    <t xml:space="preserve">2.06410598754883</t>
   </si>
   <si>
     <t xml:space="preserve">2.10488629341125</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00920963287354</t>
+    <t xml:space="preserve">2.00920939445496</t>
   </si>
   <si>
     <t xml:space="preserve">2.0139148235321</t>
@@ -509,55 +509,55 @@
     <t xml:space="preserve">2.16448783874512</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1848783493042</t>
+    <t xml:space="preserve">2.18487811088562</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26643872261047</t>
+    <t xml:space="preserve">2.26643824577332</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27271270751953</t>
+    <t xml:space="preserve">2.27271246910095</t>
   </si>
   <si>
     <t xml:space="preserve">2.2570276260376</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30721855163574</t>
+    <t xml:space="preserve">2.30721879005432</t>
   </si>
   <si>
     <t xml:space="preserve">2.2303638458252</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37152576446533</t>
+    <t xml:space="preserve">2.37152600288391</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35270428657532</t>
+    <t xml:space="preserve">2.35270404815674</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39191651344299</t>
+    <t xml:space="preserve">2.39191603660583</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33545112609863</t>
+    <t xml:space="preserve">2.33545136451721</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3134925365448</t>
+    <t xml:space="preserve">2.31349277496338</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37623143196106</t>
+    <t xml:space="preserve">2.37623167037964</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32917761802673</t>
+    <t xml:space="preserve">2.32917714118958</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24918556213379</t>
+    <t xml:space="preserve">2.24918532371521</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28839683532715</t>
+    <t xml:space="preserve">2.28839707374573</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33701968193054</t>
+    <t xml:space="preserve">2.33701944351196</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34486174583435</t>
+    <t xml:space="preserve">2.34486198425293</t>
   </si>
   <si>
     <t xml:space="preserve">2.34956765174866</t>
@@ -569,25 +569,25 @@
     <t xml:space="preserve">2.30251336097717</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31192421913147</t>
+    <t xml:space="preserve">2.31192445755005</t>
   </si>
   <si>
     <t xml:space="preserve">2.25075364112854</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27428078651428</t>
+    <t xml:space="preserve">2.27428126335144</t>
   </si>
   <si>
     <t xml:space="preserve">2.43897008895874</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48445558547974</t>
+    <t xml:space="preserve">2.48445582389832</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46249723434448</t>
+    <t xml:space="preserve">2.46249747276306</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50798296928406</t>
+    <t xml:space="preserve">2.50798273086548</t>
   </si>
   <si>
     <t xml:space="preserve">2.48602437973022</t>
@@ -608,25 +608,25 @@
     <t xml:space="preserve">2.64287114143372</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65855598449707</t>
+    <t xml:space="preserve">2.65855574607849</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60209131240845</t>
+    <t xml:space="preserve">2.60209107398987</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55033159255981</t>
+    <t xml:space="preserve">2.55033183097839</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63816571235657</t>
+    <t xml:space="preserve">2.63816595077515</t>
   </si>
   <si>
     <t xml:space="preserve">2.58013248443604</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59581685066223</t>
+    <t xml:space="preserve">2.59581708908081</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58170080184937</t>
+    <t xml:space="preserve">2.58170104026794</t>
   </si>
   <si>
     <t xml:space="preserve">2.6036593914032</t>
@@ -638,25 +638,25 @@
     <t xml:space="preserve">2.57542705535889</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57385849952698</t>
+    <t xml:space="preserve">2.57385873794556</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50955104827881</t>
+    <t xml:space="preserve">2.50955152511597</t>
   </si>
   <si>
     <t xml:space="preserve">2.58797478675842</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56444787979126</t>
+    <t xml:space="preserve">2.56444764137268</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61150145530701</t>
+    <t xml:space="preserve">2.61150169372559</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56915307044983</t>
+    <t xml:space="preserve">2.56915330886841</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63502883911133</t>
+    <t xml:space="preserve">2.63502860069275</t>
   </si>
   <si>
     <t xml:space="preserve">2.62561798095703</t>
@@ -665,7 +665,7 @@
     <t xml:space="preserve">2.62718653678894</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83422470092773</t>
+    <t xml:space="preserve">2.83422446250916</t>
   </si>
   <si>
     <t xml:space="preserve">2.79030752182007</t>
@@ -674,16 +674,16 @@
     <t xml:space="preserve">2.77619099617004</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78089666366577</t>
+    <t xml:space="preserve">2.78089618682861</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69149374961853</t>
+    <t xml:space="preserve">2.69149422645569</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7824649810791</t>
+    <t xml:space="preserve">2.78246521949768</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8122661113739</t>
+    <t xml:space="preserve">2.81226587295532</t>
   </si>
   <si>
     <t xml:space="preserve">2.82324528694153</t>
@@ -698,16 +698,16 @@
     <t xml:space="preserve">2.80657124519348</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86433959007263</t>
+    <t xml:space="preserve">2.86433935165405</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81940889358521</t>
+    <t xml:space="preserve">2.81940865516663</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80817604064941</t>
+    <t xml:space="preserve">2.80817627906799</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88038635253906</t>
+    <t xml:space="preserve">2.88038611412048</t>
   </si>
   <si>
     <t xml:space="preserve">2.8338508605957</t>
@@ -716,19 +716,19 @@
     <t xml:space="preserve">2.74398899078369</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72794222831726</t>
+    <t xml:space="preserve">2.72794246673584</t>
   </si>
   <si>
     <t xml:space="preserve">2.70547699928284</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73275637626648</t>
+    <t xml:space="preserve">2.7327561378479</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67177867889404</t>
+    <t xml:space="preserve">2.67177891731262</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62363886833191</t>
+    <t xml:space="preserve">2.62363910675049</t>
   </si>
   <si>
     <t xml:space="preserve">2.61722016334534</t>
@@ -740,13 +740,13 @@
     <t xml:space="preserve">2.62524342536926</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64128994941711</t>
+    <t xml:space="preserve">2.64129066467285</t>
   </si>
   <si>
     <t xml:space="preserve">2.6958487033844</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75040793418884</t>
+    <t xml:space="preserve">2.75040769577026</t>
   </si>
   <si>
     <t xml:space="preserve">2.74719858169556</t>
@@ -755,19 +755,19 @@
     <t xml:space="preserve">2.71991920471191</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72633790969849</t>
+    <t xml:space="preserve">2.72633767127991</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74238443374634</t>
+    <t xml:space="preserve">2.74238467216492</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80015254020691</t>
+    <t xml:space="preserve">2.80015277862549</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78571033477783</t>
+    <t xml:space="preserve">2.78571057319641</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82422232627869</t>
+    <t xml:space="preserve">2.82422256469727</t>
   </si>
   <si>
     <t xml:space="preserve">2.78731560707092</t>
@@ -776,7 +776,7 @@
     <t xml:space="preserve">2.79373407363892</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80496668815613</t>
+    <t xml:space="preserve">2.80496692657471</t>
   </si>
   <si>
     <t xml:space="preserve">2.78410601615906</t>
@@ -788,13 +788,13 @@
     <t xml:space="preserve">2.79533863067627</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82261800765991</t>
+    <t xml:space="preserve">2.82261824607849</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7600359916687</t>
+    <t xml:space="preserve">2.76003623008728</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77929186820984</t>
+    <t xml:space="preserve">2.77929162979126</t>
   </si>
   <si>
     <t xml:space="preserve">2.79854774475098</t>
@@ -809,43 +809,43 @@
     <t xml:space="preserve">2.83545565605164</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8402693271637</t>
+    <t xml:space="preserve">2.84026956558228</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83224630355835</t>
+    <t xml:space="preserve">2.83224606513977</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8113853931427</t>
+    <t xml:space="preserve">2.81138515472412</t>
   </si>
   <si>
     <t xml:space="preserve">2.81619930267334</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76324534416199</t>
+    <t xml:space="preserve">2.76324510574341</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71189570426941</t>
+    <t xml:space="preserve">2.71189618110657</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72473311424255</t>
+    <t xml:space="preserve">2.72473335266113</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79694318771362</t>
+    <t xml:space="preserve">2.79694294929504</t>
   </si>
   <si>
     <t xml:space="preserve">2.79052448272705</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76805901527405</t>
+    <t xml:space="preserve">2.76805925369263</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73115181922913</t>
+    <t xml:space="preserve">2.73115158081055</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7038722038269</t>
+    <t xml:space="preserve">2.70387244224548</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81459474563599</t>
+    <t xml:space="preserve">2.81459450721741</t>
   </si>
   <si>
     <t xml:space="preserve">2.82903647422791</t>
@@ -857,13 +857,13 @@
     <t xml:space="preserve">2.77768731117249</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77126836776733</t>
+    <t xml:space="preserve">2.77126860618591</t>
   </si>
   <si>
     <t xml:space="preserve">2.88840961456299</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87236285209656</t>
+    <t xml:space="preserve">2.87236261367798</t>
   </si>
   <si>
     <t xml:space="preserve">2.89161896705627</t>
@@ -872,37 +872,37 @@
     <t xml:space="preserve">2.92852663993835</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85952544212341</t>
+    <t xml:space="preserve">2.85952520370483</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90927028656006</t>
+    <t xml:space="preserve">2.90927052497864</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99913191795349</t>
+    <t xml:space="preserve">2.99913215637207</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96864295005798</t>
+    <t xml:space="preserve">2.96864318847656</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83064150810242</t>
+    <t xml:space="preserve">2.830641746521</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87878131866455</t>
+    <t xml:space="preserve">2.87878179550171</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87717700004578</t>
+    <t xml:space="preserve">2.8771767616272</t>
   </si>
   <si>
     <t xml:space="preserve">2.87557244300842</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75201225280762</t>
+    <t xml:space="preserve">2.7520124912262</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76164031028748</t>
+    <t xml:space="preserve">2.7616400718689</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7889199256897</t>
+    <t xml:space="preserve">2.78892016410828</t>
   </si>
   <si>
     <t xml:space="preserve">2.67980241775513</t>
@@ -917,46 +917,46 @@
     <t xml:space="preserve">2.8482928276062</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82101321220398</t>
+    <t xml:space="preserve">2.82101345062256</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73436093330383</t>
+    <t xml:space="preserve">2.73436117172241</t>
   </si>
   <si>
     <t xml:space="preserve">2.81780457496643</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7648503780365</t>
+    <t xml:space="preserve">2.76485013961792</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74077963829041</t>
+    <t xml:space="preserve">2.74077987670898</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79212951660156</t>
+    <t xml:space="preserve">2.79212927818298</t>
   </si>
   <si>
     <t xml:space="preserve">2.6637556552887</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60759234428406</t>
+    <t xml:space="preserve">2.60759210586548</t>
   </si>
   <si>
     <t xml:space="preserve">2.55142855644226</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56747531890869</t>
+    <t xml:space="preserve">2.56747508049011</t>
   </si>
   <si>
     <t xml:space="preserve">2.59956860542297</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55945181846619</t>
+    <t xml:space="preserve">2.55945205688477</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50328803062439</t>
+    <t xml:space="preserve">2.50328826904297</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45514798164368</t>
+    <t xml:space="preserve">2.45514822006226</t>
   </si>
   <si>
     <t xml:space="preserve">2.47921800613403</t>
@@ -965,7 +965,7 @@
     <t xml:space="preserve">2.47119474411011</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43107771873474</t>
+    <t xml:space="preserve">2.43107795715332</t>
   </si>
   <si>
     <t xml:space="preserve">2.46317172050476</t>
@@ -980,22 +980,22 @@
     <t xml:space="preserve">2.52735829353333</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58352184295654</t>
+    <t xml:space="preserve">2.58352208137512</t>
   </si>
   <si>
     <t xml:space="preserve">2.65573215484619</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91247987747192</t>
+    <t xml:space="preserve">2.91247963905334</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82002472877502</t>
+    <t xml:space="preserve">2.8200249671936</t>
   </si>
   <si>
     <t xml:space="preserve">2.80358171463013</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86935472488403</t>
+    <t xml:space="preserve">2.86935496330261</t>
   </si>
   <si>
     <t xml:space="preserve">2.84468984603882</t>
@@ -1010,22 +1010,22 @@
     <t xml:space="preserve">2.72136497497559</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68025708198547</t>
+    <t xml:space="preserve">2.68025660514832</t>
   </si>
   <si>
     <t xml:space="preserve">2.69670009613037</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64737010002136</t>
+    <t xml:space="preserve">2.64737033843994</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65559196472168</t>
+    <t xml:space="preserve">2.65559220314026</t>
   </si>
   <si>
     <t xml:space="preserve">2.66381359100342</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63092708587646</t>
+    <t xml:space="preserve">2.63092684745789</t>
   </si>
   <si>
     <t xml:space="preserve">2.6391487121582</t>
@@ -1040,7 +1040,7 @@
     <t xml:space="preserve">2.5487105846405</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46649384498596</t>
+    <t xml:space="preserve">2.46649408340454</t>
   </si>
   <si>
     <t xml:space="preserve">2.60626220703125</t>
@@ -1058,58 +1058,58 @@
     <t xml:space="preserve">2.58981871604919</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62270522117615</t>
+    <t xml:space="preserve">2.62270545959473</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51582384109497</t>
+    <t xml:space="preserve">2.51582407951355</t>
   </si>
   <si>
     <t xml:space="preserve">2.57337546348572</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5651535987854</t>
+    <t xml:space="preserve">2.56515383720398</t>
   </si>
   <si>
     <t xml:space="preserve">2.53226709365845</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47471570968628</t>
+    <t xml:space="preserve">2.47471594810486</t>
   </si>
   <si>
     <t xml:space="preserve">2.48293733596802</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45005083084106</t>
+    <t xml:space="preserve">2.45005059242249</t>
   </si>
   <si>
     <t xml:space="preserve">2.44182920455933</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42538595199585</t>
+    <t xml:space="preserve">2.42538619041443</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43360781669617</t>
+    <t xml:space="preserve">2.43360733985901</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49115872383118</t>
+    <t xml:space="preserve">2.49115896224976</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50760245323181</t>
+    <t xml:space="preserve">2.50760221481323</t>
   </si>
   <si>
     <t xml:space="preserve">2.54048871994019</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67203545570374</t>
+    <t xml:space="preserve">2.67203521728516</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68847870826721</t>
+    <t xml:space="preserve">2.68847894668579</t>
   </si>
   <si>
     <t xml:space="preserve">2.70492196083069</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71314358711243</t>
+    <t xml:space="preserve">2.71314334869385</t>
   </si>
   <si>
     <t xml:space="preserve">2.75425171852112</t>
@@ -1118,7 +1118,7 @@
     <t xml:space="preserve">2.78713846206665</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77069473266602</t>
+    <t xml:space="preserve">2.77069497108459</t>
   </si>
   <si>
     <t xml:space="preserve">2.7295868396759</t>
@@ -1127,52 +1127,52 @@
     <t xml:space="preserve">2.74603009223938</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77891659736633</t>
+    <t xml:space="preserve">2.77891707420349</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79535984992981</t>
+    <t xml:space="preserve">2.79536008834839</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87757635116577</t>
+    <t xml:space="preserve">2.87757658958435</t>
   </si>
   <si>
     <t xml:space="preserve">2.91868472099304</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89401936531067</t>
+    <t xml:space="preserve">2.89401960372925</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86113333702087</t>
+    <t xml:space="preserve">2.86113309860229</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90224146842957</t>
+    <t xml:space="preserve">2.90224123001099</t>
   </si>
   <si>
     <t xml:space="preserve">2.88579797744751</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8364679813385</t>
+    <t xml:space="preserve">2.83646821975708</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94334959983826</t>
+    <t xml:space="preserve">2.94334936141968</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82824659347534</t>
+    <t xml:space="preserve">2.82824683189392</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92690634727478</t>
+    <t xml:space="preserve">2.9269061088562</t>
   </si>
   <si>
     <t xml:space="preserve">2.80358147621155</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77809453010559</t>
+    <t xml:space="preserve">2.77809476852417</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82057285308838</t>
+    <t xml:space="preserve">2.82057309150696</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8290684223175</t>
+    <t xml:space="preserve">2.82906866073608</t>
   </si>
   <si>
     <t xml:space="preserve">2.88853859901428</t>
@@ -1181,31 +1181,31 @@
     <t xml:space="preserve">2.88004302978516</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92252135276794</t>
+    <t xml:space="preserve">2.92252159118652</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90552997589111</t>
+    <t xml:space="preserve">2.90552973747253</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87154698371887</t>
+    <t xml:space="preserve">2.87154746055603</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85455560684204</t>
+    <t xml:space="preserve">2.85455536842346</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91402554512024</t>
+    <t xml:space="preserve">2.91402578353882</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93101692199707</t>
+    <t xml:space="preserve">2.93101716041565</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9480082988739</t>
+    <t xml:space="preserve">2.94800853729248</t>
   </si>
   <si>
     <t xml:space="preserve">2.89703440666199</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93951296806335</t>
+    <t xml:space="preserve">2.93951272964478</t>
   </si>
   <si>
     <t xml:space="preserve">2.98199105262756</t>
@@ -1217,10 +1217,10 @@
     <t xml:space="preserve">2.78659009933472</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76110315322876</t>
+    <t xml:space="preserve">2.76110291481018</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76959872245789</t>
+    <t xml:space="preserve">2.76959848403931</t>
   </si>
   <si>
     <t xml:space="preserve">2.81207704544067</t>
@@ -1241,13 +1241,10 @@
     <t xml:space="preserve">2.61667585372925</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55720615386963</t>
+    <t xml:space="preserve">2.55720639228821</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54871034622192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51472783088684</t>
+    <t xml:space="preserve">2.51472759246826</t>
   </si>
   <si>
     <t xml:space="preserve">2.49773621559143</t>
@@ -1256,22 +1253,22 @@
     <t xml:space="preserve">2.4807448387146</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53171920776367</t>
+    <t xml:space="preserve">2.53171896934509</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46375322341919</t>
+    <t xml:space="preserve">2.46375346183777</t>
   </si>
   <si>
     <t xml:space="preserve">2.58269309997559</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54021453857422</t>
+    <t xml:space="preserve">2.5402147769928</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56570196151733</t>
+    <t xml:space="preserve">2.56570172309875</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59118914604187</t>
+    <t xml:space="preserve">2.59118890762329</t>
   </si>
   <si>
     <t xml:space="preserve">2.47224926948547</t>
@@ -1283,28 +1280,28 @@
     <t xml:space="preserve">2.599684715271</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52322363853455</t>
+    <t xml:space="preserve">2.52322340011597</t>
   </si>
   <si>
     <t xml:space="preserve">2.57419753074646</t>
   </si>
   <si>
-    <t xml:space="preserve">3.075443983078</t>
+    <t xml:space="preserve">3.07544374465942</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0074782371521</t>
+    <t xml:space="preserve">3.00747847557068</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99048662185669</t>
+    <t xml:space="preserve">2.99048686027527</t>
   </si>
   <si>
     <t xml:space="preserve">2.96499991416931</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97349548339844</t>
+    <t xml:space="preserve">2.97349572181702</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95650434494019</t>
+    <t xml:space="preserve">2.95650410652161</t>
   </si>
   <si>
     <t xml:space="preserve">2.84606003761292</t>
@@ -1316,25 +1313,25 @@
     <t xml:space="preserve">2.66765022277832</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65915441513062</t>
+    <t xml:space="preserve">2.65915465354919</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31083106994629</t>
+    <t xml:space="preserve">2.31083083152771</t>
   </si>
   <si>
     <t xml:space="preserve">2.35330939292908</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34481358528137</t>
+    <t xml:space="preserve">2.34481334686279</t>
   </si>
   <si>
     <t xml:space="preserve">2.45525789260864</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4892406463623</t>
+    <t xml:space="preserve">2.48924040794373</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65065860748291</t>
+    <t xml:space="preserve">2.65065884590149</t>
   </si>
   <si>
     <t xml:space="preserve">2.64216327667236</t>
@@ -1343,13 +1340,13 @@
     <t xml:space="preserve">2.71012878417969</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69313740730286</t>
+    <t xml:space="preserve">2.69313764572144</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71862459182739</t>
+    <t xml:space="preserve">2.71862435340881</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74411153793335</t>
+    <t xml:space="preserve">2.74411177635193</t>
   </si>
   <si>
     <t xml:space="preserve">2.68464183807373</t>
@@ -1358,16 +1355,16 @@
     <t xml:space="preserve">2.6081805229187</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50623178482056</t>
+    <t xml:space="preserve">2.50623226165771</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44676232337952</t>
+    <t xml:space="preserve">2.44676184654236</t>
   </si>
   <si>
     <t xml:space="preserve">2.37879633903503</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42977070808411</t>
+    <t xml:space="preserve">2.42977046966553</t>
   </si>
   <si>
     <t xml:space="preserve">2.37030076980591</t>
@@ -1376,7 +1373,7 @@
     <t xml:space="preserve">2.31932640075684</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27684807777405</t>
+    <t xml:space="preserve">2.27684783935547</t>
   </si>
   <si>
     <t xml:space="preserve">2.26835250854492</t>
@@ -1385,37 +1382,37 @@
     <t xml:space="preserve">2.30233502388</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33631777763367</t>
+    <t xml:space="preserve">2.33631801605225</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39578771591187</t>
+    <t xml:space="preserve">2.39578747749329</t>
   </si>
   <si>
     <t xml:space="preserve">2.72712016105652</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99898266792297</t>
+    <t xml:space="preserve">2.99898242950439</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03296542167664</t>
+    <t xml:space="preserve">3.03296518325806</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01597428321838</t>
+    <t xml:space="preserve">3.0159740447998</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04146122932434</t>
+    <t xml:space="preserve">3.04146099090576</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19438409805298</t>
+    <t xml:space="preserve">3.1943838596344</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12641835212708</t>
+    <t xml:space="preserve">3.1264181137085</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05845236778259</t>
+    <t xml:space="preserve">3.05845260620117</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09243535995483</t>
+    <t xml:space="preserve">3.09243559837341</t>
   </si>
   <si>
     <t xml:space="preserve">3.16040110588074</t>
@@ -1424,16 +1421,16 @@
     <t xml:space="preserve">3.21137523651123</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3133237361908</t>
+    <t xml:space="preserve">3.31332349777222</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26234912872314</t>
+    <t xml:space="preserve">3.26234936714172</t>
   </si>
   <si>
     <t xml:space="preserve">3.33031511306763</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22836637496948</t>
+    <t xml:space="preserve">3.22836661338806</t>
   </si>
   <si>
     <t xml:space="preserve">3.17739224433899</t>
@@ -1442,13 +1439,13 @@
     <t xml:space="preserve">3.14340949058533</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10942673683167</t>
+    <t xml:space="preserve">3.10942697525024</t>
   </si>
   <si>
     <t xml:space="preserve">3.27934074401855</t>
   </si>
   <si>
-    <t xml:space="preserve">3.48323750495911</t>
+    <t xml:space="preserve">3.48323774337769</t>
   </si>
   <si>
     <t xml:space="preserve">3.39828062057495</t>
@@ -1463,22 +1460,22 @@
     <t xml:space="preserve">3.34730648994446</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24535775184631</t>
+    <t xml:space="preserve">3.24535799026489</t>
   </si>
   <si>
     <t xml:space="preserve">3.02446961402893</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16417121887207</t>
+    <t xml:space="preserve">3.16417145729065</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05022621154785</t>
+    <t xml:space="preserve">3.05022597312927</t>
   </si>
   <si>
     <t xml:space="preserve">3.05899119377136</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01516604423523</t>
+    <t xml:space="preserve">3.01516628265381</t>
   </si>
   <si>
     <t xml:space="preserve">2.97134113311768</t>
@@ -1487,7 +1484,7 @@
     <t xml:space="preserve">3.02393102645874</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10281610488892</t>
+    <t xml:space="preserve">3.1028163433075</t>
   </si>
   <si>
     <t xml:space="preserve">3.13787627220154</t>
@@ -1502,10 +1499,13 @@
     <t xml:space="preserve">3.07652115821838</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06775617599487</t>
+    <t xml:space="preserve">3.06775641441345</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00640106201172</t>
+    <t xml:space="preserve">3.04146122932434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0064013004303</t>
   </si>
   <si>
     <t xml:space="preserve">2.9888710975647</t>
@@ -1535,10 +1535,10 @@
     <t xml:space="preserve">2.82233572006226</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94504594802856</t>
+    <t xml:space="preserve">2.94504570960999</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95381093025208</t>
+    <t xml:space="preserve">2.9538106918335</t>
   </si>
   <si>
     <t xml:space="preserve">2.83110070228577</t>
@@ -1562,10 +1562,10 @@
     <t xml:space="preserve">2.81357073783875</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83986568450928</t>
+    <t xml:space="preserve">2.83986592292786</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68209528923035</t>
+    <t xml:space="preserve">2.68209552764893</t>
   </si>
   <si>
     <t xml:space="preserve">2.69086050987244</t>
@@ -1574,28 +1574,28 @@
     <t xml:space="preserve">2.66456532478333</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85739588737488</t>
+    <t xml:space="preserve">2.8573956489563</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90998578071594</t>
+    <t xml:space="preserve">2.90998601913452</t>
   </si>
   <si>
     <t xml:space="preserve">2.7785108089447</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76974582672119</t>
+    <t xml:space="preserve">2.76974558830261</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79604077339172</t>
+    <t xml:space="preserve">2.79604053497314</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84863090515137</t>
+    <t xml:space="preserve">2.84863066673279</t>
   </si>
   <si>
     <t xml:space="preserve">3.08528614044189</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76098036766052</t>
+    <t xml:space="preserve">2.7609806060791</t>
   </si>
   <si>
     <t xml:space="preserve">2.78727579116821</t>
@@ -1622,34 +1622,34 @@
     <t xml:space="preserve">2.83221411705017</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8870313167572</t>
+    <t xml:space="preserve">2.88703107833862</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85048627853394</t>
+    <t xml:space="preserve">2.85048651695251</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96012043952942</t>
+    <t xml:space="preserve">2.960120677948</t>
   </si>
   <si>
     <t xml:space="preserve">2.99666523933411</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79566955566406</t>
+    <t xml:space="preserve">2.79566931724548</t>
   </si>
   <si>
     <t xml:space="preserve">2.81394171714783</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77739691734314</t>
+    <t xml:space="preserve">2.77739715576172</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75912475585938</t>
+    <t xml:space="preserve">2.7591245174408</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70430779457092</t>
+    <t xml:space="preserve">2.70430755615234</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64949083328247</t>
+    <t xml:space="preserve">2.64949059486389</t>
   </si>
   <si>
     <t xml:space="preserve">2.68603539466858</t>
@@ -1667,16 +1667,16 @@
     <t xml:space="preserve">2.72258019447327</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59467339515686</t>
+    <t xml:space="preserve">2.59467363357544</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5764012336731</t>
+    <t xml:space="preserve">2.57640099525452</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61294603347778</t>
+    <t xml:space="preserve">2.6129457950592</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97839307785034</t>
+    <t xml:space="preserve">2.97839283943176</t>
   </si>
   <si>
     <t xml:space="preserve">2.823077917099</t>
@@ -1697,7 +1697,7 @@
     <t xml:space="preserve">3.01493763923645</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96925687789917</t>
+    <t xml:space="preserve">2.96925663948059</t>
   </si>
   <si>
     <t xml:space="preserve">3.02674722671509</t>
@@ -1794,6 +1794,9 @@
   </si>
   <si>
     <t xml:space="preserve">3.23614478111267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96012043952942</t>
   </si>
   <si>
     <t xml:space="preserve">3.20000004768372</t>
@@ -1962,6 +1965,9 @@
   </si>
   <si>
     <t xml:space="preserve">3.77999997138977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85999989509583</t>
   </si>
 </sst>
 </file>
@@ -26160,7 +26166,7 @@
         <v>3</v>
       </c>
       <c r="G918" t="s">
-        <v>410</v>
+        <v>341</v>
       </c>
       <c r="H918" t="s">
         <v>9</v>
@@ -26186,7 +26192,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G919" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H919" t="s">
         <v>9</v>
@@ -26212,7 +26218,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G920" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="H920" t="s">
         <v>9</v>
@@ -26238,7 +26244,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G921" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H921" t="s">
         <v>9</v>
@@ -26264,7 +26270,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G922" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H922" t="s">
         <v>9</v>
@@ -26316,7 +26322,7 @@
         <v>3</v>
       </c>
       <c r="G924" t="s">
-        <v>410</v>
+        <v>341</v>
       </c>
       <c r="H924" t="s">
         <v>9</v>
@@ -26342,7 +26348,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G925" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H925" t="s">
         <v>9</v>
@@ -26368,7 +26374,7 @@
         <v>3</v>
       </c>
       <c r="G926" t="s">
-        <v>410</v>
+        <v>341</v>
       </c>
       <c r="H926" t="s">
         <v>9</v>
@@ -26394,7 +26400,7 @@
         <v>3</v>
       </c>
       <c r="G927" t="s">
-        <v>410</v>
+        <v>341</v>
       </c>
       <c r="H927" t="s">
         <v>9</v>
@@ -26420,7 +26426,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G928" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H928" t="s">
         <v>9</v>
@@ -26446,7 +26452,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G929" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H929" t="s">
         <v>9</v>
@@ -26472,7 +26478,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G930" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H930" t="s">
         <v>9</v>
@@ -26498,7 +26504,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G931" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H931" t="s">
         <v>9</v>
@@ -26524,7 +26530,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G932" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H932" t="s">
         <v>9</v>
@@ -26550,7 +26556,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G933" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="H933" t="s">
         <v>9</v>
@@ -26576,7 +26582,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G934" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="H934" t="s">
         <v>9</v>
@@ -26602,7 +26608,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G935" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="H935" t="s">
         <v>9</v>
@@ -26680,7 +26686,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G938" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="H938" t="s">
         <v>9</v>
@@ -26706,7 +26712,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G939" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H939" t="s">
         <v>9</v>
@@ -26732,7 +26738,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G940" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="H940" t="s">
         <v>9</v>
@@ -26758,7 +26764,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G941" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="H941" t="s">
         <v>9</v>
@@ -26784,7 +26790,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G942" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H942" t="s">
         <v>9</v>
@@ -26810,7 +26816,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G943" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H943" t="s">
         <v>9</v>
@@ -26836,7 +26842,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G944" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H944" t="s">
         <v>9</v>
@@ -26862,7 +26868,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G945" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H945" t="s">
         <v>9</v>
@@ -26888,7 +26894,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G946" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H946" t="s">
         <v>9</v>
@@ -26914,7 +26920,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G947" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="H947" t="s">
         <v>9</v>
@@ -26940,7 +26946,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G948" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="H948" t="s">
         <v>9</v>
@@ -26966,7 +26972,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G949" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H949" t="s">
         <v>9</v>
@@ -26992,7 +26998,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G950" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="H950" t="s">
         <v>9</v>
@@ -27018,7 +27024,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G951" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="H951" t="s">
         <v>9</v>
@@ -27044,7 +27050,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G952" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H952" t="s">
         <v>9</v>
@@ -27070,7 +27076,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G953" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H953" t="s">
         <v>9</v>
@@ -27096,7 +27102,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G954" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H954" t="s">
         <v>9</v>
@@ -27122,7 +27128,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G955" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H955" t="s">
         <v>9</v>
@@ -27148,7 +27154,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G956" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="H956" t="s">
         <v>9</v>
@@ -27174,7 +27180,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G957" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="H957" t="s">
         <v>9</v>
@@ -27200,7 +27206,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G958" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H958" t="s">
         <v>9</v>
@@ -27226,7 +27232,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G959" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H959" t="s">
         <v>9</v>
@@ -27252,7 +27258,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G960" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H960" t="s">
         <v>9</v>
@@ -27278,7 +27284,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G961" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H961" t="s">
         <v>9</v>
@@ -27304,7 +27310,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G962" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="H962" t="s">
         <v>9</v>
@@ -27330,7 +27336,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G963" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="H963" t="s">
         <v>9</v>
@@ -27434,7 +27440,7 @@
         <v>3</v>
       </c>
       <c r="G967" t="s">
-        <v>410</v>
+        <v>341</v>
       </c>
       <c r="H967" t="s">
         <v>9</v>
@@ -27460,7 +27466,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G968" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="H968" t="s">
         <v>9</v>
@@ -27486,7 +27492,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G969" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="H969" t="s">
         <v>9</v>
@@ -27512,7 +27518,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G970" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H970" t="s">
         <v>9</v>
@@ -27538,7 +27544,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G971" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H971" t="s">
         <v>9</v>
@@ -27564,7 +27570,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G972" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="H972" t="s">
         <v>9</v>
@@ -27694,7 +27700,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G977" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H977" t="s">
         <v>9</v>
@@ -27720,7 +27726,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G978" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H978" t="s">
         <v>9</v>
@@ -27746,7 +27752,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G979" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H979" t="s">
         <v>9</v>
@@ -27772,7 +27778,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G980" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H980" t="s">
         <v>9</v>
@@ -27798,7 +27804,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G981" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H981" t="s">
         <v>9</v>
@@ -27876,7 +27882,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G984" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="H984" t="s">
         <v>9</v>
@@ -27928,7 +27934,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G986" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="H986" t="s">
         <v>9</v>
@@ -27980,7 +27986,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G988" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="H988" t="s">
         <v>9</v>
@@ -28890,7 +28896,7 @@
         <v>3.5</v>
       </c>
       <c r="G1023" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="H1023" t="s">
         <v>9</v>
@@ -28916,7 +28922,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1024" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="H1024" t="s">
         <v>9</v>
@@ -29072,7 +29078,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1030" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="H1030" t="s">
         <v>9</v>
@@ -29098,7 +29104,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1031" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="H1031" t="s">
         <v>9</v>
@@ -29306,7 +29312,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G1039" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="H1039" t="s">
         <v>9</v>
@@ -29332,7 +29338,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1040" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="H1040" t="s">
         <v>9</v>
@@ -29358,7 +29364,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G1041" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="H1041" t="s">
         <v>9</v>
@@ -29384,7 +29390,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1042" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="H1042" t="s">
         <v>9</v>
@@ -29566,7 +29572,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G1049" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="H1049" t="s">
         <v>9</v>
@@ -29592,7 +29598,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1050" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="H1050" t="s">
         <v>9</v>
@@ -29852,7 +29858,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1060" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="H1060" t="s">
         <v>9</v>
@@ -29878,7 +29884,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G1061" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="H1061" t="s">
         <v>9</v>
@@ -29904,7 +29910,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G1062" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="H1062" t="s">
         <v>9</v>
@@ -29930,7 +29936,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G1063" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="H1063" t="s">
         <v>9</v>
@@ -29956,7 +29962,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G1064" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H1064" t="s">
         <v>9</v>
@@ -29982,7 +29988,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1065" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H1065" t="s">
         <v>9</v>
@@ -30008,7 +30014,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G1066" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="H1066" t="s">
         <v>9</v>
@@ -30034,7 +30040,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G1067" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="H1067" t="s">
         <v>9</v>
@@ -30060,7 +30066,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G1068" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="H1068" t="s">
         <v>9</v>
@@ -30086,7 +30092,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G1069" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="H1069" t="s">
         <v>9</v>
@@ -30112,7 +30118,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G1070" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="H1070" t="s">
         <v>9</v>
@@ -30138,7 +30144,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G1071" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="H1071" t="s">
         <v>9</v>
@@ -30164,7 +30170,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1072" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="H1072" t="s">
         <v>9</v>
@@ -30190,7 +30196,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1073" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="H1073" t="s">
         <v>9</v>
@@ -30216,7 +30222,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1074" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H1074" t="s">
         <v>9</v>
@@ -30242,7 +30248,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G1075" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H1075" t="s">
         <v>9</v>
@@ -30268,7 +30274,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G1076" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="H1076" t="s">
         <v>9</v>
@@ -30294,7 +30300,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G1077" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H1077" t="s">
         <v>9</v>
@@ -30320,7 +30326,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G1078" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H1078" t="s">
         <v>9</v>
@@ -30346,7 +30352,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1079" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="H1079" t="s">
         <v>9</v>
@@ -30398,7 +30404,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G1081" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H1081" t="s">
         <v>9</v>
@@ -30424,7 +30430,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G1082" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="H1082" t="s">
         <v>9</v>
@@ -30450,7 +30456,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1083" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="H1083" t="s">
         <v>9</v>
@@ -30476,7 +30482,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G1084" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="H1084" t="s">
         <v>9</v>
@@ -30502,7 +30508,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G1085" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="H1085" t="s">
         <v>9</v>
@@ -30528,7 +30534,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G1086" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="H1086" t="s">
         <v>9</v>
@@ -30554,7 +30560,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G1087" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="H1087" t="s">
         <v>9</v>
@@ -30580,7 +30586,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1088" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H1088" t="s">
         <v>9</v>
@@ -30606,7 +30612,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G1089" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="H1089" t="s">
         <v>9</v>
@@ -30632,7 +30638,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G1090" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="H1090" t="s">
         <v>9</v>
@@ -30684,7 +30690,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G1092" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="H1092" t="s">
         <v>9</v>
@@ -30710,7 +30716,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G1093" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="H1093" t="s">
         <v>9</v>
@@ -30762,7 +30768,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G1095" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="H1095" t="s">
         <v>9</v>
@@ -30788,7 +30794,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1096" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="H1096" t="s">
         <v>9</v>
@@ -30944,7 +30950,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G1102" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="H1102" t="s">
         <v>9</v>
@@ -30970,7 +30976,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G1103" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="H1103" t="s">
         <v>9</v>
@@ -30996,7 +31002,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G1104" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="H1104" t="s">
         <v>9</v>
@@ -31022,7 +31028,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G1105" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="H1105" t="s">
         <v>9</v>
@@ -31048,7 +31054,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G1106" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="H1106" t="s">
         <v>9</v>
@@ -31074,7 +31080,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1107" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="H1107" t="s">
         <v>9</v>
@@ -31100,7 +31106,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1108" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="H1108" t="s">
         <v>9</v>
@@ -31126,7 +31132,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G1109" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H1109" t="s">
         <v>9</v>
@@ -31152,7 +31158,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G1110" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="H1110" t="s">
         <v>9</v>
@@ -31178,7 +31184,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G1111" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H1111" t="s">
         <v>9</v>
@@ -31204,7 +31210,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G1112" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H1112" t="s">
         <v>9</v>
@@ -31256,7 +31262,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1114" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="H1114" t="s">
         <v>9</v>
@@ -31282,7 +31288,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1115" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="H1115" t="s">
         <v>9</v>
@@ -31308,7 +31314,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1116" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="H1116" t="s">
         <v>9</v>
@@ -31334,7 +31340,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1117" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="H1117" t="s">
         <v>9</v>
@@ -31360,7 +31366,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1118" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="H1118" t="s">
         <v>9</v>
@@ -31386,7 +31392,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G1119" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H1119" t="s">
         <v>9</v>
@@ -31412,7 +31418,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1120" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="H1120" t="s">
         <v>9</v>
@@ -31438,7 +31444,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1121" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="H1121" t="s">
         <v>9</v>
@@ -31464,7 +31470,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G1122" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H1122" t="s">
         <v>9</v>
@@ -31490,7 +31496,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1123" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="H1123" t="s">
         <v>9</v>
@@ -31516,7 +31522,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1124" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H1124" t="s">
         <v>9</v>
@@ -31542,7 +31548,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G1125" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H1125" t="s">
         <v>9</v>
@@ -31568,7 +31574,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1126" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H1126" t="s">
         <v>9</v>
@@ -31620,7 +31626,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1128" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H1128" t="s">
         <v>9</v>
@@ -31698,7 +31704,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G1131" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="H1131" t="s">
         <v>9</v>
@@ -31724,7 +31730,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G1132" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="H1132" t="s">
         <v>9</v>
@@ -31750,7 +31756,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1133" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H1133" t="s">
         <v>9</v>
@@ -31776,7 +31782,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1134" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="H1134" t="s">
         <v>9</v>
@@ -31802,7 +31808,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1135" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H1135" t="s">
         <v>9</v>
@@ -31828,7 +31834,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1136" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H1136" t="s">
         <v>9</v>
@@ -31906,7 +31912,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G1139" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H1139" t="s">
         <v>9</v>
@@ -31932,7 +31938,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G1140" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H1140" t="s">
         <v>9</v>
@@ -31958,7 +31964,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G1141" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H1141" t="s">
         <v>9</v>
@@ -31984,7 +31990,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G1142" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H1142" t="s">
         <v>9</v>
@@ -32010,7 +32016,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G1143" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="H1143" t="s">
         <v>9</v>
@@ -32036,7 +32042,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G1144" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="H1144" t="s">
         <v>9</v>
@@ -32062,7 +32068,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G1145" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="H1145" t="s">
         <v>9</v>
@@ -32088,7 +32094,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G1146" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H1146" t="s">
         <v>9</v>
@@ -32114,7 +32120,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G1147" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="H1147" t="s">
         <v>9</v>
@@ -32140,7 +32146,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G1148" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="H1148" t="s">
         <v>9</v>
@@ -32166,7 +32172,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G1149" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H1149" t="s">
         <v>9</v>
@@ -32192,7 +32198,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G1150" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="H1150" t="s">
         <v>9</v>
@@ -32218,7 +32224,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G1151" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H1151" t="s">
         <v>9</v>
@@ -32244,7 +32250,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1152" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="H1152" t="s">
         <v>9</v>
@@ -32270,7 +32276,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G1153" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="H1153" t="s">
         <v>9</v>
@@ -32296,7 +32302,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G1154" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="H1154" t="s">
         <v>9</v>
@@ -32322,7 +32328,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G1155" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="H1155" t="s">
         <v>9</v>
@@ -32348,7 +32354,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G1156" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H1156" t="s">
         <v>9</v>
@@ -32452,7 +32458,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G1160" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="H1160" t="s">
         <v>9</v>
@@ -32478,7 +32484,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G1161" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="H1161" t="s">
         <v>9</v>
@@ -32504,7 +32510,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G1162" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="H1162" t="s">
         <v>9</v>
@@ -32530,7 +32536,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G1163" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H1163" t="s">
         <v>9</v>
@@ -32556,7 +32562,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G1164" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H1164" t="s">
         <v>9</v>
@@ -32582,7 +32588,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G1165" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="H1165" t="s">
         <v>9</v>
@@ -32608,7 +32614,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G1166" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H1166" t="s">
         <v>9</v>
@@ -32634,7 +32640,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G1167" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H1167" t="s">
         <v>9</v>
@@ -32660,7 +32666,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G1168" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H1168" t="s">
         <v>9</v>
@@ -32686,7 +32692,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G1169" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H1169" t="s">
         <v>9</v>
@@ -32712,7 +32718,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1170" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H1170" t="s">
         <v>9</v>
@@ -32738,7 +32744,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G1171" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H1171" t="s">
         <v>9</v>
@@ -32764,7 +32770,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1172" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H1172" t="s">
         <v>9</v>
@@ -32790,7 +32796,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G1173" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H1173" t="s">
         <v>9</v>
@@ -32816,7 +32822,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G1174" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H1174" t="s">
         <v>9</v>
@@ -32842,7 +32848,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G1175" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H1175" t="s">
         <v>9</v>
@@ -32868,7 +32874,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G1176" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H1176" t="s">
         <v>9</v>
@@ -32894,7 +32900,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G1177" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="H1177" t="s">
         <v>9</v>
@@ -32972,7 +32978,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G1180" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="H1180" t="s">
         <v>9</v>
@@ -32998,7 +33004,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G1181" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="H1181" t="s">
         <v>9</v>
@@ -33128,7 +33134,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G1186" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="H1186" t="s">
         <v>9</v>
@@ -33154,7 +33160,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G1187" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="H1187" t="s">
         <v>9</v>
@@ -33180,7 +33186,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G1188" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="H1188" t="s">
         <v>9</v>
@@ -33232,7 +33238,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G1190" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H1190" t="s">
         <v>9</v>
@@ -33258,7 +33264,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G1191" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="H1191" t="s">
         <v>9</v>
@@ -33284,7 +33290,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G1192" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="H1192" t="s">
         <v>9</v>
@@ -33310,7 +33316,7 @@
         <v>3</v>
       </c>
       <c r="G1193" t="s">
-        <v>410</v>
+        <v>341</v>
       </c>
       <c r="H1193" t="s">
         <v>9</v>
@@ -33336,7 +33342,7 @@
         <v>3</v>
       </c>
       <c r="G1194" t="s">
-        <v>410</v>
+        <v>341</v>
       </c>
       <c r="H1194" t="s">
         <v>9</v>
@@ -33362,7 +33368,7 @@
         <v>3</v>
       </c>
       <c r="G1195" t="s">
-        <v>410</v>
+        <v>341</v>
       </c>
       <c r="H1195" t="s">
         <v>9</v>
@@ -33388,7 +33394,7 @@
         <v>3</v>
       </c>
       <c r="G1196" t="s">
-        <v>410</v>
+        <v>341</v>
       </c>
       <c r="H1196" t="s">
         <v>9</v>
@@ -33414,7 +33420,7 @@
         <v>3</v>
       </c>
       <c r="G1197" t="s">
-        <v>410</v>
+        <v>341</v>
       </c>
       <c r="H1197" t="s">
         <v>9</v>
@@ -33440,7 +33446,7 @@
         <v>3</v>
       </c>
       <c r="G1198" t="s">
-        <v>410</v>
+        <v>341</v>
       </c>
       <c r="H1198" t="s">
         <v>9</v>
@@ -33466,7 +33472,7 @@
         <v>3</v>
       </c>
       <c r="G1199" t="s">
-        <v>410</v>
+        <v>341</v>
       </c>
       <c r="H1199" t="s">
         <v>9</v>
@@ -33492,7 +33498,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G1200" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H1200" t="s">
         <v>9</v>
@@ -33518,7 +33524,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G1201" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H1201" t="s">
         <v>9</v>
@@ -33544,7 +33550,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G1202" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H1202" t="s">
         <v>9</v>
@@ -33570,7 +33576,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G1203" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H1203" t="s">
         <v>9</v>
@@ -33596,7 +33602,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G1204" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="H1204" t="s">
         <v>9</v>
@@ -33622,7 +33628,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G1205" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="H1205" t="s">
         <v>9</v>
@@ -33648,7 +33654,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G1206" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="H1206" t="s">
         <v>9</v>
@@ -33674,7 +33680,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G1207" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="H1207" t="s">
         <v>9</v>
@@ -33700,7 +33706,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G1208" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="H1208" t="s">
         <v>9</v>
@@ -33726,7 +33732,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G1209" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="H1209" t="s">
         <v>9</v>
@@ -33752,7 +33758,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G1210" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="H1210" t="s">
         <v>9</v>
@@ -33778,7 +33784,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G1211" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="H1211" t="s">
         <v>9</v>
@@ -33804,7 +33810,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G1212" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="H1212" t="s">
         <v>9</v>
@@ -33830,7 +33836,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G1213" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="H1213" t="s">
         <v>9</v>
@@ -33856,7 +33862,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1214" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H1214" t="s">
         <v>9</v>
@@ -33882,7 +33888,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1215" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H1215" t="s">
         <v>9</v>
@@ -33908,7 +33914,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G1216" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="H1216" t="s">
         <v>9</v>
@@ -33934,7 +33940,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G1217" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="H1217" t="s">
         <v>9</v>
@@ -33960,7 +33966,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G1218" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="H1218" t="s">
         <v>9</v>
@@ -33986,7 +33992,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G1219" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="H1219" t="s">
         <v>9</v>
@@ -34012,7 +34018,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G1220" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="H1220" t="s">
         <v>9</v>
@@ -34038,7 +34044,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G1221" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="H1221" t="s">
         <v>9</v>
@@ -34064,7 +34070,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G1222" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="H1222" t="s">
         <v>9</v>
@@ -34090,7 +34096,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G1223" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="H1223" t="s">
         <v>9</v>
@@ -34116,7 +34122,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G1224" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="H1224" t="s">
         <v>9</v>
@@ -34142,7 +34148,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G1225" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="H1225" t="s">
         <v>9</v>
@@ -34168,7 +34174,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G1226" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="H1226" t="s">
         <v>9</v>
@@ -34194,7 +34200,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G1227" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="H1227" t="s">
         <v>9</v>
@@ -34220,7 +34226,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G1228" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="H1228" t="s">
         <v>9</v>
@@ -34246,7 +34252,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G1229" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="H1229" t="s">
         <v>9</v>
@@ -34272,7 +34278,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G1230" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="H1230" t="s">
         <v>9</v>
@@ -34298,7 +34304,7 @@
         <v>2.75</v>
       </c>
       <c r="G1231" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="H1231" t="s">
         <v>9</v>
@@ -34324,7 +34330,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G1232" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="H1232" t="s">
         <v>9</v>
@@ -34350,7 +34356,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G1233" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H1233" t="s">
         <v>9</v>
@@ -34376,7 +34382,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G1234" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H1234" t="s">
         <v>9</v>
@@ -34402,7 +34408,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G1235" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H1235" t="s">
         <v>9</v>
@@ -34428,7 +34434,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G1236" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H1236" t="s">
         <v>9</v>
@@ -34454,7 +34460,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G1237" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="H1237" t="s">
         <v>9</v>
@@ -34480,7 +34486,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G1238" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="H1238" t="s">
         <v>9</v>
@@ -34506,7 +34512,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G1239" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="H1239" t="s">
         <v>9</v>
@@ -34532,7 +34538,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G1240" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="H1240" t="s">
         <v>9</v>
@@ -34558,7 +34564,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G1241" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="H1241" t="s">
         <v>9</v>
@@ -34584,7 +34590,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G1242" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H1242" t="s">
         <v>9</v>
@@ -34610,7 +34616,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G1243" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H1243" t="s">
         <v>9</v>
@@ -34636,7 +34642,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G1244" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="H1244" t="s">
         <v>9</v>
@@ -34662,7 +34668,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G1245" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="H1245" t="s">
         <v>9</v>
@@ -34688,7 +34694,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G1246" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H1246" t="s">
         <v>9</v>
@@ -34714,7 +34720,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G1247" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="H1247" t="s">
         <v>9</v>
@@ -34740,7 +34746,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G1248" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="H1248" t="s">
         <v>9</v>
@@ -34766,7 +34772,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1249" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H1249" t="s">
         <v>9</v>
@@ -34792,7 +34798,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G1250" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H1250" t="s">
         <v>9</v>
@@ -34818,7 +34824,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G1251" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H1251" t="s">
         <v>9</v>
@@ -34844,7 +34850,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G1252" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H1252" t="s">
         <v>9</v>
@@ -34870,7 +34876,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G1253" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="H1253" t="s">
         <v>9</v>
@@ -34896,7 +34902,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G1254" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="H1254" t="s">
         <v>9</v>
@@ -34922,7 +34928,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G1255" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="H1255" t="s">
         <v>9</v>
@@ -34948,7 +34954,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G1256" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="H1256" t="s">
         <v>9</v>
@@ -34974,7 +34980,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G1257" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="H1257" t="s">
         <v>9</v>
@@ -35000,7 +35006,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1258" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H1258" t="s">
         <v>9</v>
@@ -35052,7 +35058,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1260" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H1260" t="s">
         <v>9</v>
@@ -35078,7 +35084,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1261" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="H1261" t="s">
         <v>9</v>
@@ -35104,7 +35110,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G1262" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="H1262" t="s">
         <v>9</v>
@@ -35130,7 +35136,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1263" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="H1263" t="s">
         <v>9</v>
@@ -35208,7 +35214,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1266" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="H1266" t="s">
         <v>9</v>
@@ -35572,7 +35578,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1280" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="H1280" t="s">
         <v>9</v>
@@ -35598,7 +35604,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1281" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="H1281" t="s">
         <v>9</v>
@@ -35806,7 +35812,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G1289" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="H1289" t="s">
         <v>9</v>
@@ -35858,7 +35864,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G1291" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="H1291" t="s">
         <v>9</v>
@@ -36040,7 +36046,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1298" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="H1298" t="s">
         <v>9</v>
@@ -36066,7 +36072,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1299" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="H1299" t="s">
         <v>9</v>
@@ -36118,7 +36124,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G1301" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="H1301" t="s">
         <v>9</v>
@@ -36170,7 +36176,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G1303" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="H1303" t="s">
         <v>9</v>
@@ -36196,7 +36202,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1304" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="H1304" t="s">
         <v>9</v>
@@ -36326,7 +36332,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G1309" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="H1309" t="s">
         <v>9</v>
@@ -36352,7 +36358,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G1310" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="H1310" t="s">
         <v>9</v>
@@ -36482,7 +36488,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G1315" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="H1315" t="s">
         <v>9</v>
@@ -36508,7 +36514,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G1316" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="H1316" t="s">
         <v>9</v>
@@ -36560,7 +36566,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1318" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="H1318" t="s">
         <v>9</v>
@@ -36586,7 +36592,7 @@
         <v>3.5</v>
       </c>
       <c r="G1319" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="H1319" t="s">
         <v>9</v>
@@ -36612,7 +36618,7 @@
         <v>3.5</v>
       </c>
       <c r="G1320" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="H1320" t="s">
         <v>9</v>
@@ -36638,7 +36644,7 @@
         <v>3.5</v>
       </c>
       <c r="G1321" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="H1321" t="s">
         <v>9</v>
@@ -36664,7 +36670,7 @@
         <v>3.5</v>
       </c>
       <c r="G1322" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="H1322" t="s">
         <v>9</v>
@@ -36690,7 +36696,7 @@
         <v>3.5</v>
       </c>
       <c r="G1323" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="H1323" t="s">
         <v>9</v>
@@ -36716,7 +36722,7 @@
         <v>3.5</v>
       </c>
       <c r="G1324" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="H1324" t="s">
         <v>9</v>
@@ -36846,7 +36852,7 @@
         <v>3.5</v>
       </c>
       <c r="G1329" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="H1329" t="s">
         <v>9</v>
@@ -36898,7 +36904,7 @@
         <v>3.5</v>
       </c>
       <c r="G1331" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="H1331" t="s">
         <v>9</v>
@@ -37002,7 +37008,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G1335" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="H1335" t="s">
         <v>9</v>
@@ -37028,7 +37034,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1336" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="H1336" t="s">
         <v>9</v>
@@ -37054,7 +37060,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G1337" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="H1337" t="s">
         <v>9</v>
@@ -37080,7 +37086,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G1338" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="H1338" t="s">
         <v>9</v>
@@ -37106,7 +37112,7 @@
         <v>3.5</v>
       </c>
       <c r="G1339" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="H1339" t="s">
         <v>9</v>
@@ -37132,7 +37138,7 @@
         <v>3.5</v>
       </c>
       <c r="G1340" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="H1340" t="s">
         <v>9</v>
@@ -37184,7 +37190,7 @@
         <v>3.5</v>
       </c>
       <c r="G1342" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="H1342" t="s">
         <v>9</v>
@@ -37210,7 +37216,7 @@
         <v>3.5</v>
       </c>
       <c r="G1343" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="H1343" t="s">
         <v>9</v>
@@ -37236,7 +37242,7 @@
         <v>3.5</v>
       </c>
       <c r="G1344" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="H1344" t="s">
         <v>9</v>
@@ -37262,7 +37268,7 @@
         <v>3.5</v>
       </c>
       <c r="G1345" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="H1345" t="s">
         <v>9</v>
@@ -37288,7 +37294,7 @@
         <v>3.5</v>
       </c>
       <c r="G1346" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="H1346" t="s">
         <v>9</v>
@@ -37314,7 +37320,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1347" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="H1347" t="s">
         <v>9</v>
@@ -37340,7 +37346,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1348" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="H1348" t="s">
         <v>9</v>
@@ -37366,7 +37372,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1349" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="H1349" t="s">
         <v>9</v>
@@ -37496,7 +37502,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G1354" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="H1354" t="s">
         <v>9</v>
@@ -37522,7 +37528,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1355" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="H1355" t="s">
         <v>9</v>
@@ -37548,7 +37554,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1356" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="H1356" t="s">
         <v>9</v>
@@ -37574,7 +37580,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1357" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="H1357" t="s">
         <v>9</v>
@@ -37600,7 +37606,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G1358" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="H1358" t="s">
         <v>9</v>
@@ -37626,7 +37632,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1359" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="H1359" t="s">
         <v>9</v>
@@ -37652,7 +37658,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1360" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="H1360" t="s">
         <v>9</v>
@@ -37860,7 +37866,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1368" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="H1368" t="s">
         <v>9</v>
@@ -37886,7 +37892,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1369" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="H1369" t="s">
         <v>9</v>
@@ -38016,7 +38022,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1374" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="H1374" t="s">
         <v>9</v>
@@ -38042,7 +38048,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1375" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="H1375" t="s">
         <v>9</v>
@@ -38094,7 +38100,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G1377" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="H1377" t="s">
         <v>9</v>
@@ -38146,7 +38152,7 @@
         <v>3.5</v>
       </c>
       <c r="G1379" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="H1379" t="s">
         <v>9</v>
@@ -38198,7 +38204,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1381" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="H1381" t="s">
         <v>9</v>
@@ -38276,7 +38282,7 @@
         <v>3.5</v>
       </c>
       <c r="G1384" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="H1384" t="s">
         <v>9</v>
@@ -38328,7 +38334,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1386" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="H1386" t="s">
         <v>9</v>
@@ -38380,7 +38386,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1388" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="H1388" t="s">
         <v>9</v>
@@ -38406,7 +38412,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1389" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="H1389" t="s">
         <v>9</v>
@@ -39082,7 +39088,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1415" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="H1415" t="s">
         <v>9</v>
@@ -39186,7 +39192,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1419" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="H1419" t="s">
         <v>9</v>
@@ -39238,7 +39244,7 @@
         <v>3.5</v>
       </c>
       <c r="G1421" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="H1421" t="s">
         <v>9</v>
@@ -39264,7 +39270,7 @@
         <v>3.5</v>
       </c>
       <c r="G1422" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="H1422" t="s">
         <v>9</v>
@@ -39342,7 +39348,7 @@
         <v>3.5</v>
       </c>
       <c r="G1425" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="H1425" t="s">
         <v>9</v>
@@ -39368,7 +39374,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1426" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="H1426" t="s">
         <v>9</v>
@@ -39394,7 +39400,7 @@
         <v>3.5</v>
       </c>
       <c r="G1427" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="H1427" t="s">
         <v>9</v>
@@ -39420,7 +39426,7 @@
         <v>3.5</v>
       </c>
       <c r="G1428" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="H1428" t="s">
         <v>9</v>
@@ -39446,7 +39452,7 @@
         <v>3.5</v>
       </c>
       <c r="G1429" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="H1429" t="s">
         <v>9</v>
@@ -39472,7 +39478,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1430" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="H1430" t="s">
         <v>9</v>
@@ -39498,7 +39504,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1431" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="H1431" t="s">
         <v>9</v>
@@ -39576,7 +39582,7 @@
         <v>3.5</v>
       </c>
       <c r="G1434" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="H1434" t="s">
         <v>9</v>
@@ -39602,7 +39608,7 @@
         <v>3.5</v>
       </c>
       <c r="G1435" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="H1435" t="s">
         <v>9</v>
@@ -39628,7 +39634,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1436" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="H1436" t="s">
         <v>9</v>
@@ -39654,7 +39660,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1437" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="H1437" t="s">
         <v>9</v>
@@ -39680,7 +39686,7 @@
         <v>3.5</v>
       </c>
       <c r="G1438" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="H1438" t="s">
         <v>9</v>
@@ -39706,7 +39712,7 @@
         <v>3.5</v>
       </c>
       <c r="G1439" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="H1439" t="s">
         <v>9</v>
@@ -39732,7 +39738,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1440" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="H1440" t="s">
         <v>9</v>
@@ -39758,7 +39764,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1441" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="H1441" t="s">
         <v>9</v>
@@ -39784,7 +39790,7 @@
         <v>3.5</v>
       </c>
       <c r="G1442" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="H1442" t="s">
         <v>9</v>
@@ -39888,7 +39894,7 @@
         <v>3.5</v>
       </c>
       <c r="G1446" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="H1446" t="s">
         <v>9</v>
@@ -39914,7 +39920,7 @@
         <v>3.5</v>
       </c>
       <c r="G1447" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="H1447" t="s">
         <v>9</v>
@@ -39966,7 +39972,7 @@
         <v>3.5</v>
       </c>
       <c r="G1449" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="H1449" t="s">
         <v>9</v>
@@ -39992,7 +39998,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1450" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="H1450" t="s">
         <v>9</v>
@@ -40018,7 +40024,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1451" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="H1451" t="s">
         <v>9</v>
@@ -40148,7 +40154,7 @@
         <v>3.5</v>
       </c>
       <c r="G1456" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="H1456" t="s">
         <v>9</v>
@@ -40174,7 +40180,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G1457" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H1457" t="s">
         <v>9</v>
@@ -40200,7 +40206,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G1458" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="H1458" t="s">
         <v>9</v>
@@ -40226,7 +40232,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1459" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="H1459" t="s">
         <v>9</v>
@@ -40252,7 +40258,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G1460" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="H1460" t="s">
         <v>9</v>
@@ -40278,7 +40284,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1461" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="H1461" t="s">
         <v>9</v>
@@ -40304,7 +40310,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1462" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="H1462" t="s">
         <v>9</v>
@@ -40330,7 +40336,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G1463" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="H1463" t="s">
         <v>9</v>
@@ -40356,7 +40362,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G1464" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="H1464" t="s">
         <v>9</v>
@@ -40382,7 +40388,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1465" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="H1465" t="s">
         <v>9</v>
@@ -40408,7 +40414,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G1466" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="H1466" t="s">
         <v>9</v>
@@ -40434,7 +40440,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G1467" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="H1467" t="s">
         <v>9</v>
@@ -40460,7 +40466,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G1468" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="H1468" t="s">
         <v>9</v>
@@ -40486,7 +40492,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G1469" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="H1469" t="s">
         <v>9</v>
@@ -40512,7 +40518,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G1470" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="H1470" t="s">
         <v>9</v>
@@ -40538,7 +40544,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1471" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H1471" t="s">
         <v>9</v>
@@ -40564,7 +40570,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G1472" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H1472" t="s">
         <v>9</v>
@@ -40590,7 +40596,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1473" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H1473" t="s">
         <v>9</v>
@@ -40616,7 +40622,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G1474" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1474" t="s">
         <v>9</v>
@@ -40642,7 +40648,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G1475" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="H1475" t="s">
         <v>9</v>
@@ -40668,7 +40674,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1476" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H1476" t="s">
         <v>9</v>
@@ -40694,7 +40700,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1477" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="H1477" t="s">
         <v>9</v>
@@ -40720,7 +40726,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1478" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="H1478" t="s">
         <v>9</v>
@@ -40746,7 +40752,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1479" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H1479" t="s">
         <v>9</v>
@@ -40772,7 +40778,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1480" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="H1480" t="s">
         <v>9</v>
@@ -40798,7 +40804,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G1481" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H1481" t="s">
         <v>9</v>
@@ -40824,7 +40830,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1482" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H1482" t="s">
         <v>9</v>
@@ -40850,7 +40856,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G1483" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="H1483" t="s">
         <v>9</v>
@@ -40876,7 +40882,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G1484" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H1484" t="s">
         <v>9</v>
@@ -40902,7 +40908,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1485" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H1485" t="s">
         <v>9</v>
@@ -40928,7 +40934,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1486" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H1486" t="s">
         <v>9</v>
@@ -40954,7 +40960,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1487" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H1487" t="s">
         <v>9</v>
@@ -40980,7 +40986,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G1488" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="H1488" t="s">
         <v>9</v>
@@ -41006,7 +41012,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G1489" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="H1489" t="s">
         <v>9</v>
@@ -41032,7 +41038,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1490" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="H1490" t="s">
         <v>9</v>
@@ -41058,7 +41064,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1491" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="H1491" t="s">
         <v>9</v>
@@ -41084,7 +41090,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1492" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="H1492" t="s">
         <v>9</v>
@@ -41110,7 +41116,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G1493" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="H1493" t="s">
         <v>9</v>
@@ -41136,7 +41142,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1494" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="H1494" t="s">
         <v>9</v>
@@ -41162,7 +41168,7 @@
         <v>4</v>
       </c>
       <c r="G1495" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="H1495" t="s">
         <v>9</v>
@@ -41188,7 +41194,7 @@
         <v>4</v>
       </c>
       <c r="G1496" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="H1496" t="s">
         <v>9</v>
@@ -41214,7 +41220,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G1497" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="H1497" t="s">
         <v>9</v>
@@ -41240,7 +41246,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G1498" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="H1498" t="s">
         <v>9</v>
@@ -41266,7 +41272,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G1499" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="H1499" t="s">
         <v>9</v>
@@ -41292,7 +41298,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G1500" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1500" t="s">
         <v>9</v>
@@ -41318,7 +41324,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1501" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H1501" t="s">
         <v>9</v>
@@ -41344,7 +41350,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1502" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H1502" t="s">
         <v>9</v>
@@ -41370,7 +41376,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1503" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H1503" t="s">
         <v>9</v>
@@ -41396,7 +41402,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1504" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="H1504" t="s">
         <v>9</v>
@@ -41422,7 +41428,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1505" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="H1505" t="s">
         <v>9</v>
@@ -41448,7 +41454,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1506" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H1506" t="s">
         <v>9</v>
@@ -41474,7 +41480,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1507" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="H1507" t="s">
         <v>9</v>
@@ -41500,7 +41506,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G1508" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="H1508" t="s">
         <v>9</v>
@@ -41526,7 +41532,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G1509" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="H1509" t="s">
         <v>9</v>
@@ -41552,7 +41558,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1510" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H1510" t="s">
         <v>9</v>
@@ -41578,7 +41584,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1511" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H1511" t="s">
         <v>9</v>
@@ -41604,7 +41610,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1512" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H1512" t="s">
         <v>9</v>
@@ -41630,7 +41636,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1513" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H1513" t="s">
         <v>9</v>
@@ -41656,7 +41662,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1514" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H1514" t="s">
         <v>9</v>
@@ -41682,7 +41688,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G1515" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="H1515" t="s">
         <v>9</v>
@@ -41708,7 +41714,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1516" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="H1516" t="s">
         <v>9</v>
@@ -41734,7 +41740,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G1517" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="H1517" t="s">
         <v>9</v>
@@ -41760,7 +41766,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1518" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="H1518" t="s">
         <v>9</v>
@@ -41786,7 +41792,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G1519" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="H1519" t="s">
         <v>9</v>
@@ -41812,7 +41818,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G1520" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="H1520" t="s">
         <v>9</v>
@@ -41838,7 +41844,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1521" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="H1521" t="s">
         <v>9</v>
@@ -41864,7 +41870,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1522" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H1522" t="s">
         <v>9</v>
@@ -41890,7 +41896,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G1523" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="H1523" t="s">
         <v>9</v>
@@ -41916,7 +41922,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1524" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="H1524" t="s">
         <v>9</v>
@@ -41942,7 +41948,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1525" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H1525" t="s">
         <v>9</v>
@@ -41968,7 +41974,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G1526" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1526" t="s">
         <v>9</v>
@@ -41994,7 +42000,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1527" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="H1527" t="s">
         <v>9</v>
@@ -42020,7 +42026,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G1528" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H1528" t="s">
         <v>9</v>
@@ -42046,7 +42052,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1529" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H1529" t="s">
         <v>9</v>
@@ -42072,7 +42078,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G1530" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="H1530" t="s">
         <v>9</v>
@@ -42098,7 +42104,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1531" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="H1531" t="s">
         <v>9</v>
@@ -42124,7 +42130,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1532" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="H1532" t="s">
         <v>9</v>
@@ -42150,7 +42156,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1533" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="H1533" t="s">
         <v>9</v>
@@ -42176,7 +42182,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1534" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H1534" t="s">
         <v>9</v>
@@ -42202,7 +42208,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1535" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H1535" t="s">
         <v>9</v>
@@ -42228,7 +42234,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G1536" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="H1536" t="s">
         <v>9</v>
@@ -42254,7 +42260,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G1537" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H1537" t="s">
         <v>9</v>
@@ -42280,7 +42286,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1538" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="H1538" t="s">
         <v>9</v>
@@ -42306,7 +42312,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1539" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H1539" t="s">
         <v>9</v>
@@ -42332,7 +42338,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G1540" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="H1540" t="s">
         <v>9</v>
@@ -42358,7 +42364,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1541" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H1541" t="s">
         <v>9</v>
@@ -42384,7 +42390,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G1542" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="H1542" t="s">
         <v>9</v>
@@ -42410,7 +42416,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G1543" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H1543" t="s">
         <v>9</v>
@@ -42436,7 +42442,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1544" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="H1544" t="s">
         <v>9</v>
@@ -42462,7 +42468,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1545" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="H1545" t="s">
         <v>9</v>
@@ -42488,7 +42494,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1546" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H1546" t="s">
         <v>9</v>
@@ -42514,7 +42520,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G1547" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="H1547" t="s">
         <v>9</v>
@@ -42540,7 +42546,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1548" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="H1548" t="s">
         <v>9</v>
@@ -42566,7 +42572,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1549" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="H1549" t="s">
         <v>9</v>
@@ -42592,7 +42598,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1550" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="H1550" t="s">
         <v>9</v>
@@ -42618,7 +42624,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G1551" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="H1551" t="s">
         <v>9</v>
@@ -42644,7 +42650,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G1552" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="H1552" t="s">
         <v>9</v>
@@ -42670,7 +42676,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G1553" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H1553" t="s">
         <v>9</v>
@@ -42696,7 +42702,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G1554" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="H1554" t="s">
         <v>9</v>
@@ -42722,7 +42728,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G1555" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="H1555" t="s">
         <v>9</v>
@@ -42748,7 +42754,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1556" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="H1556" t="s">
         <v>9</v>
@@ -42774,7 +42780,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1557" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="H1557" t="s">
         <v>9</v>
@@ -42800,7 +42806,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G1558" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="H1558" t="s">
         <v>9</v>
@@ -42826,7 +42832,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G1559" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="H1559" t="s">
         <v>9</v>
@@ -42852,7 +42858,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G1560" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="H1560" t="s">
         <v>9</v>
@@ -42878,7 +42884,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G1561" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="H1561" t="s">
         <v>9</v>
@@ -42904,7 +42910,7 @@
         <v>3.5</v>
       </c>
       <c r="G1562" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="H1562" t="s">
         <v>9</v>
@@ -42930,7 +42936,7 @@
         <v>3.5</v>
       </c>
       <c r="G1563" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="H1563" t="s">
         <v>9</v>
@@ -43216,7 +43222,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1574" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="H1574" t="s">
         <v>9</v>
@@ -43346,7 +43352,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1579" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="H1579" t="s">
         <v>9</v>
@@ -43398,7 +43404,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1581" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="H1581" t="s">
         <v>9</v>
@@ -43424,7 +43430,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G1582" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="H1582" t="s">
         <v>9</v>
@@ -43450,7 +43456,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G1583" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="H1583" t="s">
         <v>9</v>
@@ -43476,7 +43482,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G1584" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="H1584" t="s">
         <v>9</v>
@@ -43502,7 +43508,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G1585" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H1585" t="s">
         <v>9</v>
@@ -43528,7 +43534,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1586" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="H1586" t="s">
         <v>9</v>
@@ -43554,7 +43560,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G1587" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="H1587" t="s">
         <v>9</v>
@@ -43580,7 +43586,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1588" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="H1588" t="s">
         <v>9</v>
@@ -43606,7 +43612,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G1589" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H1589" t="s">
         <v>9</v>
@@ -43632,7 +43638,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1590" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="H1590" t="s">
         <v>9</v>
@@ -43658,7 +43664,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G1591" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="H1591" t="s">
         <v>9</v>
@@ -43684,7 +43690,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G1592" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="H1592" t="s">
         <v>9</v>
@@ -43710,7 +43716,7 @@
         <v>3.5</v>
       </c>
       <c r="G1593" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="H1593" t="s">
         <v>9</v>
@@ -43736,7 +43742,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1594" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="H1594" t="s">
         <v>9</v>
@@ -43762,7 +43768,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1595" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="H1595" t="s">
         <v>9</v>
@@ -43788,7 +43794,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1596" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="H1596" t="s">
         <v>9</v>
@@ -43814,7 +43820,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G1597" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="H1597" t="s">
         <v>9</v>
@@ -43840,7 +43846,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1598" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="H1598" t="s">
         <v>9</v>
@@ -43866,7 +43872,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1599" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="H1599" t="s">
         <v>9</v>
@@ -43892,7 +43898,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G1600" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="H1600" t="s">
         <v>9</v>
@@ -43918,7 +43924,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G1601" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="H1601" t="s">
         <v>9</v>
@@ -43944,7 +43950,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G1602" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="H1602" t="s">
         <v>9</v>
@@ -43970,7 +43976,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G1603" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="H1603" t="s">
         <v>9</v>
@@ -43996,7 +44002,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G1604" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="H1604" t="s">
         <v>9</v>
@@ -44022,7 +44028,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G1605" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="H1605" t="s">
         <v>9</v>
@@ -44048,7 +44054,7 @@
         <v>3.5</v>
       </c>
       <c r="G1606" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="H1606" t="s">
         <v>9</v>
@@ -44074,7 +44080,7 @@
         <v>3.5</v>
       </c>
       <c r="G1607" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="H1607" t="s">
         <v>9</v>
@@ -44100,7 +44106,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G1608" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="H1608" t="s">
         <v>9</v>
@@ -44126,7 +44132,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G1609" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="H1609" t="s">
         <v>9</v>
@@ -44178,7 +44184,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G1611" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="H1611" t="s">
         <v>9</v>
@@ -44230,7 +44236,7 @@
         <v>3.5</v>
       </c>
       <c r="G1613" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="H1613" t="s">
         <v>9</v>
@@ -44282,7 +44288,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1615" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="H1615" t="s">
         <v>9</v>
@@ -44308,7 +44314,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1616" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="H1616" t="s">
         <v>9</v>
@@ -44334,7 +44340,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1617" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="H1617" t="s">
         <v>9</v>
@@ -44464,7 +44470,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G1622" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="H1622" t="s">
         <v>9</v>
@@ -44490,7 +44496,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G1623" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="H1623" t="s">
         <v>9</v>
@@ -44516,7 +44522,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G1624" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="H1624" t="s">
         <v>9</v>
@@ -44542,7 +44548,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G1625" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="H1625" t="s">
         <v>9</v>
@@ -44568,7 +44574,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1626" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="H1626" t="s">
         <v>9</v>
@@ -44594,7 +44600,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G1627" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="H1627" t="s">
         <v>9</v>
@@ -44620,7 +44626,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1628" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="H1628" t="s">
         <v>9</v>
@@ -44646,7 +44652,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G1629" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="H1629" t="s">
         <v>9</v>
@@ -44672,7 +44678,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G1630" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="H1630" t="s">
         <v>9</v>
@@ -44698,7 +44704,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G1631" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="H1631" t="s">
         <v>9</v>
@@ -44724,7 +44730,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G1632" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="H1632" t="s">
         <v>9</v>
@@ -44750,7 +44756,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1633" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="H1633" t="s">
         <v>9</v>
@@ -44776,7 +44782,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1634" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="H1634" t="s">
         <v>9</v>
@@ -44802,7 +44808,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G1635" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="H1635" t="s">
         <v>9</v>
@@ -44828,7 +44834,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G1636" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="H1636" t="s">
         <v>9</v>
@@ -44854,7 +44860,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G1637" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="H1637" t="s">
         <v>9</v>
@@ -44880,7 +44886,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1638" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="H1638" t="s">
         <v>9</v>
@@ -44906,7 +44912,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1639" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="H1639" t="s">
         <v>9</v>
@@ -44932,7 +44938,7 @@
         <v>3.5</v>
       </c>
       <c r="G1640" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="H1640" t="s">
         <v>9</v>
@@ -44958,7 +44964,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G1641" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="H1641" t="s">
         <v>9</v>
@@ -44984,7 +44990,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G1642" t="s">
-        <v>463</v>
+        <v>496</v>
       </c>
       <c r="H1642" t="s">
         <v>9</v>
@@ -45010,7 +45016,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G1643" t="s">
-        <v>463</v>
+        <v>496</v>
       </c>
       <c r="H1643" t="s">
         <v>9</v>
@@ -45062,7 +45068,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1645" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="H1645" t="s">
         <v>9</v>
@@ -45166,7 +45172,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1649" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="H1649" t="s">
         <v>9</v>
@@ -45400,7 +45406,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1658" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="H1658" t="s">
         <v>9</v>
@@ -46024,7 +46030,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G1682" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="H1682" t="s">
         <v>9</v>
@@ -46102,7 +46108,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G1685" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="H1685" t="s">
         <v>9</v>
@@ -46128,7 +46134,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G1686" t="s">
-        <v>463</v>
+        <v>496</v>
       </c>
       <c r="H1686" t="s">
         <v>9</v>
@@ -46154,7 +46160,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G1687" t="s">
-        <v>463</v>
+        <v>496</v>
       </c>
       <c r="H1687" t="s">
         <v>9</v>
@@ -46180,7 +46186,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G1688" t="s">
-        <v>463</v>
+        <v>496</v>
       </c>
       <c r="H1688" t="s">
         <v>9</v>
@@ -46232,7 +46238,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G1690" t="s">
-        <v>463</v>
+        <v>496</v>
       </c>
       <c r="H1690" t="s">
         <v>9</v>
@@ -46258,7 +46264,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G1691" t="s">
-        <v>463</v>
+        <v>496</v>
       </c>
       <c r="H1691" t="s">
         <v>9</v>
@@ -46284,7 +46290,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G1692" t="s">
-        <v>463</v>
+        <v>496</v>
       </c>
       <c r="H1692" t="s">
         <v>9</v>
@@ -46362,7 +46368,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G1695" t="s">
-        <v>463</v>
+        <v>496</v>
       </c>
       <c r="H1695" t="s">
         <v>9</v>
@@ -46388,7 +46394,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1696" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="H1696" t="s">
         <v>9</v>
@@ -46414,7 +46420,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1697" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="H1697" t="s">
         <v>9</v>
@@ -46518,7 +46524,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1701" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="H1701" t="s">
         <v>9</v>
@@ -46700,7 +46706,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1708" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="H1708" t="s">
         <v>9</v>
@@ -46726,7 +46732,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1709" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="H1709" t="s">
         <v>9</v>
@@ -46752,7 +46758,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1710" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="H1710" t="s">
         <v>9</v>
@@ -62586,7 +62592,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G2319" t="s">
-        <v>538</v>
+        <v>594</v>
       </c>
       <c r="H2319" t="s">
         <v>9</v>
@@ -64276,7 +64282,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2384" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="H2384" t="s">
         <v>9</v>
@@ -64302,7 +64308,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G2385" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="H2385" t="s">
         <v>9</v>
@@ -64328,7 +64334,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G2386" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="H2386" t="s">
         <v>9</v>
@@ -64354,7 +64360,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G2387" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="H2387" t="s">
         <v>9</v>
@@ -64380,7 +64386,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G2388" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="H2388" t="s">
         <v>9</v>
@@ -64406,7 +64412,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G2389" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="H2389" t="s">
         <v>9</v>
@@ -64432,7 +64438,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2390" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="H2390" t="s">
         <v>9</v>
@@ -64458,7 +64464,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2391" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="H2391" t="s">
         <v>9</v>
@@ -64510,7 +64516,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G2393" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="H2393" t="s">
         <v>9</v>
@@ -64562,7 +64568,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2395" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="H2395" t="s">
         <v>9</v>
@@ -64588,7 +64594,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2396" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="H2396" t="s">
         <v>9</v>
@@ -64614,7 +64620,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G2397" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="H2397" t="s">
         <v>9</v>
@@ -64640,7 +64646,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2398" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="H2398" t="s">
         <v>9</v>
@@ -64666,7 +64672,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G2399" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="H2399" t="s">
         <v>9</v>
@@ -64692,7 +64698,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G2400" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="H2400" t="s">
         <v>9</v>
@@ -64718,7 +64724,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G2401" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="H2401" t="s">
         <v>9</v>
@@ -64744,7 +64750,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G2402" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="H2402" t="s">
         <v>9</v>
@@ -64770,7 +64776,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G2403" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="H2403" t="s">
         <v>9</v>
@@ -64796,7 +64802,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G2404" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="H2404" t="s">
         <v>9</v>
@@ -64822,7 +64828,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G2405" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="H2405" t="s">
         <v>9</v>
@@ -64848,7 +64854,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G2406" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="H2406" t="s">
         <v>9</v>
@@ -64874,7 +64880,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G2407" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="H2407" t="s">
         <v>9</v>
@@ -64900,7 +64906,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G2408" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="H2408" t="s">
         <v>9</v>
@@ -64926,7 +64932,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2409" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="H2409" t="s">
         <v>9</v>
@@ -64952,7 +64958,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G2410" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="H2410" t="s">
         <v>9</v>
@@ -64978,7 +64984,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G2411" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="H2411" t="s">
         <v>9</v>
@@ -65004,7 +65010,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G2412" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="H2412" t="s">
         <v>9</v>
@@ -65030,7 +65036,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G2413" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="H2413" t="s">
         <v>9</v>
@@ -65056,7 +65062,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G2414" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="H2414" t="s">
         <v>9</v>
@@ -65082,7 +65088,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G2415" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="H2415" t="s">
         <v>9</v>
@@ -65108,7 +65114,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G2416" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="H2416" t="s">
         <v>9</v>
@@ -65134,7 +65140,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G2417" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="H2417" t="s">
         <v>9</v>
@@ -65160,7 +65166,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G2418" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="H2418" t="s">
         <v>9</v>
@@ -65186,7 +65192,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G2419" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="H2419" t="s">
         <v>9</v>
@@ -65212,7 +65218,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G2420" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="H2420" t="s">
         <v>9</v>
@@ -65238,7 +65244,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G2421" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="H2421" t="s">
         <v>9</v>
@@ -65264,7 +65270,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G2422" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="H2422" t="s">
         <v>9</v>
@@ -65290,7 +65296,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G2423" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="H2423" t="s">
         <v>9</v>
@@ -65316,7 +65322,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G2424" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="H2424" t="s">
         <v>9</v>
@@ -65342,7 +65348,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G2425" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="H2425" t="s">
         <v>9</v>
@@ -65368,7 +65374,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G2426" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="H2426" t="s">
         <v>9</v>
@@ -65394,7 +65400,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G2427" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="H2427" t="s">
         <v>9</v>
@@ -65420,7 +65426,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G2428" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="H2428" t="s">
         <v>9</v>
@@ -65446,7 +65452,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G2429" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="H2429" t="s">
         <v>9</v>
@@ -65472,7 +65478,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G2430" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="H2430" t="s">
         <v>9</v>
@@ -65498,7 +65504,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G2431" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="H2431" t="s">
         <v>9</v>
@@ -65524,7 +65530,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G2432" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="H2432" t="s">
         <v>9</v>
@@ -65550,7 +65556,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G2433" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="H2433" t="s">
         <v>9</v>
@@ -65576,7 +65582,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G2434" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="H2434" t="s">
         <v>9</v>
@@ -65602,7 +65608,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G2435" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="H2435" t="s">
         <v>9</v>
@@ -65628,7 +65634,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G2436" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="H2436" t="s">
         <v>9</v>
@@ -65654,7 +65660,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G2437" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="H2437" t="s">
         <v>9</v>
@@ -65680,7 +65686,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G2438" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="H2438" t="s">
         <v>9</v>
@@ -65706,7 +65712,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G2439" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="H2439" t="s">
         <v>9</v>
@@ -65732,7 +65738,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G2440" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="H2440" t="s">
         <v>9</v>
@@ -65758,7 +65764,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G2441" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="H2441" t="s">
         <v>9</v>
@@ -65784,7 +65790,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G2442" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="H2442" t="s">
         <v>9</v>
@@ -65810,7 +65816,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G2443" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="H2443" t="s">
         <v>9</v>
@@ -65836,7 +65842,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G2444" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="H2444" t="s">
         <v>9</v>
@@ -65862,7 +65868,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G2445" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="H2445" t="s">
         <v>9</v>
@@ -65888,7 +65894,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G2446" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="H2446" t="s">
         <v>9</v>
@@ -65914,7 +65920,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G2447" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="H2447" t="s">
         <v>9</v>
@@ -65940,7 +65946,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G2448" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="H2448" t="s">
         <v>9</v>
@@ -65966,7 +65972,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G2449" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="H2449" t="s">
         <v>9</v>
@@ -65992,7 +65998,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G2450" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="H2450" t="s">
         <v>9</v>
@@ -66018,7 +66024,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G2451" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="H2451" t="s">
         <v>9</v>
@@ -66044,7 +66050,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G2452" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="H2452" t="s">
         <v>9</v>
@@ -66070,7 +66076,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G2453" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="H2453" t="s">
         <v>9</v>
@@ -66096,7 +66102,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G2454" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="H2454" t="s">
         <v>9</v>
@@ -66122,7 +66128,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G2455" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="H2455" t="s">
         <v>9</v>
@@ -66148,7 +66154,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G2456" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="H2456" t="s">
         <v>9</v>
@@ -66174,7 +66180,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G2457" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="H2457" t="s">
         <v>9</v>
@@ -66200,7 +66206,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G2458" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="H2458" t="s">
         <v>9</v>
@@ -66226,7 +66232,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G2459" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="H2459" t="s">
         <v>9</v>
@@ -66252,7 +66258,7 @@
         <v>4</v>
       </c>
       <c r="G2460" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="H2460" t="s">
         <v>9</v>
@@ -66278,7 +66284,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G2461" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="H2461" t="s">
         <v>9</v>
@@ -66304,7 +66310,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G2462" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="H2462" t="s">
         <v>9</v>
@@ -66330,7 +66336,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G2463" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="H2463" t="s">
         <v>9</v>
@@ -66356,7 +66362,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G2464" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="H2464" t="s">
         <v>9</v>
@@ -66382,7 +66388,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G2465" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="H2465" t="s">
         <v>9</v>
@@ -66408,7 +66414,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G2466" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="H2466" t="s">
         <v>9</v>
@@ -66434,7 +66440,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G2467" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="H2467" t="s">
         <v>9</v>
@@ -66460,7 +66466,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G2468" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="H2468" t="s">
         <v>9</v>
@@ -66486,7 +66492,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G2469" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="H2469" t="s">
         <v>9</v>
@@ -66512,7 +66518,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G2470" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="H2470" t="s">
         <v>9</v>
@@ -66538,7 +66544,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G2471" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="H2471" t="s">
         <v>9</v>
@@ -66564,7 +66570,7 @@
         <v>4</v>
       </c>
       <c r="G2472" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="H2472" t="s">
         <v>9</v>
@@ -66590,7 +66596,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G2473" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="H2473" t="s">
         <v>9</v>
@@ -66616,7 +66622,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G2474" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="H2474" t="s">
         <v>9</v>
@@ -66642,7 +66648,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G2475" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="H2475" t="s">
         <v>9</v>
@@ -66668,7 +66674,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G2476" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="H2476" t="s">
         <v>9</v>
@@ -66694,7 +66700,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G2477" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="H2477" t="s">
         <v>9</v>
@@ -66720,7 +66726,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G2478" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="H2478" t="s">
         <v>9</v>
@@ -66746,7 +66752,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G2479" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="H2479" t="s">
         <v>9</v>
@@ -66772,7 +66778,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G2480" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="H2480" t="s">
         <v>9</v>
@@ -66798,7 +66804,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G2481" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="H2481" t="s">
         <v>9</v>
@@ -66824,7 +66830,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G2482" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="H2482" t="s">
         <v>9</v>
@@ -66850,7 +66856,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G2483" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="H2483" t="s">
         <v>9</v>
@@ -66876,7 +66882,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G2484" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="H2484" t="s">
         <v>9</v>
@@ -66902,7 +66908,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G2485" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="H2485" t="s">
         <v>9</v>
@@ -66928,7 +66934,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G2486" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="H2486" t="s">
         <v>9</v>
@@ -66954,7 +66960,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G2487" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="H2487" t="s">
         <v>9</v>
@@ -66980,7 +66986,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G2488" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="H2488" t="s">
         <v>9</v>
@@ -67006,7 +67012,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G2489" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="H2489" t="s">
         <v>9</v>
@@ -67032,7 +67038,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G2490" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="H2490" t="s">
         <v>9</v>
@@ -67058,7 +67064,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G2491" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="H2491" t="s">
         <v>9</v>
@@ -67084,7 +67090,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G2492" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="H2492" t="s">
         <v>9</v>
@@ -67110,7 +67116,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G2493" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="H2493" t="s">
         <v>9</v>
@@ -67136,7 +67142,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G2494" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="H2494" t="s">
         <v>9</v>
@@ -67162,7 +67168,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G2495" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="H2495" t="s">
         <v>9</v>
@@ -67188,7 +67194,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G2496" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="H2496" t="s">
         <v>9</v>
@@ -67214,7 +67220,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G2497" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="H2497" t="s">
         <v>9</v>
@@ -67240,7 +67246,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G2498" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="H2498" t="s">
         <v>9</v>
@@ -67266,7 +67272,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G2499" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="H2499" t="s">
         <v>9</v>
@@ -67292,7 +67298,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G2500" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="H2500" t="s">
         <v>9</v>
@@ -67318,7 +67324,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G2501" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="H2501" t="s">
         <v>9</v>
@@ -67344,7 +67350,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G2502" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="H2502" t="s">
         <v>9</v>
@@ -67370,7 +67376,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G2503" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="H2503" t="s">
         <v>9</v>
@@ -67396,7 +67402,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G2504" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="H2504" t="s">
         <v>9</v>
@@ -67422,7 +67428,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G2505" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H2505" t="s">
         <v>9</v>
@@ -67448,7 +67454,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G2506" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H2506" t="s">
         <v>9</v>
@@ -67474,7 +67480,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G2507" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="H2507" t="s">
         <v>9</v>
@@ -67500,7 +67506,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G2508" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="H2508" t="s">
         <v>9</v>
@@ -67526,7 +67532,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G2509" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="H2509" t="s">
         <v>9</v>
@@ -67552,7 +67558,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G2510" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="H2510" t="s">
         <v>9</v>
@@ -67578,7 +67584,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G2511" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="H2511" t="s">
         <v>9</v>
@@ -67604,7 +67610,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G2512" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="H2512" t="s">
         <v>9</v>
@@ -67630,7 +67636,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G2513" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="H2513" t="s">
         <v>9</v>
@@ -67638,7 +67644,7 @@
     </row>
     <row r="2514">
       <c r="A2514" s="1" t="n">
-        <v>45979.6554166667</v>
+        <v>45979.3333333333</v>
       </c>
       <c r="B2514" t="n">
         <v>15600</v>
@@ -67656,9 +67662,35 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G2514" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="H2514" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2515">
+      <c r="A2515" s="1" t="n">
+        <v>45980.6910763889</v>
+      </c>
+      <c r="B2515" t="n">
+        <v>18906</v>
+      </c>
+      <c r="C2515" t="n">
+        <v>3.90000009536743</v>
+      </c>
+      <c r="D2515" t="n">
+        <v>3.75999999046326</v>
+      </c>
+      <c r="E2515" t="n">
+        <v>3.75999999046326</v>
+      </c>
+      <c r="F2515" t="n">
+        <v>3.85999989509583</v>
+      </c>
+      <c r="G2515" t="s">
+        <v>651</v>
+      </c>
+      <c r="H2515" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ENV.MI.xlsx
+++ b/data/ENV.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="655" uniqueCount="655">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="653" uniqueCount="653">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18965268135071</t>
+    <t xml:space="preserve">2.18965220451355</t>
   </si>
   <si>
     <t xml:space="preserve">ENV.MI</t>
@@ -47,79 +47,79 @@
     <t xml:space="preserve">2.20979785919189</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14471292495728</t>
+    <t xml:space="preserve">2.14471244812012</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16175866127014</t>
+    <t xml:space="preserve">2.16175889968872</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03778719902039</t>
+    <t xml:space="preserve">2.03778696060181</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0827271938324</t>
+    <t xml:space="preserve">2.08272671699524</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05328345298767</t>
+    <t xml:space="preserve">2.05328297615051</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03623723983765</t>
+    <t xml:space="preserve">2.03623747825623</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96805286407471</t>
+    <t xml:space="preserve">1.96805262565613</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96030497550964</t>
+    <t xml:space="preserve">1.9603043794632</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89831900596619</t>
+    <t xml:space="preserve">1.89831876754761</t>
   </si>
   <si>
     <t xml:space="preserve">1.88127243518829</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96340394020081</t>
+    <t xml:space="preserve">1.96340370178223</t>
   </si>
   <si>
     <t xml:space="preserve">1.98354935646057</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01299262046814</t>
+    <t xml:space="preserve">2.01299285888672</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93551003932953</t>
+    <t xml:space="preserve">1.9355103969574</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93705952167511</t>
+    <t xml:space="preserve">1.93705987930298</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91381514072418</t>
+    <t xml:space="preserve">1.91381502151489</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91071605682373</t>
+    <t xml:space="preserve">1.91071629524231</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86577582359314</t>
+    <t xml:space="preserve">1.86577618122101</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89212000370026</t>
+    <t xml:space="preserve">1.89211988449097</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85182929039001</t>
+    <t xml:space="preserve">1.8518294095993</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93396067619324</t>
+    <t xml:space="preserve">1.93396079540253</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86732578277588</t>
+    <t xml:space="preserve">1.8673255443573</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88902056217194</t>
+    <t xml:space="preserve">1.88902068138123</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98664844036102</t>
+    <t xml:space="preserve">1.98664820194244</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11526918411255</t>
+    <t xml:space="preserve">2.11526942253113</t>
   </si>
   <si>
     <t xml:space="preserve">2.18500351905823</t>
@@ -128,40 +128,40 @@
     <t xml:space="preserve">2.20824813842773</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16950726509094</t>
+    <t xml:space="preserve">2.16950702667236</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0842764377594</t>
+    <t xml:space="preserve">2.08427619934082</t>
   </si>
   <si>
     <t xml:space="preserve">2.0145423412323</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0052444934845</t>
+    <t xml:space="preserve">2.00524425506592</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14626216888428</t>
+    <t xml:space="preserve">2.14626240730286</t>
   </si>
   <si>
     <t xml:space="preserve">2.22219514846802</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32447171211243</t>
+    <t xml:space="preserve">2.32447195053101</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20050001144409</t>
+    <t xml:space="preserve">2.20049977302551</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27178382873535</t>
+    <t xml:space="preserve">2.27178359031677</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24698948860168</t>
+    <t xml:space="preserve">2.24698925018311</t>
   </si>
   <si>
     <t xml:space="preserve">2.32137250900269</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28418111801147</t>
+    <t xml:space="preserve">2.28418064117432</t>
   </si>
   <si>
     <t xml:space="preserve">2.37870955467224</t>
@@ -170,22 +170,22 @@
     <t xml:space="preserve">2.35546469688416</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4406955242157</t>
+    <t xml:space="preserve">2.44069576263428</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43139743804932</t>
+    <t xml:space="preserve">2.43139719963074</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44999361038208</t>
+    <t xml:space="preserve">2.4499933719635</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38490796089172</t>
+    <t xml:space="preserve">2.38490772247314</t>
   </si>
   <si>
     <t xml:space="preserve">2.36166334152222</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3632128238678</t>
+    <t xml:space="preserve">2.36321330070496</t>
   </si>
   <si>
     <t xml:space="preserve">2.31982278823853</t>
@@ -200,49 +200,49 @@
     <t xml:space="preserve">2.32292222976685</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33531904220581</t>
+    <t xml:space="preserve">2.33531951904297</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33996844291687</t>
+    <t xml:space="preserve">2.33996820449829</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31052541732788</t>
+    <t xml:space="preserve">2.3105251789093</t>
   </si>
   <si>
     <t xml:space="preserve">2.28573060035706</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25473785400391</t>
+    <t xml:space="preserve">2.25473761558533</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29037952423096</t>
+    <t xml:space="preserve">2.29037976264954</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27488327026367</t>
+    <t xml:space="preserve">2.27488303184509</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23149299621582</t>
+    <t xml:space="preserve">2.23149347305298</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07497835159302</t>
+    <t xml:space="preserve">2.0749785900116</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00834369659424</t>
+    <t xml:space="preserve">2.00834393501282</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03468751907349</t>
+    <t xml:space="preserve">2.03468775749207</t>
   </si>
   <si>
     <t xml:space="preserve">2.02229046821594</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97580134868622</t>
+    <t xml:space="preserve">1.97580122947693</t>
   </si>
   <si>
-    <t xml:space="preserve">1.919806599617</t>
+    <t xml:space="preserve">1.91980671882629</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88216376304626</t>
+    <t xml:space="preserve">1.8821634054184</t>
   </si>
   <si>
     <t xml:space="preserve">2.00136733055115</t>
@@ -251,67 +251,67 @@
     <t xml:space="preserve">1.96058702468872</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9025536775589</t>
+    <t xml:space="preserve">1.90255355834961</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92137515544891</t>
+    <t xml:space="preserve">1.92137491703033</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91353297233582</t>
+    <t xml:space="preserve">1.91353273391724</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89784824848175</t>
+    <t xml:space="preserve">1.89784836769104</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89000606536865</t>
+    <t xml:space="preserve">1.89000570774078</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85079395771027</t>
+    <t xml:space="preserve">1.85079431533813</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88059484958649</t>
+    <t xml:space="preserve">1.88059508800507</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8664790391922</t>
+    <t xml:space="preserve">1.86647891998291</t>
   </si>
   <si>
-    <t xml:space="preserve">1.546511054039</t>
+    <t xml:space="preserve">1.54651093482971</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68610501289368</t>
+    <t xml:space="preserve">1.68610465526581</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70178949832916</t>
+    <t xml:space="preserve">1.70178961753845</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70022094249725</t>
+    <t xml:space="preserve">1.70022082328796</t>
   </si>
   <si>
     <t xml:space="preserve">1.66257762908936</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64532446861267</t>
+    <t xml:space="preserve">1.64532470703125</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62336611747742</t>
+    <t xml:space="preserve">1.62336599826813</t>
   </si>
   <si>
     <t xml:space="preserve">1.61552357673645</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63120818138123</t>
+    <t xml:space="preserve">1.63120830059052</t>
   </si>
   <si>
     <t xml:space="preserve">1.58415424823761</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64689290523529</t>
+    <t xml:space="preserve">1.64689302444458</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6406192779541</t>
+    <t xml:space="preserve">1.64061915874481</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63905048370361</t>
+    <t xml:space="preserve">1.63905072212219</t>
   </si>
   <si>
     <t xml:space="preserve">1.60768127441406</t>
@@ -320,49 +320,49 @@
     <t xml:space="preserve">1.57631182670593</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59199655056</t>
+    <t xml:space="preserve">1.59199666976929</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75668597221375</t>
+    <t xml:space="preserve">1.75668573379517</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84295153617859</t>
+    <t xml:space="preserve">1.8429514169693</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84608864784241</t>
+    <t xml:space="preserve">1.84608852863312</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92921769618988</t>
+    <t xml:space="preserve">1.92921757698059</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88530027866364</t>
+    <t xml:space="preserve">1.88530051708221</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9009850025177</t>
+    <t xml:space="preserve">1.90098536014557</t>
   </si>
   <si>
     <t xml:space="preserve">1.91823840141296</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94960761070251</t>
+    <t xml:space="preserve">1.94960749149323</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93078577518463</t>
+    <t xml:space="preserve">1.9307861328125</t>
   </si>
   <si>
     <t xml:space="preserve">1.84922552108765</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82413005828857</t>
+    <t xml:space="preserve">1.82412981987</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85549938678741</t>
+    <t xml:space="preserve">1.85549962520599</t>
   </si>
   <si>
     <t xml:space="preserve">1.89627969264984</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93705976009369</t>
+    <t xml:space="preserve">1.93705999851227</t>
   </si>
   <si>
     <t xml:space="preserve">1.87432134151459</t>
@@ -374,16 +374,16 @@
     <t xml:space="preserve">1.94490230083466</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96686053276062</t>
+    <t xml:space="preserve">1.96686065196991</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98411417007446</t>
+    <t xml:space="preserve">1.98411405086517</t>
   </si>
   <si>
     <t xml:space="preserve">2.06253743171692</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05312657356262</t>
+    <t xml:space="preserve">2.0531268119812</t>
   </si>
   <si>
     <t xml:space="preserve">2.05155801773071</t>
@@ -398,61 +398,61 @@
     <t xml:space="preserve">2.03116798400879</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06096863746643</t>
+    <t xml:space="preserve">2.06096911430359</t>
   </si>
   <si>
     <t xml:space="preserve">2.09390687942505</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08606457710266</t>
+    <t xml:space="preserve">2.08606433868408</t>
   </si>
   <si>
     <t xml:space="preserve">2.1550772190094</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18801498413086</t>
+    <t xml:space="preserve">2.18801522254944</t>
   </si>
   <si>
     <t xml:space="preserve">2.19585728645325</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20213150978088</t>
+    <t xml:space="preserve">2.2021312713623</t>
   </si>
   <si>
     <t xml:space="preserve">2.23350071907043</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20997357368469</t>
+    <t xml:space="preserve">2.20997381210327</t>
   </si>
   <si>
     <t xml:space="preserve">2.18017268180847</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16605663299561</t>
+    <t xml:space="preserve">2.16605639457703</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19428896903992</t>
+    <t xml:space="preserve">2.1942892074585</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17389869689941</t>
+    <t xml:space="preserve">2.17389917373657</t>
   </si>
   <si>
     <t xml:space="preserve">2.2005627155304</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21938443183899</t>
+    <t xml:space="preserve">2.21938419342041</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21781611442566</t>
+    <t xml:space="preserve">2.21781587600708</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1911518573761</t>
+    <t xml:space="preserve">2.19115209579468</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12057137489319</t>
+    <t xml:space="preserve">2.12057089805603</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15350890159607</t>
+    <t xml:space="preserve">2.15350866317749</t>
   </si>
   <si>
     <t xml:space="preserve">2.11743402481079</t>
@@ -464,19 +464,19 @@
     <t xml:space="preserve">2.10802292823792</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01548314094543</t>
+    <t xml:space="preserve">2.01548361778259</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04528403282166</t>
+    <t xml:space="preserve">2.04528474807739</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98568248748779</t>
+    <t xml:space="preserve">1.98568260669708</t>
   </si>
   <si>
     <t xml:space="preserve">2.07822203636169</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06724262237549</t>
+    <t xml:space="preserve">2.06724286079407</t>
   </si>
   <si>
     <t xml:space="preserve">2.12998175621033</t>
@@ -488,43 +488,43 @@
     <t xml:space="preserve">2.05469512939453</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11429738998413</t>
+    <t xml:space="preserve">2.11429691314697</t>
   </si>
   <si>
     <t xml:space="preserve">2.05626344680786</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06410574913025</t>
+    <t xml:space="preserve">2.06410622596741</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10488629341125</t>
+    <t xml:space="preserve">2.10488605499268</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00920939445496</t>
+    <t xml:space="preserve">2.00920963287354</t>
   </si>
   <si>
     <t xml:space="preserve">2.01391506195068</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04842114448547</t>
+    <t xml:space="preserve">2.04842138290405</t>
   </si>
   <si>
     <t xml:space="preserve">2.1644880771637</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18487811088562</t>
+    <t xml:space="preserve">2.1848783493042</t>
   </si>
   <si>
     <t xml:space="preserve">2.26643848419189</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27271223068237</t>
+    <t xml:space="preserve">2.27271270751953</t>
   </si>
   <si>
     <t xml:space="preserve">2.2570276260376</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3072190284729</t>
+    <t xml:space="preserve">2.30721879005432</t>
   </si>
   <si>
     <t xml:space="preserve">2.2303638458252</t>
@@ -536,28 +536,28 @@
     <t xml:space="preserve">2.35270428657532</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39191603660583</t>
+    <t xml:space="preserve">2.39191651344299</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33545088768005</t>
+    <t xml:space="preserve">2.33545112609863</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31349301338196</t>
+    <t xml:space="preserve">2.3134925365448</t>
   </si>
   <si>
     <t xml:space="preserve">2.37623119354248</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32917761802673</t>
+    <t xml:space="preserve">2.32917737960815</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24918556213379</t>
+    <t xml:space="preserve">2.24918532371521</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28839707374573</t>
+    <t xml:space="preserve">2.28839731216431</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33701992034912</t>
+    <t xml:space="preserve">2.33701968193054</t>
   </si>
   <si>
     <t xml:space="preserve">2.34486222267151</t>
@@ -566,13 +566,13 @@
     <t xml:space="preserve">2.34956741333008</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32604074478149</t>
+    <t xml:space="preserve">2.32604026794434</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30251312255859</t>
+    <t xml:space="preserve">2.30251336097717</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31192445755005</t>
+    <t xml:space="preserve">2.31192421913147</t>
   </si>
   <si>
     <t xml:space="preserve">2.25075364112854</t>
@@ -581,31 +581,31 @@
     <t xml:space="preserve">2.27428102493286</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43897008895874</t>
+    <t xml:space="preserve">2.43896985054016</t>
   </si>
   <si>
     <t xml:space="preserve">2.48445582389832</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46249771118164</t>
+    <t xml:space="preserve">2.46249723434448</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50798273086548</t>
+    <t xml:space="preserve">2.50798296928406</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4860246181488</t>
+    <t xml:space="preserve">2.48602437973022</t>
   </si>
   <si>
     <t xml:space="preserve">2.60993337631226</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66639852523804</t>
+    <t xml:space="preserve">2.66639828681946</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66326141357422</t>
+    <t xml:space="preserve">2.66326117515564</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66012454032898</t>
+    <t xml:space="preserve">2.6601243019104</t>
   </si>
   <si>
     <t xml:space="preserve">2.64287137985229</t>
@@ -614,28 +614,28 @@
     <t xml:space="preserve">2.65855598449707</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60209083557129</t>
+    <t xml:space="preserve">2.60209131240845</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55033159255981</t>
+    <t xml:space="preserve">2.55033183097839</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63816595077515</t>
+    <t xml:space="preserve">2.63816571235657</t>
   </si>
   <si>
     <t xml:space="preserve">2.58013248443604</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59581685066223</t>
+    <t xml:space="preserve">2.59581708908081</t>
   </si>
   <si>
     <t xml:space="preserve">2.58170080184937</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60365915298462</t>
+    <t xml:space="preserve">2.6036593914032</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61934399604797</t>
+    <t xml:space="preserve">2.61934375762939</t>
   </si>
   <si>
     <t xml:space="preserve">2.57542705535889</t>
@@ -644,10 +644,10 @@
     <t xml:space="preserve">2.57385873794556</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50955152511597</t>
+    <t xml:space="preserve">2.50955128669739</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58797454833984</t>
+    <t xml:space="preserve">2.58797478675842</t>
   </si>
   <si>
     <t xml:space="preserve">2.56444787979126</t>
@@ -656,13 +656,13 @@
     <t xml:space="preserve">2.61150169372559</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56915307044983</t>
+    <t xml:space="preserve">2.56915330886841</t>
   </si>
   <si>
     <t xml:space="preserve">2.63502883911133</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62561798095703</t>
+    <t xml:space="preserve">2.62561821937561</t>
   </si>
   <si>
     <t xml:space="preserve">2.62718653678894</t>
@@ -680,10 +680,10 @@
     <t xml:space="preserve">2.78089642524719</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69149351119995</t>
+    <t xml:space="preserve">2.69149398803711</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7824649810791</t>
+    <t xml:space="preserve">2.78246521949768</t>
   </si>
   <si>
     <t xml:space="preserve">2.81226587295532</t>
@@ -695,10 +695,10 @@
     <t xml:space="preserve">2.68678832054138</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70090460777283</t>
+    <t xml:space="preserve">2.70090436935425</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80657148361206</t>
+    <t xml:space="preserve">2.80657124519348</t>
   </si>
   <si>
     <t xml:space="preserve">2.86433959007263</t>
@@ -710,10 +710,10 @@
     <t xml:space="preserve">2.80817627906799</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8803858757019</t>
+    <t xml:space="preserve">2.88038611412048</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83385062217712</t>
+    <t xml:space="preserve">2.8338508605957</t>
   </si>
   <si>
     <t xml:space="preserve">2.74398922920227</t>
@@ -725,13 +725,13 @@
     <t xml:space="preserve">2.70547676086426</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73275637626648</t>
+    <t xml:space="preserve">2.7327561378479</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67177891731262</t>
+    <t xml:space="preserve">2.67177867889404</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62363886833191</t>
+    <t xml:space="preserve">2.62363862991333</t>
   </si>
   <si>
     <t xml:space="preserve">2.61722016334534</t>
@@ -740,10 +740,10 @@
     <t xml:space="preserve">2.60438299179077</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62524318695068</t>
+    <t xml:space="preserve">2.62524366378784</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64129042625427</t>
+    <t xml:space="preserve">2.64129018783569</t>
   </si>
   <si>
     <t xml:space="preserve">2.69584894180298</t>
@@ -755,46 +755,46 @@
     <t xml:space="preserve">2.74719858169556</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71991920471191</t>
+    <t xml:space="preserve">2.71991896629333</t>
   </si>
   <si>
     <t xml:space="preserve">2.72633790969849</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74238419532776</t>
+    <t xml:space="preserve">2.74238443374634</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80015277862549</t>
+    <t xml:space="preserve">2.80015254020691</t>
   </si>
   <si>
     <t xml:space="preserve">2.78571033477783</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82422280311584</t>
+    <t xml:space="preserve">2.82422256469727</t>
   </si>
   <si>
     <t xml:space="preserve">2.78731536865234</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7937343120575</t>
+    <t xml:space="preserve">2.79373407363892</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80496644973755</t>
+    <t xml:space="preserve">2.80496668815613</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78410601615906</t>
+    <t xml:space="preserve">2.78410625457764</t>
   </si>
   <si>
     <t xml:space="preserve">2.77608251571655</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79533839225769</t>
+    <t xml:space="preserve">2.79533863067627</t>
   </si>
   <si>
     <t xml:space="preserve">2.82261800765991</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76003575325012</t>
+    <t xml:space="preserve">2.7600359916687</t>
   </si>
   <si>
     <t xml:space="preserve">2.77929210662842</t>
@@ -803,28 +803,28 @@
     <t xml:space="preserve">2.79854774475098</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7744779586792</t>
+    <t xml:space="preserve">2.77447772026062</t>
   </si>
   <si>
     <t xml:space="preserve">2.80336213111877</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83545517921448</t>
+    <t xml:space="preserve">2.83545541763306</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84026956558228</t>
+    <t xml:space="preserve">2.8402693271637</t>
   </si>
   <si>
     <t xml:space="preserve">2.83224606513977</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8113853931427</t>
+    <t xml:space="preserve">2.81138515472412</t>
   </si>
   <si>
     <t xml:space="preserve">2.81619930267334</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76324510574341</t>
+    <t xml:space="preserve">2.76324486732483</t>
   </si>
   <si>
     <t xml:space="preserve">2.71189570426941</t>
@@ -833,25 +833,25 @@
     <t xml:space="preserve">2.72473287582397</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79694318771362</t>
+    <t xml:space="preserve">2.7969434261322</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79052448272705</t>
+    <t xml:space="preserve">2.79052472114563</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76805949211121</t>
+    <t xml:space="preserve">2.76805925369263</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73115205764771</t>
+    <t xml:space="preserve">2.73115181922913</t>
   </si>
   <si>
     <t xml:space="preserve">2.70387244224548</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81459474563599</t>
+    <t xml:space="preserve">2.81459450721741</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82903695106506</t>
+    <t xml:space="preserve">2.82903647422791</t>
   </si>
   <si>
     <t xml:space="preserve">2.84347867965698</t>
@@ -860,10 +860,10 @@
     <t xml:space="preserve">2.77768731117249</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77126860618591</t>
+    <t xml:space="preserve">2.77126836776733</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88840961456299</t>
+    <t xml:space="preserve">2.88840937614441</t>
   </si>
   <si>
     <t xml:space="preserve">2.87236285209656</t>
@@ -878,22 +878,22 @@
     <t xml:space="preserve">2.85952544212341</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90927004814148</t>
+    <t xml:space="preserve">2.90927028656006</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99913191795349</t>
+    <t xml:space="preserve">2.99913215637207</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96864342689514</t>
+    <t xml:space="preserve">2.96864318847656</t>
   </si>
   <si>
     <t xml:space="preserve">2.830641746521</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87878155708313</t>
+    <t xml:space="preserve">2.87878179550171</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87717700004578</t>
+    <t xml:space="preserve">2.8771767616272</t>
   </si>
   <si>
     <t xml:space="preserve">2.87557244300842</t>
@@ -902,10 +902,10 @@
     <t xml:space="preserve">2.75201225280762</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76164031028748</t>
+    <t xml:space="preserve">2.76164054870605</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78892016410828</t>
+    <t xml:space="preserve">2.7889199256897</t>
   </si>
   <si>
     <t xml:space="preserve">2.67980217933655</t>
@@ -923,25 +923,25 @@
     <t xml:space="preserve">2.82101345062256</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73436093330383</t>
+    <t xml:space="preserve">2.73436117172241</t>
   </si>
   <si>
     <t xml:space="preserve">2.81780433654785</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76484990119934</t>
+    <t xml:space="preserve">2.76485013961792</t>
   </si>
   <si>
     <t xml:space="preserve">2.74077963829041</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79212951660156</t>
+    <t xml:space="preserve">2.79212927818298</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66375589370728</t>
+    <t xml:space="preserve">2.66375541687012</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6075918674469</t>
+    <t xml:space="preserve">2.60759210586548</t>
   </si>
   <si>
     <t xml:space="preserve">2.55142855644226</t>
@@ -950,46 +950,46 @@
     <t xml:space="preserve">2.56747531890869</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59956884384155</t>
+    <t xml:space="preserve">2.59956860542297</t>
   </si>
   <si>
     <t xml:space="preserve">2.55945205688477</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50328803062439</t>
+    <t xml:space="preserve">2.50328826904297</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45514822006226</t>
+    <t xml:space="preserve">2.45514798164368</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47921800613403</t>
+    <t xml:space="preserve">2.47921824455261</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47119498252869</t>
+    <t xml:space="preserve">2.47119474411011</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43107795715332</t>
+    <t xml:space="preserve">2.43107771873474</t>
   </si>
   <si>
     <t xml:space="preserve">2.46317148208618</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48724150657654</t>
+    <t xml:space="preserve">2.48724174499512</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49526500701904</t>
+    <t xml:space="preserve">2.49526476860046</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5273585319519</t>
+    <t xml:space="preserve">2.52735829353333</t>
   </si>
   <si>
     <t xml:space="preserve">2.58352184295654</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65573215484619</t>
+    <t xml:space="preserve">2.65573239326477</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9124801158905</t>
+    <t xml:space="preserve">2.91247987747192</t>
   </si>
   <si>
     <t xml:space="preserve">2.82002472877502</t>
@@ -1004,37 +1004,37 @@
     <t xml:space="preserve">2.84468984603882</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85291147232056</t>
+    <t xml:space="preserve">2.85291171073914</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81180310249329</t>
+    <t xml:space="preserve">2.81180334091187</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72136545181274</t>
+    <t xml:space="preserve">2.72136521339417</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68025684356689</t>
+    <t xml:space="preserve">2.68025708198547</t>
   </si>
   <si>
     <t xml:space="preserve">2.69670009613037</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64737033843994</t>
+    <t xml:space="preserve">2.64737010002136</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6555917263031</t>
+    <t xml:space="preserve">2.65559196472168</t>
   </si>
   <si>
-    <t xml:space="preserve">2.663813829422</t>
+    <t xml:space="preserve">2.66381359100342</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63092732429504</t>
+    <t xml:space="preserve">2.63092708587646</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63914847373962</t>
+    <t xml:space="preserve">2.6391487121582</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55693221092224</t>
+    <t xml:space="preserve">2.55693197250366</t>
   </si>
   <si>
     <t xml:space="preserve">2.59804058074951</t>
@@ -1049,13 +1049,13 @@
     <t xml:space="preserve">2.60626220703125</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52404570579529</t>
+    <t xml:space="preserve">2.52404546737671</t>
   </si>
   <si>
     <t xml:space="preserve">2.58159708976746</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61448407173157</t>
+    <t xml:space="preserve">2.61448383331299</t>
   </si>
   <si>
     <t xml:space="preserve">2.58981871604919</t>
@@ -1064,19 +1064,19 @@
     <t xml:space="preserve">2.62270545959473</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51582407951355</t>
+    <t xml:space="preserve">2.51582384109497</t>
   </si>
   <si>
     <t xml:space="preserve">2.57337546348572</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5651535987854</t>
+    <t xml:space="preserve">2.56515383720398</t>
   </si>
   <si>
     <t xml:space="preserve">2.53226709365845</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47471570968628</t>
+    <t xml:space="preserve">2.4747154712677</t>
   </si>
   <si>
     <t xml:space="preserve">2.48293733596802</t>
@@ -1091,40 +1091,40 @@
     <t xml:space="preserve">2.42538571357727</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43360733985901</t>
+    <t xml:space="preserve">2.43360757827759</t>
   </si>
   <si>
     <t xml:space="preserve">2.49115872383118</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50760245323181</t>
+    <t xml:space="preserve">2.50760269165039</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54048871994019</t>
+    <t xml:space="preserve">2.54048895835876</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67203497886658</t>
+    <t xml:space="preserve">2.67203521728516</t>
   </si>
   <si>
     <t xml:space="preserve">2.68847846984863</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70492172241211</t>
+    <t xml:space="preserve">2.70492196083069</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71314334869385</t>
+    <t xml:space="preserve">2.71314358711243</t>
   </si>
   <si>
     <t xml:space="preserve">2.75425171852112</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78713846206665</t>
+    <t xml:space="preserve">2.78713822364807</t>
   </si>
   <si>
     <t xml:space="preserve">2.77069520950317</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7295868396759</t>
+    <t xml:space="preserve">2.72958660125732</t>
   </si>
   <si>
     <t xml:space="preserve">2.7460298538208</t>
@@ -1139,19 +1139,19 @@
     <t xml:space="preserve">2.87757658958435</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91868448257446</t>
+    <t xml:space="preserve">2.91868472099304</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89401984214783</t>
+    <t xml:space="preserve">2.89401960372925</t>
   </si>
   <si>
     <t xml:space="preserve">2.86113309860229</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90224146842957</t>
+    <t xml:space="preserve">2.90224123001099</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88579821586609</t>
+    <t xml:space="preserve">2.88579797744751</t>
   </si>
   <si>
     <t xml:space="preserve">2.83646821975708</t>
@@ -1163,19 +1163,19 @@
     <t xml:space="preserve">2.82824659347534</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9269061088562</t>
+    <t xml:space="preserve">2.92690634727478</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80358123779297</t>
+    <t xml:space="preserve">2.80358147621155</t>
   </si>
   <si>
     <t xml:space="preserve">2.77809453010559</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82057309150696</t>
+    <t xml:space="preserve">2.82057285308838</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82906889915466</t>
+    <t xml:space="preserve">2.8290684223175</t>
   </si>
   <si>
     <t xml:space="preserve">2.88853859901428</t>
@@ -1187,7 +1187,7 @@
     <t xml:space="preserve">2.92252135276794</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90552973747253</t>
+    <t xml:space="preserve">2.90552997589111</t>
   </si>
   <si>
     <t xml:space="preserve">2.87154722213745</t>
@@ -1196,37 +1196,37 @@
     <t xml:space="preserve">2.85455560684204</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91402578353882</t>
+    <t xml:space="preserve">2.91402554512024</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93101716041565</t>
+    <t xml:space="preserve">2.93101692199707</t>
   </si>
   <si>
     <t xml:space="preserve">2.94800853729248</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89703440666199</t>
+    <t xml:space="preserve">2.89703416824341</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93951272964478</t>
+    <t xml:space="preserve">2.93951296806335</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98199105262756</t>
+    <t xml:space="preserve">2.98199129104614</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79508566856384</t>
+    <t xml:space="preserve">2.79508590698242</t>
   </si>
   <si>
     <t xml:space="preserve">2.78659009933472</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76110291481018</t>
+    <t xml:space="preserve">2.76110315322876</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76959848403931</t>
+    <t xml:space="preserve">2.76959872245789</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81207728385925</t>
+    <t xml:space="preserve">2.81207704544067</t>
   </si>
   <si>
     <t xml:space="preserve">2.83756422996521</t>
@@ -1235,28 +1235,28 @@
     <t xml:space="preserve">2.86305141448975</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62517166137695</t>
+    <t xml:space="preserve">2.62517189979553</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67614603042603</t>
+    <t xml:space="preserve">2.67614579200745</t>
   </si>
   <si>
     <t xml:space="preserve">2.61667585372925</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55720639228821</t>
+    <t xml:space="preserve">2.55720591545105</t>
   </si>
   <si>
     <t xml:space="preserve">2.51472759246826</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49773621559143</t>
+    <t xml:space="preserve">2.49773597717285</t>
   </si>
   <si>
     <t xml:space="preserve">2.4807448387146</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53171896934509</t>
+    <t xml:space="preserve">2.53171920776367</t>
   </si>
   <si>
     <t xml:space="preserve">2.46375346183777</t>
@@ -1271,19 +1271,19 @@
     <t xml:space="preserve">2.56570196151733</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59118890762329</t>
+    <t xml:space="preserve">2.59118914604187</t>
   </si>
   <si>
     <t xml:space="preserve">2.47224926948547</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63366723060608</t>
+    <t xml:space="preserve">2.63366746902466</t>
   </si>
   <si>
-    <t xml:space="preserve">2.599684715271</t>
+    <t xml:space="preserve">2.59968447685242</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52322340011597</t>
+    <t xml:space="preserve">2.52322363853455</t>
   </si>
   <si>
     <t xml:space="preserve">2.57419753074646</t>
@@ -1292,7 +1292,7 @@
     <t xml:space="preserve">3.075443983078</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00747847557068</t>
+    <t xml:space="preserve">3.0074782371521</t>
   </si>
   <si>
     <t xml:space="preserve">2.99048686027527</t>
@@ -1301,10 +1301,10 @@
     <t xml:space="preserve">2.96499991416931</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97349572181702</t>
+    <t xml:space="preserve">2.97349548339844</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95650434494019</t>
+    <t xml:space="preserve">2.95650410652161</t>
   </si>
   <si>
     <t xml:space="preserve">2.84606003761292</t>
@@ -1313,10 +1313,10 @@
     <t xml:space="preserve">2.75260734558105</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66765022277832</t>
+    <t xml:space="preserve">2.6676504611969</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65915465354919</t>
+    <t xml:space="preserve">2.65915441513062</t>
   </si>
   <si>
     <t xml:space="preserve">2.31083083152771</t>
@@ -1328,16 +1328,16 @@
     <t xml:space="preserve">2.34481358528137</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45525789260864</t>
+    <t xml:space="preserve">2.45525765419006</t>
   </si>
   <si>
     <t xml:space="preserve">2.4892406463623</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65065860748291</t>
+    <t xml:space="preserve">2.65065884590149</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64216327667236</t>
+    <t xml:space="preserve">2.64216303825378</t>
   </si>
   <si>
     <t xml:space="preserve">2.71012902259827</t>
@@ -1346,10 +1346,10 @@
     <t xml:space="preserve">2.69313764572144</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71862459182739</t>
+    <t xml:space="preserve">2.71862435340881</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74411177635193</t>
+    <t xml:space="preserve">2.74411153793335</t>
   </si>
   <si>
     <t xml:space="preserve">2.68464183807373</t>
@@ -1361,13 +1361,13 @@
     <t xml:space="preserve">2.50623202323914</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44676208496094</t>
+    <t xml:space="preserve">2.44676232337952</t>
   </si>
   <si>
     <t xml:space="preserve">2.37879633903503</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42977046966553</t>
+    <t xml:space="preserve">2.42977070808411</t>
   </si>
   <si>
     <t xml:space="preserve">2.37030076980591</t>
@@ -1376,37 +1376,37 @@
     <t xml:space="preserve">2.31932640075684</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27684783935547</t>
+    <t xml:space="preserve">2.27684807777405</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26835227012634</t>
+    <t xml:space="preserve">2.26835250854492</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30233526229858</t>
+    <t xml:space="preserve">2.30233502388</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33631801605225</t>
+    <t xml:space="preserve">2.33631777763367</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39578747749329</t>
+    <t xml:space="preserve">2.39578771591187</t>
   </si>
   <si>
     <t xml:space="preserve">2.72712016105652</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99898266792297</t>
+    <t xml:space="preserve">2.99898242950439</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03296518325806</t>
+    <t xml:space="preserve">3.03296542167664</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01597380638123</t>
+    <t xml:space="preserve">3.0159740447998</t>
   </si>
   <si>
     <t xml:space="preserve">3.04146099090576</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1943838596344</t>
+    <t xml:space="preserve">3.19438409805298</t>
   </si>
   <si>
     <t xml:space="preserve">3.1264181137085</t>
@@ -1421,25 +1421,25 @@
     <t xml:space="preserve">3.16040086746216</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21137523651123</t>
+    <t xml:space="preserve">3.21137547492981</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31332349777222</t>
+    <t xml:space="preserve">3.3133237361908</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26234936714172</t>
+    <t xml:space="preserve">3.26234912872314</t>
   </si>
   <si>
     <t xml:space="preserve">3.33031511306763</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22836685180664</t>
+    <t xml:space="preserve">3.22836637496948</t>
   </si>
   <si>
     <t xml:space="preserve">3.17739224433899</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14340972900391</t>
+    <t xml:space="preserve">3.14340949058533</t>
   </si>
   <si>
     <t xml:space="preserve">3.10942697525024</t>
@@ -1448,25 +1448,25 @@
     <t xml:space="preserve">3.27934074401855</t>
   </si>
   <si>
-    <t xml:space="preserve">3.48323774337769</t>
+    <t xml:space="preserve">3.48323750495911</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39828062057495</t>
+    <t xml:space="preserve">3.39828038215637</t>
   </si>
   <si>
     <t xml:space="preserve">3.46624636650085</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36429810523987</t>
+    <t xml:space="preserve">3.36429786682129</t>
   </si>
   <si>
     <t xml:space="preserve">3.34730648994446</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24535799026489</t>
+    <t xml:space="preserve">3.24535775184631</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02446961402893</t>
+    <t xml:space="preserve">3.02446985244751</t>
   </si>
   <si>
     <t xml:space="preserve">3.16417121887207</t>
@@ -1487,7 +1487,7 @@
     <t xml:space="preserve">3.02393102645874</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1028163433075</t>
+    <t xml:space="preserve">3.10281610488892</t>
   </si>
   <si>
     <t xml:space="preserve">3.13787627220154</t>
@@ -1496,13 +1496,13 @@
     <t xml:space="preserve">2.98010611534119</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09405136108398</t>
+    <t xml:space="preserve">3.09405112266541</t>
   </si>
   <si>
     <t xml:space="preserve">3.07652115821838</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06775641441345</t>
+    <t xml:space="preserve">3.06775617599487</t>
   </si>
   <si>
     <t xml:space="preserve">3.04146122932434</t>
@@ -1514,7 +1514,7 @@
     <t xml:space="preserve">2.9888710975647</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89245557785034</t>
+    <t xml:space="preserve">2.89245581626892</t>
   </si>
   <si>
     <t xml:space="preserve">2.92751574516296</t>
@@ -1523,16 +1523,16 @@
     <t xml:space="preserve">2.99763607978821</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96257591247559</t>
+    <t xml:space="preserve">2.96257615089417</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86616063117981</t>
+    <t xml:space="preserve">2.86616086959839</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91875100135803</t>
+    <t xml:space="preserve">2.91875076293945</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80480575561523</t>
+    <t xml:space="preserve">2.80480551719666</t>
   </si>
   <si>
     <t xml:space="preserve">2.82233572006226</t>
@@ -1553,10 +1553,10 @@
     <t xml:space="preserve">3.03269624710083</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90122103691101</t>
+    <t xml:space="preserve">2.90122079849243</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88369059562683</t>
+    <t xml:space="preserve">2.88369083404541</t>
   </si>
   <si>
     <t xml:space="preserve">2.8749258518219</t>
@@ -1565,10 +1565,10 @@
     <t xml:space="preserve">2.81357073783875</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83986592292786</t>
+    <t xml:space="preserve">2.83986568450928</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68209552764893</t>
+    <t xml:space="preserve">2.68209528923035</t>
   </si>
   <si>
     <t xml:space="preserve">2.69086050987244</t>
@@ -1577,28 +1577,28 @@
     <t xml:space="preserve">2.66456532478333</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8573956489563</t>
+    <t xml:space="preserve">2.85739588737488</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90998601913452</t>
+    <t xml:space="preserve">2.90998578071594</t>
   </si>
   <si>
     <t xml:space="preserve">2.7785108089447</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76974558830261</t>
+    <t xml:space="preserve">2.76974582672119</t>
   </si>
   <si>
     <t xml:space="preserve">2.79604077339172</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84863066673279</t>
+    <t xml:space="preserve">2.84863090515137</t>
   </si>
   <si>
     <t xml:space="preserve">3.08528614044189</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7609806060791</t>
+    <t xml:space="preserve">2.76098036766052</t>
   </si>
   <si>
     <t xml:space="preserve">2.78727579116821</t>
@@ -1607,7 +1607,7 @@
     <t xml:space="preserve">2.75221562385559</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73468518257141</t>
+    <t xml:space="preserve">2.73468542098999</t>
   </si>
   <si>
     <t xml:space="preserve">2.86875891685486</t>
@@ -1625,34 +1625,34 @@
     <t xml:space="preserve">2.83221411705017</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88703107833862</t>
+    <t xml:space="preserve">2.8870313167572</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85048651695251</t>
+    <t xml:space="preserve">2.85048627853394</t>
   </si>
   <si>
-    <t xml:space="preserve">2.960120677948</t>
+    <t xml:space="preserve">2.96012043952942</t>
   </si>
   <si>
     <t xml:space="preserve">2.99666523933411</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79566931724548</t>
+    <t xml:space="preserve">2.79566955566406</t>
   </si>
   <si>
     <t xml:space="preserve">2.81394171714783</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77739715576172</t>
+    <t xml:space="preserve">2.77739691734314</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7591245174408</t>
+    <t xml:space="preserve">2.75912475585938</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70430755615234</t>
+    <t xml:space="preserve">2.70430779457092</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64949059486389</t>
+    <t xml:space="preserve">2.64949083328247</t>
   </si>
   <si>
     <t xml:space="preserve">2.68603539466858</t>
@@ -1670,25 +1670,22 @@
     <t xml:space="preserve">2.72258019447327</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59467363357544</t>
+    <t xml:space="preserve">2.59467339515686</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57640099525452</t>
+    <t xml:space="preserve">2.5764012336731</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6129457950592</t>
+    <t xml:space="preserve">2.61294603347778</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97839283943176</t>
+    <t xml:space="preserve">2.97839307785034</t>
   </si>
   <si>
     <t xml:space="preserve">2.823077917099</t>
   </si>
   <si>
     <t xml:space="preserve">2.85962271690369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80480551719666</t>
   </si>
   <si>
     <t xml:space="preserve">2.89616751670837</t>
@@ -1703,7 +1700,7 @@
     <t xml:space="preserve">3.01493763923645</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96925663948059</t>
+    <t xml:space="preserve">2.96925687789917</t>
   </si>
   <si>
     <t xml:space="preserve">3.02674722671509</t>
@@ -1800,9 +1797,6 @@
   </si>
   <si>
     <t xml:space="preserve">3.23614478111267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96012043952942</t>
   </si>
   <si>
     <t xml:space="preserve">3.20000004768372</t>
@@ -56985,7 +56979,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G2103" t="s">
-        <v>558</v>
+        <v>506</v>
       </c>
       <c r="H2103" t="s">
         <v>9</v>
@@ -57011,7 +57005,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G2104" t="s">
-        <v>558</v>
+        <v>506</v>
       </c>
       <c r="H2104" t="s">
         <v>9</v>
@@ -57219,7 +57213,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G2112" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="H2112" t="s">
         <v>9</v>
@@ -57349,7 +57343,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G2117" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="H2117" t="s">
         <v>9</v>
@@ -57375,7 +57369,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G2118" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="H2118" t="s">
         <v>9</v>
@@ -57401,7 +57395,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G2119" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="H2119" t="s">
         <v>9</v>
@@ -57453,7 +57447,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G2121" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="H2121" t="s">
         <v>9</v>
@@ -57479,7 +57473,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G2122" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="H2122" t="s">
         <v>9</v>
@@ -57531,7 +57525,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G2124" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="H2124" t="s">
         <v>9</v>
@@ -57557,7 +57551,7 @@
         <v>3.25</v>
       </c>
       <c r="G2125" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="H2125" t="s">
         <v>9</v>
@@ -57583,7 +57577,7 @@
         <v>3.25</v>
       </c>
       <c r="G2126" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="H2126" t="s">
         <v>9</v>
@@ -57609,7 +57603,7 @@
         <v>3.25</v>
       </c>
       <c r="G2127" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="H2127" t="s">
         <v>9</v>
@@ -57635,7 +57629,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G2128" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="H2128" t="s">
         <v>9</v>
@@ -57661,7 +57655,7 @@
         <v>3.25</v>
       </c>
       <c r="G2129" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="H2129" t="s">
         <v>9</v>
@@ -57765,7 +57759,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G2133" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="H2133" t="s">
         <v>9</v>
@@ -57791,7 +57785,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G2134" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H2134" t="s">
         <v>9</v>
@@ -57817,7 +57811,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G2135" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="H2135" t="s">
         <v>9</v>
@@ -57843,7 +57837,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G2136" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="H2136" t="s">
         <v>9</v>
@@ -57869,7 +57863,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G2137" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="H2137" t="s">
         <v>9</v>
@@ -57895,7 +57889,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G2138" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="H2138" t="s">
         <v>9</v>
@@ -57921,7 +57915,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G2139" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="H2139" t="s">
         <v>9</v>
@@ -57947,7 +57941,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2140" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H2140" t="s">
         <v>9</v>
@@ -57973,7 +57967,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G2141" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="H2141" t="s">
         <v>9</v>
@@ -57999,7 +57993,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G2142" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="H2142" t="s">
         <v>9</v>
@@ -58025,7 +58019,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G2143" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="H2143" t="s">
         <v>9</v>
@@ -58051,7 +58045,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G2144" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="H2144" t="s">
         <v>9</v>
@@ -58077,7 +58071,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G2145" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="H2145" t="s">
         <v>9</v>
@@ -58103,7 +58097,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G2146" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="H2146" t="s">
         <v>9</v>
@@ -58129,7 +58123,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G2147" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="H2147" t="s">
         <v>9</v>
@@ -58155,7 +58149,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G2148" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="H2148" t="s">
         <v>9</v>
@@ -58181,7 +58175,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G2149" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="H2149" t="s">
         <v>9</v>
@@ -58207,7 +58201,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G2150" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="H2150" t="s">
         <v>9</v>
@@ -58233,7 +58227,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G2151" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="H2151" t="s">
         <v>9</v>
@@ -58259,7 +58253,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G2152" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="H2152" t="s">
         <v>9</v>
@@ -58285,7 +58279,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G2153" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="H2153" t="s">
         <v>9</v>
@@ -58311,7 +58305,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G2154" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="H2154" t="s">
         <v>9</v>
@@ -58337,7 +58331,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G2155" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="H2155" t="s">
         <v>9</v>
@@ -58363,7 +58357,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G2156" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="H2156" t="s">
         <v>9</v>
@@ -58389,7 +58383,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G2157" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="H2157" t="s">
         <v>9</v>
@@ -58415,7 +58409,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G2158" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H2158" t="s">
         <v>9</v>
@@ -58441,7 +58435,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G2159" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="H2159" t="s">
         <v>9</v>
@@ -58467,7 +58461,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G2160" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="H2160" t="s">
         <v>9</v>
@@ -58493,7 +58487,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G2161" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H2161" t="s">
         <v>9</v>
@@ -58519,7 +58513,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G2162" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="H2162" t="s">
         <v>9</v>
@@ -58545,7 +58539,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G2163" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="H2163" t="s">
         <v>9</v>
@@ -58571,7 +58565,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G2164" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="H2164" t="s">
         <v>9</v>
@@ -58597,7 +58591,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G2165" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="H2165" t="s">
         <v>9</v>
@@ -58623,7 +58617,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G2166" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="H2166" t="s">
         <v>9</v>
@@ -58649,7 +58643,7 @@
         <v>3.25</v>
       </c>
       <c r="G2167" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="H2167" t="s">
         <v>9</v>
@@ -58675,7 +58669,7 @@
         <v>3.25</v>
       </c>
       <c r="G2168" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="H2168" t="s">
         <v>9</v>
@@ -58701,7 +58695,7 @@
         <v>3.25</v>
       </c>
       <c r="G2169" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="H2169" t="s">
         <v>9</v>
@@ -58727,7 +58721,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G2170" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="H2170" t="s">
         <v>9</v>
@@ -58753,7 +58747,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G2171" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="H2171" t="s">
         <v>9</v>
@@ -58779,7 +58773,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G2172" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="H2172" t="s">
         <v>9</v>
@@ -58805,7 +58799,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G2173" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="H2173" t="s">
         <v>9</v>
@@ -58831,7 +58825,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G2174" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="H2174" t="s">
         <v>9</v>
@@ -58857,7 +58851,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2175" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H2175" t="s">
         <v>9</v>
@@ -58883,7 +58877,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2176" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H2176" t="s">
         <v>9</v>
@@ -58909,7 +58903,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2177" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H2177" t="s">
         <v>9</v>
@@ -58935,7 +58929,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G2178" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="H2178" t="s">
         <v>9</v>
@@ -58961,7 +58955,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G2179" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="H2179" t="s">
         <v>9</v>
@@ -58987,7 +58981,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G2180" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="H2180" t="s">
         <v>9</v>
@@ -59013,7 +59007,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G2181" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="H2181" t="s">
         <v>9</v>
@@ -59039,7 +59033,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2182" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H2182" t="s">
         <v>9</v>
@@ -59065,7 +59059,7 @@
         <v>3.25</v>
       </c>
       <c r="G2183" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="H2183" t="s">
         <v>9</v>
@@ -59091,7 +59085,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G2184" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="H2184" t="s">
         <v>9</v>
@@ -59117,7 +59111,7 @@
         <v>3.25</v>
       </c>
       <c r="G2185" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="H2185" t="s">
         <v>9</v>
@@ -59143,7 +59137,7 @@
         <v>3.25</v>
       </c>
       <c r="G2186" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="H2186" t="s">
         <v>9</v>
@@ -59169,7 +59163,7 @@
         <v>3.25</v>
       </c>
       <c r="G2187" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="H2187" t="s">
         <v>9</v>
@@ -59195,7 +59189,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G2188" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="H2188" t="s">
         <v>9</v>
@@ -59221,7 +59215,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G2189" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="H2189" t="s">
         <v>9</v>
@@ -59247,7 +59241,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G2190" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="H2190" t="s">
         <v>9</v>
@@ -59273,7 +59267,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G2191" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="H2191" t="s">
         <v>9</v>
@@ -59299,7 +59293,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G2192" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="H2192" t="s">
         <v>9</v>
@@ -59325,7 +59319,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G2193" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="H2193" t="s">
         <v>9</v>
@@ -59351,7 +59345,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G2194" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="H2194" t="s">
         <v>9</v>
@@ -59377,7 +59371,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G2195" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="H2195" t="s">
         <v>9</v>
@@ -59403,7 +59397,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G2196" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="H2196" t="s">
         <v>9</v>
@@ -59429,7 +59423,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2197" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H2197" t="s">
         <v>9</v>
@@ -59455,7 +59449,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G2198" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="H2198" t="s">
         <v>9</v>
@@ -59481,7 +59475,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G2199" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H2199" t="s">
         <v>9</v>
@@ -59507,7 +59501,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G2200" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="H2200" t="s">
         <v>9</v>
@@ -59533,7 +59527,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G2201" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="H2201" t="s">
         <v>9</v>
@@ -59559,7 +59553,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G2202" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="H2202" t="s">
         <v>9</v>
@@ -59585,7 +59579,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G2203" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H2203" t="s">
         <v>9</v>
@@ -59611,7 +59605,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G2204" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="H2204" t="s">
         <v>9</v>
@@ -59637,7 +59631,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G2205" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="H2205" t="s">
         <v>9</v>
@@ -59663,7 +59657,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2206" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H2206" t="s">
         <v>9</v>
@@ -59689,7 +59683,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G2207" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="H2207" t="s">
         <v>9</v>
@@ -59715,7 +59709,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G2208" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="H2208" t="s">
         <v>9</v>
@@ -59741,7 +59735,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G2209" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="H2209" t="s">
         <v>9</v>
@@ -59767,7 +59761,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G2210" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="H2210" t="s">
         <v>9</v>
@@ -59793,7 +59787,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G2211" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="H2211" t="s">
         <v>9</v>
@@ -59819,7 +59813,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G2212" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H2212" t="s">
         <v>9</v>
@@ -59845,7 +59839,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G2213" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H2213" t="s">
         <v>9</v>
@@ -59871,7 +59865,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G2214" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="H2214" t="s">
         <v>9</v>
@@ -59897,7 +59891,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G2215" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H2215" t="s">
         <v>9</v>
@@ -59923,7 +59917,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G2216" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H2216" t="s">
         <v>9</v>
@@ -59949,7 +59943,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G2217" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="H2217" t="s">
         <v>9</v>
@@ -59975,7 +59969,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G2218" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="H2218" t="s">
         <v>9</v>
@@ -60001,7 +59995,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G2219" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="H2219" t="s">
         <v>9</v>
@@ -60027,7 +60021,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G2220" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H2220" t="s">
         <v>9</v>
@@ -60053,7 +60047,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G2221" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="H2221" t="s">
         <v>9</v>
@@ -60079,7 +60073,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G2222" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="H2222" t="s">
         <v>9</v>
@@ -60105,7 +60099,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G2223" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="H2223" t="s">
         <v>9</v>
@@ -60131,7 +60125,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G2224" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="H2224" t="s">
         <v>9</v>
@@ -60157,7 +60151,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G2225" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="H2225" t="s">
         <v>9</v>
@@ -60183,7 +60177,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G2226" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H2226" t="s">
         <v>9</v>
@@ -60209,7 +60203,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2227" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H2227" t="s">
         <v>9</v>
@@ -60235,7 +60229,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G2228" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H2228" t="s">
         <v>9</v>
@@ -60261,7 +60255,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G2229" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="H2229" t="s">
         <v>9</v>
@@ -60287,7 +60281,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G2230" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="H2230" t="s">
         <v>9</v>
@@ -60313,7 +60307,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G2231" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H2231" t="s">
         <v>9</v>
@@ -60339,7 +60333,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G2232" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H2232" t="s">
         <v>9</v>
@@ -60365,7 +60359,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G2233" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="H2233" t="s">
         <v>9</v>
@@ -60391,7 +60385,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G2234" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="H2234" t="s">
         <v>9</v>
@@ -60417,7 +60411,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G2235" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="H2235" t="s">
         <v>9</v>
@@ -60443,7 +60437,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G2236" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H2236" t="s">
         <v>9</v>
@@ -60469,7 +60463,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G2237" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="H2237" t="s">
         <v>9</v>
@@ -60495,7 +60489,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G2238" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="H2238" t="s">
         <v>9</v>
@@ -60521,7 +60515,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G2239" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="H2239" t="s">
         <v>9</v>
@@ -60547,7 +60541,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G2240" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="H2240" t="s">
         <v>9</v>
@@ -60573,7 +60567,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G2241" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="H2241" t="s">
         <v>9</v>
@@ -60599,7 +60593,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G2242" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="H2242" t="s">
         <v>9</v>
@@ -60625,7 +60619,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G2243" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H2243" t="s">
         <v>9</v>
@@ -60651,7 +60645,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G2244" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H2244" t="s">
         <v>9</v>
@@ -60677,7 +60671,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G2245" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H2245" t="s">
         <v>9</v>
@@ -60703,7 +60697,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G2246" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="H2246" t="s">
         <v>9</v>
@@ -60729,7 +60723,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G2247" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="H2247" t="s">
         <v>9</v>
@@ -60755,7 +60749,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G2248" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="H2248" t="s">
         <v>9</v>
@@ -60781,7 +60775,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G2249" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H2249" t="s">
         <v>9</v>
@@ -60807,7 +60801,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G2250" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H2250" t="s">
         <v>9</v>
@@ -60833,7 +60827,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G2251" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H2251" t="s">
         <v>9</v>
@@ -60859,7 +60853,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G2252" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="H2252" t="s">
         <v>9</v>
@@ -60885,7 +60879,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G2253" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="H2253" t="s">
         <v>9</v>
@@ -60911,7 +60905,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G2254" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="H2254" t="s">
         <v>9</v>
@@ -60937,7 +60931,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G2255" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="H2255" t="s">
         <v>9</v>
@@ -60963,7 +60957,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G2256" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="H2256" t="s">
         <v>9</v>
@@ -60989,7 +60983,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G2257" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H2257" t="s">
         <v>9</v>
@@ -61015,7 +61009,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G2258" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="H2258" t="s">
         <v>9</v>
@@ -61041,7 +61035,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G2259" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="H2259" t="s">
         <v>9</v>
@@ -61067,7 +61061,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G2260" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="H2260" t="s">
         <v>9</v>
@@ -61093,7 +61087,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G2261" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="H2261" t="s">
         <v>9</v>
@@ -61119,7 +61113,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G2262" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="H2262" t="s">
         <v>9</v>
@@ -61145,7 +61139,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G2263" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="H2263" t="s">
         <v>9</v>
@@ -61171,7 +61165,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G2264" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="H2264" t="s">
         <v>9</v>
@@ -61197,7 +61191,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G2265" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="H2265" t="s">
         <v>9</v>
@@ -61223,7 +61217,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G2266" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="H2266" t="s">
         <v>9</v>
@@ -61249,7 +61243,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G2267" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="H2267" t="s">
         <v>9</v>
@@ -61275,7 +61269,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G2268" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="H2268" t="s">
         <v>9</v>
@@ -61301,7 +61295,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G2269" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="H2269" t="s">
         <v>9</v>
@@ -61327,7 +61321,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G2270" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="H2270" t="s">
         <v>9</v>
@@ -61353,7 +61347,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G2271" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="H2271" t="s">
         <v>9</v>
@@ -61379,7 +61373,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G2272" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="H2272" t="s">
         <v>9</v>
@@ -61405,7 +61399,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G2273" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="H2273" t="s">
         <v>9</v>
@@ -61431,7 +61425,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G2274" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="H2274" t="s">
         <v>9</v>
@@ -61457,7 +61451,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G2275" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="H2275" t="s">
         <v>9</v>
@@ -61483,7 +61477,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G2276" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="H2276" t="s">
         <v>9</v>
@@ -61509,7 +61503,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G2277" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="H2277" t="s">
         <v>9</v>
@@ -61535,7 +61529,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G2278" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="H2278" t="s">
         <v>9</v>
@@ -61561,7 +61555,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G2279" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="H2279" t="s">
         <v>9</v>
@@ -61587,7 +61581,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G2280" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H2280" t="s">
         <v>9</v>
@@ -61613,7 +61607,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G2281" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="H2281" t="s">
         <v>9</v>
@@ -61639,7 +61633,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G2282" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H2282" t="s">
         <v>9</v>
@@ -61665,7 +61659,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G2283" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H2283" t="s">
         <v>9</v>
@@ -61691,7 +61685,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G2284" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="H2284" t="s">
         <v>9</v>
@@ -61717,7 +61711,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G2285" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H2285" t="s">
         <v>9</v>
@@ -61743,7 +61737,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G2286" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="H2286" t="s">
         <v>9</v>
@@ -61769,7 +61763,7 @@
         <v>3.25</v>
       </c>
       <c r="G2287" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="H2287" t="s">
         <v>9</v>
@@ -61795,7 +61789,7 @@
         <v>3.25</v>
       </c>
       <c r="G2288" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="H2288" t="s">
         <v>9</v>
@@ -61821,7 +61815,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G2289" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="H2289" t="s">
         <v>9</v>
@@ -61847,7 +61841,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G2290" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="H2290" t="s">
         <v>9</v>
@@ -61873,7 +61867,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G2291" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="H2291" t="s">
         <v>9</v>
@@ -61899,7 +61893,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G2292" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H2292" t="s">
         <v>9</v>
@@ -61925,7 +61919,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G2293" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H2293" t="s">
         <v>9</v>
@@ -61951,7 +61945,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G2294" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="H2294" t="s">
         <v>9</v>
@@ -61977,7 +61971,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G2295" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="H2295" t="s">
         <v>9</v>
@@ -62003,7 +61997,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G2296" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="H2296" t="s">
         <v>9</v>
@@ -62029,7 +62023,7 @@
         <v>3.25</v>
       </c>
       <c r="G2297" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="H2297" t="s">
         <v>9</v>
@@ -62055,7 +62049,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G2298" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="H2298" t="s">
         <v>9</v>
@@ -62081,7 +62075,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G2299" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="H2299" t="s">
         <v>9</v>
@@ -62107,7 +62101,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2300" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H2300" t="s">
         <v>9</v>
@@ -62133,7 +62127,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G2301" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="H2301" t="s">
         <v>9</v>
@@ -62159,7 +62153,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G2302" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="H2302" t="s">
         <v>9</v>
@@ -62185,7 +62179,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G2303" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="H2303" t="s">
         <v>9</v>
@@ -62211,7 +62205,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G2304" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="H2304" t="s">
         <v>9</v>
@@ -62237,7 +62231,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G2305" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="H2305" t="s">
         <v>9</v>
@@ -62263,7 +62257,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G2306" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="H2306" t="s">
         <v>9</v>
@@ -62289,7 +62283,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G2307" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="H2307" t="s">
         <v>9</v>
@@ -62315,7 +62309,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G2308" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="H2308" t="s">
         <v>9</v>
@@ -62341,7 +62335,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G2309" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="H2309" t="s">
         <v>9</v>
@@ -62367,7 +62361,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G2310" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="H2310" t="s">
         <v>9</v>
@@ -62393,7 +62387,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2311" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H2311" t="s">
         <v>9</v>
@@ -62419,7 +62413,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2312" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H2312" t="s">
         <v>9</v>
@@ -62445,7 +62439,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G2313" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H2313" t="s">
         <v>9</v>
@@ -62471,7 +62465,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G2314" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="H2314" t="s">
         <v>9</v>
@@ -62497,7 +62491,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G2315" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="H2315" t="s">
         <v>9</v>
@@ -62523,7 +62517,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G2316" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H2316" t="s">
         <v>9</v>
@@ -62549,7 +62543,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G2317" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="H2317" t="s">
         <v>9</v>
@@ -62575,7 +62569,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G2318" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="H2318" t="s">
         <v>9</v>
@@ -62601,7 +62595,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G2319" t="s">
-        <v>596</v>
+        <v>539</v>
       </c>
       <c r="H2319" t="s">
         <v>9</v>
@@ -62627,7 +62621,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G2320" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="H2320" t="s">
         <v>9</v>
@@ -62653,7 +62647,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G2321" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="H2321" t="s">
         <v>9</v>
@@ -62679,7 +62673,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G2322" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="H2322" t="s">
         <v>9</v>
@@ -62705,7 +62699,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2323" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H2323" t="s">
         <v>9</v>
@@ -62731,7 +62725,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2324" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H2324" t="s">
         <v>9</v>
@@ -62757,7 +62751,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2325" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H2325" t="s">
         <v>9</v>
@@ -62783,7 +62777,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G2326" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="H2326" t="s">
         <v>9</v>
@@ -62809,7 +62803,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2327" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H2327" t="s">
         <v>9</v>
@@ -62835,7 +62829,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G2328" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="H2328" t="s">
         <v>9</v>
@@ -62861,7 +62855,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G2329" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="H2329" t="s">
         <v>9</v>
@@ -62887,7 +62881,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G2330" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="H2330" t="s">
         <v>9</v>
@@ -62913,7 +62907,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G2331" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H2331" t="s">
         <v>9</v>
@@ -62939,7 +62933,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G2332" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H2332" t="s">
         <v>9</v>
@@ -62965,7 +62959,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G2333" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="H2333" t="s">
         <v>9</v>
@@ -62991,7 +62985,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G2334" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H2334" t="s">
         <v>9</v>
@@ -63017,7 +63011,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G2335" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H2335" t="s">
         <v>9</v>
@@ -63043,7 +63037,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G2336" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H2336" t="s">
         <v>9</v>
@@ -63069,7 +63063,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G2337" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="H2337" t="s">
         <v>9</v>
@@ -63095,7 +63089,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G2338" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="H2338" t="s">
         <v>9</v>
@@ -63121,7 +63115,7 @@
         <v>3.25</v>
       </c>
       <c r="G2339" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="H2339" t="s">
         <v>9</v>
@@ -63147,7 +63141,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G2340" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="H2340" t="s">
         <v>9</v>
@@ -63173,7 +63167,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G2341" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H2341" t="s">
         <v>9</v>
@@ -63199,7 +63193,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G2342" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="H2342" t="s">
         <v>9</v>
@@ -63225,7 +63219,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G2343" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H2343" t="s">
         <v>9</v>
@@ -63251,7 +63245,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G2344" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H2344" t="s">
         <v>9</v>
@@ -63277,7 +63271,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G2345" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="H2345" t="s">
         <v>9</v>
@@ -63303,7 +63297,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G2346" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H2346" t="s">
         <v>9</v>
@@ -63329,7 +63323,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G2347" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="H2347" t="s">
         <v>9</v>
@@ -63355,7 +63349,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G2348" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="H2348" t="s">
         <v>9</v>
@@ -63381,7 +63375,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G2349" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="H2349" t="s">
         <v>9</v>
@@ -63407,7 +63401,7 @@
         <v>3.25</v>
       </c>
       <c r="G2350" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="H2350" t="s">
         <v>9</v>
@@ -63433,7 +63427,7 @@
         <v>3.25</v>
       </c>
       <c r="G2351" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="H2351" t="s">
         <v>9</v>
@@ -63459,7 +63453,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G2352" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="H2352" t="s">
         <v>9</v>
@@ -63485,7 +63479,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G2353" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="H2353" t="s">
         <v>9</v>
@@ -63511,7 +63505,7 @@
         <v>3.25</v>
       </c>
       <c r="G2354" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="H2354" t="s">
         <v>9</v>
@@ -63537,7 +63531,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G2355" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="H2355" t="s">
         <v>9</v>
@@ -63563,7 +63557,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G2356" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="H2356" t="s">
         <v>9</v>
@@ -63589,7 +63583,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G2357" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H2357" t="s">
         <v>9</v>
@@ -63615,7 +63609,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G2358" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H2358" t="s">
         <v>9</v>
@@ -63641,7 +63635,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G2359" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="H2359" t="s">
         <v>9</v>
@@ -63667,7 +63661,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G2360" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="H2360" t="s">
         <v>9</v>
@@ -63693,7 +63687,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G2361" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H2361" t="s">
         <v>9</v>
@@ -63719,7 +63713,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G2362" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="H2362" t="s">
         <v>9</v>
@@ -63745,7 +63739,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2363" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H2363" t="s">
         <v>9</v>
@@ -63771,7 +63765,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2364" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H2364" t="s">
         <v>9</v>
@@ -63797,7 +63791,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G2365" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="H2365" t="s">
         <v>9</v>
@@ -63823,7 +63817,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2366" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H2366" t="s">
         <v>9</v>
@@ -63849,7 +63843,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G2367" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H2367" t="s">
         <v>9</v>
@@ -63875,7 +63869,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G2368" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H2368" t="s">
         <v>9</v>
@@ -63901,7 +63895,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G2369" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="H2369" t="s">
         <v>9</v>
@@ -63927,7 +63921,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G2370" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="H2370" t="s">
         <v>9</v>
@@ -63953,7 +63947,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G2371" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="H2371" t="s">
         <v>9</v>
@@ -63979,7 +63973,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G2372" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="H2372" t="s">
         <v>9</v>
@@ -64005,7 +63999,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G2373" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H2373" t="s">
         <v>9</v>
@@ -64031,7 +64025,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G2374" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="H2374" t="s">
         <v>9</v>
@@ -64057,7 +64051,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G2375" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H2375" t="s">
         <v>9</v>
@@ -64083,7 +64077,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G2376" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="H2376" t="s">
         <v>9</v>
@@ -64109,7 +64103,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G2377" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H2377" t="s">
         <v>9</v>
@@ -64135,7 +64129,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G2378" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="H2378" t="s">
         <v>9</v>
@@ -64161,7 +64155,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G2379" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="H2379" t="s">
         <v>9</v>
@@ -64187,7 +64181,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G2380" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="H2380" t="s">
         <v>9</v>
@@ -64213,7 +64207,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G2381" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H2381" t="s">
         <v>9</v>
@@ -64239,7 +64233,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G2382" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="H2382" t="s">
         <v>9</v>
@@ -64265,7 +64259,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G2383" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="H2383" t="s">
         <v>9</v>
@@ -64291,7 +64285,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2384" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="H2384" t="s">
         <v>9</v>
@@ -64317,7 +64311,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G2385" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="H2385" t="s">
         <v>9</v>
@@ -64343,7 +64337,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G2386" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="H2386" t="s">
         <v>9</v>
@@ -64369,7 +64363,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G2387" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="H2387" t="s">
         <v>9</v>
@@ -64395,7 +64389,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G2388" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="H2388" t="s">
         <v>9</v>
@@ -64421,7 +64415,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G2389" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="H2389" t="s">
         <v>9</v>
@@ -64447,7 +64441,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2390" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="H2390" t="s">
         <v>9</v>
@@ -64473,7 +64467,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2391" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="H2391" t="s">
         <v>9</v>
@@ -64499,7 +64493,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G2392" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="H2392" t="s">
         <v>9</v>
@@ -64525,7 +64519,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G2393" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="H2393" t="s">
         <v>9</v>
@@ -64551,7 +64545,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G2394" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="H2394" t="s">
         <v>9</v>
@@ -64577,7 +64571,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2395" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="H2395" t="s">
         <v>9</v>
@@ -64603,7 +64597,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2396" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="H2396" t="s">
         <v>9</v>
@@ -64629,7 +64623,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G2397" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="H2397" t="s">
         <v>9</v>
@@ -64655,7 +64649,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2398" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="H2398" t="s">
         <v>9</v>
@@ -64681,7 +64675,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G2399" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="H2399" t="s">
         <v>9</v>
@@ -64707,7 +64701,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G2400" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="H2400" t="s">
         <v>9</v>
@@ -64733,7 +64727,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G2401" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="H2401" t="s">
         <v>9</v>
@@ -64759,7 +64753,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G2402" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="H2402" t="s">
         <v>9</v>
@@ -64785,7 +64779,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G2403" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="H2403" t="s">
         <v>9</v>
@@ -64811,7 +64805,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G2404" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="H2404" t="s">
         <v>9</v>
@@ -64837,7 +64831,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G2405" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="H2405" t="s">
         <v>9</v>
@@ -64863,7 +64857,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G2406" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="H2406" t="s">
         <v>9</v>
@@ -64889,7 +64883,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G2407" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="H2407" t="s">
         <v>9</v>
@@ -64915,7 +64909,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G2408" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="H2408" t="s">
         <v>9</v>
@@ -64941,7 +64935,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2409" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="H2409" t="s">
         <v>9</v>
@@ -64967,7 +64961,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G2410" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="H2410" t="s">
         <v>9</v>
@@ -64993,7 +64987,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G2411" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="H2411" t="s">
         <v>9</v>
@@ -65019,7 +65013,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G2412" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="H2412" t="s">
         <v>9</v>
@@ -65045,7 +65039,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G2413" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="H2413" t="s">
         <v>9</v>
@@ -65071,7 +65065,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G2414" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="H2414" t="s">
         <v>9</v>
@@ -65097,7 +65091,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G2415" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="H2415" t="s">
         <v>9</v>
@@ -65123,7 +65117,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G2416" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="H2416" t="s">
         <v>9</v>
@@ -65149,7 +65143,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G2417" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="H2417" t="s">
         <v>9</v>
@@ -65175,7 +65169,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G2418" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="H2418" t="s">
         <v>9</v>
@@ -65201,7 +65195,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G2419" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="H2419" t="s">
         <v>9</v>
@@ -65227,7 +65221,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G2420" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="H2420" t="s">
         <v>9</v>
@@ -65253,7 +65247,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G2421" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="H2421" t="s">
         <v>9</v>
@@ -65279,7 +65273,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G2422" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="H2422" t="s">
         <v>9</v>
@@ -65305,7 +65299,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G2423" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="H2423" t="s">
         <v>9</v>
@@ -65331,7 +65325,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G2424" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="H2424" t="s">
         <v>9</v>
@@ -65357,7 +65351,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G2425" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="H2425" t="s">
         <v>9</v>
@@ -65383,7 +65377,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G2426" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="H2426" t="s">
         <v>9</v>
@@ -65409,7 +65403,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G2427" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="H2427" t="s">
         <v>9</v>
@@ -65435,7 +65429,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G2428" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="H2428" t="s">
         <v>9</v>
@@ -65461,7 +65455,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G2429" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="H2429" t="s">
         <v>9</v>
@@ -65487,7 +65481,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G2430" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="H2430" t="s">
         <v>9</v>
@@ -65513,7 +65507,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G2431" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="H2431" t="s">
         <v>9</v>
@@ -65539,7 +65533,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G2432" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="H2432" t="s">
         <v>9</v>
@@ -65565,7 +65559,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G2433" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="H2433" t="s">
         <v>9</v>
@@ -65591,7 +65585,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G2434" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="H2434" t="s">
         <v>9</v>
@@ -65617,7 +65611,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G2435" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="H2435" t="s">
         <v>9</v>
@@ -65643,7 +65637,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G2436" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="H2436" t="s">
         <v>9</v>
@@ -65669,7 +65663,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G2437" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="H2437" t="s">
         <v>9</v>
@@ -65695,7 +65689,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G2438" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="H2438" t="s">
         <v>9</v>
@@ -65721,7 +65715,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G2439" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="H2439" t="s">
         <v>9</v>
@@ -65747,7 +65741,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G2440" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="H2440" t="s">
         <v>9</v>
@@ -65773,7 +65767,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G2441" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="H2441" t="s">
         <v>9</v>
@@ -65799,7 +65793,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G2442" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="H2442" t="s">
         <v>9</v>
@@ -65825,7 +65819,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G2443" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="H2443" t="s">
         <v>9</v>
@@ -65851,7 +65845,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G2444" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="H2444" t="s">
         <v>9</v>
@@ -65877,7 +65871,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G2445" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="H2445" t="s">
         <v>9</v>
@@ -65903,7 +65897,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G2446" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="H2446" t="s">
         <v>9</v>
@@ -65929,7 +65923,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G2447" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="H2447" t="s">
         <v>9</v>
@@ -65955,7 +65949,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G2448" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="H2448" t="s">
         <v>9</v>
@@ -65981,7 +65975,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G2449" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="H2449" t="s">
         <v>9</v>
@@ -66007,7 +66001,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G2450" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="H2450" t="s">
         <v>9</v>
@@ -66033,7 +66027,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G2451" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="H2451" t="s">
         <v>9</v>
@@ -66059,7 +66053,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G2452" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="H2452" t="s">
         <v>9</v>
@@ -66085,7 +66079,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G2453" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="H2453" t="s">
         <v>9</v>
@@ -66111,7 +66105,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G2454" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="H2454" t="s">
         <v>9</v>
@@ -66137,7 +66131,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G2455" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="H2455" t="s">
         <v>9</v>
@@ -66163,7 +66157,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G2456" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="H2456" t="s">
         <v>9</v>
@@ -66189,7 +66183,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G2457" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="H2457" t="s">
         <v>9</v>
@@ -66215,7 +66209,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G2458" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="H2458" t="s">
         <v>9</v>
@@ -66241,7 +66235,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G2459" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="H2459" t="s">
         <v>9</v>
@@ -66267,7 +66261,7 @@
         <v>4</v>
       </c>
       <c r="G2460" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="H2460" t="s">
         <v>9</v>
@@ -66293,7 +66287,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G2461" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="H2461" t="s">
         <v>9</v>
@@ -66319,7 +66313,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G2462" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="H2462" t="s">
         <v>9</v>
@@ -66345,7 +66339,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G2463" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="H2463" t="s">
         <v>9</v>
@@ -66371,7 +66365,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G2464" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="H2464" t="s">
         <v>9</v>
@@ -66397,7 +66391,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G2465" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="H2465" t="s">
         <v>9</v>
@@ -66423,7 +66417,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G2466" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="H2466" t="s">
         <v>9</v>
@@ -66449,7 +66443,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G2467" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="H2467" t="s">
         <v>9</v>
@@ -66475,7 +66469,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G2468" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="H2468" t="s">
         <v>9</v>
@@ -66501,7 +66495,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G2469" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="H2469" t="s">
         <v>9</v>
@@ -66527,7 +66521,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G2470" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="H2470" t="s">
         <v>9</v>
@@ -66553,7 +66547,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G2471" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="H2471" t="s">
         <v>9</v>
@@ -66579,7 +66573,7 @@
         <v>4</v>
       </c>
       <c r="G2472" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="H2472" t="s">
         <v>9</v>
@@ -66605,7 +66599,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G2473" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="H2473" t="s">
         <v>9</v>
@@ -66631,7 +66625,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G2474" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="H2474" t="s">
         <v>9</v>
@@ -66657,7 +66651,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G2475" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="H2475" t="s">
         <v>9</v>
@@ -66683,7 +66677,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G2476" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="H2476" t="s">
         <v>9</v>
@@ -66709,7 +66703,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G2477" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="H2477" t="s">
         <v>9</v>
@@ -66735,7 +66729,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G2478" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="H2478" t="s">
         <v>9</v>
@@ -66761,7 +66755,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G2479" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="H2479" t="s">
         <v>9</v>
@@ -66787,7 +66781,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G2480" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="H2480" t="s">
         <v>9</v>
@@ -66813,7 +66807,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G2481" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="H2481" t="s">
         <v>9</v>
@@ -66839,7 +66833,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G2482" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="H2482" t="s">
         <v>9</v>
@@ -66865,7 +66859,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G2483" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="H2483" t="s">
         <v>9</v>
@@ -66891,7 +66885,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G2484" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="H2484" t="s">
         <v>9</v>
@@ -66917,7 +66911,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G2485" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="H2485" t="s">
         <v>9</v>
@@ -66943,7 +66937,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G2486" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="H2486" t="s">
         <v>9</v>
@@ -66969,7 +66963,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G2487" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="H2487" t="s">
         <v>9</v>
@@ -66995,7 +66989,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G2488" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="H2488" t="s">
         <v>9</v>
@@ -67021,7 +67015,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G2489" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="H2489" t="s">
         <v>9</v>
@@ -67047,7 +67041,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G2490" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="H2490" t="s">
         <v>9</v>
@@ -67073,7 +67067,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G2491" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="H2491" t="s">
         <v>9</v>
@@ -67099,7 +67093,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G2492" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="H2492" t="s">
         <v>9</v>
@@ -67125,7 +67119,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G2493" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="H2493" t="s">
         <v>9</v>
@@ -67151,7 +67145,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G2494" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="H2494" t="s">
         <v>9</v>
@@ -67177,7 +67171,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G2495" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="H2495" t="s">
         <v>9</v>
@@ -67203,7 +67197,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G2496" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="H2496" t="s">
         <v>9</v>
@@ -67229,7 +67223,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G2497" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="H2497" t="s">
         <v>9</v>
@@ -67255,7 +67249,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G2498" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="H2498" t="s">
         <v>9</v>
@@ -67281,7 +67275,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G2499" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="H2499" t="s">
         <v>9</v>
@@ -67307,7 +67301,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G2500" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="H2500" t="s">
         <v>9</v>
@@ -67333,7 +67327,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G2501" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="H2501" t="s">
         <v>9</v>
@@ -67359,7 +67353,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G2502" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="H2502" t="s">
         <v>9</v>
@@ -67385,7 +67379,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G2503" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="H2503" t="s">
         <v>9</v>
@@ -67411,7 +67405,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G2504" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="H2504" t="s">
         <v>9</v>
@@ -67437,7 +67431,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G2505" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="H2505" t="s">
         <v>9</v>
@@ -67463,7 +67457,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G2506" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="H2506" t="s">
         <v>9</v>
@@ -67489,7 +67483,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G2507" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="H2507" t="s">
         <v>9</v>
@@ -67515,7 +67509,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G2508" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="H2508" t="s">
         <v>9</v>
@@ -67541,7 +67535,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G2509" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="H2509" t="s">
         <v>9</v>
@@ -67567,7 +67561,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G2510" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="H2510" t="s">
         <v>9</v>
@@ -67593,7 +67587,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G2511" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="H2511" t="s">
         <v>9</v>
@@ -67619,7 +67613,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G2512" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="H2512" t="s">
         <v>9</v>
@@ -67645,7 +67639,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G2513" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="H2513" t="s">
         <v>9</v>
@@ -67671,7 +67665,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G2514" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="H2514" t="s">
         <v>9</v>
@@ -67697,7 +67691,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G2515" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="H2515" t="s">
         <v>9</v>
@@ -67723,7 +67717,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G2516" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="H2516" t="s">
         <v>9</v>
@@ -67749,7 +67743,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G2517" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="H2517" t="s">
         <v>9</v>
@@ -67775,7 +67769,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G2518" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="H2518" t="s">
         <v>9</v>
@@ -67801,7 +67795,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G2519" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="H2519" t="s">
         <v>9</v>
@@ -67827,7 +67821,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G2520" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="H2520" t="s">
         <v>9</v>
@@ -67835,7 +67829,7 @@
     </row>
     <row r="2521">
       <c r="A2521" s="1" t="n">
-        <v>45988.6247685185</v>
+        <v>45988.3333333333</v>
       </c>
       <c r="B2521" t="n">
         <v>9787</v>
@@ -67853,9 +67847,35 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G2521" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="H2521" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2522">
+      <c r="A2522" s="1" t="n">
+        <v>45989.6909837963</v>
+      </c>
+      <c r="B2522" t="n">
+        <v>3931</v>
+      </c>
+      <c r="C2522" t="n">
+        <v>3.88000011444092</v>
+      </c>
+      <c r="D2522" t="n">
+        <v>3.75999999046326</v>
+      </c>
+      <c r="E2522" t="n">
+        <v>3.88000011444092</v>
+      </c>
+      <c r="F2522" t="n">
+        <v>3.79999995231628</v>
+      </c>
+      <c r="G2522" t="s">
+        <v>617</v>
+      </c>
+      <c r="H2522" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ENV.MI.xlsx
+++ b/data/ENV.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="651" uniqueCount="651">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="652" uniqueCount="652">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,16 +38,16 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18965220451355</t>
+    <t xml:space="preserve">2.18965268135071</t>
   </si>
   <si>
     <t xml:space="preserve">ENV.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20979762077332</t>
+    <t xml:space="preserve">2.20979809761047</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1447126865387</t>
+    <t xml:space="preserve">2.14471292495728</t>
   </si>
   <si>
     <t xml:space="preserve">2.16175889968872</t>
@@ -56,28 +56,28 @@
     <t xml:space="preserve">2.03778719902039</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08272695541382</t>
+    <t xml:space="preserve">2.08272671699524</t>
   </si>
   <si>
     <t xml:space="preserve">2.05328369140625</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03623723983765</t>
+    <t xml:space="preserve">2.03623747825623</t>
   </si>
   <si>
     <t xml:space="preserve">1.96805286407471</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96030426025391</t>
+    <t xml:space="preserve">1.96030461788177</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89831864833832</t>
+    <t xml:space="preserve">1.89831876754761</t>
   </si>
   <si>
-    <t xml:space="preserve">1.881272315979</t>
+    <t xml:space="preserve">1.88127243518829</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96340382099152</t>
+    <t xml:space="preserve">1.96340370178223</t>
   </si>
   <si>
     <t xml:space="preserve">1.98354935646057</t>
@@ -86,7 +86,7 @@
     <t xml:space="preserve">2.01299262046814</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93551003932953</t>
+    <t xml:space="preserve">1.93551027774811</t>
   </si>
   <si>
     <t xml:space="preserve">1.93705999851227</t>
@@ -95,28 +95,28 @@
     <t xml:space="preserve">1.91381525993347</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91071593761444</t>
+    <t xml:space="preserve">1.91071557998657</t>
   </si>
   <si>
     <t xml:space="preserve">1.86577594280243</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89211964607239</t>
+    <t xml:space="preserve">1.89212000370026</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85182905197144</t>
+    <t xml:space="preserve">1.85182917118073</t>
   </si>
   <si>
     <t xml:space="preserve">1.93396067619324</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86732578277588</t>
+    <t xml:space="preserve">1.86732590198517</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8890209197998</t>
+    <t xml:space="preserve">1.88902056217194</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98664855957031</t>
+    <t xml:space="preserve">1.98664820194244</t>
   </si>
   <si>
     <t xml:space="preserve">2.11526942253113</t>
@@ -134,10 +134,10 @@
     <t xml:space="preserve">2.0842764377594</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0145423412323</t>
+    <t xml:space="preserve">2.01454210281372</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00524473190308</t>
+    <t xml:space="preserve">2.00524425506592</t>
   </si>
   <si>
     <t xml:space="preserve">2.14626240730286</t>
@@ -149,13 +149,13 @@
     <t xml:space="preserve">2.32447195053101</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20049977302551</t>
+    <t xml:space="preserve">2.20050001144409</t>
   </si>
   <si>
     <t xml:space="preserve">2.27178359031677</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24698948860168</t>
+    <t xml:space="preserve">2.24698925018311</t>
   </si>
   <si>
     <t xml:space="preserve">2.32137250900269</t>
@@ -164,10 +164,10 @@
     <t xml:space="preserve">2.28418111801147</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37870931625366</t>
+    <t xml:space="preserve">2.37870979309082</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35546469688416</t>
+    <t xml:space="preserve">2.35546493530273</t>
   </si>
   <si>
     <t xml:space="preserve">2.4406955242157</t>
@@ -176,49 +176,49 @@
     <t xml:space="preserve">2.43139743804932</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4499933719635</t>
+    <t xml:space="preserve">2.44999289512634</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38490796089172</t>
+    <t xml:space="preserve">2.3849081993103</t>
   </si>
   <si>
     <t xml:space="preserve">2.3616635799408</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36321306228638</t>
+    <t xml:space="preserve">2.36321330070496</t>
   </si>
   <si>
     <t xml:space="preserve">2.31982278823853</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35236549377441</t>
+    <t xml:space="preserve">2.35236525535583</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26868462562561</t>
+    <t xml:space="preserve">2.26868486404419</t>
   </si>
   <si>
     <t xml:space="preserve">2.32292222976685</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33531951904297</t>
+    <t xml:space="preserve">2.33531928062439</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33996868133545</t>
+    <t xml:space="preserve">2.33996844291687</t>
   </si>
   <si>
     <t xml:space="preserve">2.3105251789093</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28573083877563</t>
+    <t xml:space="preserve">2.28573060035706</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25473785400391</t>
+    <t xml:space="preserve">2.25473809242249</t>
   </si>
   <si>
     <t xml:space="preserve">2.29037976264954</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27488350868225</t>
+    <t xml:space="preserve">2.27488327026367</t>
   </si>
   <si>
     <t xml:space="preserve">2.23149299621582</t>
@@ -227,40 +227,40 @@
     <t xml:space="preserve">2.0749785900116</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00834369659424</t>
+    <t xml:space="preserve">2.00834345817566</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03468775749207</t>
+    <t xml:space="preserve">2.03468728065491</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02229022979736</t>
+    <t xml:space="preserve">2.02229046821594</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97580087184906</t>
+    <t xml:space="preserve">1.97580111026764</t>
   </si>
   <si>
     <t xml:space="preserve">1.919806599617</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88216376304626</t>
+    <t xml:space="preserve">1.88216364383698</t>
   </si>
   <si>
     <t xml:space="preserve">2.00136733055115</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96058714389801</t>
+    <t xml:space="preserve">1.96058702468872</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90255379676819</t>
+    <t xml:space="preserve">1.90255391597748</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92137515544891</t>
+    <t xml:space="preserve">1.92137539386749</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91353285312653</t>
+    <t xml:space="preserve">1.9135330915451</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89784848690033</t>
+    <t xml:space="preserve">1.89784836769104</t>
   </si>
   <si>
     <t xml:space="preserve">1.89000594615936</t>
@@ -269,10 +269,10 @@
     <t xml:space="preserve">1.85079383850098</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8805947303772</t>
+    <t xml:space="preserve">1.88059520721436</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8664790391922</t>
+    <t xml:space="preserve">1.86647868156433</t>
   </si>
   <si>
     <t xml:space="preserve">1.546511054039</t>
@@ -281,7 +281,7 @@
     <t xml:space="preserve">1.68610489368439</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70178949832916</t>
+    <t xml:space="preserve">1.70178973674774</t>
   </si>
   <si>
     <t xml:space="preserve">1.70022094249725</t>
@@ -290,28 +290,28 @@
     <t xml:space="preserve">1.66257774829865</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64532470703125</t>
+    <t xml:space="preserve">1.64532446861267</t>
   </si>
   <si>
     <t xml:space="preserve">1.62336599826813</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61552345752716</t>
+    <t xml:space="preserve">1.61552357673645</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6312084197998</t>
+    <t xml:space="preserve">1.63120830059052</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5841543674469</t>
+    <t xml:space="preserve">1.58415424823761</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64689302444458</t>
+    <t xml:space="preserve">1.646892786026</t>
   </si>
   <si>
     <t xml:space="preserve">1.64061915874481</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63905048370361</t>
+    <t xml:space="preserve">1.6390506029129</t>
   </si>
   <si>
     <t xml:space="preserve">1.60768127441406</t>
@@ -323,16 +323,16 @@
     <t xml:space="preserve">1.59199666976929</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75668597221375</t>
+    <t xml:space="preserve">1.75668573379517</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84295189380646</t>
+    <t xml:space="preserve">1.84295165538788</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84608900547028</t>
+    <t xml:space="preserve">1.84608852863312</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92921721935272</t>
+    <t xml:space="preserve">1.9292174577713</t>
   </si>
   <si>
     <t xml:space="preserve">1.88530027866364</t>
@@ -344,25 +344,25 @@
     <t xml:space="preserve">1.91823840141296</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94960749149323</t>
+    <t xml:space="preserve">1.9496077299118</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93078589439392</t>
+    <t xml:space="preserve">1.93078577518463</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84922575950623</t>
+    <t xml:space="preserve">1.84922564029694</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82412993907928</t>
+    <t xml:space="preserve">1.82413005828857</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8554995059967</t>
+    <t xml:space="preserve">1.85549938678741</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89627981185913</t>
+    <t xml:space="preserve">1.89627969264984</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87432098388672</t>
+    <t xml:space="preserve">1.8743212223053</t>
   </si>
   <si>
     <t xml:space="preserve">1.94333374500275</t>
@@ -374,37 +374,37 @@
     <t xml:space="preserve">1.9668607711792</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9841136932373</t>
+    <t xml:space="preserve">1.98411393165588</t>
   </si>
   <si>
     <t xml:space="preserve">2.0625376701355</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05312657356262</t>
+    <t xml:space="preserve">2.0531268119812</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05155849456787</t>
+    <t xml:space="preserve">2.05155801773071</t>
   </si>
   <si>
     <t xml:space="preserve">2.0233256816864</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02959990501404</t>
+    <t xml:space="preserve">2.02959942817688</t>
   </si>
   <si>
     <t xml:space="preserve">2.03116798400879</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06096887588501</t>
+    <t xml:space="preserve">2.06096911430359</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09390711784363</t>
+    <t xml:space="preserve">2.09390687942505</t>
   </si>
   <si>
     <t xml:space="preserve">2.08606457710266</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1550772190094</t>
+    <t xml:space="preserve">2.15507698059082</t>
   </si>
   <si>
     <t xml:space="preserve">2.18801522254944</t>
@@ -416,16 +416,16 @@
     <t xml:space="preserve">2.2021312713623</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23350071907043</t>
+    <t xml:space="preserve">2.23350048065186</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20997381210327</t>
+    <t xml:space="preserve">2.20997333526611</t>
   </si>
   <si>
     <t xml:space="preserve">2.18017244338989</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16605639457703</t>
+    <t xml:space="preserve">2.16605663299561</t>
   </si>
   <si>
     <t xml:space="preserve">2.19428896903992</t>
@@ -434,13 +434,13 @@
     <t xml:space="preserve">2.17389869689941</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20056247711182</t>
+    <t xml:space="preserve">2.2005627155304</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21938443183899</t>
+    <t xml:space="preserve">2.21938419342041</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21781587600708</t>
+    <t xml:space="preserve">2.21781611442566</t>
   </si>
   <si>
     <t xml:space="preserve">2.1911518573761</t>
@@ -455,7 +455,7 @@
     <t xml:space="preserve">2.11743426322937</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16291952133179</t>
+    <t xml:space="preserve">2.16291975975037</t>
   </si>
   <si>
     <t xml:space="preserve">2.10802316665649</t>
@@ -464,43 +464,43 @@
     <t xml:space="preserve">2.01548337936401</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04528450965881</t>
+    <t xml:space="preserve">2.04528427124023</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9856823682785</t>
+    <t xml:space="preserve">1.98568248748779</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07822251319885</t>
+    <t xml:space="preserve">2.07822203636169</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06724286079407</t>
+    <t xml:space="preserve">2.06724262237549</t>
   </si>
   <si>
     <t xml:space="preserve">2.12998151779175</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11586570739746</t>
+    <t xml:space="preserve">2.11586546897888</t>
   </si>
   <si>
     <t xml:space="preserve">2.05469489097595</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11429691314697</t>
+    <t xml:space="preserve">2.11429715156555</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05626368522644</t>
+    <t xml:space="preserve">2.05626344680786</t>
   </si>
   <si>
     <t xml:space="preserve">2.06410574913025</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10488605499268</t>
+    <t xml:space="preserve">2.10488629341125</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00920939445496</t>
+    <t xml:space="preserve">2.00920915603638</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01391506195068</t>
+    <t xml:space="preserve">2.0139148235321</t>
   </si>
   <si>
     <t xml:space="preserve">2.04842114448547</t>
@@ -509,7 +509,7 @@
     <t xml:space="preserve">2.16448783874512</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1848783493042</t>
+    <t xml:space="preserve">2.18487787246704</t>
   </si>
   <si>
     <t xml:space="preserve">2.26643872261047</t>
@@ -518,13 +518,13 @@
     <t xml:space="preserve">2.27271246910095</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25702738761902</t>
+    <t xml:space="preserve">2.2570276260376</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30721879005432</t>
+    <t xml:space="preserve">2.3072190284729</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23036360740662</t>
+    <t xml:space="preserve">2.23036336898804</t>
   </si>
   <si>
     <t xml:space="preserve">2.37152600288391</t>
@@ -539,40 +539,40 @@
     <t xml:space="preserve">2.33545088768005</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31349277496338</t>
+    <t xml:space="preserve">2.3134925365448</t>
   </si>
   <si>
     <t xml:space="preserve">2.37623119354248</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32917714118958</t>
+    <t xml:space="preserve">2.32917737960815</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24918508529663</t>
+    <t xml:space="preserve">2.24918532371521</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28839707374573</t>
+    <t xml:space="preserve">2.28839731216431</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33701992034912</t>
+    <t xml:space="preserve">2.33701944351196</t>
   </si>
   <si>
     <t xml:space="preserve">2.34486198425293</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34956741333008</t>
+    <t xml:space="preserve">2.34956765174866</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32604026794434</t>
+    <t xml:space="preserve">2.32604074478149</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30251383781433</t>
+    <t xml:space="preserve">2.30251336097717</t>
   </si>
   <si>
     <t xml:space="preserve">2.31192421913147</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25075364112854</t>
+    <t xml:space="preserve">2.25075340270996</t>
   </si>
   <si>
     <t xml:space="preserve">2.27428102493286</t>
@@ -581,16 +581,16 @@
     <t xml:space="preserve">2.43897008895874</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48445558547974</t>
+    <t xml:space="preserve">2.48445582389832</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46249723434448</t>
+    <t xml:space="preserve">2.46249771118164</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50798273086548</t>
+    <t xml:space="preserve">2.50798320770264</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4860246181488</t>
+    <t xml:space="preserve">2.48602437973022</t>
   </si>
   <si>
     <t xml:space="preserve">2.60993313789368</t>
@@ -599,7 +599,7 @@
     <t xml:space="preserve">2.66639828681946</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66326117515564</t>
+    <t xml:space="preserve">2.66326141357422</t>
   </si>
   <si>
     <t xml:space="preserve">2.6601243019104</t>
@@ -611,10 +611,10 @@
     <t xml:space="preserve">2.65855598449707</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60209131240845</t>
+    <t xml:space="preserve">2.60209083557129</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55033135414124</t>
+    <t xml:space="preserve">2.55033183097839</t>
   </si>
   <si>
     <t xml:space="preserve">2.63816595077515</t>
@@ -632,10 +632,10 @@
     <t xml:space="preserve">2.6036593914032</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61934423446655</t>
+    <t xml:space="preserve">2.61934399604797</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57542705535889</t>
+    <t xml:space="preserve">2.57542681694031</t>
   </si>
   <si>
     <t xml:space="preserve">2.57385897636414</t>
@@ -644,31 +644,31 @@
     <t xml:space="preserve">2.50955128669739</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58797478675842</t>
+    <t xml:space="preserve">2.587975025177</t>
   </si>
   <si>
     <t xml:space="preserve">2.56444764137268</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61150193214417</t>
+    <t xml:space="preserve">2.61150169372559</t>
   </si>
   <si>
     <t xml:space="preserve">2.56915307044983</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63502860069275</t>
+    <t xml:space="preserve">2.63502883911133</t>
   </si>
   <si>
     <t xml:space="preserve">2.62561798095703</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62718629837036</t>
+    <t xml:space="preserve">2.62718653678894</t>
   </si>
   <si>
     <t xml:space="preserve">2.83422446250916</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79030704498291</t>
+    <t xml:space="preserve">2.79030728340149</t>
   </si>
   <si>
     <t xml:space="preserve">2.77619099617004</t>
@@ -680,10 +680,10 @@
     <t xml:space="preserve">2.69149374961853</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78246545791626</t>
+    <t xml:space="preserve">2.78246474266052</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81226587295532</t>
+    <t xml:space="preserve">2.8122661113739</t>
   </si>
   <si>
     <t xml:space="preserve">2.82324528694153</t>
@@ -692,7 +692,7 @@
     <t xml:space="preserve">2.68678855895996</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70090484619141</t>
+    <t xml:space="preserve">2.70090436935425</t>
   </si>
   <si>
     <t xml:space="preserve">2.80657148361206</t>
@@ -701,7 +701,7 @@
     <t xml:space="preserve">2.86433959007263</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81940865516663</t>
+    <t xml:space="preserve">2.81940841674805</t>
   </si>
   <si>
     <t xml:space="preserve">2.80817604064941</t>
@@ -710,7 +710,7 @@
     <t xml:space="preserve">2.88038611412048</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83385062217712</t>
+    <t xml:space="preserve">2.8338508605957</t>
   </si>
   <si>
     <t xml:space="preserve">2.74398922920227</t>
@@ -722,34 +722,34 @@
     <t xml:space="preserve">2.70547676086426</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7327561378479</t>
+    <t xml:space="preserve">2.73275637626648</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67177891731262</t>
+    <t xml:space="preserve">2.67177867889404</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62363839149475</t>
+    <t xml:space="preserve">2.62363886833191</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61722016334534</t>
+    <t xml:space="preserve">2.61722040176392</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60438251495361</t>
+    <t xml:space="preserve">2.60438275337219</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62524342536926</t>
+    <t xml:space="preserve">2.62524318695068</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64129018783569</t>
+    <t xml:space="preserve">2.64129042625427</t>
   </si>
   <si>
     <t xml:space="preserve">2.6958487033844</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75040769577026</t>
+    <t xml:space="preserve">2.75040793418884</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74719834327698</t>
+    <t xml:space="preserve">2.74719858169556</t>
   </si>
   <si>
     <t xml:space="preserve">2.71991920471191</t>
@@ -758,13 +758,13 @@
     <t xml:space="preserve">2.72633767127991</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74238467216492</t>
+    <t xml:space="preserve">2.74238419532776</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80015301704407</t>
+    <t xml:space="preserve">2.80015254020691</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78571081161499</t>
+    <t xml:space="preserve">2.78571057319641</t>
   </si>
   <si>
     <t xml:space="preserve">2.82422256469727</t>
@@ -773,55 +773,55 @@
     <t xml:space="preserve">2.78731513023376</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79373407363892</t>
+    <t xml:space="preserve">2.7937343120575</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80496692657471</t>
+    <t xml:space="preserve">2.80496668815613</t>
   </si>
   <si>
     <t xml:space="preserve">2.78410601615906</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77608275413513</t>
+    <t xml:space="preserve">2.77608251571655</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79533863067627</t>
+    <t xml:space="preserve">2.79533839225769</t>
   </si>
   <si>
     <t xml:space="preserve">2.82261800765991</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76003575325012</t>
+    <t xml:space="preserve">2.7600359916687</t>
   </si>
   <si>
     <t xml:space="preserve">2.77929210662842</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79854774475098</t>
+    <t xml:space="preserve">2.79854798316956</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77447772026062</t>
+    <t xml:space="preserve">2.7744779586792</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8033618927002</t>
+    <t xml:space="preserve">2.80336213111877</t>
   </si>
   <si>
     <t xml:space="preserve">2.83545541763306</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8402693271637</t>
+    <t xml:space="preserve">2.84026956558228</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83224630355835</t>
+    <t xml:space="preserve">2.83224606513977</t>
   </si>
   <si>
     <t xml:space="preserve">2.8113853931427</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81619930267334</t>
+    <t xml:space="preserve">2.8161997795105</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76324534416199</t>
+    <t xml:space="preserve">2.76324510574341</t>
   </si>
   <si>
     <t xml:space="preserve">2.71189570426941</t>
@@ -830,22 +830,22 @@
     <t xml:space="preserve">2.72473311424255</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7969434261322</t>
+    <t xml:space="preserve">2.79694366455078</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79052472114563</t>
+    <t xml:space="preserve">2.79052448272705</t>
   </si>
   <si>
     <t xml:space="preserve">2.76805925369263</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73115181922913</t>
+    <t xml:space="preserve">2.73115158081055</t>
   </si>
   <si>
     <t xml:space="preserve">2.70387244224548</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81459474563599</t>
+    <t xml:space="preserve">2.81459450721741</t>
   </si>
   <si>
     <t xml:space="preserve">2.82903671264648</t>
@@ -854,58 +854,58 @@
     <t xml:space="preserve">2.84347867965698</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77768707275391</t>
+    <t xml:space="preserve">2.77768683433533</t>
   </si>
   <si>
     <t xml:space="preserve">2.77126860618591</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88840961456299</t>
+    <t xml:space="preserve">2.88840985298157</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87236285209656</t>
+    <t xml:space="preserve">2.87236261367798</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89161920547485</t>
+    <t xml:space="preserve">2.89161896705627</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92852663993835</t>
+    <t xml:space="preserve">2.92852640151978</t>
   </si>
   <si>
     <t xml:space="preserve">2.85952520370483</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90927052497864</t>
+    <t xml:space="preserve">2.90927028656006</t>
   </si>
   <si>
     <t xml:space="preserve">2.99913191795349</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96864318847656</t>
+    <t xml:space="preserve">2.96864366531372</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83064150810242</t>
+    <t xml:space="preserve">2.830641746521</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87878203392029</t>
+    <t xml:space="preserve">2.87878179550171</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87717700004578</t>
+    <t xml:space="preserve">2.8771767616272</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87557220458984</t>
+    <t xml:space="preserve">2.87557244300842</t>
   </si>
   <si>
     <t xml:space="preserve">2.7520124912262</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76164031028748</t>
+    <t xml:space="preserve">2.76164054870605</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7889199256897</t>
+    <t xml:space="preserve">2.78892016410828</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67980241775513</t>
+    <t xml:space="preserve">2.67980217933655</t>
   </si>
   <si>
     <t xml:space="preserve">2.73596572875977</t>
@@ -917,22 +917,22 @@
     <t xml:space="preserve">2.8482928276062</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82101345062256</t>
+    <t xml:space="preserve">2.82101368904114</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73436117172241</t>
+    <t xml:space="preserve">2.73436141014099</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81780385971069</t>
+    <t xml:space="preserve">2.81780409812927</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76484990119934</t>
+    <t xml:space="preserve">2.76485013961792</t>
   </si>
   <si>
     <t xml:space="preserve">2.74077987670898</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79212927818298</t>
+    <t xml:space="preserve">2.79212951660156</t>
   </si>
   <si>
     <t xml:space="preserve">2.6637556552887</t>
@@ -941,37 +941,37 @@
     <t xml:space="preserve">2.60759210586548</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55142855644226</t>
+    <t xml:space="preserve">2.55142879486084</t>
   </si>
   <si>
     <t xml:space="preserve">2.56747508049011</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59956860542297</t>
+    <t xml:space="preserve">2.59956884384155</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55945181846619</t>
+    <t xml:space="preserve">2.55945205688477</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50328826904297</t>
+    <t xml:space="preserve">2.50328850746155</t>
   </si>
   <si>
     <t xml:space="preserve">2.45514822006226</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47921824455261</t>
+    <t xml:space="preserve">2.47921848297119</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47119498252869</t>
+    <t xml:space="preserve">2.47119474411011</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43107795715332</t>
+    <t xml:space="preserve">2.4310781955719</t>
   </si>
   <si>
     <t xml:space="preserve">2.46317148208618</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48724150657654</t>
+    <t xml:space="preserve">2.48724126815796</t>
   </si>
   <si>
     <t xml:space="preserve">2.49526500701904</t>
@@ -983,31 +983,31 @@
     <t xml:space="preserve">2.58352184295654</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65573215484619</t>
+    <t xml:space="preserve">2.65573239326477</t>
   </si>
   <si>
     <t xml:space="preserve">2.91247987747192</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82002472877502</t>
+    <t xml:space="preserve">2.8200249671936</t>
   </si>
   <si>
     <t xml:space="preserve">2.80358147621155</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86935496330261</t>
+    <t xml:space="preserve">2.86935472488403</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8446900844574</t>
+    <t xml:space="preserve">2.84468984603882</t>
   </si>
   <si>
     <t xml:space="preserve">2.85291147232056</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81180334091187</t>
+    <t xml:space="preserve">2.81180357933044</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72136497497559</t>
+    <t xml:space="preserve">2.72136521339417</t>
   </si>
   <si>
     <t xml:space="preserve">2.68025684356689</t>
@@ -1016,7 +1016,7 @@
     <t xml:space="preserve">2.69670009613037</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64737033843994</t>
+    <t xml:space="preserve">2.64737057685852</t>
   </si>
   <si>
     <t xml:space="preserve">2.65559196472168</t>
@@ -1025,88 +1025,88 @@
     <t xml:space="preserve">2.66381359100342</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63092684745789</t>
+    <t xml:space="preserve">2.63092732429504</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6391487121582</t>
+    <t xml:space="preserve">2.63914847373962</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55693197250366</t>
+    <t xml:space="preserve">2.55693221092224</t>
   </si>
   <si>
     <t xml:space="preserve">2.59804058074951</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5487105846405</t>
+    <t xml:space="preserve">2.54871034622192</t>
   </si>
   <si>
     <t xml:space="preserve">2.46649408340454</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60626220703125</t>
+    <t xml:space="preserve">2.60626196861267</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52404570579529</t>
+    <t xml:space="preserve">2.52404546737671</t>
   </si>
   <si>
     <t xml:space="preserve">2.58159732818604</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61448383331299</t>
+    <t xml:space="preserve">2.61448407173157</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58981847763062</t>
+    <t xml:space="preserve">2.58981871604919</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62270569801331</t>
+    <t xml:space="preserve">2.62270522117615</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51582384109497</t>
+    <t xml:space="preserve">2.51582407951355</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57337522506714</t>
+    <t xml:space="preserve">2.57337546348572</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56515383720398</t>
+    <t xml:space="preserve">2.5651535987854</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53226709365845</t>
+    <t xml:space="preserve">2.53226733207703</t>
   </si>
   <si>
     <t xml:space="preserve">2.4747154712677</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4829375743866</t>
+    <t xml:space="preserve">2.48293733596802</t>
   </si>
   <si>
     <t xml:space="preserve">2.45005083084106</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44182944297791</t>
+    <t xml:space="preserve">2.44182920455933</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42538595199585</t>
+    <t xml:space="preserve">2.42538571357727</t>
   </si>
   <si>
     <t xml:space="preserve">2.43360733985901</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49115896224976</t>
+    <t xml:space="preserve">2.49115872383118</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50760245323181</t>
+    <t xml:space="preserve">2.50760221481323</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54048895835876</t>
+    <t xml:space="preserve">2.54048871994019</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67203545570374</t>
+    <t xml:space="preserve">2.67203521728516</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68847870826721</t>
+    <t xml:space="preserve">2.68847846984863</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70492196083069</t>
+    <t xml:space="preserve">2.70492172241211</t>
   </si>
   <si>
     <t xml:space="preserve">2.71314334869385</t>
@@ -1115,7 +1115,7 @@
     <t xml:space="preserve">2.75425171852112</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78713846206665</t>
+    <t xml:space="preserve">2.78713870048523</t>
   </si>
   <si>
     <t xml:space="preserve">2.77069497108459</t>
@@ -1124,10 +1124,10 @@
     <t xml:space="preserve">2.72958660125732</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74603009223938</t>
+    <t xml:space="preserve">2.7460298538208</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77891683578491</t>
+    <t xml:space="preserve">2.77891659736633</t>
   </si>
   <si>
     <t xml:space="preserve">2.79536008834839</t>
@@ -1145,16 +1145,16 @@
     <t xml:space="preserve">2.86113309860229</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90224123001099</t>
+    <t xml:space="preserve">2.90224146842957</t>
   </si>
   <si>
     <t xml:space="preserve">2.88579821586609</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8364679813385</t>
+    <t xml:space="preserve">2.83646821975708</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94334936141968</t>
+    <t xml:space="preserve">2.94334959983826</t>
   </si>
   <si>
     <t xml:space="preserve">2.82824659347534</t>
@@ -1181,7 +1181,7 @@
     <t xml:space="preserve">2.92252135276794</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90552997589111</t>
+    <t xml:space="preserve">2.90553021430969</t>
   </si>
   <si>
     <t xml:space="preserve">2.87154722213745</t>
@@ -1190,10 +1190,10 @@
     <t xml:space="preserve">2.85455560684204</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91402554512024</t>
+    <t xml:space="preserve">2.91402578353882</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93101692199707</t>
+    <t xml:space="preserve">2.93101716041565</t>
   </si>
   <si>
     <t xml:space="preserve">2.94800853729248</t>
@@ -1202,13 +1202,13 @@
     <t xml:space="preserve">2.89703416824341</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93951296806335</t>
+    <t xml:space="preserve">2.93951272964478</t>
   </si>
   <si>
     <t xml:space="preserve">2.98199129104614</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79508590698242</t>
+    <t xml:space="preserve">2.79508566856384</t>
   </si>
   <si>
     <t xml:space="preserve">2.78659009933472</t>
@@ -1220,7 +1220,7 @@
     <t xml:space="preserve">2.76959872245789</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81207704544067</t>
+    <t xml:space="preserve">2.81207728385925</t>
   </si>
   <si>
     <t xml:space="preserve">2.83756422996521</t>
@@ -1229,28 +1229,28 @@
     <t xml:space="preserve">2.86305141448975</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62517189979553</t>
+    <t xml:space="preserve">2.62517166137695</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67614579200745</t>
+    <t xml:space="preserve">2.67614603042603</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61667585372925</t>
+    <t xml:space="preserve">2.61667609214783</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55720591545105</t>
+    <t xml:space="preserve">2.55720615386963</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51472759246826</t>
+    <t xml:space="preserve">2.51472735404968</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49773597717285</t>
+    <t xml:space="preserve">2.49773645401001</t>
   </si>
   <si>
     <t xml:space="preserve">2.4807448387146</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53171920776367</t>
+    <t xml:space="preserve">2.53171896934509</t>
   </si>
   <si>
     <t xml:space="preserve">2.46375346183777</t>
@@ -1259,22 +1259,22 @@
     <t xml:space="preserve">2.58269309997559</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54021453857422</t>
+    <t xml:space="preserve">2.5402147769928</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56570196151733</t>
+    <t xml:space="preserve">2.56570172309875</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59118914604187</t>
+    <t xml:space="preserve">2.59118890762329</t>
   </si>
   <si>
     <t xml:space="preserve">2.47224926948547</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63366746902466</t>
+    <t xml:space="preserve">2.63366723060608</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59968447685242</t>
+    <t xml:space="preserve">2.599684715271</t>
   </si>
   <si>
     <t xml:space="preserve">2.52322363853455</t>
@@ -1286,7 +1286,7 @@
     <t xml:space="preserve">3.075443983078</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0074782371521</t>
+    <t xml:space="preserve">3.00747847557068</t>
   </si>
   <si>
     <t xml:space="preserve">2.99048686027527</t>
@@ -1304,82 +1304,82 @@
     <t xml:space="preserve">2.84606003761292</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75260734558105</t>
+    <t xml:space="preserve">2.75260710716248</t>
   </si>
   <si>
     <t xml:space="preserve">2.6676504611969</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65915441513062</t>
+    <t xml:space="preserve">2.65915465354919</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31083083152771</t>
+    <t xml:space="preserve">2.31083059310913</t>
   </si>
   <si>
     <t xml:space="preserve">2.35330939292908</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34481358528137</t>
+    <t xml:space="preserve">2.34481334686279</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45525765419006</t>
+    <t xml:space="preserve">2.45525789260864</t>
   </si>
   <si>
     <t xml:space="preserve">2.4892406463623</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65065884590149</t>
+    <t xml:space="preserve">2.65065860748291</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64216303825378</t>
+    <t xml:space="preserve">2.64216327667236</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71012902259827</t>
+    <t xml:space="preserve">2.71012878417969</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69313764572144</t>
+    <t xml:space="preserve">2.69313740730286</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71862435340881</t>
+    <t xml:space="preserve">2.71862459182739</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74411153793335</t>
+    <t xml:space="preserve">2.74411177635193</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68464183807373</t>
+    <t xml:space="preserve">2.68464159965515</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6081805229187</t>
+    <t xml:space="preserve">2.60818028450012</t>
   </si>
   <si>
     <t xml:space="preserve">2.50623202323914</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44676232337952</t>
+    <t xml:space="preserve">2.44676208496094</t>
   </si>
   <si>
     <t xml:space="preserve">2.37879633903503</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42977070808411</t>
+    <t xml:space="preserve">2.42977046966553</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37030076980591</t>
+    <t xml:space="preserve">2.37030053138733</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31932640075684</t>
+    <t xml:space="preserve">2.31932663917542</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27684807777405</t>
+    <t xml:space="preserve">2.27684783935547</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26835250854492</t>
+    <t xml:space="preserve">2.26835227012634</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30233502388</t>
+    <t xml:space="preserve">2.30233526229858</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33631777763367</t>
+    <t xml:space="preserve">2.33631801605225</t>
   </si>
   <si>
     <t xml:space="preserve">2.39578771591187</t>
@@ -1391,49 +1391,49 @@
     <t xml:space="preserve">2.99898242950439</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03296542167664</t>
+    <t xml:space="preserve">3.03296518325806</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0159740447998</t>
+    <t xml:space="preserve">3.01597380638123</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04146099090576</t>
+    <t xml:space="preserve">3.04146122932434</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19438409805298</t>
+    <t xml:space="preserve">3.1943838596344</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1264181137085</t>
+    <t xml:space="preserve">3.12641835212708</t>
   </si>
   <si>
     <t xml:space="preserve">3.05845236778259</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09243559837341</t>
+    <t xml:space="preserve">3.09243535995483</t>
   </si>
   <si>
     <t xml:space="preserve">3.16040086746216</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21137547492981</t>
+    <t xml:space="preserve">3.21137523651123</t>
   </si>
   <si>
     <t xml:space="preserve">3.3133237361908</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26234912872314</t>
+    <t xml:space="preserve">3.26234936714172</t>
   </si>
   <si>
     <t xml:space="preserve">3.33031511306763</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22836637496948</t>
+    <t xml:space="preserve">3.22836661338806</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17739224433899</t>
+    <t xml:space="preserve">3.17739248275757</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14340949058533</t>
+    <t xml:space="preserve">3.14340972900391</t>
   </si>
   <si>
     <t xml:space="preserve">3.10942697525024</t>
@@ -1445,19 +1445,19 @@
     <t xml:space="preserve">3.48323750495911</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39828038215637</t>
+    <t xml:space="preserve">3.39828062057495</t>
   </si>
   <si>
     <t xml:space="preserve">3.46624636650085</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36429786682129</t>
+    <t xml:space="preserve">3.36429810523987</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34730648994446</t>
+    <t xml:space="preserve">3.34730672836304</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24535775184631</t>
+    <t xml:space="preserve">3.24535822868347</t>
   </si>
   <si>
     <t xml:space="preserve">3.02446985244751</t>
@@ -1481,7 +1481,7 @@
     <t xml:space="preserve">3.02393102645874</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10281610488892</t>
+    <t xml:space="preserve">3.1028163433075</t>
   </si>
   <si>
     <t xml:space="preserve">3.13787627220154</t>
@@ -1490,16 +1490,13 @@
     <t xml:space="preserve">2.98010611534119</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09405112266541</t>
+    <t xml:space="preserve">3.09405136108398</t>
   </si>
   <si>
     <t xml:space="preserve">3.07652115821838</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06775617599487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04146122932434</t>
+    <t xml:space="preserve">3.06775641441345</t>
   </si>
   <si>
     <t xml:space="preserve">3.00640106201172</t>
@@ -1508,7 +1505,7 @@
     <t xml:space="preserve">2.9888710975647</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89245581626892</t>
+    <t xml:space="preserve">2.89245557785034</t>
   </si>
   <si>
     <t xml:space="preserve">2.92751574516296</t>
@@ -1517,16 +1514,16 @@
     <t xml:space="preserve">2.99763607978821</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96257615089417</t>
+    <t xml:space="preserve">2.96257591247559</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86616086959839</t>
+    <t xml:space="preserve">2.86616063117981</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91875076293945</t>
+    <t xml:space="preserve">2.91875100135803</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80480551719666</t>
+    <t xml:space="preserve">2.80480575561523</t>
   </si>
   <si>
     <t xml:space="preserve">2.82233572006226</t>
@@ -1547,10 +1544,10 @@
     <t xml:space="preserve">3.03269624710083</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90122079849243</t>
+    <t xml:space="preserve">2.90122103691101</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88369083404541</t>
+    <t xml:space="preserve">2.88369059562683</t>
   </si>
   <si>
     <t xml:space="preserve">2.8749258518219</t>
@@ -1559,10 +1556,10 @@
     <t xml:space="preserve">2.81357073783875</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83986568450928</t>
+    <t xml:space="preserve">2.83986592292786</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68209528923035</t>
+    <t xml:space="preserve">2.68209552764893</t>
   </si>
   <si>
     <t xml:space="preserve">2.69086050987244</t>
@@ -1571,28 +1568,28 @@
     <t xml:space="preserve">2.66456532478333</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85739588737488</t>
+    <t xml:space="preserve">2.8573956489563</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90998578071594</t>
+    <t xml:space="preserve">2.90998601913452</t>
   </si>
   <si>
     <t xml:space="preserve">2.7785108089447</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76974582672119</t>
+    <t xml:space="preserve">2.76974558830261</t>
   </si>
   <si>
     <t xml:space="preserve">2.79604077339172</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84863090515137</t>
+    <t xml:space="preserve">2.84863066673279</t>
   </si>
   <si>
     <t xml:space="preserve">3.08528614044189</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76098036766052</t>
+    <t xml:space="preserve">2.7609806060791</t>
   </si>
   <si>
     <t xml:space="preserve">2.78727579116821</t>
@@ -1601,7 +1598,7 @@
     <t xml:space="preserve">2.75221562385559</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73468542098999</t>
+    <t xml:space="preserve">2.73468518257141</t>
   </si>
   <si>
     <t xml:space="preserve">2.86875891685486</t>
@@ -1619,34 +1616,34 @@
     <t xml:space="preserve">2.83221411705017</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8870313167572</t>
+    <t xml:space="preserve">2.88703107833862</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85048627853394</t>
+    <t xml:space="preserve">2.85048651695251</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96012043952942</t>
+    <t xml:space="preserve">2.960120677948</t>
   </si>
   <si>
     <t xml:space="preserve">2.99666523933411</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79566955566406</t>
+    <t xml:space="preserve">2.79566931724548</t>
   </si>
   <si>
     <t xml:space="preserve">2.81394171714783</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77739691734314</t>
+    <t xml:space="preserve">2.77739715576172</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75912475585938</t>
+    <t xml:space="preserve">2.7591245174408</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70430779457092</t>
+    <t xml:space="preserve">2.70430755615234</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64949083328247</t>
+    <t xml:space="preserve">2.64949059486389</t>
   </si>
   <si>
     <t xml:space="preserve">2.68603539466858</t>
@@ -1664,22 +1661,25 @@
     <t xml:space="preserve">2.72258019447327</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59467339515686</t>
+    <t xml:space="preserve">2.59467363357544</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5764012336731</t>
+    <t xml:space="preserve">2.57640099525452</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61294603347778</t>
+    <t xml:space="preserve">2.6129457950592</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97839307785034</t>
+    <t xml:space="preserve">2.97839283943176</t>
   </si>
   <si>
     <t xml:space="preserve">2.823077917099</t>
   </si>
   <si>
     <t xml:space="preserve">2.85962271690369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80480551719666</t>
   </si>
   <si>
     <t xml:space="preserve">2.89616751670837</t>
@@ -1694,7 +1694,7 @@
     <t xml:space="preserve">3.01493763923645</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96925687789917</t>
+    <t xml:space="preserve">2.96925663948059</t>
   </si>
   <si>
     <t xml:space="preserve">3.02674722671509</t>
@@ -1791,6 +1791,9 @@
   </si>
   <si>
     <t xml:space="preserve">3.23614478111267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96012043952942</t>
   </si>
   <si>
     <t xml:space="preserve">3.20000004768372</t>
@@ -44987,7 +44990,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G1642" t="s">
-        <v>495</v>
+        <v>461</v>
       </c>
       <c r="H1642" t="s">
         <v>9</v>
@@ -45013,7 +45016,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G1643" t="s">
-        <v>495</v>
+        <v>461</v>
       </c>
       <c r="H1643" t="s">
         <v>9</v>
@@ -45039,7 +45042,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G1644" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="H1644" t="s">
         <v>9</v>
@@ -45091,7 +45094,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G1646" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="H1646" t="s">
         <v>9</v>
@@ -45117,7 +45120,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1647" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="H1647" t="s">
         <v>9</v>
@@ -45143,7 +45146,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G1648" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="H1648" t="s">
         <v>9</v>
@@ -45195,7 +45198,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1650" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="H1650" t="s">
         <v>9</v>
@@ -45221,7 +45224,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1651" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="H1651" t="s">
         <v>9</v>
@@ -45247,7 +45250,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1652" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="H1652" t="s">
         <v>9</v>
@@ -45273,7 +45276,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G1653" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="H1653" t="s">
         <v>9</v>
@@ -45299,7 +45302,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G1654" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="H1654" t="s">
         <v>9</v>
@@ -45325,7 +45328,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G1655" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="H1655" t="s">
         <v>9</v>
@@ -45351,7 +45354,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G1656" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="H1656" t="s">
         <v>9</v>
@@ -45377,7 +45380,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G1657" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="H1657" t="s">
         <v>9</v>
@@ -45429,7 +45432,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G1659" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H1659" t="s">
         <v>9</v>
@@ -45455,7 +45458,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1660" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="H1660" t="s">
         <v>9</v>
@@ -45481,7 +45484,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G1661" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="H1661" t="s">
         <v>9</v>
@@ -45507,7 +45510,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1662" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="H1662" t="s">
         <v>9</v>
@@ -45533,7 +45536,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1663" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="H1663" t="s">
         <v>9</v>
@@ -45559,7 +45562,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1664" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="H1664" t="s">
         <v>9</v>
@@ -45585,7 +45588,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1665" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="H1665" t="s">
         <v>9</v>
@@ -45611,7 +45614,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1666" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="H1666" t="s">
         <v>9</v>
@@ -45637,7 +45640,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1667" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="H1667" t="s">
         <v>9</v>
@@ -45663,7 +45666,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G1668" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="H1668" t="s">
         <v>9</v>
@@ -45689,7 +45692,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1669" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="H1669" t="s">
         <v>9</v>
@@ -45715,7 +45718,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1670" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="H1670" t="s">
         <v>9</v>
@@ -45741,7 +45744,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G1671" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H1671" t="s">
         <v>9</v>
@@ -45767,7 +45770,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1672" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="H1672" t="s">
         <v>9</v>
@@ -45793,7 +45796,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G1673" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="H1673" t="s">
         <v>9</v>
@@ -45819,7 +45822,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G1674" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="H1674" t="s">
         <v>9</v>
@@ -45845,7 +45848,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G1675" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="H1675" t="s">
         <v>9</v>
@@ -45871,7 +45874,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G1676" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="H1676" t="s">
         <v>9</v>
@@ -45897,7 +45900,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1677" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="H1677" t="s">
         <v>9</v>
@@ -45923,7 +45926,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G1678" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="H1678" t="s">
         <v>9</v>
@@ -45949,7 +45952,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G1679" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H1679" t="s">
         <v>9</v>
@@ -45975,7 +45978,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1680" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="H1680" t="s">
         <v>9</v>
@@ -46001,7 +46004,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G1681" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="H1681" t="s">
         <v>9</v>
@@ -46053,7 +46056,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1683" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="H1683" t="s">
         <v>9</v>
@@ -46079,7 +46082,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G1684" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="H1684" t="s">
         <v>9</v>
@@ -46131,7 +46134,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G1686" t="s">
-        <v>495</v>
+        <v>461</v>
       </c>
       <c r="H1686" t="s">
         <v>9</v>
@@ -46157,7 +46160,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G1687" t="s">
-        <v>495</v>
+        <v>461</v>
       </c>
       <c r="H1687" t="s">
         <v>9</v>
@@ -46183,7 +46186,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G1688" t="s">
-        <v>495</v>
+        <v>461</v>
       </c>
       <c r="H1688" t="s">
         <v>9</v>
@@ -46209,7 +46212,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1689" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="H1689" t="s">
         <v>9</v>
@@ -46235,7 +46238,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G1690" t="s">
-        <v>495</v>
+        <v>461</v>
       </c>
       <c r="H1690" t="s">
         <v>9</v>
@@ -46261,7 +46264,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G1691" t="s">
-        <v>495</v>
+        <v>461</v>
       </c>
       <c r="H1691" t="s">
         <v>9</v>
@@ -46287,7 +46290,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G1692" t="s">
-        <v>495</v>
+        <v>461</v>
       </c>
       <c r="H1692" t="s">
         <v>9</v>
@@ -46313,7 +46316,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1693" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="H1693" t="s">
         <v>9</v>
@@ -46339,7 +46342,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G1694" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="H1694" t="s">
         <v>9</v>
@@ -46365,7 +46368,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G1695" t="s">
-        <v>495</v>
+        <v>461</v>
       </c>
       <c r="H1695" t="s">
         <v>9</v>
@@ -46443,7 +46446,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G1698" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="H1698" t="s">
         <v>9</v>
@@ -46469,7 +46472,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G1699" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="H1699" t="s">
         <v>9</v>
@@ -46495,7 +46498,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1700" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="H1700" t="s">
         <v>9</v>
@@ -46547,7 +46550,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G1702" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="H1702" t="s">
         <v>9</v>
@@ -46573,7 +46576,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1703" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="H1703" t="s">
         <v>9</v>
@@ -46599,7 +46602,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G1704" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="H1704" t="s">
         <v>9</v>
@@ -46625,7 +46628,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G1705" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="H1705" t="s">
         <v>9</v>
@@ -46651,7 +46654,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1706" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="H1706" t="s">
         <v>9</v>
@@ -46677,7 +46680,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1707" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="H1707" t="s">
         <v>9</v>
@@ -46781,7 +46784,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G1711" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="H1711" t="s">
         <v>9</v>
@@ -46807,7 +46810,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1712" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="H1712" t="s">
         <v>9</v>
@@ -46833,7 +46836,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G1713" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="H1713" t="s">
         <v>9</v>
@@ -46859,7 +46862,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G1714" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="H1714" t="s">
         <v>9</v>
@@ -46885,7 +46888,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G1715" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="H1715" t="s">
         <v>9</v>
@@ -46911,7 +46914,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1716" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="H1716" t="s">
         <v>9</v>
@@ -46937,7 +46940,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G1717" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="H1717" t="s">
         <v>9</v>
@@ -46963,7 +46966,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G1718" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="H1718" t="s">
         <v>9</v>
@@ -46989,7 +46992,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1719" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="H1719" t="s">
         <v>9</v>
@@ -47015,7 +47018,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G1720" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="H1720" t="s">
         <v>9</v>
@@ -47041,7 +47044,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G1721" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="H1721" t="s">
         <v>9</v>
@@ -47067,7 +47070,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G1722" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="H1722" t="s">
         <v>9</v>
@@ -47093,7 +47096,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G1723" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="H1723" t="s">
         <v>9</v>
@@ -47119,7 +47122,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G1724" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="H1724" t="s">
         <v>9</v>
@@ -47145,7 +47148,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G1725" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="H1725" t="s">
         <v>9</v>
@@ -47171,7 +47174,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G1726" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="H1726" t="s">
         <v>9</v>
@@ -47197,7 +47200,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G1727" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="H1727" t="s">
         <v>9</v>
@@ -47223,7 +47226,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G1728" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="H1728" t="s">
         <v>9</v>
@@ -47249,7 +47252,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G1729" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H1729" t="s">
         <v>9</v>
@@ -47275,7 +47278,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G1730" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="H1730" t="s">
         <v>9</v>
@@ -47301,7 +47304,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G1731" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="H1731" t="s">
         <v>9</v>
@@ -47327,7 +47330,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G1732" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="H1732" t="s">
         <v>9</v>
@@ -47353,7 +47356,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G1733" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="H1733" t="s">
         <v>9</v>
@@ -47379,7 +47382,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1734" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="H1734" t="s">
         <v>9</v>
@@ -47405,7 +47408,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1735" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="H1735" t="s">
         <v>9</v>
@@ -47431,7 +47434,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G1736" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="H1736" t="s">
         <v>9</v>
@@ -47457,7 +47460,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1737" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="H1737" t="s">
         <v>9</v>
@@ -47483,7 +47486,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G1738" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="H1738" t="s">
         <v>9</v>
@@ -47509,7 +47512,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G1739" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="H1739" t="s">
         <v>9</v>
@@ -47535,7 +47538,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G1740" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="H1740" t="s">
         <v>9</v>
@@ -47561,7 +47564,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1741" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="H1741" t="s">
         <v>9</v>
@@ -47587,7 +47590,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1742" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="H1742" t="s">
         <v>9</v>
@@ -47613,7 +47616,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G1743" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="H1743" t="s">
         <v>9</v>
@@ -47639,7 +47642,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G1744" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="H1744" t="s">
         <v>9</v>
@@ -47665,7 +47668,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G1745" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="H1745" t="s">
         <v>9</v>
@@ -47691,7 +47694,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G1746" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="H1746" t="s">
         <v>9</v>
@@ -47717,7 +47720,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1747" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="H1747" t="s">
         <v>9</v>
@@ -47743,7 +47746,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G1748" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="H1748" t="s">
         <v>9</v>
@@ -47769,7 +47772,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G1749" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="H1749" t="s">
         <v>9</v>
@@ -47795,7 +47798,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1750" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="H1750" t="s">
         <v>9</v>
@@ -47821,7 +47824,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G1751" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H1751" t="s">
         <v>9</v>
@@ -47847,7 +47850,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1752" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="H1752" t="s">
         <v>9</v>
@@ -47873,7 +47876,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G1753" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H1753" t="s">
         <v>9</v>
@@ -47899,7 +47902,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G1754" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="H1754" t="s">
         <v>9</v>
@@ -47925,7 +47928,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G1755" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H1755" t="s">
         <v>9</v>
@@ -47951,7 +47954,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G1756" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="H1756" t="s">
         <v>9</v>
@@ -47977,7 +47980,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1757" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="H1757" t="s">
         <v>9</v>
@@ -48003,7 +48006,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G1758" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="H1758" t="s">
         <v>9</v>
@@ -48029,7 +48032,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G1759" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="H1759" t="s">
         <v>9</v>
@@ -48055,7 +48058,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G1760" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="H1760" t="s">
         <v>9</v>
@@ -48081,7 +48084,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G1761" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="H1761" t="s">
         <v>9</v>
@@ -48107,7 +48110,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G1762" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="H1762" t="s">
         <v>9</v>
@@ -48133,7 +48136,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1763" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H1763" t="s">
         <v>9</v>
@@ -48159,7 +48162,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G1764" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H1764" t="s">
         <v>9</v>
@@ -48185,7 +48188,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G1765" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H1765" t="s">
         <v>9</v>
@@ -48211,7 +48214,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G1766" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H1766" t="s">
         <v>9</v>
@@ -48237,7 +48240,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G1767" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="H1767" t="s">
         <v>9</v>
@@ -48263,7 +48266,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G1768" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="H1768" t="s">
         <v>9</v>
@@ -48289,7 +48292,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G1769" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="H1769" t="s">
         <v>9</v>
@@ -48315,7 +48318,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G1770" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="H1770" t="s">
         <v>9</v>
@@ -48341,7 +48344,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G1771" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H1771" t="s">
         <v>9</v>
@@ -48367,7 +48370,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1772" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="H1772" t="s">
         <v>9</v>
@@ -48393,7 +48396,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1773" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="H1773" t="s">
         <v>9</v>
@@ -48419,7 +48422,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1774" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="H1774" t="s">
         <v>9</v>
@@ -48445,7 +48448,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1775" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="H1775" t="s">
         <v>9</v>
@@ -48471,7 +48474,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1776" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="H1776" t="s">
         <v>9</v>
@@ -48497,7 +48500,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1777" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="H1777" t="s">
         <v>9</v>
@@ -48523,7 +48526,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1778" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="H1778" t="s">
         <v>9</v>
@@ -48549,7 +48552,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1779" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="H1779" t="s">
         <v>9</v>
@@ -48575,7 +48578,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1780" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="H1780" t="s">
         <v>9</v>
@@ -48601,7 +48604,7 @@
         <v>3.25</v>
       </c>
       <c r="G1781" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="H1781" t="s">
         <v>9</v>
@@ -48627,7 +48630,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G1782" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="H1782" t="s">
         <v>9</v>
@@ -48653,7 +48656,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G1783" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H1783" t="s">
         <v>9</v>
@@ -48679,7 +48682,7 @@
         <v>3.25</v>
       </c>
       <c r="G1784" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="H1784" t="s">
         <v>9</v>
@@ -48705,7 +48708,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G1785" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="H1785" t="s">
         <v>9</v>
@@ -48731,7 +48734,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G1786" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="H1786" t="s">
         <v>9</v>
@@ -48757,7 +48760,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G1787" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="H1787" t="s">
         <v>9</v>
@@ -48783,7 +48786,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G1788" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="H1788" t="s">
         <v>9</v>
@@ -48809,7 +48812,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1789" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="H1789" t="s">
         <v>9</v>
@@ -48835,7 +48838,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1790" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="H1790" t="s">
         <v>9</v>
@@ -48861,7 +48864,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1791" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="H1791" t="s">
         <v>9</v>
@@ -48887,7 +48890,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1792" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="H1792" t="s">
         <v>9</v>
@@ -48913,7 +48916,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G1793" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="H1793" t="s">
         <v>9</v>
@@ -48939,7 +48942,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1794" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="H1794" t="s">
         <v>9</v>
@@ -48965,7 +48968,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G1795" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="H1795" t="s">
         <v>9</v>
@@ -48991,7 +48994,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G1796" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="H1796" t="s">
         <v>9</v>
@@ -49017,7 +49020,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1797" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="H1797" t="s">
         <v>9</v>
@@ -49043,7 +49046,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G1798" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="H1798" t="s">
         <v>9</v>
@@ -49069,7 +49072,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G1799" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H1799" t="s">
         <v>9</v>
@@ -49095,7 +49098,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G1800" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="H1800" t="s">
         <v>9</v>
@@ -49121,7 +49124,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1801" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="H1801" t="s">
         <v>9</v>
@@ -49147,7 +49150,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G1802" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H1802" t="s">
         <v>9</v>
@@ -49173,7 +49176,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G1803" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H1803" t="s">
         <v>9</v>
@@ -49199,7 +49202,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G1804" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="H1804" t="s">
         <v>9</v>
@@ -49225,7 +49228,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G1805" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="H1805" t="s">
         <v>9</v>
@@ -49251,7 +49254,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G1806" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="H1806" t="s">
         <v>9</v>
@@ -49277,7 +49280,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G1807" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="H1807" t="s">
         <v>9</v>
@@ -49303,7 +49306,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G1808" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="H1808" t="s">
         <v>9</v>
@@ -49329,7 +49332,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1809" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="H1809" t="s">
         <v>9</v>
@@ -49355,7 +49358,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G1810" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="H1810" t="s">
         <v>9</v>
@@ -49381,7 +49384,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1811" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="H1811" t="s">
         <v>9</v>
@@ -49407,7 +49410,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G1812" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="H1812" t="s">
         <v>9</v>
@@ -49433,7 +49436,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G1813" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H1813" t="s">
         <v>9</v>
@@ -49459,7 +49462,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G1814" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="H1814" t="s">
         <v>9</v>
@@ -49485,7 +49488,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1815" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="H1815" t="s">
         <v>9</v>
@@ -49511,7 +49514,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G1816" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H1816" t="s">
         <v>9</v>
@@ -49537,7 +49540,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G1817" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H1817" t="s">
         <v>9</v>
@@ -49563,7 +49566,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G1818" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H1818" t="s">
         <v>9</v>
@@ -49589,7 +49592,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1819" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="H1819" t="s">
         <v>9</v>
@@ -49615,7 +49618,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1820" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="H1820" t="s">
         <v>9</v>
@@ -49641,7 +49644,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1821" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="H1821" t="s">
         <v>9</v>
@@ -49667,7 +49670,7 @@
         <v>3.25</v>
       </c>
       <c r="G1822" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="H1822" t="s">
         <v>9</v>
@@ -49693,7 +49696,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G1823" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H1823" t="s">
         <v>9</v>
@@ -49719,7 +49722,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G1824" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="H1824" t="s">
         <v>9</v>
@@ -49745,7 +49748,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G1825" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H1825" t="s">
         <v>9</v>
@@ -49771,7 +49774,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G1826" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="H1826" t="s">
         <v>9</v>
@@ -49797,7 +49800,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G1827" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H1827" t="s">
         <v>9</v>
@@ -49823,7 +49826,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G1828" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H1828" t="s">
         <v>9</v>
@@ -49849,7 +49852,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G1829" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H1829" t="s">
         <v>9</v>
@@ -49875,7 +49878,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1830" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="H1830" t="s">
         <v>9</v>
@@ -49901,7 +49904,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G1831" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="H1831" t="s">
         <v>9</v>
@@ -49927,7 +49930,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1832" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H1832" t="s">
         <v>9</v>
@@ -49953,7 +49956,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G1833" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="H1833" t="s">
         <v>9</v>
@@ -49979,7 +49982,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G1834" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="H1834" t="s">
         <v>9</v>
@@ -50005,7 +50008,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G1835" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H1835" t="s">
         <v>9</v>
@@ -50031,7 +50034,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G1836" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="H1836" t="s">
         <v>9</v>
@@ -50057,7 +50060,7 @@
         <v>3.25</v>
       </c>
       <c r="G1837" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="H1837" t="s">
         <v>9</v>
@@ -50083,7 +50086,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G1838" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="H1838" t="s">
         <v>9</v>
@@ -50109,7 +50112,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G1839" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="H1839" t="s">
         <v>9</v>
@@ -50135,7 +50138,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1840" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="H1840" t="s">
         <v>9</v>
@@ -50161,7 +50164,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G1841" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="H1841" t="s">
         <v>9</v>
@@ -50187,7 +50190,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G1842" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="H1842" t="s">
         <v>9</v>
@@ -50213,7 +50216,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G1843" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="H1843" t="s">
         <v>9</v>
@@ -50239,7 +50242,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G1844" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H1844" t="s">
         <v>9</v>
@@ -50265,7 +50268,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1845" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="H1845" t="s">
         <v>9</v>
@@ -50291,7 +50294,7 @@
         <v>3.25</v>
       </c>
       <c r="G1846" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="H1846" t="s">
         <v>9</v>
@@ -50317,7 +50320,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1847" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="H1847" t="s">
         <v>9</v>
@@ -50343,7 +50346,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G1848" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="H1848" t="s">
         <v>9</v>
@@ -50369,7 +50372,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G1849" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="H1849" t="s">
         <v>9</v>
@@ -50395,7 +50398,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1850" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="H1850" t="s">
         <v>9</v>
@@ -50421,7 +50424,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1851" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="H1851" t="s">
         <v>9</v>
@@ -50447,7 +50450,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1852" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="H1852" t="s">
         <v>9</v>
@@ -50473,7 +50476,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G1853" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H1853" t="s">
         <v>9</v>
@@ -50499,7 +50502,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1854" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H1854" t="s">
         <v>9</v>
@@ -50525,7 +50528,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1855" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H1855" t="s">
         <v>9</v>
@@ -50551,7 +50554,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G1856" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H1856" t="s">
         <v>9</v>
@@ -50577,7 +50580,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1857" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H1857" t="s">
         <v>9</v>
@@ -50603,7 +50606,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1858" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="H1858" t="s">
         <v>9</v>
@@ -50629,7 +50632,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G1859" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H1859" t="s">
         <v>9</v>
@@ -50655,7 +50658,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G1860" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="H1860" t="s">
         <v>9</v>
@@ -50681,7 +50684,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G1861" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="H1861" t="s">
         <v>9</v>
@@ -50707,7 +50710,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G1862" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="H1862" t="s">
         <v>9</v>
@@ -50733,7 +50736,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1863" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H1863" t="s">
         <v>9</v>
@@ -50759,7 +50762,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G1864" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H1864" t="s">
         <v>9</v>
@@ -50785,7 +50788,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G1865" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H1865" t="s">
         <v>9</v>
@@ -50811,7 +50814,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G1866" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="H1866" t="s">
         <v>9</v>
@@ -50837,7 +50840,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G1867" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="H1867" t="s">
         <v>9</v>
@@ -50863,7 +50866,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G1868" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H1868" t="s">
         <v>9</v>
@@ -50889,7 +50892,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G1869" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H1869" t="s">
         <v>9</v>
@@ -50915,7 +50918,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G1870" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H1870" t="s">
         <v>9</v>
@@ -50941,7 +50944,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G1871" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H1871" t="s">
         <v>9</v>
@@ -50967,7 +50970,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1872" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H1872" t="s">
         <v>9</v>
@@ -50993,7 +50996,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1873" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H1873" t="s">
         <v>9</v>
@@ -51019,7 +51022,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1874" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H1874" t="s">
         <v>9</v>
@@ -51045,7 +51048,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G1875" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="H1875" t="s">
         <v>9</v>
@@ -51071,7 +51074,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1876" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H1876" t="s">
         <v>9</v>
@@ -51097,7 +51100,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1877" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="H1877" t="s">
         <v>9</v>
@@ -51123,7 +51126,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G1878" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="H1878" t="s">
         <v>9</v>
@@ -51149,7 +51152,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G1879" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H1879" t="s">
         <v>9</v>
@@ -51175,7 +51178,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G1880" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="H1880" t="s">
         <v>9</v>
@@ -51201,7 +51204,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G1881" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="H1881" t="s">
         <v>9</v>
@@ -51227,7 +51230,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G1882" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H1882" t="s">
         <v>9</v>
@@ -51253,7 +51256,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G1883" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H1883" t="s">
         <v>9</v>
@@ -51279,7 +51282,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G1884" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H1884" t="s">
         <v>9</v>
@@ -51305,7 +51308,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1885" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="H1885" t="s">
         <v>9</v>
@@ -51331,7 +51334,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1886" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="H1886" t="s">
         <v>9</v>
@@ -51357,7 +51360,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1887" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H1887" t="s">
         <v>9</v>
@@ -51383,7 +51386,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1888" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H1888" t="s">
         <v>9</v>
@@ -51409,7 +51412,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G1889" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="H1889" t="s">
         <v>9</v>
@@ -51435,7 +51438,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1890" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H1890" t="s">
         <v>9</v>
@@ -51461,7 +51464,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1891" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H1891" t="s">
         <v>9</v>
@@ -51487,7 +51490,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G1892" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="H1892" t="s">
         <v>9</v>
@@ -51513,7 +51516,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1893" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H1893" t="s">
         <v>9</v>
@@ -51539,7 +51542,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G1894" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H1894" t="s">
         <v>9</v>
@@ -51565,7 +51568,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1895" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H1895" t="s">
         <v>9</v>
@@ -51591,7 +51594,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1896" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H1896" t="s">
         <v>9</v>
@@ -51617,7 +51620,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1897" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H1897" t="s">
         <v>9</v>
@@ -51643,7 +51646,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1898" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H1898" t="s">
         <v>9</v>
@@ -51669,7 +51672,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1899" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H1899" t="s">
         <v>9</v>
@@ -51695,7 +51698,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1900" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H1900" t="s">
         <v>9</v>
@@ -51721,7 +51724,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1901" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H1901" t="s">
         <v>9</v>
@@ -51747,7 +51750,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1902" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H1902" t="s">
         <v>9</v>
@@ -51773,7 +51776,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G1903" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H1903" t="s">
         <v>9</v>
@@ -51799,7 +51802,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G1904" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="H1904" t="s">
         <v>9</v>
@@ -51825,7 +51828,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1905" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H1905" t="s">
         <v>9</v>
@@ -51851,7 +51854,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1906" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="H1906" t="s">
         <v>9</v>
@@ -51877,7 +51880,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1907" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H1907" t="s">
         <v>9</v>
@@ -51903,7 +51906,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1908" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H1908" t="s">
         <v>9</v>
@@ -51929,7 +51932,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1909" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H1909" t="s">
         <v>9</v>
@@ -51955,7 +51958,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G1910" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="H1910" t="s">
         <v>9</v>
@@ -51981,7 +51984,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1911" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H1911" t="s">
         <v>9</v>
@@ -52007,7 +52010,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1912" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H1912" t="s">
         <v>9</v>
@@ -52033,7 +52036,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1913" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H1913" t="s">
         <v>9</v>
@@ -52059,7 +52062,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1914" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H1914" t="s">
         <v>9</v>
@@ -52085,7 +52088,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1915" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H1915" t="s">
         <v>9</v>
@@ -52111,7 +52114,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1916" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H1916" t="s">
         <v>9</v>
@@ -52137,7 +52140,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1917" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H1917" t="s">
         <v>9</v>
@@ -52163,7 +52166,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G1918" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="H1918" t="s">
         <v>9</v>
@@ -52189,7 +52192,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G1919" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H1919" t="s">
         <v>9</v>
@@ -52215,7 +52218,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G1920" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="H1920" t="s">
         <v>9</v>
@@ -52241,7 +52244,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1921" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H1921" t="s">
         <v>9</v>
@@ -52267,7 +52270,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1922" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H1922" t="s">
         <v>9</v>
@@ -52293,7 +52296,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G1923" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="H1923" t="s">
         <v>9</v>
@@ -52319,7 +52322,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G1924" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="H1924" t="s">
         <v>9</v>
@@ -52345,7 +52348,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1925" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H1925" t="s">
         <v>9</v>
@@ -52371,7 +52374,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G1926" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H1926" t="s">
         <v>9</v>
@@ -52397,7 +52400,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1927" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="H1927" t="s">
         <v>9</v>
@@ -52423,7 +52426,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G1928" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="H1928" t="s">
         <v>9</v>
@@ -52449,7 +52452,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G1929" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="H1929" t="s">
         <v>9</v>
@@ -52475,7 +52478,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G1930" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H1930" t="s">
         <v>9</v>
@@ -52501,7 +52504,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G1931" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H1931" t="s">
         <v>9</v>
@@ -52527,7 +52530,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G1932" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="H1932" t="s">
         <v>9</v>
@@ -52553,7 +52556,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G1933" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H1933" t="s">
         <v>9</v>
@@ -52579,7 +52582,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G1934" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H1934" t="s">
         <v>9</v>
@@ -52605,7 +52608,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1935" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H1935" t="s">
         <v>9</v>
@@ -52631,7 +52634,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1936" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H1936" t="s">
         <v>9</v>
@@ -52657,7 +52660,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1937" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H1937" t="s">
         <v>9</v>
@@ -52683,7 +52686,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1938" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H1938" t="s">
         <v>9</v>
@@ -52709,7 +52712,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1939" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H1939" t="s">
         <v>9</v>
@@ -52735,7 +52738,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G1940" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="H1940" t="s">
         <v>9</v>
@@ -52761,7 +52764,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1941" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H1941" t="s">
         <v>9</v>
@@ -52787,7 +52790,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1942" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H1942" t="s">
         <v>9</v>
@@ -52813,7 +52816,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1943" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H1943" t="s">
         <v>9</v>
@@ -52839,7 +52842,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1944" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H1944" t="s">
         <v>9</v>
@@ -52865,7 +52868,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1945" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="H1945" t="s">
         <v>9</v>
@@ -52891,7 +52894,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G1946" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="H1946" t="s">
         <v>9</v>
@@ -52917,7 +52920,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1947" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H1947" t="s">
         <v>9</v>
@@ -52943,7 +52946,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1948" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H1948" t="s">
         <v>9</v>
@@ -52969,7 +52972,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1949" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H1949" t="s">
         <v>9</v>
@@ -52995,7 +52998,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G1950" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="H1950" t="s">
         <v>9</v>
@@ -53021,7 +53024,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G1951" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="H1951" t="s">
         <v>9</v>
@@ -53047,7 +53050,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1952" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H1952" t="s">
         <v>9</v>
@@ -53073,7 +53076,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1953" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="H1953" t="s">
         <v>9</v>
@@ -53099,7 +53102,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1954" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H1954" t="s">
         <v>9</v>
@@ -53125,7 +53128,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G1955" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="H1955" t="s">
         <v>9</v>
@@ -53151,7 +53154,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G1956" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="H1956" t="s">
         <v>9</v>
@@ -53177,7 +53180,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G1957" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="H1957" t="s">
         <v>9</v>
@@ -53203,7 +53206,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1958" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="H1958" t="s">
         <v>9</v>
@@ -53229,7 +53232,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1959" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="H1959" t="s">
         <v>9</v>
@@ -53255,7 +53258,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1960" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="H1960" t="s">
         <v>9</v>
@@ -53281,7 +53284,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G1961" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="H1961" t="s">
         <v>9</v>
@@ -53307,7 +53310,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G1962" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="H1962" t="s">
         <v>9</v>
@@ -53333,7 +53336,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G1963" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H1963" t="s">
         <v>9</v>
@@ -53359,7 +53362,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G1964" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="H1964" t="s">
         <v>9</v>
@@ -53385,7 +53388,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G1965" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="H1965" t="s">
         <v>9</v>
@@ -53411,7 +53414,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G1966" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="H1966" t="s">
         <v>9</v>
@@ -53437,7 +53440,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1967" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H1967" t="s">
         <v>9</v>
@@ -53463,7 +53466,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G1968" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="H1968" t="s">
         <v>9</v>
@@ -53489,7 +53492,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G1969" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="H1969" t="s">
         <v>9</v>
@@ -53515,7 +53518,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G1970" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="H1970" t="s">
         <v>9</v>
@@ -53541,7 +53544,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G1971" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="H1971" t="s">
         <v>9</v>
@@ -53567,7 +53570,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G1972" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="H1972" t="s">
         <v>9</v>
@@ -53593,7 +53596,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G1973" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="H1973" t="s">
         <v>9</v>
@@ -53619,7 +53622,7 @@
         <v>3</v>
       </c>
       <c r="G1974" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="H1974" t="s">
         <v>9</v>
@@ -53645,7 +53648,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1975" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H1975" t="s">
         <v>9</v>
@@ -53671,7 +53674,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G1976" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="H1976" t="s">
         <v>9</v>
@@ -53697,7 +53700,7 @@
         <v>3</v>
       </c>
       <c r="G1977" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="H1977" t="s">
         <v>9</v>
@@ -53723,7 +53726,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G1978" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="H1978" t="s">
         <v>9</v>
@@ -53749,7 +53752,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G1979" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="H1979" t="s">
         <v>9</v>
@@ -53775,7 +53778,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1980" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H1980" t="s">
         <v>9</v>
@@ -53801,7 +53804,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G1981" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="H1981" t="s">
         <v>9</v>
@@ -53827,7 +53830,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G1982" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="H1982" t="s">
         <v>9</v>
@@ -53853,7 +53856,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1983" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="H1983" t="s">
         <v>9</v>
@@ -53879,7 +53882,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1984" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="H1984" t="s">
         <v>9</v>
@@ -53905,7 +53908,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G1985" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="H1985" t="s">
         <v>9</v>
@@ -53931,7 +53934,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1986" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="H1986" t="s">
         <v>9</v>
@@ -53957,7 +53960,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1987" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="H1987" t="s">
         <v>9</v>
@@ -53983,7 +53986,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G1988" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="H1988" t="s">
         <v>9</v>
@@ -54009,7 +54012,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G1989" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="H1989" t="s">
         <v>9</v>
@@ -54035,7 +54038,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G1990" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="H1990" t="s">
         <v>9</v>
@@ -54061,7 +54064,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G1991" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="H1991" t="s">
         <v>9</v>
@@ -54087,7 +54090,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1992" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="H1992" t="s">
         <v>9</v>
@@ -54113,7 +54116,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1993" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="H1993" t="s">
         <v>9</v>
@@ -54139,7 +54142,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1994" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="H1994" t="s">
         <v>9</v>
@@ -54165,7 +54168,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1995" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="H1995" t="s">
         <v>9</v>
@@ -54191,7 +54194,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G1996" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="H1996" t="s">
         <v>9</v>
@@ -54217,7 +54220,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G1997" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="H1997" t="s">
         <v>9</v>
@@ -54243,7 +54246,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1998" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="H1998" t="s">
         <v>9</v>
@@ -54269,7 +54272,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1999" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H1999" t="s">
         <v>9</v>
@@ -54295,7 +54298,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G2000" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="H2000" t="s">
         <v>9</v>
@@ -54321,7 +54324,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G2001" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="H2001" t="s">
         <v>9</v>
@@ -54347,7 +54350,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G2002" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="H2002" t="s">
         <v>9</v>
@@ -54373,7 +54376,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G2003" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="H2003" t="s">
         <v>9</v>
@@ -54399,7 +54402,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G2004" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H2004" t="s">
         <v>9</v>
@@ -54425,7 +54428,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G2005" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H2005" t="s">
         <v>9</v>
@@ -54451,7 +54454,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G2006" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="H2006" t="s">
         <v>9</v>
@@ -54477,7 +54480,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G2007" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H2007" t="s">
         <v>9</v>
@@ -54503,7 +54506,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G2008" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="H2008" t="s">
         <v>9</v>
@@ -54529,7 +54532,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G2009" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="H2009" t="s">
         <v>9</v>
@@ -54555,7 +54558,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G2010" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="H2010" t="s">
         <v>9</v>
@@ -54581,7 +54584,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G2011" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="H2011" t="s">
         <v>9</v>
@@ -54607,7 +54610,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G2012" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="H2012" t="s">
         <v>9</v>
@@ -54633,7 +54636,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G2013" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="H2013" t="s">
         <v>9</v>
@@ -54659,7 +54662,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2014" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H2014" t="s">
         <v>9</v>
@@ -54685,7 +54688,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G2015" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="H2015" t="s">
         <v>9</v>
@@ -54711,7 +54714,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G2016" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H2016" t="s">
         <v>9</v>
@@ -54737,7 +54740,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G2017" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H2017" t="s">
         <v>9</v>
@@ -54763,7 +54766,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2018" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H2018" t="s">
         <v>9</v>
@@ -54789,7 +54792,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2019" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H2019" t="s">
         <v>9</v>
@@ -54815,7 +54818,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G2020" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H2020" t="s">
         <v>9</v>
@@ -54841,7 +54844,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2021" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H2021" t="s">
         <v>9</v>
@@ -54867,7 +54870,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G2022" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H2022" t="s">
         <v>9</v>
@@ -54893,7 +54896,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2023" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H2023" t="s">
         <v>9</v>
@@ -54919,7 +54922,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2024" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H2024" t="s">
         <v>9</v>
@@ -54945,7 +54948,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G2025" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H2025" t="s">
         <v>9</v>
@@ -54971,7 +54974,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G2026" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="H2026" t="s">
         <v>9</v>
@@ -54997,7 +55000,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2027" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H2027" t="s">
         <v>9</v>
@@ -55023,7 +55026,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2028" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H2028" t="s">
         <v>9</v>
@@ -55049,7 +55052,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G2029" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="H2029" t="s">
         <v>9</v>
@@ -55075,7 +55078,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2030" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H2030" t="s">
         <v>9</v>
@@ -55101,7 +55104,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G2031" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="H2031" t="s">
         <v>9</v>
@@ -55127,7 +55130,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G2032" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H2032" t="s">
         <v>9</v>
@@ -55153,7 +55156,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G2033" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="H2033" t="s">
         <v>9</v>
@@ -55179,7 +55182,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G2034" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="H2034" t="s">
         <v>9</v>
@@ -55205,7 +55208,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G2035" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H2035" t="s">
         <v>9</v>
@@ -55231,7 +55234,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2036" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H2036" t="s">
         <v>9</v>
@@ -55257,7 +55260,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G2037" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="H2037" t="s">
         <v>9</v>
@@ -55283,7 +55286,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G2038" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="H2038" t="s">
         <v>9</v>
@@ -55309,7 +55312,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2039" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H2039" t="s">
         <v>9</v>
@@ -55335,7 +55338,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G2040" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H2040" t="s">
         <v>9</v>
@@ -55361,7 +55364,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G2041" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H2041" t="s">
         <v>9</v>
@@ -55387,7 +55390,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G2042" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H2042" t="s">
         <v>9</v>
@@ -55413,7 +55416,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G2043" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H2043" t="s">
         <v>9</v>
@@ -55439,7 +55442,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2044" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H2044" t="s">
         <v>9</v>
@@ -55465,7 +55468,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2045" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H2045" t="s">
         <v>9</v>
@@ -55491,7 +55494,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2046" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H2046" t="s">
         <v>9</v>
@@ -55517,7 +55520,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G2047" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="H2047" t="s">
         <v>9</v>
@@ -55543,7 +55546,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2048" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H2048" t="s">
         <v>9</v>
@@ -55569,7 +55572,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2049" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H2049" t="s">
         <v>9</v>
@@ -55595,7 +55598,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2050" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H2050" t="s">
         <v>9</v>
@@ -55621,7 +55624,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G2051" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="H2051" t="s">
         <v>9</v>
@@ -55647,7 +55650,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G2052" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="H2052" t="s">
         <v>9</v>
@@ -55673,7 +55676,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G2053" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="H2053" t="s">
         <v>9</v>
@@ -55699,7 +55702,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2054" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H2054" t="s">
         <v>9</v>
@@ -55725,7 +55728,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G2055" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H2055" t="s">
         <v>9</v>
@@ -55751,7 +55754,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2056" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H2056" t="s">
         <v>9</v>
@@ -55777,7 +55780,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2057" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H2057" t="s">
         <v>9</v>
@@ -55803,7 +55806,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G2058" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H2058" t="s">
         <v>9</v>
@@ -55829,7 +55832,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G2059" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H2059" t="s">
         <v>9</v>
@@ -55855,7 +55858,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2060" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H2060" t="s">
         <v>9</v>
@@ -55881,7 +55884,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2061" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H2061" t="s">
         <v>9</v>
@@ -55907,7 +55910,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2062" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H2062" t="s">
         <v>9</v>
@@ -55933,7 +55936,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G2063" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="H2063" t="s">
         <v>9</v>
@@ -55959,7 +55962,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G2064" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="H2064" t="s">
         <v>9</v>
@@ -55985,7 +55988,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G2065" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="H2065" t="s">
         <v>9</v>
@@ -56011,7 +56014,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G2066" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="H2066" t="s">
         <v>9</v>
@@ -56037,7 +56040,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G2067" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H2067" t="s">
         <v>9</v>
@@ -56063,7 +56066,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G2068" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H2068" t="s">
         <v>9</v>
@@ -56089,7 +56092,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G2069" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H2069" t="s">
         <v>9</v>
@@ -56115,7 +56118,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G2070" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="H2070" t="s">
         <v>9</v>
@@ -56141,7 +56144,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G2071" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H2071" t="s">
         <v>9</v>
@@ -56167,7 +56170,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G2072" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="H2072" t="s">
         <v>9</v>
@@ -56193,7 +56196,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G2073" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H2073" t="s">
         <v>9</v>
@@ -56219,7 +56222,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2074" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H2074" t="s">
         <v>9</v>
@@ -56245,7 +56248,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G2075" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="H2075" t="s">
         <v>9</v>
@@ -56271,7 +56274,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G2076" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="H2076" t="s">
         <v>9</v>
@@ -56297,7 +56300,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G2077" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="H2077" t="s">
         <v>9</v>
@@ -56323,7 +56326,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G2078" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H2078" t="s">
         <v>9</v>
@@ -56349,7 +56352,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G2079" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H2079" t="s">
         <v>9</v>
@@ -56375,7 +56378,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G2080" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H2080" t="s">
         <v>9</v>
@@ -56401,7 +56404,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G2081" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="H2081" t="s">
         <v>9</v>
@@ -56427,7 +56430,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G2082" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="H2082" t="s">
         <v>9</v>
@@ -56453,7 +56456,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G2083" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H2083" t="s">
         <v>9</v>
@@ -56479,7 +56482,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G2084" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H2084" t="s">
         <v>9</v>
@@ -56505,7 +56508,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G2085" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H2085" t="s">
         <v>9</v>
@@ -56531,7 +56534,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G2086" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H2086" t="s">
         <v>9</v>
@@ -56557,7 +56560,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G2087" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H2087" t="s">
         <v>9</v>
@@ -56583,7 +56586,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G2088" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H2088" t="s">
         <v>9</v>
@@ -56609,7 +56612,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2089" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H2089" t="s">
         <v>9</v>
@@ -56635,7 +56638,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G2090" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H2090" t="s">
         <v>9</v>
@@ -56661,7 +56664,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2091" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H2091" t="s">
         <v>9</v>
@@ -56687,7 +56690,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2092" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H2092" t="s">
         <v>9</v>
@@ -56713,7 +56716,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2093" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H2093" t="s">
         <v>9</v>
@@ -56739,7 +56742,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G2094" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="H2094" t="s">
         <v>9</v>
@@ -56765,7 +56768,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G2095" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H2095" t="s">
         <v>9</v>
@@ -56791,7 +56794,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G2096" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H2096" t="s">
         <v>9</v>
@@ -56817,7 +56820,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G2097" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="H2097" t="s">
         <v>9</v>
@@ -56843,7 +56846,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G2098" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H2098" t="s">
         <v>9</v>
@@ -56869,7 +56872,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G2099" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H2099" t="s">
         <v>9</v>
@@ -56895,7 +56898,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G2100" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="H2100" t="s">
         <v>9</v>
@@ -56921,7 +56924,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G2101" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="H2101" t="s">
         <v>9</v>
@@ -56947,7 +56950,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G2102" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="H2102" t="s">
         <v>9</v>
@@ -56973,7 +56976,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G2103" t="s">
-        <v>504</v>
+        <v>555</v>
       </c>
       <c r="H2103" t="s">
         <v>9</v>
@@ -56999,7 +57002,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G2104" t="s">
-        <v>504</v>
+        <v>555</v>
       </c>
       <c r="H2104" t="s">
         <v>9</v>
@@ -57025,7 +57028,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G2105" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="H2105" t="s">
         <v>9</v>
@@ -57051,7 +57054,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G2106" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="H2106" t="s">
         <v>9</v>
@@ -57077,7 +57080,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G2107" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="H2107" t="s">
         <v>9</v>
@@ -57103,7 +57106,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G2108" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="H2108" t="s">
         <v>9</v>
@@ -57129,7 +57132,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G2109" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="H2109" t="s">
         <v>9</v>
@@ -57155,7 +57158,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G2110" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="H2110" t="s">
         <v>9</v>
@@ -57181,7 +57184,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G2111" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="H2111" t="s">
         <v>9</v>
@@ -57233,7 +57236,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G2113" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="H2113" t="s">
         <v>9</v>
@@ -57259,7 +57262,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G2114" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="H2114" t="s">
         <v>9</v>
@@ -57285,7 +57288,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G2115" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="H2115" t="s">
         <v>9</v>
@@ -57311,7 +57314,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G2116" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="H2116" t="s">
         <v>9</v>
@@ -57415,7 +57418,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G2120" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H2120" t="s">
         <v>9</v>
@@ -57493,7 +57496,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2123" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H2123" t="s">
         <v>9</v>
@@ -57675,7 +57678,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G2130" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="H2130" t="s">
         <v>9</v>
@@ -57701,7 +57704,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G2131" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="H2131" t="s">
         <v>9</v>
@@ -57727,7 +57730,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G2132" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="H2132" t="s">
         <v>9</v>
@@ -62589,7 +62592,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G2319" t="s">
-        <v>537</v>
+        <v>593</v>
       </c>
       <c r="H2319" t="s">
         <v>9</v>
@@ -64279,7 +64282,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2384" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="H2384" t="s">
         <v>9</v>
@@ -64305,7 +64308,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G2385" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="H2385" t="s">
         <v>9</v>
@@ -64331,7 +64334,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G2386" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="H2386" t="s">
         <v>9</v>
@@ -64357,7 +64360,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G2387" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="H2387" t="s">
         <v>9</v>
@@ -64383,7 +64386,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G2388" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="H2388" t="s">
         <v>9</v>
@@ -64409,7 +64412,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G2389" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="H2389" t="s">
         <v>9</v>
@@ -64435,7 +64438,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2390" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="H2390" t="s">
         <v>9</v>
@@ -64461,7 +64464,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2391" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="H2391" t="s">
         <v>9</v>
@@ -64513,7 +64516,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G2393" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="H2393" t="s">
         <v>9</v>
@@ -64565,7 +64568,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2395" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="H2395" t="s">
         <v>9</v>
@@ -64591,7 +64594,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2396" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="H2396" t="s">
         <v>9</v>
@@ -64617,7 +64620,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G2397" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="H2397" t="s">
         <v>9</v>
@@ -64643,7 +64646,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2398" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="H2398" t="s">
         <v>9</v>
@@ -64669,7 +64672,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G2399" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="H2399" t="s">
         <v>9</v>
@@ -64695,7 +64698,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G2400" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="H2400" t="s">
         <v>9</v>
@@ -64721,7 +64724,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G2401" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="H2401" t="s">
         <v>9</v>
@@ -64747,7 +64750,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G2402" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="H2402" t="s">
         <v>9</v>
@@ -64773,7 +64776,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G2403" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="H2403" t="s">
         <v>9</v>
@@ -64799,7 +64802,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G2404" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="H2404" t="s">
         <v>9</v>
@@ -64825,7 +64828,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G2405" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="H2405" t="s">
         <v>9</v>
@@ -64851,7 +64854,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G2406" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="H2406" t="s">
         <v>9</v>
@@ -64877,7 +64880,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G2407" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="H2407" t="s">
         <v>9</v>
@@ -64903,7 +64906,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G2408" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="H2408" t="s">
         <v>9</v>
@@ -64929,7 +64932,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2409" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="H2409" t="s">
         <v>9</v>
@@ -64955,7 +64958,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G2410" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="H2410" t="s">
         <v>9</v>
@@ -64981,7 +64984,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G2411" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="H2411" t="s">
         <v>9</v>
@@ -65007,7 +65010,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G2412" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="H2412" t="s">
         <v>9</v>
@@ -65033,7 +65036,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G2413" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="H2413" t="s">
         <v>9</v>
@@ -65059,7 +65062,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G2414" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="H2414" t="s">
         <v>9</v>
@@ -65085,7 +65088,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G2415" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="H2415" t="s">
         <v>9</v>
@@ -65111,7 +65114,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G2416" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="H2416" t="s">
         <v>9</v>
@@ -65137,7 +65140,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G2417" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="H2417" t="s">
         <v>9</v>
@@ -65163,7 +65166,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G2418" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="H2418" t="s">
         <v>9</v>
@@ -65189,7 +65192,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G2419" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="H2419" t="s">
         <v>9</v>
@@ -65215,7 +65218,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G2420" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="H2420" t="s">
         <v>9</v>
@@ -65241,7 +65244,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G2421" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="H2421" t="s">
         <v>9</v>
@@ -65267,7 +65270,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G2422" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="H2422" t="s">
         <v>9</v>
@@ -65293,7 +65296,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G2423" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="H2423" t="s">
         <v>9</v>
@@ -65319,7 +65322,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G2424" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="H2424" t="s">
         <v>9</v>
@@ -65345,7 +65348,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G2425" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="H2425" t="s">
         <v>9</v>
@@ -65371,7 +65374,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G2426" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="H2426" t="s">
         <v>9</v>
@@ -65397,7 +65400,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G2427" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="H2427" t="s">
         <v>9</v>
@@ -65423,7 +65426,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G2428" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="H2428" t="s">
         <v>9</v>
@@ -65449,7 +65452,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G2429" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="H2429" t="s">
         <v>9</v>
@@ -65475,7 +65478,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G2430" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="H2430" t="s">
         <v>9</v>
@@ -65501,7 +65504,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G2431" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="H2431" t="s">
         <v>9</v>
@@ -65527,7 +65530,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G2432" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="H2432" t="s">
         <v>9</v>
@@ -65553,7 +65556,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G2433" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="H2433" t="s">
         <v>9</v>
@@ -65579,7 +65582,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G2434" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="H2434" t="s">
         <v>9</v>
@@ -65605,7 +65608,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G2435" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="H2435" t="s">
         <v>9</v>
@@ -65631,7 +65634,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G2436" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="H2436" t="s">
         <v>9</v>
@@ -65657,7 +65660,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G2437" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="H2437" t="s">
         <v>9</v>
@@ -65683,7 +65686,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G2438" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="H2438" t="s">
         <v>9</v>
@@ -65709,7 +65712,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G2439" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="H2439" t="s">
         <v>9</v>
@@ -65735,7 +65738,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G2440" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="H2440" t="s">
         <v>9</v>
@@ -65761,7 +65764,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G2441" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="H2441" t="s">
         <v>9</v>
@@ -65787,7 +65790,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G2442" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="H2442" t="s">
         <v>9</v>
@@ -65813,7 +65816,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G2443" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="H2443" t="s">
         <v>9</v>
@@ -65839,7 +65842,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G2444" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="H2444" t="s">
         <v>9</v>
@@ -65865,7 +65868,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G2445" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="H2445" t="s">
         <v>9</v>
@@ -65891,7 +65894,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G2446" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="H2446" t="s">
         <v>9</v>
@@ -65917,7 +65920,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G2447" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="H2447" t="s">
         <v>9</v>
@@ -65943,7 +65946,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G2448" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="H2448" t="s">
         <v>9</v>
@@ -65969,7 +65972,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G2449" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="H2449" t="s">
         <v>9</v>
@@ -65995,7 +65998,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G2450" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="H2450" t="s">
         <v>9</v>
@@ -66021,7 +66024,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G2451" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="H2451" t="s">
         <v>9</v>
@@ -66047,7 +66050,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G2452" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="H2452" t="s">
         <v>9</v>
@@ -66073,7 +66076,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G2453" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="H2453" t="s">
         <v>9</v>
@@ -66099,7 +66102,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G2454" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="H2454" t="s">
         <v>9</v>
@@ -66125,7 +66128,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G2455" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="H2455" t="s">
         <v>9</v>
@@ -66151,7 +66154,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G2456" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="H2456" t="s">
         <v>9</v>
@@ -66177,7 +66180,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G2457" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="H2457" t="s">
         <v>9</v>
@@ -66203,7 +66206,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G2458" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="H2458" t="s">
         <v>9</v>
@@ -66229,7 +66232,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G2459" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="H2459" t="s">
         <v>9</v>
@@ -66255,7 +66258,7 @@
         <v>4</v>
       </c>
       <c r="G2460" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="H2460" t="s">
         <v>9</v>
@@ -66281,7 +66284,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G2461" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="H2461" t="s">
         <v>9</v>
@@ -66307,7 +66310,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G2462" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="H2462" t="s">
         <v>9</v>
@@ -66333,7 +66336,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G2463" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="H2463" t="s">
         <v>9</v>
@@ -66359,7 +66362,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G2464" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="H2464" t="s">
         <v>9</v>
@@ -66385,7 +66388,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G2465" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="H2465" t="s">
         <v>9</v>
@@ -66411,7 +66414,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G2466" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="H2466" t="s">
         <v>9</v>
@@ -66437,7 +66440,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G2467" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="H2467" t="s">
         <v>9</v>
@@ -66463,7 +66466,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G2468" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="H2468" t="s">
         <v>9</v>
@@ -66489,7 +66492,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G2469" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="H2469" t="s">
         <v>9</v>
@@ -66515,7 +66518,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G2470" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="H2470" t="s">
         <v>9</v>
@@ -66541,7 +66544,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G2471" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="H2471" t="s">
         <v>9</v>
@@ -66567,7 +66570,7 @@
         <v>4</v>
       </c>
       <c r="G2472" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="H2472" t="s">
         <v>9</v>
@@ -66593,7 +66596,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G2473" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="H2473" t="s">
         <v>9</v>
@@ -66619,7 +66622,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G2474" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="H2474" t="s">
         <v>9</v>
@@ -66645,7 +66648,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G2475" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="H2475" t="s">
         <v>9</v>
@@ -66671,7 +66674,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G2476" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="H2476" t="s">
         <v>9</v>
@@ -66697,7 +66700,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G2477" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="H2477" t="s">
         <v>9</v>
@@ -66723,7 +66726,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G2478" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="H2478" t="s">
         <v>9</v>
@@ -66749,7 +66752,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G2479" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="H2479" t="s">
         <v>9</v>
@@ -66775,7 +66778,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G2480" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="H2480" t="s">
         <v>9</v>
@@ -66801,7 +66804,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G2481" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="H2481" t="s">
         <v>9</v>
@@ -66827,7 +66830,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G2482" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="H2482" t="s">
         <v>9</v>
@@ -66853,7 +66856,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G2483" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="H2483" t="s">
         <v>9</v>
@@ -66879,7 +66882,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G2484" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="H2484" t="s">
         <v>9</v>
@@ -66905,7 +66908,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G2485" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="H2485" t="s">
         <v>9</v>
@@ -66931,7 +66934,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G2486" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="H2486" t="s">
         <v>9</v>
@@ -66957,7 +66960,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G2487" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="H2487" t="s">
         <v>9</v>
@@ -66983,7 +66986,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G2488" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="H2488" t="s">
         <v>9</v>
@@ -67009,7 +67012,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G2489" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="H2489" t="s">
         <v>9</v>
@@ -67035,7 +67038,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G2490" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="H2490" t="s">
         <v>9</v>
@@ -67061,7 +67064,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G2491" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="H2491" t="s">
         <v>9</v>
@@ -67087,7 +67090,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G2492" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="H2492" t="s">
         <v>9</v>
@@ -67113,7 +67116,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G2493" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="H2493" t="s">
         <v>9</v>
@@ -67139,7 +67142,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G2494" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="H2494" t="s">
         <v>9</v>
@@ -67165,7 +67168,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G2495" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="H2495" t="s">
         <v>9</v>
@@ -67191,7 +67194,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G2496" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="H2496" t="s">
         <v>9</v>
@@ -67217,7 +67220,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G2497" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="H2497" t="s">
         <v>9</v>
@@ -67243,7 +67246,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G2498" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="H2498" t="s">
         <v>9</v>
@@ -67269,7 +67272,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G2499" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="H2499" t="s">
         <v>9</v>
@@ -67295,7 +67298,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G2500" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="H2500" t="s">
         <v>9</v>
@@ -67321,7 +67324,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G2501" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="H2501" t="s">
         <v>9</v>
@@ -67347,7 +67350,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G2502" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="H2502" t="s">
         <v>9</v>
@@ -67373,7 +67376,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G2503" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="H2503" t="s">
         <v>9</v>
@@ -67399,7 +67402,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G2504" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="H2504" t="s">
         <v>9</v>
@@ -67425,7 +67428,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G2505" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="H2505" t="s">
         <v>9</v>
@@ -67451,7 +67454,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G2506" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="H2506" t="s">
         <v>9</v>
@@ -67477,7 +67480,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G2507" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="H2507" t="s">
         <v>9</v>
@@ -67503,7 +67506,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G2508" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="H2508" t="s">
         <v>9</v>
@@ -67529,7 +67532,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G2509" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="H2509" t="s">
         <v>9</v>
@@ -67555,7 +67558,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G2510" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="H2510" t="s">
         <v>9</v>
@@ -67581,7 +67584,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G2511" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="H2511" t="s">
         <v>9</v>
@@ -67607,7 +67610,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G2512" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="H2512" t="s">
         <v>9</v>
@@ -67633,7 +67636,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G2513" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H2513" t="s">
         <v>9</v>
@@ -67659,7 +67662,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G2514" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H2514" t="s">
         <v>9</v>
@@ -67685,7 +67688,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G2515" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="H2515" t="s">
         <v>9</v>
@@ -67711,7 +67714,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G2516" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="H2516" t="s">
         <v>9</v>
@@ -67737,7 +67740,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G2517" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="H2517" t="s">
         <v>9</v>
@@ -67763,7 +67766,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G2518" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="H2518" t="s">
         <v>9</v>
@@ -67789,7 +67792,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G2519" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="H2519" t="s">
         <v>9</v>
@@ -67815,7 +67818,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G2520" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="H2520" t="s">
         <v>9</v>
@@ -67841,7 +67844,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G2521" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="H2521" t="s">
         <v>9</v>
@@ -67867,7 +67870,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G2522" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="H2522" t="s">
         <v>9</v>
@@ -67893,7 +67896,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G2523" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H2523" t="s">
         <v>9</v>
@@ -67919,7 +67922,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G2524" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="H2524" t="s">
         <v>9</v>
@@ -67927,13 +67930,13 @@
     </row>
     <row r="2525">
       <c r="A2525" s="1" t="n">
-        <v>45994.6912962963</v>
+        <v>45994.3333333333</v>
       </c>
       <c r="B2525" t="n">
         <v>13579</v>
       </c>
       <c r="C2525" t="n">
-        <v>3.8199999332428</v>
+        <v>3.83999991416931</v>
       </c>
       <c r="D2525" t="n">
         <v>3.77999997138977</v>
@@ -67945,9 +67948,35 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G2525" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="H2525" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2526">
+      <c r="A2526" s="1" t="n">
+        <v>45995.691087963</v>
+      </c>
+      <c r="B2526" t="n">
+        <v>3016</v>
+      </c>
+      <c r="C2526" t="n">
+        <v>3.85999989509583</v>
+      </c>
+      <c r="D2526" t="n">
+        <v>3.74000000953674</v>
+      </c>
+      <c r="E2526" t="n">
+        <v>3.85999989509583</v>
+      </c>
+      <c r="F2526" t="n">
+        <v>3.83999991416931</v>
+      </c>
+      <c r="G2526" t="s">
+        <v>651</v>
+      </c>
+      <c r="H2526" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ENV.MI.xlsx
+++ b/data/ENV.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="652" uniqueCount="652">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="654" uniqueCount="654">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,16 +38,16 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18965244293213</t>
+    <t xml:space="preserve">2.18965220451355</t>
   </si>
   <si>
     <t xml:space="preserve">ENV.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20979785919189</t>
+    <t xml:space="preserve">2.20979762077332</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14471292495728</t>
+    <t xml:space="preserve">2.1447126865387</t>
   </si>
   <si>
     <t xml:space="preserve">2.16175866127014</t>
@@ -56,43 +56,43 @@
     <t xml:space="preserve">2.03778696060181</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08272671699524</t>
+    <t xml:space="preserve">2.08272647857666</t>
   </si>
   <si>
     <t xml:space="preserve">2.05328345298767</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03623747825623</t>
+    <t xml:space="preserve">2.03623723983765</t>
   </si>
   <si>
     <t xml:space="preserve">1.96805274486542</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96030461788177</t>
+    <t xml:space="preserve">1.9603043794632</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89831864833832</t>
+    <t xml:space="preserve">1.8983188867569</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88127255439758</t>
+    <t xml:space="preserve">1.88127267360687</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96340382099152</t>
+    <t xml:space="preserve">1.96340394020081</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9835489988327</t>
+    <t xml:space="preserve">1.98354911804199</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01299262046814</t>
+    <t xml:space="preserve">2.01299285888672</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93551003932953</t>
+    <t xml:space="preserve">1.9355103969574</t>
   </si>
   <si>
     <t xml:space="preserve">1.93705987930298</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91381537914276</t>
+    <t xml:space="preserve">1.91381525993347</t>
   </si>
   <si>
     <t xml:space="preserve">1.91071581840515</t>
@@ -101,13 +101,13 @@
     <t xml:space="preserve">1.86577606201172</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89212000370026</t>
+    <t xml:space="preserve">1.89212012290955</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85182929039001</t>
+    <t xml:space="preserve">1.8518294095993</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93396079540253</t>
+    <t xml:space="preserve">1.93396055698395</t>
   </si>
   <si>
     <t xml:space="preserve">1.86732578277588</t>
@@ -116,31 +116,31 @@
     <t xml:space="preserve">1.8890209197998</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98664879798889</t>
+    <t xml:space="preserve">1.9866486787796</t>
   </si>
   <si>
     <t xml:space="preserve">2.11526942253113</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18500351905823</t>
+    <t xml:space="preserve">2.18500328063965</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20824813842773</t>
+    <t xml:space="preserve">2.20824837684631</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16950726509094</t>
+    <t xml:space="preserve">2.16950678825378</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08427667617798</t>
+    <t xml:space="preserve">2.0842764377594</t>
   </si>
   <si>
     <t xml:space="preserve">2.01454210281372</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00524401664734</t>
+    <t xml:space="preserve">2.00524473190308</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14626216888428</t>
+    <t xml:space="preserve">2.14626240730286</t>
   </si>
   <si>
     <t xml:space="preserve">2.22219514846802</t>
@@ -149,16 +149,16 @@
     <t xml:space="preserve">2.32447195053101</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20049977302551</t>
+    <t xml:space="preserve">2.20050001144409</t>
   </si>
   <si>
     <t xml:space="preserve">2.27178382873535</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24698972702026</t>
+    <t xml:space="preserve">2.24698948860168</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32137274742126</t>
+    <t xml:space="preserve">2.32137250900269</t>
   </si>
   <si>
     <t xml:space="preserve">2.2841808795929</t>
@@ -170,19 +170,19 @@
     <t xml:space="preserve">2.35546493530273</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4406955242157</t>
+    <t xml:space="preserve">2.44069528579712</t>
   </si>
   <si>
     <t xml:space="preserve">2.43139743804932</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44999361038208</t>
+    <t xml:space="preserve">2.44999313354492</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3849081993103</t>
+    <t xml:space="preserve">2.38490796089172</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36166334152222</t>
+    <t xml:space="preserve">2.3616635799408</t>
   </si>
   <si>
     <t xml:space="preserve">2.3632128238678</t>
@@ -191,25 +191,25 @@
     <t xml:space="preserve">2.3198230266571</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35236597061157</t>
+    <t xml:space="preserve">2.35236549377441</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26868438720703</t>
+    <t xml:space="preserve">2.26868462562561</t>
   </si>
   <si>
     <t xml:space="preserve">2.32292199134827</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33531928062439</t>
+    <t xml:space="preserve">2.33531975746155</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33996844291687</t>
+    <t xml:space="preserve">2.33996820449829</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3105251789093</t>
+    <t xml:space="preserve">2.31052470207214</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28573060035706</t>
+    <t xml:space="preserve">2.28573083877563</t>
   </si>
   <si>
     <t xml:space="preserve">2.25473785400391</t>
@@ -221,22 +221,22 @@
     <t xml:space="preserve">2.27488327026367</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2314932346344</t>
+    <t xml:space="preserve">2.23149299621582</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0749785900116</t>
+    <t xml:space="preserve">2.07497882843018</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00834369659424</t>
+    <t xml:space="preserve">2.00834345817566</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03468799591064</t>
+    <t xml:space="preserve">2.03468751907349</t>
   </si>
   <si>
     <t xml:space="preserve">2.02229046821594</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97580111026764</t>
+    <t xml:space="preserve">1.97580099105835</t>
   </si>
   <si>
     <t xml:space="preserve">1.919806599617</t>
@@ -248,37 +248,37 @@
     <t xml:space="preserve">2.00136709213257</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96058702468872</t>
+    <t xml:space="preserve">1.96058714389801</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9025536775589</t>
+    <t xml:space="preserve">1.90255379676819</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92137551307678</t>
+    <t xml:space="preserve">1.92137515544891</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91353285312653</t>
+    <t xml:space="preserve">1.9135330915451</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89784848690033</t>
+    <t xml:space="preserve">1.89784836769104</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89000570774078</t>
+    <t xml:space="preserve">1.89000594615936</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85079395771027</t>
+    <t xml:space="preserve">1.85079407691956</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8805947303772</t>
+    <t xml:space="preserve">1.88059496879578</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86647891998291</t>
+    <t xml:space="preserve">1.86647868156433</t>
   </si>
   <si>
-    <t xml:space="preserve">1.546511054039</t>
+    <t xml:space="preserve">1.54651093482971</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6861047744751</t>
+    <t xml:space="preserve">1.68610489368439</t>
   </si>
   <si>
     <t xml:space="preserve">1.70178949832916</t>
@@ -287,31 +287,31 @@
     <t xml:space="preserve">1.70022106170654</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66257750988007</t>
+    <t xml:space="preserve">1.66257762908936</t>
   </si>
   <si>
     <t xml:space="preserve">1.64532470703125</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62336587905884</t>
+    <t xml:space="preserve">1.62336599826813</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61552357673645</t>
+    <t xml:space="preserve">1.61552345752716</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63120830059052</t>
+    <t xml:space="preserve">1.6312084197998</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5841543674469</t>
+    <t xml:space="preserve">1.58415412902832</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64689302444458</t>
+    <t xml:space="preserve">1.646892786026</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64061915874481</t>
+    <t xml:space="preserve">1.64061903953552</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63905072212219</t>
+    <t xml:space="preserve">1.6390506029129</t>
   </si>
   <si>
     <t xml:space="preserve">1.60768127441406</t>
@@ -320,25 +320,25 @@
     <t xml:space="preserve">1.57631182670593</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59199643135071</t>
+    <t xml:space="preserve">1.59199666976929</t>
   </si>
   <si>
     <t xml:space="preserve">1.75668585300446</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84295153617859</t>
+    <t xml:space="preserve">1.8429514169693</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84608864784241</t>
+    <t xml:space="preserve">1.8460887670517</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92921733856201</t>
+    <t xml:space="preserve">1.92921757698059</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88530051708221</t>
+    <t xml:space="preserve">1.88530075550079</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9009850025177</t>
+    <t xml:space="preserve">1.90098524093628</t>
   </si>
   <si>
     <t xml:space="preserve">1.91823828220367</t>
@@ -347,40 +347,40 @@
     <t xml:space="preserve">1.9496077299118</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93078601360321</t>
+    <t xml:space="preserve">1.93078577518463</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84922587871552</t>
+    <t xml:space="preserve">1.84922564029694</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82413029670715</t>
+    <t xml:space="preserve">1.82413017749786</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85549914836884</t>
+    <t xml:space="preserve">1.85549926757812</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89627981185913</t>
+    <t xml:space="preserve">1.89628005027771</t>
   </si>
   <si>
     <t xml:space="preserve">1.8743212223053</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94333362579346</t>
+    <t xml:space="preserve">1.94333374500275</t>
   </si>
   <si>
     <t xml:space="preserve">1.94490218162537</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96686065196991</t>
+    <t xml:space="preserve">1.9668607711792</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98411428928375</t>
+    <t xml:space="preserve">1.98411417007446</t>
   </si>
   <si>
     <t xml:space="preserve">2.0625376701355</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05312657356262</t>
+    <t xml:space="preserve">2.0531268119812</t>
   </si>
   <si>
     <t xml:space="preserve">2.05155801773071</t>
@@ -407,13 +407,13 @@
     <t xml:space="preserve">2.15507698059082</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18801474571228</t>
+    <t xml:space="preserve">2.18801498413086</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19585728645325</t>
+    <t xml:space="preserve">2.19585704803467</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20213103294373</t>
+    <t xml:space="preserve">2.20213150978088</t>
   </si>
   <si>
     <t xml:space="preserve">2.23350071907043</t>
@@ -431,7 +431,7 @@
     <t xml:space="preserve">2.1942892074585</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17389893531799</t>
+    <t xml:space="preserve">2.17389869689941</t>
   </si>
   <si>
     <t xml:space="preserve">2.20056295394897</t>
@@ -443,82 +443,82 @@
     <t xml:space="preserve">2.21781587600708</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19115209579468</t>
+    <t xml:space="preserve">2.1911518573761</t>
   </si>
   <si>
     <t xml:space="preserve">2.12057065963745</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15350890159607</t>
+    <t xml:space="preserve">2.15350866317749</t>
   </si>
   <si>
     <t xml:space="preserve">2.11743402481079</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16291952133179</t>
+    <t xml:space="preserve">2.16291928291321</t>
   </si>
   <si>
     <t xml:space="preserve">2.10802292823792</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01548314094543</t>
+    <t xml:space="preserve">2.01548337936401</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04528450965881</t>
+    <t xml:space="preserve">2.04528403282166</t>
   </si>
   <si>
     <t xml:space="preserve">1.98568248748779</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07822251319885</t>
+    <t xml:space="preserve">2.07822203636169</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06724286079407</t>
+    <t xml:space="preserve">2.06724262237549</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12998175621033</t>
+    <t xml:space="preserve">2.12998151779175</t>
   </si>
   <si>
     <t xml:space="preserve">2.11586546897888</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05469512939453</t>
+    <t xml:space="preserve">2.05469489097595</t>
   </si>
   <si>
     <t xml:space="preserve">2.11429691314697</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05626368522644</t>
+    <t xml:space="preserve">2.05626344680786</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06410574913025</t>
+    <t xml:space="preserve">2.06410598754883</t>
   </si>
   <si>
     <t xml:space="preserve">2.10488629341125</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00920963287354</t>
+    <t xml:space="preserve">2.00920987129211</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0139148235321</t>
+    <t xml:space="preserve">2.01391530036926</t>
   </si>
   <si>
     <t xml:space="preserve">2.04842114448547</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16448783874512</t>
+    <t xml:space="preserve">2.1644880771637</t>
   </si>
   <si>
     <t xml:space="preserve">2.18487811088562</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26643872261047</t>
+    <t xml:space="preserve">2.26643848419189</t>
   </si>
   <si>
     <t xml:space="preserve">2.27271270751953</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2570276260376</t>
+    <t xml:space="preserve">2.25702786445618</t>
   </si>
   <si>
     <t xml:space="preserve">2.30721879005432</t>
@@ -527,40 +527,40 @@
     <t xml:space="preserve">2.2303638458252</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37152576446533</t>
+    <t xml:space="preserve">2.37152624130249</t>
   </si>
   <si>
     <t xml:space="preserve">2.35270428657532</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39191603660583</t>
+    <t xml:space="preserve">2.39191627502441</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33545112609863</t>
+    <t xml:space="preserve">2.33545136451721</t>
   </si>
   <si>
     <t xml:space="preserve">2.3134925365448</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37623119354248</t>
+    <t xml:space="preserve">2.37623143196106</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32917737960815</t>
+    <t xml:space="preserve">2.32917714118958</t>
   </si>
   <si>
     <t xml:space="preserve">2.24918556213379</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28839683532715</t>
+    <t xml:space="preserve">2.28839707374573</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33701968193054</t>
+    <t xml:space="preserve">2.33701992034912</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34486222267151</t>
+    <t xml:space="preserve">2.34486198425293</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3495671749115</t>
+    <t xml:space="preserve">2.34956741333008</t>
   </si>
   <si>
     <t xml:space="preserve">2.32604050636292</t>
@@ -569,49 +569,49 @@
     <t xml:space="preserve">2.30251336097717</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31192374229431</t>
+    <t xml:space="preserve">2.31192421913147</t>
   </si>
   <si>
     <t xml:space="preserve">2.25075364112854</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27428078651428</t>
+    <t xml:space="preserve">2.27428126335144</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43897032737732</t>
+    <t xml:space="preserve">2.43897008895874</t>
   </si>
   <si>
     <t xml:space="preserve">2.48445606231689</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46249723434448</t>
+    <t xml:space="preserve">2.46249747276306</t>
   </si>
   <si>
     <t xml:space="preserve">2.50798273086548</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48602414131165</t>
+    <t xml:space="preserve">2.48602437973022</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60993313789368</t>
+    <t xml:space="preserve">2.60993361473083</t>
   </si>
   <si>
     <t xml:space="preserve">2.66639828681946</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66326141357422</t>
+    <t xml:space="preserve">2.66326093673706</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66012406349182</t>
+    <t xml:space="preserve">2.6601243019104</t>
   </si>
   <si>
     <t xml:space="preserve">2.64287114143372</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65855598449707</t>
+    <t xml:space="preserve">2.65855574607849</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60209107398987</t>
+    <t xml:space="preserve">2.60209131240845</t>
   </si>
   <si>
     <t xml:space="preserve">2.55033159255981</t>
@@ -620,43 +620,43 @@
     <t xml:space="preserve">2.63816595077515</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58013200759888</t>
+    <t xml:space="preserve">2.58013248443604</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59581708908081</t>
+    <t xml:space="preserve">2.59581685066223</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58170127868652</t>
+    <t xml:space="preserve">2.58170104026794</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60365962982178</t>
+    <t xml:space="preserve">2.6036593914032</t>
   </si>
   <si>
     <t xml:space="preserve">2.61934423446655</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57542681694031</t>
+    <t xml:space="preserve">2.57542705535889</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57385849952698</t>
+    <t xml:space="preserve">2.57385873794556</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50955128669739</t>
+    <t xml:space="preserve">2.50955152511597</t>
   </si>
   <si>
-    <t xml:space="preserve">2.587975025177</t>
+    <t xml:space="preserve">2.58797478675842</t>
   </si>
   <si>
     <t xml:space="preserve">2.56444787979126</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61150169372559</t>
+    <t xml:space="preserve">2.61150193214417</t>
   </si>
   <si>
     <t xml:space="preserve">2.56915330886841</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63502883911133</t>
+    <t xml:space="preserve">2.63502907752991</t>
   </si>
   <si>
     <t xml:space="preserve">2.62561821937561</t>
@@ -668,52 +668,52 @@
     <t xml:space="preserve">2.83422470092773</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79030728340149</t>
+    <t xml:space="preserve">2.79030752182007</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7761914730072</t>
+    <t xml:space="preserve">2.77619123458862</t>
   </si>
   <si>
     <t xml:space="preserve">2.78089642524719</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69149351119995</t>
+    <t xml:space="preserve">2.69149374961853</t>
   </si>
   <si>
     <t xml:space="preserve">2.78246521949768</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81226587295532</t>
+    <t xml:space="preserve">2.8122661113739</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82324504852295</t>
+    <t xml:space="preserve">2.82324552536011</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68678855895996</t>
+    <t xml:space="preserve">2.68678879737854</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70090484619141</t>
+    <t xml:space="preserve">2.70090460777283</t>
   </si>
   <si>
     <t xml:space="preserve">2.80657124519348</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86433935165405</t>
+    <t xml:space="preserve">2.86433959007263</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81940841674805</t>
+    <t xml:space="preserve">2.81940889358521</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80817627906799</t>
+    <t xml:space="preserve">2.80817580223083</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88038611412048</t>
+    <t xml:space="preserve">2.88038635253906</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83385109901428</t>
+    <t xml:space="preserve">2.8338508605957</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74398922920227</t>
+    <t xml:space="preserve">2.74398899078369</t>
   </si>
   <si>
     <t xml:space="preserve">2.72794246673584</t>
@@ -725,37 +725,37 @@
     <t xml:space="preserve">2.7327561378479</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67177867889404</t>
+    <t xml:space="preserve">2.67177891731262</t>
   </si>
   <si>
     <t xml:space="preserve">2.62363886833191</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61722016334534</t>
+    <t xml:space="preserve">2.61721992492676</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60438275337219</t>
+    <t xml:space="preserve">2.60438251495361</t>
   </si>
   <si>
     <t xml:space="preserve">2.62524342536926</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64129042625427</t>
+    <t xml:space="preserve">2.64128994941711</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6958487033844</t>
+    <t xml:space="preserve">2.69584894180298</t>
   </si>
   <si>
     <t xml:space="preserve">2.75040793418884</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74719834327698</t>
+    <t xml:space="preserve">2.74719858169556</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71991920471191</t>
+    <t xml:space="preserve">2.71991896629333</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72633790969849</t>
+    <t xml:space="preserve">2.72633767127991</t>
   </si>
   <si>
     <t xml:space="preserve">2.74238443374634</t>
@@ -764,43 +764,43 @@
     <t xml:space="preserve">2.80015254020691</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78571081161499</t>
+    <t xml:space="preserve">2.78571033477783</t>
   </si>
   <si>
     <t xml:space="preserve">2.82422280311584</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78731513023376</t>
+    <t xml:space="preserve">2.78731536865234</t>
   </si>
   <si>
     <t xml:space="preserve">2.79373383522034</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80496644973755</t>
+    <t xml:space="preserve">2.80496668815613</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78410601615906</t>
+    <t xml:space="preserve">2.78410577774048</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77608251571655</t>
+    <t xml:space="preserve">2.77608275413513</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79533886909485</t>
+    <t xml:space="preserve">2.79533863067627</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82261824607849</t>
+    <t xml:space="preserve">2.82261800765991</t>
   </si>
   <si>
     <t xml:space="preserve">2.7600359916687</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77929210662842</t>
+    <t xml:space="preserve">2.77929162979126</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79854774475098</t>
+    <t xml:space="preserve">2.79854822158813</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7744779586792</t>
+    <t xml:space="preserve">2.77447819709778</t>
   </si>
   <si>
     <t xml:space="preserve">2.80336213111877</t>
@@ -812,13 +812,13 @@
     <t xml:space="preserve">2.84026980400085</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83224582672119</t>
+    <t xml:space="preserve">2.83224606513977</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8113853931427</t>
+    <t xml:space="preserve">2.81138563156128</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81619954109192</t>
+    <t xml:space="preserve">2.81619930267334</t>
   </si>
   <si>
     <t xml:space="preserve">2.76324534416199</t>
@@ -827,10 +827,10 @@
     <t xml:space="preserve">2.71189594268799</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72473311424255</t>
+    <t xml:space="preserve">2.72473287582397</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7969434261322</t>
+    <t xml:space="preserve">2.79694318771362</t>
   </si>
   <si>
     <t xml:space="preserve">2.79052472114563</t>
@@ -839,43 +839,43 @@
     <t xml:space="preserve">2.76805925369263</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73115181922913</t>
+    <t xml:space="preserve">2.73115158081055</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70387244224548</t>
+    <t xml:space="preserve">2.7038722038269</t>
   </si>
   <si>
     <t xml:space="preserve">2.81459474563599</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82903695106506</t>
+    <t xml:space="preserve">2.82903671264648</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8434784412384</t>
+    <t xml:space="preserve">2.84347867965698</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77768707275391</t>
+    <t xml:space="preserve">2.77768731117249</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77126860618591</t>
+    <t xml:space="preserve">2.77126836776733</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88840937614441</t>
+    <t xml:space="preserve">2.88840985298157</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87236309051514</t>
+    <t xml:space="preserve">2.87236285209656</t>
   </si>
   <si>
     <t xml:space="preserve">2.89161920547485</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92852640151978</t>
+    <t xml:space="preserve">2.92852663993835</t>
   </si>
   <si>
     <t xml:space="preserve">2.85952544212341</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90927004814148</t>
+    <t xml:space="preserve">2.90927028656006</t>
   </si>
   <si>
     <t xml:space="preserve">2.99913215637207</t>
@@ -884,25 +884,25 @@
     <t xml:space="preserve">2.96864342689514</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83064150810242</t>
+    <t xml:space="preserve">2.830641746521</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87878155708313</t>
+    <t xml:space="preserve">2.87878179550171</t>
   </si>
   <si>
     <t xml:space="preserve">2.87717700004578</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87557244300842</t>
+    <t xml:space="preserve">2.875572681427</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75201272964478</t>
+    <t xml:space="preserve">2.7520124912262</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7616400718689</t>
+    <t xml:space="preserve">2.76164054870605</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78892016410828</t>
+    <t xml:space="preserve">2.7889199256897</t>
   </si>
   <si>
     <t xml:space="preserve">2.67980217933655</t>
@@ -914,10 +914,10 @@
     <t xml:space="preserve">2.82582759857178</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8482928276062</t>
+    <t xml:space="preserve">2.84829258918762</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82101345062256</t>
+    <t xml:space="preserve">2.82101321220398</t>
   </si>
   <si>
     <t xml:space="preserve">2.73436117172241</t>
@@ -926,46 +926,46 @@
     <t xml:space="preserve">2.81780409812927</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76485013961792</t>
+    <t xml:space="preserve">2.76484990119934</t>
   </si>
   <si>
     <t xml:space="preserve">2.74077963829041</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79212927818298</t>
+    <t xml:space="preserve">2.7921290397644</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6637556552887</t>
+    <t xml:space="preserve">2.66375541687012</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60759210586548</t>
+    <t xml:space="preserve">2.60759234428406</t>
   </si>
   <si>
     <t xml:space="preserve">2.55142855644226</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56747531890869</t>
+    <t xml:space="preserve">2.56747555732727</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59956836700439</t>
+    <t xml:space="preserve">2.59956860542297</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55945181846619</t>
+    <t xml:space="preserve">2.55945205688477</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50328826904297</t>
+    <t xml:space="preserve">2.50328850746155</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45514822006226</t>
+    <t xml:space="preserve">2.45514845848083</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47921800613403</t>
+    <t xml:space="preserve">2.47921824455261</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47119498252869</t>
+    <t xml:space="preserve">2.47119474411011</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43107795715332</t>
+    <t xml:space="preserve">2.4310781955719</t>
   </si>
   <si>
     <t xml:space="preserve">2.4631712436676</t>
@@ -977,19 +977,19 @@
     <t xml:space="preserve">2.49526500701904</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5273585319519</t>
+    <t xml:space="preserve">2.52735829353333</t>
   </si>
   <si>
     <t xml:space="preserve">2.58352208137512</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65573215484619</t>
+    <t xml:space="preserve">2.65573191642761</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9124801158905</t>
+    <t xml:space="preserve">2.91247963905334</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82002472877502</t>
+    <t xml:space="preserve">2.8200249671936</t>
   </si>
   <si>
     <t xml:space="preserve">2.80358147621155</t>
@@ -998,7 +998,7 @@
     <t xml:space="preserve">2.86935472488403</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84468960762024</t>
+    <t xml:space="preserve">2.8446900844574</t>
   </si>
   <si>
     <t xml:space="preserve">2.85291147232056</t>
@@ -1016,10 +1016,10 @@
     <t xml:space="preserve">2.69670009613037</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64737033843994</t>
+    <t xml:space="preserve">2.64737057685852</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65559220314026</t>
+    <t xml:space="preserve">2.6555917263031</t>
   </si>
   <si>
     <t xml:space="preserve">2.66381359100342</t>
@@ -1037,19 +1037,19 @@
     <t xml:space="preserve">2.59804034233093</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5487105846405</t>
+    <t xml:space="preserve">2.54871034622192</t>
   </si>
   <si>
     <t xml:space="preserve">2.46649384498596</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60626196861267</t>
+    <t xml:space="preserve">2.60626220703125</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52404546737671</t>
+    <t xml:space="preserve">2.52404522895813</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58159732818604</t>
+    <t xml:space="preserve">2.58159708976746</t>
   </si>
   <si>
     <t xml:space="preserve">2.61448383331299</t>
@@ -1058,19 +1058,19 @@
     <t xml:space="preserve">2.58981871604919</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62270522117615</t>
+    <t xml:space="preserve">2.62270545959473</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51582384109497</t>
+    <t xml:space="preserve">2.51582407951355</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57337546348572</t>
+    <t xml:space="preserve">2.57337594032288</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5651535987854</t>
+    <t xml:space="preserve">2.56515383720398</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53226733207703</t>
+    <t xml:space="preserve">2.53226709365845</t>
   </si>
   <si>
     <t xml:space="preserve">2.47471570968628</t>
@@ -1085,16 +1085,16 @@
     <t xml:space="preserve">2.44182920455933</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42538619041443</t>
+    <t xml:space="preserve">2.42538595199585</t>
   </si>
   <si>
     <t xml:space="preserve">2.43360757827759</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49115872383118</t>
+    <t xml:space="preserve">2.49115896224976</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50760197639465</t>
+    <t xml:space="preserve">2.50760245323181</t>
   </si>
   <si>
     <t xml:space="preserve">2.54048871994019</t>
@@ -1103,7 +1103,7 @@
     <t xml:space="preserve">2.67203521728516</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68847870826721</t>
+    <t xml:space="preserve">2.68847846984863</t>
   </si>
   <si>
     <t xml:space="preserve">2.70492172241211</t>
@@ -1118,10 +1118,10 @@
     <t xml:space="preserve">2.78713846206665</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77069473266602</t>
+    <t xml:space="preserve">2.77069497108459</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7295868396759</t>
+    <t xml:space="preserve">2.72958660125732</t>
   </si>
   <si>
     <t xml:space="preserve">2.74603009223938</t>
@@ -1130,10 +1130,10 @@
     <t xml:space="preserve">2.77891683578491</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79535984992981</t>
+    <t xml:space="preserve">2.79536008834839</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87757658958435</t>
+    <t xml:space="preserve">2.87757635116577</t>
   </si>
   <si>
     <t xml:space="preserve">2.91868448257446</t>
@@ -1142,16 +1142,16 @@
     <t xml:space="preserve">2.89401960372925</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86113309860229</t>
+    <t xml:space="preserve">2.86113286018372</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90224123001099</t>
+    <t xml:space="preserve">2.90224146842957</t>
   </si>
   <si>
     <t xml:space="preserve">2.88579821586609</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8364679813385</t>
+    <t xml:space="preserve">2.83646821975708</t>
   </si>
   <si>
     <t xml:space="preserve">2.94334959983826</t>
@@ -1160,7 +1160,7 @@
     <t xml:space="preserve">2.82824659347534</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92690634727478</t>
+    <t xml:space="preserve">2.9269061088562</t>
   </si>
   <si>
     <t xml:space="preserve">2.77809453010559</t>
@@ -1175,28 +1175,28 @@
     <t xml:space="preserve">2.88853859901428</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88004302978516</t>
+    <t xml:space="preserve">2.88004279136658</t>
   </si>
   <si>
     <t xml:space="preserve">2.92252135276794</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90553021430969</t>
+    <t xml:space="preserve">2.90552997589111</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87154722213745</t>
+    <t xml:space="preserve">2.87154746055603</t>
   </si>
   <si>
     <t xml:space="preserve">2.85455560684204</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91402554512024</t>
+    <t xml:space="preserve">2.91402578353882</t>
   </si>
   <si>
     <t xml:space="preserve">2.93101692199707</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9480082988739</t>
+    <t xml:space="preserve">2.94800877571106</t>
   </si>
   <si>
     <t xml:space="preserve">2.89703416824341</t>
@@ -1205,10 +1205,10 @@
     <t xml:space="preserve">2.93951272964478</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98199129104614</t>
+    <t xml:space="preserve">2.98199105262756</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79508566856384</t>
+    <t xml:space="preserve">2.79508590698242</t>
   </si>
   <si>
     <t xml:space="preserve">2.78659009933472</t>
@@ -1223,7 +1223,7 @@
     <t xml:space="preserve">2.81207704544067</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83756422996521</t>
+    <t xml:space="preserve">2.83756399154663</t>
   </si>
   <si>
     <t xml:space="preserve">2.86305141448975</t>
@@ -1232,16 +1232,13 @@
     <t xml:space="preserve">2.62517166137695</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67614603042603</t>
+    <t xml:space="preserve">2.6761462688446</t>
   </si>
   <si>
     <t xml:space="preserve">2.61667609214783</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55720615386963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54871034622192</t>
+    <t xml:space="preserve">2.55720639228821</t>
   </si>
   <si>
     <t xml:space="preserve">2.51472759246826</t>
@@ -1259,40 +1256,40 @@
     <t xml:space="preserve">2.46375346183777</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58269309997559</t>
+    <t xml:space="preserve">2.58269333839417</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5402147769928</t>
+    <t xml:space="preserve">2.54021453857422</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56570196151733</t>
+    <t xml:space="preserve">2.56570172309875</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59118866920471</t>
+    <t xml:space="preserve">2.59118890762329</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47224903106689</t>
+    <t xml:space="preserve">2.47224926948547</t>
   </si>
   <si>
     <t xml:space="preserve">2.63366746902466</t>
   </si>
   <si>
-    <t xml:space="preserve">2.599684715271</t>
+    <t xml:space="preserve">2.59968447685242</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52322363853455</t>
+    <t xml:space="preserve">2.52322316169739</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57419753074646</t>
+    <t xml:space="preserve">2.57419776916504</t>
   </si>
   <si>
     <t xml:space="preserve">3.075443983078</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00747847557068</t>
+    <t xml:space="preserve">3.0074782371521</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99048686027527</t>
+    <t xml:space="preserve">2.99048709869385</t>
   </si>
   <si>
     <t xml:space="preserve">2.96499991416931</t>
@@ -1307,7 +1304,7 @@
     <t xml:space="preserve">2.84606003761292</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75260734558105</t>
+    <t xml:space="preserve">2.75260758399963</t>
   </si>
   <si>
     <t xml:space="preserve">2.6676504611969</t>
@@ -1322,7 +1319,7 @@
     <t xml:space="preserve">2.3533091545105</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34481358528137</t>
+    <t xml:space="preserve">2.34481334686279</t>
   </si>
   <si>
     <t xml:space="preserve">2.45525789260864</t>
@@ -1331,25 +1328,25 @@
     <t xml:space="preserve">2.4892406463623</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65065860748291</t>
+    <t xml:space="preserve">2.65065884590149</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64216327667236</t>
+    <t xml:space="preserve">2.64216279983521</t>
   </si>
   <si>
     <t xml:space="preserve">2.71012878417969</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69313716888428</t>
+    <t xml:space="preserve">2.69313764572144</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71862459182739</t>
+    <t xml:space="preserve">2.71862435340881</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74411177635193</t>
+    <t xml:space="preserve">2.74411153793335</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68464183807373</t>
+    <t xml:space="preserve">2.68464159965515</t>
   </si>
   <si>
     <t xml:space="preserve">2.60818028450012</t>
@@ -1361,31 +1358,31 @@
     <t xml:space="preserve">2.44676208496094</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37879633903503</t>
+    <t xml:space="preserve">2.37879657745361</t>
   </si>
   <si>
     <t xml:space="preserve">2.42977046966553</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37030053138733</t>
+    <t xml:space="preserve">2.37030076980591</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31932663917542</t>
+    <t xml:space="preserve">2.31932640075684</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27684807777405</t>
+    <t xml:space="preserve">2.27684831619263</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26835227012634</t>
+    <t xml:space="preserve">2.26835250854492</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30233526229858</t>
+    <t xml:space="preserve">2.30233502388</t>
   </si>
   <si>
     <t xml:space="preserve">2.33631801605225</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39578795433044</t>
+    <t xml:space="preserve">2.39578771591187</t>
   </si>
   <si>
     <t xml:space="preserve">2.72712016105652</t>
@@ -1394,10 +1391,10 @@
     <t xml:space="preserve">2.99898242950439</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03296518325806</t>
+    <t xml:space="preserve">3.03296542167664</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0159740447998</t>
+    <t xml:space="preserve">3.01597380638123</t>
   </si>
   <si>
     <t xml:space="preserve">3.04146122932434</t>
@@ -1406,49 +1403,49 @@
     <t xml:space="preserve">3.1943838596344</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12641835212708</t>
+    <t xml:space="preserve">3.1264181137085</t>
   </si>
   <si>
     <t xml:space="preserve">3.05845236778259</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09243535995483</t>
+    <t xml:space="preserve">3.09243559837341</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16040086746216</t>
+    <t xml:space="preserve">3.16040110588074</t>
   </si>
   <si>
     <t xml:space="preserve">3.21137523651123</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3133237361908</t>
+    <t xml:space="preserve">3.31332349777222</t>
   </si>
   <si>
     <t xml:space="preserve">3.26234936714172</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33031511306763</t>
+    <t xml:space="preserve">3.33031535148621</t>
   </si>
   <si>
     <t xml:space="preserve">3.22836661338806</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17739248275757</t>
+    <t xml:space="preserve">3.17739224433899</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14340972900391</t>
+    <t xml:space="preserve">3.14340949058533</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10942697525024</t>
+    <t xml:space="preserve">3.10942673683167</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27934050559998</t>
+    <t xml:space="preserve">3.27934074401855</t>
   </si>
   <si>
-    <t xml:space="preserve">3.48323726654053</t>
+    <t xml:space="preserve">3.48323750495911</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39828062057495</t>
+    <t xml:space="preserve">3.39828038215637</t>
   </si>
   <si>
     <t xml:space="preserve">3.46624612808228</t>
@@ -1457,13 +1454,13 @@
     <t xml:space="preserve">3.36429786682129</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34730672836304</t>
+    <t xml:space="preserve">3.34730648994446</t>
   </si>
   <si>
     <t xml:space="preserve">3.24535799026489</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02446961402893</t>
+    <t xml:space="preserve">3.02446937561035</t>
   </si>
   <si>
     <t xml:space="preserve">3.16417121887207</t>
@@ -1475,7 +1472,7 @@
     <t xml:space="preserve">3.05899119377136</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01516604423523</t>
+    <t xml:space="preserve">3.01516628265381</t>
   </si>
   <si>
     <t xml:space="preserve">2.97134113311768</t>
@@ -1484,10 +1481,10 @@
     <t xml:space="preserve">3.02393102645874</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1028163433075</t>
+    <t xml:space="preserve">3.10281610488892</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13787603378296</t>
+    <t xml:space="preserve">3.13787627220154</t>
   </si>
   <si>
     <t xml:space="preserve">2.98010611534119</t>
@@ -1499,16 +1496,19 @@
     <t xml:space="preserve">3.07652115821838</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06775641441345</t>
+    <t xml:space="preserve">3.06775617599487</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00640106201172</t>
+    <t xml:space="preserve">3.04146146774292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0064013004303</t>
   </si>
   <si>
     <t xml:space="preserve">2.9888710975647</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89245557785034</t>
+    <t xml:space="preserve">2.89245581626892</t>
   </si>
   <si>
     <t xml:space="preserve">2.92751574516296</t>
@@ -1520,10 +1520,10 @@
     <t xml:space="preserve">2.96257615089417</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86616063117981</t>
+    <t xml:space="preserve">2.86616086959839</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91875100135803</t>
+    <t xml:space="preserve">2.91875076293945</t>
   </si>
   <si>
     <t xml:space="preserve">2.80480575561523</t>
@@ -1532,7 +1532,7 @@
     <t xml:space="preserve">2.82233572006226</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94504594802856</t>
+    <t xml:space="preserve">2.94504570960999</t>
   </si>
   <si>
     <t xml:space="preserve">2.95381093025208</t>
@@ -1547,13 +1547,13 @@
     <t xml:space="preserve">3.03269600868225</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90122103691101</t>
+    <t xml:space="preserve">2.90122079849243</t>
   </si>
   <si>
     <t xml:space="preserve">2.88369083404541</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87492561340332</t>
+    <t xml:space="preserve">2.8749258518219</t>
   </si>
   <si>
     <t xml:space="preserve">2.81357073783875</t>
@@ -1565,25 +1565,25 @@
     <t xml:space="preserve">2.68209528923035</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69086050987244</t>
+    <t xml:space="preserve">2.69086027145386</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66456532478333</t>
+    <t xml:space="preserve">2.6645655632019</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85739588737488</t>
+    <t xml:space="preserve">2.8573956489563</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90998578071594</t>
+    <t xml:space="preserve">2.90998601913452</t>
   </si>
   <si>
     <t xml:space="preserve">2.7785108089447</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76974582672119</t>
+    <t xml:space="preserve">2.76974558830261</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79604077339172</t>
+    <t xml:space="preserve">2.79604053497314</t>
   </si>
   <si>
     <t xml:space="preserve">2.84863066673279</t>
@@ -1592,7 +1592,7 @@
     <t xml:space="preserve">3.08528637886047</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76098036766052</t>
+    <t xml:space="preserve">2.7609806060791</t>
   </si>
   <si>
     <t xml:space="preserve">2.78727579116821</t>
@@ -1601,7 +1601,7 @@
     <t xml:space="preserve">2.75221562385559</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73468542098999</t>
+    <t xml:space="preserve">2.73468565940857</t>
   </si>
   <si>
     <t xml:space="preserve">2.86875891685486</t>
@@ -1619,34 +1619,34 @@
     <t xml:space="preserve">2.83221411705017</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8870313167572</t>
+    <t xml:space="preserve">2.88703107833862</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85048627853394</t>
+    <t xml:space="preserve">2.85048651695251</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96012043952942</t>
+    <t xml:space="preserve">2.960120677948</t>
   </si>
   <si>
     <t xml:space="preserve">2.99666523933411</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79566955566406</t>
+    <t xml:space="preserve">2.79566931724548</t>
   </si>
   <si>
     <t xml:space="preserve">2.81394171714783</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77739691734314</t>
+    <t xml:space="preserve">2.77739715576172</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75912475585938</t>
+    <t xml:space="preserve">2.7591245174408</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70430779457092</t>
+    <t xml:space="preserve">2.70430755615234</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64949083328247</t>
+    <t xml:space="preserve">2.64949059486389</t>
   </si>
   <si>
     <t xml:space="preserve">2.68603539466858</t>
@@ -1664,16 +1664,16 @@
     <t xml:space="preserve">2.72258019447327</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59467339515686</t>
+    <t xml:space="preserve">2.59467363357544</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5764012336731</t>
+    <t xml:space="preserve">2.57640099525452</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61294603347778</t>
+    <t xml:space="preserve">2.6129457950592</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97839307785034</t>
+    <t xml:space="preserve">2.97839283943176</t>
   </si>
   <si>
     <t xml:space="preserve">2.823077917099</t>
@@ -1697,7 +1697,7 @@
     <t xml:space="preserve">3.01493763923645</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96925687789917</t>
+    <t xml:space="preserve">2.96925663948059</t>
   </si>
   <si>
     <t xml:space="preserve">3.02674722671509</t>
@@ -1794,6 +1794,9 @@
   </si>
   <si>
     <t xml:space="preserve">3.23614478111267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96012043952942</t>
   </si>
   <si>
     <t xml:space="preserve">3.20000004768372</t>
@@ -1968,6 +1971,9 @@
   </si>
   <si>
     <t xml:space="preserve">3.83999991416931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8199999332428</t>
   </si>
 </sst>
 </file>
@@ -26166,7 +26172,7 @@
         <v>3</v>
       </c>
       <c r="G918" t="s">
-        <v>409</v>
+        <v>341</v>
       </c>
       <c r="H918" t="s">
         <v>9</v>
@@ -26192,7 +26198,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G919" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H919" t="s">
         <v>9</v>
@@ -26218,7 +26224,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G920" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H920" t="s">
         <v>9</v>
@@ -26244,7 +26250,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G921" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="H921" t="s">
         <v>9</v>
@@ -26270,7 +26276,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G922" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="H922" t="s">
         <v>9</v>
@@ -26322,7 +26328,7 @@
         <v>3</v>
       </c>
       <c r="G924" t="s">
-        <v>409</v>
+        <v>341</v>
       </c>
       <c r="H924" t="s">
         <v>9</v>
@@ -26348,7 +26354,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G925" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H925" t="s">
         <v>9</v>
@@ -26374,7 +26380,7 @@
         <v>3</v>
       </c>
       <c r="G926" t="s">
-        <v>409</v>
+        <v>341</v>
       </c>
       <c r="H926" t="s">
         <v>9</v>
@@ -26400,7 +26406,7 @@
         <v>3</v>
       </c>
       <c r="G927" t="s">
-        <v>409</v>
+        <v>341</v>
       </c>
       <c r="H927" t="s">
         <v>9</v>
@@ -26426,7 +26432,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G928" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H928" t="s">
         <v>9</v>
@@ -26452,7 +26458,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G929" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H929" t="s">
         <v>9</v>
@@ -26478,7 +26484,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G930" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H930" t="s">
         <v>9</v>
@@ -26504,7 +26510,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G931" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H931" t="s">
         <v>9</v>
@@ -26530,7 +26536,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G932" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H932" t="s">
         <v>9</v>
@@ -26556,7 +26562,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G933" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H933" t="s">
         <v>9</v>
@@ -26582,7 +26588,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G934" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H934" t="s">
         <v>9</v>
@@ -26608,7 +26614,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G935" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="H935" t="s">
         <v>9</v>
@@ -26686,7 +26692,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G938" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H938" t="s">
         <v>9</v>
@@ -26712,7 +26718,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G939" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H939" t="s">
         <v>9</v>
@@ -26738,7 +26744,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G940" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H940" t="s">
         <v>9</v>
@@ -26764,7 +26770,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G941" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="H941" t="s">
         <v>9</v>
@@ -26790,7 +26796,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G942" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H942" t="s">
         <v>9</v>
@@ -26816,7 +26822,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G943" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H943" t="s">
         <v>9</v>
@@ -26842,7 +26848,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G944" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H944" t="s">
         <v>9</v>
@@ -26868,7 +26874,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G945" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H945" t="s">
         <v>9</v>
@@ -26894,7 +26900,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G946" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="H946" t="s">
         <v>9</v>
@@ -26920,7 +26926,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G947" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H947" t="s">
         <v>9</v>
@@ -26946,7 +26952,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G948" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H948" t="s">
         <v>9</v>
@@ -26972,7 +26978,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G949" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H949" t="s">
         <v>9</v>
@@ -26998,7 +27004,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G950" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="H950" t="s">
         <v>9</v>
@@ -27024,7 +27030,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G951" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="H951" t="s">
         <v>9</v>
@@ -27050,7 +27056,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G952" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H952" t="s">
         <v>9</v>
@@ -27076,7 +27082,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G953" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H953" t="s">
         <v>9</v>
@@ -27102,7 +27108,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G954" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H954" t="s">
         <v>9</v>
@@ -27128,7 +27134,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G955" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H955" t="s">
         <v>9</v>
@@ -27154,7 +27160,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G956" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H956" t="s">
         <v>9</v>
@@ -27180,7 +27186,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G957" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H957" t="s">
         <v>9</v>
@@ -27206,7 +27212,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G958" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H958" t="s">
         <v>9</v>
@@ -27232,7 +27238,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G959" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H959" t="s">
         <v>9</v>
@@ -27258,7 +27264,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G960" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H960" t="s">
         <v>9</v>
@@ -27284,7 +27290,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G961" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H961" t="s">
         <v>9</v>
@@ -27310,7 +27316,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G962" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="H962" t="s">
         <v>9</v>
@@ -27336,7 +27342,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G963" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="H963" t="s">
         <v>9</v>
@@ -27440,7 +27446,7 @@
         <v>3</v>
       </c>
       <c r="G967" t="s">
-        <v>409</v>
+        <v>341</v>
       </c>
       <c r="H967" t="s">
         <v>9</v>
@@ -27466,7 +27472,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G968" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="H968" t="s">
         <v>9</v>
@@ -27492,7 +27498,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G969" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="H969" t="s">
         <v>9</v>
@@ -27518,7 +27524,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G970" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H970" t="s">
         <v>9</v>
@@ -27544,7 +27550,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G971" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H971" t="s">
         <v>9</v>
@@ -27570,7 +27576,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G972" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="H972" t="s">
         <v>9</v>
@@ -27700,7 +27706,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G977" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="H977" t="s">
         <v>9</v>
@@ -27726,7 +27732,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G978" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="H978" t="s">
         <v>9</v>
@@ -27752,7 +27758,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G979" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="H979" t="s">
         <v>9</v>
@@ -27778,7 +27784,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G980" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="H980" t="s">
         <v>9</v>
@@ -27804,7 +27810,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G981" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="H981" t="s">
         <v>9</v>
@@ -27882,7 +27888,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G984" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H984" t="s">
         <v>9</v>
@@ -27934,7 +27940,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G986" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="H986" t="s">
         <v>9</v>
@@ -27986,7 +27992,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G988" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="H988" t="s">
         <v>9</v>
@@ -28896,7 +28902,7 @@
         <v>3.5</v>
       </c>
       <c r="G1023" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="H1023" t="s">
         <v>9</v>
@@ -28922,7 +28928,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1024" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="H1024" t="s">
         <v>9</v>
@@ -29078,7 +29084,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1030" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="H1030" t="s">
         <v>9</v>
@@ -29104,7 +29110,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1031" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="H1031" t="s">
         <v>9</v>
@@ -29312,7 +29318,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G1039" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="H1039" t="s">
         <v>9</v>
@@ -29338,7 +29344,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1040" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="H1040" t="s">
         <v>9</v>
@@ -29364,7 +29370,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G1041" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="H1041" t="s">
         <v>9</v>
@@ -29390,7 +29396,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1042" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="H1042" t="s">
         <v>9</v>
@@ -29572,7 +29578,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G1049" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="H1049" t="s">
         <v>9</v>
@@ -29598,7 +29604,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1050" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="H1050" t="s">
         <v>9</v>
@@ -29858,7 +29864,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1060" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="H1060" t="s">
         <v>9</v>
@@ -29884,7 +29890,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G1061" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="H1061" t="s">
         <v>9</v>
@@ -29910,7 +29916,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G1062" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="H1062" t="s">
         <v>9</v>
@@ -29936,7 +29942,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G1063" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="H1063" t="s">
         <v>9</v>
@@ -29962,7 +29968,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G1064" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H1064" t="s">
         <v>9</v>
@@ -29988,7 +29994,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1065" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H1065" t="s">
         <v>9</v>
@@ -30014,7 +30020,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G1066" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="H1066" t="s">
         <v>9</v>
@@ -30040,7 +30046,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G1067" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="H1067" t="s">
         <v>9</v>
@@ -30066,7 +30072,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G1068" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="H1068" t="s">
         <v>9</v>
@@ -30092,7 +30098,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G1069" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="H1069" t="s">
         <v>9</v>
@@ -30118,7 +30124,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G1070" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="H1070" t="s">
         <v>9</v>
@@ -30144,7 +30150,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G1071" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="H1071" t="s">
         <v>9</v>
@@ -30170,7 +30176,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1072" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="H1072" t="s">
         <v>9</v>
@@ -30196,7 +30202,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1073" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="H1073" t="s">
         <v>9</v>
@@ -30222,7 +30228,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1074" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H1074" t="s">
         <v>9</v>
@@ -30248,7 +30254,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G1075" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="H1075" t="s">
         <v>9</v>
@@ -30274,7 +30280,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G1076" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H1076" t="s">
         <v>9</v>
@@ -30300,7 +30306,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G1077" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="H1077" t="s">
         <v>9</v>
@@ -30326,7 +30332,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G1078" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H1078" t="s">
         <v>9</v>
@@ -30352,7 +30358,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1079" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H1079" t="s">
         <v>9</v>
@@ -30404,7 +30410,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G1081" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="H1081" t="s">
         <v>9</v>
@@ -30430,7 +30436,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G1082" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H1082" t="s">
         <v>9</v>
@@ -30456,7 +30462,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1083" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H1083" t="s">
         <v>9</v>
@@ -30482,7 +30488,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G1084" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H1084" t="s">
         <v>9</v>
@@ -30508,7 +30514,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G1085" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H1085" t="s">
         <v>9</v>
@@ -30534,7 +30540,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G1086" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="H1086" t="s">
         <v>9</v>
@@ -30560,7 +30566,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G1087" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H1087" t="s">
         <v>9</v>
@@ -30586,7 +30592,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1088" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="H1088" t="s">
         <v>9</v>
@@ -30612,7 +30618,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G1089" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="H1089" t="s">
         <v>9</v>
@@ -30638,7 +30644,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G1090" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="H1090" t="s">
         <v>9</v>
@@ -30690,7 +30696,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G1092" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="H1092" t="s">
         <v>9</v>
@@ -30716,7 +30722,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G1093" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H1093" t="s">
         <v>9</v>
@@ -30768,7 +30774,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G1095" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="H1095" t="s">
         <v>9</v>
@@ -30794,7 +30800,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1096" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="H1096" t="s">
         <v>9</v>
@@ -30950,7 +30956,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G1102" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H1102" t="s">
         <v>9</v>
@@ -30976,7 +30982,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G1103" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="H1103" t="s">
         <v>9</v>
@@ -31002,7 +31008,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G1104" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="H1104" t="s">
         <v>9</v>
@@ -31028,7 +31034,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G1105" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="H1105" t="s">
         <v>9</v>
@@ -31054,7 +31060,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G1106" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="H1106" t="s">
         <v>9</v>
@@ -31080,7 +31086,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1107" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="H1107" t="s">
         <v>9</v>
@@ -31106,7 +31112,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1108" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H1108" t="s">
         <v>9</v>
@@ -31132,7 +31138,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G1109" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H1109" t="s">
         <v>9</v>
@@ -31158,7 +31164,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G1110" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="H1110" t="s">
         <v>9</v>
@@ -31184,7 +31190,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G1111" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="H1111" t="s">
         <v>9</v>
@@ -31210,7 +31216,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G1112" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="H1112" t="s">
         <v>9</v>
@@ -31262,7 +31268,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1114" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H1114" t="s">
         <v>9</v>
@@ -31288,7 +31294,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1115" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H1115" t="s">
         <v>9</v>
@@ -31314,7 +31320,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1116" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H1116" t="s">
         <v>9</v>
@@ -31340,7 +31346,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1117" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H1117" t="s">
         <v>9</v>
@@ -31366,7 +31372,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1118" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H1118" t="s">
         <v>9</v>
@@ -31392,7 +31398,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G1119" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="H1119" t="s">
         <v>9</v>
@@ -31418,7 +31424,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1120" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H1120" t="s">
         <v>9</v>
@@ -31444,7 +31450,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1121" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H1121" t="s">
         <v>9</v>
@@ -31470,7 +31476,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G1122" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="H1122" t="s">
         <v>9</v>
@@ -31496,7 +31502,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1123" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H1123" t="s">
         <v>9</v>
@@ -31522,7 +31528,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1124" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="H1124" t="s">
         <v>9</v>
@@ -31548,7 +31554,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G1125" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="H1125" t="s">
         <v>9</v>
@@ -31574,7 +31580,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1126" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="H1126" t="s">
         <v>9</v>
@@ -31626,7 +31632,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1128" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="H1128" t="s">
         <v>9</v>
@@ -31704,7 +31710,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G1131" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="H1131" t="s">
         <v>9</v>
@@ -31730,7 +31736,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G1132" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="H1132" t="s">
         <v>9</v>
@@ -31756,7 +31762,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1133" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="H1133" t="s">
         <v>9</v>
@@ -31782,7 +31788,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1134" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H1134" t="s">
         <v>9</v>
@@ -31808,7 +31814,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1135" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="H1135" t="s">
         <v>9</v>
@@ -31834,7 +31840,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1136" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="H1136" t="s">
         <v>9</v>
@@ -31912,7 +31918,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G1139" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H1139" t="s">
         <v>9</v>
@@ -31938,7 +31944,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G1140" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H1140" t="s">
         <v>9</v>
@@ -31964,7 +31970,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G1141" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H1141" t="s">
         <v>9</v>
@@ -31990,7 +31996,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G1142" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H1142" t="s">
         <v>9</v>
@@ -32016,7 +32022,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G1143" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="H1143" t="s">
         <v>9</v>
@@ -32042,7 +32048,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G1144" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H1144" t="s">
         <v>9</v>
@@ -32068,7 +32074,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G1145" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H1145" t="s">
         <v>9</v>
@@ -32094,7 +32100,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G1146" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H1146" t="s">
         <v>9</v>
@@ -32120,7 +32126,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G1147" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="H1147" t="s">
         <v>9</v>
@@ -32146,7 +32152,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G1148" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H1148" t="s">
         <v>9</v>
@@ -32172,7 +32178,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G1149" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H1149" t="s">
         <v>9</v>
@@ -32198,7 +32204,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G1150" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="H1150" t="s">
         <v>9</v>
@@ -32224,7 +32230,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G1151" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="H1151" t="s">
         <v>9</v>
@@ -32250,7 +32256,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1152" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="H1152" t="s">
         <v>9</v>
@@ -32276,7 +32282,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G1153" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="H1153" t="s">
         <v>9</v>
@@ -32302,7 +32308,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G1154" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="H1154" t="s">
         <v>9</v>
@@ -32328,7 +32334,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G1155" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="H1155" t="s">
         <v>9</v>
@@ -32354,7 +32360,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G1156" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H1156" t="s">
         <v>9</v>
@@ -32458,7 +32464,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G1160" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="H1160" t="s">
         <v>9</v>
@@ -32484,7 +32490,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G1161" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="H1161" t="s">
         <v>9</v>
@@ -32510,7 +32516,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G1162" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="H1162" t="s">
         <v>9</v>
@@ -32536,7 +32542,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G1163" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H1163" t="s">
         <v>9</v>
@@ -32562,7 +32568,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G1164" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H1164" t="s">
         <v>9</v>
@@ -32588,7 +32594,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G1165" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="H1165" t="s">
         <v>9</v>
@@ -32614,7 +32620,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G1166" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H1166" t="s">
         <v>9</v>
@@ -32640,7 +32646,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G1167" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H1167" t="s">
         <v>9</v>
@@ -32666,7 +32672,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G1168" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H1168" t="s">
         <v>9</v>
@@ -32692,7 +32698,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G1169" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H1169" t="s">
         <v>9</v>
@@ -32718,7 +32724,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1170" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H1170" t="s">
         <v>9</v>
@@ -32744,7 +32750,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G1171" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="H1171" t="s">
         <v>9</v>
@@ -32770,7 +32776,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1172" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H1172" t="s">
         <v>9</v>
@@ -32796,7 +32802,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G1173" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="H1173" t="s">
         <v>9</v>
@@ -32822,7 +32828,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G1174" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="H1174" t="s">
         <v>9</v>
@@ -32848,7 +32854,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G1175" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H1175" t="s">
         <v>9</v>
@@ -32874,7 +32880,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G1176" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H1176" t="s">
         <v>9</v>
@@ -32900,7 +32906,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G1177" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="H1177" t="s">
         <v>9</v>
@@ -32978,7 +32984,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G1180" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="H1180" t="s">
         <v>9</v>
@@ -33004,7 +33010,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G1181" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="H1181" t="s">
         <v>9</v>
@@ -33134,7 +33140,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G1186" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H1186" t="s">
         <v>9</v>
@@ -33160,7 +33166,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G1187" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="H1187" t="s">
         <v>9</v>
@@ -33186,7 +33192,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G1188" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="H1188" t="s">
         <v>9</v>
@@ -33238,7 +33244,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G1190" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H1190" t="s">
         <v>9</v>
@@ -33264,7 +33270,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G1191" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="H1191" t="s">
         <v>9</v>
@@ -33290,7 +33296,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G1192" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="H1192" t="s">
         <v>9</v>
@@ -33316,7 +33322,7 @@
         <v>3</v>
       </c>
       <c r="G1193" t="s">
-        <v>409</v>
+        <v>341</v>
       </c>
       <c r="H1193" t="s">
         <v>9</v>
@@ -33342,7 +33348,7 @@
         <v>3</v>
       </c>
       <c r="G1194" t="s">
-        <v>409</v>
+        <v>341</v>
       </c>
       <c r="H1194" t="s">
         <v>9</v>
@@ -33368,7 +33374,7 @@
         <v>3</v>
       </c>
       <c r="G1195" t="s">
-        <v>409</v>
+        <v>341</v>
       </c>
       <c r="H1195" t="s">
         <v>9</v>
@@ -33394,7 +33400,7 @@
         <v>3</v>
       </c>
       <c r="G1196" t="s">
-        <v>409</v>
+        <v>341</v>
       </c>
       <c r="H1196" t="s">
         <v>9</v>
@@ -33420,7 +33426,7 @@
         <v>3</v>
       </c>
       <c r="G1197" t="s">
-        <v>409</v>
+        <v>341</v>
       </c>
       <c r="H1197" t="s">
         <v>9</v>
@@ -33446,7 +33452,7 @@
         <v>3</v>
       </c>
       <c r="G1198" t="s">
-        <v>409</v>
+        <v>341</v>
       </c>
       <c r="H1198" t="s">
         <v>9</v>
@@ -33472,7 +33478,7 @@
         <v>3</v>
       </c>
       <c r="G1199" t="s">
-        <v>409</v>
+        <v>341</v>
       </c>
       <c r="H1199" t="s">
         <v>9</v>
@@ -33498,7 +33504,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G1200" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H1200" t="s">
         <v>9</v>
@@ -33524,7 +33530,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G1201" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H1201" t="s">
         <v>9</v>
@@ -33550,7 +33556,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G1202" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H1202" t="s">
         <v>9</v>
@@ -33576,7 +33582,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G1203" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H1203" t="s">
         <v>9</v>
@@ -33602,7 +33608,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G1204" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="H1204" t="s">
         <v>9</v>
@@ -33628,7 +33634,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G1205" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="H1205" t="s">
         <v>9</v>
@@ -33654,7 +33660,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G1206" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="H1206" t="s">
         <v>9</v>
@@ -33680,7 +33686,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G1207" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="H1207" t="s">
         <v>9</v>
@@ -33706,7 +33712,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G1208" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="H1208" t="s">
         <v>9</v>
@@ -33732,7 +33738,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G1209" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="H1209" t="s">
         <v>9</v>
@@ -33758,7 +33764,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G1210" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="H1210" t="s">
         <v>9</v>
@@ -33784,7 +33790,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G1211" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="H1211" t="s">
         <v>9</v>
@@ -33810,7 +33816,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G1212" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="H1212" t="s">
         <v>9</v>
@@ -33836,7 +33842,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G1213" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="H1213" t="s">
         <v>9</v>
@@ -33862,7 +33868,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1214" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H1214" t="s">
         <v>9</v>
@@ -33888,7 +33894,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1215" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H1215" t="s">
         <v>9</v>
@@ -33914,7 +33920,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G1216" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="H1216" t="s">
         <v>9</v>
@@ -33940,7 +33946,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G1217" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="H1217" t="s">
         <v>9</v>
@@ -33966,7 +33972,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G1218" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="H1218" t="s">
         <v>9</v>
@@ -33992,7 +33998,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G1219" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="H1219" t="s">
         <v>9</v>
@@ -34018,7 +34024,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G1220" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="H1220" t="s">
         <v>9</v>
@@ -34044,7 +34050,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G1221" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="H1221" t="s">
         <v>9</v>
@@ -34070,7 +34076,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G1222" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="H1222" t="s">
         <v>9</v>
@@ -34096,7 +34102,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G1223" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="H1223" t="s">
         <v>9</v>
@@ -34122,7 +34128,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G1224" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="H1224" t="s">
         <v>9</v>
@@ -34148,7 +34154,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G1225" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="H1225" t="s">
         <v>9</v>
@@ -34174,7 +34180,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G1226" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="H1226" t="s">
         <v>9</v>
@@ -34200,7 +34206,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G1227" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="H1227" t="s">
         <v>9</v>
@@ -34226,7 +34232,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G1228" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="H1228" t="s">
         <v>9</v>
@@ -34252,7 +34258,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G1229" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="H1229" t="s">
         <v>9</v>
@@ -34278,7 +34284,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G1230" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="H1230" t="s">
         <v>9</v>
@@ -34304,7 +34310,7 @@
         <v>2.75</v>
       </c>
       <c r="G1231" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="H1231" t="s">
         <v>9</v>
@@ -34330,7 +34336,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G1232" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="H1232" t="s">
         <v>9</v>
@@ -34356,7 +34362,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G1233" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="H1233" t="s">
         <v>9</v>
@@ -34382,7 +34388,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G1234" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H1234" t="s">
         <v>9</v>
@@ -34408,7 +34414,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G1235" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H1235" t="s">
         <v>9</v>
@@ -34434,7 +34440,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G1236" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H1236" t="s">
         <v>9</v>
@@ -34460,7 +34466,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G1237" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="H1237" t="s">
         <v>9</v>
@@ -34486,7 +34492,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G1238" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="H1238" t="s">
         <v>9</v>
@@ -34512,7 +34518,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G1239" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="H1239" t="s">
         <v>9</v>
@@ -34538,7 +34544,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G1240" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="H1240" t="s">
         <v>9</v>
@@ -34564,7 +34570,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G1241" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="H1241" t="s">
         <v>9</v>
@@ -34590,7 +34596,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G1242" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H1242" t="s">
         <v>9</v>
@@ -34616,7 +34622,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G1243" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H1243" t="s">
         <v>9</v>
@@ -34642,7 +34648,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G1244" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="H1244" t="s">
         <v>9</v>
@@ -34668,7 +34674,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G1245" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="H1245" t="s">
         <v>9</v>
@@ -34694,7 +34700,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G1246" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H1246" t="s">
         <v>9</v>
@@ -34720,7 +34726,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G1247" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="H1247" t="s">
         <v>9</v>
@@ -34746,7 +34752,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G1248" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="H1248" t="s">
         <v>9</v>
@@ -34772,7 +34778,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1249" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H1249" t="s">
         <v>9</v>
@@ -34798,7 +34804,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G1250" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="H1250" t="s">
         <v>9</v>
@@ -34824,7 +34830,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G1251" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="H1251" t="s">
         <v>9</v>
@@ -34850,7 +34856,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G1252" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H1252" t="s">
         <v>9</v>
@@ -34876,7 +34882,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G1253" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H1253" t="s">
         <v>9</v>
@@ -34902,7 +34908,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G1254" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H1254" t="s">
         <v>9</v>
@@ -34928,7 +34934,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G1255" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="H1255" t="s">
         <v>9</v>
@@ -34954,7 +34960,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G1256" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="H1256" t="s">
         <v>9</v>
@@ -34980,7 +34986,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G1257" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="H1257" t="s">
         <v>9</v>
@@ -35006,7 +35012,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1258" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="H1258" t="s">
         <v>9</v>
@@ -35058,7 +35064,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1260" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="H1260" t="s">
         <v>9</v>
@@ -35084,7 +35090,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1261" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="H1261" t="s">
         <v>9</v>
@@ -35110,7 +35116,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G1262" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H1262" t="s">
         <v>9</v>
@@ -35136,7 +35142,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1263" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="H1263" t="s">
         <v>9</v>
@@ -35214,7 +35220,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1266" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="H1266" t="s">
         <v>9</v>
@@ -35578,7 +35584,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1280" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="H1280" t="s">
         <v>9</v>
@@ -35604,7 +35610,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1281" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="H1281" t="s">
         <v>9</v>
@@ -35812,7 +35818,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G1289" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="H1289" t="s">
         <v>9</v>
@@ -35864,7 +35870,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G1291" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="H1291" t="s">
         <v>9</v>
@@ -36046,7 +36052,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1298" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="H1298" t="s">
         <v>9</v>
@@ -36072,7 +36078,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1299" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="H1299" t="s">
         <v>9</v>
@@ -36124,7 +36130,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G1301" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="H1301" t="s">
         <v>9</v>
@@ -36176,7 +36182,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G1303" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="H1303" t="s">
         <v>9</v>
@@ -36202,7 +36208,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1304" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="H1304" t="s">
         <v>9</v>
@@ -36332,7 +36338,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G1309" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="H1309" t="s">
         <v>9</v>
@@ -36358,7 +36364,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G1310" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H1310" t="s">
         <v>9</v>
@@ -36488,7 +36494,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G1315" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="H1315" t="s">
         <v>9</v>
@@ -36514,7 +36520,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G1316" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="H1316" t="s">
         <v>9</v>
@@ -36566,7 +36572,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1318" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="H1318" t="s">
         <v>9</v>
@@ -36592,7 +36598,7 @@
         <v>3.5</v>
       </c>
       <c r="G1319" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="H1319" t="s">
         <v>9</v>
@@ -36618,7 +36624,7 @@
         <v>3.5</v>
       </c>
       <c r="G1320" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="H1320" t="s">
         <v>9</v>
@@ -36644,7 +36650,7 @@
         <v>3.5</v>
       </c>
       <c r="G1321" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="H1321" t="s">
         <v>9</v>
@@ -36670,7 +36676,7 @@
         <v>3.5</v>
       </c>
       <c r="G1322" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="H1322" t="s">
         <v>9</v>
@@ -36696,7 +36702,7 @@
         <v>3.5</v>
       </c>
       <c r="G1323" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="H1323" t="s">
         <v>9</v>
@@ -36722,7 +36728,7 @@
         <v>3.5</v>
       </c>
       <c r="G1324" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="H1324" t="s">
         <v>9</v>
@@ -36852,7 +36858,7 @@
         <v>3.5</v>
       </c>
       <c r="G1329" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="H1329" t="s">
         <v>9</v>
@@ -36904,7 +36910,7 @@
         <v>3.5</v>
       </c>
       <c r="G1331" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="H1331" t="s">
         <v>9</v>
@@ -37008,7 +37014,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G1335" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H1335" t="s">
         <v>9</v>
@@ -37034,7 +37040,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1336" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="H1336" t="s">
         <v>9</v>
@@ -37060,7 +37066,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G1337" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H1337" t="s">
         <v>9</v>
@@ -37086,7 +37092,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G1338" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H1338" t="s">
         <v>9</v>
@@ -37112,7 +37118,7 @@
         <v>3.5</v>
       </c>
       <c r="G1339" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="H1339" t="s">
         <v>9</v>
@@ -37138,7 +37144,7 @@
         <v>3.5</v>
       </c>
       <c r="G1340" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="H1340" t="s">
         <v>9</v>
@@ -37190,7 +37196,7 @@
         <v>3.5</v>
       </c>
       <c r="G1342" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="H1342" t="s">
         <v>9</v>
@@ -37216,7 +37222,7 @@
         <v>3.5</v>
       </c>
       <c r="G1343" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="H1343" t="s">
         <v>9</v>
@@ -37242,7 +37248,7 @@
         <v>3.5</v>
       </c>
       <c r="G1344" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="H1344" t="s">
         <v>9</v>
@@ -37268,7 +37274,7 @@
         <v>3.5</v>
       </c>
       <c r="G1345" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="H1345" t="s">
         <v>9</v>
@@ -37294,7 +37300,7 @@
         <v>3.5</v>
       </c>
       <c r="G1346" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="H1346" t="s">
         <v>9</v>
@@ -37320,7 +37326,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1347" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="H1347" t="s">
         <v>9</v>
@@ -37346,7 +37352,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1348" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="H1348" t="s">
         <v>9</v>
@@ -37372,7 +37378,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1349" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="H1349" t="s">
         <v>9</v>
@@ -37502,7 +37508,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G1354" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="H1354" t="s">
         <v>9</v>
@@ -37528,7 +37534,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1355" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="H1355" t="s">
         <v>9</v>
@@ -37554,7 +37560,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1356" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="H1356" t="s">
         <v>9</v>
@@ -37580,7 +37586,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1357" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="H1357" t="s">
         <v>9</v>
@@ -37606,7 +37612,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G1358" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H1358" t="s">
         <v>9</v>
@@ -37632,7 +37638,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1359" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="H1359" t="s">
         <v>9</v>
@@ -37658,7 +37664,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1360" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="H1360" t="s">
         <v>9</v>
@@ -37866,7 +37872,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1368" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="H1368" t="s">
         <v>9</v>
@@ -37892,7 +37898,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1369" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="H1369" t="s">
         <v>9</v>
@@ -38022,7 +38028,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1374" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="H1374" t="s">
         <v>9</v>
@@ -38048,7 +38054,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1375" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="H1375" t="s">
         <v>9</v>
@@ -38100,7 +38106,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G1377" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H1377" t="s">
         <v>9</v>
@@ -38152,7 +38158,7 @@
         <v>3.5</v>
       </c>
       <c r="G1379" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="H1379" t="s">
         <v>9</v>
@@ -38204,7 +38210,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1381" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="H1381" t="s">
         <v>9</v>
@@ -38282,7 +38288,7 @@
         <v>3.5</v>
       </c>
       <c r="G1384" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="H1384" t="s">
         <v>9</v>
@@ -38334,7 +38340,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1386" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="H1386" t="s">
         <v>9</v>
@@ -38386,7 +38392,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1388" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="H1388" t="s">
         <v>9</v>
@@ -38412,7 +38418,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1389" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="H1389" t="s">
         <v>9</v>
@@ -39088,7 +39094,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1415" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="H1415" t="s">
         <v>9</v>
@@ -39192,7 +39198,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1419" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="H1419" t="s">
         <v>9</v>
@@ -39244,7 +39250,7 @@
         <v>3.5</v>
       </c>
       <c r="G1421" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="H1421" t="s">
         <v>9</v>
@@ -39270,7 +39276,7 @@
         <v>3.5</v>
       </c>
       <c r="G1422" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="H1422" t="s">
         <v>9</v>
@@ -39348,7 +39354,7 @@
         <v>3.5</v>
       </c>
       <c r="G1425" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="H1425" t="s">
         <v>9</v>
@@ -39374,7 +39380,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1426" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="H1426" t="s">
         <v>9</v>
@@ -39400,7 +39406,7 @@
         <v>3.5</v>
       </c>
       <c r="G1427" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="H1427" t="s">
         <v>9</v>
@@ -39426,7 +39432,7 @@
         <v>3.5</v>
       </c>
       <c r="G1428" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="H1428" t="s">
         <v>9</v>
@@ -39452,7 +39458,7 @@
         <v>3.5</v>
       </c>
       <c r="G1429" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="H1429" t="s">
         <v>9</v>
@@ -39478,7 +39484,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1430" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="H1430" t="s">
         <v>9</v>
@@ -39504,7 +39510,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1431" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="H1431" t="s">
         <v>9</v>
@@ -39582,7 +39588,7 @@
         <v>3.5</v>
       </c>
       <c r="G1434" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="H1434" t="s">
         <v>9</v>
@@ -39608,7 +39614,7 @@
         <v>3.5</v>
       </c>
       <c r="G1435" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="H1435" t="s">
         <v>9</v>
@@ -39634,7 +39640,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1436" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="H1436" t="s">
         <v>9</v>
@@ -39660,7 +39666,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1437" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="H1437" t="s">
         <v>9</v>
@@ -39686,7 +39692,7 @@
         <v>3.5</v>
       </c>
       <c r="G1438" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="H1438" t="s">
         <v>9</v>
@@ -39712,7 +39718,7 @@
         <v>3.5</v>
       </c>
       <c r="G1439" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="H1439" t="s">
         <v>9</v>
@@ -39738,7 +39744,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1440" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="H1440" t="s">
         <v>9</v>
@@ -39764,7 +39770,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1441" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="H1441" t="s">
         <v>9</v>
@@ -39790,7 +39796,7 @@
         <v>3.5</v>
       </c>
       <c r="G1442" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="H1442" t="s">
         <v>9</v>
@@ -39894,7 +39900,7 @@
         <v>3.5</v>
       </c>
       <c r="G1446" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="H1446" t="s">
         <v>9</v>
@@ -39920,7 +39926,7 @@
         <v>3.5</v>
       </c>
       <c r="G1447" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="H1447" t="s">
         <v>9</v>
@@ -39972,7 +39978,7 @@
         <v>3.5</v>
       </c>
       <c r="G1449" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="H1449" t="s">
         <v>9</v>
@@ -39998,7 +40004,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1450" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="H1450" t="s">
         <v>9</v>
@@ -40024,7 +40030,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1451" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="H1451" t="s">
         <v>9</v>
@@ -40154,7 +40160,7 @@
         <v>3.5</v>
       </c>
       <c r="G1456" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="H1456" t="s">
         <v>9</v>
@@ -40180,7 +40186,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G1457" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="H1457" t="s">
         <v>9</v>
@@ -40206,7 +40212,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G1458" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="H1458" t="s">
         <v>9</v>
@@ -40232,7 +40238,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1459" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="H1459" t="s">
         <v>9</v>
@@ -40258,7 +40264,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G1460" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="H1460" t="s">
         <v>9</v>
@@ -40284,7 +40290,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1461" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="H1461" t="s">
         <v>9</v>
@@ -40310,7 +40316,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1462" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="H1462" t="s">
         <v>9</v>
@@ -40336,7 +40342,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G1463" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="H1463" t="s">
         <v>9</v>
@@ -40362,7 +40368,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G1464" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="H1464" t="s">
         <v>9</v>
@@ -40388,7 +40394,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1465" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="H1465" t="s">
         <v>9</v>
@@ -40414,7 +40420,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G1466" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="H1466" t="s">
         <v>9</v>
@@ -40440,7 +40446,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G1467" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="H1467" t="s">
         <v>9</v>
@@ -40466,7 +40472,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G1468" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="H1468" t="s">
         <v>9</v>
@@ -40492,7 +40498,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G1469" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="H1469" t="s">
         <v>9</v>
@@ -40518,7 +40524,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G1470" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H1470" t="s">
         <v>9</v>
@@ -40544,7 +40550,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1471" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="H1471" t="s">
         <v>9</v>
@@ -40570,7 +40576,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G1472" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H1472" t="s">
         <v>9</v>
@@ -40596,7 +40602,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1473" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H1473" t="s">
         <v>9</v>
@@ -40622,7 +40628,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G1474" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H1474" t="s">
         <v>9</v>
@@ -40648,7 +40654,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G1475" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1475" t="s">
         <v>9</v>
@@ -40674,7 +40680,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1476" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H1476" t="s">
         <v>9</v>
@@ -40700,7 +40706,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1477" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="H1477" t="s">
         <v>9</v>
@@ -40726,7 +40732,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1478" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="H1478" t="s">
         <v>9</v>
@@ -40752,7 +40758,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1479" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H1479" t="s">
         <v>9</v>
@@ -40778,7 +40784,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1480" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="H1480" t="s">
         <v>9</v>
@@ -40804,7 +40810,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G1481" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H1481" t="s">
         <v>9</v>
@@ -40830,7 +40836,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1482" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="H1482" t="s">
         <v>9</v>
@@ -40856,7 +40862,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G1483" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="H1483" t="s">
         <v>9</v>
@@ -40882,7 +40888,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G1484" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H1484" t="s">
         <v>9</v>
@@ -40908,7 +40914,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1485" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="H1485" t="s">
         <v>9</v>
@@ -40934,7 +40940,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1486" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="H1486" t="s">
         <v>9</v>
@@ -40960,7 +40966,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1487" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="H1487" t="s">
         <v>9</v>
@@ -40986,7 +40992,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G1488" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H1488" t="s">
         <v>9</v>
@@ -41012,7 +41018,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G1489" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="H1489" t="s">
         <v>9</v>
@@ -41038,7 +41044,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1490" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="H1490" t="s">
         <v>9</v>
@@ -41064,7 +41070,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1491" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="H1491" t="s">
         <v>9</v>
@@ -41090,7 +41096,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1492" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="H1492" t="s">
         <v>9</v>
@@ -41116,7 +41122,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G1493" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="H1493" t="s">
         <v>9</v>
@@ -41142,7 +41148,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1494" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="H1494" t="s">
         <v>9</v>
@@ -41168,7 +41174,7 @@
         <v>4</v>
       </c>
       <c r="G1495" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="H1495" t="s">
         <v>9</v>
@@ -41194,7 +41200,7 @@
         <v>4</v>
       </c>
       <c r="G1496" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="H1496" t="s">
         <v>9</v>
@@ -41220,7 +41226,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G1497" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="H1497" t="s">
         <v>9</v>
@@ -41246,7 +41252,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G1498" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="H1498" t="s">
         <v>9</v>
@@ -41272,7 +41278,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G1499" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="H1499" t="s">
         <v>9</v>
@@ -41298,7 +41304,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G1500" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H1500" t="s">
         <v>9</v>
@@ -41324,7 +41330,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1501" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="H1501" t="s">
         <v>9</v>
@@ -41350,7 +41356,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1502" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="H1502" t="s">
         <v>9</v>
@@ -41376,7 +41382,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1503" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="H1503" t="s">
         <v>9</v>
@@ -41402,7 +41408,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1504" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="H1504" t="s">
         <v>9</v>
@@ -41428,7 +41434,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1505" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="H1505" t="s">
         <v>9</v>
@@ -41454,7 +41460,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1506" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="H1506" t="s">
         <v>9</v>
@@ -41480,7 +41486,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1507" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="H1507" t="s">
         <v>9</v>
@@ -41506,7 +41512,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G1508" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H1508" t="s">
         <v>9</v>
@@ -41532,7 +41538,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G1509" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H1509" t="s">
         <v>9</v>
@@ -41558,7 +41564,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1510" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="H1510" t="s">
         <v>9</v>
@@ -41584,7 +41590,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1511" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="H1511" t="s">
         <v>9</v>
@@ -41610,7 +41616,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1512" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="H1512" t="s">
         <v>9</v>
@@ -41636,7 +41642,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1513" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="H1513" t="s">
         <v>9</v>
@@ -41662,7 +41668,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1514" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="H1514" t="s">
         <v>9</v>
@@ -41688,7 +41694,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G1515" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H1515" t="s">
         <v>9</v>
@@ -41714,7 +41720,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1516" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="H1516" t="s">
         <v>9</v>
@@ -41740,7 +41746,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G1517" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="H1517" t="s">
         <v>9</v>
@@ -41766,7 +41772,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1518" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="H1518" t="s">
         <v>9</v>
@@ -41792,7 +41798,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G1519" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H1519" t="s">
         <v>9</v>
@@ -41818,7 +41824,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G1520" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H1520" t="s">
         <v>9</v>
@@ -41844,7 +41850,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1521" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="H1521" t="s">
         <v>9</v>
@@ -41870,7 +41876,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1522" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="H1522" t="s">
         <v>9</v>
@@ -41896,7 +41902,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G1523" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="H1523" t="s">
         <v>9</v>
@@ -41922,7 +41928,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1524" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="H1524" t="s">
         <v>9</v>
@@ -41948,7 +41954,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1525" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="H1525" t="s">
         <v>9</v>
@@ -41974,7 +41980,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G1526" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H1526" t="s">
         <v>9</v>
@@ -42000,7 +42006,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1527" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="H1527" t="s">
         <v>9</v>
@@ -42026,7 +42032,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G1528" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H1528" t="s">
         <v>9</v>
@@ -42052,7 +42058,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1529" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="H1529" t="s">
         <v>9</v>
@@ -42078,7 +42084,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G1530" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="H1530" t="s">
         <v>9</v>
@@ -42104,7 +42110,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1531" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="H1531" t="s">
         <v>9</v>
@@ -42130,7 +42136,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1532" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="H1532" t="s">
         <v>9</v>
@@ -42156,7 +42162,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1533" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="H1533" t="s">
         <v>9</v>
@@ -42182,7 +42188,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1534" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="H1534" t="s">
         <v>9</v>
@@ -42208,7 +42214,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1535" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="H1535" t="s">
         <v>9</v>
@@ -42234,7 +42240,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G1536" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="H1536" t="s">
         <v>9</v>
@@ -42260,7 +42266,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G1537" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H1537" t="s">
         <v>9</v>
@@ -42286,7 +42292,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1538" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="H1538" t="s">
         <v>9</v>
@@ -42312,7 +42318,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1539" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="H1539" t="s">
         <v>9</v>
@@ -42338,7 +42344,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G1540" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="H1540" t="s">
         <v>9</v>
@@ -42364,7 +42370,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1541" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="H1541" t="s">
         <v>9</v>
@@ -42390,7 +42396,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G1542" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="H1542" t="s">
         <v>9</v>
@@ -42416,7 +42422,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G1543" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="H1543" t="s">
         <v>9</v>
@@ -42442,7 +42448,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1544" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="H1544" t="s">
         <v>9</v>
@@ -42468,7 +42474,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1545" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="H1545" t="s">
         <v>9</v>
@@ -42494,7 +42500,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1546" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="H1546" t="s">
         <v>9</v>
@@ -42520,7 +42526,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G1547" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="H1547" t="s">
         <v>9</v>
@@ -42546,7 +42552,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1548" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="H1548" t="s">
         <v>9</v>
@@ -42572,7 +42578,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1549" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="H1549" t="s">
         <v>9</v>
@@ -42598,7 +42604,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1550" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="H1550" t="s">
         <v>9</v>
@@ -42624,7 +42630,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G1551" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H1551" t="s">
         <v>9</v>
@@ -42650,7 +42656,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G1552" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="H1552" t="s">
         <v>9</v>
@@ -42676,7 +42682,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G1553" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="H1553" t="s">
         <v>9</v>
@@ -42702,7 +42708,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G1554" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H1554" t="s">
         <v>9</v>
@@ -42728,7 +42734,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G1555" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="H1555" t="s">
         <v>9</v>
@@ -42754,7 +42760,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1556" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="H1556" t="s">
         <v>9</v>
@@ -42780,7 +42786,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1557" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="H1557" t="s">
         <v>9</v>
@@ -42806,7 +42812,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G1558" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H1558" t="s">
         <v>9</v>
@@ -42832,7 +42838,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G1559" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H1559" t="s">
         <v>9</v>
@@ -42858,7 +42864,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G1560" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H1560" t="s">
         <v>9</v>
@@ -42884,7 +42890,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G1561" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H1561" t="s">
         <v>9</v>
@@ -42910,7 +42916,7 @@
         <v>3.5</v>
       </c>
       <c r="G1562" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="H1562" t="s">
         <v>9</v>
@@ -42936,7 +42942,7 @@
         <v>3.5</v>
       </c>
       <c r="G1563" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="H1563" t="s">
         <v>9</v>
@@ -43222,7 +43228,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1574" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="H1574" t="s">
         <v>9</v>
@@ -43352,7 +43358,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1579" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="H1579" t="s">
         <v>9</v>
@@ -43404,7 +43410,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1581" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="H1581" t="s">
         <v>9</v>
@@ -43430,7 +43436,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G1582" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="H1582" t="s">
         <v>9</v>
@@ -43456,7 +43462,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G1583" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="H1583" t="s">
         <v>9</v>
@@ -43482,7 +43488,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G1584" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H1584" t="s">
         <v>9</v>
@@ -43508,7 +43514,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G1585" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="H1585" t="s">
         <v>9</v>
@@ -43534,7 +43540,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1586" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="H1586" t="s">
         <v>9</v>
@@ -43560,7 +43566,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G1587" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="H1587" t="s">
         <v>9</v>
@@ -43586,7 +43592,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1588" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="H1588" t="s">
         <v>9</v>
@@ -43612,7 +43618,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G1589" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="H1589" t="s">
         <v>9</v>
@@ -43638,7 +43644,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1590" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="H1590" t="s">
         <v>9</v>
@@ -43664,7 +43670,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G1591" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="H1591" t="s">
         <v>9</v>
@@ -43690,7 +43696,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G1592" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="H1592" t="s">
         <v>9</v>
@@ -43716,7 +43722,7 @@
         <v>3.5</v>
       </c>
       <c r="G1593" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="H1593" t="s">
         <v>9</v>
@@ -43742,7 +43748,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1594" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="H1594" t="s">
         <v>9</v>
@@ -43768,7 +43774,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1595" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="H1595" t="s">
         <v>9</v>
@@ -43794,7 +43800,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1596" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="H1596" t="s">
         <v>9</v>
@@ -43820,7 +43826,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G1597" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="H1597" t="s">
         <v>9</v>
@@ -43846,7 +43852,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1598" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="H1598" t="s">
         <v>9</v>
@@ -43872,7 +43878,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1599" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="H1599" t="s">
         <v>9</v>
@@ -43898,7 +43904,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G1600" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="H1600" t="s">
         <v>9</v>
@@ -43924,7 +43930,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G1601" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="H1601" t="s">
         <v>9</v>
@@ -43950,7 +43956,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G1602" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="H1602" t="s">
         <v>9</v>
@@ -43976,7 +43982,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G1603" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="H1603" t="s">
         <v>9</v>
@@ -44002,7 +44008,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G1604" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="H1604" t="s">
         <v>9</v>
@@ -44028,7 +44034,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G1605" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="H1605" t="s">
         <v>9</v>
@@ -44054,7 +44060,7 @@
         <v>3.5</v>
       </c>
       <c r="G1606" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="H1606" t="s">
         <v>9</v>
@@ -44080,7 +44086,7 @@
         <v>3.5</v>
       </c>
       <c r="G1607" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="H1607" t="s">
         <v>9</v>
@@ -44106,7 +44112,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G1608" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="H1608" t="s">
         <v>9</v>
@@ -44132,7 +44138,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G1609" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H1609" t="s">
         <v>9</v>
@@ -44184,7 +44190,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G1611" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="H1611" t="s">
         <v>9</v>
@@ -44236,7 +44242,7 @@
         <v>3.5</v>
       </c>
       <c r="G1613" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="H1613" t="s">
         <v>9</v>
@@ -44288,7 +44294,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1615" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="H1615" t="s">
         <v>9</v>
@@ -44314,7 +44320,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1616" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="H1616" t="s">
         <v>9</v>
@@ -44340,7 +44346,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1617" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="H1617" t="s">
         <v>9</v>
@@ -44470,7 +44476,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G1622" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="H1622" t="s">
         <v>9</v>
@@ -44496,7 +44502,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G1623" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="H1623" t="s">
         <v>9</v>
@@ -44522,7 +44528,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G1624" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="H1624" t="s">
         <v>9</v>
@@ -44548,7 +44554,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G1625" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="H1625" t="s">
         <v>9</v>
@@ -44574,7 +44580,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1626" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="H1626" t="s">
         <v>9</v>
@@ -44600,7 +44606,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G1627" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="H1627" t="s">
         <v>9</v>
@@ -44626,7 +44632,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1628" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="H1628" t="s">
         <v>9</v>
@@ -44652,7 +44658,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G1629" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="H1629" t="s">
         <v>9</v>
@@ -44678,7 +44684,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G1630" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="H1630" t="s">
         <v>9</v>
@@ -44704,7 +44710,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G1631" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="H1631" t="s">
         <v>9</v>
@@ -44730,7 +44736,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G1632" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="H1632" t="s">
         <v>9</v>
@@ -44756,7 +44762,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1633" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="H1633" t="s">
         <v>9</v>
@@ -44782,7 +44788,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1634" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="H1634" t="s">
         <v>9</v>
@@ -44808,7 +44814,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G1635" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="H1635" t="s">
         <v>9</v>
@@ -44834,7 +44840,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G1636" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="H1636" t="s">
         <v>9</v>
@@ -44860,7 +44866,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G1637" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="H1637" t="s">
         <v>9</v>
@@ -44886,7 +44892,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1638" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="H1638" t="s">
         <v>9</v>
@@ -44912,7 +44918,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1639" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="H1639" t="s">
         <v>9</v>
@@ -44938,7 +44944,7 @@
         <v>3.5</v>
       </c>
       <c r="G1640" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="H1640" t="s">
         <v>9</v>
@@ -44964,7 +44970,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G1641" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="H1641" t="s">
         <v>9</v>
@@ -44990,7 +44996,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G1642" t="s">
-        <v>462</v>
+        <v>495</v>
       </c>
       <c r="H1642" t="s">
         <v>9</v>
@@ -45016,7 +45022,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G1643" t="s">
-        <v>462</v>
+        <v>495</v>
       </c>
       <c r="H1643" t="s">
         <v>9</v>
@@ -45068,7 +45074,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1645" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="H1645" t="s">
         <v>9</v>
@@ -45172,7 +45178,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1649" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="H1649" t="s">
         <v>9</v>
@@ -45406,7 +45412,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1658" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="H1658" t="s">
         <v>9</v>
@@ -46030,7 +46036,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G1682" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="H1682" t="s">
         <v>9</v>
@@ -46108,7 +46114,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G1685" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="H1685" t="s">
         <v>9</v>
@@ -46134,7 +46140,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G1686" t="s">
-        <v>462</v>
+        <v>495</v>
       </c>
       <c r="H1686" t="s">
         <v>9</v>
@@ -46160,7 +46166,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G1687" t="s">
-        <v>462</v>
+        <v>495</v>
       </c>
       <c r="H1687" t="s">
         <v>9</v>
@@ -46186,7 +46192,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G1688" t="s">
-        <v>462</v>
+        <v>495</v>
       </c>
       <c r="H1688" t="s">
         <v>9</v>
@@ -46238,7 +46244,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G1690" t="s">
-        <v>462</v>
+        <v>495</v>
       </c>
       <c r="H1690" t="s">
         <v>9</v>
@@ -46264,7 +46270,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G1691" t="s">
-        <v>462</v>
+        <v>495</v>
       </c>
       <c r="H1691" t="s">
         <v>9</v>
@@ -46290,7 +46296,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G1692" t="s">
-        <v>462</v>
+        <v>495</v>
       </c>
       <c r="H1692" t="s">
         <v>9</v>
@@ -46368,7 +46374,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G1695" t="s">
-        <v>462</v>
+        <v>495</v>
       </c>
       <c r="H1695" t="s">
         <v>9</v>
@@ -46394,7 +46400,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1696" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="H1696" t="s">
         <v>9</v>
@@ -46420,7 +46426,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1697" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="H1697" t="s">
         <v>9</v>
@@ -46524,7 +46530,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1701" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="H1701" t="s">
         <v>9</v>
@@ -46706,7 +46712,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1708" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="H1708" t="s">
         <v>9</v>
@@ -46732,7 +46738,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1709" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="H1709" t="s">
         <v>9</v>
@@ -46758,7 +46764,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1710" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="H1710" t="s">
         <v>9</v>
@@ -62592,7 +62598,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G2319" t="s">
-        <v>537</v>
+        <v>594</v>
       </c>
       <c r="H2319" t="s">
         <v>9</v>
@@ -64282,7 +64288,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2384" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="H2384" t="s">
         <v>9</v>
@@ -64308,7 +64314,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G2385" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="H2385" t="s">
         <v>9</v>
@@ -64334,7 +64340,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G2386" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="H2386" t="s">
         <v>9</v>
@@ -64360,7 +64366,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G2387" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="H2387" t="s">
         <v>9</v>
@@ -64386,7 +64392,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G2388" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="H2388" t="s">
         <v>9</v>
@@ -64412,7 +64418,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G2389" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="H2389" t="s">
         <v>9</v>
@@ -64438,7 +64444,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2390" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="H2390" t="s">
         <v>9</v>
@@ -64464,7 +64470,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2391" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="H2391" t="s">
         <v>9</v>
@@ -64516,7 +64522,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G2393" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="H2393" t="s">
         <v>9</v>
@@ -64568,7 +64574,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2395" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="H2395" t="s">
         <v>9</v>
@@ -64594,7 +64600,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2396" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="H2396" t="s">
         <v>9</v>
@@ -64620,7 +64626,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G2397" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="H2397" t="s">
         <v>9</v>
@@ -64646,7 +64652,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2398" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="H2398" t="s">
         <v>9</v>
@@ -64672,7 +64678,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G2399" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="H2399" t="s">
         <v>9</v>
@@ -64698,7 +64704,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G2400" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="H2400" t="s">
         <v>9</v>
@@ -64724,7 +64730,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G2401" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="H2401" t="s">
         <v>9</v>
@@ -64750,7 +64756,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G2402" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="H2402" t="s">
         <v>9</v>
@@ -64776,7 +64782,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G2403" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="H2403" t="s">
         <v>9</v>
@@ -64802,7 +64808,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G2404" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="H2404" t="s">
         <v>9</v>
@@ -64828,7 +64834,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G2405" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="H2405" t="s">
         <v>9</v>
@@ -64854,7 +64860,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G2406" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="H2406" t="s">
         <v>9</v>
@@ -64880,7 +64886,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G2407" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="H2407" t="s">
         <v>9</v>
@@ -64906,7 +64912,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G2408" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="H2408" t="s">
         <v>9</v>
@@ -64932,7 +64938,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2409" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="H2409" t="s">
         <v>9</v>
@@ -64958,7 +64964,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G2410" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="H2410" t="s">
         <v>9</v>
@@ -64984,7 +64990,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G2411" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="H2411" t="s">
         <v>9</v>
@@ -65010,7 +65016,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G2412" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="H2412" t="s">
         <v>9</v>
@@ -65036,7 +65042,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G2413" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="H2413" t="s">
         <v>9</v>
@@ -65062,7 +65068,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G2414" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="H2414" t="s">
         <v>9</v>
@@ -65088,7 +65094,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G2415" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="H2415" t="s">
         <v>9</v>
@@ -65114,7 +65120,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G2416" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="H2416" t="s">
         <v>9</v>
@@ -65140,7 +65146,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G2417" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="H2417" t="s">
         <v>9</v>
@@ -65166,7 +65172,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G2418" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="H2418" t="s">
         <v>9</v>
@@ -65192,7 +65198,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G2419" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="H2419" t="s">
         <v>9</v>
@@ -65218,7 +65224,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G2420" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="H2420" t="s">
         <v>9</v>
@@ -65244,7 +65250,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G2421" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="H2421" t="s">
         <v>9</v>
@@ -65270,7 +65276,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G2422" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="H2422" t="s">
         <v>9</v>
@@ -65296,7 +65302,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G2423" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="H2423" t="s">
         <v>9</v>
@@ -65322,7 +65328,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G2424" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="H2424" t="s">
         <v>9</v>
@@ -65348,7 +65354,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G2425" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="H2425" t="s">
         <v>9</v>
@@ -65374,7 +65380,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G2426" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="H2426" t="s">
         <v>9</v>
@@ -65400,7 +65406,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G2427" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="H2427" t="s">
         <v>9</v>
@@ -65426,7 +65432,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G2428" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="H2428" t="s">
         <v>9</v>
@@ -65452,7 +65458,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G2429" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="H2429" t="s">
         <v>9</v>
@@ -65478,7 +65484,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G2430" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="H2430" t="s">
         <v>9</v>
@@ -65504,7 +65510,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G2431" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="H2431" t="s">
         <v>9</v>
@@ -65530,7 +65536,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G2432" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="H2432" t="s">
         <v>9</v>
@@ -65556,7 +65562,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G2433" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="H2433" t="s">
         <v>9</v>
@@ -65582,7 +65588,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G2434" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="H2434" t="s">
         <v>9</v>
@@ -65608,7 +65614,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G2435" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="H2435" t="s">
         <v>9</v>
@@ -65634,7 +65640,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G2436" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="H2436" t="s">
         <v>9</v>
@@ -65660,7 +65666,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G2437" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="H2437" t="s">
         <v>9</v>
@@ -65686,7 +65692,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G2438" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="H2438" t="s">
         <v>9</v>
@@ -65712,7 +65718,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G2439" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="H2439" t="s">
         <v>9</v>
@@ -65738,7 +65744,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G2440" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="H2440" t="s">
         <v>9</v>
@@ -65764,7 +65770,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G2441" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="H2441" t="s">
         <v>9</v>
@@ -65790,7 +65796,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G2442" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="H2442" t="s">
         <v>9</v>
@@ -65816,7 +65822,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G2443" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="H2443" t="s">
         <v>9</v>
@@ -65842,7 +65848,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G2444" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="H2444" t="s">
         <v>9</v>
@@ -65868,7 +65874,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G2445" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="H2445" t="s">
         <v>9</v>
@@ -65894,7 +65900,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G2446" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="H2446" t="s">
         <v>9</v>
@@ -65920,7 +65926,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G2447" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="H2447" t="s">
         <v>9</v>
@@ -65946,7 +65952,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G2448" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="H2448" t="s">
         <v>9</v>
@@ -65972,7 +65978,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G2449" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="H2449" t="s">
         <v>9</v>
@@ -65998,7 +66004,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G2450" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="H2450" t="s">
         <v>9</v>
@@ -66024,7 +66030,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G2451" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="H2451" t="s">
         <v>9</v>
@@ -66050,7 +66056,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G2452" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="H2452" t="s">
         <v>9</v>
@@ -66076,7 +66082,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G2453" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="H2453" t="s">
         <v>9</v>
@@ -66102,7 +66108,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G2454" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="H2454" t="s">
         <v>9</v>
@@ -66128,7 +66134,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G2455" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="H2455" t="s">
         <v>9</v>
@@ -66154,7 +66160,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G2456" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="H2456" t="s">
         <v>9</v>
@@ -66180,7 +66186,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G2457" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="H2457" t="s">
         <v>9</v>
@@ -66206,7 +66212,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G2458" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="H2458" t="s">
         <v>9</v>
@@ -66232,7 +66238,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G2459" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="H2459" t="s">
         <v>9</v>
@@ -66258,7 +66264,7 @@
         <v>4</v>
       </c>
       <c r="G2460" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="H2460" t="s">
         <v>9</v>
@@ -66284,7 +66290,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G2461" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="H2461" t="s">
         <v>9</v>
@@ -66310,7 +66316,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G2462" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="H2462" t="s">
         <v>9</v>
@@ -66336,7 +66342,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G2463" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="H2463" t="s">
         <v>9</v>
@@ -66362,7 +66368,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G2464" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="H2464" t="s">
         <v>9</v>
@@ -66388,7 +66394,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G2465" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="H2465" t="s">
         <v>9</v>
@@ -66414,7 +66420,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G2466" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="H2466" t="s">
         <v>9</v>
@@ -66440,7 +66446,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G2467" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="H2467" t="s">
         <v>9</v>
@@ -66466,7 +66472,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G2468" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="H2468" t="s">
         <v>9</v>
@@ -66492,7 +66498,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G2469" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="H2469" t="s">
         <v>9</v>
@@ -66518,7 +66524,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G2470" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="H2470" t="s">
         <v>9</v>
@@ -66544,7 +66550,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G2471" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="H2471" t="s">
         <v>9</v>
@@ -66570,7 +66576,7 @@
         <v>4</v>
       </c>
       <c r="G2472" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="H2472" t="s">
         <v>9</v>
@@ -66596,7 +66602,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G2473" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="H2473" t="s">
         <v>9</v>
@@ -66622,7 +66628,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G2474" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="H2474" t="s">
         <v>9</v>
@@ -66648,7 +66654,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G2475" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="H2475" t="s">
         <v>9</v>
@@ -66674,7 +66680,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G2476" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="H2476" t="s">
         <v>9</v>
@@ -66700,7 +66706,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G2477" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="H2477" t="s">
         <v>9</v>
@@ -66726,7 +66732,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G2478" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="H2478" t="s">
         <v>9</v>
@@ -66752,7 +66758,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G2479" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="H2479" t="s">
         <v>9</v>
@@ -66778,7 +66784,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G2480" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="H2480" t="s">
         <v>9</v>
@@ -66804,7 +66810,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G2481" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="H2481" t="s">
         <v>9</v>
@@ -66830,7 +66836,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G2482" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="H2482" t="s">
         <v>9</v>
@@ -66856,7 +66862,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G2483" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="H2483" t="s">
         <v>9</v>
@@ -66882,7 +66888,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G2484" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="H2484" t="s">
         <v>9</v>
@@ -66908,7 +66914,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G2485" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="H2485" t="s">
         <v>9</v>
@@ -66934,7 +66940,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G2486" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="H2486" t="s">
         <v>9</v>
@@ -66960,7 +66966,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G2487" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="H2487" t="s">
         <v>9</v>
@@ -66986,7 +66992,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G2488" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="H2488" t="s">
         <v>9</v>
@@ -67012,7 +67018,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G2489" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="H2489" t="s">
         <v>9</v>
@@ -67038,7 +67044,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G2490" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="H2490" t="s">
         <v>9</v>
@@ -67064,7 +67070,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G2491" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="H2491" t="s">
         <v>9</v>
@@ -67090,7 +67096,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G2492" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="H2492" t="s">
         <v>9</v>
@@ -67116,7 +67122,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G2493" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="H2493" t="s">
         <v>9</v>
@@ -67142,7 +67148,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G2494" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="H2494" t="s">
         <v>9</v>
@@ -67168,7 +67174,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G2495" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="H2495" t="s">
         <v>9</v>
@@ -67194,7 +67200,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G2496" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="H2496" t="s">
         <v>9</v>
@@ -67220,7 +67226,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G2497" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="H2497" t="s">
         <v>9</v>
@@ -67246,7 +67252,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G2498" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="H2498" t="s">
         <v>9</v>
@@ -67272,7 +67278,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G2499" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="H2499" t="s">
         <v>9</v>
@@ -67298,7 +67304,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G2500" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="H2500" t="s">
         <v>9</v>
@@ -67324,7 +67330,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G2501" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="H2501" t="s">
         <v>9</v>
@@ -67350,7 +67356,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G2502" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="H2502" t="s">
         <v>9</v>
@@ -67376,7 +67382,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G2503" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="H2503" t="s">
         <v>9</v>
@@ -67402,7 +67408,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G2504" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="H2504" t="s">
         <v>9</v>
@@ -67428,7 +67434,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G2505" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H2505" t="s">
         <v>9</v>
@@ -67454,7 +67460,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G2506" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H2506" t="s">
         <v>9</v>
@@ -67480,7 +67486,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G2507" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="H2507" t="s">
         <v>9</v>
@@ -67506,7 +67512,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G2508" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="H2508" t="s">
         <v>9</v>
@@ -67532,7 +67538,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G2509" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="H2509" t="s">
         <v>9</v>
@@ -67558,7 +67564,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G2510" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="H2510" t="s">
         <v>9</v>
@@ -67584,7 +67590,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G2511" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="H2511" t="s">
         <v>9</v>
@@ -67610,7 +67616,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G2512" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="H2512" t="s">
         <v>9</v>
@@ -67636,7 +67642,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G2513" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="H2513" t="s">
         <v>9</v>
@@ -67662,7 +67668,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G2514" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="H2514" t="s">
         <v>9</v>
@@ -67688,7 +67694,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G2515" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="H2515" t="s">
         <v>9</v>
@@ -67714,7 +67720,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G2516" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="H2516" t="s">
         <v>9</v>
@@ -67740,7 +67746,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G2517" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="H2517" t="s">
         <v>9</v>
@@ -67766,7 +67772,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G2518" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="H2518" t="s">
         <v>9</v>
@@ -67792,7 +67798,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G2519" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="H2519" t="s">
         <v>9</v>
@@ -67818,7 +67824,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G2520" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="H2520" t="s">
         <v>9</v>
@@ -67844,7 +67850,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G2521" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="H2521" t="s">
         <v>9</v>
@@ -67870,7 +67876,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G2522" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="H2522" t="s">
         <v>9</v>
@@ -67896,7 +67902,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G2523" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="H2523" t="s">
         <v>9</v>
@@ -67922,7 +67928,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G2524" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="H2524" t="s">
         <v>9</v>
@@ -67948,7 +67954,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G2525" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="H2525" t="s">
         <v>9</v>
@@ -67974,7 +67980,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G2526" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="H2526" t="s">
         <v>9</v>
@@ -68000,7 +68006,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G2527" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="H2527" t="s">
         <v>9</v>
@@ -68026,7 +68032,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G2528" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="H2528" t="s">
         <v>9</v>
@@ -68052,7 +68058,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G2529" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="H2529" t="s">
         <v>9</v>
@@ -68060,7 +68066,7 @@
     </row>
     <row r="2530">
       <c r="A2530" s="1" t="n">
-        <v>46001.4789930556</v>
+        <v>46001.3333333333</v>
       </c>
       <c r="B2530" t="n">
         <v>1034</v>
@@ -68078,9 +68084,35 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G2530" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="H2530" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2531">
+      <c r="A2531" s="1" t="n">
+        <v>46002.4129976852</v>
+      </c>
+      <c r="B2531" t="n">
+        <v>6300</v>
+      </c>
+      <c r="C2531" t="n">
+        <v>3.8199999332428</v>
+      </c>
+      <c r="D2531" t="n">
+        <v>3.74000000953674</v>
+      </c>
+      <c r="E2531" t="n">
+        <v>3.79999995231628</v>
+      </c>
+      <c r="F2531" t="n">
+        <v>3.8199999332428</v>
+      </c>
+      <c r="G2531" t="s">
+        <v>653</v>
+      </c>
+      <c r="H2531" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ENV.MI.xlsx
+++ b/data/ENV.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="654" uniqueCount="654">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="652" uniqueCount="652">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18965220451355</t>
+    <t xml:space="preserve">2.18965244293213</t>
   </si>
   <si>
     <t xml:space="preserve">ENV.MI</t>
@@ -50,64 +50,64 @@
     <t xml:space="preserve">2.14471292495728</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16175842285156</t>
+    <t xml:space="preserve">2.16175889968872</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03778719902039</t>
+    <t xml:space="preserve">2.03778696060181</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08272671699524</t>
+    <t xml:space="preserve">2.08272647857666</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05328321456909</t>
+    <t xml:space="preserve">2.05328369140625</t>
   </si>
   <si>
     <t xml:space="preserve">2.03623747825623</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96805274486542</t>
+    <t xml:space="preserve">1.96805286407471</t>
   </si>
   <si>
     <t xml:space="preserve">1.96030461788177</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8983188867569</t>
+    <t xml:space="preserve">1.89831864833832</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88127291202545</t>
+    <t xml:space="preserve">1.88127255439758</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9634040594101</t>
+    <t xml:space="preserve">1.96340382099152</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98354911804199</t>
+    <t xml:space="preserve">1.98354923725128</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01299238204956</t>
+    <t xml:space="preserve">2.01299262046814</t>
   </si>
   <si>
     <t xml:space="preserve">1.93551003932953</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93705999851227</t>
+    <t xml:space="preserve">1.93705987930298</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91381502151489</t>
+    <t xml:space="preserve">1.91381537914276</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91071605682373</t>
+    <t xml:space="preserve">1.91071581840515</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86577606201172</t>
+    <t xml:space="preserve">1.86577618122101</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89212036132812</t>
+    <t xml:space="preserve">1.89212000370026</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85182917118073</t>
+    <t xml:space="preserve">1.85182905197144</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93396091461182</t>
+    <t xml:space="preserve">1.93396055698395</t>
   </si>
   <si>
     <t xml:space="preserve">1.8673255443573</t>
@@ -125,10 +125,10 @@
     <t xml:space="preserve">2.18500351905823</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20824861526489</t>
+    <t xml:space="preserve">2.20824837684631</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16950678825378</t>
+    <t xml:space="preserve">2.16950702667236</t>
   </si>
   <si>
     <t xml:space="preserve">2.0842764377594</t>
@@ -137,7 +137,7 @@
     <t xml:space="preserve">2.0145423412323</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0052444934845</t>
+    <t xml:space="preserve">2.00524425506592</t>
   </si>
   <si>
     <t xml:space="preserve">2.14626240730286</t>
@@ -146,25 +146,25 @@
     <t xml:space="preserve">2.22219514846802</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32447195053101</t>
+    <t xml:space="preserve">2.32447171211243</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20049977302551</t>
+    <t xml:space="preserve">2.20050001144409</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27178382873535</t>
+    <t xml:space="preserve">2.27178359031677</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24698972702026</t>
+    <t xml:space="preserve">2.24698948860168</t>
   </si>
   <si>
     <t xml:space="preserve">2.32137274742126</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28418111801147</t>
+    <t xml:space="preserve">2.2841808795929</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37870931625366</t>
+    <t xml:space="preserve">2.37870955467224</t>
   </si>
   <si>
     <t xml:space="preserve">2.35546493530273</t>
@@ -173,13 +173,13 @@
     <t xml:space="preserve">2.44069576263428</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4313976764679</t>
+    <t xml:space="preserve">2.43139743804932</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44999289512634</t>
+    <t xml:space="preserve">2.44999361038208</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3849081993103</t>
+    <t xml:space="preserve">2.38490843772888</t>
   </si>
   <si>
     <t xml:space="preserve">2.36166334152222</t>
@@ -188,28 +188,28 @@
     <t xml:space="preserve">2.36321306228638</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31982278823853</t>
+    <t xml:space="preserve">2.3198230266571</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35236549377441</t>
+    <t xml:space="preserve">2.35236573219299</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26868414878845</t>
+    <t xml:space="preserve">2.26868462562561</t>
   </si>
   <si>
     <t xml:space="preserve">2.32292222976685</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33531928062439</t>
+    <t xml:space="preserve">2.33531951904297</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33996796607971</t>
+    <t xml:space="preserve">2.33996844291687</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31052470207214</t>
+    <t xml:space="preserve">2.3105251789093</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28573083877563</t>
+    <t xml:space="preserve">2.28573060035706</t>
   </si>
   <si>
     <t xml:space="preserve">2.25473785400391</t>
@@ -218,10 +218,10 @@
     <t xml:space="preserve">2.29037976264954</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27488303184509</t>
+    <t xml:space="preserve">2.27488350868225</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23149299621582</t>
+    <t xml:space="preserve">2.2314932346344</t>
   </si>
   <si>
     <t xml:space="preserve">2.0749785900116</t>
@@ -233,16 +233,16 @@
     <t xml:space="preserve">2.03468775749207</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02229022979736</t>
+    <t xml:space="preserve">2.02229046821594</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97580122947693</t>
+    <t xml:space="preserve">1.97580075263977</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91980671882629</t>
+    <t xml:space="preserve">1.91980683803558</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8821634054184</t>
+    <t xml:space="preserve">1.88216364383698</t>
   </si>
   <si>
     <t xml:space="preserve">2.00136709213257</t>
@@ -251,34 +251,34 @@
     <t xml:space="preserve">1.96058702468872</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90255379676819</t>
+    <t xml:space="preserve">1.9025536775589</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92137515544891</t>
+    <t xml:space="preserve">1.9213752746582</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91353332996368</t>
+    <t xml:space="preserve">1.91353285312653</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89784836769104</t>
+    <t xml:space="preserve">1.89784824848175</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89000594615936</t>
+    <t xml:space="preserve">1.89000570774078</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85079383850098</t>
+    <t xml:space="preserve">1.85079419612885</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88059484958649</t>
+    <t xml:space="preserve">1.88059496879578</t>
   </si>
   <si>
     <t xml:space="preserve">1.86647891998291</t>
   </si>
   <si>
-    <t xml:space="preserve">1.546511054039</t>
+    <t xml:space="preserve">1.54651093482971</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68610489368439</t>
+    <t xml:space="preserve">1.6861047744751</t>
   </si>
   <si>
     <t xml:space="preserve">1.70178961753845</t>
@@ -290,22 +290,22 @@
     <t xml:space="preserve">1.66257762908936</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64532446861267</t>
+    <t xml:space="preserve">1.64532470703125</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62336611747742</t>
+    <t xml:space="preserve">1.62336587905884</t>
   </si>
   <si>
     <t xml:space="preserve">1.61552357673645</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63120830059052</t>
+    <t xml:space="preserve">1.6312084197998</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5841543674469</t>
+    <t xml:space="preserve">1.58415424823761</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64689302444458</t>
+    <t xml:space="preserve">1.64689314365387</t>
   </si>
   <si>
     <t xml:space="preserve">1.64061915874481</t>
@@ -314,7 +314,7 @@
     <t xml:space="preserve">1.6390506029129</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60768139362335</t>
+    <t xml:space="preserve">1.60768127441406</t>
   </si>
   <si>
     <t xml:space="preserve">1.57631182670593</t>
@@ -323,40 +323,40 @@
     <t xml:space="preserve">1.59199655056</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75668585300446</t>
+    <t xml:space="preserve">1.75668561458588</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84295189380646</t>
+    <t xml:space="preserve">1.84295201301575</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8460887670517</t>
+    <t xml:space="preserve">1.84608864784241</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92921757698059</t>
+    <t xml:space="preserve">1.92921769618988</t>
   </si>
   <si>
     <t xml:space="preserve">1.88530051708221</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9009850025177</t>
+    <t xml:space="preserve">1.90098524093628</t>
   </si>
   <si>
     <t xml:space="preserve">1.91823852062225</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94960784912109</t>
+    <t xml:space="preserve">1.9496077299118</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93078589439392</t>
+    <t xml:space="preserve">1.93078601360321</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84922575950623</t>
+    <t xml:space="preserve">1.84922552108765</t>
   </si>
   <si>
     <t xml:space="preserve">1.82412993907928</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8554995059967</t>
+    <t xml:space="preserve">1.85549938678741</t>
   </si>
   <si>
     <t xml:space="preserve">1.89627981185913</t>
@@ -365,22 +365,22 @@
     <t xml:space="preserve">1.87432098388672</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94333386421204</t>
+    <t xml:space="preserve">1.94333338737488</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94490253925323</t>
+    <t xml:space="preserve">1.94490230083466</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9668607711792</t>
+    <t xml:space="preserve">1.96686065196991</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98411417007446</t>
+    <t xml:space="preserve">1.98411405086517</t>
   </si>
   <si>
     <t xml:space="preserve">2.0625376701355</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0531268119812</t>
+    <t xml:space="preserve">2.05312657356262</t>
   </si>
   <si>
     <t xml:space="preserve">2.05155825614929</t>
@@ -389,16 +389,16 @@
     <t xml:space="preserve">2.0233256816864</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02959966659546</t>
+    <t xml:space="preserve">2.02959942817688</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03116822242737</t>
+    <t xml:space="preserve">2.03116798400879</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06096887588501</t>
+    <t xml:space="preserve">2.06096911430359</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09390687942505</t>
+    <t xml:space="preserve">2.09390711784363</t>
   </si>
   <si>
     <t xml:space="preserve">2.08606481552124</t>
@@ -407,43 +407,43 @@
     <t xml:space="preserve">2.1550772190094</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18801522254944</t>
+    <t xml:space="preserve">2.18801498413086</t>
   </si>
   <si>
     <t xml:space="preserve">2.19585728645325</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20213150978088</t>
+    <t xml:space="preserve">2.2021312713623</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23350048065186</t>
+    <t xml:space="preserve">2.23350071907043</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20997357368469</t>
+    <t xml:space="preserve">2.20997381210327</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18017244338989</t>
+    <t xml:space="preserve">2.18017268180847</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16605663299561</t>
+    <t xml:space="preserve">2.16605639457703</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19428873062134</t>
+    <t xml:space="preserve">2.1942892074585</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17389869689941</t>
+    <t xml:space="preserve">2.17389917373657</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2005627155304</t>
+    <t xml:space="preserve">2.20056295394897</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21938443183899</t>
+    <t xml:space="preserve">2.21938419342041</t>
   </si>
   <si>
     <t xml:space="preserve">2.21781611442566</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19115161895752</t>
+    <t xml:space="preserve">2.19115209579468</t>
   </si>
   <si>
     <t xml:space="preserve">2.12057089805603</t>
@@ -452,28 +452,28 @@
     <t xml:space="preserve">2.15350890159607</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11743426322937</t>
+    <t xml:space="preserve">2.11743378639221</t>
   </si>
   <si>
     <t xml:space="preserve">2.16291952133179</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10802316665649</t>
+    <t xml:space="preserve">2.10802292823792</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01548361778259</t>
+    <t xml:space="preserve">2.01548337936401</t>
   </si>
   <si>
     <t xml:space="preserve">2.04528450965881</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9856823682785</t>
+    <t xml:space="preserve">1.98568248748779</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07822203636169</t>
+    <t xml:space="preserve">2.07822251319885</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06724262237549</t>
+    <t xml:space="preserve">2.06724286079407</t>
   </si>
   <si>
     <t xml:space="preserve">2.12998151779175</t>
@@ -485,19 +485,19 @@
     <t xml:space="preserve">2.05469489097595</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11429691314697</t>
+    <t xml:space="preserve">2.11429667472839</t>
   </si>
   <si>
     <t xml:space="preserve">2.05626368522644</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06410574913025</t>
+    <t xml:space="preserve">2.06410598754883</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10488605499268</t>
+    <t xml:space="preserve">2.10488629341125</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00920963287354</t>
+    <t xml:space="preserve">2.00920987129211</t>
   </si>
   <si>
     <t xml:space="preserve">2.0139148235321</t>
@@ -506,28 +506,28 @@
     <t xml:space="preserve">2.04842138290405</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16448783874512</t>
+    <t xml:space="preserve">2.1644880771637</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18487787246704</t>
+    <t xml:space="preserve">2.18487811088562</t>
   </si>
   <si>
     <t xml:space="preserve">2.26643872261047</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27271270751953</t>
+    <t xml:space="preserve">2.27271246910095</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25702738761902</t>
+    <t xml:space="preserve">2.25702786445618</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30721855163574</t>
+    <t xml:space="preserve">2.30721879005432</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23036360740662</t>
+    <t xml:space="preserve">2.2303638458252</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37152600288391</t>
+    <t xml:space="preserve">2.37152576446533</t>
   </si>
   <si>
     <t xml:space="preserve">2.35270428657532</t>
@@ -539,31 +539,31 @@
     <t xml:space="preserve">2.33545088768005</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31349301338196</t>
+    <t xml:space="preserve">2.31349277496338</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37623143196106</t>
+    <t xml:space="preserve">2.37623119354248</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32917714118958</t>
+    <t xml:space="preserve">2.32917737960815</t>
   </si>
   <si>
     <t xml:space="preserve">2.24918532371521</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28839707374573</t>
+    <t xml:space="preserve">2.28839683532715</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33701968193054</t>
+    <t xml:space="preserve">2.33701992034912</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34486222267151</t>
+    <t xml:space="preserve">2.34486174583435</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34956741333008</t>
+    <t xml:space="preserve">2.3495671749115</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32604026794434</t>
+    <t xml:space="preserve">2.32604050636292</t>
   </si>
   <si>
     <t xml:space="preserve">2.30251336097717</t>
@@ -572,40 +572,40 @@
     <t xml:space="preserve">2.31192398071289</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25075340270996</t>
+    <t xml:space="preserve">2.25075387954712</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27428102493286</t>
+    <t xml:space="preserve">2.27428078651428</t>
   </si>
   <si>
     <t xml:space="preserve">2.43897008895874</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48445558547974</t>
+    <t xml:space="preserve">2.48445582389832</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46249747276306</t>
+    <t xml:space="preserve">2.4624969959259</t>
   </si>
   <si>
     <t xml:space="preserve">2.50798273086548</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48602437973022</t>
+    <t xml:space="preserve">2.4860246181488</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60993313789368</t>
+    <t xml:space="preserve">2.60993337631226</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66639852523804</t>
+    <t xml:space="preserve">2.66639828681946</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66326117515564</t>
+    <t xml:space="preserve">2.66326093673706</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6601243019104</t>
+    <t xml:space="preserve">2.66012454032898</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64287137985229</t>
+    <t xml:space="preserve">2.64287114143372</t>
   </si>
   <si>
     <t xml:space="preserve">2.65855622291565</t>
@@ -614,19 +614,19 @@
     <t xml:space="preserve">2.60209131240845</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55033135414124</t>
+    <t xml:space="preserve">2.55033159255981</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63816618919373</t>
+    <t xml:space="preserve">2.63816595077515</t>
   </si>
   <si>
     <t xml:space="preserve">2.58013224601746</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59581732749939</t>
+    <t xml:space="preserve">2.59581685066223</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58170080184937</t>
+    <t xml:space="preserve">2.58170104026794</t>
   </si>
   <si>
     <t xml:space="preserve">2.6036593914032</t>
@@ -635,25 +635,25 @@
     <t xml:space="preserve">2.61934423446655</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57542705535889</t>
+    <t xml:space="preserve">2.57542681694031</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57385849952698</t>
+    <t xml:space="preserve">2.57385873794556</t>
   </si>
   <si>
     <t xml:space="preserve">2.50955104827881</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58797478675842</t>
+    <t xml:space="preserve">2.587975025177</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56444764137268</t>
+    <t xml:space="preserve">2.56444811820984</t>
   </si>
   <si>
     <t xml:space="preserve">2.61150169372559</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56915307044983</t>
+    <t xml:space="preserve">2.56915330886841</t>
   </si>
   <si>
     <t xml:space="preserve">2.63502883911133</t>
@@ -662,13 +662,13 @@
     <t xml:space="preserve">2.62561798095703</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62718653678894</t>
+    <t xml:space="preserve">2.62718629837036</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83422446250916</t>
+    <t xml:space="preserve">2.83422493934631</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79030752182007</t>
+    <t xml:space="preserve">2.79030728340149</t>
   </si>
   <si>
     <t xml:space="preserve">2.77619099617004</t>
@@ -683,13 +683,13 @@
     <t xml:space="preserve">2.78246521949768</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8122661113739</t>
+    <t xml:space="preserve">2.81226587295532</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82324552536011</t>
+    <t xml:space="preserve">2.82324528694153</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68678832054138</t>
+    <t xml:space="preserve">2.68678855895996</t>
   </si>
   <si>
     <t xml:space="preserve">2.70090460777283</t>
@@ -698,16 +698,16 @@
     <t xml:space="preserve">2.80657124519348</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86433959007263</t>
+    <t xml:space="preserve">2.86433935165405</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81940865516663</t>
+    <t xml:space="preserve">2.81940889358521</t>
   </si>
   <si>
     <t xml:space="preserve">2.80817604064941</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88038635253906</t>
+    <t xml:space="preserve">2.88038611412048</t>
   </si>
   <si>
     <t xml:space="preserve">2.8338508605957</t>
@@ -722,25 +722,25 @@
     <t xml:space="preserve">2.70547699928284</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7327561378479</t>
+    <t xml:space="preserve">2.73275637626648</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67177891731262</t>
+    <t xml:space="preserve">2.67177867889404</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62363862991333</t>
+    <t xml:space="preserve">2.62363910675049</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61722040176392</t>
+    <t xml:space="preserve">2.61722016334534</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60438251495361</t>
+    <t xml:space="preserve">2.60438275337219</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62524342536926</t>
+    <t xml:space="preserve">2.62524318695068</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64128994941711</t>
+    <t xml:space="preserve">2.64129018783569</t>
   </si>
   <si>
     <t xml:space="preserve">2.6958487033844</t>
@@ -752,10 +752,10 @@
     <t xml:space="preserve">2.74719858169556</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71991920471191</t>
+    <t xml:space="preserve">2.71991944313049</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72633743286133</t>
+    <t xml:space="preserve">2.72633790969849</t>
   </si>
   <si>
     <t xml:space="preserve">2.74238467216492</t>
@@ -767,13 +767,13 @@
     <t xml:space="preserve">2.78571033477783</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82422280311584</t>
+    <t xml:space="preserve">2.82422256469727</t>
   </si>
   <si>
     <t xml:space="preserve">2.78731536865234</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79373407363892</t>
+    <t xml:space="preserve">2.79373383522034</t>
   </si>
   <si>
     <t xml:space="preserve">2.80496668815613</t>
@@ -791,7 +791,7 @@
     <t xml:space="preserve">2.82261800765991</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7600359916687</t>
+    <t xml:space="preserve">2.76003575325012</t>
   </si>
   <si>
     <t xml:space="preserve">2.77929210662842</t>
@@ -800,7 +800,7 @@
     <t xml:space="preserve">2.79854774475098</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77447772026062</t>
+    <t xml:space="preserve">2.7744779586792</t>
   </si>
   <si>
     <t xml:space="preserve">2.8033618927002</t>
@@ -809,28 +809,28 @@
     <t xml:space="preserve">2.83545541763306</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84026956558228</t>
+    <t xml:space="preserve">2.8402693271637</t>
   </si>
   <si>
     <t xml:space="preserve">2.83224630355835</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81138515472412</t>
+    <t xml:space="preserve">2.8113853931427</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81619930267334</t>
+    <t xml:space="preserve">2.81619954109192</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76324510574341</t>
+    <t xml:space="preserve">2.76324534416199</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71189594268799</t>
+    <t xml:space="preserve">2.71189618110657</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72473311424255</t>
+    <t xml:space="preserve">2.7247326374054</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79694390296936</t>
+    <t xml:space="preserve">2.79694318771362</t>
   </si>
   <si>
     <t xml:space="preserve">2.79052472114563</t>
@@ -839,19 +839,19 @@
     <t xml:space="preserve">2.76805901527405</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73115158081055</t>
+    <t xml:space="preserve">2.73115181922913</t>
   </si>
   <si>
     <t xml:space="preserve">2.70387244224548</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81459474563599</t>
+    <t xml:space="preserve">2.81459450721741</t>
   </si>
   <si>
     <t xml:space="preserve">2.82903671264648</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84347867965698</t>
+    <t xml:space="preserve">2.8434784412384</t>
   </si>
   <si>
     <t xml:space="preserve">2.77768707275391</t>
@@ -863,10 +863,10 @@
     <t xml:space="preserve">2.88840961456299</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87236285209656</t>
+    <t xml:space="preserve">2.87236309051514</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89161896705627</t>
+    <t xml:space="preserve">2.89161920547485</t>
   </si>
   <si>
     <t xml:space="preserve">2.92852640151978</t>
@@ -875,46 +875,46 @@
     <t xml:space="preserve">2.85952544212341</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90927052497864</t>
+    <t xml:space="preserve">2.90927004814148</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99913215637207</t>
+    <t xml:space="preserve">2.99913191795349</t>
   </si>
   <si>
     <t xml:space="preserve">2.96864318847656</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83064150810242</t>
+    <t xml:space="preserve">2.830641746521</t>
   </si>
   <si>
     <t xml:space="preserve">2.87878155708313</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87717723846436</t>
+    <t xml:space="preserve">2.87717700004578</t>
   </si>
   <si>
     <t xml:space="preserve">2.87557244300842</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75201272964478</t>
+    <t xml:space="preserve">2.7520124912262</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76164031028748</t>
+    <t xml:space="preserve">2.76164054870605</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7889199256897</t>
+    <t xml:space="preserve">2.78892016410828</t>
   </si>
   <si>
     <t xml:space="preserve">2.67980217933655</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73596572875977</t>
+    <t xml:space="preserve">2.73596596717834</t>
   </si>
   <si>
     <t xml:space="preserve">2.82582759857178</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84829258918762</t>
+    <t xml:space="preserve">2.8482928276062</t>
   </si>
   <si>
     <t xml:space="preserve">2.82101345062256</t>
@@ -923,13 +923,13 @@
     <t xml:space="preserve">2.73436117172241</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81780409812927</t>
+    <t xml:space="preserve">2.81780433654785</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76484990119934</t>
+    <t xml:space="preserve">2.76485013961792</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74077987670898</t>
+    <t xml:space="preserve">2.74077963829041</t>
   </si>
   <si>
     <t xml:space="preserve">2.79212951660156</t>
@@ -941,19 +941,19 @@
     <t xml:space="preserve">2.60759210586548</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55142855644226</t>
+    <t xml:space="preserve">2.55142879486084</t>
   </si>
   <si>
     <t xml:space="preserve">2.56747508049011</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59956860542297</t>
+    <t xml:space="preserve">2.59956836700439</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55945181846619</t>
+    <t xml:space="preserve">2.55945205688477</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50328850746155</t>
+    <t xml:space="preserve">2.50328826904297</t>
   </si>
   <si>
     <t xml:space="preserve">2.45514822006226</t>
@@ -962,31 +962,31 @@
     <t xml:space="preserve">2.47921824455261</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47119474411011</t>
+    <t xml:space="preserve">2.47119498252869</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43107771873474</t>
+    <t xml:space="preserve">2.43107795715332</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46317148208618</t>
+    <t xml:space="preserve">2.46317172050476</t>
   </si>
   <si>
     <t xml:space="preserve">2.48724150657654</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49526500701904</t>
+    <t xml:space="preserve">2.49526476860046</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52735877037048</t>
+    <t xml:space="preserve">2.52735829353333</t>
   </si>
   <si>
     <t xml:space="preserve">2.58352184295654</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65573215484619</t>
+    <t xml:space="preserve">2.65573191642761</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9124801158905</t>
+    <t xml:space="preserve">2.91247987747192</t>
   </si>
   <si>
     <t xml:space="preserve">2.82002472877502</t>
@@ -995,16 +995,16 @@
     <t xml:space="preserve">2.80358171463013</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86935496330261</t>
+    <t xml:space="preserve">2.86935472488403</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8446900844574</t>
+    <t xml:space="preserve">2.84468984603882</t>
   </si>
   <si>
     <t xml:space="preserve">2.85291147232056</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81180334091187</t>
+    <t xml:space="preserve">2.81180310249329</t>
   </si>
   <si>
     <t xml:space="preserve">2.72136521339417</t>
@@ -1016,13 +1016,13 @@
     <t xml:space="preserve">2.69670009613037</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64737033843994</t>
+    <t xml:space="preserve">2.64737010002136</t>
   </si>
   <si>
     <t xml:space="preserve">2.65559196472168</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66381359100342</t>
+    <t xml:space="preserve">2.66381335258484</t>
   </si>
   <si>
     <t xml:space="preserve">2.63092684745789</t>
@@ -1031,19 +1031,19 @@
     <t xml:space="preserve">2.6391487121582</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55693197250366</t>
+    <t xml:space="preserve">2.55693221092224</t>
   </si>
   <si>
     <t xml:space="preserve">2.59804058074951</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5487105846405</t>
+    <t xml:space="preserve">2.54871034622192</t>
   </si>
   <si>
     <t xml:space="preserve">2.46649408340454</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60626244544983</t>
+    <t xml:space="preserve">2.60626220703125</t>
   </si>
   <si>
     <t xml:space="preserve">2.52404546737671</t>
@@ -1058,43 +1058,43 @@
     <t xml:space="preserve">2.58981871604919</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62270522117615</t>
+    <t xml:space="preserve">2.62270545959473</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51582407951355</t>
+    <t xml:space="preserve">2.51582384109497</t>
   </si>
   <si>
     <t xml:space="preserve">2.57337546348572</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56515383720398</t>
+    <t xml:space="preserve">2.5651535987854</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53226733207703</t>
+    <t xml:space="preserve">2.53226709365845</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47471570968628</t>
+    <t xml:space="preserve">2.4747154712677</t>
   </si>
   <si>
     <t xml:space="preserve">2.48293733596802</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45005106925964</t>
+    <t xml:space="preserve">2.45005083084106</t>
   </si>
   <si>
     <t xml:space="preserve">2.44182920455933</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42538571357727</t>
+    <t xml:space="preserve">2.42538595199585</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43360757827759</t>
+    <t xml:space="preserve">2.43360781669617</t>
   </si>
   <si>
     <t xml:space="preserve">2.49115872383118</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50760245323181</t>
+    <t xml:space="preserve">2.50760221481323</t>
   </si>
   <si>
     <t xml:space="preserve">2.54048895835876</t>
@@ -1103,7 +1103,7 @@
     <t xml:space="preserve">2.67203545570374</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68847846984863</t>
+    <t xml:space="preserve">2.68847870826721</t>
   </si>
   <si>
     <t xml:space="preserve">2.70492196083069</t>
@@ -1112,52 +1112,52 @@
     <t xml:space="preserve">2.71314358711243</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75425148010254</t>
+    <t xml:space="preserve">2.75425171852112</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78713822364807</t>
+    <t xml:space="preserve">2.78713846206665</t>
   </si>
   <si>
     <t xml:space="preserve">2.77069497108459</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72958660125732</t>
+    <t xml:space="preserve">2.7295868396759</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7460298538208</t>
+    <t xml:space="preserve">2.74603009223938</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77891683578491</t>
+    <t xml:space="preserve">2.77891659736633</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79536008834839</t>
+    <t xml:space="preserve">2.79535984992981</t>
   </si>
   <si>
     <t xml:space="preserve">2.87757635116577</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91868472099304</t>
+    <t xml:space="preserve">2.91868495941162</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89401936531067</t>
+    <t xml:space="preserve">2.89401960372925</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86113333702087</t>
+    <t xml:space="preserve">2.86113309860229</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90224123001099</t>
+    <t xml:space="preserve">2.90224146842957</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88579797744751</t>
+    <t xml:space="preserve">2.88579821586609</t>
   </si>
   <si>
     <t xml:space="preserve">2.8364679813385</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94334936141968</t>
+    <t xml:space="preserve">2.94334959983826</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82824659347534</t>
+    <t xml:space="preserve">2.82824635505676</t>
   </si>
   <si>
     <t xml:space="preserve">2.92690634727478</t>
@@ -1166,7 +1166,7 @@
     <t xml:space="preserve">2.80358147621155</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77809429168701</t>
+    <t xml:space="preserve">2.77809453010559</t>
   </si>
   <si>
     <t xml:space="preserve">2.82057285308838</t>
@@ -1187,7 +1187,7 @@
     <t xml:space="preserve">2.90552997589111</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87154722213745</t>
+    <t xml:space="preserve">2.87154698371887</t>
   </si>
   <si>
     <t xml:space="preserve">2.85455560684204</t>
@@ -1199,16 +1199,16 @@
     <t xml:space="preserve">2.93101692199707</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94800853729248</t>
+    <t xml:space="preserve">2.9480082988739</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89703416824341</t>
+    <t xml:space="preserve">2.89703440666199</t>
   </si>
   <si>
     <t xml:space="preserve">2.93951296806335</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98199152946472</t>
+    <t xml:space="preserve">2.98199105262756</t>
   </si>
   <si>
     <t xml:space="preserve">2.79508590698242</t>
@@ -1232,13 +1232,13 @@
     <t xml:space="preserve">2.86305141448975</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62517189979553</t>
+    <t xml:space="preserve">2.62517166137695</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67614579200745</t>
+    <t xml:space="preserve">2.67614603042603</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61667609214783</t>
+    <t xml:space="preserve">2.61667585372925</t>
   </si>
   <si>
     <t xml:space="preserve">2.55720615386963</t>
@@ -1250,13 +1250,13 @@
     <t xml:space="preserve">2.49773621559143</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48074507713318</t>
+    <t xml:space="preserve">2.4807448387146</t>
   </si>
   <si>
     <t xml:space="preserve">2.53171920776367</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46375370025635</t>
+    <t xml:space="preserve">2.46375322341919</t>
   </si>
   <si>
     <t xml:space="preserve">2.58269309997559</t>
@@ -1271,7 +1271,7 @@
     <t xml:space="preserve">2.59118914604187</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47224903106689</t>
+    <t xml:space="preserve">2.47224926948547</t>
   </si>
   <si>
     <t xml:space="preserve">2.63366746902466</t>
@@ -1283,16 +1283,16 @@
     <t xml:space="preserve">2.52322363853455</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57419729232788</t>
+    <t xml:space="preserve">2.57419753074646</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07544374465942</t>
+    <t xml:space="preserve">3.075443983078</t>
   </si>
   <si>
     <t xml:space="preserve">3.0074782371521</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99048686027527</t>
+    <t xml:space="preserve">2.99048662185669</t>
   </si>
   <si>
     <t xml:space="preserve">2.96499991416931</t>
@@ -1301,7 +1301,7 @@
     <t xml:space="preserve">2.97349548339844</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95650410652161</t>
+    <t xml:space="preserve">2.95650434494019</t>
   </si>
   <si>
     <t xml:space="preserve">2.84606003761292</t>
@@ -1310,13 +1310,13 @@
     <t xml:space="preserve">2.75260734558105</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6676504611969</t>
+    <t xml:space="preserve">2.66765022277832</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65915465354919</t>
+    <t xml:space="preserve">2.65915441513062</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31083059310913</t>
+    <t xml:space="preserve">2.31083106994629</t>
   </si>
   <si>
     <t xml:space="preserve">2.35330939292908</t>
@@ -1331,34 +1331,34 @@
     <t xml:space="preserve">2.4892406463623</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65065884590149</t>
+    <t xml:space="preserve">2.65065860748291</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64216279983521</t>
+    <t xml:space="preserve">2.64216327667236</t>
   </si>
   <si>
     <t xml:space="preserve">2.71012878417969</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69313764572144</t>
+    <t xml:space="preserve">2.69313740730286</t>
   </si>
   <si>
     <t xml:space="preserve">2.71862459182739</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74411129951477</t>
+    <t xml:space="preserve">2.74411153793335</t>
   </si>
   <si>
     <t xml:space="preserve">2.68464183807373</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60818028450012</t>
+    <t xml:space="preserve">2.6081805229187</t>
   </si>
   <si>
     <t xml:space="preserve">2.50623178482056</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44676208496094</t>
+    <t xml:space="preserve">2.44676232337952</t>
   </si>
   <si>
     <t xml:space="preserve">2.37879633903503</t>
@@ -1367,16 +1367,16 @@
     <t xml:space="preserve">2.42977070808411</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37030053138733</t>
+    <t xml:space="preserve">2.37030076980591</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31932663917542</t>
+    <t xml:space="preserve">2.31932640075684</t>
   </si>
   <si>
     <t xml:space="preserve">2.27684807777405</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26835227012634</t>
+    <t xml:space="preserve">2.26835250854492</t>
   </si>
   <si>
     <t xml:space="preserve">2.30233502388</t>
@@ -1385,28 +1385,28 @@
     <t xml:space="preserve">2.33631777763367</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39578795433044</t>
+    <t xml:space="preserve">2.39578771591187</t>
   </si>
   <si>
     <t xml:space="preserve">2.72712016105652</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99898242950439</t>
+    <t xml:space="preserve">2.99898266792297</t>
   </si>
   <si>
     <t xml:space="preserve">3.03296542167664</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0159740447998</t>
+    <t xml:space="preserve">3.01597428321838</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04146099090576</t>
+    <t xml:space="preserve">3.04146122932434</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1943838596344</t>
+    <t xml:space="preserve">3.19438409805298</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1264181137085</t>
+    <t xml:space="preserve">3.12641835212708</t>
   </si>
   <si>
     <t xml:space="preserve">3.05845236778259</t>
@@ -1415,7 +1415,7 @@
     <t xml:space="preserve">3.09243535995483</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16040086746216</t>
+    <t xml:space="preserve">3.16040110588074</t>
   </si>
   <si>
     <t xml:space="preserve">3.21137523651123</t>
@@ -1427,7 +1427,7 @@
     <t xml:space="preserve">3.26234912872314</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33031487464905</t>
+    <t xml:space="preserve">3.33031511306763</t>
   </si>
   <si>
     <t xml:space="preserve">3.22836637496948</t>
@@ -1439,16 +1439,16 @@
     <t xml:space="preserve">3.14340949058533</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10942697525024</t>
+    <t xml:space="preserve">3.10942673683167</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27934098243713</t>
+    <t xml:space="preserve">3.27934074401855</t>
   </si>
   <si>
-    <t xml:space="preserve">3.48323774337769</t>
+    <t xml:space="preserve">3.48323750495911</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39828038215637</t>
+    <t xml:space="preserve">3.39828062057495</t>
   </si>
   <si>
     <t xml:space="preserve">3.46624612808228</t>
@@ -1460,10 +1460,10 @@
     <t xml:space="preserve">3.34730648994446</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24535799026489</t>
+    <t xml:space="preserve">3.24535775184631</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02446985244751</t>
+    <t xml:space="preserve">3.02446961402893</t>
   </si>
   <si>
     <t xml:space="preserve">3.16417121887207</t>
@@ -1496,13 +1496,10 @@
     <t xml:space="preserve">3.09405112266541</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07652139663696</t>
+    <t xml:space="preserve">3.07652115821838</t>
   </si>
   <si>
     <t xml:space="preserve">3.06775617599487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04146122932434</t>
   </si>
   <si>
     <t xml:space="preserve">3.00640106201172</t>
@@ -1523,13 +1520,13 @@
     <t xml:space="preserve">2.96257615089417</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86616063117981</t>
+    <t xml:space="preserve">2.86616086959839</t>
   </si>
   <si>
     <t xml:space="preserve">2.91875076293945</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80480575561523</t>
+    <t xml:space="preserve">2.80480551719666</t>
   </si>
   <si>
     <t xml:space="preserve">2.82233572006226</t>
@@ -1541,7 +1538,7 @@
     <t xml:space="preserve">2.95381093025208</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83110046386719</t>
+    <t xml:space="preserve">2.83110070228577</t>
   </si>
   <si>
     <t xml:space="preserve">2.93628096580505</t>
@@ -1565,10 +1562,10 @@
     <t xml:space="preserve">2.83986568450928</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68209552764893</t>
+    <t xml:space="preserve">2.68209528923035</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69086027145386</t>
+    <t xml:space="preserve">2.69086050987244</t>
   </si>
   <si>
     <t xml:space="preserve">2.66456532478333</t>
@@ -1586,7 +1583,7 @@
     <t xml:space="preserve">2.76974582672119</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79604053497314</t>
+    <t xml:space="preserve">2.79604077339172</t>
   </si>
   <si>
     <t xml:space="preserve">2.84863090515137</t>
@@ -1683,9 +1680,6 @@
   </si>
   <si>
     <t xml:space="preserve">2.85962271690369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80480551719666</t>
   </si>
   <si>
     <t xml:space="preserve">2.89616751670837</t>
@@ -44996,7 +44990,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G1642" t="s">
-        <v>496</v>
+        <v>462</v>
       </c>
       <c r="H1642" t="s">
         <v>9</v>
@@ -45022,7 +45016,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G1643" t="s">
-        <v>496</v>
+        <v>462</v>
       </c>
       <c r="H1643" t="s">
         <v>9</v>
@@ -45048,7 +45042,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G1644" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="H1644" t="s">
         <v>9</v>
@@ -45100,7 +45094,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G1646" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="H1646" t="s">
         <v>9</v>
@@ -45126,7 +45120,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1647" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="H1647" t="s">
         <v>9</v>
@@ -45152,7 +45146,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G1648" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="H1648" t="s">
         <v>9</v>
@@ -45204,7 +45198,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1650" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="H1650" t="s">
         <v>9</v>
@@ -45230,7 +45224,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1651" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="H1651" t="s">
         <v>9</v>
@@ -45256,7 +45250,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1652" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="H1652" t="s">
         <v>9</v>
@@ -45282,7 +45276,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G1653" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="H1653" t="s">
         <v>9</v>
@@ -45308,7 +45302,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G1654" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H1654" t="s">
         <v>9</v>
@@ -45334,7 +45328,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G1655" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="H1655" t="s">
         <v>9</v>
@@ -45360,7 +45354,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G1656" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="H1656" t="s">
         <v>9</v>
@@ -45386,7 +45380,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G1657" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="H1657" t="s">
         <v>9</v>
@@ -45438,7 +45432,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G1659" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="H1659" t="s">
         <v>9</v>
@@ -45464,7 +45458,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1660" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="H1660" t="s">
         <v>9</v>
@@ -45490,7 +45484,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G1661" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="H1661" t="s">
         <v>9</v>
@@ -45516,7 +45510,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1662" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="H1662" t="s">
         <v>9</v>
@@ -45542,7 +45536,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1663" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="H1663" t="s">
         <v>9</v>
@@ -45568,7 +45562,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1664" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="H1664" t="s">
         <v>9</v>
@@ -45594,7 +45588,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1665" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="H1665" t="s">
         <v>9</v>
@@ -45620,7 +45614,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1666" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="H1666" t="s">
         <v>9</v>
@@ -45646,7 +45640,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1667" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="H1667" t="s">
         <v>9</v>
@@ -45672,7 +45666,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G1668" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H1668" t="s">
         <v>9</v>
@@ -45698,7 +45692,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1669" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="H1669" t="s">
         <v>9</v>
@@ -45724,7 +45718,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1670" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="H1670" t="s">
         <v>9</v>
@@ -45750,7 +45744,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G1671" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="H1671" t="s">
         <v>9</v>
@@ -45776,7 +45770,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1672" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="H1672" t="s">
         <v>9</v>
@@ -45802,7 +45796,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G1673" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="H1673" t="s">
         <v>9</v>
@@ -45828,7 +45822,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G1674" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="H1674" t="s">
         <v>9</v>
@@ -45854,7 +45848,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G1675" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H1675" t="s">
         <v>9</v>
@@ -45880,7 +45874,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G1676" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="H1676" t="s">
         <v>9</v>
@@ -45906,7 +45900,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1677" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="H1677" t="s">
         <v>9</v>
@@ -45932,7 +45926,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G1678" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="H1678" t="s">
         <v>9</v>
@@ -45958,7 +45952,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G1679" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="H1679" t="s">
         <v>9</v>
@@ -45984,7 +45978,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1680" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="H1680" t="s">
         <v>9</v>
@@ -46010,7 +46004,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G1681" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H1681" t="s">
         <v>9</v>
@@ -46062,7 +46056,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1683" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="H1683" t="s">
         <v>9</v>
@@ -46088,7 +46082,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G1684" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="H1684" t="s">
         <v>9</v>
@@ -46140,7 +46134,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G1686" t="s">
-        <v>496</v>
+        <v>462</v>
       </c>
       <c r="H1686" t="s">
         <v>9</v>
@@ -46166,7 +46160,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G1687" t="s">
-        <v>496</v>
+        <v>462</v>
       </c>
       <c r="H1687" t="s">
         <v>9</v>
@@ -46192,7 +46186,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G1688" t="s">
-        <v>496</v>
+        <v>462</v>
       </c>
       <c r="H1688" t="s">
         <v>9</v>
@@ -46218,7 +46212,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1689" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="H1689" t="s">
         <v>9</v>
@@ -46244,7 +46238,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G1690" t="s">
-        <v>496</v>
+        <v>462</v>
       </c>
       <c r="H1690" t="s">
         <v>9</v>
@@ -46270,7 +46264,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G1691" t="s">
-        <v>496</v>
+        <v>462</v>
       </c>
       <c r="H1691" t="s">
         <v>9</v>
@@ -46296,7 +46290,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G1692" t="s">
-        <v>496</v>
+        <v>462</v>
       </c>
       <c r="H1692" t="s">
         <v>9</v>
@@ -46322,7 +46316,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1693" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="H1693" t="s">
         <v>9</v>
@@ -46348,7 +46342,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G1694" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="H1694" t="s">
         <v>9</v>
@@ -46374,7 +46368,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G1695" t="s">
-        <v>496</v>
+        <v>462</v>
       </c>
       <c r="H1695" t="s">
         <v>9</v>
@@ -46452,7 +46446,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G1698" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="H1698" t="s">
         <v>9</v>
@@ -46478,7 +46472,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G1699" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="H1699" t="s">
         <v>9</v>
@@ -46504,7 +46498,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1700" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="H1700" t="s">
         <v>9</v>
@@ -46556,7 +46550,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G1702" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="H1702" t="s">
         <v>9</v>
@@ -46582,7 +46576,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1703" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="H1703" t="s">
         <v>9</v>
@@ -46608,7 +46602,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G1704" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="H1704" t="s">
         <v>9</v>
@@ -46634,7 +46628,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G1705" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="H1705" t="s">
         <v>9</v>
@@ -46660,7 +46654,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1706" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="H1706" t="s">
         <v>9</v>
@@ -46686,7 +46680,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1707" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="H1707" t="s">
         <v>9</v>
@@ -46790,7 +46784,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G1711" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="H1711" t="s">
         <v>9</v>
@@ -46816,7 +46810,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1712" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="H1712" t="s">
         <v>9</v>
@@ -46842,7 +46836,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G1713" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="H1713" t="s">
         <v>9</v>
@@ -46868,7 +46862,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G1714" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="H1714" t="s">
         <v>9</v>
@@ -46894,7 +46888,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G1715" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="H1715" t="s">
         <v>9</v>
@@ -46920,7 +46914,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1716" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="H1716" t="s">
         <v>9</v>
@@ -46946,7 +46940,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G1717" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="H1717" t="s">
         <v>9</v>
@@ -46972,7 +46966,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G1718" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="H1718" t="s">
         <v>9</v>
@@ -46998,7 +46992,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1719" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="H1719" t="s">
         <v>9</v>
@@ -47024,7 +47018,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G1720" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H1720" t="s">
         <v>9</v>
@@ -47050,7 +47044,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G1721" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="H1721" t="s">
         <v>9</v>
@@ -47076,7 +47070,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G1722" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="H1722" t="s">
         <v>9</v>
@@ -47102,7 +47096,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G1723" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="H1723" t="s">
         <v>9</v>
@@ -47128,7 +47122,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G1724" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="H1724" t="s">
         <v>9</v>
@@ -47154,7 +47148,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G1725" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="H1725" t="s">
         <v>9</v>
@@ -47180,7 +47174,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G1726" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="H1726" t="s">
         <v>9</v>
@@ -47206,7 +47200,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G1727" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="H1727" t="s">
         <v>9</v>
@@ -47232,7 +47226,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G1728" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="H1728" t="s">
         <v>9</v>
@@ -47258,7 +47252,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G1729" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="H1729" t="s">
         <v>9</v>
@@ -47284,7 +47278,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G1730" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="H1730" t="s">
         <v>9</v>
@@ -47310,7 +47304,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G1731" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H1731" t="s">
         <v>9</v>
@@ -47336,7 +47330,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G1732" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H1732" t="s">
         <v>9</v>
@@ -47362,7 +47356,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G1733" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="H1733" t="s">
         <v>9</v>
@@ -47388,7 +47382,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1734" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="H1734" t="s">
         <v>9</v>
@@ -47414,7 +47408,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1735" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="H1735" t="s">
         <v>9</v>
@@ -47440,7 +47434,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G1736" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="H1736" t="s">
         <v>9</v>
@@ -47466,7 +47460,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1737" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="H1737" t="s">
         <v>9</v>
@@ -47492,7 +47486,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G1738" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="H1738" t="s">
         <v>9</v>
@@ -47518,7 +47512,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G1739" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="H1739" t="s">
         <v>9</v>
@@ -47544,7 +47538,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G1740" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="H1740" t="s">
         <v>9</v>
@@ -47570,7 +47564,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1741" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="H1741" t="s">
         <v>9</v>
@@ -47596,7 +47590,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1742" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="H1742" t="s">
         <v>9</v>
@@ -47622,7 +47616,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G1743" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H1743" t="s">
         <v>9</v>
@@ -47648,7 +47642,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G1744" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="H1744" t="s">
         <v>9</v>
@@ -47674,7 +47668,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G1745" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="H1745" t="s">
         <v>9</v>
@@ -47700,7 +47694,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G1746" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="H1746" t="s">
         <v>9</v>
@@ -47726,7 +47720,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1747" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="H1747" t="s">
         <v>9</v>
@@ -47752,7 +47746,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G1748" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="H1748" t="s">
         <v>9</v>
@@ -47778,7 +47772,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G1749" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H1749" t="s">
         <v>9</v>
@@ -47804,7 +47798,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1750" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="H1750" t="s">
         <v>9</v>
@@ -47830,7 +47824,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G1751" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="H1751" t="s">
         <v>9</v>
@@ -47856,7 +47850,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1752" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="H1752" t="s">
         <v>9</v>
@@ -47882,7 +47876,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G1753" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="H1753" t="s">
         <v>9</v>
@@ -47908,7 +47902,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G1754" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H1754" t="s">
         <v>9</v>
@@ -47934,7 +47928,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G1755" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="H1755" t="s">
         <v>9</v>
@@ -47960,7 +47954,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G1756" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="H1756" t="s">
         <v>9</v>
@@ -47986,7 +47980,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1757" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="H1757" t="s">
         <v>9</v>
@@ -48012,7 +48006,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G1758" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H1758" t="s">
         <v>9</v>
@@ -48038,7 +48032,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G1759" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="H1759" t="s">
         <v>9</v>
@@ -48064,7 +48058,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G1760" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="H1760" t="s">
         <v>9</v>
@@ -48090,7 +48084,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G1761" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="H1761" t="s">
         <v>9</v>
@@ -48116,7 +48110,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G1762" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="H1762" t="s">
         <v>9</v>
@@ -48142,7 +48136,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1763" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="H1763" t="s">
         <v>9</v>
@@ -48168,7 +48162,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G1764" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="H1764" t="s">
         <v>9</v>
@@ -48194,7 +48188,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G1765" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="H1765" t="s">
         <v>9</v>
@@ -48220,7 +48214,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G1766" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="H1766" t="s">
         <v>9</v>
@@ -48246,7 +48240,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G1767" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="H1767" t="s">
         <v>9</v>
@@ -48272,7 +48266,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G1768" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="H1768" t="s">
         <v>9</v>
@@ -48298,7 +48292,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G1769" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="H1769" t="s">
         <v>9</v>
@@ -48324,7 +48318,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G1770" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="H1770" t="s">
         <v>9</v>
@@ -48350,7 +48344,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G1771" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="H1771" t="s">
         <v>9</v>
@@ -48376,7 +48370,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1772" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="H1772" t="s">
         <v>9</v>
@@ -48402,7 +48396,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1773" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="H1773" t="s">
         <v>9</v>
@@ -48428,7 +48422,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1774" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="H1774" t="s">
         <v>9</v>
@@ -48454,7 +48448,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1775" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="H1775" t="s">
         <v>9</v>
@@ -48480,7 +48474,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1776" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="H1776" t="s">
         <v>9</v>
@@ -48506,7 +48500,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1777" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="H1777" t="s">
         <v>9</v>
@@ -48532,7 +48526,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1778" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="H1778" t="s">
         <v>9</v>
@@ -48558,7 +48552,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1779" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="H1779" t="s">
         <v>9</v>
@@ -48584,7 +48578,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1780" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="H1780" t="s">
         <v>9</v>
@@ -48610,7 +48604,7 @@
         <v>3.25</v>
       </c>
       <c r="G1781" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="H1781" t="s">
         <v>9</v>
@@ -48636,7 +48630,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G1782" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H1782" t="s">
         <v>9</v>
@@ -48662,7 +48656,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G1783" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="H1783" t="s">
         <v>9</v>
@@ -48688,7 +48682,7 @@
         <v>3.25</v>
       </c>
       <c r="G1784" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="H1784" t="s">
         <v>9</v>
@@ -48714,7 +48708,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G1785" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H1785" t="s">
         <v>9</v>
@@ -48740,7 +48734,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G1786" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="H1786" t="s">
         <v>9</v>
@@ -48766,7 +48760,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G1787" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="H1787" t="s">
         <v>9</v>
@@ -48792,7 +48786,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G1788" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="H1788" t="s">
         <v>9</v>
@@ -48818,7 +48812,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1789" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="H1789" t="s">
         <v>9</v>
@@ -48844,7 +48838,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1790" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="H1790" t="s">
         <v>9</v>
@@ -48870,7 +48864,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1791" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="H1791" t="s">
         <v>9</v>
@@ -48896,7 +48890,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1792" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="H1792" t="s">
         <v>9</v>
@@ -48922,7 +48916,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G1793" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="H1793" t="s">
         <v>9</v>
@@ -48948,7 +48942,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1794" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="H1794" t="s">
         <v>9</v>
@@ -48974,7 +48968,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G1795" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="H1795" t="s">
         <v>9</v>
@@ -49000,7 +48994,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G1796" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H1796" t="s">
         <v>9</v>
@@ -49026,7 +49020,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1797" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="H1797" t="s">
         <v>9</v>
@@ -49052,7 +49046,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G1798" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H1798" t="s">
         <v>9</v>
@@ -49078,7 +49072,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G1799" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="H1799" t="s">
         <v>9</v>
@@ -49104,7 +49098,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G1800" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H1800" t="s">
         <v>9</v>
@@ -49130,7 +49124,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1801" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="H1801" t="s">
         <v>9</v>
@@ -49156,7 +49150,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G1802" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="H1802" t="s">
         <v>9</v>
@@ -49182,7 +49176,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G1803" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="H1803" t="s">
         <v>9</v>
@@ -49208,7 +49202,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G1804" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="H1804" t="s">
         <v>9</v>
@@ -49234,7 +49228,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G1805" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="H1805" t="s">
         <v>9</v>
@@ -49260,7 +49254,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G1806" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="H1806" t="s">
         <v>9</v>
@@ -49286,7 +49280,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G1807" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="H1807" t="s">
         <v>9</v>
@@ -49312,7 +49306,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G1808" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="H1808" t="s">
         <v>9</v>
@@ -49338,7 +49332,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1809" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="H1809" t="s">
         <v>9</v>
@@ -49364,7 +49358,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G1810" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="H1810" t="s">
         <v>9</v>
@@ -49390,7 +49384,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1811" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="H1811" t="s">
         <v>9</v>
@@ -49416,7 +49410,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G1812" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="H1812" t="s">
         <v>9</v>
@@ -49442,7 +49436,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G1813" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="H1813" t="s">
         <v>9</v>
@@ -49468,7 +49462,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G1814" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H1814" t="s">
         <v>9</v>
@@ -49494,7 +49488,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1815" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="H1815" t="s">
         <v>9</v>
@@ -49520,7 +49514,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G1816" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="H1816" t="s">
         <v>9</v>
@@ -49546,7 +49540,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G1817" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="H1817" t="s">
         <v>9</v>
@@ -49572,7 +49566,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G1818" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="H1818" t="s">
         <v>9</v>
@@ -49598,7 +49592,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1819" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="H1819" t="s">
         <v>9</v>
@@ -49624,7 +49618,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1820" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="H1820" t="s">
         <v>9</v>
@@ -49650,7 +49644,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1821" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="H1821" t="s">
         <v>9</v>
@@ -49676,7 +49670,7 @@
         <v>3.25</v>
       </c>
       <c r="G1822" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="H1822" t="s">
         <v>9</v>
@@ -49702,7 +49696,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G1823" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="H1823" t="s">
         <v>9</v>
@@ -49728,7 +49722,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G1824" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H1824" t="s">
         <v>9</v>
@@ -49754,7 +49748,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G1825" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="H1825" t="s">
         <v>9</v>
@@ -49780,7 +49774,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G1826" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="H1826" t="s">
         <v>9</v>
@@ -49806,7 +49800,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G1827" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="H1827" t="s">
         <v>9</v>
@@ -49832,7 +49826,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G1828" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="H1828" t="s">
         <v>9</v>
@@ -49858,7 +49852,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G1829" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="H1829" t="s">
         <v>9</v>
@@ -49884,7 +49878,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1830" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="H1830" t="s">
         <v>9</v>
@@ -49910,7 +49904,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G1831" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="H1831" t="s">
         <v>9</v>
@@ -49936,7 +49930,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1832" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="H1832" t="s">
         <v>9</v>
@@ -49962,7 +49956,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G1833" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H1833" t="s">
         <v>9</v>
@@ -49988,7 +49982,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G1834" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H1834" t="s">
         <v>9</v>
@@ -50014,7 +50008,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G1835" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="H1835" t="s">
         <v>9</v>
@@ -50040,7 +50034,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G1836" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="H1836" t="s">
         <v>9</v>
@@ -50066,7 +50060,7 @@
         <v>3.25</v>
       </c>
       <c r="G1837" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="H1837" t="s">
         <v>9</v>
@@ -50092,7 +50086,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G1838" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="H1838" t="s">
         <v>9</v>
@@ -50118,7 +50112,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G1839" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="H1839" t="s">
         <v>9</v>
@@ -50144,7 +50138,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1840" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="H1840" t="s">
         <v>9</v>
@@ -50170,7 +50164,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G1841" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="H1841" t="s">
         <v>9</v>
@@ -50196,7 +50190,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G1842" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="H1842" t="s">
         <v>9</v>
@@ -50222,7 +50216,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G1843" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H1843" t="s">
         <v>9</v>
@@ -50248,7 +50242,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G1844" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="H1844" t="s">
         <v>9</v>
@@ -50274,7 +50268,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1845" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="H1845" t="s">
         <v>9</v>
@@ -50300,7 +50294,7 @@
         <v>3.25</v>
       </c>
       <c r="G1846" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="H1846" t="s">
         <v>9</v>
@@ -50326,7 +50320,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1847" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="H1847" t="s">
         <v>9</v>
@@ -50352,7 +50346,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G1848" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="H1848" t="s">
         <v>9</v>
@@ -50378,7 +50372,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G1849" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H1849" t="s">
         <v>9</v>
@@ -50404,7 +50398,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1850" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="H1850" t="s">
         <v>9</v>
@@ -50430,7 +50424,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1851" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="H1851" t="s">
         <v>9</v>
@@ -50456,7 +50450,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1852" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="H1852" t="s">
         <v>9</v>
@@ -50482,7 +50476,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G1853" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="H1853" t="s">
         <v>9</v>
@@ -50508,7 +50502,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1854" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="H1854" t="s">
         <v>9</v>
@@ -50534,7 +50528,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1855" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="H1855" t="s">
         <v>9</v>
@@ -50560,7 +50554,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G1856" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="H1856" t="s">
         <v>9</v>
@@ -50586,7 +50580,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1857" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="H1857" t="s">
         <v>9</v>
@@ -50612,7 +50606,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1858" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="H1858" t="s">
         <v>9</v>
@@ -50638,7 +50632,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G1859" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="H1859" t="s">
         <v>9</v>
@@ -50664,7 +50658,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G1860" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="H1860" t="s">
         <v>9</v>
@@ -50690,7 +50684,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G1861" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="H1861" t="s">
         <v>9</v>
@@ -50716,7 +50710,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G1862" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H1862" t="s">
         <v>9</v>
@@ -50742,7 +50736,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1863" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="H1863" t="s">
         <v>9</v>
@@ -50768,7 +50762,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G1864" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="H1864" t="s">
         <v>9</v>
@@ -50794,7 +50788,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G1865" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="H1865" t="s">
         <v>9</v>
@@ -50820,7 +50814,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G1866" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H1866" t="s">
         <v>9</v>
@@ -50846,7 +50840,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G1867" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H1867" t="s">
         <v>9</v>
@@ -50872,7 +50866,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G1868" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="H1868" t="s">
         <v>9</v>
@@ -50898,7 +50892,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G1869" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="H1869" t="s">
         <v>9</v>
@@ -50924,7 +50918,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G1870" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="H1870" t="s">
         <v>9</v>
@@ -50950,7 +50944,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G1871" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="H1871" t="s">
         <v>9</v>
@@ -50976,7 +50970,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1872" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="H1872" t="s">
         <v>9</v>
@@ -51002,7 +50996,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1873" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="H1873" t="s">
         <v>9</v>
@@ -51028,7 +51022,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1874" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="H1874" t="s">
         <v>9</v>
@@ -51054,7 +51048,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G1875" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H1875" t="s">
         <v>9</v>
@@ -51080,7 +51074,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1876" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="H1876" t="s">
         <v>9</v>
@@ -51106,7 +51100,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1877" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="H1877" t="s">
         <v>9</v>
@@ -51132,7 +51126,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G1878" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H1878" t="s">
         <v>9</v>
@@ -51158,7 +51152,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G1879" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="H1879" t="s">
         <v>9</v>
@@ -51184,7 +51178,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G1880" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="H1880" t="s">
         <v>9</v>
@@ -51210,7 +51204,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G1881" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H1881" t="s">
         <v>9</v>
@@ -51236,7 +51230,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G1882" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H1882" t="s">
         <v>9</v>
@@ -51262,7 +51256,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G1883" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="H1883" t="s">
         <v>9</v>
@@ -51288,7 +51282,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G1884" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H1884" t="s">
         <v>9</v>
@@ -51314,7 +51308,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1885" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H1885" t="s">
         <v>9</v>
@@ -51340,7 +51334,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1886" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H1886" t="s">
         <v>9</v>
@@ -51366,7 +51360,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1887" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H1887" t="s">
         <v>9</v>
@@ -51392,7 +51386,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1888" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H1888" t="s">
         <v>9</v>
@@ -51418,7 +51412,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G1889" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="H1889" t="s">
         <v>9</v>
@@ -51444,7 +51438,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1890" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H1890" t="s">
         <v>9</v>
@@ -51470,7 +51464,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1891" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H1891" t="s">
         <v>9</v>
@@ -51496,7 +51490,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G1892" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="H1892" t="s">
         <v>9</v>
@@ -51522,7 +51516,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1893" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H1893" t="s">
         <v>9</v>
@@ -51548,7 +51542,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G1894" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H1894" t="s">
         <v>9</v>
@@ -51574,7 +51568,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1895" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H1895" t="s">
         <v>9</v>
@@ -51600,7 +51594,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1896" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H1896" t="s">
         <v>9</v>
@@ -51626,7 +51620,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1897" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H1897" t="s">
         <v>9</v>
@@ -51652,7 +51646,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1898" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H1898" t="s">
         <v>9</v>
@@ -51678,7 +51672,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1899" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H1899" t="s">
         <v>9</v>
@@ -51704,7 +51698,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1900" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H1900" t="s">
         <v>9</v>
@@ -51730,7 +51724,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1901" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H1901" t="s">
         <v>9</v>
@@ -51756,7 +51750,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1902" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H1902" t="s">
         <v>9</v>
@@ -51782,7 +51776,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G1903" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H1903" t="s">
         <v>9</v>
@@ -51808,7 +51802,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G1904" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="H1904" t="s">
         <v>9</v>
@@ -51834,7 +51828,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1905" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="H1905" t="s">
         <v>9</v>
@@ -51860,7 +51854,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1906" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H1906" t="s">
         <v>9</v>
@@ -51886,7 +51880,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1907" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H1907" t="s">
         <v>9</v>
@@ -51912,7 +51906,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1908" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H1908" t="s">
         <v>9</v>
@@ -51938,7 +51932,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1909" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H1909" t="s">
         <v>9</v>
@@ -51964,7 +51958,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G1910" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="H1910" t="s">
         <v>9</v>
@@ -51990,7 +51984,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1911" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H1911" t="s">
         <v>9</v>
@@ -52016,7 +52010,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1912" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="H1912" t="s">
         <v>9</v>
@@ -52042,7 +52036,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1913" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="H1913" t="s">
         <v>9</v>
@@ -52068,7 +52062,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1914" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="H1914" t="s">
         <v>9</v>
@@ -52094,7 +52088,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1915" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="H1915" t="s">
         <v>9</v>
@@ -52120,7 +52114,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1916" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H1916" t="s">
         <v>9</v>
@@ -52146,7 +52140,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1917" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="H1917" t="s">
         <v>9</v>
@@ -52172,7 +52166,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G1918" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="H1918" t="s">
         <v>9</v>
@@ -52198,7 +52192,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G1919" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H1919" t="s">
         <v>9</v>
@@ -52224,7 +52218,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G1920" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="H1920" t="s">
         <v>9</v>
@@ -52250,7 +52244,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1921" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="H1921" t="s">
         <v>9</v>
@@ -52276,7 +52270,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1922" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="H1922" t="s">
         <v>9</v>
@@ -52302,7 +52296,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G1923" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="H1923" t="s">
         <v>9</v>
@@ -52328,7 +52322,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G1924" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H1924" t="s">
         <v>9</v>
@@ -52354,7 +52348,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1925" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H1925" t="s">
         <v>9</v>
@@ -52380,7 +52374,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G1926" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="H1926" t="s">
         <v>9</v>
@@ -52406,7 +52400,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1927" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="H1927" t="s">
         <v>9</v>
@@ -52432,7 +52426,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G1928" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="H1928" t="s">
         <v>9</v>
@@ -52458,7 +52452,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G1929" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H1929" t="s">
         <v>9</v>
@@ -52484,7 +52478,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G1930" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="H1930" t="s">
         <v>9</v>
@@ -52510,7 +52504,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G1931" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="H1931" t="s">
         <v>9</v>
@@ -52536,7 +52530,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G1932" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="H1932" t="s">
         <v>9</v>
@@ -52562,7 +52556,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G1933" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H1933" t="s">
         <v>9</v>
@@ -52588,7 +52582,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G1934" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H1934" t="s">
         <v>9</v>
@@ -52614,7 +52608,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1935" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="H1935" t="s">
         <v>9</v>
@@ -52640,7 +52634,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1936" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="H1936" t="s">
         <v>9</v>
@@ -52666,7 +52660,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1937" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="H1937" t="s">
         <v>9</v>
@@ -52692,7 +52686,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1938" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H1938" t="s">
         <v>9</v>
@@ -52718,7 +52712,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1939" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H1939" t="s">
         <v>9</v>
@@ -52744,7 +52738,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G1940" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="H1940" t="s">
         <v>9</v>
@@ -52770,7 +52764,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1941" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="H1941" t="s">
         <v>9</v>
@@ -52796,7 +52790,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1942" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="H1942" t="s">
         <v>9</v>
@@ -52822,7 +52816,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1943" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="H1943" t="s">
         <v>9</v>
@@ -52848,7 +52842,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1944" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="H1944" t="s">
         <v>9</v>
@@ -52874,7 +52868,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1945" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H1945" t="s">
         <v>9</v>
@@ -52900,7 +52894,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G1946" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="H1946" t="s">
         <v>9</v>
@@ -52926,7 +52920,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1947" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="H1947" t="s">
         <v>9</v>
@@ -52952,7 +52946,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1948" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="H1948" t="s">
         <v>9</v>
@@ -52978,7 +52972,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1949" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="H1949" t="s">
         <v>9</v>
@@ -53004,7 +52998,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G1950" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="H1950" t="s">
         <v>9</v>
@@ -53030,7 +53024,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G1951" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="H1951" t="s">
         <v>9</v>
@@ -53056,7 +53050,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1952" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="H1952" t="s">
         <v>9</v>
@@ -53082,7 +53076,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1953" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H1953" t="s">
         <v>9</v>
@@ -53108,7 +53102,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1954" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H1954" t="s">
         <v>9</v>
@@ -53134,7 +53128,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G1955" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="H1955" t="s">
         <v>9</v>
@@ -53160,7 +53154,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G1956" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="H1956" t="s">
         <v>9</v>
@@ -53186,7 +53180,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G1957" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H1957" t="s">
         <v>9</v>
@@ -53212,7 +53206,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1958" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H1958" t="s">
         <v>9</v>
@@ -53238,7 +53232,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1959" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H1959" t="s">
         <v>9</v>
@@ -53264,7 +53258,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1960" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H1960" t="s">
         <v>9</v>
@@ -53290,7 +53284,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G1961" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H1961" t="s">
         <v>9</v>
@@ -53316,7 +53310,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G1962" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="H1962" t="s">
         <v>9</v>
@@ -53342,7 +53336,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G1963" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="H1963" t="s">
         <v>9</v>
@@ -53368,7 +53362,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G1964" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H1964" t="s">
         <v>9</v>
@@ -53394,7 +53388,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G1965" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H1965" t="s">
         <v>9</v>
@@ -53420,7 +53414,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G1966" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H1966" t="s">
         <v>9</v>
@@ -53446,7 +53440,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1967" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="H1967" t="s">
         <v>9</v>
@@ -53472,7 +53466,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G1968" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="H1968" t="s">
         <v>9</v>
@@ -53498,7 +53492,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G1969" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H1969" t="s">
         <v>9</v>
@@ -53524,7 +53518,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G1970" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H1970" t="s">
         <v>9</v>
@@ -53550,7 +53544,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G1971" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H1971" t="s">
         <v>9</v>
@@ -53576,7 +53570,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G1972" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="H1972" t="s">
         <v>9</v>
@@ -53602,7 +53596,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G1973" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H1973" t="s">
         <v>9</v>
@@ -53628,7 +53622,7 @@
         <v>3</v>
       </c>
       <c r="G1974" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="H1974" t="s">
         <v>9</v>
@@ -53654,7 +53648,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1975" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="H1975" t="s">
         <v>9</v>
@@ -53680,7 +53674,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G1976" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="H1976" t="s">
         <v>9</v>
@@ -53706,7 +53700,7 @@
         <v>3</v>
       </c>
       <c r="G1977" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="H1977" t="s">
         <v>9</v>
@@ -53732,7 +53726,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G1978" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="H1978" t="s">
         <v>9</v>
@@ -53758,7 +53752,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G1979" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="H1979" t="s">
         <v>9</v>
@@ -53784,7 +53778,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1980" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="H1980" t="s">
         <v>9</v>
@@ -53810,7 +53804,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G1981" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="H1981" t="s">
         <v>9</v>
@@ -53836,7 +53830,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G1982" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="H1982" t="s">
         <v>9</v>
@@ -53862,7 +53856,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1983" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="H1983" t="s">
         <v>9</v>
@@ -53888,7 +53882,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1984" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="H1984" t="s">
         <v>9</v>
@@ -53914,7 +53908,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G1985" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="H1985" t="s">
         <v>9</v>
@@ -53940,7 +53934,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1986" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="H1986" t="s">
         <v>9</v>
@@ -53966,7 +53960,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1987" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="H1987" t="s">
         <v>9</v>
@@ -53992,7 +53986,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G1988" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="H1988" t="s">
         <v>9</v>
@@ -54018,7 +54012,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G1989" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="H1989" t="s">
         <v>9</v>
@@ -54044,7 +54038,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G1990" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="H1990" t="s">
         <v>9</v>
@@ -54070,7 +54064,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G1991" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H1991" t="s">
         <v>9</v>
@@ -54096,7 +54090,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1992" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="H1992" t="s">
         <v>9</v>
@@ -54122,7 +54116,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1993" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="H1993" t="s">
         <v>9</v>
@@ -54148,7 +54142,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1994" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="H1994" t="s">
         <v>9</v>
@@ -54174,7 +54168,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1995" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="H1995" t="s">
         <v>9</v>
@@ -54200,7 +54194,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G1996" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="H1996" t="s">
         <v>9</v>
@@ -54226,7 +54220,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G1997" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="H1997" t="s">
         <v>9</v>
@@ -54252,7 +54246,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1998" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="H1998" t="s">
         <v>9</v>
@@ -54278,7 +54272,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1999" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="H1999" t="s">
         <v>9</v>
@@ -54304,7 +54298,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G2000" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="H2000" t="s">
         <v>9</v>
@@ -54330,7 +54324,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G2001" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="H2001" t="s">
         <v>9</v>
@@ -54356,7 +54350,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G2002" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="H2002" t="s">
         <v>9</v>
@@ -54382,7 +54376,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G2003" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="H2003" t="s">
         <v>9</v>
@@ -54408,7 +54402,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G2004" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="H2004" t="s">
         <v>9</v>
@@ -54434,7 +54428,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G2005" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="H2005" t="s">
         <v>9</v>
@@ -54460,7 +54454,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G2006" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="H2006" t="s">
         <v>9</v>
@@ -54486,7 +54480,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G2007" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="H2007" t="s">
         <v>9</v>
@@ -54512,7 +54506,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G2008" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="H2008" t="s">
         <v>9</v>
@@ -54538,7 +54532,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G2009" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="H2009" t="s">
         <v>9</v>
@@ -54564,7 +54558,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G2010" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="H2010" t="s">
         <v>9</v>
@@ -54590,7 +54584,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G2011" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H2011" t="s">
         <v>9</v>
@@ -54616,7 +54610,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G2012" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="H2012" t="s">
         <v>9</v>
@@ -54642,7 +54636,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G2013" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="H2013" t="s">
         <v>9</v>
@@ -54668,7 +54662,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2014" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="H2014" t="s">
         <v>9</v>
@@ -54694,7 +54688,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G2015" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H2015" t="s">
         <v>9</v>
@@ -54720,7 +54714,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G2016" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H2016" t="s">
         <v>9</v>
@@ -54746,7 +54740,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G2017" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H2017" t="s">
         <v>9</v>
@@ -54772,7 +54766,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2018" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="H2018" t="s">
         <v>9</v>
@@ -54798,7 +54792,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2019" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="H2019" t="s">
         <v>9</v>
@@ -54824,7 +54818,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G2020" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="H2020" t="s">
         <v>9</v>
@@ -54850,7 +54844,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2021" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="H2021" t="s">
         <v>9</v>
@@ -54876,7 +54870,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G2022" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="H2022" t="s">
         <v>9</v>
@@ -54902,7 +54896,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2023" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="H2023" t="s">
         <v>9</v>
@@ -54928,7 +54922,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2024" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="H2024" t="s">
         <v>9</v>
@@ -54954,7 +54948,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G2025" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H2025" t="s">
         <v>9</v>
@@ -54980,7 +54974,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G2026" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="H2026" t="s">
         <v>9</v>
@@ -55006,7 +55000,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2027" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="H2027" t="s">
         <v>9</v>
@@ -55032,7 +55026,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2028" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="H2028" t="s">
         <v>9</v>
@@ -55058,7 +55052,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G2029" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="H2029" t="s">
         <v>9</v>
@@ -55084,7 +55078,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2030" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="H2030" t="s">
         <v>9</v>
@@ -55110,7 +55104,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G2031" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H2031" t="s">
         <v>9</v>
@@ -55136,7 +55130,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G2032" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H2032" t="s">
         <v>9</v>
@@ -55162,7 +55156,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G2033" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="H2033" t="s">
         <v>9</v>
@@ -55188,7 +55182,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G2034" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="H2034" t="s">
         <v>9</v>
@@ -55214,7 +55208,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G2035" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H2035" t="s">
         <v>9</v>
@@ -55240,7 +55234,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2036" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="H2036" t="s">
         <v>9</v>
@@ -55266,7 +55260,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G2037" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="H2037" t="s">
         <v>9</v>
@@ -55292,7 +55286,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G2038" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H2038" t="s">
         <v>9</v>
@@ -55318,7 +55312,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2039" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="H2039" t="s">
         <v>9</v>
@@ -55344,7 +55338,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G2040" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="H2040" t="s">
         <v>9</v>
@@ -55370,7 +55364,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G2041" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="H2041" t="s">
         <v>9</v>
@@ -55396,7 +55390,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G2042" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H2042" t="s">
         <v>9</v>
@@ -55422,7 +55416,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G2043" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H2043" t="s">
         <v>9</v>
@@ -55448,7 +55442,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2044" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="H2044" t="s">
         <v>9</v>
@@ -55474,7 +55468,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2045" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="H2045" t="s">
         <v>9</v>
@@ -55500,7 +55494,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2046" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="H2046" t="s">
         <v>9</v>
@@ -55526,7 +55520,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G2047" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="H2047" t="s">
         <v>9</v>
@@ -55552,7 +55546,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2048" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="H2048" t="s">
         <v>9</v>
@@ -55578,7 +55572,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2049" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="H2049" t="s">
         <v>9</v>
@@ -55604,7 +55598,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2050" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="H2050" t="s">
         <v>9</v>
@@ -55630,7 +55624,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G2051" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="H2051" t="s">
         <v>9</v>
@@ -55656,7 +55650,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G2052" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H2052" t="s">
         <v>9</v>
@@ -55682,7 +55676,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G2053" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H2053" t="s">
         <v>9</v>
@@ -55708,7 +55702,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2054" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="H2054" t="s">
         <v>9</v>
@@ -55734,7 +55728,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G2055" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H2055" t="s">
         <v>9</v>
@@ -55760,7 +55754,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2056" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="H2056" t="s">
         <v>9</v>
@@ -55786,7 +55780,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2057" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="H2057" t="s">
         <v>9</v>
@@ -55812,7 +55806,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G2058" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H2058" t="s">
         <v>9</v>
@@ -55838,7 +55832,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G2059" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H2059" t="s">
         <v>9</v>
@@ -55864,7 +55858,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2060" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="H2060" t="s">
         <v>9</v>
@@ -55890,7 +55884,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2061" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="H2061" t="s">
         <v>9</v>
@@ -55916,7 +55910,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2062" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="H2062" t="s">
         <v>9</v>
@@ -55942,7 +55936,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G2063" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="H2063" t="s">
         <v>9</v>
@@ -55968,7 +55962,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G2064" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="H2064" t="s">
         <v>9</v>
@@ -55994,7 +55988,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G2065" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="H2065" t="s">
         <v>9</v>
@@ -56020,7 +56014,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G2066" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H2066" t="s">
         <v>9</v>
@@ -56046,7 +56040,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G2067" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H2067" t="s">
         <v>9</v>
@@ -56072,7 +56066,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G2068" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H2068" t="s">
         <v>9</v>
@@ -56098,7 +56092,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G2069" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H2069" t="s">
         <v>9</v>
@@ -56124,7 +56118,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G2070" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="H2070" t="s">
         <v>9</v>
@@ -56150,7 +56144,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G2071" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H2071" t="s">
         <v>9</v>
@@ -56176,7 +56170,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G2072" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="H2072" t="s">
         <v>9</v>
@@ -56202,7 +56196,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G2073" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H2073" t="s">
         <v>9</v>
@@ -56228,7 +56222,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2074" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="H2074" t="s">
         <v>9</v>
@@ -56254,7 +56248,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G2075" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H2075" t="s">
         <v>9</v>
@@ -56280,7 +56274,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G2076" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H2076" t="s">
         <v>9</v>
@@ -56306,7 +56300,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G2077" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H2077" t="s">
         <v>9</v>
@@ -56332,7 +56326,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G2078" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="H2078" t="s">
         <v>9</v>
@@ -56358,7 +56352,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G2079" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H2079" t="s">
         <v>9</v>
@@ -56384,7 +56378,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G2080" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H2080" t="s">
         <v>9</v>
@@ -56410,7 +56404,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G2081" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="H2081" t="s">
         <v>9</v>
@@ -56436,7 +56430,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G2082" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="H2082" t="s">
         <v>9</v>
@@ -56462,7 +56456,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G2083" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H2083" t="s">
         <v>9</v>
@@ -56488,7 +56482,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G2084" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H2084" t="s">
         <v>9</v>
@@ -56514,7 +56508,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G2085" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H2085" t="s">
         <v>9</v>
@@ -56540,7 +56534,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G2086" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H2086" t="s">
         <v>9</v>
@@ -56566,7 +56560,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G2087" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H2087" t="s">
         <v>9</v>
@@ -56592,7 +56586,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G2088" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H2088" t="s">
         <v>9</v>
@@ -56618,7 +56612,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2089" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="H2089" t="s">
         <v>9</v>
@@ -56644,7 +56638,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G2090" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H2090" t="s">
         <v>9</v>
@@ -56670,7 +56664,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2091" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="H2091" t="s">
         <v>9</v>
@@ -56696,7 +56690,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2092" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="H2092" t="s">
         <v>9</v>
@@ -56722,7 +56716,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2093" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="H2093" t="s">
         <v>9</v>
@@ -56748,7 +56742,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G2094" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="H2094" t="s">
         <v>9</v>
@@ -56774,7 +56768,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G2095" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H2095" t="s">
         <v>9</v>
@@ -56800,7 +56794,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G2096" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H2096" t="s">
         <v>9</v>
@@ -56826,7 +56820,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G2097" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H2097" t="s">
         <v>9</v>
@@ -56852,7 +56846,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G2098" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="H2098" t="s">
         <v>9</v>
@@ -56878,7 +56872,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G2099" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="H2099" t="s">
         <v>9</v>
@@ -56904,7 +56898,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G2100" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="H2100" t="s">
         <v>9</v>
@@ -56930,7 +56924,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G2101" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="H2101" t="s">
         <v>9</v>
@@ -56956,7 +56950,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G2102" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="H2102" t="s">
         <v>9</v>
@@ -56982,7 +56976,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G2103" t="s">
-        <v>557</v>
+        <v>504</v>
       </c>
       <c r="H2103" t="s">
         <v>9</v>
@@ -57008,7 +57002,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G2104" t="s">
-        <v>557</v>
+        <v>504</v>
       </c>
       <c r="H2104" t="s">
         <v>9</v>
@@ -57034,7 +57028,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G2105" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="H2105" t="s">
         <v>9</v>
@@ -57060,7 +57054,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G2106" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="H2106" t="s">
         <v>9</v>
@@ -57086,7 +57080,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G2107" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="H2107" t="s">
         <v>9</v>
@@ -57112,7 +57106,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G2108" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="H2108" t="s">
         <v>9</v>
@@ -57138,7 +57132,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G2109" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="H2109" t="s">
         <v>9</v>
@@ -57164,7 +57158,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G2110" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="H2110" t="s">
         <v>9</v>
@@ -57190,7 +57184,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G2111" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="H2111" t="s">
         <v>9</v>
@@ -57216,7 +57210,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G2112" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="H2112" t="s">
         <v>9</v>
@@ -57242,7 +57236,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G2113" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H2113" t="s">
         <v>9</v>
@@ -57268,7 +57262,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G2114" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="H2114" t="s">
         <v>9</v>
@@ -57294,7 +57288,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G2115" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="H2115" t="s">
         <v>9</v>
@@ -57320,7 +57314,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G2116" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="H2116" t="s">
         <v>9</v>
@@ -57346,7 +57340,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G2117" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="H2117" t="s">
         <v>9</v>
@@ -57372,7 +57366,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G2118" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="H2118" t="s">
         <v>9</v>
@@ -57398,7 +57392,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G2119" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="H2119" t="s">
         <v>9</v>
@@ -57424,7 +57418,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G2120" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H2120" t="s">
         <v>9</v>
@@ -57450,7 +57444,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G2121" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="H2121" t="s">
         <v>9</v>
@@ -57476,7 +57470,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G2122" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="H2122" t="s">
         <v>9</v>
@@ -57502,7 +57496,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2123" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="H2123" t="s">
         <v>9</v>
@@ -57528,7 +57522,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G2124" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="H2124" t="s">
         <v>9</v>
@@ -57554,7 +57548,7 @@
         <v>3.25</v>
       </c>
       <c r="G2125" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="H2125" t="s">
         <v>9</v>
@@ -57580,7 +57574,7 @@
         <v>3.25</v>
       </c>
       <c r="G2126" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="H2126" t="s">
         <v>9</v>
@@ -57606,7 +57600,7 @@
         <v>3.25</v>
       </c>
       <c r="G2127" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="H2127" t="s">
         <v>9</v>
@@ -57632,7 +57626,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G2128" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="H2128" t="s">
         <v>9</v>
@@ -57658,7 +57652,7 @@
         <v>3.25</v>
       </c>
       <c r="G2129" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="H2129" t="s">
         <v>9</v>
@@ -57684,7 +57678,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G2130" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="H2130" t="s">
         <v>9</v>
@@ -57710,7 +57704,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G2131" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="H2131" t="s">
         <v>9</v>
@@ -57736,7 +57730,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G2132" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="H2132" t="s">
         <v>9</v>
@@ -57762,7 +57756,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G2133" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="H2133" t="s">
         <v>9</v>
@@ -57788,7 +57782,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G2134" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="H2134" t="s">
         <v>9</v>
@@ -57814,7 +57808,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G2135" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="H2135" t="s">
         <v>9</v>
@@ -57840,7 +57834,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G2136" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="H2136" t="s">
         <v>9</v>
@@ -57866,7 +57860,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G2137" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="H2137" t="s">
         <v>9</v>
@@ -57892,7 +57886,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G2138" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="H2138" t="s">
         <v>9</v>
@@ -57918,7 +57912,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G2139" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="H2139" t="s">
         <v>9</v>
@@ -57944,7 +57938,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2140" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="H2140" t="s">
         <v>9</v>
@@ -57970,7 +57964,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G2141" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="H2141" t="s">
         <v>9</v>
@@ -57996,7 +57990,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G2142" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="H2142" t="s">
         <v>9</v>
@@ -58022,7 +58016,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G2143" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="H2143" t="s">
         <v>9</v>
@@ -58048,7 +58042,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G2144" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="H2144" t="s">
         <v>9</v>
@@ -58074,7 +58068,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G2145" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="H2145" t="s">
         <v>9</v>
@@ -58100,7 +58094,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G2146" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="H2146" t="s">
         <v>9</v>
@@ -58126,7 +58120,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G2147" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="H2147" t="s">
         <v>9</v>
@@ -58152,7 +58146,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G2148" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="H2148" t="s">
         <v>9</v>
@@ -58178,7 +58172,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G2149" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="H2149" t="s">
         <v>9</v>
@@ -58204,7 +58198,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G2150" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="H2150" t="s">
         <v>9</v>
@@ -58230,7 +58224,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G2151" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="H2151" t="s">
         <v>9</v>
@@ -58256,7 +58250,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G2152" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="H2152" t="s">
         <v>9</v>
@@ -58282,7 +58276,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G2153" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="H2153" t="s">
         <v>9</v>
@@ -58308,7 +58302,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G2154" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="H2154" t="s">
         <v>9</v>
@@ -58334,7 +58328,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G2155" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="H2155" t="s">
         <v>9</v>
@@ -58360,7 +58354,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G2156" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="H2156" t="s">
         <v>9</v>
@@ -58386,7 +58380,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G2157" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="H2157" t="s">
         <v>9</v>
@@ -58412,7 +58406,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G2158" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="H2158" t="s">
         <v>9</v>
@@ -58438,7 +58432,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G2159" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="H2159" t="s">
         <v>9</v>
@@ -58464,7 +58458,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G2160" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="H2160" t="s">
         <v>9</v>
@@ -58490,7 +58484,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G2161" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="H2161" t="s">
         <v>9</v>
@@ -58516,7 +58510,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G2162" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="H2162" t="s">
         <v>9</v>
@@ -58542,7 +58536,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G2163" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="H2163" t="s">
         <v>9</v>
@@ -58568,7 +58562,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G2164" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="H2164" t="s">
         <v>9</v>
@@ -58594,7 +58588,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G2165" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="H2165" t="s">
         <v>9</v>
@@ -58620,7 +58614,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G2166" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="H2166" t="s">
         <v>9</v>
@@ -58646,7 +58640,7 @@
         <v>3.25</v>
       </c>
       <c r="G2167" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="H2167" t="s">
         <v>9</v>
@@ -58672,7 +58666,7 @@
         <v>3.25</v>
       </c>
       <c r="G2168" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="H2168" t="s">
         <v>9</v>
@@ -58698,7 +58692,7 @@
         <v>3.25</v>
       </c>
       <c r="G2169" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="H2169" t="s">
         <v>9</v>
@@ -58724,7 +58718,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G2170" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="H2170" t="s">
         <v>9</v>
@@ -58750,7 +58744,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G2171" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="H2171" t="s">
         <v>9</v>
@@ -58776,7 +58770,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G2172" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="H2172" t="s">
         <v>9</v>
@@ -58802,7 +58796,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G2173" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="H2173" t="s">
         <v>9</v>
@@ -58828,7 +58822,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G2174" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="H2174" t="s">
         <v>9</v>
@@ -58854,7 +58848,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2175" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="H2175" t="s">
         <v>9</v>
@@ -58880,7 +58874,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2176" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="H2176" t="s">
         <v>9</v>
@@ -58906,7 +58900,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2177" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="H2177" t="s">
         <v>9</v>
@@ -58932,7 +58926,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G2178" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="H2178" t="s">
         <v>9</v>
@@ -58958,7 +58952,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G2179" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="H2179" t="s">
         <v>9</v>
@@ -58984,7 +58978,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G2180" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="H2180" t="s">
         <v>9</v>
@@ -59010,7 +59004,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G2181" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="H2181" t="s">
         <v>9</v>
@@ -59036,7 +59030,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2182" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="H2182" t="s">
         <v>9</v>
@@ -59062,7 +59056,7 @@
         <v>3.25</v>
       </c>
       <c r="G2183" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="H2183" t="s">
         <v>9</v>
@@ -59088,7 +59082,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G2184" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="H2184" t="s">
         <v>9</v>
@@ -59114,7 +59108,7 @@
         <v>3.25</v>
       </c>
       <c r="G2185" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="H2185" t="s">
         <v>9</v>
@@ -59140,7 +59134,7 @@
         <v>3.25</v>
       </c>
       <c r="G2186" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="H2186" t="s">
         <v>9</v>
@@ -59166,7 +59160,7 @@
         <v>3.25</v>
       </c>
       <c r="G2187" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="H2187" t="s">
         <v>9</v>
@@ -59192,7 +59186,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G2188" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="H2188" t="s">
         <v>9</v>
@@ -59218,7 +59212,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G2189" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="H2189" t="s">
         <v>9</v>
@@ -59244,7 +59238,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G2190" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="H2190" t="s">
         <v>9</v>
@@ -59270,7 +59264,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G2191" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="H2191" t="s">
         <v>9</v>
@@ -59296,7 +59290,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G2192" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="H2192" t="s">
         <v>9</v>
@@ -59322,7 +59316,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G2193" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="H2193" t="s">
         <v>9</v>
@@ -59348,7 +59342,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G2194" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="H2194" t="s">
         <v>9</v>
@@ -59374,7 +59368,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G2195" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="H2195" t="s">
         <v>9</v>
@@ -59400,7 +59394,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G2196" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="H2196" t="s">
         <v>9</v>
@@ -59426,7 +59420,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2197" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="H2197" t="s">
         <v>9</v>
@@ -59452,7 +59446,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G2198" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="H2198" t="s">
         <v>9</v>
@@ -59478,7 +59472,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G2199" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="H2199" t="s">
         <v>9</v>
@@ -59504,7 +59498,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G2200" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="H2200" t="s">
         <v>9</v>
@@ -59530,7 +59524,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G2201" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="H2201" t="s">
         <v>9</v>
@@ -59556,7 +59550,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G2202" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="H2202" t="s">
         <v>9</v>
@@ -59582,7 +59576,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G2203" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="H2203" t="s">
         <v>9</v>
@@ -59608,7 +59602,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G2204" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="H2204" t="s">
         <v>9</v>
@@ -59634,7 +59628,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G2205" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="H2205" t="s">
         <v>9</v>
@@ -59660,7 +59654,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2206" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="H2206" t="s">
         <v>9</v>
@@ -59686,7 +59680,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G2207" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="H2207" t="s">
         <v>9</v>
@@ -59712,7 +59706,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G2208" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="H2208" t="s">
         <v>9</v>
@@ -59738,7 +59732,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G2209" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="H2209" t="s">
         <v>9</v>
@@ -59764,7 +59758,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G2210" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="H2210" t="s">
         <v>9</v>
@@ -59790,7 +59784,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G2211" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="H2211" t="s">
         <v>9</v>
@@ -59816,7 +59810,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G2212" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="H2212" t="s">
         <v>9</v>
@@ -59842,7 +59836,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G2213" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="H2213" t="s">
         <v>9</v>
@@ -59868,7 +59862,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G2214" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="H2214" t="s">
         <v>9</v>
@@ -59894,7 +59888,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G2215" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="H2215" t="s">
         <v>9</v>
@@ -59920,7 +59914,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G2216" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="H2216" t="s">
         <v>9</v>
@@ -59946,7 +59940,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G2217" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="H2217" t="s">
         <v>9</v>
@@ -59972,7 +59966,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G2218" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="H2218" t="s">
         <v>9</v>
@@ -59998,7 +59992,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G2219" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="H2219" t="s">
         <v>9</v>
@@ -60024,7 +60018,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G2220" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="H2220" t="s">
         <v>9</v>
@@ -60050,7 +60044,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G2221" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="H2221" t="s">
         <v>9</v>
@@ -60076,7 +60070,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G2222" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="H2222" t="s">
         <v>9</v>
@@ -60102,7 +60096,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G2223" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="H2223" t="s">
         <v>9</v>
@@ -60128,7 +60122,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G2224" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="H2224" t="s">
         <v>9</v>
@@ -60154,7 +60148,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G2225" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="H2225" t="s">
         <v>9</v>
@@ -60180,7 +60174,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G2226" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="H2226" t="s">
         <v>9</v>
@@ -60206,7 +60200,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2227" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="H2227" t="s">
         <v>9</v>
@@ -60232,7 +60226,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G2228" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="H2228" t="s">
         <v>9</v>
@@ -60258,7 +60252,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G2229" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="H2229" t="s">
         <v>9</v>
@@ -60284,7 +60278,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G2230" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="H2230" t="s">
         <v>9</v>
@@ -60310,7 +60304,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G2231" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="H2231" t="s">
         <v>9</v>
@@ -60336,7 +60330,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G2232" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="H2232" t="s">
         <v>9</v>
@@ -60362,7 +60356,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G2233" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="H2233" t="s">
         <v>9</v>
@@ -60388,7 +60382,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G2234" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="H2234" t="s">
         <v>9</v>
@@ -60414,7 +60408,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G2235" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="H2235" t="s">
         <v>9</v>
@@ -60440,7 +60434,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G2236" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="H2236" t="s">
         <v>9</v>
@@ -60466,7 +60460,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G2237" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="H2237" t="s">
         <v>9</v>
@@ -60492,7 +60486,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G2238" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="H2238" t="s">
         <v>9</v>
@@ -60518,7 +60512,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G2239" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="H2239" t="s">
         <v>9</v>
@@ -60544,7 +60538,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G2240" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="H2240" t="s">
         <v>9</v>
@@ -60570,7 +60564,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G2241" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="H2241" t="s">
         <v>9</v>
@@ -60596,7 +60590,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G2242" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="H2242" t="s">
         <v>9</v>
@@ -60622,7 +60616,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G2243" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="H2243" t="s">
         <v>9</v>
@@ -60648,7 +60642,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G2244" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="H2244" t="s">
         <v>9</v>
@@ -60674,7 +60668,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G2245" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="H2245" t="s">
         <v>9</v>
@@ -60700,7 +60694,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G2246" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="H2246" t="s">
         <v>9</v>
@@ -60726,7 +60720,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G2247" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="H2247" t="s">
         <v>9</v>
@@ -60752,7 +60746,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G2248" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="H2248" t="s">
         <v>9</v>
@@ -60778,7 +60772,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G2249" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="H2249" t="s">
         <v>9</v>
@@ -60804,7 +60798,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G2250" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="H2250" t="s">
         <v>9</v>
@@ -60830,7 +60824,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G2251" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="H2251" t="s">
         <v>9</v>
@@ -60856,7 +60850,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G2252" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="H2252" t="s">
         <v>9</v>
@@ -60882,7 +60876,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G2253" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="H2253" t="s">
         <v>9</v>
@@ -60908,7 +60902,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G2254" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="H2254" t="s">
         <v>9</v>
@@ -60934,7 +60928,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G2255" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="H2255" t="s">
         <v>9</v>
@@ -60960,7 +60954,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G2256" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="H2256" t="s">
         <v>9</v>
@@ -60986,7 +60980,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G2257" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="H2257" t="s">
         <v>9</v>
@@ -61012,7 +61006,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G2258" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="H2258" t="s">
         <v>9</v>
@@ -61038,7 +61032,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G2259" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="H2259" t="s">
         <v>9</v>
@@ -61064,7 +61058,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G2260" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="H2260" t="s">
         <v>9</v>
@@ -61090,7 +61084,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G2261" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="H2261" t="s">
         <v>9</v>
@@ -61116,7 +61110,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G2262" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="H2262" t="s">
         <v>9</v>
@@ -61142,7 +61136,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G2263" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="H2263" t="s">
         <v>9</v>
@@ -61168,7 +61162,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G2264" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="H2264" t="s">
         <v>9</v>
@@ -61194,7 +61188,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G2265" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="H2265" t="s">
         <v>9</v>
@@ -61220,7 +61214,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G2266" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="H2266" t="s">
         <v>9</v>
@@ -61246,7 +61240,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G2267" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="H2267" t="s">
         <v>9</v>
@@ -61272,7 +61266,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G2268" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="H2268" t="s">
         <v>9</v>
@@ -61298,7 +61292,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G2269" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="H2269" t="s">
         <v>9</v>
@@ -61324,7 +61318,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G2270" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="H2270" t="s">
         <v>9</v>
@@ -61350,7 +61344,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G2271" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="H2271" t="s">
         <v>9</v>
@@ -61376,7 +61370,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G2272" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="H2272" t="s">
         <v>9</v>
@@ -61402,7 +61396,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G2273" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="H2273" t="s">
         <v>9</v>
@@ -61428,7 +61422,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G2274" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="H2274" t="s">
         <v>9</v>
@@ -61454,7 +61448,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G2275" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="H2275" t="s">
         <v>9</v>
@@ -61480,7 +61474,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G2276" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="H2276" t="s">
         <v>9</v>
@@ -61506,7 +61500,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G2277" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="H2277" t="s">
         <v>9</v>
@@ -61532,7 +61526,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G2278" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="H2278" t="s">
         <v>9</v>
@@ -61558,7 +61552,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G2279" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="H2279" t="s">
         <v>9</v>
@@ -61584,7 +61578,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G2280" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="H2280" t="s">
         <v>9</v>
@@ -61610,7 +61604,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G2281" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="H2281" t="s">
         <v>9</v>
@@ -61636,7 +61630,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G2282" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="H2282" t="s">
         <v>9</v>
@@ -61662,7 +61656,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G2283" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="H2283" t="s">
         <v>9</v>
@@ -61688,7 +61682,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G2284" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="H2284" t="s">
         <v>9</v>
@@ -61714,7 +61708,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G2285" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="H2285" t="s">
         <v>9</v>
@@ -61740,7 +61734,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G2286" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="H2286" t="s">
         <v>9</v>
@@ -61766,7 +61760,7 @@
         <v>3.25</v>
       </c>
       <c r="G2287" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="H2287" t="s">
         <v>9</v>
@@ -61792,7 +61786,7 @@
         <v>3.25</v>
       </c>
       <c r="G2288" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="H2288" t="s">
         <v>9</v>
@@ -61818,7 +61812,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G2289" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="H2289" t="s">
         <v>9</v>
@@ -61844,7 +61838,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G2290" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="H2290" t="s">
         <v>9</v>
@@ -61870,7 +61864,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G2291" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="H2291" t="s">
         <v>9</v>
@@ -61896,7 +61890,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G2292" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="H2292" t="s">
         <v>9</v>
@@ -61922,7 +61916,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G2293" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="H2293" t="s">
         <v>9</v>
@@ -61948,7 +61942,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G2294" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="H2294" t="s">
         <v>9</v>
@@ -61974,7 +61968,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G2295" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="H2295" t="s">
         <v>9</v>
@@ -62000,7 +61994,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G2296" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="H2296" t="s">
         <v>9</v>
@@ -62026,7 +62020,7 @@
         <v>3.25</v>
       </c>
       <c r="G2297" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="H2297" t="s">
         <v>9</v>
@@ -62052,7 +62046,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G2298" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="H2298" t="s">
         <v>9</v>
@@ -62078,7 +62072,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G2299" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="H2299" t="s">
         <v>9</v>
@@ -62104,7 +62098,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2300" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="H2300" t="s">
         <v>9</v>
@@ -62130,7 +62124,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G2301" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="H2301" t="s">
         <v>9</v>
@@ -62156,7 +62150,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G2302" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="H2302" t="s">
         <v>9</v>
@@ -62182,7 +62176,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G2303" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="H2303" t="s">
         <v>9</v>
@@ -62208,7 +62202,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G2304" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="H2304" t="s">
         <v>9</v>
@@ -62234,7 +62228,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G2305" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="H2305" t="s">
         <v>9</v>
@@ -62260,7 +62254,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G2306" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="H2306" t="s">
         <v>9</v>
@@ -62286,7 +62280,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G2307" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="H2307" t="s">
         <v>9</v>
@@ -62312,7 +62306,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G2308" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="H2308" t="s">
         <v>9</v>
@@ -62338,7 +62332,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G2309" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="H2309" t="s">
         <v>9</v>
@@ -62364,7 +62358,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G2310" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="H2310" t="s">
         <v>9</v>
@@ -62390,7 +62384,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2311" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="H2311" t="s">
         <v>9</v>
@@ -62416,7 +62410,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2312" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="H2312" t="s">
         <v>9</v>
@@ -62442,7 +62436,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G2313" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="H2313" t="s">
         <v>9</v>
@@ -62468,7 +62462,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G2314" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="H2314" t="s">
         <v>9</v>
@@ -62494,7 +62488,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G2315" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="H2315" t="s">
         <v>9</v>
@@ -62520,7 +62514,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G2316" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="H2316" t="s">
         <v>9</v>
@@ -62546,7 +62540,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G2317" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="H2317" t="s">
         <v>9</v>
@@ -62572,7 +62566,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G2318" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="H2318" t="s">
         <v>9</v>
@@ -62598,7 +62592,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G2319" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="H2319" t="s">
         <v>9</v>
@@ -62624,7 +62618,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G2320" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="H2320" t="s">
         <v>9</v>
@@ -62650,7 +62644,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G2321" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="H2321" t="s">
         <v>9</v>
@@ -62676,7 +62670,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G2322" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="H2322" t="s">
         <v>9</v>
@@ -62702,7 +62696,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2323" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="H2323" t="s">
         <v>9</v>
@@ -62728,7 +62722,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2324" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="H2324" t="s">
         <v>9</v>
@@ -62754,7 +62748,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2325" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="H2325" t="s">
         <v>9</v>
@@ -62780,7 +62774,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G2326" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="H2326" t="s">
         <v>9</v>
@@ -62806,7 +62800,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2327" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="H2327" t="s">
         <v>9</v>
@@ -62832,7 +62826,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G2328" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="H2328" t="s">
         <v>9</v>
@@ -62858,7 +62852,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G2329" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="H2329" t="s">
         <v>9</v>
@@ -62884,7 +62878,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G2330" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="H2330" t="s">
         <v>9</v>
@@ -62910,7 +62904,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G2331" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="H2331" t="s">
         <v>9</v>
@@ -62936,7 +62930,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G2332" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="H2332" t="s">
         <v>9</v>
@@ -62962,7 +62956,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G2333" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="H2333" t="s">
         <v>9</v>
@@ -62988,7 +62982,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G2334" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="H2334" t="s">
         <v>9</v>
@@ -63014,7 +63008,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G2335" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="H2335" t="s">
         <v>9</v>
@@ -63040,7 +63034,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G2336" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="H2336" t="s">
         <v>9</v>
@@ -63066,7 +63060,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G2337" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="H2337" t="s">
         <v>9</v>
@@ -63092,7 +63086,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G2338" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="H2338" t="s">
         <v>9</v>
@@ -63118,7 +63112,7 @@
         <v>3.25</v>
       </c>
       <c r="G2339" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="H2339" t="s">
         <v>9</v>
@@ -63144,7 +63138,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G2340" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="H2340" t="s">
         <v>9</v>
@@ -63170,7 +63164,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G2341" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="H2341" t="s">
         <v>9</v>
@@ -63196,7 +63190,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G2342" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="H2342" t="s">
         <v>9</v>
@@ -63222,7 +63216,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G2343" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="H2343" t="s">
         <v>9</v>
@@ -63248,7 +63242,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G2344" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="H2344" t="s">
         <v>9</v>
@@ -63274,7 +63268,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G2345" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="H2345" t="s">
         <v>9</v>
@@ -63300,7 +63294,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G2346" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="H2346" t="s">
         <v>9</v>
@@ -63326,7 +63320,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G2347" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="H2347" t="s">
         <v>9</v>
@@ -63352,7 +63346,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G2348" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="H2348" t="s">
         <v>9</v>
@@ -63378,7 +63372,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G2349" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="H2349" t="s">
         <v>9</v>
@@ -63404,7 +63398,7 @@
         <v>3.25</v>
       </c>
       <c r="G2350" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="H2350" t="s">
         <v>9</v>
@@ -63430,7 +63424,7 @@
         <v>3.25</v>
       </c>
       <c r="G2351" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="H2351" t="s">
         <v>9</v>
@@ -63456,7 +63450,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G2352" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="H2352" t="s">
         <v>9</v>
@@ -63482,7 +63476,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G2353" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="H2353" t="s">
         <v>9</v>
@@ -63508,7 +63502,7 @@
         <v>3.25</v>
       </c>
       <c r="G2354" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="H2354" t="s">
         <v>9</v>
@@ -63534,7 +63528,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G2355" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="H2355" t="s">
         <v>9</v>
@@ -63560,7 +63554,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G2356" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="H2356" t="s">
         <v>9</v>
@@ -63586,7 +63580,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G2357" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="H2357" t="s">
         <v>9</v>
@@ -63612,7 +63606,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G2358" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="H2358" t="s">
         <v>9</v>
@@ -63638,7 +63632,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G2359" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="H2359" t="s">
         <v>9</v>
@@ -63664,7 +63658,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G2360" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="H2360" t="s">
         <v>9</v>
@@ -63690,7 +63684,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G2361" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="H2361" t="s">
         <v>9</v>
@@ -63716,7 +63710,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G2362" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="H2362" t="s">
         <v>9</v>
@@ -63742,7 +63736,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2363" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="H2363" t="s">
         <v>9</v>
@@ -63768,7 +63762,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2364" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="H2364" t="s">
         <v>9</v>
@@ -63794,7 +63788,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G2365" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="H2365" t="s">
         <v>9</v>
@@ -63820,7 +63814,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2366" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="H2366" t="s">
         <v>9</v>
@@ -63846,7 +63840,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G2367" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="H2367" t="s">
         <v>9</v>
@@ -63872,7 +63866,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G2368" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="H2368" t="s">
         <v>9</v>
@@ -63898,7 +63892,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G2369" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="H2369" t="s">
         <v>9</v>
@@ -63924,7 +63918,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G2370" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="H2370" t="s">
         <v>9</v>
@@ -63950,7 +63944,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G2371" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="H2371" t="s">
         <v>9</v>
@@ -63976,7 +63970,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G2372" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="H2372" t="s">
         <v>9</v>
@@ -64002,7 +63996,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G2373" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="H2373" t="s">
         <v>9</v>
@@ -64028,7 +64022,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G2374" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="H2374" t="s">
         <v>9</v>
@@ -64054,7 +64048,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G2375" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="H2375" t="s">
         <v>9</v>
@@ -64080,7 +64074,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G2376" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="H2376" t="s">
         <v>9</v>
@@ -64106,7 +64100,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G2377" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="H2377" t="s">
         <v>9</v>
@@ -64132,7 +64126,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G2378" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="H2378" t="s">
         <v>9</v>
@@ -64158,7 +64152,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G2379" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="H2379" t="s">
         <v>9</v>
@@ -64184,7 +64178,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G2380" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="H2380" t="s">
         <v>9</v>
@@ -64210,7 +64204,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G2381" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="H2381" t="s">
         <v>9</v>
@@ -64236,7 +64230,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G2382" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="H2382" t="s">
         <v>9</v>
@@ -64262,7 +64256,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G2383" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="H2383" t="s">
         <v>9</v>
@@ -64288,7 +64282,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2384" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="H2384" t="s">
         <v>9</v>
@@ -64314,7 +64308,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G2385" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="H2385" t="s">
         <v>9</v>
@@ -64340,7 +64334,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G2386" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="H2386" t="s">
         <v>9</v>
@@ -64366,7 +64360,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G2387" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="H2387" t="s">
         <v>9</v>
@@ -64392,7 +64386,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G2388" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="H2388" t="s">
         <v>9</v>
@@ -64418,7 +64412,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G2389" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="H2389" t="s">
         <v>9</v>
@@ -64444,7 +64438,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2390" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="H2390" t="s">
         <v>9</v>
@@ -64470,7 +64464,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2391" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="H2391" t="s">
         <v>9</v>
@@ -64496,7 +64490,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G2392" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="H2392" t="s">
         <v>9</v>
@@ -64522,7 +64516,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G2393" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="H2393" t="s">
         <v>9</v>
@@ -64548,7 +64542,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G2394" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="H2394" t="s">
         <v>9</v>
@@ -64574,7 +64568,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2395" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="H2395" t="s">
         <v>9</v>
@@ -64600,7 +64594,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2396" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="H2396" t="s">
         <v>9</v>
@@ -64626,7 +64620,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G2397" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="H2397" t="s">
         <v>9</v>
@@ -64652,7 +64646,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2398" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="H2398" t="s">
         <v>9</v>
@@ -64678,7 +64672,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G2399" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="H2399" t="s">
         <v>9</v>
@@ -64704,7 +64698,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G2400" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="H2400" t="s">
         <v>9</v>
@@ -64730,7 +64724,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G2401" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="H2401" t="s">
         <v>9</v>
@@ -64756,7 +64750,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G2402" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="H2402" t="s">
         <v>9</v>
@@ -64782,7 +64776,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G2403" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="H2403" t="s">
         <v>9</v>
@@ -64808,7 +64802,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G2404" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="H2404" t="s">
         <v>9</v>
@@ -64834,7 +64828,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G2405" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="H2405" t="s">
         <v>9</v>
@@ -64860,7 +64854,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G2406" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="H2406" t="s">
         <v>9</v>
@@ -64886,7 +64880,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G2407" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="H2407" t="s">
         <v>9</v>
@@ -64912,7 +64906,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G2408" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="H2408" t="s">
         <v>9</v>
@@ -64938,7 +64932,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2409" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="H2409" t="s">
         <v>9</v>
@@ -64964,7 +64958,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G2410" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="H2410" t="s">
         <v>9</v>
@@ -64990,7 +64984,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G2411" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="H2411" t="s">
         <v>9</v>
@@ -65016,7 +65010,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G2412" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="H2412" t="s">
         <v>9</v>
@@ -65042,7 +65036,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G2413" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="H2413" t="s">
         <v>9</v>
@@ -65068,7 +65062,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G2414" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="H2414" t="s">
         <v>9</v>
@@ -65094,7 +65088,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G2415" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="H2415" t="s">
         <v>9</v>
@@ -65120,7 +65114,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G2416" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="H2416" t="s">
         <v>9</v>
@@ -65146,7 +65140,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G2417" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="H2417" t="s">
         <v>9</v>
@@ -65172,7 +65166,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G2418" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="H2418" t="s">
         <v>9</v>
@@ -65198,7 +65192,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G2419" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="H2419" t="s">
         <v>9</v>
@@ -65224,7 +65218,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G2420" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="H2420" t="s">
         <v>9</v>
@@ -65250,7 +65244,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G2421" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="H2421" t="s">
         <v>9</v>
@@ -65276,7 +65270,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G2422" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="H2422" t="s">
         <v>9</v>
@@ -65302,7 +65296,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G2423" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="H2423" t="s">
         <v>9</v>
@@ -65328,7 +65322,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G2424" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="H2424" t="s">
         <v>9</v>
@@ -65354,7 +65348,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G2425" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="H2425" t="s">
         <v>9</v>
@@ -65380,7 +65374,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G2426" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="H2426" t="s">
         <v>9</v>
@@ -65406,7 +65400,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G2427" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="H2427" t="s">
         <v>9</v>
@@ -65432,7 +65426,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G2428" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="H2428" t="s">
         <v>9</v>
@@ -65458,7 +65452,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G2429" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="H2429" t="s">
         <v>9</v>
@@ -65484,7 +65478,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G2430" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="H2430" t="s">
         <v>9</v>
@@ -65510,7 +65504,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G2431" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="H2431" t="s">
         <v>9</v>
@@ -65536,7 +65530,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G2432" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="H2432" t="s">
         <v>9</v>
@@ -65562,7 +65556,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G2433" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="H2433" t="s">
         <v>9</v>
@@ -65588,7 +65582,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G2434" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="H2434" t="s">
         <v>9</v>
@@ -65614,7 +65608,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G2435" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="H2435" t="s">
         <v>9</v>
@@ -65640,7 +65634,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G2436" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="H2436" t="s">
         <v>9</v>
@@ -65666,7 +65660,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G2437" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="H2437" t="s">
         <v>9</v>
@@ -65692,7 +65686,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G2438" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="H2438" t="s">
         <v>9</v>
@@ -65718,7 +65712,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G2439" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="H2439" t="s">
         <v>9</v>
@@ -65744,7 +65738,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G2440" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="H2440" t="s">
         <v>9</v>
@@ -65770,7 +65764,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G2441" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="H2441" t="s">
         <v>9</v>
@@ -65796,7 +65790,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G2442" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="H2442" t="s">
         <v>9</v>
@@ -65822,7 +65816,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G2443" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="H2443" t="s">
         <v>9</v>
@@ -65848,7 +65842,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G2444" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="H2444" t="s">
         <v>9</v>
@@ -65874,7 +65868,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G2445" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="H2445" t="s">
         <v>9</v>
@@ -65900,7 +65894,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G2446" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="H2446" t="s">
         <v>9</v>
@@ -65926,7 +65920,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G2447" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="H2447" t="s">
         <v>9</v>
@@ -65952,7 +65946,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G2448" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="H2448" t="s">
         <v>9</v>
@@ -65978,7 +65972,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G2449" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="H2449" t="s">
         <v>9</v>
@@ -66004,7 +65998,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G2450" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="H2450" t="s">
         <v>9</v>
@@ -66030,7 +66024,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G2451" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="H2451" t="s">
         <v>9</v>
@@ -66056,7 +66050,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G2452" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="H2452" t="s">
         <v>9</v>
@@ -66082,7 +66076,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G2453" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="H2453" t="s">
         <v>9</v>
@@ -66108,7 +66102,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G2454" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="H2454" t="s">
         <v>9</v>
@@ -66134,7 +66128,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G2455" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="H2455" t="s">
         <v>9</v>
@@ -66160,7 +66154,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G2456" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="H2456" t="s">
         <v>9</v>
@@ -66186,7 +66180,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G2457" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="H2457" t="s">
         <v>9</v>
@@ -66212,7 +66206,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G2458" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="H2458" t="s">
         <v>9</v>
@@ -66238,7 +66232,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G2459" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="H2459" t="s">
         <v>9</v>
@@ -66264,7 +66258,7 @@
         <v>4</v>
       </c>
       <c r="G2460" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="H2460" t="s">
         <v>9</v>
@@ -66290,7 +66284,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G2461" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="H2461" t="s">
         <v>9</v>
@@ -66316,7 +66310,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G2462" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="H2462" t="s">
         <v>9</v>
@@ -66342,7 +66336,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G2463" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="H2463" t="s">
         <v>9</v>
@@ -66368,7 +66362,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G2464" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="H2464" t="s">
         <v>9</v>
@@ -66394,7 +66388,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G2465" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="H2465" t="s">
         <v>9</v>
@@ -66420,7 +66414,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G2466" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="H2466" t="s">
         <v>9</v>
@@ -66446,7 +66440,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G2467" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="H2467" t="s">
         <v>9</v>
@@ -66472,7 +66466,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G2468" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="H2468" t="s">
         <v>9</v>
@@ -66498,7 +66492,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G2469" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="H2469" t="s">
         <v>9</v>
@@ -66524,7 +66518,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G2470" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="H2470" t="s">
         <v>9</v>
@@ -66550,7 +66544,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G2471" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="H2471" t="s">
         <v>9</v>
@@ -66576,7 +66570,7 @@
         <v>4</v>
       </c>
       <c r="G2472" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="H2472" t="s">
         <v>9</v>
@@ -66602,7 +66596,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G2473" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="H2473" t="s">
         <v>9</v>
@@ -66628,7 +66622,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G2474" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="H2474" t="s">
         <v>9</v>
@@ -66654,7 +66648,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G2475" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="H2475" t="s">
         <v>9</v>
@@ -66680,7 +66674,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G2476" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="H2476" t="s">
         <v>9</v>
@@ -66706,7 +66700,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G2477" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="H2477" t="s">
         <v>9</v>
@@ -66732,7 +66726,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G2478" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="H2478" t="s">
         <v>9</v>
@@ -66758,7 +66752,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G2479" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="H2479" t="s">
         <v>9</v>
@@ -66784,7 +66778,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G2480" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="H2480" t="s">
         <v>9</v>
@@ -66810,7 +66804,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G2481" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="H2481" t="s">
         <v>9</v>
@@ -66836,7 +66830,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G2482" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="H2482" t="s">
         <v>9</v>
@@ -66862,7 +66856,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G2483" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="H2483" t="s">
         <v>9</v>
@@ -66888,7 +66882,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G2484" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="H2484" t="s">
         <v>9</v>
@@ -66914,7 +66908,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G2485" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="H2485" t="s">
         <v>9</v>
@@ -66940,7 +66934,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G2486" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="H2486" t="s">
         <v>9</v>
@@ -66966,7 +66960,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G2487" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="H2487" t="s">
         <v>9</v>
@@ -66992,7 +66986,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G2488" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="H2488" t="s">
         <v>9</v>
@@ -67018,7 +67012,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G2489" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="H2489" t="s">
         <v>9</v>
@@ -67044,7 +67038,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G2490" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="H2490" t="s">
         <v>9</v>
@@ -67070,7 +67064,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G2491" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="H2491" t="s">
         <v>9</v>
@@ -67096,7 +67090,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G2492" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="H2492" t="s">
         <v>9</v>
@@ -67122,7 +67116,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G2493" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="H2493" t="s">
         <v>9</v>
@@ -67148,7 +67142,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G2494" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="H2494" t="s">
         <v>9</v>
@@ -67174,7 +67168,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G2495" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="H2495" t="s">
         <v>9</v>
@@ -67200,7 +67194,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G2496" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="H2496" t="s">
         <v>9</v>
@@ -67226,7 +67220,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G2497" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="H2497" t="s">
         <v>9</v>
@@ -67252,7 +67246,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G2498" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="H2498" t="s">
         <v>9</v>
@@ -67278,7 +67272,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G2499" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="H2499" t="s">
         <v>9</v>
@@ -67304,7 +67298,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G2500" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="H2500" t="s">
         <v>9</v>
@@ -67330,7 +67324,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G2501" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="H2501" t="s">
         <v>9</v>
@@ -67356,7 +67350,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G2502" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="H2502" t="s">
         <v>9</v>
@@ -67382,7 +67376,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G2503" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="H2503" t="s">
         <v>9</v>
@@ -67408,7 +67402,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G2504" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="H2504" t="s">
         <v>9</v>
@@ -67434,7 +67428,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G2505" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="H2505" t="s">
         <v>9</v>
@@ -67460,7 +67454,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G2506" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="H2506" t="s">
         <v>9</v>
@@ -67486,7 +67480,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G2507" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="H2507" t="s">
         <v>9</v>
@@ -67512,7 +67506,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G2508" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="H2508" t="s">
         <v>9</v>
@@ -67538,7 +67532,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G2509" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="H2509" t="s">
         <v>9</v>
@@ -67564,7 +67558,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G2510" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="H2510" t="s">
         <v>9</v>
@@ -67590,7 +67584,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G2511" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="H2511" t="s">
         <v>9</v>
@@ -67616,7 +67610,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G2512" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="H2512" t="s">
         <v>9</v>
@@ -67642,7 +67636,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G2513" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="H2513" t="s">
         <v>9</v>
@@ -67668,7 +67662,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G2514" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="H2514" t="s">
         <v>9</v>
@@ -67694,7 +67688,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G2515" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="H2515" t="s">
         <v>9</v>
@@ -67720,7 +67714,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G2516" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="H2516" t="s">
         <v>9</v>
@@ -67746,7 +67740,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G2517" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="H2517" t="s">
         <v>9</v>
@@ -67772,7 +67766,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G2518" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="H2518" t="s">
         <v>9</v>
@@ -67798,7 +67792,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G2519" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="H2519" t="s">
         <v>9</v>
@@ -67824,7 +67818,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G2520" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="H2520" t="s">
         <v>9</v>
@@ -67850,7 +67844,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G2521" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="H2521" t="s">
         <v>9</v>
@@ -67876,7 +67870,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G2522" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="H2522" t="s">
         <v>9</v>
@@ -67902,7 +67896,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G2523" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="H2523" t="s">
         <v>9</v>
@@ -67928,7 +67922,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G2524" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="H2524" t="s">
         <v>9</v>
@@ -67954,7 +67948,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G2525" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="H2525" t="s">
         <v>9</v>
@@ -67980,7 +67974,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G2526" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="H2526" t="s">
         <v>9</v>
@@ -68006,7 +68000,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G2527" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="H2527" t="s">
         <v>9</v>
@@ -68032,7 +68026,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G2528" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="H2528" t="s">
         <v>9</v>
@@ -68058,7 +68052,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G2529" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="H2529" t="s">
         <v>9</v>
@@ -68084,7 +68078,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G2530" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="H2530" t="s">
         <v>9</v>
@@ -68110,7 +68104,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G2531" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="H2531" t="s">
         <v>9</v>
@@ -68136,7 +68130,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G2532" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="H2532" t="s">
         <v>9</v>
@@ -68162,7 +68156,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G2533" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="H2533" t="s">
         <v>9</v>
@@ -68188,7 +68182,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G2534" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="H2534" t="s">
         <v>9</v>
@@ -68196,7 +68190,7 @@
     </row>
     <row r="2535">
       <c r="A2535" s="1" t="n">
-        <v>46008.6511111111</v>
+        <v>46008.3333333333</v>
       </c>
       <c r="B2535" t="n">
         <v>24515</v>
@@ -68214,9 +68208,35 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G2535" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="H2535" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2536">
+      <c r="A2536" s="1" t="n">
+        <v>46009.6911805556</v>
+      </c>
+      <c r="B2536" t="n">
+        <v>3770</v>
+      </c>
+      <c r="C2536" t="n">
+        <v>3.83999991416931</v>
+      </c>
+      <c r="D2536" t="n">
+        <v>3.75999999046326</v>
+      </c>
+      <c r="E2536" t="n">
+        <v>3.83999991416931</v>
+      </c>
+      <c r="F2536" t="n">
+        <v>3.74000000953674</v>
+      </c>
+      <c r="G2536" t="s">
+        <v>613</v>
+      </c>
+      <c r="H2536" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ENV.MI.xlsx
+++ b/data/ENV.MI.xlsx
@@ -44,79 +44,79 @@
     <t xml:space="preserve">ENV.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20979785919189</t>
+    <t xml:space="preserve">2.20979762077332</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1447126865387</t>
+    <t xml:space="preserve">2.14471244812012</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16175866127014</t>
+    <t xml:space="preserve">2.16175842285156</t>
   </si>
   <si>
     <t xml:space="preserve">2.03778696060181</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08272624015808</t>
+    <t xml:space="preserve">2.08272671699524</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05328369140625</t>
+    <t xml:space="preserve">2.05328345298767</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03623747825623</t>
+    <t xml:space="preserve">2.03623700141907</t>
   </si>
   <si>
     <t xml:space="preserve">1.96805286407471</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96030426025391</t>
+    <t xml:space="preserve">1.9603043794632</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8983188867569</t>
+    <t xml:space="preserve">1.89831852912903</t>
   </si>
   <si>
     <t xml:space="preserve">1.88127255439758</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96340382099152</t>
+    <t xml:space="preserve">1.96340370178223</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98354947566986</t>
+    <t xml:space="preserve">1.98354911804199</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01299262046814</t>
+    <t xml:space="preserve">2.01299285888672</t>
   </si>
   <si>
     <t xml:space="preserve">1.93551027774811</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93705987930298</t>
+    <t xml:space="preserve">1.93705952167511</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91381514072418</t>
+    <t xml:space="preserve">1.91381549835205</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91071581840515</t>
+    <t xml:space="preserve">1.91071593761444</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86577606201172</t>
+    <t xml:space="preserve">1.86577618122101</t>
   </si>
   <si>
     <t xml:space="preserve">1.89212000370026</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85182929039001</t>
+    <t xml:space="preserve">1.8518294095993</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93396079540253</t>
+    <t xml:space="preserve">1.93396067619324</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86732578277588</t>
+    <t xml:space="preserve">1.86732602119446</t>
   </si>
   <si>
     <t xml:space="preserve">1.8890209197998</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98664832115173</t>
+    <t xml:space="preserve">1.98664820194244</t>
   </si>
   <si>
     <t xml:space="preserve">2.11526918411255</t>
@@ -125,22 +125,22 @@
     <t xml:space="preserve">2.18500351905823</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20824813842773</t>
+    <t xml:space="preserve">2.20824837684631</t>
   </si>
   <si>
     <t xml:space="preserve">2.16950702667236</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0842764377594</t>
+    <t xml:space="preserve">2.08427667617798</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0145423412323</t>
+    <t xml:space="preserve">2.01454186439514</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00524425506592</t>
+    <t xml:space="preserve">2.0052444934845</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14626240730286</t>
+    <t xml:space="preserve">2.14626216888428</t>
   </si>
   <si>
     <t xml:space="preserve">2.22219491004944</t>
@@ -149,142 +149,142 @@
     <t xml:space="preserve">2.32447195053101</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20049953460693</t>
+    <t xml:space="preserve">2.20050001144409</t>
   </si>
   <si>
     <t xml:space="preserve">2.27178359031677</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24698972702026</t>
+    <t xml:space="preserve">2.24698925018311</t>
   </si>
   <si>
     <t xml:space="preserve">2.32137250900269</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2841808795929</t>
+    <t xml:space="preserve">2.28418111801147</t>
   </si>
   <si>
     <t xml:space="preserve">2.37870955467224</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35546493530273</t>
+    <t xml:space="preserve">2.35546469688416</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44069528579712</t>
+    <t xml:space="preserve">2.4406955242157</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4313976764679</t>
+    <t xml:space="preserve">2.43139743804932</t>
   </si>
   <si>
     <t xml:space="preserve">2.4499933719635</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38490843772888</t>
+    <t xml:space="preserve">2.3849081993103</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36166334152222</t>
+    <t xml:space="preserve">2.3616635799408</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36321306228638</t>
+    <t xml:space="preserve">2.3632128238678</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31982326507568</t>
+    <t xml:space="preserve">2.31982254981995</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35236573219299</t>
+    <t xml:space="preserve">2.35236525535583</t>
   </si>
   <si>
     <t xml:space="preserve">2.26868462562561</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32292199134827</t>
+    <t xml:space="preserve">2.32292222976685</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33531951904297</t>
+    <t xml:space="preserve">2.33531928062439</t>
   </si>
   <si>
     <t xml:space="preserve">2.33996844291687</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31052541732788</t>
+    <t xml:space="preserve">2.31052470207214</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28573060035706</t>
+    <t xml:space="preserve">2.28573083877563</t>
   </si>
   <si>
     <t xml:space="preserve">2.25473761558533</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29038000106812</t>
+    <t xml:space="preserve">2.29037976264954</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27488327026367</t>
+    <t xml:space="preserve">2.27488350868225</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2314932346344</t>
+    <t xml:space="preserve">2.23149275779724</t>
   </si>
   <si>
     <t xml:space="preserve">2.07497835159302</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00834369659424</t>
+    <t xml:space="preserve">2.00834345817566</t>
   </si>
   <si>
     <t xml:space="preserve">2.03468775749207</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02229046821594</t>
+    <t xml:space="preserve">2.02229070663452</t>
   </si>
   <si>
     <t xml:space="preserve">1.97580111026764</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91980683803558</t>
+    <t xml:space="preserve">1.919806599617</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88216388225555</t>
+    <t xml:space="preserve">1.88216352462769</t>
   </si>
   <si>
     <t xml:space="preserve">2.00136709213257</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96058702468872</t>
+    <t xml:space="preserve">1.96058678627014</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9025536775589</t>
+    <t xml:space="preserve">1.90255343914032</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92137551307678</t>
+    <t xml:space="preserve">1.92137515544891</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91353285312653</t>
+    <t xml:space="preserve">1.91353297233582</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89784824848175</t>
+    <t xml:space="preserve">1.89784812927246</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89000594615936</t>
+    <t xml:space="preserve">1.89000606536865</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85079395771027</t>
+    <t xml:space="preserve">1.85079383850098</t>
   </si>
   <si>
     <t xml:space="preserve">1.88059496879578</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86647891998291</t>
+    <t xml:space="preserve">1.8664790391922</t>
   </si>
   <si>
     <t xml:space="preserve">1.546511054039</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68610489368439</t>
+    <t xml:space="preserve">1.68610501289368</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70178937911987</t>
+    <t xml:space="preserve">1.70178961753845</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70022118091583</t>
+    <t xml:space="preserve">1.70022082328796</t>
   </si>
   <si>
     <t xml:space="preserve">1.66257762908936</t>
@@ -293,25 +293,25 @@
     <t xml:space="preserve">1.64532458782196</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62336587905884</t>
+    <t xml:space="preserve">1.62336599826813</t>
   </si>
   <si>
     <t xml:space="preserve">1.61552357673645</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63120830059052</t>
+    <t xml:space="preserve">1.63120806217194</t>
   </si>
   <si>
     <t xml:space="preserve">1.58415424823761</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64689326286316</t>
+    <t xml:space="preserve">1.64689290523529</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64061915874481</t>
+    <t xml:space="preserve">1.64061903953552</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6390506029129</t>
+    <t xml:space="preserve">1.63905072212219</t>
   </si>
   <si>
     <t xml:space="preserve">1.60768139362335</t>
@@ -320,10 +320,10 @@
     <t xml:space="preserve">1.57631182670593</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59199643135071</t>
+    <t xml:space="preserve">1.59199666976929</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75668585300446</t>
+    <t xml:space="preserve">1.75668597221375</t>
   </si>
   <si>
     <t xml:space="preserve">1.84295177459717</t>
@@ -338,34 +338,34 @@
     <t xml:space="preserve">1.88530027866364</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9009850025177</t>
+    <t xml:space="preserve">1.90098512172699</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91823828220367</t>
+    <t xml:space="preserve">1.91823852062225</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9496077299118</t>
+    <t xml:space="preserve">1.94960761070251</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93078625202179</t>
+    <t xml:space="preserve">1.93078601360321</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84922575950623</t>
+    <t xml:space="preserve">1.84922552108765</t>
   </si>
   <si>
     <t xml:space="preserve">1.82413017749786</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85549938678741</t>
+    <t xml:space="preserve">1.8554995059967</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89627981185913</t>
+    <t xml:space="preserve">1.89627969264984</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93705976009369</t>
+    <t xml:space="preserve">1.93706023693085</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8743212223053</t>
+    <t xml:space="preserve">1.87432134151459</t>
   </si>
   <si>
     <t xml:space="preserve">1.94333362579346</t>
@@ -374,16 +374,16 @@
     <t xml:space="preserve">1.94490230083466</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96686041355133</t>
+    <t xml:space="preserve">1.9668607711792</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98411381244659</t>
+    <t xml:space="preserve">1.98411393165588</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0625376701355</t>
+    <t xml:space="preserve">2.06253719329834</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05312657356262</t>
+    <t xml:space="preserve">2.0531268119812</t>
   </si>
   <si>
     <t xml:space="preserve">2.05155825614929</t>
@@ -398,7 +398,7 @@
     <t xml:space="preserve">2.03116798400879</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06096911430359</t>
+    <t xml:space="preserve">2.06096887588501</t>
   </si>
   <si>
     <t xml:space="preserve">2.09390711784363</t>
@@ -416,106 +416,106 @@
     <t xml:space="preserve">2.19585728645325</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2021312713623</t>
+    <t xml:space="preserve">2.20213103294373</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23350071907043</t>
+    <t xml:space="preserve">2.23350095748901</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20997381210327</t>
+    <t xml:space="preserve">2.20997357368469</t>
   </si>
   <si>
     <t xml:space="preserve">2.18017268180847</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16605639457703</t>
+    <t xml:space="preserve">2.16605663299561</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1942892074585</t>
+    <t xml:space="preserve">2.19428896903992</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17389893531799</t>
+    <t xml:space="preserve">2.17389869689941</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2005627155304</t>
+    <t xml:space="preserve">2.20056295394897</t>
   </si>
   <si>
     <t xml:space="preserve">2.21938419342041</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21781587600708</t>
+    <t xml:space="preserve">2.21781635284424</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19115209579468</t>
+    <t xml:space="preserve">2.1911518573761</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12057089805603</t>
+    <t xml:space="preserve">2.12057065963745</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15350866317749</t>
+    <t xml:space="preserve">2.15350842475891</t>
   </si>
   <si>
     <t xml:space="preserve">2.11743378639221</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16291952133179</t>
+    <t xml:space="preserve">2.16291928291321</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10802268981934</t>
+    <t xml:space="preserve">2.10802316665649</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01548337936401</t>
+    <t xml:space="preserve">2.01548314094543</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04528450965881</t>
+    <t xml:space="preserve">2.04528427124023</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98568248748779</t>
+    <t xml:space="preserve">1.98568272590637</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07822251319885</t>
+    <t xml:space="preserve">2.07822203636169</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06724286079407</t>
+    <t xml:space="preserve">2.06724262237549</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12998175621033</t>
+    <t xml:space="preserve">2.12998151779175</t>
   </si>
   <si>
     <t xml:space="preserve">2.11586546897888</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05469512939453</t>
+    <t xml:space="preserve">2.05469489097595</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11429691314697</t>
+    <t xml:space="preserve">2.11429715156555</t>
   </si>
   <si>
     <t xml:space="preserve">2.05626344680786</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06410598754883</t>
+    <t xml:space="preserve">2.06410574913025</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10488629341125</t>
+    <t xml:space="preserve">2.10488653182983</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00920987129211</t>
+    <t xml:space="preserve">2.00920963287354</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01391506195068</t>
+    <t xml:space="preserve">2.0139148235321</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04842138290405</t>
+    <t xml:space="preserve">2.04842114448547</t>
   </si>
   <si>
     <t xml:space="preserve">2.1644880771637</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18487811088562</t>
+    <t xml:space="preserve">2.1848783493042</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26643848419189</t>
+    <t xml:space="preserve">2.26643872261047</t>
   </si>
   <si>
     <t xml:space="preserve">2.27271246910095</t>
@@ -524,22 +524,22 @@
     <t xml:space="preserve">2.25702786445618</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30721855163574</t>
+    <t xml:space="preserve">2.3072190284729</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2303638458252</t>
+    <t xml:space="preserve">2.23036360740662</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37152600288391</t>
+    <t xml:space="preserve">2.37152624130249</t>
   </si>
   <si>
     <t xml:space="preserve">2.35270428657532</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39191603660583</t>
+    <t xml:space="preserve">2.39191579818726</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33545088768005</t>
+    <t xml:space="preserve">2.33545112609863</t>
   </si>
   <si>
     <t xml:space="preserve">2.31349277496338</t>
@@ -557,22 +557,22 @@
     <t xml:space="preserve">2.28839707374573</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33701968193054</t>
+    <t xml:space="preserve">2.33701992034912</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34486198425293</t>
+    <t xml:space="preserve">2.34486174583435</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3495671749115</t>
+    <t xml:space="preserve">2.34956741333008</t>
   </si>
   <si>
     <t xml:space="preserve">2.32604050636292</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30251336097717</t>
+    <t xml:space="preserve">2.30251359939575</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31192398071289</t>
+    <t xml:space="preserve">2.31192421913147</t>
   </si>
   <si>
     <t xml:space="preserve">2.25075387954712</t>
@@ -581,70 +581,70 @@
     <t xml:space="preserve">2.27428102493286</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43896985054016</t>
+    <t xml:space="preserve">2.43897008895874</t>
   </si>
   <si>
     <t xml:space="preserve">2.48445582389832</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46249723434448</t>
+    <t xml:space="preserve">2.46249747276306</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50798273086548</t>
+    <t xml:space="preserve">2.50798296928406</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4860246181488</t>
+    <t xml:space="preserve">2.48602414131165</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60993313789368</t>
+    <t xml:space="preserve">2.60993361473083</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66639828681946</t>
+    <t xml:space="preserve">2.66639876365662</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66326117515564</t>
+    <t xml:space="preserve">2.66326141357422</t>
   </si>
   <si>
     <t xml:space="preserve">2.66012454032898</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64287114143372</t>
+    <t xml:space="preserve">2.64287137985229</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65855622291565</t>
+    <t xml:space="preserve">2.65855598449707</t>
   </si>
   <si>
     <t xml:space="preserve">2.60209107398987</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55033135414124</t>
+    <t xml:space="preserve">2.55033159255981</t>
   </si>
   <si>
     <t xml:space="preserve">2.63816595077515</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58013248443604</t>
+    <t xml:space="preserve">2.58013224601746</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59581732749939</t>
+    <t xml:space="preserve">2.59581685066223</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58170127868652</t>
+    <t xml:space="preserve">2.58170104026794</t>
   </si>
   <si>
     <t xml:space="preserve">2.6036593914032</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61934423446655</t>
+    <t xml:space="preserve">2.61934399604797</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57542681694031</t>
+    <t xml:space="preserve">2.57542705535889</t>
   </si>
   <si>
     <t xml:space="preserve">2.57385873794556</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50955128669739</t>
+    <t xml:space="preserve">2.50955152511597</t>
   </si>
   <si>
     <t xml:space="preserve">2.58797478675842</t>
@@ -653,7 +653,7 @@
     <t xml:space="preserve">2.56444787979126</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61150193214417</t>
+    <t xml:space="preserve">2.61150145530701</t>
   </si>
   <si>
     <t xml:space="preserve">2.56915330886841</t>
@@ -662,37 +662,37 @@
     <t xml:space="preserve">2.63502883911133</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62561821937561</t>
+    <t xml:space="preserve">2.62561798095703</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62718629837036</t>
+    <t xml:space="preserve">2.62718653678894</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83422470092773</t>
+    <t xml:space="preserve">2.83422446250916</t>
   </si>
   <si>
     <t xml:space="preserve">2.79030752182007</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77619123458862</t>
+    <t xml:space="preserve">2.77619075775146</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78089666366577</t>
+    <t xml:space="preserve">2.78089642524719</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69149351119995</t>
+    <t xml:space="preserve">2.69149374961853</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78246521949768</t>
+    <t xml:space="preserve">2.7824649810791</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81226587295532</t>
+    <t xml:space="preserve">2.8122661113739</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82324504852295</t>
+    <t xml:space="preserve">2.82324552536011</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68678855895996</t>
+    <t xml:space="preserve">2.6867880821228</t>
   </si>
   <si>
     <t xml:space="preserve">2.70090460777283</t>
@@ -701,10 +701,10 @@
     <t xml:space="preserve">2.80657124519348</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86433935165405</t>
+    <t xml:space="preserve">2.86433959007263</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81940865516663</t>
+    <t xml:space="preserve">2.81940889358521</t>
   </si>
   <si>
     <t xml:space="preserve">2.80817627906799</t>
@@ -713,34 +713,34 @@
     <t xml:space="preserve">2.88038611412048</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83385062217712</t>
+    <t xml:space="preserve">2.8338508605957</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74398899078369</t>
+    <t xml:space="preserve">2.74398922920227</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72794246673584</t>
+    <t xml:space="preserve">2.72794270515442</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70547699928284</t>
+    <t xml:space="preserve">2.70547676086426</t>
   </si>
   <si>
     <t xml:space="preserve">2.73275637626648</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67177891731262</t>
+    <t xml:space="preserve">2.67177844047546</t>
   </si>
   <si>
     <t xml:space="preserve">2.62363886833191</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61721992492676</t>
+    <t xml:space="preserve">2.61722016334534</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60438275337219</t>
+    <t xml:space="preserve">2.60438299179077</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62524318695068</t>
+    <t xml:space="preserve">2.62524342536926</t>
   </si>
   <si>
     <t xml:space="preserve">2.64129042625427</t>
@@ -755,16 +755,16 @@
     <t xml:space="preserve">2.74719858169556</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71991944313049</t>
+    <t xml:space="preserve">2.71991896629333</t>
   </si>
   <si>
     <t xml:space="preserve">2.72633767127991</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74238443374634</t>
+    <t xml:space="preserve">2.74238467216492</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80015277862549</t>
+    <t xml:space="preserve">2.80015254020691</t>
   </si>
   <si>
     <t xml:space="preserve">2.78571057319641</t>
@@ -773,73 +773,73 @@
     <t xml:space="preserve">2.82422280311584</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78731536865234</t>
+    <t xml:space="preserve">2.78731513023376</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79373383522034</t>
+    <t xml:space="preserve">2.7937343120575</t>
   </si>
   <si>
     <t xml:space="preserve">2.80496668815613</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78410601615906</t>
+    <t xml:space="preserve">2.78410625457764</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77608227729797</t>
+    <t xml:space="preserve">2.77608251571655</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79533839225769</t>
+    <t xml:space="preserve">2.79533863067627</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82261824607849</t>
+    <t xml:space="preserve">2.82261800765991</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76003575325012</t>
+    <t xml:space="preserve">2.7600359916687</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77929186820984</t>
+    <t xml:space="preserve">2.77929210662842</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79854774475098</t>
+    <t xml:space="preserve">2.79854798316956</t>
   </si>
   <si>
     <t xml:space="preserve">2.7744779586792</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8033618927002</t>
+    <t xml:space="preserve">2.80336213111877</t>
   </si>
   <si>
     <t xml:space="preserve">2.83545517921448</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84026956558228</t>
+    <t xml:space="preserve">2.8402693271637</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83224630355835</t>
+    <t xml:space="preserve">2.83224606513977</t>
   </si>
   <si>
     <t xml:space="preserve">2.8113853931427</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81619954109192</t>
+    <t xml:space="preserve">2.81619930267334</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76324534416199</t>
+    <t xml:space="preserve">2.76324510574341</t>
   </si>
   <si>
     <t xml:space="preserve">2.71189594268799</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72473287582397</t>
+    <t xml:space="preserve">2.72473311424255</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79694318771362</t>
+    <t xml:space="preserve">2.7969434261322</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79052472114563</t>
+    <t xml:space="preserve">2.79052448272705</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76805901527405</t>
+    <t xml:space="preserve">2.76805925369263</t>
   </si>
   <si>
     <t xml:space="preserve">2.73115181922913</t>
@@ -854,7 +854,7 @@
     <t xml:space="preserve">2.82903671264648</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84347867965698</t>
+    <t xml:space="preserve">2.84347891807556</t>
   </si>
   <si>
     <t xml:space="preserve">2.77768707275391</t>
@@ -863,25 +863,25 @@
     <t xml:space="preserve">2.77126884460449</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88840937614441</t>
+    <t xml:space="preserve">2.88840985298157</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87236309051514</t>
+    <t xml:space="preserve">2.87236285209656</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89161920547485</t>
+    <t xml:space="preserve">2.89161896705627</t>
   </si>
   <si>
     <t xml:space="preserve">2.92852640151978</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85952544212341</t>
+    <t xml:space="preserve">2.85952568054199</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90927028656006</t>
+    <t xml:space="preserve">2.90927004814148</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99913167953491</t>
+    <t xml:space="preserve">2.99913191795349</t>
   </si>
   <si>
     <t xml:space="preserve">2.96864318847656</t>
@@ -890,13 +890,13 @@
     <t xml:space="preserve">2.830641746521</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87878155708313</t>
+    <t xml:space="preserve">2.87878203392029</t>
   </si>
   <si>
     <t xml:space="preserve">2.87717700004578</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87557244300842</t>
+    <t xml:space="preserve">2.87557220458984</t>
   </si>
   <si>
     <t xml:space="preserve">2.7520124912262</t>
@@ -917,28 +917,28 @@
     <t xml:space="preserve">2.82582759857178</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84829258918762</t>
+    <t xml:space="preserve">2.84829306602478</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82101321220398</t>
+    <t xml:space="preserve">2.82101345062256</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73436117172241</t>
+    <t xml:space="preserve">2.73436093330383</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81780433654785</t>
+    <t xml:space="preserve">2.81780409812927</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76484990119934</t>
+    <t xml:space="preserve">2.76485013961792</t>
   </si>
   <si>
     <t xml:space="preserve">2.74077963829041</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79212951660156</t>
+    <t xml:space="preserve">2.79212927818298</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66375541687012</t>
+    <t xml:space="preserve">2.6637556552887</t>
   </si>
   <si>
     <t xml:space="preserve">2.6075918674469</t>
@@ -950,16 +950,16 @@
     <t xml:space="preserve">2.56747531890869</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59956860542297</t>
+    <t xml:space="preserve">2.59956884384155</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55945205688477</t>
+    <t xml:space="preserve">2.55945181846619</t>
   </si>
   <si>
     <t xml:space="preserve">2.50328826904297</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45514798164368</t>
+    <t xml:space="preserve">2.45514845848083</t>
   </si>
   <si>
     <t xml:space="preserve">2.47921824455261</t>
@@ -971,25 +971,25 @@
     <t xml:space="preserve">2.4310781955719</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46317172050476</t>
+    <t xml:space="preserve">2.46317148208618</t>
   </si>
   <si>
     <t xml:space="preserve">2.48724150657654</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49526453018188</t>
+    <t xml:space="preserve">2.49526500701904</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52735829353333</t>
+    <t xml:space="preserve">2.5273585319519</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58352208137512</t>
+    <t xml:space="preserve">2.58352184295654</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65573239326477</t>
+    <t xml:space="preserve">2.65573215484619</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91247987747192</t>
+    <t xml:space="preserve">2.9124801158905</t>
   </si>
   <si>
     <t xml:space="preserve">2.82002472877502</t>
@@ -998,22 +998,22 @@
     <t xml:space="preserve">2.80358171463013</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86935472488403</t>
+    <t xml:space="preserve">2.86935448646545</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84468960762024</t>
+    <t xml:space="preserve">2.8446900844574</t>
   </si>
   <si>
     <t xml:space="preserve">2.85291147232056</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81180310249329</t>
+    <t xml:space="preserve">2.81180334091187</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72136545181274</t>
+    <t xml:space="preserve">2.72136521339417</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68025684356689</t>
+    <t xml:space="preserve">2.68025708198547</t>
   </si>
   <si>
     <t xml:space="preserve">2.69670009613037</t>
@@ -1022,13 +1022,13 @@
     <t xml:space="preserve">2.64737033843994</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65559196472168</t>
+    <t xml:space="preserve">2.6555917263031</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66381359100342</t>
+    <t xml:space="preserve">2.663813829422</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63092708587646</t>
+    <t xml:space="preserve">2.63092732429504</t>
   </si>
   <si>
     <t xml:space="preserve">2.6391487121582</t>
@@ -1040,7 +1040,7 @@
     <t xml:space="preserve">2.59804058074951</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54871034622192</t>
+    <t xml:space="preserve">2.5487105846405</t>
   </si>
   <si>
     <t xml:space="preserve">2.46649408340454</t>
@@ -1049,28 +1049,28 @@
     <t xml:space="preserve">2.60626220703125</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52404546737671</t>
+    <t xml:space="preserve">2.52404570579529</t>
   </si>
   <si>
     <t xml:space="preserve">2.58159708976746</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61448383331299</t>
+    <t xml:space="preserve">2.61448407173157</t>
   </si>
   <si>
     <t xml:space="preserve">2.58981871604919</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62270545959473</t>
+    <t xml:space="preserve">2.62270522117615</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51582384109497</t>
+    <t xml:space="preserve">2.51582407951355</t>
   </si>
   <si>
     <t xml:space="preserve">2.57337546348572</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5651535987854</t>
+    <t xml:space="preserve">2.56515383720398</t>
   </si>
   <si>
     <t xml:space="preserve">2.53226709365845</t>
@@ -1082,25 +1082,25 @@
     <t xml:space="preserve">2.48293733596802</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45005083084106</t>
+    <t xml:space="preserve">2.45005106925964</t>
   </si>
   <si>
     <t xml:space="preserve">2.44182920455933</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42538595199585</t>
+    <t xml:space="preserve">2.42538571357727</t>
   </si>
   <si>
     <t xml:space="preserve">2.43360757827759</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49115896224976</t>
+    <t xml:space="preserve">2.49115872383118</t>
   </si>
   <si>
     <t xml:space="preserve">2.50760221481323</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54048895835876</t>
+    <t xml:space="preserve">2.54048871994019</t>
   </si>
   <si>
     <t xml:space="preserve">2.67203521728516</t>
@@ -1109,16 +1109,16 @@
     <t xml:space="preserve">2.68847846984863</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70492196083069</t>
+    <t xml:space="preserve">2.70492172241211</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71314334869385</t>
+    <t xml:space="preserve">2.71314358711243</t>
   </si>
   <si>
     <t xml:space="preserve">2.75425171852112</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78713846206665</t>
+    <t xml:space="preserve">2.78713822364807</t>
   </si>
   <si>
     <t xml:space="preserve">2.77069497108459</t>
@@ -1127,13 +1127,13 @@
     <t xml:space="preserve">2.7295868396759</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74603009223938</t>
+    <t xml:space="preserve">2.7460298538208</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77891659736633</t>
+    <t xml:space="preserve">2.77891683578491</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79535984992981</t>
+    <t xml:space="preserve">2.79536032676697</t>
   </si>
   <si>
     <t xml:space="preserve">2.87757658958435</t>
@@ -1148,31 +1148,31 @@
     <t xml:space="preserve">2.86113309860229</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90224146842957</t>
+    <t xml:space="preserve">2.90224123001099</t>
   </si>
   <si>
     <t xml:space="preserve">2.88579821586609</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8364679813385</t>
+    <t xml:space="preserve">2.83646821975708</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94334936141968</t>
+    <t xml:space="preserve">2.94334959983826</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82824635505676</t>
+    <t xml:space="preserve">2.82824683189392</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92690634727478</t>
+    <t xml:space="preserve">2.9269061088562</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80358123779297</t>
+    <t xml:space="preserve">2.80358147621155</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77809429168701</t>
+    <t xml:space="preserve">2.77809476852417</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82057285308838</t>
+    <t xml:space="preserve">2.82057309150696</t>
   </si>
   <si>
     <t xml:space="preserve">2.82906866073608</t>
@@ -1184,25 +1184,25 @@
     <t xml:space="preserve">2.88004302978516</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92252135276794</t>
+    <t xml:space="preserve">2.92252159118652</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90552997589111</t>
+    <t xml:space="preserve">2.90552973747253</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87154698371887</t>
+    <t xml:space="preserve">2.87154746055603</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85455560684204</t>
+    <t xml:space="preserve">2.85455536842346</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91402554512024</t>
+    <t xml:space="preserve">2.91402578353882</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93101692199707</t>
+    <t xml:space="preserve">2.93101716041565</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9480082988739</t>
+    <t xml:space="preserve">2.94800853729248</t>
   </si>
   <si>
     <t xml:space="preserve">2.89703440666199</t>
@@ -1217,16 +1217,16 @@
     <t xml:space="preserve">2.79508590698242</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78658986091614</t>
+    <t xml:space="preserve">2.78659009933472</t>
   </si>
   <si>
     <t xml:space="preserve">2.76110291481018</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76959872245789</t>
+    <t xml:space="preserve">2.76959848403931</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81207728385925</t>
+    <t xml:space="preserve">2.81207704544067</t>
   </si>
   <si>
     <t xml:space="preserve">2.83756422996521</t>
@@ -1250,10 +1250,10 @@
     <t xml:space="preserve">2.51472759246826</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49773645401001</t>
+    <t xml:space="preserve">2.49773621559143</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48074507713318</t>
+    <t xml:space="preserve">2.4807448387146</t>
   </si>
   <si>
     <t xml:space="preserve">2.53171896934509</t>
@@ -1265,13 +1265,13 @@
     <t xml:space="preserve">2.58269309997559</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54021453857422</t>
+    <t xml:space="preserve">2.5402147769928</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56570196151733</t>
+    <t xml:space="preserve">2.56570172309875</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59118914604187</t>
+    <t xml:space="preserve">2.59118890762329</t>
   </si>
   <si>
     <t xml:space="preserve">2.47224926948547</t>
@@ -1289,7 +1289,7 @@
     <t xml:space="preserve">2.57419753074646</t>
   </si>
   <si>
-    <t xml:space="preserve">3.075443983078</t>
+    <t xml:space="preserve">3.07544374465942</t>
   </si>
   <si>
     <t xml:space="preserve">3.00747847557068</t>
@@ -1304,37 +1304,37 @@
     <t xml:space="preserve">2.97349572181702</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95650434494019</t>
+    <t xml:space="preserve">2.95650410652161</t>
   </si>
   <si>
     <t xml:space="preserve">2.84606003761292</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75260758399963</t>
+    <t xml:space="preserve">2.75260734558105</t>
   </si>
   <si>
     <t xml:space="preserve">2.66765022277832</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65915441513062</t>
+    <t xml:space="preserve">2.65915465354919</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31083106994629</t>
+    <t xml:space="preserve">2.31083083152771</t>
   </si>
   <si>
     <t xml:space="preserve">2.35330939292908</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34481358528137</t>
+    <t xml:space="preserve">2.34481334686279</t>
   </si>
   <si>
     <t xml:space="preserve">2.45525789260864</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4892406463623</t>
+    <t xml:space="preserve">2.48924040794373</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65065860748291</t>
+    <t xml:space="preserve">2.65065884590149</t>
   </si>
   <si>
     <t xml:space="preserve">2.64216327667236</t>
@@ -1343,13 +1343,13 @@
     <t xml:space="preserve">2.71012878417969</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69313740730286</t>
+    <t xml:space="preserve">2.69313764572144</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71862483024597</t>
+    <t xml:space="preserve">2.71862435340881</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74411153793335</t>
+    <t xml:space="preserve">2.74411177635193</t>
   </si>
   <si>
     <t xml:space="preserve">2.68464183807373</t>
@@ -1358,46 +1358,46 @@
     <t xml:space="preserve">2.6081805229187</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50623178482056</t>
+    <t xml:space="preserve">2.50623226165771</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44676232337952</t>
+    <t xml:space="preserve">2.44676184654236</t>
   </si>
   <si>
     <t xml:space="preserve">2.37879633903503</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42977070808411</t>
+    <t xml:space="preserve">2.42977046966553</t>
   </si>
   <si>
     <t xml:space="preserve">2.37030076980591</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31932663917542</t>
+    <t xml:space="preserve">2.31932640075684</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27684807777405</t>
+    <t xml:space="preserve">2.27684783935547</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26835227012634</t>
+    <t xml:space="preserve">2.26835250854492</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30233526229858</t>
+    <t xml:space="preserve">2.30233502388</t>
   </si>
   <si>
     <t xml:space="preserve">2.33631801605225</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39578771591187</t>
+    <t xml:space="preserve">2.39578747749329</t>
   </si>
   <si>
     <t xml:space="preserve">2.72712016105652</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99898266792297</t>
+    <t xml:space="preserve">2.99898242950439</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03296542167664</t>
+    <t xml:space="preserve">3.03296518325806</t>
   </si>
   <si>
     <t xml:space="preserve">3.0159740447998</t>
@@ -1409,13 +1409,13 @@
     <t xml:space="preserve">3.1943838596344</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12641835212708</t>
+    <t xml:space="preserve">3.1264181137085</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05845212936401</t>
+    <t xml:space="preserve">3.05845260620117</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09243535995483</t>
+    <t xml:space="preserve">3.09243559837341</t>
   </si>
   <si>
     <t xml:space="preserve">3.16040110588074</t>
@@ -1424,13 +1424,13 @@
     <t xml:space="preserve">3.21137523651123</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3133237361908</t>
+    <t xml:space="preserve">3.31332349777222</t>
   </si>
   <si>
     <t xml:space="preserve">3.26234936714172</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33031487464905</t>
+    <t xml:space="preserve">3.33031511306763</t>
   </si>
   <si>
     <t xml:space="preserve">3.22836661338806</t>
@@ -1442,7 +1442,7 @@
     <t xml:space="preserve">3.14340949058533</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10942673683167</t>
+    <t xml:space="preserve">3.10942697525024</t>
   </si>
   <si>
     <t xml:space="preserve">3.27934074401855</t>
@@ -1469,16 +1469,16 @@
     <t xml:space="preserve">3.02446961402893</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16417121887207</t>
+    <t xml:space="preserve">3.16417145729065</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05022621154785</t>
+    <t xml:space="preserve">3.05022597312927</t>
   </si>
   <si>
     <t xml:space="preserve">3.05899119377136</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01516604423523</t>
+    <t xml:space="preserve">3.01516628265381</t>
   </si>
   <si>
     <t xml:space="preserve">2.97134113311768</t>
@@ -1490,7 +1490,7 @@
     <t xml:space="preserve">3.1028163433075</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13787603378296</t>
+    <t xml:space="preserve">3.13787627220154</t>
   </si>
   <si>
     <t xml:space="preserve">2.98010611534119</t>
@@ -1508,13 +1508,13 @@
     <t xml:space="preserve">3.04146122932434</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00640106201172</t>
+    <t xml:space="preserve">3.0064013004303</t>
   </si>
   <si>
     <t xml:space="preserve">2.9888710975647</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89245557785034</t>
+    <t xml:space="preserve">2.89245581626892</t>
   </si>
   <si>
     <t xml:space="preserve">2.92751574516296</t>
@@ -1526,22 +1526,22 @@
     <t xml:space="preserve">2.96257615089417</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86616063117981</t>
+    <t xml:space="preserve">2.86616086959839</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91875100135803</t>
+    <t xml:space="preserve">2.91875076293945</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80480575561523</t>
+    <t xml:space="preserve">2.80480551719666</t>
   </si>
   <si>
     <t xml:space="preserve">2.82233572006226</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94504594802856</t>
+    <t xml:space="preserve">2.94504570960999</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95381093025208</t>
+    <t xml:space="preserve">2.9538106918335</t>
   </si>
   <si>
     <t xml:space="preserve">2.83110070228577</t>
@@ -1550,16 +1550,16 @@
     <t xml:space="preserve">2.93628096580505</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03269600868225</t>
+    <t xml:space="preserve">3.03269624710083</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90122103691101</t>
+    <t xml:space="preserve">2.90122079849243</t>
   </si>
   <si>
     <t xml:space="preserve">2.88369083404541</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87492561340332</t>
+    <t xml:space="preserve">2.8749258518219</t>
   </si>
   <si>
     <t xml:space="preserve">2.81357073783875</t>
@@ -1568,7 +1568,7 @@
     <t xml:space="preserve">2.83986592292786</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68209528923035</t>
+    <t xml:space="preserve">2.68209552764893</t>
   </si>
   <si>
     <t xml:space="preserve">2.69086050987244</t>
@@ -1577,28 +1577,28 @@
     <t xml:space="preserve">2.66456532478333</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85739588737488</t>
+    <t xml:space="preserve">2.8573956489563</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90998578071594</t>
+    <t xml:space="preserve">2.90998601913452</t>
   </si>
   <si>
     <t xml:space="preserve">2.7785108089447</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76974582672119</t>
+    <t xml:space="preserve">2.76974558830261</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79604077339172</t>
+    <t xml:space="preserve">2.79604053497314</t>
   </si>
   <si>
     <t xml:space="preserve">2.84863066673279</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08528637886047</t>
+    <t xml:space="preserve">3.08528614044189</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76098036766052</t>
+    <t xml:space="preserve">2.7609806060791</t>
   </si>
   <si>
     <t xml:space="preserve">2.78727579116821</t>
@@ -1625,34 +1625,34 @@
     <t xml:space="preserve">2.83221411705017</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8870313167572</t>
+    <t xml:space="preserve">2.88703107833862</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85048627853394</t>
+    <t xml:space="preserve">2.85048651695251</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96012043952942</t>
+    <t xml:space="preserve">2.960120677948</t>
   </si>
   <si>
     <t xml:space="preserve">2.99666523933411</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79566955566406</t>
+    <t xml:space="preserve">2.79566931724548</t>
   </si>
   <si>
     <t xml:space="preserve">2.81394171714783</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77739691734314</t>
+    <t xml:space="preserve">2.77739715576172</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75912475585938</t>
+    <t xml:space="preserve">2.7591245174408</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70430779457092</t>
+    <t xml:space="preserve">2.70430755615234</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64949083328247</t>
+    <t xml:space="preserve">2.64949059486389</t>
   </si>
   <si>
     <t xml:space="preserve">2.68603539466858</t>
@@ -1670,25 +1670,22 @@
     <t xml:space="preserve">2.72258019447327</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59467339515686</t>
+    <t xml:space="preserve">2.59467363357544</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5764012336731</t>
+    <t xml:space="preserve">2.57640099525452</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61294603347778</t>
+    <t xml:space="preserve">2.6129457950592</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97839307785034</t>
+    <t xml:space="preserve">2.97839283943176</t>
   </si>
   <si>
     <t xml:space="preserve">2.823077917099</t>
   </si>
   <si>
     <t xml:space="preserve">2.85962271690369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80480551719666</t>
   </si>
   <si>
     <t xml:space="preserve">2.89616751670837</t>
@@ -1703,7 +1700,7 @@
     <t xml:space="preserve">3.01493763923645</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96925687789917</t>
+    <t xml:space="preserve">2.96925663948059</t>
   </si>
   <si>
     <t xml:space="preserve">3.02674722671509</t>
@@ -1800,6 +1797,9 @@
   </si>
   <si>
     <t xml:space="preserve">3.23614478111267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96012043952942</t>
   </si>
   <si>
     <t xml:space="preserve">3.20000004768372</t>
@@ -56985,7 +56985,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G2103" t="s">
-        <v>558</v>
+        <v>506</v>
       </c>
       <c r="H2103" t="s">
         <v>9</v>
@@ -57011,7 +57011,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G2104" t="s">
-        <v>558</v>
+        <v>506</v>
       </c>
       <c r="H2104" t="s">
         <v>9</v>
@@ -57219,7 +57219,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G2112" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="H2112" t="s">
         <v>9</v>
@@ -57349,7 +57349,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G2117" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="H2117" t="s">
         <v>9</v>
@@ -57375,7 +57375,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G2118" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="H2118" t="s">
         <v>9</v>
@@ -57401,7 +57401,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G2119" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="H2119" t="s">
         <v>9</v>
@@ -57453,7 +57453,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G2121" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="H2121" t="s">
         <v>9</v>
@@ -57479,7 +57479,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G2122" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="H2122" t="s">
         <v>9</v>
@@ -57531,7 +57531,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G2124" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="H2124" t="s">
         <v>9</v>
@@ -57557,7 +57557,7 @@
         <v>3.25</v>
       </c>
       <c r="G2125" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="H2125" t="s">
         <v>9</v>
@@ -57583,7 +57583,7 @@
         <v>3.25</v>
       </c>
       <c r="G2126" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="H2126" t="s">
         <v>9</v>
@@ -57609,7 +57609,7 @@
         <v>3.25</v>
       </c>
       <c r="G2127" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="H2127" t="s">
         <v>9</v>
@@ -57635,7 +57635,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G2128" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="H2128" t="s">
         <v>9</v>
@@ -57661,7 +57661,7 @@
         <v>3.25</v>
       </c>
       <c r="G2129" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="H2129" t="s">
         <v>9</v>
@@ -57765,7 +57765,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G2133" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="H2133" t="s">
         <v>9</v>
@@ -57791,7 +57791,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G2134" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H2134" t="s">
         <v>9</v>
@@ -57817,7 +57817,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G2135" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="H2135" t="s">
         <v>9</v>
@@ -57843,7 +57843,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G2136" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="H2136" t="s">
         <v>9</v>
@@ -57869,7 +57869,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G2137" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="H2137" t="s">
         <v>9</v>
@@ -57895,7 +57895,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G2138" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="H2138" t="s">
         <v>9</v>
@@ -57921,7 +57921,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G2139" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="H2139" t="s">
         <v>9</v>
@@ -57947,7 +57947,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2140" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H2140" t="s">
         <v>9</v>
@@ -57973,7 +57973,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G2141" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="H2141" t="s">
         <v>9</v>
@@ -57999,7 +57999,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G2142" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="H2142" t="s">
         <v>9</v>
@@ -58025,7 +58025,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G2143" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="H2143" t="s">
         <v>9</v>
@@ -58051,7 +58051,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G2144" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="H2144" t="s">
         <v>9</v>
@@ -58077,7 +58077,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G2145" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="H2145" t="s">
         <v>9</v>
@@ -58103,7 +58103,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G2146" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="H2146" t="s">
         <v>9</v>
@@ -58129,7 +58129,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G2147" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="H2147" t="s">
         <v>9</v>
@@ -58155,7 +58155,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G2148" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="H2148" t="s">
         <v>9</v>
@@ -58181,7 +58181,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G2149" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="H2149" t="s">
         <v>9</v>
@@ -58207,7 +58207,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G2150" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="H2150" t="s">
         <v>9</v>
@@ -58233,7 +58233,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G2151" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="H2151" t="s">
         <v>9</v>
@@ -58259,7 +58259,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G2152" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="H2152" t="s">
         <v>9</v>
@@ -58285,7 +58285,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G2153" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="H2153" t="s">
         <v>9</v>
@@ -58311,7 +58311,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G2154" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="H2154" t="s">
         <v>9</v>
@@ -58337,7 +58337,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G2155" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="H2155" t="s">
         <v>9</v>
@@ -58363,7 +58363,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G2156" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="H2156" t="s">
         <v>9</v>
@@ -58389,7 +58389,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G2157" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="H2157" t="s">
         <v>9</v>
@@ -58415,7 +58415,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G2158" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H2158" t="s">
         <v>9</v>
@@ -58441,7 +58441,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G2159" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="H2159" t="s">
         <v>9</v>
@@ -58467,7 +58467,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G2160" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="H2160" t="s">
         <v>9</v>
@@ -58493,7 +58493,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G2161" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H2161" t="s">
         <v>9</v>
@@ -58519,7 +58519,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G2162" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="H2162" t="s">
         <v>9</v>
@@ -58545,7 +58545,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G2163" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="H2163" t="s">
         <v>9</v>
@@ -58571,7 +58571,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G2164" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="H2164" t="s">
         <v>9</v>
@@ -58597,7 +58597,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G2165" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="H2165" t="s">
         <v>9</v>
@@ -58623,7 +58623,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G2166" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="H2166" t="s">
         <v>9</v>
@@ -58649,7 +58649,7 @@
         <v>3.25</v>
       </c>
       <c r="G2167" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="H2167" t="s">
         <v>9</v>
@@ -58675,7 +58675,7 @@
         <v>3.25</v>
       </c>
       <c r="G2168" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="H2168" t="s">
         <v>9</v>
@@ -58701,7 +58701,7 @@
         <v>3.25</v>
       </c>
       <c r="G2169" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="H2169" t="s">
         <v>9</v>
@@ -58727,7 +58727,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G2170" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="H2170" t="s">
         <v>9</v>
@@ -58753,7 +58753,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G2171" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="H2171" t="s">
         <v>9</v>
@@ -58779,7 +58779,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G2172" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="H2172" t="s">
         <v>9</v>
@@ -58805,7 +58805,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G2173" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="H2173" t="s">
         <v>9</v>
@@ -58831,7 +58831,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G2174" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="H2174" t="s">
         <v>9</v>
@@ -58857,7 +58857,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2175" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H2175" t="s">
         <v>9</v>
@@ -58883,7 +58883,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2176" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H2176" t="s">
         <v>9</v>
@@ -58909,7 +58909,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2177" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H2177" t="s">
         <v>9</v>
@@ -58935,7 +58935,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G2178" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="H2178" t="s">
         <v>9</v>
@@ -58961,7 +58961,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G2179" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="H2179" t="s">
         <v>9</v>
@@ -58987,7 +58987,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G2180" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="H2180" t="s">
         <v>9</v>
@@ -59013,7 +59013,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G2181" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="H2181" t="s">
         <v>9</v>
@@ -59039,7 +59039,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2182" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H2182" t="s">
         <v>9</v>
@@ -59065,7 +59065,7 @@
         <v>3.25</v>
       </c>
       <c r="G2183" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="H2183" t="s">
         <v>9</v>
@@ -59091,7 +59091,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G2184" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="H2184" t="s">
         <v>9</v>
@@ -59117,7 +59117,7 @@
         <v>3.25</v>
       </c>
       <c r="G2185" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="H2185" t="s">
         <v>9</v>
@@ -59143,7 +59143,7 @@
         <v>3.25</v>
       </c>
       <c r="G2186" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="H2186" t="s">
         <v>9</v>
@@ -59169,7 +59169,7 @@
         <v>3.25</v>
       </c>
       <c r="G2187" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="H2187" t="s">
         <v>9</v>
@@ -59195,7 +59195,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G2188" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="H2188" t="s">
         <v>9</v>
@@ -59221,7 +59221,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G2189" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="H2189" t="s">
         <v>9</v>
@@ -59247,7 +59247,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G2190" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="H2190" t="s">
         <v>9</v>
@@ -59273,7 +59273,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G2191" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="H2191" t="s">
         <v>9</v>
@@ -59299,7 +59299,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G2192" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="H2192" t="s">
         <v>9</v>
@@ -59325,7 +59325,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G2193" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="H2193" t="s">
         <v>9</v>
@@ -59351,7 +59351,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G2194" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="H2194" t="s">
         <v>9</v>
@@ -59377,7 +59377,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G2195" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="H2195" t="s">
         <v>9</v>
@@ -59403,7 +59403,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G2196" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="H2196" t="s">
         <v>9</v>
@@ -59429,7 +59429,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2197" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H2197" t="s">
         <v>9</v>
@@ -59455,7 +59455,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G2198" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="H2198" t="s">
         <v>9</v>
@@ -59481,7 +59481,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G2199" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H2199" t="s">
         <v>9</v>
@@ -59507,7 +59507,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G2200" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="H2200" t="s">
         <v>9</v>
@@ -59533,7 +59533,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G2201" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="H2201" t="s">
         <v>9</v>
@@ -59559,7 +59559,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G2202" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="H2202" t="s">
         <v>9</v>
@@ -59585,7 +59585,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G2203" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H2203" t="s">
         <v>9</v>
@@ -59611,7 +59611,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G2204" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="H2204" t="s">
         <v>9</v>
@@ -59637,7 +59637,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G2205" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="H2205" t="s">
         <v>9</v>
@@ -59663,7 +59663,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2206" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H2206" t="s">
         <v>9</v>
@@ -59689,7 +59689,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G2207" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="H2207" t="s">
         <v>9</v>
@@ -59715,7 +59715,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G2208" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="H2208" t="s">
         <v>9</v>
@@ -59741,7 +59741,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G2209" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="H2209" t="s">
         <v>9</v>
@@ -59767,7 +59767,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G2210" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="H2210" t="s">
         <v>9</v>
@@ -59793,7 +59793,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G2211" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="H2211" t="s">
         <v>9</v>
@@ -59819,7 +59819,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G2212" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H2212" t="s">
         <v>9</v>
@@ -59845,7 +59845,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G2213" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H2213" t="s">
         <v>9</v>
@@ -59871,7 +59871,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G2214" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="H2214" t="s">
         <v>9</v>
@@ -59897,7 +59897,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G2215" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H2215" t="s">
         <v>9</v>
@@ -59923,7 +59923,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G2216" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H2216" t="s">
         <v>9</v>
@@ -59949,7 +59949,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G2217" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="H2217" t="s">
         <v>9</v>
@@ -59975,7 +59975,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G2218" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="H2218" t="s">
         <v>9</v>
@@ -60001,7 +60001,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G2219" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="H2219" t="s">
         <v>9</v>
@@ -60027,7 +60027,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G2220" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H2220" t="s">
         <v>9</v>
@@ -60053,7 +60053,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G2221" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="H2221" t="s">
         <v>9</v>
@@ -60079,7 +60079,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G2222" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="H2222" t="s">
         <v>9</v>
@@ -60105,7 +60105,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G2223" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="H2223" t="s">
         <v>9</v>
@@ -60131,7 +60131,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G2224" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="H2224" t="s">
         <v>9</v>
@@ -60157,7 +60157,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G2225" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="H2225" t="s">
         <v>9</v>
@@ -60183,7 +60183,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G2226" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H2226" t="s">
         <v>9</v>
@@ -60209,7 +60209,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2227" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H2227" t="s">
         <v>9</v>
@@ -60235,7 +60235,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G2228" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H2228" t="s">
         <v>9</v>
@@ -60261,7 +60261,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G2229" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="H2229" t="s">
         <v>9</v>
@@ -60287,7 +60287,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G2230" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="H2230" t="s">
         <v>9</v>
@@ -60313,7 +60313,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G2231" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H2231" t="s">
         <v>9</v>
@@ -60339,7 +60339,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G2232" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H2232" t="s">
         <v>9</v>
@@ -60365,7 +60365,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G2233" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="H2233" t="s">
         <v>9</v>
@@ -60391,7 +60391,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G2234" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="H2234" t="s">
         <v>9</v>
@@ -60417,7 +60417,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G2235" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="H2235" t="s">
         <v>9</v>
@@ -60443,7 +60443,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G2236" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H2236" t="s">
         <v>9</v>
@@ -60469,7 +60469,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G2237" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="H2237" t="s">
         <v>9</v>
@@ -60495,7 +60495,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G2238" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="H2238" t="s">
         <v>9</v>
@@ -60521,7 +60521,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G2239" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="H2239" t="s">
         <v>9</v>
@@ -60547,7 +60547,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G2240" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="H2240" t="s">
         <v>9</v>
@@ -60573,7 +60573,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G2241" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="H2241" t="s">
         <v>9</v>
@@ -60599,7 +60599,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G2242" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="H2242" t="s">
         <v>9</v>
@@ -60625,7 +60625,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G2243" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H2243" t="s">
         <v>9</v>
@@ -60651,7 +60651,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G2244" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H2244" t="s">
         <v>9</v>
@@ -60677,7 +60677,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G2245" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H2245" t="s">
         <v>9</v>
@@ -60703,7 +60703,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G2246" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="H2246" t="s">
         <v>9</v>
@@ -60729,7 +60729,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G2247" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="H2247" t="s">
         <v>9</v>
@@ -60755,7 +60755,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G2248" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="H2248" t="s">
         <v>9</v>
@@ -60781,7 +60781,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G2249" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H2249" t="s">
         <v>9</v>
@@ -60807,7 +60807,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G2250" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H2250" t="s">
         <v>9</v>
@@ -60833,7 +60833,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G2251" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H2251" t="s">
         <v>9</v>
@@ -60859,7 +60859,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G2252" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="H2252" t="s">
         <v>9</v>
@@ -60885,7 +60885,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G2253" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="H2253" t="s">
         <v>9</v>
@@ -60911,7 +60911,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G2254" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="H2254" t="s">
         <v>9</v>
@@ -60937,7 +60937,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G2255" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="H2255" t="s">
         <v>9</v>
@@ -60963,7 +60963,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G2256" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="H2256" t="s">
         <v>9</v>
@@ -60989,7 +60989,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G2257" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H2257" t="s">
         <v>9</v>
@@ -61015,7 +61015,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G2258" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="H2258" t="s">
         <v>9</v>
@@ -61041,7 +61041,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G2259" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="H2259" t="s">
         <v>9</v>
@@ -61067,7 +61067,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G2260" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="H2260" t="s">
         <v>9</v>
@@ -61093,7 +61093,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G2261" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="H2261" t="s">
         <v>9</v>
@@ -61119,7 +61119,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G2262" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="H2262" t="s">
         <v>9</v>
@@ -61145,7 +61145,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G2263" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="H2263" t="s">
         <v>9</v>
@@ -61171,7 +61171,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G2264" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="H2264" t="s">
         <v>9</v>
@@ -61197,7 +61197,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G2265" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="H2265" t="s">
         <v>9</v>
@@ -61223,7 +61223,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G2266" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="H2266" t="s">
         <v>9</v>
@@ -61249,7 +61249,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G2267" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="H2267" t="s">
         <v>9</v>
@@ -61275,7 +61275,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G2268" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="H2268" t="s">
         <v>9</v>
@@ -61301,7 +61301,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G2269" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="H2269" t="s">
         <v>9</v>
@@ -61327,7 +61327,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G2270" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="H2270" t="s">
         <v>9</v>
@@ -61353,7 +61353,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G2271" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="H2271" t="s">
         <v>9</v>
@@ -61379,7 +61379,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G2272" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="H2272" t="s">
         <v>9</v>
@@ -61405,7 +61405,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G2273" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="H2273" t="s">
         <v>9</v>
@@ -61431,7 +61431,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G2274" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="H2274" t="s">
         <v>9</v>
@@ -61457,7 +61457,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G2275" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="H2275" t="s">
         <v>9</v>
@@ -61483,7 +61483,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G2276" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="H2276" t="s">
         <v>9</v>
@@ -61509,7 +61509,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G2277" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="H2277" t="s">
         <v>9</v>
@@ -61535,7 +61535,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G2278" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="H2278" t="s">
         <v>9</v>
@@ -61561,7 +61561,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G2279" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="H2279" t="s">
         <v>9</v>
@@ -61587,7 +61587,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G2280" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H2280" t="s">
         <v>9</v>
@@ -61613,7 +61613,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G2281" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="H2281" t="s">
         <v>9</v>
@@ -61639,7 +61639,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G2282" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H2282" t="s">
         <v>9</v>
@@ -61665,7 +61665,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G2283" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H2283" t="s">
         <v>9</v>
@@ -61691,7 +61691,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G2284" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="H2284" t="s">
         <v>9</v>
@@ -61717,7 +61717,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G2285" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H2285" t="s">
         <v>9</v>
@@ -61743,7 +61743,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G2286" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="H2286" t="s">
         <v>9</v>
@@ -61769,7 +61769,7 @@
         <v>3.25</v>
       </c>
       <c r="G2287" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="H2287" t="s">
         <v>9</v>
@@ -61795,7 +61795,7 @@
         <v>3.25</v>
       </c>
       <c r="G2288" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="H2288" t="s">
         <v>9</v>
@@ -61821,7 +61821,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G2289" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="H2289" t="s">
         <v>9</v>
@@ -61847,7 +61847,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G2290" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="H2290" t="s">
         <v>9</v>
@@ -61873,7 +61873,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G2291" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="H2291" t="s">
         <v>9</v>
@@ -61899,7 +61899,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G2292" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H2292" t="s">
         <v>9</v>
@@ -61925,7 +61925,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G2293" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H2293" t="s">
         <v>9</v>
@@ -61951,7 +61951,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G2294" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="H2294" t="s">
         <v>9</v>
@@ -61977,7 +61977,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G2295" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="H2295" t="s">
         <v>9</v>
@@ -62003,7 +62003,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G2296" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="H2296" t="s">
         <v>9</v>
@@ -62029,7 +62029,7 @@
         <v>3.25</v>
       </c>
       <c r="G2297" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="H2297" t="s">
         <v>9</v>
@@ -62055,7 +62055,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G2298" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="H2298" t="s">
         <v>9</v>
@@ -62081,7 +62081,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G2299" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="H2299" t="s">
         <v>9</v>
@@ -62107,7 +62107,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2300" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H2300" t="s">
         <v>9</v>
@@ -62133,7 +62133,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G2301" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="H2301" t="s">
         <v>9</v>
@@ -62159,7 +62159,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G2302" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="H2302" t="s">
         <v>9</v>
@@ -62185,7 +62185,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G2303" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="H2303" t="s">
         <v>9</v>
@@ -62211,7 +62211,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G2304" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="H2304" t="s">
         <v>9</v>
@@ -62237,7 +62237,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G2305" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="H2305" t="s">
         <v>9</v>
@@ -62263,7 +62263,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G2306" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="H2306" t="s">
         <v>9</v>
@@ -62289,7 +62289,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G2307" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="H2307" t="s">
         <v>9</v>
@@ -62315,7 +62315,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G2308" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="H2308" t="s">
         <v>9</v>
@@ -62341,7 +62341,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G2309" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="H2309" t="s">
         <v>9</v>
@@ -62367,7 +62367,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G2310" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="H2310" t="s">
         <v>9</v>
@@ -62393,7 +62393,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2311" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H2311" t="s">
         <v>9</v>
@@ -62419,7 +62419,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2312" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H2312" t="s">
         <v>9</v>
@@ -62445,7 +62445,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G2313" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H2313" t="s">
         <v>9</v>
@@ -62471,7 +62471,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G2314" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="H2314" t="s">
         <v>9</v>
@@ -62497,7 +62497,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G2315" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="H2315" t="s">
         <v>9</v>
@@ -62523,7 +62523,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G2316" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H2316" t="s">
         <v>9</v>
@@ -62549,7 +62549,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G2317" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="H2317" t="s">
         <v>9</v>
@@ -62575,7 +62575,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G2318" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="H2318" t="s">
         <v>9</v>
@@ -62601,7 +62601,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G2319" t="s">
-        <v>539</v>
+        <v>595</v>
       </c>
       <c r="H2319" t="s">
         <v>9</v>
@@ -62627,7 +62627,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G2320" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="H2320" t="s">
         <v>9</v>
@@ -62653,7 +62653,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G2321" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="H2321" t="s">
         <v>9</v>
@@ -62679,7 +62679,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G2322" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="H2322" t="s">
         <v>9</v>
@@ -62705,7 +62705,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2323" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H2323" t="s">
         <v>9</v>
@@ -62731,7 +62731,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2324" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H2324" t="s">
         <v>9</v>
@@ -62757,7 +62757,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2325" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H2325" t="s">
         <v>9</v>
@@ -62783,7 +62783,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G2326" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="H2326" t="s">
         <v>9</v>
@@ -62809,7 +62809,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2327" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H2327" t="s">
         <v>9</v>
@@ -62835,7 +62835,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G2328" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="H2328" t="s">
         <v>9</v>
@@ -62861,7 +62861,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G2329" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="H2329" t="s">
         <v>9</v>
@@ -62887,7 +62887,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G2330" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="H2330" t="s">
         <v>9</v>
@@ -62913,7 +62913,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G2331" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H2331" t="s">
         <v>9</v>
@@ -62939,7 +62939,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G2332" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H2332" t="s">
         <v>9</v>
@@ -62965,7 +62965,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G2333" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="H2333" t="s">
         <v>9</v>
@@ -62991,7 +62991,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G2334" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H2334" t="s">
         <v>9</v>
@@ -63017,7 +63017,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G2335" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H2335" t="s">
         <v>9</v>
@@ -63043,7 +63043,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G2336" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H2336" t="s">
         <v>9</v>
@@ -63069,7 +63069,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G2337" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="H2337" t="s">
         <v>9</v>
@@ -63095,7 +63095,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G2338" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="H2338" t="s">
         <v>9</v>
@@ -63121,7 +63121,7 @@
         <v>3.25</v>
       </c>
       <c r="G2339" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="H2339" t="s">
         <v>9</v>
@@ -63147,7 +63147,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G2340" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="H2340" t="s">
         <v>9</v>
@@ -63173,7 +63173,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G2341" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H2341" t="s">
         <v>9</v>
@@ -63199,7 +63199,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G2342" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="H2342" t="s">
         <v>9</v>
@@ -63225,7 +63225,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G2343" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H2343" t="s">
         <v>9</v>
@@ -63251,7 +63251,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G2344" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H2344" t="s">
         <v>9</v>
@@ -63277,7 +63277,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G2345" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="H2345" t="s">
         <v>9</v>
@@ -63303,7 +63303,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G2346" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H2346" t="s">
         <v>9</v>
@@ -63329,7 +63329,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G2347" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="H2347" t="s">
         <v>9</v>
@@ -63355,7 +63355,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G2348" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="H2348" t="s">
         <v>9</v>
@@ -63381,7 +63381,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G2349" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="H2349" t="s">
         <v>9</v>
@@ -63407,7 +63407,7 @@
         <v>3.25</v>
       </c>
       <c r="G2350" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="H2350" t="s">
         <v>9</v>
@@ -63433,7 +63433,7 @@
         <v>3.25</v>
       </c>
       <c r="G2351" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="H2351" t="s">
         <v>9</v>
@@ -63459,7 +63459,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G2352" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="H2352" t="s">
         <v>9</v>
@@ -63485,7 +63485,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G2353" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="H2353" t="s">
         <v>9</v>
@@ -63511,7 +63511,7 @@
         <v>3.25</v>
       </c>
       <c r="G2354" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="H2354" t="s">
         <v>9</v>
@@ -63537,7 +63537,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G2355" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="H2355" t="s">
         <v>9</v>
@@ -63563,7 +63563,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G2356" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="H2356" t="s">
         <v>9</v>
@@ -63589,7 +63589,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G2357" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H2357" t="s">
         <v>9</v>
@@ -63615,7 +63615,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G2358" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H2358" t="s">
         <v>9</v>
@@ -63641,7 +63641,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G2359" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="H2359" t="s">
         <v>9</v>
@@ -63667,7 +63667,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G2360" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="H2360" t="s">
         <v>9</v>
@@ -63693,7 +63693,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G2361" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H2361" t="s">
         <v>9</v>
@@ -63719,7 +63719,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G2362" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="H2362" t="s">
         <v>9</v>
@@ -63745,7 +63745,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2363" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H2363" t="s">
         <v>9</v>
@@ -63771,7 +63771,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2364" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H2364" t="s">
         <v>9</v>
@@ -63797,7 +63797,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G2365" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="H2365" t="s">
         <v>9</v>
@@ -63823,7 +63823,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2366" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H2366" t="s">
         <v>9</v>
@@ -63849,7 +63849,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G2367" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H2367" t="s">
         <v>9</v>
@@ -63875,7 +63875,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G2368" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H2368" t="s">
         <v>9</v>
@@ -63901,7 +63901,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G2369" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="H2369" t="s">
         <v>9</v>
@@ -63927,7 +63927,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G2370" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="H2370" t="s">
         <v>9</v>
@@ -63953,7 +63953,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G2371" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="H2371" t="s">
         <v>9</v>
@@ -63979,7 +63979,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G2372" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="H2372" t="s">
         <v>9</v>
@@ -64005,7 +64005,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G2373" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H2373" t="s">
         <v>9</v>
@@ -64031,7 +64031,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G2374" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="H2374" t="s">
         <v>9</v>
@@ -64057,7 +64057,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G2375" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H2375" t="s">
         <v>9</v>
@@ -64083,7 +64083,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G2376" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="H2376" t="s">
         <v>9</v>
@@ -64109,7 +64109,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G2377" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H2377" t="s">
         <v>9</v>
@@ -64135,7 +64135,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G2378" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="H2378" t="s">
         <v>9</v>
@@ -64161,7 +64161,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G2379" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="H2379" t="s">
         <v>9</v>
@@ -64187,7 +64187,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G2380" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="H2380" t="s">
         <v>9</v>
@@ -64213,7 +64213,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G2381" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H2381" t="s">
         <v>9</v>
@@ -64239,7 +64239,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G2382" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="H2382" t="s">
         <v>9</v>
@@ -64265,7 +64265,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G2383" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="H2383" t="s">
         <v>9</v>
@@ -64499,7 +64499,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G2392" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="H2392" t="s">
         <v>9</v>
@@ -64551,7 +64551,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G2394" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="H2394" t="s">
         <v>9</v>
@@ -68324,6 +68324,32 @@
         <v>654</v>
       </c>
       <c r="H2539" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2540">
+      <c r="A2540" s="1" t="n">
+        <v>46020.6911689815</v>
+      </c>
+      <c r="B2540" t="n">
+        <v>4700</v>
+      </c>
+      <c r="C2540" t="n">
+        <v>3.85999989509583</v>
+      </c>
+      <c r="D2540" t="n">
+        <v>3.74000000953674</v>
+      </c>
+      <c r="E2540" t="n">
+        <v>3.79999995231628</v>
+      </c>
+      <c r="F2540" t="n">
+        <v>3.8199999332428</v>
+      </c>
+      <c r="G2540" t="s">
+        <v>654</v>
+      </c>
+      <c r="H2540" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ENV.MI.xlsx
+++ b/data/ENV.MI.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18965244293213</t>
+    <t xml:space="preserve">2.18965220451355</t>
   </si>
   <si>
     <t xml:space="preserve">ENV.MI</t>
@@ -50,52 +50,52 @@
     <t xml:space="preserve">2.14471244812012</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16175889968872</t>
+    <t xml:space="preserve">2.16175866127014</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03778719902039</t>
+    <t xml:space="preserve">2.03778696060181</t>
   </si>
   <si>
     <t xml:space="preserve">2.08272671699524</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05328321456909</t>
+    <t xml:space="preserve">2.05328345298767</t>
   </si>
   <si>
     <t xml:space="preserve">2.03623747825623</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96805286407471</t>
+    <t xml:space="preserve">1.968052983284</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96030461788177</t>
+    <t xml:space="preserve">1.9603043794632</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89831864833832</t>
+    <t xml:space="preserve">1.89831829071045</t>
   </si>
   <si>
-    <t xml:space="preserve">1.881272315979</t>
+    <t xml:space="preserve">1.88127243518829</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9634040594101</t>
+    <t xml:space="preserve">1.96340370178223</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98354923725128</t>
+    <t xml:space="preserve">1.98354911804199</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01299262046814</t>
+    <t xml:space="preserve">2.01299285888672</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93551027774811</t>
+    <t xml:space="preserve">1.9355103969574</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93705952167511</t>
+    <t xml:space="preserve">1.93705987930298</t>
   </si>
   <si>
     <t xml:space="preserve">1.91381537914276</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91071629524231</t>
+    <t xml:space="preserve">1.91071593761444</t>
   </si>
   <si>
     <t xml:space="preserve">1.86577618122101</t>
@@ -110,31 +110,31 @@
     <t xml:space="preserve">1.93396055698395</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86732602119446</t>
+    <t xml:space="preserve">1.86732566356659</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88902068138123</t>
+    <t xml:space="preserve">1.88902080059052</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98664879798889</t>
+    <t xml:space="preserve">1.98664844036102</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11526942253113</t>
+    <t xml:space="preserve">2.11526894569397</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18500351905823</t>
+    <t xml:space="preserve">2.18500328063965</t>
   </si>
   <si>
     <t xml:space="preserve">2.20824813842773</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16950702667236</t>
+    <t xml:space="preserve">2.16950654983521</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0842764377594</t>
+    <t xml:space="preserve">2.08427619934082</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01454210281372</t>
+    <t xml:space="preserve">2.0145423412323</t>
   </si>
   <si>
     <t xml:space="preserve">2.00524425506592</t>
@@ -143,13 +143,13 @@
     <t xml:space="preserve">2.14626240730286</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22219491004944</t>
+    <t xml:space="preserve">2.22219514846802</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32447195053101</t>
+    <t xml:space="preserve">2.32447171211243</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20050001144409</t>
+    <t xml:space="preserve">2.20050024986267</t>
   </si>
   <si>
     <t xml:space="preserve">2.27178382873535</t>
@@ -158,19 +158,19 @@
     <t xml:space="preserve">2.24698972702026</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32137298583984</t>
+    <t xml:space="preserve">2.32137274742126</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28418111801147</t>
+    <t xml:space="preserve">2.2841808795929</t>
   </si>
   <si>
     <t xml:space="preserve">2.37870931625366</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35546469688416</t>
+    <t xml:space="preserve">2.35546445846558</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4406955242157</t>
+    <t xml:space="preserve">2.44069528579712</t>
   </si>
   <si>
     <t xml:space="preserve">2.4313976764679</t>
@@ -188,22 +188,22 @@
     <t xml:space="preserve">2.3632128238678</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3198230266571</t>
+    <t xml:space="preserve">2.31982278823853</t>
   </si>
   <si>
     <t xml:space="preserve">2.35236549377441</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26868438720703</t>
+    <t xml:space="preserve">2.26868462562561</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32292222976685</t>
+    <t xml:space="preserve">2.32292199134827</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33531904220581</t>
+    <t xml:space="preserve">2.33531951904297</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33996844291687</t>
+    <t xml:space="preserve">2.33996820449829</t>
   </si>
   <si>
     <t xml:space="preserve">2.3105251789093</t>
@@ -218,19 +218,19 @@
     <t xml:space="preserve">2.29037952423096</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27488327026367</t>
+    <t xml:space="preserve">2.27488350868225</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23149275779724</t>
+    <t xml:space="preserve">2.2314932346344</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07497835159302</t>
+    <t xml:space="preserve">2.0749785900116</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00834393501282</t>
+    <t xml:space="preserve">2.00834345817566</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03468775749207</t>
+    <t xml:space="preserve">2.03468751907349</t>
   </si>
   <si>
     <t xml:space="preserve">2.02229022979736</t>
@@ -239,79 +239,79 @@
     <t xml:space="preserve">1.97580099105835</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91980683803558</t>
+    <t xml:space="preserve">1.919806599617</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8821634054184</t>
+    <t xml:space="preserve">1.88216364383698</t>
   </si>
   <si>
     <t xml:space="preserve">2.00136709213257</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96058678627014</t>
+    <t xml:space="preserve">1.96058690547943</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9025536775589</t>
+    <t xml:space="preserve">1.90255355834961</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9213752746582</t>
+    <t xml:space="preserve">1.92137503623962</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9135330915451</t>
+    <t xml:space="preserve">1.91353297233582</t>
   </si>
   <si>
     <t xml:space="preserve">1.89784801006317</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89000606536865</t>
+    <t xml:space="preserve">1.89000570774078</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85079395771027</t>
+    <t xml:space="preserve">1.85079407691956</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8805947303772</t>
+    <t xml:space="preserve">1.88059508800507</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8664790391922</t>
+    <t xml:space="preserve">1.86647880077362</t>
   </si>
   <si>
     <t xml:space="preserve">1.54651093482971</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68610489368439</t>
+    <t xml:space="preserve">1.68610465526581</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70178961753845</t>
+    <t xml:space="preserve">1.70178949832916</t>
   </si>
   <si>
     <t xml:space="preserve">1.70022094249725</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66257750988007</t>
+    <t xml:space="preserve">1.66257762908936</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64532458782196</t>
+    <t xml:space="preserve">1.64532470703125</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62336611747742</t>
+    <t xml:space="preserve">1.62336587905884</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61552369594574</t>
+    <t xml:space="preserve">1.61552357673645</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63120818138123</t>
+    <t xml:space="preserve">1.6312084197998</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58415412902832</t>
+    <t xml:space="preserve">1.58415424823761</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64689314365387</t>
+    <t xml:space="preserve">1.64689290523529</t>
   </si>
   <si>
     <t xml:space="preserve">1.64061915874481</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63905072212219</t>
+    <t xml:space="preserve">1.6390506029129</t>
   </si>
   <si>
     <t xml:space="preserve">1.60768127441406</t>
@@ -320,76 +320,76 @@
     <t xml:space="preserve">1.57631182670593</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59199655056</t>
+    <t xml:space="preserve">1.59199678897858</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75668585300446</t>
+    <t xml:space="preserve">1.75668573379517</t>
   </si>
   <si>
     <t xml:space="preserve">1.84295165538788</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8460887670517</t>
+    <t xml:space="preserve">1.84608864784241</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9292174577713</t>
+    <t xml:space="preserve">1.92921781539917</t>
   </si>
   <si>
     <t xml:space="preserve">1.88530051708221</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90098512172699</t>
+    <t xml:space="preserve">1.90098524093628</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91823852062225</t>
+    <t xml:space="preserve">1.91823840141296</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94960749149323</t>
+    <t xml:space="preserve">1.94960796833038</t>
   </si>
   <si>
     <t xml:space="preserve">1.93078601360321</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84922564029694</t>
+    <t xml:space="preserve">1.84922552108765</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82412981987</t>
+    <t xml:space="preserve">1.82413005828857</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85549914836884</t>
+    <t xml:space="preserve">1.85549974441528</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89627981185913</t>
+    <t xml:space="preserve">1.89627969264984</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93705976009369</t>
+    <t xml:space="preserve">1.93706011772156</t>
   </si>
   <si>
     <t xml:space="preserve">1.8743212223053</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94333386421204</t>
+    <t xml:space="preserve">1.94333374500275</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94490230083466</t>
+    <t xml:space="preserve">1.94490218162537</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96686089038849</t>
+    <t xml:space="preserve">1.9668607711792</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98411428928375</t>
+    <t xml:space="preserve">1.98411393165588</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0625376701355</t>
+    <t xml:space="preserve">2.06253743171692</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05312633514404</t>
+    <t xml:space="preserve">2.0531268119812</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05155825614929</t>
+    <t xml:space="preserve">2.05155801773071</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0233256816864</t>
+    <t xml:space="preserve">2.02332544326782</t>
   </si>
   <si>
     <t xml:space="preserve">2.02959942817688</t>
@@ -401,67 +401,67 @@
     <t xml:space="preserve">2.06096887588501</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09390711784363</t>
+    <t xml:space="preserve">2.09390735626221</t>
   </si>
   <si>
     <t xml:space="preserve">2.08606457710266</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1550772190094</t>
+    <t xml:space="preserve">2.15507698059082</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18801522254944</t>
+    <t xml:space="preserve">2.18801498413086</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19585728645325</t>
+    <t xml:space="preserve">2.19585704803467</t>
   </si>
   <si>
     <t xml:space="preserve">2.2021312713623</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23350048065186</t>
+    <t xml:space="preserve">2.23350071907043</t>
   </si>
   <si>
     <t xml:space="preserve">2.20997357368469</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18017268180847</t>
+    <t xml:space="preserve">2.18017292022705</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16605639457703</t>
+    <t xml:space="preserve">2.16605615615845</t>
   </si>
   <si>
     <t xml:space="preserve">2.1942892074585</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17389869689941</t>
+    <t xml:space="preserve">2.17389893531799</t>
   </si>
   <si>
     <t xml:space="preserve">2.20056295394897</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21938443183899</t>
+    <t xml:space="preserve">2.21938419342041</t>
   </si>
   <si>
     <t xml:space="preserve">2.21781611442566</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1911518573761</t>
+    <t xml:space="preserve">2.19115209579468</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12057089805603</t>
+    <t xml:space="preserve">2.12057113647461</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15350866317749</t>
+    <t xml:space="preserve">2.15350890159607</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11743378639221</t>
+    <t xml:space="preserve">2.11743402481079</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16291952133179</t>
+    <t xml:space="preserve">2.16291928291321</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10802340507507</t>
+    <t xml:space="preserve">2.10802268981934</t>
   </si>
   <si>
     <t xml:space="preserve">2.01548337936401</t>
@@ -470,19 +470,19 @@
     <t xml:space="preserve">2.04528450965881</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9856823682785</t>
+    <t xml:space="preserve">1.98568248748779</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07822227478027</t>
+    <t xml:space="preserve">2.07822179794312</t>
   </si>
   <si>
     <t xml:space="preserve">2.06724286079407</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12998151779175</t>
+    <t xml:space="preserve">2.12998175621033</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1158652305603</t>
+    <t xml:space="preserve">2.11586546897888</t>
   </si>
   <si>
     <t xml:space="preserve">2.05469489097595</t>
@@ -491,13 +491,13 @@
     <t xml:space="preserve">2.11429715156555</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05626392364502</t>
+    <t xml:space="preserve">2.05626344680786</t>
   </si>
   <si>
     <t xml:space="preserve">2.06410598754883</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10488605499268</t>
+    <t xml:space="preserve">2.10488629341125</t>
   </si>
   <si>
     <t xml:space="preserve">2.00920963287354</t>
@@ -512,7 +512,7 @@
     <t xml:space="preserve">2.1644880771637</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18487787246704</t>
+    <t xml:space="preserve">2.18487811088562</t>
   </si>
   <si>
     <t xml:space="preserve">2.26643848419189</t>
@@ -521,31 +521,31 @@
     <t xml:space="preserve">2.27271246910095</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25702786445618</t>
+    <t xml:space="preserve">2.2570276260376</t>
   </si>
   <si>
     <t xml:space="preserve">2.30721879005432</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2303638458252</t>
+    <t xml:space="preserve">2.23036408424377</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37152600288391</t>
+    <t xml:space="preserve">2.37152576446533</t>
   </si>
   <si>
     <t xml:space="preserve">2.35270428657532</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39191603660583</t>
+    <t xml:space="preserve">2.39191627502441</t>
   </si>
   <si>
     <t xml:space="preserve">2.33545112609863</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3134925365448</t>
+    <t xml:space="preserve">2.31349229812622</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37623143196106</t>
+    <t xml:space="preserve">2.37623119354248</t>
   </si>
   <si>
     <t xml:space="preserve">2.32917737960815</t>
@@ -554,13 +554,13 @@
     <t xml:space="preserve">2.24918532371521</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28839731216431</t>
+    <t xml:space="preserve">2.28839707374573</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33701968193054</t>
+    <t xml:space="preserve">2.33701992034912</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34486222267151</t>
+    <t xml:space="preserve">2.34486198425293</t>
   </si>
   <si>
     <t xml:space="preserve">2.34956741333008</t>
@@ -572,16 +572,16 @@
     <t xml:space="preserve">2.30251336097717</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31192398071289</t>
+    <t xml:space="preserve">2.31192421913147</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25075387954712</t>
+    <t xml:space="preserve">2.25075364112854</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27428126335144</t>
+    <t xml:space="preserve">2.27428102493286</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43897008895874</t>
+    <t xml:space="preserve">2.43896985054016</t>
   </si>
   <si>
     <t xml:space="preserve">2.48445582389832</t>
@@ -593,7 +593,7 @@
     <t xml:space="preserve">2.50798273086548</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48602414131165</t>
+    <t xml:space="preserve">2.48602437973022</t>
   </si>
   <si>
     <t xml:space="preserve">2.60993337631226</t>
@@ -602,25 +602,25 @@
     <t xml:space="preserve">2.66639852523804</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66326117515564</t>
+    <t xml:space="preserve">2.66326093673706</t>
   </si>
   <si>
     <t xml:space="preserve">2.6601243019104</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64287114143372</t>
+    <t xml:space="preserve">2.64287137985229</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65855574607849</t>
+    <t xml:space="preserve">2.65855598449707</t>
   </si>
   <si>
     <t xml:space="preserve">2.60209107398987</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55033159255981</t>
+    <t xml:space="preserve">2.55033183097839</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63816595077515</t>
+    <t xml:space="preserve">2.63816571235657</t>
   </si>
   <si>
     <t xml:space="preserve">2.58013248443604</t>
@@ -635,10 +635,10 @@
     <t xml:space="preserve">2.60365962982178</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61934423446655</t>
+    <t xml:space="preserve">2.61934399604797</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57542681694031</t>
+    <t xml:space="preserve">2.57542705535889</t>
   </si>
   <si>
     <t xml:space="preserve">2.57385873794556</t>
@@ -665,37 +665,37 @@
     <t xml:space="preserve">2.62561798095703</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62718605995178</t>
+    <t xml:space="preserve">2.62718677520752</t>
   </si>
   <si>
     <t xml:space="preserve">2.83422470092773</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79030752182007</t>
+    <t xml:space="preserve">2.79030728340149</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77619099617004</t>
+    <t xml:space="preserve">2.77619123458862</t>
   </si>
   <si>
     <t xml:space="preserve">2.78089642524719</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69149374961853</t>
+    <t xml:space="preserve">2.69149398803711</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78246521949768</t>
+    <t xml:space="preserve">2.78246545791626</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81226587295532</t>
+    <t xml:space="preserve">2.8122661113739</t>
   </si>
   <si>
     <t xml:space="preserve">2.82324504852295</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68678855895996</t>
+    <t xml:space="preserve">2.68678832054138</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70090484619141</t>
+    <t xml:space="preserve">2.70090436935425</t>
   </si>
   <si>
     <t xml:space="preserve">2.80657124519348</t>
@@ -704,13 +704,13 @@
     <t xml:space="preserve">2.86433935165405</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81940841674805</t>
+    <t xml:space="preserve">2.81940865516663</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80817627906799</t>
+    <t xml:space="preserve">2.80817604064941</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88038611412048</t>
+    <t xml:space="preserve">2.88038635253906</t>
   </si>
   <si>
     <t xml:space="preserve">2.83385109901428</t>
@@ -719,7 +719,7 @@
     <t xml:space="preserve">2.74398922920227</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72794246673584</t>
+    <t xml:space="preserve">2.72794270515442</t>
   </si>
   <si>
     <t xml:space="preserve">2.70547699928284</t>
@@ -728,58 +728,58 @@
     <t xml:space="preserve">2.7327561378479</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67177867889404</t>
+    <t xml:space="preserve">2.67177891731262</t>
   </si>
   <si>
     <t xml:space="preserve">2.62363886833191</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61722016334534</t>
+    <t xml:space="preserve">2.61722040176392</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60438275337219</t>
+    <t xml:space="preserve">2.60438299179077</t>
   </si>
   <si>
     <t xml:space="preserve">2.62524342536926</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64129042625427</t>
+    <t xml:space="preserve">2.64129018783569</t>
   </si>
   <si>
     <t xml:space="preserve">2.6958487033844</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75040793418884</t>
+    <t xml:space="preserve">2.75040769577026</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74719834327698</t>
+    <t xml:space="preserve">2.74719858169556</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71991920471191</t>
+    <t xml:space="preserve">2.71991896629333</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72633790969849</t>
+    <t xml:space="preserve">2.72633767127991</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74238443374634</t>
+    <t xml:space="preserve">2.74238467216492</t>
   </si>
   <si>
     <t xml:space="preserve">2.80015254020691</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78571081161499</t>
+    <t xml:space="preserve">2.78571057319641</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82422280311584</t>
+    <t xml:space="preserve">2.82422256469727</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78731513023376</t>
+    <t xml:space="preserve">2.78731536865234</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79373383522034</t>
+    <t xml:space="preserve">2.79373407363892</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80496644973755</t>
+    <t xml:space="preserve">2.80496668815613</t>
   </si>
   <si>
     <t xml:space="preserve">2.78410601615906</t>
@@ -788,16 +788,16 @@
     <t xml:space="preserve">2.77608251571655</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79533886909485</t>
+    <t xml:space="preserve">2.79533863067627</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82261824607849</t>
+    <t xml:space="preserve">2.82261800765991</t>
   </si>
   <si>
     <t xml:space="preserve">2.7600359916687</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77929210662842</t>
+    <t xml:space="preserve">2.77929162979126</t>
   </si>
   <si>
     <t xml:space="preserve">2.79854774475098</t>
@@ -812,10 +812,10 @@
     <t xml:space="preserve">2.83545541763306</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84026980400085</t>
+    <t xml:space="preserve">2.8402693271637</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83224582672119</t>
+    <t xml:space="preserve">2.83224606513977</t>
   </si>
   <si>
     <t xml:space="preserve">2.8113853931427</t>
@@ -824,28 +824,28 @@
     <t xml:space="preserve">2.81619954109192</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76324534416199</t>
+    <t xml:space="preserve">2.76324510574341</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71189594268799</t>
+    <t xml:space="preserve">2.71189570426941</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72473311424255</t>
+    <t xml:space="preserve">2.7247326374054</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7969434261322</t>
+    <t xml:space="preserve">2.79694318771362</t>
   </si>
   <si>
     <t xml:space="preserve">2.79052472114563</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76805925369263</t>
+    <t xml:space="preserve">2.76805901527405</t>
   </si>
   <si>
     <t xml:space="preserve">2.73115181922913</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70387244224548</t>
+    <t xml:space="preserve">2.7038722038269</t>
   </si>
   <si>
     <t xml:space="preserve">2.81459474563599</t>
@@ -854,19 +854,19 @@
     <t xml:space="preserve">2.82903695106506</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8434784412384</t>
+    <t xml:space="preserve">2.84347867965698</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77768707275391</t>
+    <t xml:space="preserve">2.77768731117249</t>
   </si>
   <si>
     <t xml:space="preserve">2.77126860618591</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88840937614441</t>
+    <t xml:space="preserve">2.88840961456299</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87236309051514</t>
+    <t xml:space="preserve">2.87236285209656</t>
   </si>
   <si>
     <t xml:space="preserve">2.89161920547485</t>
@@ -878,10 +878,10 @@
     <t xml:space="preserve">2.85952544212341</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90927004814148</t>
+    <t xml:space="preserve">2.90927028656006</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99913215637207</t>
+    <t xml:space="preserve">2.99913191795349</t>
   </si>
   <si>
     <t xml:space="preserve">2.96864342689514</t>
@@ -899,22 +899,22 @@
     <t xml:space="preserve">2.87557244300842</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75201272964478</t>
+    <t xml:space="preserve">2.75201225280762</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7616400718689</t>
+    <t xml:space="preserve">2.76164054870605</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78892016410828</t>
+    <t xml:space="preserve">2.7889199256897</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67980217933655</t>
+    <t xml:space="preserve">2.67980194091797</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73596572875977</t>
+    <t xml:space="preserve">2.73596596717834</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82582759857178</t>
+    <t xml:space="preserve">2.8258273601532</t>
   </si>
   <si>
     <t xml:space="preserve">2.8482928276062</t>
@@ -926,10 +926,10 @@
     <t xml:space="preserve">2.73436117172241</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81780409812927</t>
+    <t xml:space="preserve">2.81780433654785</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76485013961792</t>
+    <t xml:space="preserve">2.76484990119934</t>
   </si>
   <si>
     <t xml:space="preserve">2.74077963829041</t>
@@ -938,7 +938,7 @@
     <t xml:space="preserve">2.79212927818298</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6637556552887</t>
+    <t xml:space="preserve">2.66375541687012</t>
   </si>
   <si>
     <t xml:space="preserve">2.60759210586548</t>
@@ -950,34 +950,34 @@
     <t xml:space="preserve">2.56747531890869</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59956836700439</t>
+    <t xml:space="preserve">2.59956884384155</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55945181846619</t>
+    <t xml:space="preserve">2.55945205688477</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50328826904297</t>
+    <t xml:space="preserve">2.50328850746155</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45514822006226</t>
+    <t xml:space="preserve">2.45514845848083</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47921800613403</t>
+    <t xml:space="preserve">2.47921824455261</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47119498252869</t>
+    <t xml:space="preserve">2.47119474411011</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43107795715332</t>
+    <t xml:space="preserve">2.4310781955719</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4631712436676</t>
+    <t xml:space="preserve">2.46317148208618</t>
   </si>
   <si>
     <t xml:space="preserve">2.48724150657654</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49526500701904</t>
+    <t xml:space="preserve">2.49526476860046</t>
   </si>
   <si>
     <t xml:space="preserve">2.5273585319519</t>
@@ -989,22 +989,22 @@
     <t xml:space="preserve">2.65573215484619</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9124801158905</t>
+    <t xml:space="preserve">2.91247963905334</t>
   </si>
   <si>
     <t xml:space="preserve">2.82002472877502</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80358147621155</t>
+    <t xml:space="preserve">2.80358171463013</t>
   </si>
   <si>
     <t xml:space="preserve">2.86935472488403</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84468960762024</t>
+    <t xml:space="preserve">2.84468984603882</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85291147232056</t>
+    <t xml:space="preserve">2.85291171073914</t>
   </si>
   <si>
     <t xml:space="preserve">2.81180334091187</t>
@@ -1022,7 +1022,7 @@
     <t xml:space="preserve">2.64737033843994</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65559220314026</t>
+    <t xml:space="preserve">2.6555917263031</t>
   </si>
   <si>
     <t xml:space="preserve">2.66381359100342</t>
@@ -1034,25 +1034,25 @@
     <t xml:space="preserve">2.6391487121582</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55693221092224</t>
+    <t xml:space="preserve">2.55693197250366</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59804034233093</t>
+    <t xml:space="preserve">2.59804058074951</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5487105846405</t>
+    <t xml:space="preserve">2.54871034622192</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46649384498596</t>
+    <t xml:space="preserve">2.46649408340454</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60626196861267</t>
+    <t xml:space="preserve">2.60626220703125</t>
   </si>
   <si>
     <t xml:space="preserve">2.52404546737671</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58159732818604</t>
+    <t xml:space="preserve">2.58159708976746</t>
   </si>
   <si>
     <t xml:space="preserve">2.61448383331299</t>
@@ -1061,19 +1061,19 @@
     <t xml:space="preserve">2.58981871604919</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62270522117615</t>
+    <t xml:space="preserve">2.62270545959473</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51582384109497</t>
+    <t xml:space="preserve">2.51582407951355</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57337546348572</t>
+    <t xml:space="preserve">2.5733757019043</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5651535987854</t>
+    <t xml:space="preserve">2.56515383720398</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53226733207703</t>
+    <t xml:space="preserve">2.53226709365845</t>
   </si>
   <si>
     <t xml:space="preserve">2.47471570968628</t>
@@ -1088,25 +1088,25 @@
     <t xml:space="preserve">2.44182920455933</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42538619041443</t>
+    <t xml:space="preserve">2.42538595199585</t>
   </si>
   <si>
     <t xml:space="preserve">2.43360757827759</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49115872383118</t>
+    <t xml:space="preserve">2.49115896224976</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50760197639465</t>
+    <t xml:space="preserve">2.50760245323181</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54048871994019</t>
+    <t xml:space="preserve">2.54048895835876</t>
   </si>
   <si>
     <t xml:space="preserve">2.67203521728516</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68847870826721</t>
+    <t xml:space="preserve">2.68847846984863</t>
   </si>
   <si>
     <t xml:space="preserve">2.70492172241211</t>
@@ -1121,25 +1121,25 @@
     <t xml:space="preserve">2.78713846206665</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77069473266602</t>
+    <t xml:space="preserve">2.77069497108459</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7295868396759</t>
+    <t xml:space="preserve">2.72958660125732</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74603009223938</t>
+    <t xml:space="preserve">2.7460298538208</t>
   </si>
   <si>
     <t xml:space="preserve">2.77891683578491</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79535984992981</t>
+    <t xml:space="preserve">2.79536008834839</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87757658958435</t>
+    <t xml:space="preserve">2.87757635116577</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91868448257446</t>
+    <t xml:space="preserve">2.91868472099304</t>
   </si>
   <si>
     <t xml:space="preserve">2.89401960372925</t>
@@ -1166,10 +1166,13 @@
     <t xml:space="preserve">2.92690634727478</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77809453010559</t>
+    <t xml:space="preserve">2.80358147621155</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82057285308838</t>
+    <t xml:space="preserve">2.77809429168701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8205726146698</t>
   </si>
   <si>
     <t xml:space="preserve">2.8290684223175</t>
@@ -1178,19 +1181,19 @@
     <t xml:space="preserve">2.88853859901428</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88004302978516</t>
+    <t xml:space="preserve">2.88004279136658</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92252135276794</t>
+    <t xml:space="preserve">2.92252111434937</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90553021430969</t>
+    <t xml:space="preserve">2.90552997589111</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87154722213745</t>
+    <t xml:space="preserve">2.87154746055603</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85455560684204</t>
+    <t xml:space="preserve">2.85455584526062</t>
   </si>
   <si>
     <t xml:space="preserve">2.91402554512024</t>
@@ -1199,7 +1202,7 @@
     <t xml:space="preserve">2.93101692199707</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9480082988739</t>
+    <t xml:space="preserve">2.94800853729248</t>
   </si>
   <si>
     <t xml:space="preserve">2.89703416824341</t>
@@ -1211,22 +1214,22 @@
     <t xml:space="preserve">2.98199129104614</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79508566856384</t>
+    <t xml:space="preserve">2.79508590698242</t>
   </si>
   <si>
     <t xml:space="preserve">2.78659009933472</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76110291481018</t>
+    <t xml:space="preserve">2.76110315322876</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76959872245789</t>
+    <t xml:space="preserve">2.76959896087646</t>
   </si>
   <si>
     <t xml:space="preserve">2.81207704544067</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83756422996521</t>
+    <t xml:space="preserve">2.83756399154663</t>
   </si>
   <si>
     <t xml:space="preserve">2.86305141448975</t>
@@ -1241,13 +1244,10 @@
     <t xml:space="preserve">2.61667609214783</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55720615386963</t>
+    <t xml:space="preserve">2.55720639228821</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54871034622192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51472759246826</t>
+    <t xml:space="preserve">2.51472783088684</t>
   </si>
   <si>
     <t xml:space="preserve">2.49773645401001</t>
@@ -1259,22 +1259,22 @@
     <t xml:space="preserve">2.53171920776367</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46375346183777</t>
+    <t xml:space="preserve">2.46375370025635</t>
   </si>
   <si>
     <t xml:space="preserve">2.58269309997559</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5402147769928</t>
+    <t xml:space="preserve">2.54021453857422</t>
   </si>
   <si>
     <t xml:space="preserve">2.56570196151733</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59118866920471</t>
+    <t xml:space="preserve">2.59118914604187</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47224903106689</t>
+    <t xml:space="preserve">2.47224926948547</t>
   </si>
   <si>
     <t xml:space="preserve">2.63366746902466</t>
@@ -1283,7 +1283,7 @@
     <t xml:space="preserve">2.599684715271</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52322363853455</t>
+    <t xml:space="preserve">2.52322340011597</t>
   </si>
   <si>
     <t xml:space="preserve">2.57419753074646</t>
@@ -1292,7 +1292,7 @@
     <t xml:space="preserve">3.075443983078</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00747847557068</t>
+    <t xml:space="preserve">3.0074782371521</t>
   </si>
   <si>
     <t xml:space="preserve">2.99048686027527</t>
@@ -1322,7 +1322,7 @@
     <t xml:space="preserve">2.31083083152771</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3533091545105</t>
+    <t xml:space="preserve">2.35330939292908</t>
   </si>
   <si>
     <t xml:space="preserve">2.34481358528137</t>
@@ -1334,22 +1334,22 @@
     <t xml:space="preserve">2.4892406463623</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65065860748291</t>
+    <t xml:space="preserve">2.65065884590149</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64216327667236</t>
+    <t xml:space="preserve">2.64216279983521</t>
   </si>
   <si>
     <t xml:space="preserve">2.71012878417969</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69313716888428</t>
+    <t xml:space="preserve">2.69313764572144</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71862459182739</t>
+    <t xml:space="preserve">2.71862435340881</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74411177635193</t>
+    <t xml:space="preserve">2.74411153793335</t>
   </si>
   <si>
     <t xml:space="preserve">2.68464183807373</t>
@@ -1358,34 +1358,34 @@
     <t xml:space="preserve">2.60818028450012</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50623202323914</t>
+    <t xml:space="preserve">2.50623178482056</t>
   </si>
   <si>
     <t xml:space="preserve">2.44676208496094</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37879633903503</t>
+    <t xml:space="preserve">2.37879657745361</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42977046966553</t>
+    <t xml:space="preserve">2.42977070808411</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37030053138733</t>
+    <t xml:space="preserve">2.37030076980591</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31932663917542</t>
+    <t xml:space="preserve">2.31932640075684</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27684807777405</t>
+    <t xml:space="preserve">2.27684831619263</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26835227012634</t>
+    <t xml:space="preserve">2.26835250854492</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30233526229858</t>
+    <t xml:space="preserve">2.30233502388</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33631801605225</t>
+    <t xml:space="preserve">2.33631777763367</t>
   </si>
   <si>
     <t xml:space="preserve">2.39578795433044</t>
@@ -1397,10 +1397,10 @@
     <t xml:space="preserve">2.99898242950439</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03296518325806</t>
+    <t xml:space="preserve">3.03296542167664</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0159740447998</t>
+    <t xml:space="preserve">3.01597380638123</t>
   </si>
   <si>
     <t xml:space="preserve">3.04146122932434</t>
@@ -1409,7 +1409,7 @@
     <t xml:space="preserve">3.1943838596344</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12641835212708</t>
+    <t xml:space="preserve">3.1264181137085</t>
   </si>
   <si>
     <t xml:space="preserve">3.05845236778259</t>
@@ -1427,7 +1427,7 @@
     <t xml:space="preserve">3.3133237361908</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26234936714172</t>
+    <t xml:space="preserve">3.26234912872314</t>
   </si>
   <si>
     <t xml:space="preserve">3.33031511306763</t>
@@ -1436,7 +1436,7 @@
     <t xml:space="preserve">3.22836661338806</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17739248275757</t>
+    <t xml:space="preserve">3.17739224433899</t>
   </si>
   <si>
     <t xml:space="preserve">3.14340972900391</t>
@@ -1445,13 +1445,13 @@
     <t xml:space="preserve">3.10942697525024</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27934050559998</t>
+    <t xml:space="preserve">3.27934074401855</t>
   </si>
   <si>
-    <t xml:space="preserve">3.48323726654053</t>
+    <t xml:space="preserve">3.48323750495911</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39828062057495</t>
+    <t xml:space="preserve">3.39828038215637</t>
   </si>
   <si>
     <t xml:space="preserve">3.46624612808228</t>
@@ -1460,7 +1460,7 @@
     <t xml:space="preserve">3.36429786682129</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34730672836304</t>
+    <t xml:space="preserve">3.34730648994446</t>
   </si>
   <si>
     <t xml:space="preserve">3.24535799026489</t>
@@ -1487,10 +1487,10 @@
     <t xml:space="preserve">3.02393102645874</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1028163433075</t>
+    <t xml:space="preserve">3.10281610488892</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13787603378296</t>
+    <t xml:space="preserve">3.13787627220154</t>
   </si>
   <si>
     <t xml:space="preserve">2.98010611534119</t>
@@ -1499,10 +1499,10 @@
     <t xml:space="preserve">3.09405112266541</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07652115821838</t>
+    <t xml:space="preserve">3.07652139663696</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06775641441345</t>
+    <t xml:space="preserve">3.06775617599487</t>
   </si>
   <si>
     <t xml:space="preserve">3.00640106201172</t>
@@ -1511,7 +1511,7 @@
     <t xml:space="preserve">2.9888710975647</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89245557785034</t>
+    <t xml:space="preserve">2.89245581626892</t>
   </si>
   <si>
     <t xml:space="preserve">2.92751574516296</t>
@@ -1526,7 +1526,7 @@
     <t xml:space="preserve">2.86616063117981</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91875100135803</t>
+    <t xml:space="preserve">2.91875076293945</t>
   </si>
   <si>
     <t xml:space="preserve">2.80480575561523</t>
@@ -1541,34 +1541,34 @@
     <t xml:space="preserve">2.95381093025208</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83110070228577</t>
+    <t xml:space="preserve">2.83110046386719</t>
   </si>
   <si>
     <t xml:space="preserve">2.93628096580505</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03269600868225</t>
+    <t xml:space="preserve">3.03269624710083</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90122103691101</t>
+    <t xml:space="preserve">2.90122079849243</t>
   </si>
   <si>
     <t xml:space="preserve">2.88369083404541</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87492561340332</t>
+    <t xml:space="preserve">2.8749258518219</t>
   </si>
   <si>
     <t xml:space="preserve">2.81357073783875</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83986592292786</t>
+    <t xml:space="preserve">2.83986568450928</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68209528923035</t>
+    <t xml:space="preserve">2.68209552764893</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69086050987244</t>
+    <t xml:space="preserve">2.69086027145386</t>
   </si>
   <si>
     <t xml:space="preserve">2.66456532478333</t>
@@ -1586,13 +1586,13 @@
     <t xml:space="preserve">2.76974582672119</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79604077339172</t>
+    <t xml:space="preserve">2.79604053497314</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84863066673279</t>
+    <t xml:space="preserve">2.84863090515137</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08528637886047</t>
+    <t xml:space="preserve">3.08528614044189</t>
   </si>
   <si>
     <t xml:space="preserve">2.76098036766052</t>
@@ -24641,7 +24641,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G859" t="s">
-        <v>327</v>
+        <v>384</v>
       </c>
       <c r="H859" t="s">
         <v>9</v>
@@ -24667,7 +24667,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G860" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="H860" t="s">
         <v>9</v>
@@ -24693,7 +24693,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G861" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="H861" t="s">
         <v>9</v>
@@ -24719,7 +24719,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G862" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="H862" t="s">
         <v>9</v>
@@ -24745,7 +24745,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G863" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="H863" t="s">
         <v>9</v>
@@ -24771,7 +24771,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G864" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="H864" t="s">
         <v>9</v>
@@ -24797,7 +24797,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G865" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="H865" t="s">
         <v>9</v>
@@ -24823,7 +24823,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G866" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H866" t="s">
         <v>9</v>
@@ -24849,7 +24849,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G867" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H867" t="s">
         <v>9</v>
@@ -24875,7 +24875,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G868" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H868" t="s">
         <v>9</v>
@@ -24901,7 +24901,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G869" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H869" t="s">
         <v>9</v>
@@ -24927,7 +24927,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G870" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H870" t="s">
         <v>9</v>
@@ -24953,7 +24953,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G871" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H871" t="s">
         <v>9</v>
@@ -24979,7 +24979,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G872" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="H872" t="s">
         <v>9</v>
@@ -25005,7 +25005,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G873" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="H873" t="s">
         <v>9</v>
@@ -25031,7 +25031,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G874" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="H874" t="s">
         <v>9</v>
@@ -25057,7 +25057,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G875" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H875" t="s">
         <v>9</v>
@@ -25083,7 +25083,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G876" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="H876" t="s">
         <v>9</v>
@@ -25109,7 +25109,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G877" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="H877" t="s">
         <v>9</v>
@@ -25135,7 +25135,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G878" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="H878" t="s">
         <v>9</v>
@@ -25161,7 +25161,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G879" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="H879" t="s">
         <v>9</v>
@@ -25187,7 +25187,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G880" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="H880" t="s">
         <v>9</v>
@@ -25213,7 +25213,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G881" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="H881" t="s">
         <v>9</v>
@@ -25239,7 +25239,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G882" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="H882" t="s">
         <v>9</v>
@@ -25265,7 +25265,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G883" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="H883" t="s">
         <v>9</v>
@@ -25291,7 +25291,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G884" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="H884" t="s">
         <v>9</v>
@@ -25317,7 +25317,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G885" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="H885" t="s">
         <v>9</v>
@@ -25343,7 +25343,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G886" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="H886" t="s">
         <v>9</v>
@@ -25369,7 +25369,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G887" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="H887" t="s">
         <v>9</v>
@@ -25395,7 +25395,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G888" t="s">
-        <v>327</v>
+        <v>384</v>
       </c>
       <c r="H888" t="s">
         <v>9</v>
@@ -25421,7 +25421,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G889" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="H889" t="s">
         <v>9</v>
@@ -25447,7 +25447,7 @@
         <v>3.25</v>
       </c>
       <c r="G890" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="H890" t="s">
         <v>9</v>
@@ -25473,7 +25473,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G891" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="H891" t="s">
         <v>9</v>
@@ -25499,7 +25499,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G892" t="s">
-        <v>327</v>
+        <v>384</v>
       </c>
       <c r="H892" t="s">
         <v>9</v>
@@ -25525,7 +25525,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G893" t="s">
-        <v>327</v>
+        <v>384</v>
       </c>
       <c r="H893" t="s">
         <v>9</v>
@@ -25551,7 +25551,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G894" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="H894" t="s">
         <v>9</v>
@@ -25577,7 +25577,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G895" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H895" t="s">
         <v>9</v>
@@ -25603,7 +25603,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G896" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="H896" t="s">
         <v>9</v>
@@ -25629,7 +25629,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G897" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="H897" t="s">
         <v>9</v>
@@ -25655,7 +25655,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G898" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="H898" t="s">
         <v>9</v>
@@ -25681,7 +25681,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G899" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="H899" t="s">
         <v>9</v>
@@ -25707,7 +25707,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G900" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="H900" t="s">
         <v>9</v>
@@ -25733,7 +25733,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G901" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="H901" t="s">
         <v>9</v>
@@ -25759,7 +25759,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G902" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="H902" t="s">
         <v>9</v>
@@ -25785,7 +25785,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G903" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="H903" t="s">
         <v>9</v>
@@ -25811,7 +25811,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G904" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="H904" t="s">
         <v>9</v>
@@ -25837,7 +25837,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G905" t="s">
-        <v>327</v>
+        <v>384</v>
       </c>
       <c r="H905" t="s">
         <v>9</v>
@@ -25863,7 +25863,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G906" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="H906" t="s">
         <v>9</v>
@@ -25889,7 +25889,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G907" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="H907" t="s">
         <v>9</v>
@@ -25915,7 +25915,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G908" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="H908" t="s">
         <v>9</v>
@@ -25941,7 +25941,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G909" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="H909" t="s">
         <v>9</v>
@@ -25967,7 +25967,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G910" t="s">
-        <v>327</v>
+        <v>384</v>
       </c>
       <c r="H910" t="s">
         <v>9</v>
@@ -25993,7 +25993,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G911" t="s">
-        <v>327</v>
+        <v>384</v>
       </c>
       <c r="H911" t="s">
         <v>9</v>
@@ -26019,7 +26019,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G912" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="H912" t="s">
         <v>9</v>
@@ -26045,7 +26045,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G913" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="H913" t="s">
         <v>9</v>
@@ -26071,7 +26071,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G914" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="H914" t="s">
         <v>9</v>
@@ -26097,7 +26097,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G915" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="H915" t="s">
         <v>9</v>
@@ -26123,7 +26123,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G916" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="H916" t="s">
         <v>9</v>
@@ -26149,7 +26149,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G917" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="H917" t="s">
         <v>9</v>
@@ -26175,7 +26175,7 @@
         <v>3</v>
       </c>
       <c r="G918" t="s">
-        <v>410</v>
+        <v>342</v>
       </c>
       <c r="H918" t="s">
         <v>9</v>
@@ -26305,7 +26305,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G923" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="H923" t="s">
         <v>9</v>
@@ -26331,7 +26331,7 @@
         <v>3</v>
       </c>
       <c r="G924" t="s">
-        <v>410</v>
+        <v>342</v>
       </c>
       <c r="H924" t="s">
         <v>9</v>
@@ -26383,7 +26383,7 @@
         <v>3</v>
       </c>
       <c r="G926" t="s">
-        <v>410</v>
+        <v>342</v>
       </c>
       <c r="H926" t="s">
         <v>9</v>
@@ -26409,7 +26409,7 @@
         <v>3</v>
       </c>
       <c r="G927" t="s">
-        <v>410</v>
+        <v>342</v>
       </c>
       <c r="H927" t="s">
         <v>9</v>
@@ -26643,7 +26643,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G936" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="H936" t="s">
         <v>9</v>
@@ -26669,7 +26669,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G937" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="H937" t="s">
         <v>9</v>
@@ -27371,7 +27371,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G964" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="H964" t="s">
         <v>9</v>
@@ -27397,7 +27397,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G965" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="H965" t="s">
         <v>9</v>
@@ -27423,7 +27423,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G966" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="H966" t="s">
         <v>9</v>
@@ -27449,7 +27449,7 @@
         <v>3</v>
       </c>
       <c r="G967" t="s">
-        <v>410</v>
+        <v>342</v>
       </c>
       <c r="H967" t="s">
         <v>9</v>
@@ -27605,7 +27605,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G973" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="H973" t="s">
         <v>9</v>
@@ -27631,7 +27631,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G974" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="H974" t="s">
         <v>9</v>
@@ -27657,7 +27657,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G975" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="H975" t="s">
         <v>9</v>
@@ -27683,7 +27683,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G976" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="H976" t="s">
         <v>9</v>
@@ -27839,7 +27839,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G982" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="H982" t="s">
         <v>9</v>
@@ -27865,7 +27865,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G983" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H983" t="s">
         <v>9</v>
@@ -27917,7 +27917,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G985" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="H985" t="s">
         <v>9</v>
@@ -27969,7 +27969,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G987" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H987" t="s">
         <v>9</v>
@@ -28021,7 +28021,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G989" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H989" t="s">
         <v>9</v>
@@ -28047,7 +28047,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G990" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="H990" t="s">
         <v>9</v>
@@ -28073,7 +28073,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G991" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="H991" t="s">
         <v>9</v>
@@ -28099,7 +28099,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G992" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="H992" t="s">
         <v>9</v>
@@ -28125,7 +28125,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G993" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H993" t="s">
         <v>9</v>
@@ -28151,7 +28151,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G994" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H994" t="s">
         <v>9</v>
@@ -28177,7 +28177,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G995" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H995" t="s">
         <v>9</v>
@@ -28203,7 +28203,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G996" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="H996" t="s">
         <v>9</v>
@@ -28229,7 +28229,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G997" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H997" t="s">
         <v>9</v>
@@ -28255,7 +28255,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G998" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="H998" t="s">
         <v>9</v>
@@ -28281,7 +28281,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G999" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="H999" t="s">
         <v>9</v>
@@ -28307,7 +28307,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1000" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="H1000" t="s">
         <v>9</v>
@@ -28333,7 +28333,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G1001" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H1001" t="s">
         <v>9</v>
@@ -28359,7 +28359,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G1002" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H1002" t="s">
         <v>9</v>
@@ -28385,7 +28385,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1003" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H1003" t="s">
         <v>9</v>
@@ -28411,7 +28411,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1004" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="H1004" t="s">
         <v>9</v>
@@ -28437,7 +28437,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G1005" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H1005" t="s">
         <v>9</v>
@@ -28463,7 +28463,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G1006" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H1006" t="s">
         <v>9</v>
@@ -28489,7 +28489,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1007" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="H1007" t="s">
         <v>9</v>
@@ -28515,7 +28515,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1008" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="H1008" t="s">
         <v>9</v>
@@ -28541,7 +28541,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1009" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="H1009" t="s">
         <v>9</v>
@@ -28567,7 +28567,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G1010" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H1010" t="s">
         <v>9</v>
@@ -28593,7 +28593,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1011" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H1011" t="s">
         <v>9</v>
@@ -28619,7 +28619,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G1012" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H1012" t="s">
         <v>9</v>
@@ -28645,7 +28645,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1013" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="H1013" t="s">
         <v>9</v>
@@ -28671,7 +28671,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G1014" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H1014" t="s">
         <v>9</v>
@@ -28697,7 +28697,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G1015" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="H1015" t="s">
         <v>9</v>
@@ -28723,7 +28723,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1016" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="H1016" t="s">
         <v>9</v>
@@ -28749,7 +28749,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G1017" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H1017" t="s">
         <v>9</v>
@@ -28775,7 +28775,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G1018" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H1018" t="s">
         <v>9</v>
@@ -28801,7 +28801,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1019" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="H1019" t="s">
         <v>9</v>
@@ -28827,7 +28827,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1020" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="H1020" t="s">
         <v>9</v>
@@ -28853,7 +28853,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G1021" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H1021" t="s">
         <v>9</v>
@@ -28879,7 +28879,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1022" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="H1022" t="s">
         <v>9</v>
@@ -28957,7 +28957,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G1025" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H1025" t="s">
         <v>9</v>
@@ -28983,7 +28983,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1026" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H1026" t="s">
         <v>9</v>
@@ -29009,7 +29009,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1027" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H1027" t="s">
         <v>9</v>
@@ -29035,7 +29035,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G1028" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H1028" t="s">
         <v>9</v>
@@ -29061,7 +29061,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G1029" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H1029" t="s">
         <v>9</v>
@@ -29139,7 +29139,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1032" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="H1032" t="s">
         <v>9</v>
@@ -29165,7 +29165,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1033" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H1033" t="s">
         <v>9</v>
@@ -29191,7 +29191,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G1034" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H1034" t="s">
         <v>9</v>
@@ -29217,7 +29217,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G1035" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H1035" t="s">
         <v>9</v>
@@ -29243,7 +29243,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G1036" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="H1036" t="s">
         <v>9</v>
@@ -29269,7 +29269,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1037" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H1037" t="s">
         <v>9</v>
@@ -29295,7 +29295,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G1038" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="H1038" t="s">
         <v>9</v>
@@ -29425,7 +29425,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G1043" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="H1043" t="s">
         <v>9</v>
@@ -29451,7 +29451,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G1044" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="H1044" t="s">
         <v>9</v>
@@ -29477,7 +29477,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G1045" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="H1045" t="s">
         <v>9</v>
@@ -29503,7 +29503,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1046" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="H1046" t="s">
         <v>9</v>
@@ -29529,7 +29529,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G1047" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="H1047" t="s">
         <v>9</v>
@@ -29555,7 +29555,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1048" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H1048" t="s">
         <v>9</v>
@@ -29633,7 +29633,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1051" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H1051" t="s">
         <v>9</v>
@@ -29659,7 +29659,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G1052" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H1052" t="s">
         <v>9</v>
@@ -29685,7 +29685,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G1053" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="H1053" t="s">
         <v>9</v>
@@ -29711,7 +29711,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G1054" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="H1054" t="s">
         <v>9</v>
@@ -29737,7 +29737,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G1055" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="H1055" t="s">
         <v>9</v>
@@ -29763,7 +29763,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G1056" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="H1056" t="s">
         <v>9</v>
@@ -29789,7 +29789,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1057" t="s">
-        <v>327</v>
+        <v>384</v>
       </c>
       <c r="H1057" t="s">
         <v>9</v>
@@ -29815,7 +29815,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G1058" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="H1058" t="s">
         <v>9</v>
@@ -29841,7 +29841,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G1059" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="H1059" t="s">
         <v>9</v>
@@ -30387,7 +30387,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1080" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="H1080" t="s">
         <v>9</v>
@@ -30673,7 +30673,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G1091" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="H1091" t="s">
         <v>9</v>
@@ -30751,7 +30751,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G1094" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="H1094" t="s">
         <v>9</v>
@@ -30829,7 +30829,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G1097" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="H1097" t="s">
         <v>9</v>
@@ -30855,7 +30855,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G1098" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="H1098" t="s">
         <v>9</v>
@@ -30881,7 +30881,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G1099" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="H1099" t="s">
         <v>9</v>
@@ -30907,7 +30907,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G1100" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="H1100" t="s">
         <v>9</v>
@@ -30933,7 +30933,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1101" t="s">
-        <v>327</v>
+        <v>384</v>
       </c>
       <c r="H1101" t="s">
         <v>9</v>
@@ -31245,7 +31245,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G1113" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="H1113" t="s">
         <v>9</v>
@@ -31609,7 +31609,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1127" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="H1127" t="s">
         <v>9</v>
@@ -31661,7 +31661,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G1129" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="H1129" t="s">
         <v>9</v>
@@ -31687,7 +31687,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1130" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="H1130" t="s">
         <v>9</v>
@@ -31869,7 +31869,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G1137" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="H1137" t="s">
         <v>9</v>
@@ -31895,7 +31895,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G1138" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="H1138" t="s">
         <v>9</v>
@@ -32389,7 +32389,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G1157" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="H1157" t="s">
         <v>9</v>
@@ -32415,7 +32415,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G1158" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="H1158" t="s">
         <v>9</v>
@@ -32441,7 +32441,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G1159" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="H1159" t="s">
         <v>9</v>
@@ -32935,7 +32935,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1178" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="H1178" t="s">
         <v>9</v>
@@ -32961,7 +32961,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1179" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="H1179" t="s">
         <v>9</v>
@@ -33039,7 +33039,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1182" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="H1182" t="s">
         <v>9</v>
@@ -33065,7 +33065,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1183" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="H1183" t="s">
         <v>9</v>
@@ -33091,7 +33091,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G1184" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="H1184" t="s">
         <v>9</v>
@@ -33117,7 +33117,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G1185" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="H1185" t="s">
         <v>9</v>
@@ -33221,7 +33221,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G1189" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="H1189" t="s">
         <v>9</v>
@@ -33325,7 +33325,7 @@
         <v>3</v>
       </c>
       <c r="G1193" t="s">
-        <v>410</v>
+        <v>342</v>
       </c>
       <c r="H1193" t="s">
         <v>9</v>
@@ -33351,7 +33351,7 @@
         <v>3</v>
       </c>
       <c r="G1194" t="s">
-        <v>410</v>
+        <v>342</v>
       </c>
       <c r="H1194" t="s">
         <v>9</v>
@@ -33377,7 +33377,7 @@
         <v>3</v>
       </c>
       <c r="G1195" t="s">
-        <v>410</v>
+        <v>342</v>
       </c>
       <c r="H1195" t="s">
         <v>9</v>
@@ -33403,7 +33403,7 @@
         <v>3</v>
       </c>
       <c r="G1196" t="s">
-        <v>410</v>
+        <v>342</v>
       </c>
       <c r="H1196" t="s">
         <v>9</v>
@@ -33429,7 +33429,7 @@
         <v>3</v>
       </c>
       <c r="G1197" t="s">
-        <v>410</v>
+        <v>342</v>
       </c>
       <c r="H1197" t="s">
         <v>9</v>
@@ -33455,7 +33455,7 @@
         <v>3</v>
       </c>
       <c r="G1198" t="s">
-        <v>410</v>
+        <v>342</v>
       </c>
       <c r="H1198" t="s">
         <v>9</v>
@@ -33481,7 +33481,7 @@
         <v>3</v>
       </c>
       <c r="G1199" t="s">
-        <v>410</v>
+        <v>342</v>
       </c>
       <c r="H1199" t="s">
         <v>9</v>
@@ -35041,7 +35041,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1259" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="H1259" t="s">
         <v>9</v>
@@ -35171,7 +35171,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G1264" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="H1264" t="s">
         <v>9</v>
@@ -35197,7 +35197,7 @@
         <v>3.25</v>
       </c>
       <c r="G1265" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="H1265" t="s">
         <v>9</v>
@@ -35249,7 +35249,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G1267" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="H1267" t="s">
         <v>9</v>
@@ -35275,7 +35275,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1268" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="H1268" t="s">
         <v>9</v>
@@ -35301,7 +35301,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1269" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="H1269" t="s">
         <v>9</v>
@@ -35327,7 +35327,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1270" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="H1270" t="s">
         <v>9</v>
@@ -35353,7 +35353,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G1271" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="H1271" t="s">
         <v>9</v>
@@ -35379,7 +35379,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G1272" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H1272" t="s">
         <v>9</v>
@@ -35405,7 +35405,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G1273" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="H1273" t="s">
         <v>9</v>
@@ -35431,7 +35431,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G1274" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="H1274" t="s">
         <v>9</v>
@@ -35457,7 +35457,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1275" t="s">
-        <v>327</v>
+        <v>384</v>
       </c>
       <c r="H1275" t="s">
         <v>9</v>
@@ -35483,7 +35483,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G1276" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="H1276" t="s">
         <v>9</v>
@@ -35509,7 +35509,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1277" t="s">
-        <v>327</v>
+        <v>384</v>
       </c>
       <c r="H1277" t="s">
         <v>9</v>
@@ -35535,7 +35535,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G1278" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="H1278" t="s">
         <v>9</v>
@@ -35561,7 +35561,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G1279" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="H1279" t="s">
         <v>9</v>
@@ -35639,7 +35639,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1282" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H1282" t="s">
         <v>9</v>
@@ -35665,7 +35665,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1283" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H1283" t="s">
         <v>9</v>
@@ -35691,7 +35691,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1284" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="H1284" t="s">
         <v>9</v>
@@ -35717,7 +35717,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G1285" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H1285" t="s">
         <v>9</v>
@@ -35743,7 +35743,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G1286" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="H1286" t="s">
         <v>9</v>
@@ -35769,7 +35769,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G1287" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="H1287" t="s">
         <v>9</v>
@@ -35795,7 +35795,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G1288" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="H1288" t="s">
         <v>9</v>
@@ -35847,7 +35847,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G1290" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="H1290" t="s">
         <v>9</v>
@@ -35899,7 +35899,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1292" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="H1292" t="s">
         <v>9</v>
@@ -35925,7 +35925,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G1293" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H1293" t="s">
         <v>9</v>
@@ -35951,7 +35951,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G1294" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="H1294" t="s">
         <v>9</v>
@@ -35977,7 +35977,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1295" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H1295" t="s">
         <v>9</v>
@@ -36003,7 +36003,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G1296" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="H1296" t="s">
         <v>9</v>
@@ -36029,7 +36029,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G1297" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="H1297" t="s">
         <v>9</v>
@@ -36107,7 +36107,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G1300" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="H1300" t="s">
         <v>9</v>
@@ -36159,7 +36159,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G1302" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="H1302" t="s">
         <v>9</v>
@@ -36237,7 +36237,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1305" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="H1305" t="s">
         <v>9</v>
@@ -36263,7 +36263,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1306" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="H1306" t="s">
         <v>9</v>
@@ -36289,7 +36289,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1307" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="H1307" t="s">
         <v>9</v>
@@ -36315,7 +36315,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1308" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="H1308" t="s">
         <v>9</v>
@@ -36393,7 +36393,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G1311" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="H1311" t="s">
         <v>9</v>
@@ -36419,7 +36419,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G1312" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="H1312" t="s">
         <v>9</v>
@@ -36445,7 +36445,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G1313" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H1313" t="s">
         <v>9</v>
@@ -36471,7 +36471,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G1314" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H1314" t="s">
         <v>9</v>
@@ -36549,7 +36549,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G1317" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="H1317" t="s">
         <v>9</v>
@@ -36757,7 +36757,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G1325" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="H1325" t="s">
         <v>9</v>
@@ -36783,7 +36783,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G1326" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="H1326" t="s">
         <v>9</v>
@@ -36809,7 +36809,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G1327" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="H1327" t="s">
         <v>9</v>
@@ -36835,7 +36835,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1328" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="H1328" t="s">
         <v>9</v>
@@ -36887,7 +36887,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1330" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H1330" t="s">
         <v>9</v>
@@ -36939,7 +36939,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1332" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="H1332" t="s">
         <v>9</v>
@@ -36965,7 +36965,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1333" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="H1333" t="s">
         <v>9</v>
@@ -36991,7 +36991,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1334" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H1334" t="s">
         <v>9</v>
@@ -37173,7 +37173,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1341" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H1341" t="s">
         <v>9</v>
@@ -37407,7 +37407,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1350" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="H1350" t="s">
         <v>9</v>
@@ -37433,7 +37433,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1351" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="H1351" t="s">
         <v>9</v>
@@ -37459,7 +37459,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1352" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="H1352" t="s">
         <v>9</v>
@@ -37485,7 +37485,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1353" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="H1353" t="s">
         <v>9</v>
@@ -37693,7 +37693,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1361" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="H1361" t="s">
         <v>9</v>
@@ -37719,7 +37719,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1362" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="H1362" t="s">
         <v>9</v>
@@ -37745,7 +37745,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1363" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="H1363" t="s">
         <v>9</v>
@@ -37771,7 +37771,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1364" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="H1364" t="s">
         <v>9</v>
@@ -37797,7 +37797,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1365" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H1365" t="s">
         <v>9</v>
@@ -37823,7 +37823,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1366" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H1366" t="s">
         <v>9</v>
@@ -37849,7 +37849,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1367" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H1367" t="s">
         <v>9</v>
@@ -37927,7 +37927,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1370" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="H1370" t="s">
         <v>9</v>
@@ -37953,7 +37953,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1371" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H1371" t="s">
         <v>9</v>
@@ -37979,7 +37979,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1372" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="H1372" t="s">
         <v>9</v>
@@ -38005,7 +38005,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1373" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H1373" t="s">
         <v>9</v>
@@ -38083,7 +38083,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1376" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H1376" t="s">
         <v>9</v>
@@ -38135,7 +38135,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1378" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="H1378" t="s">
         <v>9</v>
@@ -38187,7 +38187,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1380" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H1380" t="s">
         <v>9</v>
@@ -38239,7 +38239,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1382" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H1382" t="s">
         <v>9</v>
@@ -38265,7 +38265,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1383" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H1383" t="s">
         <v>9</v>
@@ -38317,7 +38317,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1385" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H1385" t="s">
         <v>9</v>
@@ -38369,7 +38369,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1387" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="H1387" t="s">
         <v>9</v>
@@ -38447,7 +38447,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1390" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H1390" t="s">
         <v>9</v>
@@ -38473,7 +38473,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1391" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H1391" t="s">
         <v>9</v>
@@ -38499,7 +38499,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1392" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H1392" t="s">
         <v>9</v>
@@ -38525,7 +38525,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1393" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H1393" t="s">
         <v>9</v>
@@ -38551,7 +38551,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1394" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H1394" t="s">
         <v>9</v>
@@ -38577,7 +38577,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1395" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="H1395" t="s">
         <v>9</v>
@@ -38603,7 +38603,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1396" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="H1396" t="s">
         <v>9</v>
@@ -38629,7 +38629,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1397" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="H1397" t="s">
         <v>9</v>
@@ -38655,7 +38655,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1398" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="H1398" t="s">
         <v>9</v>
@@ -38681,7 +38681,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1399" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="H1399" t="s">
         <v>9</v>
@@ -38707,7 +38707,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1400" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="H1400" t="s">
         <v>9</v>
@@ -38733,7 +38733,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1401" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="H1401" t="s">
         <v>9</v>
@@ -38759,7 +38759,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1402" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="H1402" t="s">
         <v>9</v>
@@ -38785,7 +38785,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1403" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="H1403" t="s">
         <v>9</v>
@@ -38811,7 +38811,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1404" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="H1404" t="s">
         <v>9</v>
@@ -38837,7 +38837,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1405" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="H1405" t="s">
         <v>9</v>
@@ -38863,7 +38863,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1406" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="H1406" t="s">
         <v>9</v>
@@ -38889,7 +38889,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G1407" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="H1407" t="s">
         <v>9</v>
@@ -38915,7 +38915,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1408" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="H1408" t="s">
         <v>9</v>
@@ -38941,7 +38941,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1409" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="H1409" t="s">
         <v>9</v>
@@ -38967,7 +38967,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1410" t="s">
-        <v>327</v>
+        <v>384</v>
       </c>
       <c r="H1410" t="s">
         <v>9</v>
@@ -38993,7 +38993,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1411" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="H1411" t="s">
         <v>9</v>
@@ -39019,7 +39019,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1412" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="H1412" t="s">
         <v>9</v>
@@ -39045,7 +39045,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1413" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="H1413" t="s">
         <v>9</v>
@@ -39071,7 +39071,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1414" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H1414" t="s">
         <v>9</v>
@@ -39123,7 +39123,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1416" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="H1416" t="s">
         <v>9</v>
@@ -39149,7 +39149,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G1417" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="H1417" t="s">
         <v>9</v>
@@ -39175,7 +39175,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1418" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H1418" t="s">
         <v>9</v>
@@ -39227,7 +39227,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1420" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="H1420" t="s">
         <v>9</v>
@@ -39305,7 +39305,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1423" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H1423" t="s">
         <v>9</v>
@@ -39331,7 +39331,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1424" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="H1424" t="s">
         <v>9</v>
@@ -39539,7 +39539,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1432" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="H1432" t="s">
         <v>9</v>
@@ -39565,7 +39565,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1433" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="H1433" t="s">
         <v>9</v>
@@ -39825,7 +39825,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1443" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H1443" t="s">
         <v>9</v>
@@ -39851,7 +39851,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1444" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H1444" t="s">
         <v>9</v>
@@ -39877,7 +39877,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1445" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H1445" t="s">
         <v>9</v>
@@ -39955,7 +39955,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1448" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="H1448" t="s">
         <v>9</v>
@@ -40059,7 +40059,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1452" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="H1452" t="s">
         <v>9</v>
@@ -40085,7 +40085,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1453" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="H1453" t="s">
         <v>9</v>
@@ -40111,7 +40111,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1454" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H1454" t="s">
         <v>9</v>
@@ -40137,7 +40137,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1455" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H1455" t="s">
         <v>9</v>
@@ -42971,7 +42971,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1564" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H1564" t="s">
         <v>9</v>
@@ -42997,7 +42997,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G1565" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="H1565" t="s">
         <v>9</v>
@@ -43023,7 +43023,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1566" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="H1566" t="s">
         <v>9</v>
@@ -43049,7 +43049,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1567" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="H1567" t="s">
         <v>9</v>
@@ -43075,7 +43075,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1568" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H1568" t="s">
         <v>9</v>
@@ -43101,7 +43101,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1569" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H1569" t="s">
         <v>9</v>
@@ -43127,7 +43127,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1570" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H1570" t="s">
         <v>9</v>
@@ -43153,7 +43153,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1571" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="H1571" t="s">
         <v>9</v>
@@ -43179,7 +43179,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1572" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="H1572" t="s">
         <v>9</v>
@@ -43205,7 +43205,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G1573" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="H1573" t="s">
         <v>9</v>
@@ -43257,7 +43257,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1575" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="H1575" t="s">
         <v>9</v>
@@ -43283,7 +43283,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1576" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="H1576" t="s">
         <v>9</v>
@@ -43309,7 +43309,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1577" t="s">
-        <v>327</v>
+        <v>384</v>
       </c>
       <c r="H1577" t="s">
         <v>9</v>
@@ -43335,7 +43335,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G1578" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="H1578" t="s">
         <v>9</v>
@@ -43387,7 +43387,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1580" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="H1580" t="s">
         <v>9</v>
@@ -44167,7 +44167,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G1610" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="H1610" t="s">
         <v>9</v>
@@ -44219,7 +44219,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G1612" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="H1612" t="s">
         <v>9</v>
@@ -44271,7 +44271,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G1614" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="H1614" t="s">
         <v>9</v>
@@ -44375,7 +44375,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G1618" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="H1618" t="s">
         <v>9</v>
@@ -44401,7 +44401,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G1619" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="H1619" t="s">
         <v>9</v>
@@ -44427,7 +44427,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1620" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="H1620" t="s">
         <v>9</v>
@@ -44453,7 +44453,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G1621" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="H1621" t="s">
         <v>9</v>

--- a/data/ENV.MI.xlsx
+++ b/data/ENV.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="655" uniqueCount="655">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="656" uniqueCount="656">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,130 +38,130 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18965220451355</t>
+    <t xml:space="preserve">2.18965244293213</t>
   </si>
   <si>
     <t xml:space="preserve">ENV.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20979785919189</t>
+    <t xml:space="preserve">2.20979762077332</t>
   </si>
   <si>
     <t xml:space="preserve">2.14471244812012</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16175866127014</t>
+    <t xml:space="preserve">2.16175842285156</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03778696060181</t>
+    <t xml:space="preserve">2.03778719902039</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08272671699524</t>
+    <t xml:space="preserve">2.08272647857666</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05328345298767</t>
+    <t xml:space="preserve">2.05328321456909</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03623747825623</t>
+    <t xml:space="preserve">2.03623723983765</t>
   </si>
   <si>
-    <t xml:space="preserve">1.968052983284</t>
+    <t xml:space="preserve">1.96805274486542</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9603043794632</t>
+    <t xml:space="preserve">1.96030473709106</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89831829071045</t>
+    <t xml:space="preserve">1.8983188867569</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88127243518829</t>
+    <t xml:space="preserve">1.88127255439758</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96340370178223</t>
+    <t xml:space="preserve">1.96340382099152</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98354911804199</t>
+    <t xml:space="preserve">1.98354935646057</t>
   </si>
   <si>
     <t xml:space="preserve">2.01299285888672</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9355103969574</t>
+    <t xml:space="preserve">1.93551015853882</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93705987930298</t>
+    <t xml:space="preserve">1.93705999851227</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91381537914276</t>
+    <t xml:space="preserve">1.91381514072418</t>
   </si>
   <si>
     <t xml:space="preserve">1.91071593761444</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86577618122101</t>
+    <t xml:space="preserve">1.86577606201172</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89212000370026</t>
+    <t xml:space="preserve">1.89212012290955</t>
   </si>
   <si>
     <t xml:space="preserve">1.85182929039001</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93396055698395</t>
+    <t xml:space="preserve">1.93396031856537</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86732566356659</t>
+    <t xml:space="preserve">1.86732578277588</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88902080059052</t>
+    <t xml:space="preserve">1.88902103900909</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98664844036102</t>
+    <t xml:space="preserve">1.98664855957031</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11526894569397</t>
+    <t xml:space="preserve">2.11526942253113</t>
   </si>
   <si>
     <t xml:space="preserve">2.18500328063965</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20824813842773</t>
+    <t xml:space="preserve">2.20824861526489</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16950654983521</t>
+    <t xml:space="preserve">2.16950702667236</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08427619934082</t>
+    <t xml:space="preserve">2.08427667617798</t>
   </si>
   <si>
     <t xml:space="preserve">2.0145423412323</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00524425506592</t>
+    <t xml:space="preserve">2.0052444934845</t>
   </si>
   <si>
     <t xml:space="preserve">2.14626240730286</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22219514846802</t>
+    <t xml:space="preserve">2.2221953868866</t>
   </si>
   <si>
     <t xml:space="preserve">2.32447171211243</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20050024986267</t>
+    <t xml:space="preserve">2.20050001144409</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27178382873535</t>
+    <t xml:space="preserve">2.27178359031677</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24698972702026</t>
+    <t xml:space="preserve">2.24698948860168</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32137274742126</t>
+    <t xml:space="preserve">2.32137227058411</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2841808795929</t>
+    <t xml:space="preserve">2.28418111801147</t>
   </si>
   <si>
     <t xml:space="preserve">2.37870931625366</t>
@@ -173,7 +173,7 @@
     <t xml:space="preserve">2.44069528579712</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4313976764679</t>
+    <t xml:space="preserve">2.43139743804932</t>
   </si>
   <si>
     <t xml:space="preserve">2.4499933719635</t>
@@ -185,13 +185,13 @@
     <t xml:space="preserve">2.3616635799408</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3632128238678</t>
+    <t xml:space="preserve">2.36321330070496</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31982278823853</t>
+    <t xml:space="preserve">2.3198230266571</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35236549377441</t>
+    <t xml:space="preserve">2.35236573219299</t>
   </si>
   <si>
     <t xml:space="preserve">2.26868462562561</t>
@@ -200,10 +200,10 @@
     <t xml:space="preserve">2.32292199134827</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33531951904297</t>
+    <t xml:space="preserve">2.33531975746155</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33996820449829</t>
+    <t xml:space="preserve">2.33996844291687</t>
   </si>
   <si>
     <t xml:space="preserve">2.3105251789093</t>
@@ -212,79 +212,79 @@
     <t xml:space="preserve">2.28573060035706</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25473785400391</t>
+    <t xml:space="preserve">2.25473809242249</t>
   </si>
   <si>
     <t xml:space="preserve">2.29037952423096</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27488350868225</t>
+    <t xml:space="preserve">2.27488279342651</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2314932346344</t>
+    <t xml:space="preserve">2.23149299621582</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0749785900116</t>
+    <t xml:space="preserve">2.07497835159302</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00834345817566</t>
+    <t xml:space="preserve">2.00834369659424</t>
   </si>
   <si>
     <t xml:space="preserve">2.03468751907349</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02229022979736</t>
+    <t xml:space="preserve">2.02229046821594</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97580099105835</t>
+    <t xml:space="preserve">1.97580087184906</t>
   </si>
   <si>
-    <t xml:space="preserve">1.919806599617</t>
+    <t xml:space="preserve">1.91980683803558</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88216364383698</t>
+    <t xml:space="preserve">1.88216328620911</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00136709213257</t>
+    <t xml:space="preserve">2.00136733055115</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96058690547943</t>
+    <t xml:space="preserve">1.96058714389801</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90255355834961</t>
+    <t xml:space="preserve">1.90255379676819</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92137503623962</t>
+    <t xml:space="preserve">1.92137539386749</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91353297233582</t>
+    <t xml:space="preserve">1.91353285312653</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89784801006317</t>
+    <t xml:space="preserve">1.89784812927246</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89000570774078</t>
+    <t xml:space="preserve">1.89000594615936</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85079407691956</t>
+    <t xml:space="preserve">1.85079383850098</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88059508800507</t>
+    <t xml:space="preserve">1.88059496879578</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86647880077362</t>
+    <t xml:space="preserve">1.86647891998291</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54651093482971</t>
+    <t xml:space="preserve">1.546511054039</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68610465526581</t>
+    <t xml:space="preserve">1.68610501289368</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70178949832916</t>
+    <t xml:space="preserve">1.70178961753845</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70022094249725</t>
+    <t xml:space="preserve">1.70022070407867</t>
   </si>
   <si>
     <t xml:space="preserve">1.66257762908936</t>
@@ -293,22 +293,22 @@
     <t xml:space="preserve">1.64532470703125</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62336587905884</t>
+    <t xml:space="preserve">1.62336599826813</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61552357673645</t>
+    <t xml:space="preserve">1.61552345752716</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6312084197998</t>
+    <t xml:space="preserve">1.63120818138123</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58415424823761</t>
+    <t xml:space="preserve">1.58415412902832</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64689290523529</t>
+    <t xml:space="preserve">1.64689302444458</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64061915874481</t>
+    <t xml:space="preserve">1.6406192779541</t>
   </si>
   <si>
     <t xml:space="preserve">1.6390506029129</t>
@@ -317,19 +317,19 @@
     <t xml:space="preserve">1.60768127441406</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57631182670593</t>
+    <t xml:space="preserve">1.57631194591522</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59199678897858</t>
+    <t xml:space="preserve">1.59199666976929</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75668573379517</t>
+    <t xml:space="preserve">1.75668585300446</t>
   </si>
   <si>
     <t xml:space="preserve">1.84295165538788</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84608864784241</t>
+    <t xml:space="preserve">1.84608888626099</t>
   </si>
   <si>
     <t xml:space="preserve">1.92921781539917</t>
@@ -338,49 +338,49 @@
     <t xml:space="preserve">1.88530051708221</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90098524093628</t>
+    <t xml:space="preserve">1.90098512172699</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91823840141296</t>
+    <t xml:space="preserve">1.91823828220367</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94960796833038</t>
+    <t xml:space="preserve">1.9496077299118</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93078601360321</t>
+    <t xml:space="preserve">1.93078577518463</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84922552108765</t>
+    <t xml:space="preserve">1.84922540187836</t>
   </si>
   <si>
     <t xml:space="preserve">1.82413005828857</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85549974441528</t>
+    <t xml:space="preserve">1.85549938678741</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89627969264984</t>
+    <t xml:space="preserve">1.89627981185913</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93706011772156</t>
+    <t xml:space="preserve">1.93705987930298</t>
   </si>
   <si>
     <t xml:space="preserve">1.8743212223053</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94333374500275</t>
+    <t xml:space="preserve">1.94333350658417</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94490218162537</t>
+    <t xml:space="preserve">1.94490194320679</t>
   </si>
   <si>
     <t xml:space="preserve">1.9668607711792</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98411393165588</t>
+    <t xml:space="preserve">1.98411417007446</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06253743171692</t>
+    <t xml:space="preserve">2.0625376701355</t>
   </si>
   <si>
     <t xml:space="preserve">2.0531268119812</t>
@@ -389,10 +389,10 @@
     <t xml:space="preserve">2.05155801773071</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02332544326782</t>
+    <t xml:space="preserve">2.02332592010498</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02959942817688</t>
+    <t xml:space="preserve">2.02959966659546</t>
   </si>
   <si>
     <t xml:space="preserve">2.03116798400879</t>
@@ -401,19 +401,19 @@
     <t xml:space="preserve">2.06096887588501</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09390735626221</t>
+    <t xml:space="preserve">2.09390687942505</t>
   </si>
   <si>
     <t xml:space="preserve">2.08606457710266</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15507698059082</t>
+    <t xml:space="preserve">2.1550772190094</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18801498413086</t>
+    <t xml:space="preserve">2.18801474571228</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19585704803467</t>
+    <t xml:space="preserve">2.19585728645325</t>
   </si>
   <si>
     <t xml:space="preserve">2.2021312713623</t>
@@ -422,16 +422,16 @@
     <t xml:space="preserve">2.23350071907043</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20997357368469</t>
+    <t xml:space="preserve">2.20997381210327</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18017292022705</t>
+    <t xml:space="preserve">2.18017268180847</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16605615615845</t>
+    <t xml:space="preserve">2.16605663299561</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1942892074585</t>
+    <t xml:space="preserve">2.19428896903992</t>
   </si>
   <si>
     <t xml:space="preserve">2.17389893531799</t>
@@ -440,19 +440,19 @@
     <t xml:space="preserve">2.20056295394897</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21938419342041</t>
+    <t xml:space="preserve">2.21938443183899</t>
   </si>
   <si>
     <t xml:space="preserve">2.21781611442566</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19115209579468</t>
+    <t xml:space="preserve">2.1911518573761</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12057113647461</t>
+    <t xml:space="preserve">2.12057089805603</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15350890159607</t>
+    <t xml:space="preserve">2.15350914001465</t>
   </si>
   <si>
     <t xml:space="preserve">2.11743402481079</t>
@@ -467,19 +467,19 @@
     <t xml:space="preserve">2.01548337936401</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04528450965881</t>
+    <t xml:space="preserve">2.04528427124023</t>
   </si>
   <si>
     <t xml:space="preserve">1.98568248748779</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07822179794312</t>
+    <t xml:space="preserve">2.07822203636169</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06724286079407</t>
+    <t xml:space="preserve">2.06724262237549</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12998175621033</t>
+    <t xml:space="preserve">2.12998151779175</t>
   </si>
   <si>
     <t xml:space="preserve">2.11586546897888</t>
@@ -488,7 +488,7 @@
     <t xml:space="preserve">2.05469489097595</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11429715156555</t>
+    <t xml:space="preserve">2.11429691314697</t>
   </si>
   <si>
     <t xml:space="preserve">2.05626344680786</t>
@@ -497,31 +497,31 @@
     <t xml:space="preserve">2.06410598754883</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10488629341125</t>
+    <t xml:space="preserve">2.10488653182983</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00920963287354</t>
+    <t xml:space="preserve">2.00920987129211</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01391506195068</t>
+    <t xml:space="preserve">2.0139148235321</t>
   </si>
   <si>
     <t xml:space="preserve">2.04842114448547</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1644880771637</t>
+    <t xml:space="preserve">2.16448783874512</t>
   </si>
   <si>
     <t xml:space="preserve">2.18487811088562</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26643848419189</t>
+    <t xml:space="preserve">2.26643872261047</t>
   </si>
   <si>
     <t xml:space="preserve">2.27271246910095</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2570276260376</t>
+    <t xml:space="preserve">2.25702786445618</t>
   </si>
   <si>
     <t xml:space="preserve">2.30721879005432</t>
@@ -539,37 +539,37 @@
     <t xml:space="preserve">2.39191627502441</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33545112609863</t>
+    <t xml:space="preserve">2.33545088768005</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31349229812622</t>
+    <t xml:space="preserve">2.3134925365448</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37623119354248</t>
+    <t xml:space="preserve">2.37623143196106</t>
   </si>
   <si>
     <t xml:space="preserve">2.32917737960815</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24918532371521</t>
+    <t xml:space="preserve">2.24918556213379</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28839707374573</t>
+    <t xml:space="preserve">2.28839683532715</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33701992034912</t>
+    <t xml:space="preserve">2.33701968193054</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34486198425293</t>
+    <t xml:space="preserve">2.34486222267151</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34956741333008</t>
+    <t xml:space="preserve">2.3495671749115</t>
   </si>
   <si>
     <t xml:space="preserve">2.32604050636292</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30251336097717</t>
+    <t xml:space="preserve">2.30251312255859</t>
   </si>
   <si>
     <t xml:space="preserve">2.31192421913147</t>
@@ -581,73 +581,73 @@
     <t xml:space="preserve">2.27428102493286</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43896985054016</t>
+    <t xml:space="preserve">2.43897008895874</t>
   </si>
   <si>
     <t xml:space="preserve">2.48445582389832</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46249723434448</t>
+    <t xml:space="preserve">2.46249747276306</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50798273086548</t>
+    <t xml:space="preserve">2.50798296928406</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48602437973022</t>
+    <t xml:space="preserve">2.48602414131165</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60993337631226</t>
+    <t xml:space="preserve">2.60993361473083</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66639852523804</t>
+    <t xml:space="preserve">2.66639828681946</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66326093673706</t>
+    <t xml:space="preserve">2.66326117515564</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6601243019104</t>
+    <t xml:space="preserve">2.66012406349182</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64287137985229</t>
+    <t xml:space="preserve">2.64287090301514</t>
   </si>
   <si>
     <t xml:space="preserve">2.65855598449707</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60209107398987</t>
+    <t xml:space="preserve">2.60209131240845</t>
   </si>
   <si>
     <t xml:space="preserve">2.55033183097839</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63816571235657</t>
+    <t xml:space="preserve">2.63816595077515</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58013248443604</t>
+    <t xml:space="preserve">2.58013224601746</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59581708908081</t>
+    <t xml:space="preserve">2.59581732749939</t>
   </si>
   <si>
     <t xml:space="preserve">2.58170080184937</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60365962982178</t>
+    <t xml:space="preserve">2.6036593914032</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61934399604797</t>
+    <t xml:space="preserve">2.61934423446655</t>
   </si>
   <si>
     <t xml:space="preserve">2.57542705535889</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57385873794556</t>
+    <t xml:space="preserve">2.57385849952698</t>
   </si>
   <si>
     <t xml:space="preserve">2.50955128669739</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58797478675842</t>
+    <t xml:space="preserve">2.587975025177</t>
   </si>
   <si>
     <t xml:space="preserve">2.56444764137268</t>
@@ -662,49 +662,49 @@
     <t xml:space="preserve">2.63502883911133</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62561798095703</t>
+    <t xml:space="preserve">2.62561821937561</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62718677520752</t>
+    <t xml:space="preserve">2.62718653678894</t>
   </si>
   <si>
     <t xml:space="preserve">2.83422470092773</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79030728340149</t>
+    <t xml:space="preserve">2.79030752182007</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77619123458862</t>
+    <t xml:space="preserve">2.77619099617004</t>
   </si>
   <si>
     <t xml:space="preserve">2.78089642524719</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69149398803711</t>
+    <t xml:space="preserve">2.69149374961853</t>
   </si>
   <si>
     <t xml:space="preserve">2.78246545791626</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8122661113739</t>
+    <t xml:space="preserve">2.81226587295532</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82324504852295</t>
+    <t xml:space="preserve">2.82324528694153</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68678832054138</t>
+    <t xml:space="preserve">2.68678879737854</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70090436935425</t>
+    <t xml:space="preserve">2.70090460777283</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80657124519348</t>
+    <t xml:space="preserve">2.8065710067749</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86433935165405</t>
+    <t xml:space="preserve">2.86433959007263</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81940865516663</t>
+    <t xml:space="preserve">2.81940841674805</t>
   </si>
   <si>
     <t xml:space="preserve">2.80817604064941</t>
@@ -713,7 +713,7 @@
     <t xml:space="preserve">2.88038635253906</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83385109901428</t>
+    <t xml:space="preserve">2.83385062217712</t>
   </si>
   <si>
     <t xml:space="preserve">2.74398922920227</t>
@@ -722,13 +722,13 @@
     <t xml:space="preserve">2.72794270515442</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70547699928284</t>
+    <t xml:space="preserve">2.70547676086426</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7327561378479</t>
+    <t xml:space="preserve">2.73275637626648</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67177891731262</t>
+    <t xml:space="preserve">2.67177867889404</t>
   </si>
   <si>
     <t xml:space="preserve">2.62363886833191</t>
@@ -737,16 +737,16 @@
     <t xml:space="preserve">2.61722040176392</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60438299179077</t>
+    <t xml:space="preserve">2.60438275337219</t>
   </si>
   <si>
     <t xml:space="preserve">2.62524342536926</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64129018783569</t>
+    <t xml:space="preserve">2.64128994941711</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6958487033844</t>
+    <t xml:space="preserve">2.69584894180298</t>
   </si>
   <si>
     <t xml:space="preserve">2.75040769577026</t>
@@ -755,37 +755,37 @@
     <t xml:space="preserve">2.74719858169556</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71991896629333</t>
+    <t xml:space="preserve">2.71991920471191</t>
   </si>
   <si>
     <t xml:space="preserve">2.72633767127991</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74238467216492</t>
+    <t xml:space="preserve">2.74238443374634</t>
   </si>
   <si>
     <t xml:space="preserve">2.80015254020691</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78571057319641</t>
+    <t xml:space="preserve">2.78571033477783</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82422256469727</t>
+    <t xml:space="preserve">2.82422280311584</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78731536865234</t>
+    <t xml:space="preserve">2.78731513023376</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79373407363892</t>
+    <t xml:space="preserve">2.79373383522034</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80496668815613</t>
+    <t xml:space="preserve">2.80496692657471</t>
   </si>
   <si>
     <t xml:space="preserve">2.78410601615906</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77608251571655</t>
+    <t xml:space="preserve">2.77608275413513</t>
   </si>
   <si>
     <t xml:space="preserve">2.79533863067627</t>
@@ -797,22 +797,22 @@
     <t xml:space="preserve">2.7600359916687</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77929162979126</t>
+    <t xml:space="preserve">2.77929210662842</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79854774475098</t>
+    <t xml:space="preserve">2.79854798316956</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7744779586792</t>
+    <t xml:space="preserve">2.77447772026062</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80336213111877</t>
+    <t xml:space="preserve">2.8033618927002</t>
   </si>
   <si>
     <t xml:space="preserve">2.83545541763306</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8402693271637</t>
+    <t xml:space="preserve">2.84026956558228</t>
   </si>
   <si>
     <t xml:space="preserve">2.83224606513977</t>
@@ -821,25 +821,25 @@
     <t xml:space="preserve">2.8113853931427</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81619954109192</t>
+    <t xml:space="preserve">2.81619930267334</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76324510574341</t>
+    <t xml:space="preserve">2.76324534416199</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71189570426941</t>
+    <t xml:space="preserve">2.71189594268799</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7247326374054</t>
+    <t xml:space="preserve">2.72473287582397</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79694318771362</t>
+    <t xml:space="preserve">2.79694366455078</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79052472114563</t>
+    <t xml:space="preserve">2.79052448272705</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76805901527405</t>
+    <t xml:space="preserve">2.76805925369263</t>
   </si>
   <si>
     <t xml:space="preserve">2.73115181922913</t>
@@ -854,10 +854,10 @@
     <t xml:space="preserve">2.82903695106506</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84347867965698</t>
+    <t xml:space="preserve">2.84347891807556</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77768731117249</t>
+    <t xml:space="preserve">2.77768707275391</t>
   </si>
   <si>
     <t xml:space="preserve">2.77126860618591</t>
@@ -872,7 +872,7 @@
     <t xml:space="preserve">2.89161920547485</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92852640151978</t>
+    <t xml:space="preserve">2.92852663993835</t>
   </si>
   <si>
     <t xml:space="preserve">2.85952544212341</t>
@@ -881,16 +881,16 @@
     <t xml:space="preserve">2.90927028656006</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99913191795349</t>
+    <t xml:space="preserve">2.99913167953491</t>
   </si>
   <si>
     <t xml:space="preserve">2.96864342689514</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83064150810242</t>
+    <t xml:space="preserve">2.830641746521</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87878155708313</t>
+    <t xml:space="preserve">2.87878179550171</t>
   </si>
   <si>
     <t xml:space="preserve">2.87717700004578</t>
@@ -899,46 +899,46 @@
     <t xml:space="preserve">2.87557244300842</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75201225280762</t>
+    <t xml:space="preserve">2.7520124912262</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76164054870605</t>
+    <t xml:space="preserve">2.76164031028748</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7889199256897</t>
+    <t xml:space="preserve">2.78892016410828</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67980194091797</t>
+    <t xml:space="preserve">2.67980217933655</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73596596717834</t>
+    <t xml:space="preserve">2.73596572875977</t>
   </si>
   <si>
     <t xml:space="preserve">2.8258273601532</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8482928276062</t>
+    <t xml:space="preserve">2.84829306602478</t>
   </si>
   <si>
     <t xml:space="preserve">2.82101345062256</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73436117172241</t>
+    <t xml:space="preserve">2.73436093330383</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81780433654785</t>
+    <t xml:space="preserve">2.81780409812927</t>
   </si>
   <si>
     <t xml:space="preserve">2.76484990119934</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74077963829041</t>
+    <t xml:space="preserve">2.74077987670898</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79212927818298</t>
+    <t xml:space="preserve">2.79212951660156</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66375541687012</t>
+    <t xml:space="preserve">2.6637556552887</t>
   </si>
   <si>
     <t xml:space="preserve">2.60759210586548</t>
@@ -953,22 +953,22 @@
     <t xml:space="preserve">2.59956884384155</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55945205688477</t>
+    <t xml:space="preserve">2.55945181846619</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50328850746155</t>
+    <t xml:space="preserve">2.50328803062439</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45514845848083</t>
+    <t xml:space="preserve">2.45514822006226</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47921824455261</t>
+    <t xml:space="preserve">2.47921800613403</t>
   </si>
   <si>
     <t xml:space="preserve">2.47119474411011</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4310781955719</t>
+    <t xml:space="preserve">2.43107795715332</t>
   </si>
   <si>
     <t xml:space="preserve">2.46317148208618</t>
@@ -989,10 +989,10 @@
     <t xml:space="preserve">2.65573215484619</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91247963905334</t>
+    <t xml:space="preserve">2.9124801158905</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82002472877502</t>
+    <t xml:space="preserve">2.8200249671936</t>
   </si>
   <si>
     <t xml:space="preserve">2.80358171463013</t>
@@ -1013,7 +1013,7 @@
     <t xml:space="preserve">2.72136497497559</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68025708198547</t>
+    <t xml:space="preserve">2.68025684356689</t>
   </si>
   <si>
     <t xml:space="preserve">2.69670009613037</t>
@@ -1022,7 +1022,7 @@
     <t xml:space="preserve">2.64737033843994</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6555917263031</t>
+    <t xml:space="preserve">2.65559196472168</t>
   </si>
   <si>
     <t xml:space="preserve">2.66381359100342</t>
@@ -1031,10 +1031,10 @@
     <t xml:space="preserve">2.63092708587646</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6391487121582</t>
+    <t xml:space="preserve">2.63914847373962</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55693197250366</t>
+    <t xml:space="preserve">2.55693221092224</t>
   </si>
   <si>
     <t xml:space="preserve">2.59804058074951</t>
@@ -1046,10 +1046,10 @@
     <t xml:space="preserve">2.46649408340454</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60626220703125</t>
+    <t xml:space="preserve">2.60626196861267</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52404546737671</t>
+    <t xml:space="preserve">2.52404570579529</t>
   </si>
   <si>
     <t xml:space="preserve">2.58159708976746</t>
@@ -1058,19 +1058,19 @@
     <t xml:space="preserve">2.61448383331299</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58981871604919</t>
+    <t xml:space="preserve">2.58981895446777</t>
   </si>
   <si>
     <t xml:space="preserve">2.62270545959473</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51582407951355</t>
+    <t xml:space="preserve">2.51582384109497</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5733757019043</t>
+    <t xml:space="preserve">2.57337546348572</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56515383720398</t>
+    <t xml:space="preserve">2.5651535987854</t>
   </si>
   <si>
     <t xml:space="preserve">2.53226709365845</t>
@@ -1097,22 +1097,22 @@
     <t xml:space="preserve">2.49115896224976</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50760245323181</t>
+    <t xml:space="preserve">2.50760221481323</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54048895835876</t>
+    <t xml:space="preserve">2.54048871994019</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67203521728516</t>
+    <t xml:space="preserve">2.67203545570374</t>
   </si>
   <si>
     <t xml:space="preserve">2.68847846984863</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70492172241211</t>
+    <t xml:space="preserve">2.70492196083069</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71314358711243</t>
+    <t xml:space="preserve">2.71314334869385</t>
   </si>
   <si>
     <t xml:space="preserve">2.75425171852112</t>
@@ -1133,7 +1133,7 @@
     <t xml:space="preserve">2.77891683578491</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79536008834839</t>
+    <t xml:space="preserve">2.79535984992981</t>
   </si>
   <si>
     <t xml:space="preserve">2.87757635116577</t>
@@ -1145,7 +1145,7 @@
     <t xml:space="preserve">2.89401960372925</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86113309860229</t>
+    <t xml:space="preserve">2.86113286018372</t>
   </si>
   <si>
     <t xml:space="preserve">2.90224123001099</t>
@@ -1154,13 +1154,13 @@
     <t xml:space="preserve">2.88579821586609</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8364679813385</t>
+    <t xml:space="preserve">2.83646821975708</t>
   </si>
   <si>
     <t xml:space="preserve">2.94334959983826</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82824659347534</t>
+    <t xml:space="preserve">2.82824635505676</t>
   </si>
   <si>
     <t xml:space="preserve">2.92690634727478</t>
@@ -1169,10 +1169,10 @@
     <t xml:space="preserve">2.80358147621155</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77809429168701</t>
+    <t xml:space="preserve">2.77809453010559</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8205726146698</t>
+    <t xml:space="preserve">2.82057285308838</t>
   </si>
   <si>
     <t xml:space="preserve">2.8290684223175</t>
@@ -1181,19 +1181,19 @@
     <t xml:space="preserve">2.88853859901428</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88004279136658</t>
+    <t xml:space="preserve">2.88004302978516</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92252111434937</t>
+    <t xml:space="preserve">2.92252135276794</t>
   </si>
   <si>
     <t xml:space="preserve">2.90552997589111</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87154746055603</t>
+    <t xml:space="preserve">2.87154722213745</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85455584526062</t>
+    <t xml:space="preserve">2.85455560684204</t>
   </si>
   <si>
     <t xml:space="preserve">2.91402554512024</t>
@@ -1214,7 +1214,7 @@
     <t xml:space="preserve">2.98199129104614</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79508590698242</t>
+    <t xml:space="preserve">2.79508566856384</t>
   </si>
   <si>
     <t xml:space="preserve">2.78659009933472</t>
@@ -1223,28 +1223,28 @@
     <t xml:space="preserve">2.76110315322876</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76959896087646</t>
+    <t xml:space="preserve">2.76959872245789</t>
   </si>
   <si>
     <t xml:space="preserve">2.81207704544067</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83756399154663</t>
+    <t xml:space="preserve">2.83756422996521</t>
   </si>
   <si>
     <t xml:space="preserve">2.86305141448975</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62517166137695</t>
+    <t xml:space="preserve">2.62517142295837</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67614603042603</t>
+    <t xml:space="preserve">2.6761462688446</t>
   </si>
   <si>
     <t xml:space="preserve">2.61667609214783</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55720639228821</t>
+    <t xml:space="preserve">2.55720615386963</t>
   </si>
   <si>
     <t xml:space="preserve">2.51472783088684</t>
@@ -1256,28 +1256,28 @@
     <t xml:space="preserve">2.4807448387146</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53171920776367</t>
+    <t xml:space="preserve">2.53171896934509</t>
   </si>
   <si>
     <t xml:space="preserve">2.46375370025635</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58269309997559</t>
+    <t xml:space="preserve">2.58269333839417</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54021453857422</t>
+    <t xml:space="preserve">2.5402147769928</t>
   </si>
   <si>
     <t xml:space="preserve">2.56570196151733</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59118914604187</t>
+    <t xml:space="preserve">2.59118866920471</t>
   </si>
   <si>
     <t xml:space="preserve">2.47224926948547</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63366746902466</t>
+    <t xml:space="preserve">2.63366723060608</t>
   </si>
   <si>
     <t xml:space="preserve">2.599684715271</t>
@@ -1292,7 +1292,7 @@
     <t xml:space="preserve">3.075443983078</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0074782371521</t>
+    <t xml:space="preserve">3.00747847557068</t>
   </si>
   <si>
     <t xml:space="preserve">2.99048686027527</t>
@@ -1301,7 +1301,7 @@
     <t xml:space="preserve">2.96499991416931</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97349572181702</t>
+    <t xml:space="preserve">2.97349548339844</t>
   </si>
   <si>
     <t xml:space="preserve">2.95650410652161</t>
@@ -1319,13 +1319,13 @@
     <t xml:space="preserve">2.65915465354919</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31083083152771</t>
+    <t xml:space="preserve">2.31083059310913</t>
   </si>
   <si>
     <t xml:space="preserve">2.35330939292908</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34481358528137</t>
+    <t xml:space="preserve">2.34481334686279</t>
   </si>
   <si>
     <t xml:space="preserve">2.45525789260864</t>
@@ -1337,16 +1337,16 @@
     <t xml:space="preserve">2.65065884590149</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64216279983521</t>
+    <t xml:space="preserve">2.64216303825378</t>
   </si>
   <si>
     <t xml:space="preserve">2.71012878417969</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69313764572144</t>
+    <t xml:space="preserve">2.69313716888428</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71862435340881</t>
+    <t xml:space="preserve">2.71862459182739</t>
   </si>
   <si>
     <t xml:space="preserve">2.74411153793335</t>
@@ -1358,43 +1358,43 @@
     <t xml:space="preserve">2.60818028450012</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50623178482056</t>
+    <t xml:space="preserve">2.50623202323914</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44676208496094</t>
+    <t xml:space="preserve">2.44676184654236</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37879657745361</t>
+    <t xml:space="preserve">2.37879633903503</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42977070808411</t>
+    <t xml:space="preserve">2.42977046966553</t>
   </si>
   <si>
     <t xml:space="preserve">2.37030076980591</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31932640075684</t>
+    <t xml:space="preserve">2.31932663917542</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27684831619263</t>
+    <t xml:space="preserve">2.27684807777405</t>
   </si>
   <si>
     <t xml:space="preserve">2.26835250854492</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30233502388</t>
+    <t xml:space="preserve">2.30233526229858</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33631777763367</t>
+    <t xml:space="preserve">2.33631801605225</t>
   </si>
   <si>
     <t xml:space="preserve">2.39578795433044</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72712016105652</t>
+    <t xml:space="preserve">2.72711992263794</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99898242950439</t>
+    <t xml:space="preserve">2.99898266792297</t>
   </si>
   <si>
     <t xml:space="preserve">3.03296542167664</t>
@@ -1403,10 +1403,10 @@
     <t xml:space="preserve">3.01597380638123</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04146122932434</t>
+    <t xml:space="preserve">3.04146146774292</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1943838596344</t>
+    <t xml:space="preserve">3.19438362121582</t>
   </si>
   <si>
     <t xml:space="preserve">3.1264181137085</t>
@@ -1418,7 +1418,7 @@
     <t xml:space="preserve">3.09243535995483</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16040086746216</t>
+    <t xml:space="preserve">3.16040110588074</t>
   </si>
   <si>
     <t xml:space="preserve">3.21137523651123</t>
@@ -1427,7 +1427,7 @@
     <t xml:space="preserve">3.3133237361908</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26234912872314</t>
+    <t xml:space="preserve">3.26234936714172</t>
   </si>
   <si>
     <t xml:space="preserve">3.33031511306763</t>
@@ -1436,10 +1436,10 @@
     <t xml:space="preserve">3.22836661338806</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17739224433899</t>
+    <t xml:space="preserve">3.17739248275757</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14340972900391</t>
+    <t xml:space="preserve">3.14340996742249</t>
   </si>
   <si>
     <t xml:space="preserve">3.10942697525024</t>
@@ -1460,10 +1460,10 @@
     <t xml:space="preserve">3.36429786682129</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34730648994446</t>
+    <t xml:space="preserve">3.34730672836304</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24535799026489</t>
+    <t xml:space="preserve">3.24535822868347</t>
   </si>
   <si>
     <t xml:space="preserve">3.02446961402893</t>
@@ -1478,7 +1478,7 @@
     <t xml:space="preserve">3.05899119377136</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01516604423523</t>
+    <t xml:space="preserve">3.01516628265381</t>
   </si>
   <si>
     <t xml:space="preserve">2.97134113311768</t>
@@ -1499,13 +1499,13 @@
     <t xml:space="preserve">3.09405112266541</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07652139663696</t>
+    <t xml:space="preserve">3.07652115821838</t>
   </si>
   <si>
     <t xml:space="preserve">3.06775617599487</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00640106201172</t>
+    <t xml:space="preserve">3.0064013004303</t>
   </si>
   <si>
     <t xml:space="preserve">2.9888710975647</t>
@@ -1523,7 +1523,7 @@
     <t xml:space="preserve">2.96257615089417</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86616063117981</t>
+    <t xml:space="preserve">2.86616086959839</t>
   </si>
   <si>
     <t xml:space="preserve">2.91875076293945</t>
@@ -1535,19 +1535,19 @@
     <t xml:space="preserve">2.82233572006226</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94504594802856</t>
+    <t xml:space="preserve">2.94504570960999</t>
   </si>
   <si>
     <t xml:space="preserve">2.95381093025208</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83110046386719</t>
+    <t xml:space="preserve">2.83110070228577</t>
   </si>
   <si>
     <t xml:space="preserve">2.93628096580505</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03269624710083</t>
+    <t xml:space="preserve">3.03269600868225</t>
   </si>
   <si>
     <t xml:space="preserve">2.90122079849243</t>
@@ -1562,40 +1562,40 @@
     <t xml:space="preserve">2.81357073783875</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83986568450928</t>
+    <t xml:space="preserve">2.83986592292786</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68209552764893</t>
+    <t xml:space="preserve">2.68209528923035</t>
   </si>
   <si>
     <t xml:space="preserve">2.69086027145386</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66456532478333</t>
+    <t xml:space="preserve">2.6645655632019</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85739588737488</t>
+    <t xml:space="preserve">2.8573956489563</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90998578071594</t>
+    <t xml:space="preserve">2.90998601913452</t>
   </si>
   <si>
     <t xml:space="preserve">2.7785108089447</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76974582672119</t>
+    <t xml:space="preserve">2.76974558830261</t>
   </si>
   <si>
     <t xml:space="preserve">2.79604053497314</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84863090515137</t>
+    <t xml:space="preserve">2.84863066673279</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08528614044189</t>
+    <t xml:space="preserve">3.08528637886047</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76098036766052</t>
+    <t xml:space="preserve">2.7609806060791</t>
   </si>
   <si>
     <t xml:space="preserve">2.78727579116821</t>
@@ -1604,7 +1604,7 @@
     <t xml:space="preserve">2.75221562385559</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73468542098999</t>
+    <t xml:space="preserve">2.73468565940857</t>
   </si>
   <si>
     <t xml:space="preserve">2.86875891685486</t>
@@ -1622,34 +1622,34 @@
     <t xml:space="preserve">2.83221411705017</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8870313167572</t>
+    <t xml:space="preserve">2.88703107833862</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85048627853394</t>
+    <t xml:space="preserve">2.85048651695251</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96012043952942</t>
+    <t xml:space="preserve">2.960120677948</t>
   </si>
   <si>
     <t xml:space="preserve">2.99666523933411</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79566955566406</t>
+    <t xml:space="preserve">2.79566931724548</t>
   </si>
   <si>
     <t xml:space="preserve">2.81394171714783</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77739691734314</t>
+    <t xml:space="preserve">2.77739715576172</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75912475585938</t>
+    <t xml:space="preserve">2.7591245174408</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70430779457092</t>
+    <t xml:space="preserve">2.70430755615234</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64949083328247</t>
+    <t xml:space="preserve">2.64949059486389</t>
   </si>
   <si>
     <t xml:space="preserve">2.68603539466858</t>
@@ -1667,16 +1667,16 @@
     <t xml:space="preserve">2.72258019447327</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59467339515686</t>
+    <t xml:space="preserve">2.59467363357544</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5764012336731</t>
+    <t xml:space="preserve">2.57640099525452</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61294603347778</t>
+    <t xml:space="preserve">2.6129457950592</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97839307785034</t>
+    <t xml:space="preserve">2.97839283943176</t>
   </si>
   <si>
     <t xml:space="preserve">2.823077917099</t>
@@ -1700,7 +1700,7 @@
     <t xml:space="preserve">3.01493763923645</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96925687789917</t>
+    <t xml:space="preserve">2.96925663948059</t>
   </si>
   <si>
     <t xml:space="preserve">3.02674722671509</t>
@@ -1797,6 +1797,9 @@
   </si>
   <si>
     <t xml:space="preserve">3.23614478111267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96012043952942</t>
   </si>
   <si>
     <t xml:space="preserve">3.20000004768372</t>
@@ -62601,7 +62604,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G2319" t="s">
-        <v>538</v>
+        <v>595</v>
       </c>
       <c r="H2319" t="s">
         <v>9</v>
@@ -64291,7 +64294,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2384" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="H2384" t="s">
         <v>9</v>
@@ -64317,7 +64320,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G2385" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="H2385" t="s">
         <v>9</v>
@@ -64343,7 +64346,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G2386" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="H2386" t="s">
         <v>9</v>
@@ -64369,7 +64372,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G2387" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="H2387" t="s">
         <v>9</v>
@@ -64395,7 +64398,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G2388" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="H2388" t="s">
         <v>9</v>
@@ -64421,7 +64424,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G2389" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="H2389" t="s">
         <v>9</v>
@@ -64447,7 +64450,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2390" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="H2390" t="s">
         <v>9</v>
@@ -64473,7 +64476,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2391" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="H2391" t="s">
         <v>9</v>
@@ -64525,7 +64528,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G2393" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="H2393" t="s">
         <v>9</v>
@@ -64577,7 +64580,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2395" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="H2395" t="s">
         <v>9</v>
@@ -64603,7 +64606,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2396" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="H2396" t="s">
         <v>9</v>
@@ -64629,7 +64632,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G2397" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="H2397" t="s">
         <v>9</v>
@@ -64655,7 +64658,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2398" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="H2398" t="s">
         <v>9</v>
@@ -64681,7 +64684,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G2399" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="H2399" t="s">
         <v>9</v>
@@ -64707,7 +64710,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G2400" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="H2400" t="s">
         <v>9</v>
@@ -64733,7 +64736,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G2401" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="H2401" t="s">
         <v>9</v>
@@ -64759,7 +64762,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G2402" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="H2402" t="s">
         <v>9</v>
@@ -64785,7 +64788,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G2403" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="H2403" t="s">
         <v>9</v>
@@ -64811,7 +64814,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G2404" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="H2404" t="s">
         <v>9</v>
@@ -64837,7 +64840,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G2405" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="H2405" t="s">
         <v>9</v>
@@ -64863,7 +64866,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G2406" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="H2406" t="s">
         <v>9</v>
@@ -64889,7 +64892,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G2407" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="H2407" t="s">
         <v>9</v>
@@ -64915,7 +64918,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G2408" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="H2408" t="s">
         <v>9</v>
@@ -64941,7 +64944,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2409" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="H2409" t="s">
         <v>9</v>
@@ -64967,7 +64970,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G2410" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="H2410" t="s">
         <v>9</v>
@@ -64993,7 +64996,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G2411" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="H2411" t="s">
         <v>9</v>
@@ -65019,7 +65022,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G2412" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="H2412" t="s">
         <v>9</v>
@@ -65045,7 +65048,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G2413" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="H2413" t="s">
         <v>9</v>
@@ -65071,7 +65074,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G2414" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="H2414" t="s">
         <v>9</v>
@@ -65097,7 +65100,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G2415" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="H2415" t="s">
         <v>9</v>
@@ -65123,7 +65126,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G2416" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="H2416" t="s">
         <v>9</v>
@@ -65149,7 +65152,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G2417" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="H2417" t="s">
         <v>9</v>
@@ -65175,7 +65178,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G2418" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="H2418" t="s">
         <v>9</v>
@@ -65201,7 +65204,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G2419" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="H2419" t="s">
         <v>9</v>
@@ -65227,7 +65230,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G2420" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="H2420" t="s">
         <v>9</v>
@@ -65253,7 +65256,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G2421" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="H2421" t="s">
         <v>9</v>
@@ -65279,7 +65282,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G2422" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="H2422" t="s">
         <v>9</v>
@@ -65305,7 +65308,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G2423" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="H2423" t="s">
         <v>9</v>
@@ -65331,7 +65334,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G2424" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="H2424" t="s">
         <v>9</v>
@@ -65357,7 +65360,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G2425" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="H2425" t="s">
         <v>9</v>
@@ -65383,7 +65386,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G2426" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="H2426" t="s">
         <v>9</v>
@@ -65409,7 +65412,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G2427" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="H2427" t="s">
         <v>9</v>
@@ -65435,7 +65438,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G2428" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="H2428" t="s">
         <v>9</v>
@@ -65461,7 +65464,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G2429" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="H2429" t="s">
         <v>9</v>
@@ -65487,7 +65490,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G2430" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="H2430" t="s">
         <v>9</v>
@@ -65513,7 +65516,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G2431" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="H2431" t="s">
         <v>9</v>
@@ -65539,7 +65542,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G2432" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="H2432" t="s">
         <v>9</v>
@@ -65565,7 +65568,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G2433" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="H2433" t="s">
         <v>9</v>
@@ -65591,7 +65594,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G2434" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="H2434" t="s">
         <v>9</v>
@@ -65617,7 +65620,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G2435" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="H2435" t="s">
         <v>9</v>
@@ -65643,7 +65646,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G2436" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="H2436" t="s">
         <v>9</v>
@@ -65669,7 +65672,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G2437" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="H2437" t="s">
         <v>9</v>
@@ -65695,7 +65698,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G2438" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="H2438" t="s">
         <v>9</v>
@@ -65721,7 +65724,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G2439" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="H2439" t="s">
         <v>9</v>
@@ -65747,7 +65750,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G2440" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="H2440" t="s">
         <v>9</v>
@@ -65773,7 +65776,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G2441" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="H2441" t="s">
         <v>9</v>
@@ -65799,7 +65802,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G2442" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="H2442" t="s">
         <v>9</v>
@@ -65825,7 +65828,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G2443" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="H2443" t="s">
         <v>9</v>
@@ -65851,7 +65854,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G2444" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="H2444" t="s">
         <v>9</v>
@@ -65877,7 +65880,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G2445" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="H2445" t="s">
         <v>9</v>
@@ -65903,7 +65906,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G2446" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="H2446" t="s">
         <v>9</v>
@@ -65929,7 +65932,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G2447" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="H2447" t="s">
         <v>9</v>
@@ -65955,7 +65958,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G2448" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="H2448" t="s">
         <v>9</v>
@@ -65981,7 +65984,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G2449" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="H2449" t="s">
         <v>9</v>
@@ -66007,7 +66010,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G2450" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="H2450" t="s">
         <v>9</v>
@@ -66033,7 +66036,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G2451" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="H2451" t="s">
         <v>9</v>
@@ -66059,7 +66062,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G2452" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="H2452" t="s">
         <v>9</v>
@@ -66085,7 +66088,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G2453" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="H2453" t="s">
         <v>9</v>
@@ -66111,7 +66114,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G2454" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="H2454" t="s">
         <v>9</v>
@@ -66137,7 +66140,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G2455" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="H2455" t="s">
         <v>9</v>
@@ -66163,7 +66166,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G2456" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="H2456" t="s">
         <v>9</v>
@@ -66189,7 +66192,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G2457" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="H2457" t="s">
         <v>9</v>
@@ -66215,7 +66218,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G2458" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="H2458" t="s">
         <v>9</v>
@@ -66241,7 +66244,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G2459" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="H2459" t="s">
         <v>9</v>
@@ -66267,7 +66270,7 @@
         <v>4</v>
       </c>
       <c r="G2460" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="H2460" t="s">
         <v>9</v>
@@ -66293,7 +66296,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G2461" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="H2461" t="s">
         <v>9</v>
@@ -66319,7 +66322,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G2462" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="H2462" t="s">
         <v>9</v>
@@ -66345,7 +66348,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G2463" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="H2463" t="s">
         <v>9</v>
@@ -66371,7 +66374,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G2464" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="H2464" t="s">
         <v>9</v>
@@ -66397,7 +66400,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G2465" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="H2465" t="s">
         <v>9</v>
@@ -66423,7 +66426,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G2466" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="H2466" t="s">
         <v>9</v>
@@ -66449,7 +66452,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G2467" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="H2467" t="s">
         <v>9</v>
@@ -66475,7 +66478,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G2468" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="H2468" t="s">
         <v>9</v>
@@ -66501,7 +66504,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G2469" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="H2469" t="s">
         <v>9</v>
@@ -66527,7 +66530,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G2470" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="H2470" t="s">
         <v>9</v>
@@ -66553,7 +66556,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G2471" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="H2471" t="s">
         <v>9</v>
@@ -66579,7 +66582,7 @@
         <v>4</v>
       </c>
       <c r="G2472" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="H2472" t="s">
         <v>9</v>
@@ -66605,7 +66608,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G2473" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="H2473" t="s">
         <v>9</v>
@@ -66631,7 +66634,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G2474" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="H2474" t="s">
         <v>9</v>
@@ -66657,7 +66660,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G2475" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="H2475" t="s">
         <v>9</v>
@@ -66683,7 +66686,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G2476" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="H2476" t="s">
         <v>9</v>
@@ -66709,7 +66712,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G2477" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="H2477" t="s">
         <v>9</v>
@@ -66735,7 +66738,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G2478" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="H2478" t="s">
         <v>9</v>
@@ -66761,7 +66764,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G2479" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="H2479" t="s">
         <v>9</v>
@@ -66787,7 +66790,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G2480" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="H2480" t="s">
         <v>9</v>
@@ -66813,7 +66816,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G2481" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="H2481" t="s">
         <v>9</v>
@@ -66839,7 +66842,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G2482" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="H2482" t="s">
         <v>9</v>
@@ -66865,7 +66868,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G2483" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="H2483" t="s">
         <v>9</v>
@@ -66891,7 +66894,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G2484" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="H2484" t="s">
         <v>9</v>
@@ -66917,7 +66920,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G2485" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="H2485" t="s">
         <v>9</v>
@@ -66943,7 +66946,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G2486" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="H2486" t="s">
         <v>9</v>
@@ -66969,7 +66972,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G2487" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="H2487" t="s">
         <v>9</v>
@@ -66995,7 +66998,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G2488" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="H2488" t="s">
         <v>9</v>
@@ -67021,7 +67024,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G2489" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="H2489" t="s">
         <v>9</v>
@@ -67047,7 +67050,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G2490" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="H2490" t="s">
         <v>9</v>
@@ -67073,7 +67076,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G2491" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="H2491" t="s">
         <v>9</v>
@@ -67099,7 +67102,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G2492" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="H2492" t="s">
         <v>9</v>
@@ -67125,7 +67128,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G2493" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="H2493" t="s">
         <v>9</v>
@@ -67151,7 +67154,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G2494" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="H2494" t="s">
         <v>9</v>
@@ -67177,7 +67180,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G2495" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="H2495" t="s">
         <v>9</v>
@@ -67203,7 +67206,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G2496" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="H2496" t="s">
         <v>9</v>
@@ -67229,7 +67232,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G2497" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="H2497" t="s">
         <v>9</v>
@@ -67255,7 +67258,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G2498" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="H2498" t="s">
         <v>9</v>
@@ -67281,7 +67284,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G2499" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="H2499" t="s">
         <v>9</v>
@@ -67307,7 +67310,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G2500" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="H2500" t="s">
         <v>9</v>
@@ -67333,7 +67336,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G2501" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="H2501" t="s">
         <v>9</v>
@@ -67359,7 +67362,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G2502" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="H2502" t="s">
         <v>9</v>
@@ -67385,7 +67388,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G2503" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="H2503" t="s">
         <v>9</v>
@@ -67411,7 +67414,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G2504" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H2504" t="s">
         <v>9</v>
@@ -67437,7 +67440,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G2505" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="H2505" t="s">
         <v>9</v>
@@ -67463,7 +67466,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G2506" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="H2506" t="s">
         <v>9</v>
@@ -67489,7 +67492,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G2507" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="H2507" t="s">
         <v>9</v>
@@ -67515,7 +67518,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G2508" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="H2508" t="s">
         <v>9</v>
@@ -67541,7 +67544,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G2509" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="H2509" t="s">
         <v>9</v>
@@ -67567,7 +67570,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G2510" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="H2510" t="s">
         <v>9</v>
@@ -67593,7 +67596,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G2511" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="H2511" t="s">
         <v>9</v>
@@ -67619,7 +67622,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G2512" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="H2512" t="s">
         <v>9</v>
@@ -67645,7 +67648,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G2513" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="H2513" t="s">
         <v>9</v>
@@ -67671,7 +67674,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G2514" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="H2514" t="s">
         <v>9</v>
@@ -67697,7 +67700,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G2515" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="H2515" t="s">
         <v>9</v>
@@ -67723,7 +67726,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G2516" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="H2516" t="s">
         <v>9</v>
@@ -67749,7 +67752,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G2517" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="H2517" t="s">
         <v>9</v>
@@ -67775,7 +67778,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G2518" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="H2518" t="s">
         <v>9</v>
@@ -67801,7 +67804,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G2519" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="H2519" t="s">
         <v>9</v>
@@ -67827,7 +67830,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G2520" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="H2520" t="s">
         <v>9</v>
@@ -67853,7 +67856,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G2521" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="H2521" t="s">
         <v>9</v>
@@ -67879,7 +67882,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G2522" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="H2522" t="s">
         <v>9</v>
@@ -67905,7 +67908,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G2523" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="H2523" t="s">
         <v>9</v>
@@ -67931,7 +67934,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G2524" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="H2524" t="s">
         <v>9</v>
@@ -67957,7 +67960,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G2525" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="H2525" t="s">
         <v>9</v>
@@ -67983,7 +67986,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G2526" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="H2526" t="s">
         <v>9</v>
@@ -68009,7 +68012,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G2527" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="H2527" t="s">
         <v>9</v>
@@ -68035,7 +68038,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G2528" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="H2528" t="s">
         <v>9</v>
@@ -68061,7 +68064,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G2529" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="H2529" t="s">
         <v>9</v>
@@ -68087,7 +68090,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G2530" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="H2530" t="s">
         <v>9</v>
@@ -68113,7 +68116,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G2531" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="H2531" t="s">
         <v>9</v>
@@ -68139,7 +68142,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G2532" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="H2532" t="s">
         <v>9</v>
@@ -68165,7 +68168,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G2533" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="H2533" t="s">
         <v>9</v>
@@ -68191,7 +68194,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G2534" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="H2534" t="s">
         <v>9</v>
@@ -68217,7 +68220,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G2535" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="H2535" t="s">
         <v>9</v>
@@ -68243,7 +68246,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G2536" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="H2536" t="s">
         <v>9</v>
@@ -68269,7 +68272,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G2537" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="H2537" t="s">
         <v>9</v>
@@ -68295,7 +68298,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G2538" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="H2538" t="s">
         <v>9</v>
@@ -68321,7 +68324,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G2539" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="H2539" t="s">
         <v>9</v>
@@ -68347,7 +68350,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G2540" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="H2540" t="s">
         <v>9</v>
@@ -68373,9 +68376,35 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G2541" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="H2541" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2542">
+      <c r="A2542" s="1" t="n">
+        <v>46024.6940856482</v>
+      </c>
+      <c r="B2542" t="n">
+        <v>25434</v>
+      </c>
+      <c r="C2542" t="n">
+        <v>3.77999997138977</v>
+      </c>
+      <c r="D2542" t="n">
+        <v>3.51999998092651</v>
+      </c>
+      <c r="E2542" t="n">
+        <v>3.77999997138977</v>
+      </c>
+      <c r="F2542" t="n">
+        <v>3.75999999046326</v>
+      </c>
+      <c r="G2542" t="s">
+        <v>613</v>
+      </c>
+      <c r="H2542" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ENV.MI.xlsx
+++ b/data/ENV.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="656" uniqueCount="656">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="657" uniqueCount="657">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -44,37 +44,37 @@
     <t xml:space="preserve">ENV.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20979762077332</t>
+    <t xml:space="preserve">2.20979785919189</t>
   </si>
   <si>
     <t xml:space="preserve">2.14471244812012</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16175842285156</t>
+    <t xml:space="preserve">2.16175889968872</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03778719902039</t>
+    <t xml:space="preserve">2.03778696060181</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08272647857666</t>
+    <t xml:space="preserve">2.08272671699524</t>
   </si>
   <si>
     <t xml:space="preserve">2.05328321456909</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03623723983765</t>
+    <t xml:space="preserve">2.03623747825623</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96805274486542</t>
+    <t xml:space="preserve">1.96805322170258</t>
   </si>
   <si>
     <t xml:space="preserve">1.96030473709106</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8983188867569</t>
+    <t xml:space="preserve">1.89831876754761</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88127255439758</t>
+    <t xml:space="preserve">1.88127243518829</t>
   </si>
   <si>
     <t xml:space="preserve">1.96340382099152</t>
@@ -83,16 +83,16 @@
     <t xml:space="preserve">1.98354935646057</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01299285888672</t>
+    <t xml:space="preserve">2.01299262046814</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93551015853882</t>
+    <t xml:space="preserve">1.93551003932953</t>
   </si>
   <si>
     <t xml:space="preserve">1.93705999851227</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91381514072418</t>
+    <t xml:space="preserve">1.91381537914276</t>
   </si>
   <si>
     <t xml:space="preserve">1.91071593761444</t>
@@ -101,106 +101,106 @@
     <t xml:space="preserve">1.86577606201172</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89212012290955</t>
+    <t xml:space="preserve">1.89211988449097</t>
   </si>
   <si>
     <t xml:space="preserve">1.85182929039001</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93396031856537</t>
+    <t xml:space="preserve">1.93396043777466</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86732578277588</t>
+    <t xml:space="preserve">1.86732590198517</t>
   </si>
   <si>
     <t xml:space="preserve">1.88902103900909</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98664855957031</t>
+    <t xml:space="preserve">1.9866486787796</t>
   </si>
   <si>
     <t xml:space="preserve">2.11526942253113</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18500328063965</t>
+    <t xml:space="preserve">2.18500351905823</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20824861526489</t>
+    <t xml:space="preserve">2.20824837684631</t>
   </si>
   <si>
     <t xml:space="preserve">2.16950702667236</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08427667617798</t>
+    <t xml:space="preserve">2.08427619934082</t>
   </si>
   <si>
     <t xml:space="preserve">2.0145423412323</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0052444934845</t>
+    <t xml:space="preserve">2.00524473190308</t>
   </si>
   <si>
     <t xml:space="preserve">2.14626240730286</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2221953868866</t>
+    <t xml:space="preserve">2.22219491004944</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32447171211243</t>
+    <t xml:space="preserve">2.32447218894958</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20050001144409</t>
+    <t xml:space="preserve">2.20049977302551</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27178359031677</t>
+    <t xml:space="preserve">2.27178382873535</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24698948860168</t>
+    <t xml:space="preserve">2.24698925018311</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32137227058411</t>
+    <t xml:space="preserve">2.32137250900269</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28418111801147</t>
+    <t xml:space="preserve">2.2841808795929</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37870931625366</t>
+    <t xml:space="preserve">2.37870979309082</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35546445846558</t>
+    <t xml:space="preserve">2.35546469688416</t>
   </si>
   <si>
     <t xml:space="preserve">2.44069528579712</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43139743804932</t>
+    <t xml:space="preserve">2.4313976764679</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4499933719635</t>
+    <t xml:space="preserve">2.44999361038208</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38490796089172</t>
+    <t xml:space="preserve">2.3849081993103</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3616635799408</t>
+    <t xml:space="preserve">2.36166381835938</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36321330070496</t>
+    <t xml:space="preserve">2.3632128238678</t>
   </si>
   <si>
     <t xml:space="preserve">2.3198230266571</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35236573219299</t>
+    <t xml:space="preserve">2.35236549377441</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26868462562561</t>
+    <t xml:space="preserve">2.26868438720703</t>
   </si>
   <si>
     <t xml:space="preserve">2.32292199134827</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33531975746155</t>
+    <t xml:space="preserve">2.33531928062439</t>
   </si>
   <si>
     <t xml:space="preserve">2.33996844291687</t>
@@ -209,16 +209,16 @@
     <t xml:space="preserve">2.3105251789093</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28573060035706</t>
+    <t xml:space="preserve">2.28573036193848</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25473809242249</t>
+    <t xml:space="preserve">2.25473785400391</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29037952423096</t>
+    <t xml:space="preserve">2.29037976264954</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27488279342651</t>
+    <t xml:space="preserve">2.27488350868225</t>
   </si>
   <si>
     <t xml:space="preserve">2.23149299621582</t>
@@ -236,13 +236,13 @@
     <t xml:space="preserve">2.02229046821594</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97580087184906</t>
+    <t xml:space="preserve">1.97580111026764</t>
   </si>
   <si>
     <t xml:space="preserve">1.91980683803558</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88216328620911</t>
+    <t xml:space="preserve">1.88216352462769</t>
   </si>
   <si>
     <t xml:space="preserve">2.00136733055115</t>
@@ -260,49 +260,49 @@
     <t xml:space="preserve">1.91353285312653</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89784812927246</t>
+    <t xml:space="preserve">1.89784848690033</t>
   </si>
   <si>
     <t xml:space="preserve">1.89000594615936</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85079383850098</t>
+    <t xml:space="preserve">1.85079371929169</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88059496879578</t>
+    <t xml:space="preserve">1.8805947303772</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86647891998291</t>
+    <t xml:space="preserve">1.86647880077362</t>
   </si>
   <si>
     <t xml:space="preserve">1.546511054039</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68610501289368</t>
+    <t xml:space="preserve">1.68610489368439</t>
   </si>
   <si>
     <t xml:space="preserve">1.70178961753845</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70022070407867</t>
+    <t xml:space="preserve">1.70022094249725</t>
   </si>
   <si>
     <t xml:space="preserve">1.66257762908936</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64532470703125</t>
+    <t xml:space="preserve">1.64532446861267</t>
   </si>
   <si>
     <t xml:space="preserve">1.62336599826813</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61552345752716</t>
+    <t xml:space="preserve">1.61552357673645</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63120818138123</t>
+    <t xml:space="preserve">1.6312084197998</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58415412902832</t>
+    <t xml:space="preserve">1.58415424823761</t>
   </si>
   <si>
     <t xml:space="preserve">1.64689302444458</t>
@@ -311,112 +311,112 @@
     <t xml:space="preserve">1.6406192779541</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6390506029129</t>
+    <t xml:space="preserve">1.63905084133148</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60768127441406</t>
+    <t xml:space="preserve">1.60768139362335</t>
   </si>
   <si>
     <t xml:space="preserve">1.57631194591522</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59199666976929</t>
+    <t xml:space="preserve">1.59199655056</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75668585300446</t>
+    <t xml:space="preserve">1.75668597221375</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84295165538788</t>
+    <t xml:space="preserve">1.84295153617859</t>
   </si>
   <si>
     <t xml:space="preserve">1.84608888626099</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92921781539917</t>
+    <t xml:space="preserve">1.92921769618988</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88530051708221</t>
+    <t xml:space="preserve">1.88530027866364</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90098512172699</t>
+    <t xml:space="preserve">1.9009850025177</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91823828220367</t>
+    <t xml:space="preserve">1.91823816299438</t>
   </si>
   <si>
     <t xml:space="preserve">1.9496077299118</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93078577518463</t>
+    <t xml:space="preserve">1.93078589439392</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84922540187836</t>
+    <t xml:space="preserve">1.84922575950623</t>
   </si>
   <si>
     <t xml:space="preserve">1.82413005828857</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85549938678741</t>
+    <t xml:space="preserve">1.8554995059967</t>
   </si>
   <si>
     <t xml:space="preserve">1.89627981185913</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93705987930298</t>
+    <t xml:space="preserve">1.93706023693085</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8743212223053</t>
+    <t xml:space="preserve">1.87432110309601</t>
   </si>
   <si>
     <t xml:space="preserve">1.94333350658417</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94490194320679</t>
+    <t xml:space="preserve">1.94490242004395</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9668607711792</t>
+    <t xml:space="preserve">1.96686053276062</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98411417007446</t>
+    <t xml:space="preserve">1.9841136932373</t>
   </si>
   <si>
     <t xml:space="preserve">2.0625376701355</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0531268119812</t>
+    <t xml:space="preserve">2.05312657356262</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05155801773071</t>
+    <t xml:space="preserve">2.05155849456787</t>
   </si>
   <si>
     <t xml:space="preserve">2.02332592010498</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02959966659546</t>
+    <t xml:space="preserve">2.02959990501404</t>
   </si>
   <si>
     <t xml:space="preserve">2.03116798400879</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06096887588501</t>
+    <t xml:space="preserve">2.06096911430359</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09390687942505</t>
+    <t xml:space="preserve">2.09390711784363</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08606457710266</t>
+    <t xml:space="preserve">2.08606433868408</t>
   </si>
   <si>
     <t xml:space="preserve">2.1550772190094</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18801474571228</t>
+    <t xml:space="preserve">2.18801498413086</t>
   </si>
   <si>
     <t xml:space="preserve">2.19585728645325</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2021312713623</t>
+    <t xml:space="preserve">2.20213103294373</t>
   </si>
   <si>
     <t xml:space="preserve">2.23350071907043</t>
@@ -425,10 +425,10 @@
     <t xml:space="preserve">2.20997381210327</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18017268180847</t>
+    <t xml:space="preserve">2.18017244338989</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16605663299561</t>
+    <t xml:space="preserve">2.16605687141418</t>
   </si>
   <si>
     <t xml:space="preserve">2.19428896903992</t>
@@ -443,40 +443,40 @@
     <t xml:space="preserve">2.21938443183899</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21781611442566</t>
+    <t xml:space="preserve">2.21781587600708</t>
   </si>
   <si>
     <t xml:space="preserve">2.1911518573761</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12057089805603</t>
+    <t xml:space="preserve">2.12057065963745</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15350914001465</t>
+    <t xml:space="preserve">2.15350866317749</t>
   </si>
   <si>
     <t xml:space="preserve">2.11743402481079</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16291928291321</t>
+    <t xml:space="preserve">2.16291952133179</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10802268981934</t>
+    <t xml:space="preserve">2.10802292823792</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01548337936401</t>
+    <t xml:space="preserve">2.01548314094543</t>
   </si>
   <si>
     <t xml:space="preserve">2.04528427124023</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98568248748779</t>
+    <t xml:space="preserve">1.9856823682785</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07822203636169</t>
+    <t xml:space="preserve">2.07822227478027</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06724262237549</t>
+    <t xml:space="preserve">2.06724286079407</t>
   </si>
   <si>
     <t xml:space="preserve">2.12998151779175</t>
@@ -485,61 +485,61 @@
     <t xml:space="preserve">2.11586546897888</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05469489097595</t>
+    <t xml:space="preserve">2.05469512939453</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11429691314697</t>
+    <t xml:space="preserve">2.11429715156555</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05626344680786</t>
+    <t xml:space="preserve">2.05626368522644</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06410598754883</t>
+    <t xml:space="preserve">2.06410574913025</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10488653182983</t>
+    <t xml:space="preserve">2.10488629341125</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00920987129211</t>
+    <t xml:space="preserve">2.00920939445496</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0139148235321</t>
+    <t xml:space="preserve">2.01391506195068</t>
   </si>
   <si>
     <t xml:space="preserve">2.04842114448547</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16448783874512</t>
+    <t xml:space="preserve">2.1644880771637</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18487811088562</t>
+    <t xml:space="preserve">2.1848783493042</t>
   </si>
   <si>
     <t xml:space="preserve">2.26643872261047</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27271246910095</t>
+    <t xml:space="preserve">2.27271223068237</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25702786445618</t>
+    <t xml:space="preserve">2.25702810287476</t>
   </si>
   <si>
     <t xml:space="preserve">2.30721879005432</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23036408424377</t>
+    <t xml:space="preserve">2.23036360740662</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37152576446533</t>
+    <t xml:space="preserve">2.37152600288391</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35270428657532</t>
+    <t xml:space="preserve">2.3527045249939</t>
   </si>
   <si>
     <t xml:space="preserve">2.39191627502441</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33545088768005</t>
+    <t xml:space="preserve">2.33545112609863</t>
   </si>
   <si>
     <t xml:space="preserve">2.3134925365448</t>
@@ -551,31 +551,31 @@
     <t xml:space="preserve">2.32917737960815</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24918556213379</t>
+    <t xml:space="preserve">2.24918508529663</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28839683532715</t>
+    <t xml:space="preserve">2.28839707374573</t>
   </si>
   <si>
     <t xml:space="preserve">2.33701968193054</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34486222267151</t>
+    <t xml:space="preserve">2.34486174583435</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3495671749115</t>
+    <t xml:space="preserve">2.34956765174866</t>
   </si>
   <si>
     <t xml:space="preserve">2.32604050636292</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30251312255859</t>
+    <t xml:space="preserve">2.30251359939575</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31192421913147</t>
+    <t xml:space="preserve">2.31192398071289</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25075364112854</t>
+    <t xml:space="preserve">2.25075387954712</t>
   </si>
   <si>
     <t xml:space="preserve">2.27428102493286</t>
@@ -584,19 +584,19 @@
     <t xml:space="preserve">2.43897008895874</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48445582389832</t>
+    <t xml:space="preserve">2.48445558547974</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46249747276306</t>
+    <t xml:space="preserve">2.46249723434448</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50798296928406</t>
+    <t xml:space="preserve">2.50798273086548</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48602414131165</t>
+    <t xml:space="preserve">2.4860246181488</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60993361473083</t>
+    <t xml:space="preserve">2.6099328994751</t>
   </si>
   <si>
     <t xml:space="preserve">2.66639828681946</t>
@@ -608,19 +608,19 @@
     <t xml:space="preserve">2.66012406349182</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64287090301514</t>
+    <t xml:space="preserve">2.64287114143372</t>
   </si>
   <si>
     <t xml:space="preserve">2.65855598449707</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60209131240845</t>
+    <t xml:space="preserve">2.60209107398987</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55033183097839</t>
+    <t xml:space="preserve">2.55033135414124</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63816595077515</t>
+    <t xml:space="preserve">2.63816571235657</t>
   </si>
   <si>
     <t xml:space="preserve">2.58013224601746</t>
@@ -629,7 +629,7 @@
     <t xml:space="preserve">2.59581732749939</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58170080184937</t>
+    <t xml:space="preserve">2.58170104026794</t>
   </si>
   <si>
     <t xml:space="preserve">2.6036593914032</t>
@@ -638,22 +638,22 @@
     <t xml:space="preserve">2.61934423446655</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57542705535889</t>
+    <t xml:space="preserve">2.57542681694031</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57385849952698</t>
+    <t xml:space="preserve">2.57385897636414</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50955128669739</t>
+    <t xml:space="preserve">2.50955176353455</t>
   </si>
   <si>
-    <t xml:space="preserve">2.587975025177</t>
+    <t xml:space="preserve">2.58797454833984</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56444764137268</t>
+    <t xml:space="preserve">2.56444787979126</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61150169372559</t>
+    <t xml:space="preserve">2.61150217056274</t>
   </si>
   <si>
     <t xml:space="preserve">2.56915330886841</t>
@@ -662,79 +662,79 @@
     <t xml:space="preserve">2.63502883911133</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62561821937561</t>
+    <t xml:space="preserve">2.62561798095703</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62718653678894</t>
+    <t xml:space="preserve">2.62718629837036</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83422470092773</t>
+    <t xml:space="preserve">2.83422446250916</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79030752182007</t>
+    <t xml:space="preserve">2.79030728340149</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77619099617004</t>
+    <t xml:space="preserve">2.77619123458862</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78089642524719</t>
+    <t xml:space="preserve">2.78089666366577</t>
   </si>
   <si>
     <t xml:space="preserve">2.69149374961853</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78246545791626</t>
+    <t xml:space="preserve">2.78246521949768</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81226587295532</t>
+    <t xml:space="preserve">2.81226563453674</t>
   </si>
   <si>
     <t xml:space="preserve">2.82324528694153</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68678879737854</t>
+    <t xml:space="preserve">2.68678855895996</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70090460777283</t>
+    <t xml:space="preserve">2.70090484619141</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8065710067749</t>
+    <t xml:space="preserve">2.80657124519348</t>
   </si>
   <si>
     <t xml:space="preserve">2.86433959007263</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81940841674805</t>
+    <t xml:space="preserve">2.81940865516663</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80817604064941</t>
+    <t xml:space="preserve">2.80817627906799</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88038635253906</t>
+    <t xml:space="preserve">2.8803858757019</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83385062217712</t>
+    <t xml:space="preserve">2.8338508605957</t>
   </si>
   <si>
     <t xml:space="preserve">2.74398922920227</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72794270515442</t>
+    <t xml:space="preserve">2.72794246673584</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70547676086426</t>
+    <t xml:space="preserve">2.70547699928284</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73275637626648</t>
+    <t xml:space="preserve">2.7327561378479</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67177867889404</t>
+    <t xml:space="preserve">2.6717791557312</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62363886833191</t>
+    <t xml:space="preserve">2.62363862991333</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61722040176392</t>
+    <t xml:space="preserve">2.61721992492676</t>
   </si>
   <si>
     <t xml:space="preserve">2.60438275337219</t>
@@ -743,7 +743,7 @@
     <t xml:space="preserve">2.62524342536926</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64128994941711</t>
+    <t xml:space="preserve">2.64129042625427</t>
   </si>
   <si>
     <t xml:space="preserve">2.69584894180298</t>
@@ -764,22 +764,22 @@
     <t xml:space="preserve">2.74238443374634</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80015254020691</t>
+    <t xml:space="preserve">2.80015277862549</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78571033477783</t>
+    <t xml:space="preserve">2.78571057319641</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82422280311584</t>
+    <t xml:space="preserve">2.82422256469727</t>
   </si>
   <si>
     <t xml:space="preserve">2.78731513023376</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79373383522034</t>
+    <t xml:space="preserve">2.79373407363892</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80496692657471</t>
+    <t xml:space="preserve">2.80496644973755</t>
   </si>
   <si>
     <t xml:space="preserve">2.78410601615906</t>
@@ -791,10 +791,10 @@
     <t xml:space="preserve">2.79533863067627</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82261800765991</t>
+    <t xml:space="preserve">2.82261824607849</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7600359916687</t>
+    <t xml:space="preserve">2.76003575325012</t>
   </si>
   <si>
     <t xml:space="preserve">2.77929210662842</t>
@@ -806,34 +806,34 @@
     <t xml:space="preserve">2.77447772026062</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8033618927002</t>
+    <t xml:space="preserve">2.80336213111877</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83545541763306</t>
+    <t xml:space="preserve">2.83545517921448</t>
   </si>
   <si>
     <t xml:space="preserve">2.84026956558228</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83224606513977</t>
+    <t xml:space="preserve">2.83224630355835</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8113853931427</t>
+    <t xml:space="preserve">2.81138515472412</t>
   </si>
   <si>
     <t xml:space="preserve">2.81619930267334</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76324534416199</t>
+    <t xml:space="preserve">2.76324510574341</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71189594268799</t>
+    <t xml:space="preserve">2.71189546585083</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72473287582397</t>
+    <t xml:space="preserve">2.72473335266113</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79694366455078</t>
+    <t xml:space="preserve">2.79694318771362</t>
   </si>
   <si>
     <t xml:space="preserve">2.79052448272705</t>
@@ -842,34 +842,34 @@
     <t xml:space="preserve">2.76805925369263</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73115181922913</t>
+    <t xml:space="preserve">2.73115205764771</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7038722038269</t>
+    <t xml:space="preserve">2.70387244224548</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81459474563599</t>
+    <t xml:space="preserve">2.81459450721741</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82903695106506</t>
+    <t xml:space="preserve">2.82903671264648</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84347891807556</t>
+    <t xml:space="preserve">2.84347867965698</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77768707275391</t>
+    <t xml:space="preserve">2.77768731117249</t>
   </si>
   <si>
     <t xml:space="preserve">2.77126860618591</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88840961456299</t>
+    <t xml:space="preserve">2.88840937614441</t>
   </si>
   <si>
     <t xml:space="preserve">2.87236285209656</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89161920547485</t>
+    <t xml:space="preserve">2.89161944389343</t>
   </si>
   <si>
     <t xml:space="preserve">2.92852663993835</t>
@@ -881,10 +881,10 @@
     <t xml:space="preserve">2.90927028656006</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99913167953491</t>
+    <t xml:space="preserve">2.99913191795349</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96864342689514</t>
+    <t xml:space="preserve">2.96864318847656</t>
   </si>
   <si>
     <t xml:space="preserve">2.830641746521</t>
@@ -896,13 +896,13 @@
     <t xml:space="preserve">2.87717700004578</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87557244300842</t>
+    <t xml:space="preserve">2.87557220458984</t>
   </si>
   <si>
     <t xml:space="preserve">2.7520124912262</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76164031028748</t>
+    <t xml:space="preserve">2.76164054870605</t>
   </si>
   <si>
     <t xml:space="preserve">2.78892016410828</t>
@@ -911,19 +911,19 @@
     <t xml:space="preserve">2.67980217933655</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73596572875977</t>
+    <t xml:space="preserve">2.73596596717834</t>
   </si>
   <si>
     <t xml:space="preserve">2.8258273601532</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84829306602478</t>
+    <t xml:space="preserve">2.8482928276062</t>
   </si>
   <si>
     <t xml:space="preserve">2.82101345062256</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73436093330383</t>
+    <t xml:space="preserve">2.73436117172241</t>
   </si>
   <si>
     <t xml:space="preserve">2.81780409812927</t>
@@ -935,7 +935,7 @@
     <t xml:space="preserve">2.74077987670898</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79212951660156</t>
+    <t xml:space="preserve">2.79212927818298</t>
   </si>
   <si>
     <t xml:space="preserve">2.6637556552887</t>
@@ -950,25 +950,25 @@
     <t xml:space="preserve">2.56747531890869</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59956884384155</t>
+    <t xml:space="preserve">2.59956860542297</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55945181846619</t>
+    <t xml:space="preserve">2.55945205688477</t>
   </si>
   <si>
     <t xml:space="preserve">2.50328803062439</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45514822006226</t>
+    <t xml:space="preserve">2.45514845848083</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47921800613403</t>
+    <t xml:space="preserve">2.47921824455261</t>
   </si>
   <si>
     <t xml:space="preserve">2.47119474411011</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43107795715332</t>
+    <t xml:space="preserve">2.4310781955719</t>
   </si>
   <si>
     <t xml:space="preserve">2.46317148208618</t>
@@ -977,7 +977,7 @@
     <t xml:space="preserve">2.48724150657654</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49526476860046</t>
+    <t xml:space="preserve">2.49526500701904</t>
   </si>
   <si>
     <t xml:space="preserve">2.5273585319519</t>
@@ -986,34 +986,34 @@
     <t xml:space="preserve">2.58352208137512</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65573215484619</t>
+    <t xml:space="preserve">2.65573239326477</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9124801158905</t>
+    <t xml:space="preserve">2.91247963905334</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8200249671936</t>
+    <t xml:space="preserve">2.82002472877502</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80358171463013</t>
+    <t xml:space="preserve">2.80358147621155</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86935472488403</t>
+    <t xml:space="preserve">2.86935496330261</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84468984603882</t>
+    <t xml:space="preserve">2.8446900844574</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85291171073914</t>
+    <t xml:space="preserve">2.85291147232056</t>
   </si>
   <si>
     <t xml:space="preserve">2.81180334091187</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72136497497559</t>
+    <t xml:space="preserve">2.72136521339417</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68025684356689</t>
+    <t xml:space="preserve">2.68025660514832</t>
   </si>
   <si>
     <t xml:space="preserve">2.69670009613037</t>
@@ -1025,46 +1025,46 @@
     <t xml:space="preserve">2.65559196472168</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66381359100342</t>
+    <t xml:space="preserve">2.663813829422</t>
   </si>
   <si>
     <t xml:space="preserve">2.63092708587646</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63914847373962</t>
+    <t xml:space="preserve">2.6391487121582</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55693221092224</t>
+    <t xml:space="preserve">2.55693197250366</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59804058074951</t>
+    <t xml:space="preserve">2.59804034233093</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54871034622192</t>
+    <t xml:space="preserve">2.5487105846405</t>
   </si>
   <si>
     <t xml:space="preserve">2.46649408340454</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60626196861267</t>
+    <t xml:space="preserve">2.60626220703125</t>
   </si>
   <si>
     <t xml:space="preserve">2.52404570579529</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58159708976746</t>
+    <t xml:space="preserve">2.58159732818604</t>
   </si>
   <si>
     <t xml:space="preserve">2.61448383331299</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58981895446777</t>
+    <t xml:space="preserve">2.58981871604919</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62270545959473</t>
+    <t xml:space="preserve">2.62270569801331</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51582384109497</t>
+    <t xml:space="preserve">2.51582407951355</t>
   </si>
   <si>
     <t xml:space="preserve">2.57337546348572</t>
@@ -1079,10 +1079,10 @@
     <t xml:space="preserve">2.47471570968628</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48293733596802</t>
+    <t xml:space="preserve">2.4829375743866</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45005083084106</t>
+    <t xml:space="preserve">2.45005059242249</t>
   </si>
   <si>
     <t xml:space="preserve">2.44182920455933</t>
@@ -1091,7 +1091,7 @@
     <t xml:space="preserve">2.42538595199585</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43360757827759</t>
+    <t xml:space="preserve">2.43360733985901</t>
   </si>
   <si>
     <t xml:space="preserve">2.49115896224976</t>
@@ -1103,16 +1103,16 @@
     <t xml:space="preserve">2.54048871994019</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67203545570374</t>
+    <t xml:space="preserve">2.67203521728516</t>
   </si>
   <si>
     <t xml:space="preserve">2.68847846984863</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70492196083069</t>
+    <t xml:space="preserve">2.70492172241211</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71314334869385</t>
+    <t xml:space="preserve">2.71314311027527</t>
   </si>
   <si>
     <t xml:space="preserve">2.75425171852112</t>
@@ -1124,58 +1124,58 @@
     <t xml:space="preserve">2.77069497108459</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72958660125732</t>
+    <t xml:space="preserve">2.7295868396759</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7460298538208</t>
+    <t xml:space="preserve">2.74603009223938</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77891683578491</t>
+    <t xml:space="preserve">2.77891659736633</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79535984992981</t>
+    <t xml:space="preserve">2.79536008834839</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87757635116577</t>
+    <t xml:space="preserve">2.87757658958435</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91868472099304</t>
+    <t xml:space="preserve">2.91868448257446</t>
   </si>
   <si>
     <t xml:space="preserve">2.89401960372925</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86113286018372</t>
+    <t xml:space="preserve">2.86113309860229</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90224123001099</t>
+    <t xml:space="preserve">2.90224146842957</t>
   </si>
   <si>
     <t xml:space="preserve">2.88579821586609</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83646821975708</t>
+    <t xml:space="preserve">2.8364679813385</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94334959983826</t>
+    <t xml:space="preserve">2.94334936141968</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82824635505676</t>
+    <t xml:space="preserve">2.82824659347534</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92690634727478</t>
+    <t xml:space="preserve">2.9269061088562</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80358147621155</t>
+    <t xml:space="preserve">2.80358123779297</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77809453010559</t>
+    <t xml:space="preserve">2.77809429168701</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82057285308838</t>
+    <t xml:space="preserve">2.82057309150696</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8290684223175</t>
+    <t xml:space="preserve">2.82906866073608</t>
   </si>
   <si>
     <t xml:space="preserve">2.88853859901428</t>
@@ -1190,7 +1190,7 @@
     <t xml:space="preserve">2.90552997589111</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87154722213745</t>
+    <t xml:space="preserve">2.87154698371887</t>
   </si>
   <si>
     <t xml:space="preserve">2.85455560684204</t>
@@ -1208,7 +1208,7 @@
     <t xml:space="preserve">2.89703416824341</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93951272964478</t>
+    <t xml:space="preserve">2.93951296806335</t>
   </si>
   <si>
     <t xml:space="preserve">2.98199129104614</t>
@@ -1220,13 +1220,13 @@
     <t xml:space="preserve">2.78659009933472</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76110315322876</t>
+    <t xml:space="preserve">2.76110291481018</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76959872245789</t>
+    <t xml:space="preserve">2.76959848403931</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81207704544067</t>
+    <t xml:space="preserve">2.81207728385925</t>
   </si>
   <si>
     <t xml:space="preserve">2.83756422996521</t>
@@ -1235,49 +1235,49 @@
     <t xml:space="preserve">2.86305141448975</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62517142295837</t>
+    <t xml:space="preserve">2.62517166137695</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6761462688446</t>
+    <t xml:space="preserve">2.67614603042603</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61667609214783</t>
+    <t xml:space="preserve">2.61667585372925</t>
   </si>
   <si>
     <t xml:space="preserve">2.55720615386963</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51472783088684</t>
+    <t xml:space="preserve">2.51472759246826</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49773645401001</t>
+    <t xml:space="preserve">2.49773621559143</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4807448387146</t>
+    <t xml:space="preserve">2.48074507713318</t>
   </si>
   <si>
     <t xml:space="preserve">2.53171896934509</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46375370025635</t>
+    <t xml:space="preserve">2.46375346183777</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58269333839417</t>
+    <t xml:space="preserve">2.58269309997559</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5402147769928</t>
+    <t xml:space="preserve">2.54021453857422</t>
   </si>
   <si>
     <t xml:space="preserve">2.56570196151733</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59118866920471</t>
+    <t xml:space="preserve">2.59118890762329</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47224926948547</t>
+    <t xml:space="preserve">2.47224903106689</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63366723060608</t>
+    <t xml:space="preserve">2.63366746902466</t>
   </si>
   <si>
     <t xml:space="preserve">2.599684715271</t>
@@ -1301,7 +1301,7 @@
     <t xml:space="preserve">2.96499991416931</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97349548339844</t>
+    <t xml:space="preserve">2.97349572181702</t>
   </si>
   <si>
     <t xml:space="preserve">2.95650410652161</t>
@@ -1310,7 +1310,7 @@
     <t xml:space="preserve">2.84606003761292</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75260734558105</t>
+    <t xml:space="preserve">2.75260758399963</t>
   </si>
   <si>
     <t xml:space="preserve">2.6676504611969</t>
@@ -1319,13 +1319,13 @@
     <t xml:space="preserve">2.65915465354919</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31083059310913</t>
+    <t xml:space="preserve">2.31083083152771</t>
   </si>
   <si>
     <t xml:space="preserve">2.35330939292908</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34481334686279</t>
+    <t xml:space="preserve">2.34481358528137</t>
   </si>
   <si>
     <t xml:space="preserve">2.45525789260864</t>
@@ -1334,16 +1334,16 @@
     <t xml:space="preserve">2.4892406463623</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65065884590149</t>
+    <t xml:space="preserve">2.65065860748291</t>
   </si>
   <si>
     <t xml:space="preserve">2.64216303825378</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71012878417969</t>
+    <t xml:space="preserve">2.71012902259827</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69313716888428</t>
+    <t xml:space="preserve">2.69313764572144</t>
   </si>
   <si>
     <t xml:space="preserve">2.71862459182739</t>
@@ -1352,16 +1352,16 @@
     <t xml:space="preserve">2.74411153793335</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68464183807373</t>
+    <t xml:space="preserve">2.68464159965515</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60818028450012</t>
+    <t xml:space="preserve">2.6081805229187</t>
   </si>
   <si>
     <t xml:space="preserve">2.50623202323914</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44676184654236</t>
+    <t xml:space="preserve">2.44676232337952</t>
   </si>
   <si>
     <t xml:space="preserve">2.37879633903503</t>
@@ -1370,16 +1370,16 @@
     <t xml:space="preserve">2.42977046966553</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37030076980591</t>
+    <t xml:space="preserve">2.37030053138733</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31932663917542</t>
+    <t xml:space="preserve">2.31932640075684</t>
   </si>
   <si>
     <t xml:space="preserve">2.27684807777405</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26835250854492</t>
+    <t xml:space="preserve">2.26835227012634</t>
   </si>
   <si>
     <t xml:space="preserve">2.30233526229858</t>
@@ -1388,10 +1388,10 @@
     <t xml:space="preserve">2.33631801605225</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39578795433044</t>
+    <t xml:space="preserve">2.39578771591187</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72711992263794</t>
+    <t xml:space="preserve">2.72712016105652</t>
   </si>
   <si>
     <t xml:space="preserve">2.99898266792297</t>
@@ -1403,10 +1403,10 @@
     <t xml:space="preserve">3.01597380638123</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04146146774292</t>
+    <t xml:space="preserve">3.04146099090576</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19438362121582</t>
+    <t xml:space="preserve">3.1943838596344</t>
   </si>
   <si>
     <t xml:space="preserve">3.1264181137085</t>
@@ -1415,31 +1415,31 @@
     <t xml:space="preserve">3.05845236778259</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09243535995483</t>
+    <t xml:space="preserve">3.09243559837341</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16040110588074</t>
+    <t xml:space="preserve">3.16040086746216</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21137523651123</t>
+    <t xml:space="preserve">3.21137547492981</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3133237361908</t>
+    <t xml:space="preserve">3.31332349777222</t>
   </si>
   <si>
     <t xml:space="preserve">3.26234936714172</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33031511306763</t>
+    <t xml:space="preserve">3.33031487464905</t>
   </si>
   <si>
     <t xml:space="preserve">3.22836661338806</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17739248275757</t>
+    <t xml:space="preserve">3.17739224433899</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14340996742249</t>
+    <t xml:space="preserve">3.14340949058533</t>
   </si>
   <si>
     <t xml:space="preserve">3.10942697525024</t>
@@ -1448,22 +1448,22 @@
     <t xml:space="preserve">3.27934074401855</t>
   </si>
   <si>
-    <t xml:space="preserve">3.48323750495911</t>
+    <t xml:space="preserve">3.48323774337769</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39828038215637</t>
+    <t xml:space="preserve">3.39828062057495</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46624612808228</t>
+    <t xml:space="preserve">3.46624636650085</t>
   </si>
   <si>
     <t xml:space="preserve">3.36429786682129</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34730672836304</t>
+    <t xml:space="preserve">3.34730648994446</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24535822868347</t>
+    <t xml:space="preserve">3.24535799026489</t>
   </si>
   <si>
     <t xml:space="preserve">3.02446961402893</t>
@@ -1478,7 +1478,7 @@
     <t xml:space="preserve">3.05899119377136</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01516628265381</t>
+    <t xml:space="preserve">3.01516604423523</t>
   </si>
   <si>
     <t xml:space="preserve">2.97134113311768</t>
@@ -1487,7 +1487,7 @@
     <t xml:space="preserve">3.02393102645874</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10281610488892</t>
+    <t xml:space="preserve">3.1028163433075</t>
   </si>
   <si>
     <t xml:space="preserve">3.13787627220154</t>
@@ -1496,22 +1496,25 @@
     <t xml:space="preserve">2.98010611534119</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09405112266541</t>
+    <t xml:space="preserve">3.09405136108398</t>
   </si>
   <si>
     <t xml:space="preserve">3.07652115821838</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06775617599487</t>
+    <t xml:space="preserve">3.06775641441345</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0064013004303</t>
+    <t xml:space="preserve">3.04146122932434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00640106201172</t>
   </si>
   <si>
     <t xml:space="preserve">2.9888710975647</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89245581626892</t>
+    <t xml:space="preserve">2.89245557785034</t>
   </si>
   <si>
     <t xml:space="preserve">2.92751574516296</t>
@@ -1520,13 +1523,13 @@
     <t xml:space="preserve">2.99763607978821</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96257615089417</t>
+    <t xml:space="preserve">2.96257591247559</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86616086959839</t>
+    <t xml:space="preserve">2.86616063117981</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91875076293945</t>
+    <t xml:space="preserve">2.91875100135803</t>
   </si>
   <si>
     <t xml:space="preserve">2.80480575561523</t>
@@ -1535,7 +1538,7 @@
     <t xml:space="preserve">2.82233572006226</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94504570960999</t>
+    <t xml:space="preserve">2.94504594802856</t>
   </si>
   <si>
     <t xml:space="preserve">2.95381093025208</t>
@@ -1547,13 +1550,13 @@
     <t xml:space="preserve">2.93628096580505</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03269600868225</t>
+    <t xml:space="preserve">3.03269624710083</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90122079849243</t>
+    <t xml:space="preserve">2.90122103691101</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88369083404541</t>
+    <t xml:space="preserve">2.88369059562683</t>
   </si>
   <si>
     <t xml:space="preserve">2.8749258518219</t>
@@ -1565,13 +1568,13 @@
     <t xml:space="preserve">2.83986592292786</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68209528923035</t>
+    <t xml:space="preserve">2.68209552764893</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69086027145386</t>
+    <t xml:space="preserve">2.69086050987244</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6645655632019</t>
+    <t xml:space="preserve">2.66456532478333</t>
   </si>
   <si>
     <t xml:space="preserve">2.8573956489563</t>
@@ -1586,13 +1589,13 @@
     <t xml:space="preserve">2.76974558830261</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79604053497314</t>
+    <t xml:space="preserve">2.79604077339172</t>
   </si>
   <si>
     <t xml:space="preserve">2.84863066673279</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08528637886047</t>
+    <t xml:space="preserve">3.08528614044189</t>
   </si>
   <si>
     <t xml:space="preserve">2.7609806060791</t>
@@ -1604,7 +1607,7 @@
     <t xml:space="preserve">2.75221562385559</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73468565940857</t>
+    <t xml:space="preserve">2.73468518257141</t>
   </si>
   <si>
     <t xml:space="preserve">2.86875891685486</t>
@@ -45002,7 +45005,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G1642" t="s">
-        <v>463</v>
+        <v>497</v>
       </c>
       <c r="H1642" t="s">
         <v>9</v>
@@ -45028,7 +45031,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G1643" t="s">
-        <v>463</v>
+        <v>497</v>
       </c>
       <c r="H1643" t="s">
         <v>9</v>
@@ -45054,7 +45057,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G1644" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="H1644" t="s">
         <v>9</v>
@@ -45106,7 +45109,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G1646" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H1646" t="s">
         <v>9</v>
@@ -45132,7 +45135,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1647" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H1647" t="s">
         <v>9</v>
@@ -45158,7 +45161,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G1648" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="H1648" t="s">
         <v>9</v>
@@ -45210,7 +45213,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1650" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="H1650" t="s">
         <v>9</v>
@@ -45236,7 +45239,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1651" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="H1651" t="s">
         <v>9</v>
@@ -45262,7 +45265,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1652" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="H1652" t="s">
         <v>9</v>
@@ -45288,7 +45291,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G1653" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="H1653" t="s">
         <v>9</v>
@@ -45314,7 +45317,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G1654" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="H1654" t="s">
         <v>9</v>
@@ -45340,7 +45343,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G1655" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="H1655" t="s">
         <v>9</v>
@@ -45366,7 +45369,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G1656" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="H1656" t="s">
         <v>9</v>
@@ -45392,7 +45395,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G1657" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="H1657" t="s">
         <v>9</v>
@@ -45444,7 +45447,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G1659" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="H1659" t="s">
         <v>9</v>
@@ -45470,7 +45473,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1660" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="H1660" t="s">
         <v>9</v>
@@ -45496,7 +45499,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G1661" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="H1661" t="s">
         <v>9</v>
@@ -45522,7 +45525,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1662" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H1662" t="s">
         <v>9</v>
@@ -45548,7 +45551,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1663" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H1663" t="s">
         <v>9</v>
@@ -45574,7 +45577,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1664" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H1664" t="s">
         <v>9</v>
@@ -45600,7 +45603,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1665" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H1665" t="s">
         <v>9</v>
@@ -45626,7 +45629,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1666" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H1666" t="s">
         <v>9</v>
@@ -45652,7 +45655,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1667" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="H1667" t="s">
         <v>9</v>
@@ -45678,7 +45681,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G1668" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="H1668" t="s">
         <v>9</v>
@@ -45704,7 +45707,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1669" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="H1669" t="s">
         <v>9</v>
@@ -45730,7 +45733,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1670" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="H1670" t="s">
         <v>9</v>
@@ -45756,7 +45759,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G1671" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="H1671" t="s">
         <v>9</v>
@@ -45782,7 +45785,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1672" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="H1672" t="s">
         <v>9</v>
@@ -45808,7 +45811,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G1673" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="H1673" t="s">
         <v>9</v>
@@ -45834,7 +45837,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G1674" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="H1674" t="s">
         <v>9</v>
@@ -45860,7 +45863,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G1675" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="H1675" t="s">
         <v>9</v>
@@ -45886,7 +45889,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G1676" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="H1676" t="s">
         <v>9</v>
@@ -45912,7 +45915,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1677" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="H1677" t="s">
         <v>9</v>
@@ -45938,7 +45941,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G1678" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="H1678" t="s">
         <v>9</v>
@@ -45964,7 +45967,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G1679" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="H1679" t="s">
         <v>9</v>
@@ -45990,7 +45993,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1680" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="H1680" t="s">
         <v>9</v>
@@ -46016,7 +46019,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G1681" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="H1681" t="s">
         <v>9</v>
@@ -46068,7 +46071,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1683" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="H1683" t="s">
         <v>9</v>
@@ -46094,7 +46097,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G1684" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="H1684" t="s">
         <v>9</v>
@@ -46146,7 +46149,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G1686" t="s">
-        <v>463</v>
+        <v>497</v>
       </c>
       <c r="H1686" t="s">
         <v>9</v>
@@ -46172,7 +46175,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G1687" t="s">
-        <v>463</v>
+        <v>497</v>
       </c>
       <c r="H1687" t="s">
         <v>9</v>
@@ -46198,7 +46201,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G1688" t="s">
-        <v>463</v>
+        <v>497</v>
       </c>
       <c r="H1688" t="s">
         <v>9</v>
@@ -46224,7 +46227,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1689" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="H1689" t="s">
         <v>9</v>
@@ -46250,7 +46253,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G1690" t="s">
-        <v>463</v>
+        <v>497</v>
       </c>
       <c r="H1690" t="s">
         <v>9</v>
@@ -46276,7 +46279,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G1691" t="s">
-        <v>463</v>
+        <v>497</v>
       </c>
       <c r="H1691" t="s">
         <v>9</v>
@@ -46302,7 +46305,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G1692" t="s">
-        <v>463</v>
+        <v>497</v>
       </c>
       <c r="H1692" t="s">
         <v>9</v>
@@ -46328,7 +46331,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1693" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H1693" t="s">
         <v>9</v>
@@ -46354,7 +46357,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G1694" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="H1694" t="s">
         <v>9</v>
@@ -46380,7 +46383,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G1695" t="s">
-        <v>463</v>
+        <v>497</v>
       </c>
       <c r="H1695" t="s">
         <v>9</v>
@@ -46458,7 +46461,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G1698" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="H1698" t="s">
         <v>9</v>
@@ -46484,7 +46487,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G1699" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="H1699" t="s">
         <v>9</v>
@@ -46510,7 +46513,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1700" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="H1700" t="s">
         <v>9</v>
@@ -46562,7 +46565,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G1702" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="H1702" t="s">
         <v>9</v>
@@ -46588,7 +46591,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1703" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="H1703" t="s">
         <v>9</v>
@@ -46614,7 +46617,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G1704" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="H1704" t="s">
         <v>9</v>
@@ -46640,7 +46643,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G1705" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="H1705" t="s">
         <v>9</v>
@@ -46666,7 +46669,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1706" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="H1706" t="s">
         <v>9</v>
@@ -46692,7 +46695,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1707" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="H1707" t="s">
         <v>9</v>
@@ -46796,7 +46799,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G1711" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="H1711" t="s">
         <v>9</v>
@@ -46822,7 +46825,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1712" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="H1712" t="s">
         <v>9</v>
@@ -46848,7 +46851,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G1713" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="H1713" t="s">
         <v>9</v>
@@ -46874,7 +46877,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G1714" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="H1714" t="s">
         <v>9</v>
@@ -46900,7 +46903,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G1715" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="H1715" t="s">
         <v>9</v>
@@ -46926,7 +46929,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1716" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="H1716" t="s">
         <v>9</v>
@@ -46952,7 +46955,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G1717" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="H1717" t="s">
         <v>9</v>
@@ -46978,7 +46981,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G1718" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="H1718" t="s">
         <v>9</v>
@@ -47004,7 +47007,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1719" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="H1719" t="s">
         <v>9</v>
@@ -47030,7 +47033,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G1720" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="H1720" t="s">
         <v>9</v>
@@ -47056,7 +47059,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G1721" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="H1721" t="s">
         <v>9</v>
@@ -47082,7 +47085,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G1722" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="H1722" t="s">
         <v>9</v>
@@ -47108,7 +47111,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G1723" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="H1723" t="s">
         <v>9</v>
@@ -47134,7 +47137,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G1724" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="H1724" t="s">
         <v>9</v>
@@ -47160,7 +47163,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G1725" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="H1725" t="s">
         <v>9</v>
@@ -47186,7 +47189,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G1726" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="H1726" t="s">
         <v>9</v>
@@ -47212,7 +47215,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G1727" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="H1727" t="s">
         <v>9</v>
@@ -47238,7 +47241,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G1728" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="H1728" t="s">
         <v>9</v>
@@ -47264,7 +47267,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G1729" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="H1729" t="s">
         <v>9</v>
@@ -47290,7 +47293,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G1730" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="H1730" t="s">
         <v>9</v>
@@ -47316,7 +47319,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G1731" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="H1731" t="s">
         <v>9</v>
@@ -47342,7 +47345,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G1732" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="H1732" t="s">
         <v>9</v>
@@ -47368,7 +47371,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G1733" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="H1733" t="s">
         <v>9</v>
@@ -47394,7 +47397,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1734" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="H1734" t="s">
         <v>9</v>
@@ -47420,7 +47423,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1735" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="H1735" t="s">
         <v>9</v>
@@ -47446,7 +47449,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G1736" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="H1736" t="s">
         <v>9</v>
@@ -47472,7 +47475,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1737" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="H1737" t="s">
         <v>9</v>
@@ -47498,7 +47501,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G1738" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="H1738" t="s">
         <v>9</v>
@@ -47524,7 +47527,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G1739" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="H1739" t="s">
         <v>9</v>
@@ -47550,7 +47553,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G1740" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="H1740" t="s">
         <v>9</v>
@@ -47576,7 +47579,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1741" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H1741" t="s">
         <v>9</v>
@@ -47602,7 +47605,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1742" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H1742" t="s">
         <v>9</v>
@@ -47628,7 +47631,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G1743" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="H1743" t="s">
         <v>9</v>
@@ -47654,7 +47657,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G1744" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="H1744" t="s">
         <v>9</v>
@@ -47680,7 +47683,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G1745" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="H1745" t="s">
         <v>9</v>
@@ -47706,7 +47709,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G1746" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="H1746" t="s">
         <v>9</v>
@@ -47732,7 +47735,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1747" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="H1747" t="s">
         <v>9</v>
@@ -47758,7 +47761,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G1748" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="H1748" t="s">
         <v>9</v>
@@ -47784,7 +47787,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G1749" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="H1749" t="s">
         <v>9</v>
@@ -47810,7 +47813,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1750" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H1750" t="s">
         <v>9</v>
@@ -47836,7 +47839,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G1751" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="H1751" t="s">
         <v>9</v>
@@ -47862,7 +47865,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1752" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="H1752" t="s">
         <v>9</v>
@@ -47888,7 +47891,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G1753" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="H1753" t="s">
         <v>9</v>
@@ -47914,7 +47917,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G1754" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="H1754" t="s">
         <v>9</v>
@@ -47940,7 +47943,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G1755" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="H1755" t="s">
         <v>9</v>
@@ -47966,7 +47969,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G1756" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="H1756" t="s">
         <v>9</v>
@@ -47992,7 +47995,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1757" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H1757" t="s">
         <v>9</v>
@@ -48018,7 +48021,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G1758" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="H1758" t="s">
         <v>9</v>
@@ -48044,7 +48047,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G1759" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="H1759" t="s">
         <v>9</v>
@@ -48070,7 +48073,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G1760" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="H1760" t="s">
         <v>9</v>
@@ -48096,7 +48099,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G1761" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="H1761" t="s">
         <v>9</v>
@@ -48122,7 +48125,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G1762" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="H1762" t="s">
         <v>9</v>
@@ -48148,7 +48151,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1763" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="H1763" t="s">
         <v>9</v>
@@ -48174,7 +48177,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G1764" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="H1764" t="s">
         <v>9</v>
@@ -48200,7 +48203,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G1765" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="H1765" t="s">
         <v>9</v>
@@ -48226,7 +48229,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G1766" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="H1766" t="s">
         <v>9</v>
@@ -48252,7 +48255,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G1767" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="H1767" t="s">
         <v>9</v>
@@ -48278,7 +48281,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G1768" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="H1768" t="s">
         <v>9</v>
@@ -48304,7 +48307,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G1769" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="H1769" t="s">
         <v>9</v>
@@ -48330,7 +48333,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G1770" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="H1770" t="s">
         <v>9</v>
@@ -48356,7 +48359,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G1771" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="H1771" t="s">
         <v>9</v>
@@ -48382,7 +48385,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1772" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="H1772" t="s">
         <v>9</v>
@@ -48408,7 +48411,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1773" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="H1773" t="s">
         <v>9</v>
@@ -48434,7 +48437,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1774" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="H1774" t="s">
         <v>9</v>
@@ -48460,7 +48463,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1775" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="H1775" t="s">
         <v>9</v>
@@ -48486,7 +48489,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1776" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="H1776" t="s">
         <v>9</v>
@@ -48512,7 +48515,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1777" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="H1777" t="s">
         <v>9</v>
@@ -48538,7 +48541,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1778" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="H1778" t="s">
         <v>9</v>
@@ -48564,7 +48567,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1779" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="H1779" t="s">
         <v>9</v>
@@ -48590,7 +48593,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1780" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="H1780" t="s">
         <v>9</v>
@@ -48616,7 +48619,7 @@
         <v>3.25</v>
       </c>
       <c r="G1781" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="H1781" t="s">
         <v>9</v>
@@ -48642,7 +48645,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G1782" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="H1782" t="s">
         <v>9</v>
@@ -48668,7 +48671,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G1783" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="H1783" t="s">
         <v>9</v>
@@ -48694,7 +48697,7 @@
         <v>3.25</v>
       </c>
       <c r="G1784" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="H1784" t="s">
         <v>9</v>
@@ -48720,7 +48723,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G1785" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="H1785" t="s">
         <v>9</v>
@@ -48746,7 +48749,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G1786" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="H1786" t="s">
         <v>9</v>
@@ -48772,7 +48775,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G1787" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="H1787" t="s">
         <v>9</v>
@@ -48798,7 +48801,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G1788" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="H1788" t="s">
         <v>9</v>
@@ -48824,7 +48827,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1789" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H1789" t="s">
         <v>9</v>
@@ -48850,7 +48853,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1790" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H1790" t="s">
         <v>9</v>
@@ -48876,7 +48879,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1791" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H1791" t="s">
         <v>9</v>
@@ -48902,7 +48905,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1792" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H1792" t="s">
         <v>9</v>
@@ -48928,7 +48931,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G1793" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="H1793" t="s">
         <v>9</v>
@@ -48954,7 +48957,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1794" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H1794" t="s">
         <v>9</v>
@@ -48980,7 +48983,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G1795" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="H1795" t="s">
         <v>9</v>
@@ -49006,7 +49009,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G1796" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="H1796" t="s">
         <v>9</v>
@@ -49032,7 +49035,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1797" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="H1797" t="s">
         <v>9</v>
@@ -49058,7 +49061,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G1798" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="H1798" t="s">
         <v>9</v>
@@ -49084,7 +49087,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G1799" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="H1799" t="s">
         <v>9</v>
@@ -49110,7 +49113,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G1800" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="H1800" t="s">
         <v>9</v>
@@ -49136,7 +49139,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1801" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H1801" t="s">
         <v>9</v>
@@ -49162,7 +49165,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G1802" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="H1802" t="s">
         <v>9</v>
@@ -49188,7 +49191,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G1803" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="H1803" t="s">
         <v>9</v>
@@ -49214,7 +49217,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G1804" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="H1804" t="s">
         <v>9</v>
@@ -49240,7 +49243,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G1805" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="H1805" t="s">
         <v>9</v>
@@ -49266,7 +49269,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G1806" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="H1806" t="s">
         <v>9</v>
@@ -49292,7 +49295,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G1807" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="H1807" t="s">
         <v>9</v>
@@ -49318,7 +49321,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G1808" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="H1808" t="s">
         <v>9</v>
@@ -49344,7 +49347,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1809" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="H1809" t="s">
         <v>9</v>
@@ -49370,7 +49373,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G1810" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="H1810" t="s">
         <v>9</v>
@@ -49396,7 +49399,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1811" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="H1811" t="s">
         <v>9</v>
@@ -49422,7 +49425,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G1812" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="H1812" t="s">
         <v>9</v>
@@ -49448,7 +49451,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G1813" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="H1813" t="s">
         <v>9</v>
@@ -49474,7 +49477,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G1814" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="H1814" t="s">
         <v>9</v>
@@ -49500,7 +49503,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1815" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H1815" t="s">
         <v>9</v>
@@ -49526,7 +49529,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G1816" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="H1816" t="s">
         <v>9</v>
@@ -49552,7 +49555,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G1817" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="H1817" t="s">
         <v>9</v>
@@ -49578,7 +49581,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G1818" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="H1818" t="s">
         <v>9</v>
@@ -49604,7 +49607,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1819" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H1819" t="s">
         <v>9</v>
@@ -49630,7 +49633,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1820" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H1820" t="s">
         <v>9</v>
@@ -49656,7 +49659,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1821" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H1821" t="s">
         <v>9</v>
@@ -49682,7 +49685,7 @@
         <v>3.25</v>
       </c>
       <c r="G1822" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="H1822" t="s">
         <v>9</v>
@@ -49708,7 +49711,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G1823" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="H1823" t="s">
         <v>9</v>
@@ -49734,7 +49737,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G1824" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="H1824" t="s">
         <v>9</v>
@@ -49760,7 +49763,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G1825" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="H1825" t="s">
         <v>9</v>
@@ -49786,7 +49789,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G1826" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H1826" t="s">
         <v>9</v>
@@ -49812,7 +49815,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G1827" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="H1827" t="s">
         <v>9</v>
@@ -49838,7 +49841,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G1828" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="H1828" t="s">
         <v>9</v>
@@ -49864,7 +49867,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G1829" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="H1829" t="s">
         <v>9</v>
@@ -49890,7 +49893,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1830" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="H1830" t="s">
         <v>9</v>
@@ -49916,7 +49919,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G1831" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="H1831" t="s">
         <v>9</v>
@@ -49942,7 +49945,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1832" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="H1832" t="s">
         <v>9</v>
@@ -49968,7 +49971,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G1833" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="H1833" t="s">
         <v>9</v>
@@ -49994,7 +49997,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G1834" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="H1834" t="s">
         <v>9</v>
@@ -50020,7 +50023,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G1835" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="H1835" t="s">
         <v>9</v>
@@ -50046,7 +50049,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G1836" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="H1836" t="s">
         <v>9</v>
@@ -50072,7 +50075,7 @@
         <v>3.25</v>
       </c>
       <c r="G1837" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="H1837" t="s">
         <v>9</v>
@@ -50098,7 +50101,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G1838" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="H1838" t="s">
         <v>9</v>
@@ -50124,7 +50127,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G1839" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="H1839" t="s">
         <v>9</v>
@@ -50150,7 +50153,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1840" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H1840" t="s">
         <v>9</v>
@@ -50176,7 +50179,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G1841" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="H1841" t="s">
         <v>9</v>
@@ -50202,7 +50205,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G1842" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="H1842" t="s">
         <v>9</v>
@@ -50228,7 +50231,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G1843" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="H1843" t="s">
         <v>9</v>
@@ -50254,7 +50257,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G1844" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="H1844" t="s">
         <v>9</v>
@@ -50280,7 +50283,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1845" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="H1845" t="s">
         <v>9</v>
@@ -50306,7 +50309,7 @@
         <v>3.25</v>
       </c>
       <c r="G1846" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="H1846" t="s">
         <v>9</v>
@@ -50332,7 +50335,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1847" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="H1847" t="s">
         <v>9</v>
@@ -50358,7 +50361,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G1848" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="H1848" t="s">
         <v>9</v>
@@ -50384,7 +50387,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G1849" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="H1849" t="s">
         <v>9</v>
@@ -50410,7 +50413,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1850" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="H1850" t="s">
         <v>9</v>
@@ -50436,7 +50439,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1851" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="H1851" t="s">
         <v>9</v>
@@ -50462,7 +50465,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1852" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="H1852" t="s">
         <v>9</v>
@@ -50488,7 +50491,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G1853" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="H1853" t="s">
         <v>9</v>
@@ -50514,7 +50517,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1854" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="H1854" t="s">
         <v>9</v>
@@ -50540,7 +50543,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1855" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="H1855" t="s">
         <v>9</v>
@@ -50566,7 +50569,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G1856" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="H1856" t="s">
         <v>9</v>
@@ -50592,7 +50595,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1857" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="H1857" t="s">
         <v>9</v>
@@ -50618,7 +50621,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1858" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="H1858" t="s">
         <v>9</v>
@@ -50644,7 +50647,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G1859" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="H1859" t="s">
         <v>9</v>
@@ -50670,7 +50673,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G1860" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="H1860" t="s">
         <v>9</v>
@@ -50696,7 +50699,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G1861" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="H1861" t="s">
         <v>9</v>
@@ -50722,7 +50725,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G1862" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="H1862" t="s">
         <v>9</v>
@@ -50748,7 +50751,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1863" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="H1863" t="s">
         <v>9</v>
@@ -50774,7 +50777,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G1864" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="H1864" t="s">
         <v>9</v>
@@ -50800,7 +50803,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G1865" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="H1865" t="s">
         <v>9</v>
@@ -50826,7 +50829,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G1866" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="H1866" t="s">
         <v>9</v>
@@ -50852,7 +50855,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G1867" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="H1867" t="s">
         <v>9</v>
@@ -50878,7 +50881,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G1868" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="H1868" t="s">
         <v>9</v>
@@ -50904,7 +50907,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G1869" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="H1869" t="s">
         <v>9</v>
@@ -50930,7 +50933,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G1870" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="H1870" t="s">
         <v>9</v>
@@ -50956,7 +50959,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G1871" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="H1871" t="s">
         <v>9</v>
@@ -50982,7 +50985,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1872" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="H1872" t="s">
         <v>9</v>
@@ -51008,7 +51011,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1873" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="H1873" t="s">
         <v>9</v>
@@ -51034,7 +51037,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1874" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="H1874" t="s">
         <v>9</v>
@@ -51060,7 +51063,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G1875" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="H1875" t="s">
         <v>9</v>
@@ -51086,7 +51089,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1876" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="H1876" t="s">
         <v>9</v>
@@ -51112,7 +51115,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1877" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="H1877" t="s">
         <v>9</v>
@@ -51138,7 +51141,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G1878" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="H1878" t="s">
         <v>9</v>
@@ -51164,7 +51167,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G1879" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="H1879" t="s">
         <v>9</v>
@@ -51190,7 +51193,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G1880" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="H1880" t="s">
         <v>9</v>
@@ -51216,7 +51219,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G1881" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="H1881" t="s">
         <v>9</v>
@@ -51242,7 +51245,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G1882" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="H1882" t="s">
         <v>9</v>
@@ -51268,7 +51271,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G1883" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="H1883" t="s">
         <v>9</v>
@@ -51294,7 +51297,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G1884" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="H1884" t="s">
         <v>9</v>
@@ -51320,7 +51323,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1885" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="H1885" t="s">
         <v>9</v>
@@ -51346,7 +51349,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1886" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="H1886" t="s">
         <v>9</v>
@@ -51372,7 +51375,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1887" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="H1887" t="s">
         <v>9</v>
@@ -51398,7 +51401,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1888" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="H1888" t="s">
         <v>9</v>
@@ -51424,7 +51427,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G1889" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="H1889" t="s">
         <v>9</v>
@@ -51450,7 +51453,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1890" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="H1890" t="s">
         <v>9</v>
@@ -51476,7 +51479,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1891" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="H1891" t="s">
         <v>9</v>
@@ -51502,7 +51505,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G1892" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="H1892" t="s">
         <v>9</v>
@@ -51528,7 +51531,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1893" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="H1893" t="s">
         <v>9</v>
@@ -51554,7 +51557,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G1894" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="H1894" t="s">
         <v>9</v>
@@ -51580,7 +51583,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1895" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="H1895" t="s">
         <v>9</v>
@@ -51606,7 +51609,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1896" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="H1896" t="s">
         <v>9</v>
@@ -51632,7 +51635,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1897" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="H1897" t="s">
         <v>9</v>
@@ -51658,7 +51661,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1898" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="H1898" t="s">
         <v>9</v>
@@ -51684,7 +51687,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1899" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="H1899" t="s">
         <v>9</v>
@@ -51710,7 +51713,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1900" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="H1900" t="s">
         <v>9</v>
@@ -51736,7 +51739,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1901" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="H1901" t="s">
         <v>9</v>
@@ -51762,7 +51765,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1902" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="H1902" t="s">
         <v>9</v>
@@ -51788,7 +51791,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G1903" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="H1903" t="s">
         <v>9</v>
@@ -51814,7 +51817,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G1904" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="H1904" t="s">
         <v>9</v>
@@ -51840,7 +51843,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1905" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="H1905" t="s">
         <v>9</v>
@@ -51866,7 +51869,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1906" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="H1906" t="s">
         <v>9</v>
@@ -51892,7 +51895,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1907" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="H1907" t="s">
         <v>9</v>
@@ -51918,7 +51921,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1908" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="H1908" t="s">
         <v>9</v>
@@ -51944,7 +51947,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1909" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="H1909" t="s">
         <v>9</v>
@@ -51970,7 +51973,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G1910" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="H1910" t="s">
         <v>9</v>
@@ -51996,7 +51999,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1911" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="H1911" t="s">
         <v>9</v>
@@ -52022,7 +52025,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1912" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="H1912" t="s">
         <v>9</v>
@@ -52048,7 +52051,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1913" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="H1913" t="s">
         <v>9</v>
@@ -52074,7 +52077,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1914" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="H1914" t="s">
         <v>9</v>
@@ -52100,7 +52103,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1915" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="H1915" t="s">
         <v>9</v>
@@ -52126,7 +52129,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1916" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="H1916" t="s">
         <v>9</v>
@@ -52152,7 +52155,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1917" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="H1917" t="s">
         <v>9</v>
@@ -52178,7 +52181,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G1918" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="H1918" t="s">
         <v>9</v>
@@ -52204,7 +52207,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G1919" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="H1919" t="s">
         <v>9</v>
@@ -52230,7 +52233,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G1920" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="H1920" t="s">
         <v>9</v>
@@ -52256,7 +52259,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1921" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="H1921" t="s">
         <v>9</v>
@@ -52282,7 +52285,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1922" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="H1922" t="s">
         <v>9</v>
@@ -52308,7 +52311,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G1923" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="H1923" t="s">
         <v>9</v>
@@ -52334,7 +52337,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G1924" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="H1924" t="s">
         <v>9</v>
@@ -52360,7 +52363,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1925" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="H1925" t="s">
         <v>9</v>
@@ -52386,7 +52389,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G1926" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="H1926" t="s">
         <v>9</v>
@@ -52412,7 +52415,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1927" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="H1927" t="s">
         <v>9</v>
@@ -52438,7 +52441,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G1928" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="H1928" t="s">
         <v>9</v>
@@ -52464,7 +52467,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G1929" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="H1929" t="s">
         <v>9</v>
@@ -52490,7 +52493,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G1930" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="H1930" t="s">
         <v>9</v>
@@ -52516,7 +52519,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G1931" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="H1931" t="s">
         <v>9</v>
@@ -52542,7 +52545,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G1932" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="H1932" t="s">
         <v>9</v>
@@ -52568,7 +52571,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G1933" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="H1933" t="s">
         <v>9</v>
@@ -52594,7 +52597,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G1934" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="H1934" t="s">
         <v>9</v>
@@ -52620,7 +52623,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1935" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="H1935" t="s">
         <v>9</v>
@@ -52646,7 +52649,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1936" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="H1936" t="s">
         <v>9</v>
@@ -52672,7 +52675,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1937" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="H1937" t="s">
         <v>9</v>
@@ -52698,7 +52701,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1938" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="H1938" t="s">
         <v>9</v>
@@ -52724,7 +52727,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1939" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="H1939" t="s">
         <v>9</v>
@@ -52750,7 +52753,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G1940" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="H1940" t="s">
         <v>9</v>
@@ -52776,7 +52779,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1941" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="H1941" t="s">
         <v>9</v>
@@ -52802,7 +52805,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1942" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="H1942" t="s">
         <v>9</v>
@@ -52828,7 +52831,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1943" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="H1943" t="s">
         <v>9</v>
@@ -52854,7 +52857,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1944" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="H1944" t="s">
         <v>9</v>
@@ -52880,7 +52883,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1945" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="H1945" t="s">
         <v>9</v>
@@ -52906,7 +52909,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G1946" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="H1946" t="s">
         <v>9</v>
@@ -52932,7 +52935,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1947" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="H1947" t="s">
         <v>9</v>
@@ -52958,7 +52961,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1948" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="H1948" t="s">
         <v>9</v>
@@ -52984,7 +52987,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1949" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="H1949" t="s">
         <v>9</v>
@@ -53010,7 +53013,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G1950" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="H1950" t="s">
         <v>9</v>
@@ -53036,7 +53039,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G1951" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="H1951" t="s">
         <v>9</v>
@@ -53062,7 +53065,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1952" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="H1952" t="s">
         <v>9</v>
@@ -53088,7 +53091,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1953" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="H1953" t="s">
         <v>9</v>
@@ -53114,7 +53117,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1954" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="H1954" t="s">
         <v>9</v>
@@ -53140,7 +53143,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G1955" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="H1955" t="s">
         <v>9</v>
@@ -53166,7 +53169,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G1956" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="H1956" t="s">
         <v>9</v>
@@ -53192,7 +53195,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G1957" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="H1957" t="s">
         <v>9</v>
@@ -53218,7 +53221,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1958" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="H1958" t="s">
         <v>9</v>
@@ -53244,7 +53247,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1959" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="H1959" t="s">
         <v>9</v>
@@ -53270,7 +53273,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1960" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="H1960" t="s">
         <v>9</v>
@@ -53296,7 +53299,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G1961" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="H1961" t="s">
         <v>9</v>
@@ -53322,7 +53325,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G1962" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="H1962" t="s">
         <v>9</v>
@@ -53348,7 +53351,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G1963" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="H1963" t="s">
         <v>9</v>
@@ -53374,7 +53377,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G1964" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="H1964" t="s">
         <v>9</v>
@@ -53400,7 +53403,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G1965" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="H1965" t="s">
         <v>9</v>
@@ -53426,7 +53429,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G1966" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="H1966" t="s">
         <v>9</v>
@@ -53452,7 +53455,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1967" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="H1967" t="s">
         <v>9</v>
@@ -53478,7 +53481,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G1968" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="H1968" t="s">
         <v>9</v>
@@ -53504,7 +53507,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G1969" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="H1969" t="s">
         <v>9</v>
@@ -53530,7 +53533,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G1970" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="H1970" t="s">
         <v>9</v>
@@ -53556,7 +53559,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G1971" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="H1971" t="s">
         <v>9</v>
@@ -53582,7 +53585,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G1972" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="H1972" t="s">
         <v>9</v>
@@ -53608,7 +53611,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G1973" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="H1973" t="s">
         <v>9</v>
@@ -53634,7 +53637,7 @@
         <v>3</v>
       </c>
       <c r="G1974" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="H1974" t="s">
         <v>9</v>
@@ -53660,7 +53663,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1975" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="H1975" t="s">
         <v>9</v>
@@ -53686,7 +53689,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G1976" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="H1976" t="s">
         <v>9</v>
@@ -53712,7 +53715,7 @@
         <v>3</v>
       </c>
       <c r="G1977" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="H1977" t="s">
         <v>9</v>
@@ -53738,7 +53741,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G1978" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="H1978" t="s">
         <v>9</v>
@@ -53764,7 +53767,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G1979" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="H1979" t="s">
         <v>9</v>
@@ -53790,7 +53793,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1980" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="H1980" t="s">
         <v>9</v>
@@ -53816,7 +53819,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G1981" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="H1981" t="s">
         <v>9</v>
@@ -53842,7 +53845,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G1982" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="H1982" t="s">
         <v>9</v>
@@ -53868,7 +53871,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1983" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="H1983" t="s">
         <v>9</v>
@@ -53894,7 +53897,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1984" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="H1984" t="s">
         <v>9</v>
@@ -53920,7 +53923,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G1985" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="H1985" t="s">
         <v>9</v>
@@ -53946,7 +53949,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1986" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="H1986" t="s">
         <v>9</v>
@@ -53972,7 +53975,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1987" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="H1987" t="s">
         <v>9</v>
@@ -53998,7 +54001,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G1988" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="H1988" t="s">
         <v>9</v>
@@ -54024,7 +54027,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G1989" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="H1989" t="s">
         <v>9</v>
@@ -54050,7 +54053,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G1990" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="H1990" t="s">
         <v>9</v>
@@ -54076,7 +54079,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G1991" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="H1991" t="s">
         <v>9</v>
@@ -54102,7 +54105,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1992" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="H1992" t="s">
         <v>9</v>
@@ -54128,7 +54131,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1993" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="H1993" t="s">
         <v>9</v>
@@ -54154,7 +54157,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1994" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="H1994" t="s">
         <v>9</v>
@@ -54180,7 +54183,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1995" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="H1995" t="s">
         <v>9</v>
@@ -54206,7 +54209,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G1996" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="H1996" t="s">
         <v>9</v>
@@ -54232,7 +54235,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G1997" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="H1997" t="s">
         <v>9</v>
@@ -54258,7 +54261,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1998" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="H1998" t="s">
         <v>9</v>
@@ -54284,7 +54287,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1999" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="H1999" t="s">
         <v>9</v>
@@ -54310,7 +54313,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G2000" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="H2000" t="s">
         <v>9</v>
@@ -54336,7 +54339,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G2001" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="H2001" t="s">
         <v>9</v>
@@ -54362,7 +54365,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G2002" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="H2002" t="s">
         <v>9</v>
@@ -54388,7 +54391,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G2003" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="H2003" t="s">
         <v>9</v>
@@ -54414,7 +54417,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G2004" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="H2004" t="s">
         <v>9</v>
@@ -54440,7 +54443,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G2005" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="H2005" t="s">
         <v>9</v>
@@ -54466,7 +54469,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G2006" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="H2006" t="s">
         <v>9</v>
@@ -54492,7 +54495,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G2007" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="H2007" t="s">
         <v>9</v>
@@ -54518,7 +54521,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G2008" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="H2008" t="s">
         <v>9</v>
@@ -54544,7 +54547,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G2009" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="H2009" t="s">
         <v>9</v>
@@ -54570,7 +54573,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G2010" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="H2010" t="s">
         <v>9</v>
@@ -54596,7 +54599,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G2011" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="H2011" t="s">
         <v>9</v>
@@ -54622,7 +54625,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G2012" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="H2012" t="s">
         <v>9</v>
@@ -54648,7 +54651,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G2013" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="H2013" t="s">
         <v>9</v>
@@ -54674,7 +54677,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2014" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="H2014" t="s">
         <v>9</v>
@@ -54700,7 +54703,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G2015" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="H2015" t="s">
         <v>9</v>
@@ -54726,7 +54729,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G2016" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="H2016" t="s">
         <v>9</v>
@@ -54752,7 +54755,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G2017" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="H2017" t="s">
         <v>9</v>
@@ -54778,7 +54781,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2018" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="H2018" t="s">
         <v>9</v>
@@ -54804,7 +54807,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2019" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="H2019" t="s">
         <v>9</v>
@@ -54830,7 +54833,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G2020" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="H2020" t="s">
         <v>9</v>
@@ -54856,7 +54859,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2021" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="H2021" t="s">
         <v>9</v>
@@ -54882,7 +54885,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G2022" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="H2022" t="s">
         <v>9</v>
@@ -54908,7 +54911,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2023" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="H2023" t="s">
         <v>9</v>
@@ -54934,7 +54937,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2024" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="H2024" t="s">
         <v>9</v>
@@ -54960,7 +54963,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G2025" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="H2025" t="s">
         <v>9</v>
@@ -54986,7 +54989,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G2026" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="H2026" t="s">
         <v>9</v>
@@ -55012,7 +55015,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2027" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="H2027" t="s">
         <v>9</v>
@@ -55038,7 +55041,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2028" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="H2028" t="s">
         <v>9</v>
@@ -55064,7 +55067,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G2029" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="H2029" t="s">
         <v>9</v>
@@ -55090,7 +55093,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2030" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="H2030" t="s">
         <v>9</v>
@@ -55116,7 +55119,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G2031" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="H2031" t="s">
         <v>9</v>
@@ -55142,7 +55145,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G2032" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="H2032" t="s">
         <v>9</v>
@@ -55168,7 +55171,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G2033" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="H2033" t="s">
         <v>9</v>
@@ -55194,7 +55197,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G2034" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="H2034" t="s">
         <v>9</v>
@@ -55220,7 +55223,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G2035" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="H2035" t="s">
         <v>9</v>
@@ -55246,7 +55249,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2036" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="H2036" t="s">
         <v>9</v>
@@ -55272,7 +55275,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G2037" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="H2037" t="s">
         <v>9</v>
@@ -55298,7 +55301,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G2038" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="H2038" t="s">
         <v>9</v>
@@ -55324,7 +55327,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2039" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="H2039" t="s">
         <v>9</v>
@@ -55350,7 +55353,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G2040" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="H2040" t="s">
         <v>9</v>
@@ -55376,7 +55379,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G2041" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="H2041" t="s">
         <v>9</v>
@@ -55402,7 +55405,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G2042" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="H2042" t="s">
         <v>9</v>
@@ -55428,7 +55431,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G2043" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="H2043" t="s">
         <v>9</v>
@@ -55454,7 +55457,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2044" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="H2044" t="s">
         <v>9</v>
@@ -55480,7 +55483,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2045" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="H2045" t="s">
         <v>9</v>
@@ -55506,7 +55509,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2046" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="H2046" t="s">
         <v>9</v>
@@ -55532,7 +55535,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G2047" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="H2047" t="s">
         <v>9</v>
@@ -55558,7 +55561,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2048" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="H2048" t="s">
         <v>9</v>
@@ -55584,7 +55587,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2049" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="H2049" t="s">
         <v>9</v>
@@ -55610,7 +55613,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2050" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="H2050" t="s">
         <v>9</v>
@@ -55636,7 +55639,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G2051" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="H2051" t="s">
         <v>9</v>
@@ -55662,7 +55665,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G2052" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="H2052" t="s">
         <v>9</v>
@@ -55688,7 +55691,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G2053" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="H2053" t="s">
         <v>9</v>
@@ -55714,7 +55717,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2054" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="H2054" t="s">
         <v>9</v>
@@ -55740,7 +55743,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G2055" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="H2055" t="s">
         <v>9</v>
@@ -55766,7 +55769,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2056" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="H2056" t="s">
         <v>9</v>
@@ -55792,7 +55795,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2057" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="H2057" t="s">
         <v>9</v>
@@ -55818,7 +55821,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G2058" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="H2058" t="s">
         <v>9</v>
@@ -55844,7 +55847,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G2059" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="H2059" t="s">
         <v>9</v>
@@ -55870,7 +55873,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2060" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="H2060" t="s">
         <v>9</v>
@@ -55896,7 +55899,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2061" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="H2061" t="s">
         <v>9</v>
@@ -55922,7 +55925,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2062" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="H2062" t="s">
         <v>9</v>
@@ -55948,7 +55951,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G2063" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="H2063" t="s">
         <v>9</v>
@@ -55974,7 +55977,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G2064" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="H2064" t="s">
         <v>9</v>
@@ -56000,7 +56003,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G2065" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="H2065" t="s">
         <v>9</v>
@@ -56026,7 +56029,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G2066" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="H2066" t="s">
         <v>9</v>
@@ -56052,7 +56055,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G2067" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="H2067" t="s">
         <v>9</v>
@@ -56078,7 +56081,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G2068" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="H2068" t="s">
         <v>9</v>
@@ -56104,7 +56107,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G2069" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="H2069" t="s">
         <v>9</v>
@@ -56130,7 +56133,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G2070" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="H2070" t="s">
         <v>9</v>
@@ -56156,7 +56159,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G2071" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="H2071" t="s">
         <v>9</v>
@@ -56182,7 +56185,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G2072" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="H2072" t="s">
         <v>9</v>
@@ -56208,7 +56211,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G2073" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="H2073" t="s">
         <v>9</v>
@@ -56234,7 +56237,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2074" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="H2074" t="s">
         <v>9</v>
@@ -56260,7 +56263,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G2075" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="H2075" t="s">
         <v>9</v>
@@ -56286,7 +56289,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G2076" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="H2076" t="s">
         <v>9</v>
@@ -56312,7 +56315,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G2077" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="H2077" t="s">
         <v>9</v>
@@ -56338,7 +56341,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G2078" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="H2078" t="s">
         <v>9</v>
@@ -56364,7 +56367,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G2079" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="H2079" t="s">
         <v>9</v>
@@ -56390,7 +56393,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G2080" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="H2080" t="s">
         <v>9</v>
@@ -56416,7 +56419,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G2081" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="H2081" t="s">
         <v>9</v>
@@ -56442,7 +56445,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G2082" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="H2082" t="s">
         <v>9</v>
@@ -56468,7 +56471,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G2083" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="H2083" t="s">
         <v>9</v>
@@ -56494,7 +56497,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G2084" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="H2084" t="s">
         <v>9</v>
@@ -56520,7 +56523,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G2085" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="H2085" t="s">
         <v>9</v>
@@ -56546,7 +56549,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G2086" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="H2086" t="s">
         <v>9</v>
@@ -56572,7 +56575,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G2087" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="H2087" t="s">
         <v>9</v>
@@ -56598,7 +56601,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G2088" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="H2088" t="s">
         <v>9</v>
@@ -56624,7 +56627,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2089" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="H2089" t="s">
         <v>9</v>
@@ -56650,7 +56653,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G2090" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="H2090" t="s">
         <v>9</v>
@@ -56676,7 +56679,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2091" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="H2091" t="s">
         <v>9</v>
@@ -56702,7 +56705,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2092" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="H2092" t="s">
         <v>9</v>
@@ -56728,7 +56731,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2093" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="H2093" t="s">
         <v>9</v>
@@ -56754,7 +56757,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G2094" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="H2094" t="s">
         <v>9</v>
@@ -56780,7 +56783,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G2095" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="H2095" t="s">
         <v>9</v>
@@ -56806,7 +56809,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G2096" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="H2096" t="s">
         <v>9</v>
@@ -56832,7 +56835,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G2097" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="H2097" t="s">
         <v>9</v>
@@ -56858,7 +56861,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G2098" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="H2098" t="s">
         <v>9</v>
@@ -56884,7 +56887,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G2099" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="H2099" t="s">
         <v>9</v>
@@ -56910,7 +56913,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G2100" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="H2100" t="s">
         <v>9</v>
@@ -56936,7 +56939,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G2101" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="H2101" t="s">
         <v>9</v>
@@ -56962,7 +56965,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G2102" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="H2102" t="s">
         <v>9</v>
@@ -56988,7 +56991,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G2103" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="H2103" t="s">
         <v>9</v>
@@ -57014,7 +57017,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G2104" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="H2104" t="s">
         <v>9</v>
@@ -57040,7 +57043,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G2105" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="H2105" t="s">
         <v>9</v>
@@ -57066,7 +57069,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G2106" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="H2106" t="s">
         <v>9</v>
@@ -57092,7 +57095,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G2107" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="H2107" t="s">
         <v>9</v>
@@ -57118,7 +57121,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G2108" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="H2108" t="s">
         <v>9</v>
@@ -57144,7 +57147,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G2109" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="H2109" t="s">
         <v>9</v>
@@ -57170,7 +57173,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G2110" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="H2110" t="s">
         <v>9</v>
@@ -57196,7 +57199,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G2111" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="H2111" t="s">
         <v>9</v>
@@ -57222,7 +57225,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G2112" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="H2112" t="s">
         <v>9</v>
@@ -57248,7 +57251,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G2113" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="H2113" t="s">
         <v>9</v>
@@ -57274,7 +57277,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G2114" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="H2114" t="s">
         <v>9</v>
@@ -57300,7 +57303,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G2115" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="H2115" t="s">
         <v>9</v>
@@ -57326,7 +57329,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G2116" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="H2116" t="s">
         <v>9</v>
@@ -57352,7 +57355,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G2117" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="H2117" t="s">
         <v>9</v>
@@ -57378,7 +57381,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G2118" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="H2118" t="s">
         <v>9</v>
@@ -57404,7 +57407,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G2119" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="H2119" t="s">
         <v>9</v>
@@ -57430,7 +57433,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G2120" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="H2120" t="s">
         <v>9</v>
@@ -57456,7 +57459,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G2121" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="H2121" t="s">
         <v>9</v>
@@ -57482,7 +57485,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G2122" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="H2122" t="s">
         <v>9</v>
@@ -57508,7 +57511,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2123" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="H2123" t="s">
         <v>9</v>
@@ -57534,7 +57537,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G2124" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="H2124" t="s">
         <v>9</v>
@@ -57560,7 +57563,7 @@
         <v>3.25</v>
       </c>
       <c r="G2125" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="H2125" t="s">
         <v>9</v>
@@ -57586,7 +57589,7 @@
         <v>3.25</v>
       </c>
       <c r="G2126" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="H2126" t="s">
         <v>9</v>
@@ -57612,7 +57615,7 @@
         <v>3.25</v>
       </c>
       <c r="G2127" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="H2127" t="s">
         <v>9</v>
@@ -57638,7 +57641,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G2128" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="H2128" t="s">
         <v>9</v>
@@ -57664,7 +57667,7 @@
         <v>3.25</v>
       </c>
       <c r="G2129" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="H2129" t="s">
         <v>9</v>
@@ -57690,7 +57693,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G2130" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="H2130" t="s">
         <v>9</v>
@@ -57716,7 +57719,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G2131" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="H2131" t="s">
         <v>9</v>
@@ -57742,7 +57745,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G2132" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="H2132" t="s">
         <v>9</v>
@@ -57768,7 +57771,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G2133" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="H2133" t="s">
         <v>9</v>
@@ -57794,7 +57797,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G2134" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="H2134" t="s">
         <v>9</v>
@@ -57820,7 +57823,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G2135" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="H2135" t="s">
         <v>9</v>
@@ -57846,7 +57849,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G2136" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="H2136" t="s">
         <v>9</v>
@@ -57872,7 +57875,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G2137" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="H2137" t="s">
         <v>9</v>
@@ -57898,7 +57901,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G2138" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="H2138" t="s">
         <v>9</v>
@@ -57924,7 +57927,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G2139" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="H2139" t="s">
         <v>9</v>
@@ -57950,7 +57953,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2140" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="H2140" t="s">
         <v>9</v>
@@ -57976,7 +57979,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G2141" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="H2141" t="s">
         <v>9</v>
@@ -58002,7 +58005,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G2142" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="H2142" t="s">
         <v>9</v>
@@ -58028,7 +58031,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G2143" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="H2143" t="s">
         <v>9</v>
@@ -58054,7 +58057,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G2144" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="H2144" t="s">
         <v>9</v>
@@ -58080,7 +58083,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G2145" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="H2145" t="s">
         <v>9</v>
@@ -58106,7 +58109,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G2146" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="H2146" t="s">
         <v>9</v>
@@ -58132,7 +58135,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G2147" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="H2147" t="s">
         <v>9</v>
@@ -58158,7 +58161,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G2148" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="H2148" t="s">
         <v>9</v>
@@ -58184,7 +58187,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G2149" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="H2149" t="s">
         <v>9</v>
@@ -58210,7 +58213,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G2150" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="H2150" t="s">
         <v>9</v>
@@ -58236,7 +58239,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G2151" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="H2151" t="s">
         <v>9</v>
@@ -58262,7 +58265,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G2152" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="H2152" t="s">
         <v>9</v>
@@ -58288,7 +58291,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G2153" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="H2153" t="s">
         <v>9</v>
@@ -58314,7 +58317,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G2154" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="H2154" t="s">
         <v>9</v>
@@ -58340,7 +58343,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G2155" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="H2155" t="s">
         <v>9</v>
@@ -58366,7 +58369,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G2156" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="H2156" t="s">
         <v>9</v>
@@ -58392,7 +58395,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G2157" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="H2157" t="s">
         <v>9</v>
@@ -58418,7 +58421,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G2158" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="H2158" t="s">
         <v>9</v>
@@ -58444,7 +58447,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G2159" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="H2159" t="s">
         <v>9</v>
@@ -58470,7 +58473,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G2160" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="H2160" t="s">
         <v>9</v>
@@ -58496,7 +58499,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G2161" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="H2161" t="s">
         <v>9</v>
@@ -58522,7 +58525,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G2162" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="H2162" t="s">
         <v>9</v>
@@ -58548,7 +58551,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G2163" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="H2163" t="s">
         <v>9</v>
@@ -58574,7 +58577,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G2164" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="H2164" t="s">
         <v>9</v>
@@ -58600,7 +58603,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G2165" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="H2165" t="s">
         <v>9</v>
@@ -58626,7 +58629,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G2166" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="H2166" t="s">
         <v>9</v>
@@ -58652,7 +58655,7 @@
         <v>3.25</v>
       </c>
       <c r="G2167" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="H2167" t="s">
         <v>9</v>
@@ -58678,7 +58681,7 @@
         <v>3.25</v>
       </c>
       <c r="G2168" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="H2168" t="s">
         <v>9</v>
@@ -58704,7 +58707,7 @@
         <v>3.25</v>
       </c>
       <c r="G2169" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="H2169" t="s">
         <v>9</v>
@@ -58730,7 +58733,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G2170" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="H2170" t="s">
         <v>9</v>
@@ -58756,7 +58759,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G2171" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="H2171" t="s">
         <v>9</v>
@@ -58782,7 +58785,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G2172" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="H2172" t="s">
         <v>9</v>
@@ -58808,7 +58811,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G2173" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="H2173" t="s">
         <v>9</v>
@@ -58834,7 +58837,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G2174" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="H2174" t="s">
         <v>9</v>
@@ -58860,7 +58863,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2175" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="H2175" t="s">
         <v>9</v>
@@ -58886,7 +58889,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2176" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="H2176" t="s">
         <v>9</v>
@@ -58912,7 +58915,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2177" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="H2177" t="s">
         <v>9</v>
@@ -58938,7 +58941,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G2178" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="H2178" t="s">
         <v>9</v>
@@ -58964,7 +58967,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G2179" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="H2179" t="s">
         <v>9</v>
@@ -58990,7 +58993,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G2180" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="H2180" t="s">
         <v>9</v>
@@ -59016,7 +59019,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G2181" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="H2181" t="s">
         <v>9</v>
@@ -59042,7 +59045,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2182" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="H2182" t="s">
         <v>9</v>
@@ -59068,7 +59071,7 @@
         <v>3.25</v>
       </c>
       <c r="G2183" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="H2183" t="s">
         <v>9</v>
@@ -59094,7 +59097,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G2184" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="H2184" t="s">
         <v>9</v>
@@ -59120,7 +59123,7 @@
         <v>3.25</v>
       </c>
       <c r="G2185" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="H2185" t="s">
         <v>9</v>
@@ -59146,7 +59149,7 @@
         <v>3.25</v>
       </c>
       <c r="G2186" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="H2186" t="s">
         <v>9</v>
@@ -59172,7 +59175,7 @@
         <v>3.25</v>
       </c>
       <c r="G2187" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="H2187" t="s">
         <v>9</v>
@@ -59198,7 +59201,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G2188" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="H2188" t="s">
         <v>9</v>
@@ -59224,7 +59227,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G2189" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="H2189" t="s">
         <v>9</v>
@@ -59250,7 +59253,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G2190" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="H2190" t="s">
         <v>9</v>
@@ -59276,7 +59279,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G2191" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="H2191" t="s">
         <v>9</v>
@@ -59302,7 +59305,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G2192" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="H2192" t="s">
         <v>9</v>
@@ -59328,7 +59331,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G2193" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="H2193" t="s">
         <v>9</v>
@@ -59354,7 +59357,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G2194" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="H2194" t="s">
         <v>9</v>
@@ -59380,7 +59383,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G2195" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="H2195" t="s">
         <v>9</v>
@@ -59406,7 +59409,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G2196" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="H2196" t="s">
         <v>9</v>
@@ -59432,7 +59435,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2197" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="H2197" t="s">
         <v>9</v>
@@ -59458,7 +59461,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G2198" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="H2198" t="s">
         <v>9</v>
@@ -59484,7 +59487,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G2199" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="H2199" t="s">
         <v>9</v>
@@ -59510,7 +59513,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G2200" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="H2200" t="s">
         <v>9</v>
@@ -59536,7 +59539,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G2201" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="H2201" t="s">
         <v>9</v>
@@ -59562,7 +59565,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G2202" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="H2202" t="s">
         <v>9</v>
@@ -59588,7 +59591,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G2203" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="H2203" t="s">
         <v>9</v>
@@ -59614,7 +59617,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G2204" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="H2204" t="s">
         <v>9</v>
@@ -59640,7 +59643,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G2205" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="H2205" t="s">
         <v>9</v>
@@ -59666,7 +59669,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2206" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="H2206" t="s">
         <v>9</v>
@@ -59692,7 +59695,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G2207" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="H2207" t="s">
         <v>9</v>
@@ -59718,7 +59721,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G2208" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="H2208" t="s">
         <v>9</v>
@@ -59744,7 +59747,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G2209" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="H2209" t="s">
         <v>9</v>
@@ -59770,7 +59773,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G2210" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="H2210" t="s">
         <v>9</v>
@@ -59796,7 +59799,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G2211" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="H2211" t="s">
         <v>9</v>
@@ -59822,7 +59825,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G2212" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="H2212" t="s">
         <v>9</v>
@@ -59848,7 +59851,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G2213" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="H2213" t="s">
         <v>9</v>
@@ -59874,7 +59877,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G2214" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="H2214" t="s">
         <v>9</v>
@@ -59900,7 +59903,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G2215" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="H2215" t="s">
         <v>9</v>
@@ -59926,7 +59929,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G2216" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="H2216" t="s">
         <v>9</v>
@@ -59952,7 +59955,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G2217" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="H2217" t="s">
         <v>9</v>
@@ -59978,7 +59981,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G2218" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="H2218" t="s">
         <v>9</v>
@@ -60004,7 +60007,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G2219" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="H2219" t="s">
         <v>9</v>
@@ -60030,7 +60033,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G2220" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="H2220" t="s">
         <v>9</v>
@@ -60056,7 +60059,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G2221" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="H2221" t="s">
         <v>9</v>
@@ -60082,7 +60085,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G2222" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="H2222" t="s">
         <v>9</v>
@@ -60108,7 +60111,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G2223" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="H2223" t="s">
         <v>9</v>
@@ -60134,7 +60137,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G2224" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="H2224" t="s">
         <v>9</v>
@@ -60160,7 +60163,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G2225" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="H2225" t="s">
         <v>9</v>
@@ -60186,7 +60189,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G2226" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="H2226" t="s">
         <v>9</v>
@@ -60212,7 +60215,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2227" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="H2227" t="s">
         <v>9</v>
@@ -60238,7 +6024